--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BBDD5C-4B5C-4FC7-A2BD-8ED78C9CD6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B082E31-0CB5-41C5-B655-2B387B612623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="5" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="476">
   <si>
     <t>Description</t>
   </si>
@@ -2404,12 +2404,21 @@
   <si>
     <t>Scen Identifier</t>
   </si>
+  <si>
+    <t>Hotspot type</t>
+  </si>
+  <si>
+    <t>navigation</t>
+  </si>
+  <si>
+    <t>Hotspot Navigation</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2789,7 +2798,43 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="72">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3962,89 +4007,91 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B3BD341F-A9EE-47D0-8C60-8860D1D4E7C2}" name="Table2" displayName="Table2" ref="A1:Z24" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B3BD341F-A9EE-47D0-8C60-8860D1D4E7C2}" name="Table2" displayName="Table2" ref="A1:Z24" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
   <autoFilter ref="A1:Z24" xr:uid="{B3BD341F-A9EE-47D0-8C60-8860D1D4E7C2}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{3F466341-C4E1-4EB6-AED5-B3FAB9FFDB04}" name="FloorGroupName" dataDxfId="67"/>
-    <tableColumn id="15" xr3:uid="{95822792-7ABB-423C-82E9-6D0F0DB26332}" name="Section2" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{F5DD3373-E684-418A-9C83-7C1DAF3E703C}" name="SceneID" dataDxfId="65"/>
-    <tableColumn id="16" xr3:uid="{C2E35991-5AAE-4454-B112-E210FA45B5B1}" name="Scene Order" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{1B214639-BDF9-4E07-8399-162C51178468}" name="SceneDisplayName" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{5C39FDEC-5B6B-4B37-A3D9-2FF0E84DB986}" name="PanoramaURL" dataDxfId="62" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{65443BFD-E63B-46ED-9BF9-60D1AEFBE995}" name="LogoURL" dataDxfId="61" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{479ED09E-25DD-46EC-B69E-1861960DEAC2}" name="Background music URL" dataDxfId="60" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{57935DA2-FBD2-4844-9037-7137E42964CE}" name="Background music Active" dataDxfId="59"/>
-    <tableColumn id="17" xr3:uid="{C4D373A5-CE54-491B-9807-1166BCDEB305}" name="Background Voice Over URL" dataDxfId="58" dataCellStyle="Hyperlink"/>
-    <tableColumn id="19" xr3:uid="{6234DADD-60C1-4FBC-8721-B0C377137173}" name="VC Actor Avatar URL" dataDxfId="57" dataCellStyle="Hyperlink"/>
-    <tableColumn id="20" xr3:uid="{F0BFA0EF-DF4E-4896-A5FE-58501F313D77}" name="VC Actor image BG Color" dataDxfId="56" dataCellStyle="Hyperlink"/>
-    <tableColumn id="18" xr3:uid="{F78E9396-7CBD-4F84-9A86-30BE5F251A4F}" name="Background Voice Over Active" dataDxfId="55" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{9659F453-2FDD-4F12-8239-DD98421E212B}" name="InitialPitch" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{CE8A6BA7-78A8-4B32-A5C9-820E789064BA}" name="InitialYaw" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{5EF27361-EA21-49B6-B21B-8017A9DE476E}" name="InitialZoom" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{F89939D0-37DB-4307-92F3-5C4A93A00D1C}" name="AutoRotate" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{841A2892-EB40-41E4-970A-069A5F80AE6F}" name="NorthOffset" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{7990DFCD-7C68-4753-865B-59877205AB47}" name="SceneID Active" dataDxfId="49"/>
-    <tableColumn id="21" xr3:uid="{A8F84F3B-00B3-4D3C-9D9A-1341A9EFEE4D}" name="Hotspot ID" dataDxfId="48"/>
-    <tableColumn id="22" xr3:uid="{D4B98C57-A117-462D-AE9B-DEC916B1362B}" name="Hotspot Active" dataDxfId="47"/>
-    <tableColumn id="23" xr3:uid="{81D4978B-66B3-415D-8A0B-3C39AEABC8F4}" name="Floor Map" dataDxfId="46"/>
-    <tableColumn id="26" xr3:uid="{9B34F8E8-0E7B-400B-82B0-9AB62121F087}" name="Floor map Details" dataDxfId="45"/>
-    <tableColumn id="24" xr3:uid="{9B53D36C-2C6E-4874-90BE-0AE384CE5D57}" name="Floor Map Active" dataDxfId="44"/>
-    <tableColumn id="25" xr3:uid="{35D08936-E73F-4BB6-8277-979FFFDB890C}" name="Get Pitch/Yaw Data" dataDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{73FDCD44-2E0B-408D-8C8B-526CF8AD1030}" name="Scen Identifier" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{3F466341-C4E1-4EB6-AED5-B3FAB9FFDB04}" name="FloorGroupName" dataDxfId="69"/>
+    <tableColumn id="15" xr3:uid="{95822792-7ABB-423C-82E9-6D0F0DB26332}" name="Section2" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{F5DD3373-E684-418A-9C83-7C1DAF3E703C}" name="SceneID" dataDxfId="67"/>
+    <tableColumn id="16" xr3:uid="{C2E35991-5AAE-4454-B112-E210FA45B5B1}" name="Scene Order" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{1B214639-BDF9-4E07-8399-162C51178468}" name="SceneDisplayName" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{5C39FDEC-5B6B-4B37-A3D9-2FF0E84DB986}" name="PanoramaURL" dataDxfId="64" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{65443BFD-E63B-46ED-9BF9-60D1AEFBE995}" name="LogoURL" dataDxfId="63" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{479ED09E-25DD-46EC-B69E-1861960DEAC2}" name="Background music URL" dataDxfId="62" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{57935DA2-FBD2-4844-9037-7137E42964CE}" name="Background music Active" dataDxfId="61"/>
+    <tableColumn id="17" xr3:uid="{C4D373A5-CE54-491B-9807-1166BCDEB305}" name="Background Voice Over URL" dataDxfId="60" dataCellStyle="Hyperlink"/>
+    <tableColumn id="19" xr3:uid="{6234DADD-60C1-4FBC-8721-B0C377137173}" name="VC Actor Avatar URL" dataDxfId="59" dataCellStyle="Hyperlink"/>
+    <tableColumn id="20" xr3:uid="{F0BFA0EF-DF4E-4896-A5FE-58501F313D77}" name="VC Actor image BG Color" dataDxfId="58" dataCellStyle="Hyperlink"/>
+    <tableColumn id="18" xr3:uid="{F78E9396-7CBD-4F84-9A86-30BE5F251A4F}" name="Background Voice Over Active" dataDxfId="57" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{9659F453-2FDD-4F12-8239-DD98421E212B}" name="InitialPitch" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{CE8A6BA7-78A8-4B32-A5C9-820E789064BA}" name="InitialYaw" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{5EF27361-EA21-49B6-B21B-8017A9DE476E}" name="InitialZoom" dataDxfId="54"/>
+    <tableColumn id="11" xr3:uid="{F89939D0-37DB-4307-92F3-5C4A93A00D1C}" name="AutoRotate" dataDxfId="53"/>
+    <tableColumn id="12" xr3:uid="{841A2892-EB40-41E4-970A-069A5F80AE6F}" name="NorthOffset" dataDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{7990DFCD-7C68-4753-865B-59877205AB47}" name="SceneID Active" dataDxfId="51"/>
+    <tableColumn id="21" xr3:uid="{A8F84F3B-00B3-4D3C-9D9A-1341A9EFEE4D}" name="Hotspot ID" dataDxfId="50"/>
+    <tableColumn id="22" xr3:uid="{D4B98C57-A117-462D-AE9B-DEC916B1362B}" name="Hotspot Active" dataDxfId="49"/>
+    <tableColumn id="23" xr3:uid="{81D4978B-66B3-415D-8A0B-3C39AEABC8F4}" name="Floor Map" dataDxfId="48"/>
+    <tableColumn id="26" xr3:uid="{9B34F8E8-0E7B-400B-82B0-9AB62121F087}" name="Floor map Details" dataDxfId="47"/>
+    <tableColumn id="24" xr3:uid="{9B53D36C-2C6E-4874-90BE-0AE384CE5D57}" name="Floor Map Active" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{35D08936-E73F-4BB6-8277-979FFFDB890C}" name="Get Pitch/Yaw Data" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{73FDCD44-2E0B-408D-8C8B-526CF8AD1030}" name="Scen Identifier" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C481020-1612-4FDF-9B0C-75A16E8BD6EE}" name="Table1" displayName="Table1" ref="A1:T162" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
-  <autoFilter ref="A1:T162" xr:uid="{1C481020-1612-4FDF-9B0C-75A16E8BD6EE}"/>
-  <tableColumns count="20">
-    <tableColumn id="15" xr3:uid="{6C92FDC8-7FD4-4ED1-84DE-C73B1AEF49AA}" name="FloorID" dataDxfId="39"/>
-    <tableColumn id="20" xr3:uid="{D4590493-B9FB-4809-9262-EDF4D7F21ABC}" name="Scene Order" dataDxfId="38"/>
-    <tableColumn id="1" xr3:uid="{8DAC3286-642C-4DB0-A8B8-5C7BF99FB11F}" name="SceneID" dataDxfId="37"/>
-    <tableColumn id="19" xr3:uid="{79CDA865-39EA-4125-85E4-F3D78AC4893A}" name="Hotspot ID" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{4BDAA051-81D1-400A-A39C-7D867ECB0341}" name="Hotspot Name" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{F981A75D-66D8-4E38-82C9-6DCD2B17FC3E}" name="Type" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{787CBE39-1923-41F6-9372-CA2D56C6E632}" name="TargetSceneID" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{878E0985-EA91-45B5-B984-8D637B8FAC1A}" name="StyleID/CustomCSS" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{5750A58C-6161-4401-AC72-9E158AEE5857}" name="Pitch" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{BE566E3E-5C22-4617-9723-BF12A43249DE}" name="Yaw" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{5A307C93-AF79-4FC7-8CD0-D327558EE7A8}" name="Rotation" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{CDA04002-4AE2-42E0-BE80-D1092B841D6F}" name="Custom Hotspot URL" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{B760F4E6-236A-47E6-B68A-77D0E77DEBE8}" name="Hotspot HoverImage URL" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{54ECD990-86C2-40C1-B48B-2D7A81FF92B9}" name="Title" dataDxfId="26"/>
-    <tableColumn id="12" xr3:uid="{945E3504-CBC4-4B71-87A6-409E0A7C093F}" name="Description" dataDxfId="25"/>
-    <tableColumn id="17" xr3:uid="{3055829F-DDE9-4492-B64F-EA9B27D86F0D}" name="SR Currancy Symbol image URL" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{37499370-9458-4DA7-9E1E-492AC195DCB2}" name="Price" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{51AF3A7A-9E37-4EC3-95E2-04EA97CB0A3F}" name="Avatar Image URL" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{62D296DE-BD87-415D-A7A9-7B26ADBEBF6D}" name="Voice over" dataDxfId="21"/>
-    <tableColumn id="18" xr3:uid="{48873D82-692C-4357-B503-4E9A267EC815}" name="Hotspot Hover Active" dataDxfId="20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C481020-1612-4FDF-9B0C-75A16E8BD6EE}" name="Table1" displayName="Table1" ref="A1:V162" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+  <autoFilter ref="A1:V162" xr:uid="{1C481020-1612-4FDF-9B0C-75A16E8BD6EE}"/>
+  <tableColumns count="22">
+    <tableColumn id="15" xr3:uid="{6C92FDC8-7FD4-4ED1-84DE-C73B1AEF49AA}" name="FloorID" dataDxfId="41"/>
+    <tableColumn id="20" xr3:uid="{D4590493-B9FB-4809-9262-EDF4D7F21ABC}" name="Scene Order" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{8DAC3286-642C-4DB0-A8B8-5C7BF99FB11F}" name="SceneID" dataDxfId="39"/>
+    <tableColumn id="19" xr3:uid="{79CDA865-39EA-4125-85E4-F3D78AC4893A}" name="Hotspot ID" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{4BDAA051-81D1-400A-A39C-7D867ECB0341}" name="Hotspot Name" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{F981A75D-66D8-4E38-82C9-6DCD2B17FC3E}" name="Type" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{787CBE39-1923-41F6-9372-CA2D56C6E632}" name="TargetSceneID" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{878E0985-EA91-45B5-B984-8D637B8FAC1A}" name="StyleID/CustomCSS" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{5750A58C-6161-4401-AC72-9E158AEE5857}" name="Pitch" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{BE566E3E-5C22-4617-9723-BF12A43249DE}" name="Yaw" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{5A307C93-AF79-4FC7-8CD0-D327558EE7A8}" name="Rotation" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{CDA04002-4AE2-42E0-BE80-D1092B841D6F}" name="Custom Hotspot URL" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{B760F4E6-236A-47E6-B68A-77D0E77DEBE8}" name="Hotspot HoverImage URL" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{54ECD990-86C2-40C1-B48B-2D7A81FF92B9}" name="Title" dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{945E3504-CBC4-4B71-87A6-409E0A7C093F}" name="Description" dataDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{3055829F-DDE9-4492-B64F-EA9B27D86F0D}" name="SR Currancy Symbol image URL" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{37499370-9458-4DA7-9E1E-492AC195DCB2}" name="Price" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{51AF3A7A-9E37-4EC3-95E2-04EA97CB0A3F}" name="Avatar Image URL" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{62D296DE-BD87-415D-A7A9-7B26ADBEBF6D}" name="Voice over" dataDxfId="23"/>
+    <tableColumn id="18" xr3:uid="{48873D82-692C-4357-B503-4E9A267EC815}" name="Hotspot Hover Active" dataDxfId="22"/>
+    <tableColumn id="21" xr3:uid="{54CB3C40-C39A-44B4-A549-CF60CCCE8ACB}" name="Hotspot type" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{72414B5E-A62A-4803-BE10-64DE72621FD3}" name="Hotspot Navigation" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:E3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="15" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="17" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:B4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4257,7 +4304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4369BCEB-0E17-4F52-9822-7178FED3746E}">
   <dimension ref="A1:Z24"/>
-  <sheetFormatPr defaultRowHeight="12.3"/>
+  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
     <col min="2" max="2" width="13.94140625" customWidth="1"/>
@@ -4286,7 +4333,7 @@
     <col min="28" max="28" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="42.6" customHeight="1">
+    <row r="1" spans="1:26" ht="42.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>98</v>
       </c>
@@ -4366,7 +4413,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="2" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
         <v>10</v>
       </c>
@@ -4446,7 +4493,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="3" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
@@ -4527,7 +4574,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="4" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
         <v>10</v>
       </c>
@@ -4605,7 +4652,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="5" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -4683,7 +4730,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="6" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
@@ -4761,7 +4808,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="7" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>10</v>
       </c>
@@ -4839,7 +4886,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="8" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
         <v>10</v>
       </c>
@@ -4919,7 +4966,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="9" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -4999,7 +5046,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="10" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
@@ -5079,7 +5126,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="11" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
         <v>10</v>
       </c>
@@ -5157,7 +5204,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="12" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>10</v>
       </c>
@@ -5237,7 +5284,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="13" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
         <v>10</v>
       </c>
@@ -5317,7 +5364,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="14" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>10</v>
       </c>
@@ -5397,7 +5444,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="15" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
         <v>10</v>
       </c>
@@ -5477,7 +5524,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="16" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
         <v>11</v>
       </c>
@@ -5557,7 +5604,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="17" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
@@ -5637,7 +5684,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="18" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="13" t="s">
         <v>11</v>
       </c>
@@ -5717,7 +5764,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="19" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
         <v>11</v>
       </c>
@@ -5797,7 +5844,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="20" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
@@ -5877,7 +5924,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="21" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
         <v>11</v>
       </c>
@@ -5957,7 +6004,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="22" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
         <v>11</v>
       </c>
@@ -6037,7 +6084,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="20.399999999999999" customHeight="1">
+    <row r="23" spans="1:26" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
         <v>11</v>
       </c>
@@ -6117,7 +6164,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="36.9">
+    <row r="24" spans="1:26" ht="37.799999999999997" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>11</v>
       </c>
@@ -6200,7 +6247,7 @@
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{CD437926-0051-42E8-974D-E38762304209}"/>
@@ -6234,8 +6281,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{455B4130-C490-4ADF-9505-F9BCEDE9AD6E}">
-  <dimension ref="A1:T201"/>
-  <sheetFormatPr defaultRowHeight="12.3"/>
+  <dimension ref="A1:V201"/>
+  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="10.77734375" customWidth="1"/>
     <col min="3" max="3" width="9.88671875" customWidth="1"/>
@@ -6251,14 +6298,14 @@
     <col min="17" max="17" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.5" customWidth="1"/>
     <col min="19" max="19" width="57.27734375" customWidth="1"/>
-    <col min="20" max="20" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.109375" customWidth="1"/>
     <col min="23" max="23" width="29.5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="29.5" customWidth="1"/>
     <col min="25" max="25" width="26.5546875" customWidth="1"/>
     <col min="28" max="28" width="19.609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="8" customFormat="1" ht="27.6">
+    <row r="1" spans="1:22" s="8" customFormat="1" ht="37.799999999999997" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
@@ -6319,8 +6366,14 @@
       <c r="T1" s="7" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U1" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>31</v>
       </c>
@@ -6365,8 +6418,14 @@
       <c r="T2" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
@@ -6411,8 +6470,14 @@
       <c r="T3" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="U3" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>31</v>
       </c>
@@ -6471,8 +6536,12 @@
       <c r="T4" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="13"/>
+    </row>
+    <row r="5" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>31</v>
       </c>
@@ -6528,11 +6597,15 @@
       <c r="S5" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="T5" s="13" t="b">
+      <c r="T5" s="47" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V5" s="13"/>
+    </row>
+    <row r="6" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
@@ -6589,8 +6662,12 @@
       <c r="T6" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" s="13"/>
+    </row>
+    <row r="7" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>31</v>
       </c>
@@ -6647,8 +6724,12 @@
       <c r="T7" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V7" s="13"/>
+    </row>
+    <row r="8" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>31</v>
       </c>
@@ -6707,8 +6788,12 @@
       <c r="T8" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V8" s="13"/>
+    </row>
+    <row r="9" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>31</v>
       </c>
@@ -6753,8 +6838,14 @@
       <c r="T9" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="U9" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>31</v>
       </c>
@@ -6799,8 +6890,14 @@
       <c r="T10" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="U10" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V10" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>31</v>
       </c>
@@ -6859,8 +6956,12 @@
       <c r="T11" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V11" s="13"/>
+    </row>
+    <row r="12" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>31</v>
       </c>
@@ -6919,8 +7020,12 @@
       <c r="T12" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V12" s="13"/>
+    </row>
+    <row r="13" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>31</v>
       </c>
@@ -6977,8 +7082,12 @@
       <c r="T13" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V13" s="13"/>
+    </row>
+    <row r="14" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>31</v>
       </c>
@@ -7035,8 +7144,12 @@
       <c r="T14" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V14" s="13"/>
+    </row>
+    <row r="15" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>31</v>
       </c>
@@ -7093,8 +7206,12 @@
       <c r="T15" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V15" s="13"/>
+    </row>
+    <row r="16" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>31</v>
       </c>
@@ -7139,8 +7256,14 @@
       <c r="T16" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="U16" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V16" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>31</v>
       </c>
@@ -7185,8 +7308,14 @@
       <c r="T17" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="U17" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V17" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>31</v>
       </c>
@@ -7241,8 +7370,12 @@
       <c r="T18" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="U18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V18" s="13"/>
+    </row>
+    <row r="19" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>31</v>
       </c>
@@ -7297,8 +7430,12 @@
       <c r="T19" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="U19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V19" s="13"/>
+    </row>
+    <row r="20" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>31</v>
       </c>
@@ -7353,8 +7490,12 @@
       <c r="T20" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="U20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V20" s="13"/>
+    </row>
+    <row r="21" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>31</v>
       </c>
@@ -7409,8 +7550,12 @@
       <c r="T21" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="U21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V21" s="13"/>
+    </row>
+    <row r="22" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>31</v>
       </c>
@@ -7467,8 +7612,12 @@
       <c r="T22" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U22" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V22" s="13"/>
+    </row>
+    <row r="23" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>31</v>
       </c>
@@ -7513,8 +7662,14 @@
       <c r="T23" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="U23" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V23" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
@@ -7559,8 +7714,14 @@
       <c r="T24" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="U24" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V24" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
         <v>31</v>
       </c>
@@ -7617,8 +7778,12 @@
       <c r="T25" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="U25" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V25" s="13"/>
+    </row>
+    <row r="26" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A26" s="13" t="s">
         <v>31</v>
       </c>
@@ -7675,8 +7840,12 @@
       <c r="T26" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="U26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V26" s="13"/>
+    </row>
+    <row r="27" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A27" s="13" t="s">
         <v>31</v>
       </c>
@@ -7731,8 +7900,12 @@
       <c r="T27" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
+      <c r="U27" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V27" s="13"/>
+    </row>
+    <row r="28" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A28" s="13" t="s">
         <v>31</v>
       </c>
@@ -7789,8 +7962,12 @@
       <c r="T28" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
+      <c r="U28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V28" s="13"/>
+    </row>
+    <row r="29" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A29" s="13" t="s">
         <v>31</v>
       </c>
@@ -7849,8 +8026,12 @@
       <c r="T29" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V29" s="13"/>
+    </row>
+    <row r="30" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="13" t="s">
         <v>31</v>
       </c>
@@ -7895,8 +8076,14 @@
       <c r="T30" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="U30" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V30" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A31" s="13" t="s">
         <v>31</v>
       </c>
@@ -7941,8 +8128,14 @@
       <c r="T31" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="U31" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V31" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A32" s="13" t="s">
         <v>31</v>
       </c>
@@ -8001,8 +8194,12 @@
       <c r="T32" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
+      <c r="U32" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V32" s="13"/>
+    </row>
+    <row r="33" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A33" s="13" t="s">
         <v>31</v>
       </c>
@@ -8061,8 +8258,12 @@
       <c r="T33" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="U33" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V33" s="13"/>
+    </row>
+    <row r="34" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A34" s="13" t="s">
         <v>31</v>
       </c>
@@ -8119,8 +8320,12 @@
       <c r="T34" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
+      <c r="U34" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V34" s="13"/>
+    </row>
+    <row r="35" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A35" s="13" t="s">
         <v>31</v>
       </c>
@@ -8177,8 +8382,12 @@
       <c r="T35" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
+      <c r="U35" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V35" s="13"/>
+    </row>
+    <row r="36" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A36" s="13" t="s">
         <v>31</v>
       </c>
@@ -8235,8 +8444,12 @@
       <c r="T36" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U36" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V36" s="13"/>
+    </row>
+    <row r="37" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="13" t="s">
         <v>31</v>
       </c>
@@ -8281,8 +8494,14 @@
       <c r="T37" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:20">
+      <c r="U37" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V37" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A38" s="13" t="s">
         <v>31</v>
       </c>
@@ -8327,8 +8546,14 @@
       <c r="T38" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:20">
+      <c r="U38" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V38" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A39" s="13" t="s">
         <v>31</v>
       </c>
@@ -8385,8 +8610,12 @@
       <c r="T39" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:20">
+      <c r="U39" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V39" s="13"/>
+    </row>
+    <row r="40" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A40" s="13" t="s">
         <v>31</v>
       </c>
@@ -8443,8 +8672,12 @@
       <c r="T40" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="U40" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V40" s="13"/>
+    </row>
+    <row r="41" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A41" s="13" t="s">
         <v>31</v>
       </c>
@@ -8501,8 +8734,12 @@
       <c r="T41" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:20">
+      <c r="U41" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V41" s="13"/>
+    </row>
+    <row r="42" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A42" s="13" t="s">
         <v>31</v>
       </c>
@@ -8559,8 +8796,12 @@
       <c r="T42" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:20">
+      <c r="U42" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V42" s="13"/>
+    </row>
+    <row r="43" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A43" s="13" t="s">
         <v>31</v>
       </c>
@@ -8617,8 +8858,12 @@
       <c r="T43" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U43" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V43" s="13"/>
+    </row>
+    <row r="44" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="13" t="s">
         <v>31</v>
       </c>
@@ -8663,8 +8908,14 @@
       <c r="T44" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:20">
+      <c r="U44" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V44" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A45" s="13" t="s">
         <v>31</v>
       </c>
@@ -8709,8 +8960,14 @@
       <c r="T45" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:20">
+      <c r="U45" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V45" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -8765,8 +9022,12 @@
       <c r="T46" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:20">
+      <c r="U46" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V46" s="13"/>
+    </row>
+    <row r="47" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A47" s="13" t="s">
         <v>31</v>
       </c>
@@ -8821,8 +9082,12 @@
       <c r="T47" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:20">
+      <c r="U47" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V47" s="13"/>
+    </row>
+    <row r="48" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A48" s="13" t="s">
         <v>31</v>
       </c>
@@ -8877,8 +9142,12 @@
       <c r="T48" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:20">
+      <c r="U48" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V48" s="13"/>
+    </row>
+    <row r="49" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A49" s="13" t="s">
         <v>31</v>
       </c>
@@ -8933,8 +9202,12 @@
       <c r="T49" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:20">
+      <c r="U49" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V49" s="13"/>
+    </row>
+    <row r="50" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A50" s="13" t="s">
         <v>31</v>
       </c>
@@ -8989,8 +9262,12 @@
       <c r="T50" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U50" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V50" s="13"/>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="13" t="s">
         <v>31</v>
       </c>
@@ -9035,8 +9312,14 @@
       <c r="T51" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="U51" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V51" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A52" s="13" t="s">
         <v>31</v>
       </c>
@@ -9081,8 +9364,14 @@
       <c r="T52" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="U52" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V52" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A53" s="13" t="s">
         <v>31</v>
       </c>
@@ -9139,8 +9428,12 @@
       <c r="T53" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="U53" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V53" s="13"/>
+    </row>
+    <row r="54" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A54" s="13" t="s">
         <v>31</v>
       </c>
@@ -9197,8 +9490,12 @@
       <c r="T54" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:20">
+      <c r="U54" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V54" s="13"/>
+    </row>
+    <row r="55" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A55" s="13" t="s">
         <v>31</v>
       </c>
@@ -9253,8 +9550,12 @@
       <c r="T55" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:20">
+      <c r="U55" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V55" s="13"/>
+    </row>
+    <row r="56" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A56" s="13" t="s">
         <v>31</v>
       </c>
@@ -9309,8 +9610,12 @@
       <c r="T56" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:20">
+      <c r="U56" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V56" s="13"/>
+    </row>
+    <row r="57" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A57" s="13" t="s">
         <v>31</v>
       </c>
@@ -9367,8 +9672,12 @@
       <c r="T57" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U57" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V57" s="13"/>
+    </row>
+    <row r="58" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="13" t="s">
         <v>31</v>
       </c>
@@ -9413,8 +9722,14 @@
       <c r="T58" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="U58" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V58" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A59" s="13" t="s">
         <v>31</v>
       </c>
@@ -9459,8 +9774,14 @@
       <c r="T59" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:20">
+      <c r="U59" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V59" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A60" s="13" t="s">
         <v>31</v>
       </c>
@@ -9517,8 +9838,12 @@
       <c r="T60" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:20">
+      <c r="U60" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V60" s="13"/>
+    </row>
+    <row r="61" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A61" s="13" t="s">
         <v>31</v>
       </c>
@@ -9575,8 +9900,12 @@
       <c r="T61" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:20">
+      <c r="U61" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V61" s="13"/>
+    </row>
+    <row r="62" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A62" s="13" t="s">
         <v>31</v>
       </c>
@@ -9631,8 +9960,12 @@
       <c r="T62" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:20">
+      <c r="U62" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V62" s="13"/>
+    </row>
+    <row r="63" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A63" s="13" t="s">
         <v>31</v>
       </c>
@@ -9687,8 +10020,12 @@
       <c r="T63" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="U63" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V63" s="13"/>
+    </row>
+    <row r="64" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A64" s="13" t="s">
         <v>31</v>
       </c>
@@ -9743,8 +10080,12 @@
       <c r="T64" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U64" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V64" s="13"/>
+    </row>
+    <row r="65" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="13" t="s">
         <v>31</v>
       </c>
@@ -9789,8 +10130,14 @@
       <c r="T65" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="U65" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V65" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A66" s="13" t="s">
         <v>31</v>
       </c>
@@ -9835,8 +10182,14 @@
       <c r="T66" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:20">
+      <c r="U66" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V66" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A67" s="13" t="s">
         <v>31</v>
       </c>
@@ -9891,8 +10244,12 @@
       <c r="T67" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:20">
+      <c r="U67" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V67" s="13"/>
+    </row>
+    <row r="68" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A68" s="13" t="s">
         <v>31</v>
       </c>
@@ -9947,8 +10304,12 @@
       <c r="T68" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:20">
+      <c r="U68" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V68" s="13"/>
+    </row>
+    <row r="69" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A69" s="13" t="s">
         <v>31</v>
       </c>
@@ -10003,8 +10364,12 @@
       <c r="T69" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:20">
+      <c r="U69" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V69" s="13"/>
+    </row>
+    <row r="70" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A70" s="13" t="s">
         <v>31</v>
       </c>
@@ -10059,8 +10424,12 @@
       <c r="T70" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:20">
+      <c r="U70" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V70" s="13"/>
+    </row>
+    <row r="71" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A71" s="13" t="s">
         <v>31</v>
       </c>
@@ -10115,8 +10484,12 @@
       <c r="T71" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U71" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V71" s="13"/>
+    </row>
+    <row r="72" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="13" t="s">
         <v>31</v>
       </c>
@@ -10161,8 +10534,14 @@
       <c r="T72" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:20">
+      <c r="U72" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V72" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A73" s="13" t="s">
         <v>31</v>
       </c>
@@ -10207,8 +10586,14 @@
       <c r="T73" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:20">
+      <c r="U73" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V73" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A74" s="13" t="s">
         <v>31</v>
       </c>
@@ -10263,8 +10648,12 @@
       <c r="T74" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:20">
+      <c r="U74" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V74" s="13"/>
+    </row>
+    <row r="75" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A75" s="13" t="s">
         <v>31</v>
       </c>
@@ -10319,8 +10708,12 @@
       <c r="T75" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:20">
+      <c r="U75" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V75" s="13"/>
+    </row>
+    <row r="76" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A76" s="13" t="s">
         <v>31</v>
       </c>
@@ -10375,8 +10768,12 @@
       <c r="T76" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:20">
+      <c r="U76" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V76" s="13"/>
+    </row>
+    <row r="77" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A77" s="13" t="s">
         <v>31</v>
       </c>
@@ -10431,8 +10828,12 @@
       <c r="T77" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:20">
+      <c r="U77" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V77" s="13"/>
+    </row>
+    <row r="78" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A78" s="13" t="s">
         <v>31</v>
       </c>
@@ -10487,8 +10888,12 @@
       <c r="T78" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U78" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V78" s="13"/>
+    </row>
+    <row r="79" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="13" t="s">
         <v>31</v>
       </c>
@@ -10533,8 +10938,14 @@
       <c r="T79" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:20">
+      <c r="U79" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V79" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A80" s="13" t="s">
         <v>31</v>
       </c>
@@ -10579,8 +10990,14 @@
       <c r="T80" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:20">
+      <c r="U80" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V80" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A81" s="13" t="s">
         <v>31</v>
       </c>
@@ -10637,8 +11054,12 @@
       <c r="T81" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:20">
+      <c r="U81" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V81" s="13"/>
+    </row>
+    <row r="82" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A82" s="13" t="s">
         <v>31</v>
       </c>
@@ -10695,8 +11116,12 @@
       <c r="T82" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:20">
+      <c r="U82" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V82" s="13"/>
+    </row>
+    <row r="83" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A83" s="13" t="s">
         <v>31</v>
       </c>
@@ -10751,8 +11176,12 @@
       <c r="T83" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:20">
+      <c r="U83" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V83" s="13"/>
+    </row>
+    <row r="84" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A84" s="13" t="s">
         <v>31</v>
       </c>
@@ -10807,8 +11236,12 @@
       <c r="T84" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:20">
+      <c r="U84" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V84" s="13"/>
+    </row>
+    <row r="85" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A85" s="13" t="s">
         <v>31</v>
       </c>
@@ -10865,8 +11298,12 @@
       <c r="T85" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U85" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V85" s="13"/>
+    </row>
+    <row r="86" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="13" t="s">
         <v>31</v>
       </c>
@@ -10911,8 +11348,14 @@
       <c r="T86" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:20">
+      <c r="U86" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V86" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A87" s="13" t="s">
         <v>31</v>
       </c>
@@ -10957,8 +11400,14 @@
       <c r="T87" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:20">
+      <c r="U87" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V87" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A88" s="13" t="s">
         <v>31</v>
       </c>
@@ -11015,8 +11464,12 @@
       <c r="T88" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:20">
+      <c r="U88" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V88" s="13"/>
+    </row>
+    <row r="89" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A89" s="13" t="s">
         <v>31</v>
       </c>
@@ -11073,8 +11526,12 @@
       <c r="T89" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:20">
+      <c r="U89" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V89" s="13"/>
+    </row>
+    <row r="90" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A90" s="13" t="s">
         <v>31</v>
       </c>
@@ -11129,8 +11586,12 @@
       <c r="T90" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:20">
+      <c r="U90" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V90" s="13"/>
+    </row>
+    <row r="91" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A91" s="13" t="s">
         <v>31</v>
       </c>
@@ -11185,8 +11646,12 @@
       <c r="T91" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:20">
+      <c r="U91" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V91" s="13"/>
+    </row>
+    <row r="92" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A92" s="13" t="s">
         <v>31</v>
       </c>
@@ -11241,8 +11706,12 @@
       <c r="T92" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U92" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V92" s="13"/>
+    </row>
+    <row r="93" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="13" t="s">
         <v>31</v>
       </c>
@@ -11287,8 +11756,14 @@
       <c r="T93" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:20">
+      <c r="U93" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V93" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A94" s="13" t="s">
         <v>31</v>
       </c>
@@ -11333,8 +11808,14 @@
       <c r="T94" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:20">
+      <c r="U94" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V94" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A95" s="13" t="s">
         <v>31</v>
       </c>
@@ -11389,8 +11870,12 @@
       <c r="T95" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:20">
+      <c r="U95" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V95" s="13"/>
+    </row>
+    <row r="96" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A96" s="13" t="s">
         <v>31</v>
       </c>
@@ -11445,8 +11930,12 @@
       <c r="T96" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:20">
+      <c r="U96" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V96" s="13"/>
+    </row>
+    <row r="97" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A97" s="13" t="s">
         <v>31</v>
       </c>
@@ -11501,8 +11990,12 @@
       <c r="T97" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:20">
+      <c r="U97" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V97" s="13"/>
+    </row>
+    <row r="98" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A98" s="13" t="s">
         <v>31</v>
       </c>
@@ -11557,8 +12050,12 @@
       <c r="T98" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:20">
+      <c r="U98" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V98" s="13"/>
+    </row>
+    <row r="99" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A99" s="13" t="s">
         <v>31</v>
       </c>
@@ -11613,8 +12110,12 @@
       <c r="T99" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U99" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V99" s="13"/>
+    </row>
+    <row r="100" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="13" t="s">
         <v>33</v>
       </c>
@@ -11659,8 +12160,14 @@
       <c r="T100" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:20">
+      <c r="U100" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V100" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A101" s="13" t="s">
         <v>33</v>
       </c>
@@ -11705,8 +12212,14 @@
       <c r="T101" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:20">
+      <c r="U101" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V101" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A102" s="13" t="s">
         <v>33</v>
       </c>
@@ -11763,8 +12276,12 @@
       <c r="T102" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:20">
+      <c r="U102" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V102" s="13"/>
+    </row>
+    <row r="103" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A103" s="13" t="s">
         <v>33</v>
       </c>
@@ -11821,8 +12338,12 @@
       <c r="T103" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:20">
+      <c r="U103" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V103" s="13"/>
+    </row>
+    <row r="104" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A104" s="13" t="s">
         <v>33</v>
       </c>
@@ -11877,8 +12398,12 @@
       <c r="T104" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:20">
+      <c r="U104" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V104" s="13"/>
+    </row>
+    <row r="105" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A105" s="13" t="s">
         <v>33</v>
       </c>
@@ -11933,8 +12458,12 @@
       <c r="T105" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:20">
+      <c r="U105" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V105" s="13"/>
+    </row>
+    <row r="106" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A106" s="13" t="s">
         <v>33</v>
       </c>
@@ -11991,8 +12520,12 @@
       <c r="T106" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U106" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V106" s="13"/>
+    </row>
+    <row r="107" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="13" t="s">
         <v>33</v>
       </c>
@@ -12037,8 +12570,14 @@
       <c r="T107" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:20">
+      <c r="U107" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V107" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A108" s="13" t="s">
         <v>33</v>
       </c>
@@ -12083,8 +12622,14 @@
       <c r="T108" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:20">
+      <c r="U108" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V108" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A109" s="13" t="s">
         <v>33</v>
       </c>
@@ -12141,8 +12686,12 @@
       <c r="T109" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:20">
+      <c r="U109" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V109" s="13"/>
+    </row>
+    <row r="110" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A110" s="13" t="s">
         <v>33</v>
       </c>
@@ -12199,8 +12748,12 @@
       <c r="T110" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:20">
+      <c r="U110" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V110" s="13"/>
+    </row>
+    <row r="111" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A111" s="13" t="s">
         <v>33</v>
       </c>
@@ -12255,8 +12808,12 @@
       <c r="T111" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:20">
+      <c r="U111" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V111" s="13"/>
+    </row>
+    <row r="112" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A112" s="13" t="s">
         <v>33</v>
       </c>
@@ -12311,8 +12868,12 @@
       <c r="T112" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:20">
+      <c r="U112" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V112" s="13"/>
+    </row>
+    <row r="113" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A113" s="13" t="s">
         <v>33</v>
       </c>
@@ -12367,8 +12928,12 @@
       <c r="T113" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U113" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V113" s="13"/>
+    </row>
+    <row r="114" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="13" t="s">
         <v>33</v>
       </c>
@@ -12413,8 +12978,14 @@
       <c r="T114" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:20">
+      <c r="U114" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V114" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A115" s="13" t="s">
         <v>33</v>
       </c>
@@ -12459,8 +13030,14 @@
       <c r="T115" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:20">
+      <c r="U115" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V115" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A116" s="13" t="s">
         <v>33</v>
       </c>
@@ -12515,8 +13092,12 @@
       <c r="T116" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:20">
+      <c r="U116" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V116" s="13"/>
+    </row>
+    <row r="117" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A117" s="13" t="s">
         <v>33</v>
       </c>
@@ -12571,8 +13152,12 @@
       <c r="T117" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:20">
+      <c r="U117" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V117" s="13"/>
+    </row>
+    <row r="118" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A118" s="13" t="s">
         <v>33</v>
       </c>
@@ -12627,8 +13212,12 @@
       <c r="T118" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:20">
+      <c r="U118" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V118" s="13"/>
+    </row>
+    <row r="119" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A119" s="13" t="s">
         <v>33</v>
       </c>
@@ -12683,8 +13272,12 @@
       <c r="T119" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:20">
+      <c r="U119" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V119" s="13"/>
+    </row>
+    <row r="120" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A120" s="13" t="s">
         <v>33</v>
       </c>
@@ -12739,8 +13332,12 @@
       <c r="T120" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U120" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V120" s="13"/>
+    </row>
+    <row r="121" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="13" t="s">
         <v>33</v>
       </c>
@@ -12785,8 +13382,14 @@
       <c r="T121" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:20">
+      <c r="U121" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V121" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A122" s="13" t="s">
         <v>33</v>
       </c>
@@ -12831,8 +13434,14 @@
       <c r="T122" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:20">
+      <c r="U122" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V122" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A123" s="13" t="s">
         <v>33</v>
       </c>
@@ -12887,8 +13496,12 @@
       <c r="T123" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:20">
+      <c r="U123" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V123" s="13"/>
+    </row>
+    <row r="124" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A124" s="13" t="s">
         <v>33</v>
       </c>
@@ -12943,8 +13556,12 @@
       <c r="T124" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:20">
+      <c r="U124" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V124" s="13"/>
+    </row>
+    <row r="125" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A125" s="13" t="s">
         <v>33</v>
       </c>
@@ -12999,8 +13616,12 @@
       <c r="T125" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:20">
+      <c r="U125" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V125" s="13"/>
+    </row>
+    <row r="126" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A126" s="13" t="s">
         <v>33</v>
       </c>
@@ -13055,8 +13676,12 @@
       <c r="T126" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:20">
+      <c r="U126" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V126" s="13"/>
+    </row>
+    <row r="127" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A127" s="13" t="s">
         <v>33</v>
       </c>
@@ -13111,8 +13736,12 @@
       <c r="T127" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U127" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V127" s="13"/>
+    </row>
+    <row r="128" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="13" t="s">
         <v>33</v>
       </c>
@@ -13157,8 +13786,14 @@
       <c r="T128" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:20">
+      <c r="U128" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V128" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A129" s="13" t="s">
         <v>33</v>
       </c>
@@ -13203,8 +13838,14 @@
       <c r="T129" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:20">
+      <c r="U129" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V129" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A130" s="13" t="s">
         <v>33</v>
       </c>
@@ -13259,8 +13900,12 @@
       <c r="T130" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:20">
+      <c r="U130" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V130" s="13"/>
+    </row>
+    <row r="131" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A131" s="13" t="s">
         <v>33</v>
       </c>
@@ -13315,8 +13960,12 @@
       <c r="T131" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:20">
+      <c r="U131" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V131" s="13"/>
+    </row>
+    <row r="132" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A132" s="13" t="s">
         <v>33</v>
       </c>
@@ -13371,8 +14020,12 @@
       <c r="T132" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:20">
+      <c r="U132" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V132" s="13"/>
+    </row>
+    <row r="133" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A133" s="13" t="s">
         <v>33</v>
       </c>
@@ -13427,8 +14080,12 @@
       <c r="T133" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:20">
+      <c r="U133" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V133" s="13"/>
+    </row>
+    <row r="134" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A134" s="13" t="s">
         <v>33</v>
       </c>
@@ -13483,8 +14140,12 @@
       <c r="T134" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U134" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V134" s="13"/>
+    </row>
+    <row r="135" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="13" t="s">
         <v>33</v>
       </c>
@@ -13529,8 +14190,14 @@
       <c r="T135" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:20">
+      <c r="U135" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V135" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A136" s="13" t="s">
         <v>33</v>
       </c>
@@ -13575,8 +14242,14 @@
       <c r="T136" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:20">
+      <c r="U136" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V136" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A137" s="13" t="s">
         <v>33</v>
       </c>
@@ -13631,8 +14304,12 @@
       <c r="T137" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:20">
+      <c r="U137" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V137" s="13"/>
+    </row>
+    <row r="138" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A138" s="13" t="s">
         <v>33</v>
       </c>
@@ -13687,8 +14364,12 @@
       <c r="T138" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:20">
+      <c r="U138" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V138" s="13"/>
+    </row>
+    <row r="139" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A139" s="13" t="s">
         <v>33</v>
       </c>
@@ -13743,8 +14424,12 @@
       <c r="T139" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:20">
+      <c r="U139" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V139" s="13"/>
+    </row>
+    <row r="140" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A140" s="13" t="s">
         <v>33</v>
       </c>
@@ -13799,8 +14484,12 @@
       <c r="T140" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:20">
+      <c r="U140" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V140" s="13"/>
+    </row>
+    <row r="141" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A141" s="13" t="s">
         <v>33</v>
       </c>
@@ -13855,8 +14544,12 @@
       <c r="T141" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U141" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V141" s="13"/>
+    </row>
+    <row r="142" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="13" t="s">
         <v>33</v>
       </c>
@@ -13901,8 +14594,14 @@
       <c r="T142" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:20">
+      <c r="U142" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V142" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A143" s="13" t="s">
         <v>33</v>
       </c>
@@ -13947,8 +14646,14 @@
       <c r="T143" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:20">
+      <c r="U143" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V143" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A144" s="13" t="s">
         <v>33</v>
       </c>
@@ -14003,8 +14708,12 @@
       <c r="T144" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:20">
+      <c r="U144" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V144" s="13"/>
+    </row>
+    <row r="145" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A145" s="13" t="s">
         <v>33</v>
       </c>
@@ -14059,8 +14768,12 @@
       <c r="T145" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:20">
+      <c r="U145" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V145" s="13"/>
+    </row>
+    <row r="146" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A146" s="13" t="s">
         <v>33</v>
       </c>
@@ -14115,8 +14828,12 @@
       <c r="T146" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:20">
+      <c r="U146" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V146" s="13"/>
+    </row>
+    <row r="147" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A147" s="13" t="s">
         <v>33</v>
       </c>
@@ -14171,8 +14888,12 @@
       <c r="T147" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:20">
+      <c r="U147" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V147" s="13"/>
+    </row>
+    <row r="148" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A148" s="13" t="s">
         <v>33</v>
       </c>
@@ -14227,8 +14948,12 @@
       <c r="T148" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U148" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V148" s="13"/>
+    </row>
+    <row r="149" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="13" t="s">
         <v>33</v>
       </c>
@@ -14273,8 +14998,14 @@
       <c r="T149" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:20">
+      <c r="U149" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V149" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="150" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A150" s="13" t="s">
         <v>33</v>
       </c>
@@ -14319,8 +15050,14 @@
       <c r="T150" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:20">
+      <c r="U150" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V150" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="151" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A151" s="13" t="s">
         <v>33</v>
       </c>
@@ -14375,8 +15112,12 @@
       <c r="T151" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:20">
+      <c r="U151" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V151" s="13"/>
+    </row>
+    <row r="152" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A152" s="13" t="s">
         <v>33</v>
       </c>
@@ -14431,8 +15172,12 @@
       <c r="T152" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:20">
+      <c r="U152" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V152" s="13"/>
+    </row>
+    <row r="153" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A153" s="13" t="s">
         <v>33</v>
       </c>
@@ -14487,8 +15232,12 @@
       <c r="T153" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:20">
+      <c r="U153" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V153" s="13"/>
+    </row>
+    <row r="154" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A154" s="13" t="s">
         <v>33</v>
       </c>
@@ -14543,8 +15292,12 @@
       <c r="T154" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:20">
+      <c r="U154" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V154" s="13"/>
+    </row>
+    <row r="155" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A155" s="13" t="s">
         <v>33</v>
       </c>
@@ -14599,8 +15352,12 @@
       <c r="T155" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:20" ht="19.5" customHeight="1">
+      <c r="U155" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V155" s="13"/>
+    </row>
+    <row r="156" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="13" t="s">
         <v>33</v>
       </c>
@@ -14645,8 +15402,14 @@
       <c r="T156" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:20">
+      <c r="U156" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V156" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="157" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A157" s="13" t="s">
         <v>33</v>
       </c>
@@ -14691,8 +15454,14 @@
       <c r="T157" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:20">
+      <c r="U157" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="V157" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="158" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A158" s="13" t="s">
         <v>33</v>
       </c>
@@ -14747,8 +15516,12 @@
       <c r="T158" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:20">
+      <c r="U158" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V158" s="13"/>
+    </row>
+    <row r="159" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A159" s="13" t="s">
         <v>33</v>
       </c>
@@ -14803,8 +15576,12 @@
       <c r="T159" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:20">
+      <c r="U159" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V159" s="13"/>
+    </row>
+    <row r="160" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A160" s="13" t="s">
         <v>33</v>
       </c>
@@ -14859,8 +15636,12 @@
       <c r="T160" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:20">
+      <c r="U160" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V160" s="13"/>
+    </row>
+    <row r="161" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A161" s="13" t="s">
         <v>33</v>
       </c>
@@ -14915,8 +15696,12 @@
       <c r="T161" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:20">
+      <c r="U161" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V161" s="13"/>
+    </row>
+    <row r="162" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A162" s="13" t="s">
         <v>33</v>
       </c>
@@ -14971,8 +15756,12 @@
       <c r="T162" s="13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:20">
+      <c r="U162" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V162" s="13"/>
+    </row>
+    <row r="163" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A163" s="13"/>
       <c r="B163" s="13"/>
       <c r="C163" s="13"/>
@@ -14994,7 +15783,7 @@
       <c r="S163" s="13"/>
       <c r="T163" s="13"/>
     </row>
-    <row r="164" spans="1:20">
+    <row r="164" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A164" s="13"/>
       <c r="B164" s="13"/>
       <c r="C164" s="13"/>
@@ -15016,7 +15805,7 @@
       <c r="S164" s="13"/>
       <c r="T164" s="13"/>
     </row>
-    <row r="165" spans="1:20">
+    <row r="165" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A165" s="13"/>
       <c r="B165" s="13"/>
       <c r="C165" s="13"/>
@@ -15038,7 +15827,7 @@
       <c r="S165" s="13"/>
       <c r="T165" s="13"/>
     </row>
-    <row r="166" spans="1:20">
+    <row r="166" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A166" s="13"/>
       <c r="B166" s="13"/>
       <c r="C166" s="13"/>
@@ -15060,7 +15849,7 @@
       <c r="S166" s="13"/>
       <c r="T166" s="13"/>
     </row>
-    <row r="167" spans="1:20">
+    <row r="167" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A167" s="13"/>
       <c r="B167" s="13"/>
       <c r="C167" s="13"/>
@@ -15082,7 +15871,7 @@
       <c r="S167" s="13"/>
       <c r="T167" s="13"/>
     </row>
-    <row r="168" spans="1:20">
+    <row r="168" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A168" s="13"/>
       <c r="B168" s="13"/>
       <c r="C168" s="13"/>
@@ -15104,7 +15893,7 @@
       <c r="S168" s="13"/>
       <c r="T168" s="13"/>
     </row>
-    <row r="169" spans="1:20">
+    <row r="169" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A169" s="13"/>
       <c r="B169" s="13"/>
       <c r="C169" s="13"/>
@@ -15126,7 +15915,7 @@
       <c r="S169" s="13"/>
       <c r="T169" s="13"/>
     </row>
-    <row r="170" spans="1:20">
+    <row r="170" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A170" s="13"/>
       <c r="B170" s="13"/>
       <c r="C170" s="13"/>
@@ -15148,7 +15937,7 @@
       <c r="S170" s="13"/>
       <c r="T170" s="13"/>
     </row>
-    <row r="171" spans="1:20">
+    <row r="171" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A171" s="13"/>
       <c r="B171" s="13"/>
       <c r="C171" s="13"/>
@@ -15170,7 +15959,7 @@
       <c r="S171" s="13"/>
       <c r="T171" s="13"/>
     </row>
-    <row r="172" spans="1:20">
+    <row r="172" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A172" s="13"/>
       <c r="B172" s="13"/>
       <c r="C172" s="13"/>
@@ -15192,7 +15981,7 @@
       <c r="S172" s="13"/>
       <c r="T172" s="13"/>
     </row>
-    <row r="173" spans="1:20">
+    <row r="173" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A173" s="13"/>
       <c r="B173" s="13"/>
       <c r="C173" s="13"/>
@@ -15214,7 +16003,7 @@
       <c r="S173" s="13"/>
       <c r="T173" s="13"/>
     </row>
-    <row r="174" spans="1:20">
+    <row r="174" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A174" s="13"/>
       <c r="B174" s="13"/>
       <c r="C174" s="13"/>
@@ -15236,7 +16025,7 @@
       <c r="S174" s="13"/>
       <c r="T174" s="13"/>
     </row>
-    <row r="175" spans="1:20">
+    <row r="175" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A175" s="13"/>
       <c r="B175" s="13"/>
       <c r="C175" s="13"/>
@@ -15258,7 +16047,7 @@
       <c r="S175" s="13"/>
       <c r="T175" s="13"/>
     </row>
-    <row r="176" spans="1:20">
+    <row r="176" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A176" s="13"/>
       <c r="B176" s="13"/>
       <c r="C176" s="13"/>
@@ -15280,7 +16069,7 @@
       <c r="S176" s="13"/>
       <c r="T176" s="13"/>
     </row>
-    <row r="177" spans="1:20">
+    <row r="177" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A177" s="13"/>
       <c r="B177" s="13"/>
       <c r="C177" s="13"/>
@@ -15302,7 +16091,7 @@
       <c r="S177" s="13"/>
       <c r="T177" s="13"/>
     </row>
-    <row r="178" spans="1:20">
+    <row r="178" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A178" s="13"/>
       <c r="B178" s="13"/>
       <c r="C178" s="13"/>
@@ -15324,7 +16113,7 @@
       <c r="S178" s="13"/>
       <c r="T178" s="13"/>
     </row>
-    <row r="179" spans="1:20">
+    <row r="179" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A179" s="13"/>
       <c r="B179" s="13"/>
       <c r="C179" s="13"/>
@@ -15346,7 +16135,7 @@
       <c r="S179" s="13"/>
       <c r="T179" s="13"/>
     </row>
-    <row r="180" spans="1:20">
+    <row r="180" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A180" s="13"/>
       <c r="B180" s="13"/>
       <c r="C180" s="13"/>
@@ -15368,7 +16157,7 @@
       <c r="S180" s="13"/>
       <c r="T180" s="13"/>
     </row>
-    <row r="181" spans="1:20">
+    <row r="181" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A181" s="13"/>
       <c r="B181" s="13"/>
       <c r="C181" s="13"/>
@@ -15390,7 +16179,7 @@
       <c r="S181" s="13"/>
       <c r="T181" s="13"/>
     </row>
-    <row r="182" spans="1:20">
+    <row r="182" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A182" s="13"/>
       <c r="B182" s="13"/>
       <c r="C182" s="13"/>
@@ -15412,7 +16201,7 @@
       <c r="S182" s="13"/>
       <c r="T182" s="13"/>
     </row>
-    <row r="183" spans="1:20">
+    <row r="183" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A183" s="13"/>
       <c r="B183" s="13"/>
       <c r="C183" s="13"/>
@@ -15434,7 +16223,7 @@
       <c r="S183" s="13"/>
       <c r="T183" s="13"/>
     </row>
-    <row r="184" spans="1:20">
+    <row r="184" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A184" s="13"/>
       <c r="B184" s="13"/>
       <c r="C184" s="13"/>
@@ -15456,7 +16245,7 @@
       <c r="S184" s="13"/>
       <c r="T184" s="13"/>
     </row>
-    <row r="185" spans="1:20">
+    <row r="185" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A185" s="13"/>
       <c r="B185" s="13"/>
       <c r="C185" s="13"/>
@@ -15478,7 +16267,7 @@
       <c r="S185" s="13"/>
       <c r="T185" s="13"/>
     </row>
-    <row r="186" spans="1:20">
+    <row r="186" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A186" s="13"/>
       <c r="B186" s="13"/>
       <c r="C186" s="13"/>
@@ -15500,7 +16289,7 @@
       <c r="S186" s="13"/>
       <c r="T186" s="13"/>
     </row>
-    <row r="187" spans="1:20">
+    <row r="187" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A187" s="13"/>
       <c r="B187" s="13"/>
       <c r="C187" s="13"/>
@@ -15522,7 +16311,7 @@
       <c r="S187" s="13"/>
       <c r="T187" s="13"/>
     </row>
-    <row r="188" spans="1:20">
+    <row r="188" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A188" s="13"/>
       <c r="B188" s="13"/>
       <c r="C188" s="13"/>
@@ -15544,7 +16333,7 @@
       <c r="S188" s="13"/>
       <c r="T188" s="13"/>
     </row>
-    <row r="189" spans="1:20">
+    <row r="189" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A189" s="13"/>
       <c r="B189" s="13"/>
       <c r="C189" s="13"/>
@@ -15566,7 +16355,7 @@
       <c r="S189" s="13"/>
       <c r="T189" s="13"/>
     </row>
-    <row r="190" spans="1:20">
+    <row r="190" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A190" s="13"/>
       <c r="B190" s="13"/>
       <c r="C190" s="13"/>
@@ -15588,7 +16377,7 @@
       <c r="S190" s="13"/>
       <c r="T190" s="13"/>
     </row>
-    <row r="191" spans="1:20">
+    <row r="191" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A191" s="13"/>
       <c r="B191" s="13"/>
       <c r="C191" s="13"/>
@@ -15610,7 +16399,7 @@
       <c r="S191" s="13"/>
       <c r="T191" s="13"/>
     </row>
-    <row r="192" spans="1:20">
+    <row r="192" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A192" s="13"/>
       <c r="B192" s="13"/>
       <c r="C192" s="13"/>
@@ -15632,7 +16421,7 @@
       <c r="S192" s="13"/>
       <c r="T192" s="13"/>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A193" s="13"/>
       <c r="B193" s="13"/>
       <c r="C193" s="13"/>
@@ -15654,7 +16443,7 @@
       <c r="S193" s="13"/>
       <c r="T193" s="13"/>
     </row>
-    <row r="194" spans="1:20">
+    <row r="194" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A194" s="13"/>
       <c r="B194" s="13"/>
       <c r="C194" s="13"/>
@@ -15676,7 +16465,7 @@
       <c r="S194" s="13"/>
       <c r="T194" s="13"/>
     </row>
-    <row r="195" spans="1:20">
+    <row r="195" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A195" s="13"/>
       <c r="B195" s="13"/>
       <c r="C195" s="13"/>
@@ -15698,7 +16487,7 @@
       <c r="S195" s="13"/>
       <c r="T195" s="13"/>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A196" s="13"/>
       <c r="B196" s="13"/>
       <c r="C196" s="13"/>
@@ -15720,7 +16509,7 @@
       <c r="S196" s="13"/>
       <c r="T196" s="13"/>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A197" s="13"/>
       <c r="B197" s="13"/>
       <c r="C197" s="13"/>
@@ -15742,7 +16531,7 @@
       <c r="S197" s="13"/>
       <c r="T197" s="13"/>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A198" s="13"/>
       <c r="B198" s="13"/>
       <c r="C198" s="13"/>
@@ -15764,7 +16553,7 @@
       <c r="S198" s="13"/>
       <c r="T198" s="13"/>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A199" s="13"/>
       <c r="B199" s="13"/>
       <c r="C199" s="13"/>
@@ -15786,7 +16575,7 @@
       <c r="S199" s="13"/>
       <c r="T199" s="13"/>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A200" s="13"/>
       <c r="B200" s="13"/>
       <c r="C200" s="13"/>
@@ -15808,7 +16597,7 @@
       <c r="S200" s="13"/>
       <c r="T200" s="13"/>
     </row>
-    <row r="201" spans="1:20">
+    <row r="201" spans="1:20" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A201" s="13"/>
       <c r="B201" s="13"/>
       <c r="C201" s="13"/>
@@ -15833,28 +16622,28 @@
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="M4:M8">
-    <cfRule type="duplicateValues" dxfId="7" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:M24 M32:M52 M60:M80 M88:M101 M109:M162">
-    <cfRule type="duplicateValues" dxfId="6" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:M29">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53:M57">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M81:M85">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M102:M106">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M177:M181">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M182:M186">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="R4" r:id="rId1" xr:uid="{D9569CBD-1C1A-4EF0-9D90-B70EA928D150}"/>
@@ -16016,7 +16805,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B74CACAF-9354-4720-9024-D16273E302C8}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="12.3"/>
+  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="21.21875" customWidth="1"/>
@@ -16024,7 +16813,7 @@
     <col min="5" max="5" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.6">
+    <row r="1" spans="1:6" ht="28.2" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>28</v>
       </c>
@@ -16042,7 +16831,7 @@
       </c>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6" ht="15.9" customHeight="1">
+    <row r="2" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>31</v>
       </c>
@@ -16060,7 +16849,7 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" ht="15.9" customHeight="1">
+    <row r="3" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
@@ -16078,13 +16867,13 @@
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
@@ -16105,13 +16894,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC73D3E-7FF0-4153-9F26-5730282D2AEE}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="12.3"/>
+  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
     <col min="2" max="2" width="69.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.8">
+    <row r="1" spans="1:6" ht="14.1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -16123,7 +16912,7 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6" ht="13.8">
+    <row r="2" spans="1:6" ht="14.1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -16135,7 +16924,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" ht="13.8">
+    <row r="3" spans="1:6" ht="14.1" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
@@ -16147,7 +16936,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" ht="13.8">
+    <row r="4" spans="1:6" ht="14.1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>27</v>
       </c>
@@ -16159,7 +16948,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" ht="13.8">
+    <row r="5" spans="1:6" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -16167,7 +16956,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="13.8">
+    <row r="6" spans="1:6" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -16175,7 +16964,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="13.8">
+    <row r="7" spans="1:6" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -16183,7 +16972,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" ht="13.8">
+    <row r="8" spans="1:6" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -16191,7 +16980,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="13.8">
+    <row r="9" spans="1:6" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -16199,7 +16988,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="13.8">
+    <row r="10" spans="1:6" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -16207,7 +16996,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="13.8">
+    <row r="11" spans="1:6" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -16226,7 +17015,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4312CB-53A7-4009-A6C6-8EE208F0452A}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="21.44140625" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="21.44140625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -16235,7 +17024,7 @@
     <col min="5" max="5" width="55.27734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="39" t="s">
         <v>149</v>
       </c>
@@ -16252,7 +17041,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="40" t="s">
         <v>154</v>
       </c>
@@ -16269,7 +17058,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="40" t="s">
         <v>159</v>
       </c>
@@ -16286,7 +17075,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="40" t="s">
         <v>164</v>
       </c>
@@ -16303,7 +17092,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="40" t="s">
         <v>169</v>
       </c>
@@ -16320,7 +17109,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="40" t="s">
         <v>174</v>
       </c>
@@ -16337,7 +17126,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="40" t="s">
         <v>179</v>
       </c>
@@ -16354,7 +17143,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="40" t="s">
         <v>184</v>
       </c>
@@ -16371,7 +17160,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="40" t="s">
         <v>189</v>
       </c>
@@ -16388,7 +17177,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="40" t="s">
         <v>191</v>
       </c>
@@ -16405,7 +17194,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="40" t="s">
         <v>193</v>
       </c>
@@ -16422,7 +17211,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="40" t="s">
         <v>198</v>
       </c>
@@ -16439,7 +17228,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="40" t="s">
         <v>202</v>
       </c>
@@ -16456,7 +17245,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="40" t="s">
         <v>206</v>
       </c>
@@ -16473,7 +17262,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="40" t="s">
         <v>208</v>
       </c>
@@ -16490,7 +17279,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="40" t="s">
         <v>212</v>
       </c>
@@ -16507,7 +17296,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="40" t="s">
         <v>214</v>
       </c>
@@ -16524,7 +17313,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="40" t="s">
         <v>218</v>
       </c>
@@ -16541,7 +17330,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="40" t="s">
         <v>222</v>
       </c>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B082E31-0CB5-41C5-B655-2B387B612623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E52587D-9ED9-48A6-BF3B-926315F3E024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6270,11 +6270,12 @@
     <hyperlink ref="F6" r:id="rId18" xr:uid="{0F04F74A-C7AF-4270-BF3F-B892737F9485}"/>
     <hyperlink ref="F4" r:id="rId19" xr:uid="{7549D256-AA4A-4830-97CE-DE90E16987C5}"/>
     <hyperlink ref="F7" r:id="rId20" xr:uid="{1AB82CA2-ACD0-468F-9F10-9B67A3E10CC6}"/>
+    <hyperlink ref="J18" r:id="rId21" xr:uid="{1CF0B4FA-4DC1-4539-B70C-A81E891DC37D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId21"/>
+  <legacyDrawing r:id="rId22"/>
   <tableParts count="1">
-    <tablePart r:id="rId22"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6718,8 +6719,8 @@
       <c r="R7" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="S7" s="13" t="s">
-        <v>119</v>
+      <c r="S7" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="T7" s="13" t="b">
         <v>1</v>
@@ -6950,8 +6951,8 @@
       <c r="R11" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="S11" s="13" t="s">
-        <v>117</v>
+      <c r="S11" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="T11" s="13" t="b">
         <v>1</v>
@@ -16794,10 +16795,12 @@
     <hyperlink ref="L42" r:id="rId146" xr:uid="{BA739C41-4575-4A33-9C96-AD32524896E7}"/>
     <hyperlink ref="L43" r:id="rId147" xr:uid="{50713490-1903-4314-8EFA-3036EEED0BEE}"/>
     <hyperlink ref="L33" r:id="rId148" xr:uid="{8D220609-2D34-48AD-A30F-42CE121090A0}"/>
+    <hyperlink ref="S7" r:id="rId149" xr:uid="{E9C9AC5C-FB44-4DF1-9A5A-F63125F706C5}"/>
+    <hyperlink ref="S11" r:id="rId150" xr:uid="{0C1812DF-CB74-4A1D-A893-DCD676F1D4E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId149"/>
+    <tablePart r:id="rId151"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E52587D-9ED9-48A6-BF3B-926315F3E024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D757572-C1F1-4BA0-99D4-D45A8475C7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2538,7 +2538,7 @@
       <name val="Inter"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2560,6 +2560,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2636,7 +2642,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2793,48 +2799,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="72">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF404040"/>
-        <name val="Inter"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF404040"/>
-        <name val="Inter"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3194,6 +3174,42 @@
         <name val="Inter"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3375,6 +3391,12 @@
         <name val="Inter"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3393,6 +3415,12 @@
         <name val="Inter"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4065,33 +4093,33 @@
     <tableColumn id="8" xr3:uid="{51AF3A7A-9E37-4EC3-95E2-04EA97CB0A3F}" name="Avatar Image URL" dataDxfId="24"/>
     <tableColumn id="9" xr3:uid="{62D296DE-BD87-415D-A7A9-7B26ADBEBF6D}" name="Voice over" dataDxfId="23"/>
     <tableColumn id="18" xr3:uid="{48873D82-692C-4357-B503-4E9A267EC815}" name="Hotspot Hover Active" dataDxfId="22"/>
-    <tableColumn id="21" xr3:uid="{54CB3C40-C39A-44B4-A549-CF60CCCE8ACB}" name="Hotspot type" dataDxfId="1"/>
-    <tableColumn id="22" xr3:uid="{72414B5E-A62A-4803-BE10-64DE72621FD3}" name="Hotspot Navigation" dataDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{54CB3C40-C39A-44B4-A549-CF60CCCE8ACB}" name="Hotspot type" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{72414B5E-A62A-4803-BE10-64DE72621FD3}" name="Hotspot Navigation" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:E3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="17" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="15" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:B4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6247,7 +6275,7 @@
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{CD437926-0051-42E8-974D-E38762304209}"/>
@@ -6289,7 +6317,8 @@
     <col min="3" max="3" width="9.88671875" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="59"/>
+    <col min="7" max="7" width="17.1640625" style="59" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.609375" customWidth="1"/>
     <col min="12" max="12" width="58.94140625" customWidth="1"/>
     <col min="13" max="13" width="24.1640625" customWidth="1"/>
@@ -6300,6 +6329,7 @@
     <col min="18" max="18" width="22.5" customWidth="1"/>
     <col min="19" max="19" width="57.27734375" customWidth="1"/>
     <col min="20" max="20" width="23.109375" customWidth="1"/>
+    <col min="21" max="21" width="14.44140625" customWidth="1"/>
     <col min="23" max="23" width="29.5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="29.5" customWidth="1"/>
     <col min="25" max="25" width="26.5546875" customWidth="1"/>
@@ -6322,10 +6352,10 @@
       <c r="E1" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="56" t="s">
         <v>19</v>
       </c>
       <c r="H1" s="7" t="s">
@@ -6390,10 +6420,10 @@
       <c r="E2" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H2" s="14" t="s">
@@ -6442,10 +6472,10 @@
       <c r="E3" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H3" s="14" t="s">
@@ -6494,10 +6524,10 @@
       <c r="E4" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="14"/>
+      <c r="F4" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="57"/>
       <c r="H4" s="14" t="s">
         <v>24</v>
       </c>
@@ -6558,10 +6588,10 @@
       <c r="E5" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="14"/>
+      <c r="F5" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="57"/>
       <c r="H5" s="14" t="s">
         <v>24</v>
       </c>
@@ -6622,10 +6652,10 @@
       <c r="E6" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="14"/>
+      <c r="F6" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="57"/>
       <c r="H6" s="14" t="s">
         <v>24</v>
       </c>
@@ -6684,10 +6714,10 @@
       <c r="E7" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="14"/>
+      <c r="F7" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="57"/>
       <c r="H7" s="14" t="s">
         <v>24</v>
       </c>
@@ -6746,10 +6776,10 @@
       <c r="E8" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="14"/>
+      <c r="F8" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="57"/>
       <c r="H8" s="14" t="s">
         <v>24</v>
       </c>
@@ -6810,10 +6840,10 @@
       <c r="E9" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H9" s="14" t="s">
@@ -6862,10 +6892,10 @@
       <c r="E10" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H10" s="14" t="s">
@@ -6914,10 +6944,10 @@
       <c r="E11" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="14"/>
+      <c r="F11" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="57"/>
       <c r="H11" s="14" t="s">
         <v>24</v>
       </c>
@@ -6978,10 +7008,10 @@
       <c r="E12" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="14"/>
+      <c r="F12" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="57"/>
       <c r="H12" s="14" t="s">
         <v>24</v>
       </c>
@@ -7042,10 +7072,10 @@
       <c r="E13" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="14"/>
+      <c r="F13" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="57"/>
       <c r="H13" s="14" t="s">
         <v>24</v>
       </c>
@@ -7104,10 +7134,10 @@
       <c r="E14" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="14"/>
+      <c r="F14" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="57"/>
       <c r="H14" s="14" t="s">
         <v>24</v>
       </c>
@@ -7166,10 +7196,10 @@
       <c r="E15" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="14"/>
+      <c r="F15" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="57"/>
       <c r="H15" s="14" t="s">
         <v>24</v>
       </c>
@@ -7228,10 +7258,10 @@
       <c r="E16" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H16" s="25" t="s">
@@ -7280,10 +7310,10 @@
       <c r="E17" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H17" s="26" t="s">
@@ -7332,10 +7362,10 @@
       <c r="E18" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="13"/>
+      <c r="F18" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="58"/>
       <c r="H18" s="25" t="s">
         <v>24</v>
       </c>
@@ -7392,10 +7422,10 @@
       <c r="E19" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="13"/>
+      <c r="F19" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="58"/>
       <c r="H19" s="26" t="s">
         <v>24</v>
       </c>
@@ -7452,10 +7482,10 @@
       <c r="E20" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="13"/>
+      <c r="F20" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="58"/>
       <c r="H20" s="25" t="s">
         <v>24</v>
       </c>
@@ -7512,10 +7542,10 @@
       <c r="E21" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="13"/>
+      <c r="F21" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="58"/>
       <c r="H21" s="26" t="s">
         <v>24</v>
       </c>
@@ -7572,10 +7602,10 @@
       <c r="E22" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="13"/>
+      <c r="F22" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="58"/>
       <c r="H22" s="25" t="s">
         <v>24</v>
       </c>
@@ -7634,10 +7664,10 @@
       <c r="E23" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H23" s="26" t="s">
@@ -7686,10 +7716,10 @@
       <c r="E24" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H24" s="25" t="s">
@@ -7738,10 +7768,10 @@
       <c r="E25" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="13"/>
+      <c r="F25" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="58"/>
       <c r="H25" s="26" t="s">
         <v>24</v>
       </c>
@@ -7800,10 +7830,10 @@
       <c r="E26" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="13"/>
+      <c r="F26" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="58"/>
       <c r="H26" s="25" t="s">
         <v>24</v>
       </c>
@@ -7862,10 +7892,10 @@
       <c r="E27" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="13"/>
+      <c r="F27" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="58"/>
       <c r="H27" s="26" t="s">
         <v>24</v>
       </c>
@@ -7922,10 +7952,10 @@
       <c r="E28" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="13"/>
+      <c r="F28" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="58"/>
       <c r="H28" s="31" t="s">
         <v>24</v>
       </c>
@@ -7984,10 +8014,10 @@
       <c r="E29" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="13"/>
+      <c r="F29" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="58"/>
       <c r="H29" s="26" t="s">
         <v>24</v>
       </c>
@@ -8048,10 +8078,10 @@
       <c r="E30" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H30" s="13" t="s">
@@ -8100,10 +8130,10 @@
       <c r="E31" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H31" s="13" t="s">
@@ -8152,10 +8182,10 @@
       <c r="E32" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="F32" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="13"/>
+      <c r="F32" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="58"/>
       <c r="H32" s="13" t="s">
         <v>24</v>
       </c>
@@ -8216,10 +8246,10 @@
       <c r="E33" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="13"/>
+      <c r="F33" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="58"/>
       <c r="H33" s="13" t="s">
         <v>24</v>
       </c>
@@ -8280,10 +8310,10 @@
       <c r="E34" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="F34" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G34" s="13"/>
+      <c r="F34" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="58"/>
       <c r="H34" s="13" t="s">
         <v>24</v>
       </c>
@@ -8342,10 +8372,10 @@
       <c r="E35" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35" s="13"/>
+      <c r="F35" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="58"/>
       <c r="H35" s="13" t="s">
         <v>24</v>
       </c>
@@ -8404,10 +8434,10 @@
       <c r="E36" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="F36" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="13"/>
+      <c r="F36" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="58"/>
       <c r="H36" s="13" t="s">
         <v>24</v>
       </c>
@@ -8466,10 +8496,10 @@
       <c r="E37" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H37" s="13" t="s">
@@ -8518,10 +8548,10 @@
       <c r="E38" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H38" s="13" t="s">
@@ -8570,10 +8600,10 @@
       <c r="E39" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="F39" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G39" s="13"/>
+      <c r="F39" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="58"/>
       <c r="H39" s="13" t="s">
         <v>24</v>
       </c>
@@ -8632,10 +8662,10 @@
       <c r="E40" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="F40" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="13"/>
+      <c r="F40" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="58"/>
       <c r="H40" s="13" t="s">
         <v>24</v>
       </c>
@@ -8694,10 +8724,10 @@
       <c r="E41" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="F41" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="13"/>
+      <c r="F41" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="58"/>
       <c r="H41" s="13" t="s">
         <v>24</v>
       </c>
@@ -8756,10 +8786,10 @@
       <c r="E42" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="F42" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="13"/>
+      <c r="F42" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="58"/>
       <c r="H42" s="13" t="s">
         <v>24</v>
       </c>
@@ -8818,10 +8848,10 @@
       <c r="E43" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="F43" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="13"/>
+      <c r="F43" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="58"/>
       <c r="H43" s="13" t="s">
         <v>24</v>
       </c>
@@ -8880,10 +8910,10 @@
       <c r="E44" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H44" s="25" t="s">
@@ -8932,10 +8962,10 @@
       <c r="E45" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H45" s="26" t="s">
@@ -8984,10 +9014,10 @@
       <c r="E46" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="F46" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G46" s="13"/>
+      <c r="F46" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="58"/>
       <c r="H46" s="25" t="s">
         <v>24</v>
       </c>
@@ -9044,10 +9074,10 @@
       <c r="E47" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="F47" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="13"/>
+      <c r="F47" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="58"/>
       <c r="H47" s="26" t="s">
         <v>24</v>
       </c>
@@ -9104,10 +9134,10 @@
       <c r="E48" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="F48" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G48" s="13"/>
+      <c r="F48" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="58"/>
       <c r="H48" s="25" t="s">
         <v>24</v>
       </c>
@@ -9164,10 +9194,10 @@
       <c r="E49" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="F49" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="13"/>
+      <c r="F49" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="58"/>
       <c r="H49" s="26" t="s">
         <v>24</v>
       </c>
@@ -9224,10 +9254,10 @@
       <c r="E50" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="F50" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" s="13"/>
+      <c r="F50" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="58"/>
       <c r="H50" s="25" t="s">
         <v>24</v>
       </c>
@@ -9284,20 +9314,20 @@
       <c r="E51" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H51" s="26" t="s">
         <v>26</v>
       </c>
       <c r="I51" s="25">
-        <v>-24.61</v>
+        <v>-15.9</v>
       </c>
       <c r="J51" s="25">
-        <v>176.91</v>
+        <v>100.17</v>
       </c>
       <c r="K51" s="25" t="s">
         <v>42</v>
@@ -9336,20 +9366,20 @@
       <c r="E52" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H52" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I52" s="26">
-        <v>-11.7</v>
+        <v>-7.08</v>
       </c>
       <c r="J52" s="26">
-        <v>-3.78</v>
+        <v>-86.86</v>
       </c>
       <c r="K52" s="26" t="s">
         <v>42</v>
@@ -9388,10 +9418,10 @@
       <c r="E53" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="F53" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G53" s="13"/>
+      <c r="F53" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="58"/>
       <c r="H53" s="26" t="s">
         <v>24</v>
       </c>
@@ -9450,10 +9480,10 @@
       <c r="E54" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="F54" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G54" s="13"/>
+      <c r="F54" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="58"/>
       <c r="H54" s="25" t="s">
         <v>24</v>
       </c>
@@ -9512,10 +9542,10 @@
       <c r="E55" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="F55" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G55" s="13"/>
+      <c r="F55" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="58"/>
       <c r="H55" s="26" t="s">
         <v>24</v>
       </c>
@@ -9572,10 +9602,10 @@
       <c r="E56" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="F56" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="13"/>
+      <c r="F56" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="58"/>
       <c r="H56" s="25" t="s">
         <v>24</v>
       </c>
@@ -9632,10 +9662,10 @@
       <c r="E57" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="F57" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="13"/>
+      <c r="F57" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="58"/>
       <c r="H57" s="26" t="s">
         <v>24</v>
       </c>
@@ -9694,10 +9724,10 @@
       <c r="E58" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="F58" s="13" t="s">
+      <c r="F58" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="G58" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H58" s="13" t="s">
@@ -9746,10 +9776,10 @@
       <c r="E59" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="F59" s="13" t="s">
+      <c r="F59" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G59" s="13" t="s">
+      <c r="G59" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H59" s="13" t="s">
@@ -9798,10 +9828,10 @@
       <c r="E60" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="F60" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G60" s="13"/>
+      <c r="F60" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="58"/>
       <c r="H60" s="13" t="s">
         <v>24</v>
       </c>
@@ -9860,10 +9890,10 @@
       <c r="E61" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="F61" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G61" s="13"/>
+      <c r="F61" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" s="58"/>
       <c r="H61" s="13" t="s">
         <v>24</v>
       </c>
@@ -9922,10 +9952,10 @@
       <c r="E62" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="F62" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G62" s="13"/>
+      <c r="F62" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="58"/>
       <c r="H62" s="13" t="s">
         <v>24</v>
       </c>
@@ -9982,10 +10012,10 @@
       <c r="E63" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="F63" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G63" s="13"/>
+      <c r="F63" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="58"/>
       <c r="H63" s="13" t="s">
         <v>24</v>
       </c>
@@ -10042,10 +10072,10 @@
       <c r="E64" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="F64" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G64" s="13"/>
+      <c r="F64" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" s="58"/>
       <c r="H64" s="13" t="s">
         <v>24</v>
       </c>
@@ -10102,10 +10132,10 @@
       <c r="E65" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="F65" s="13" t="s">
+      <c r="F65" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G65" s="13" t="s">
+      <c r="G65" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H65" s="13" t="s">
@@ -10154,10 +10184,10 @@
       <c r="E66" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="F66" s="13" t="s">
+      <c r="F66" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G66" s="13" t="s">
+      <c r="G66" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H66" s="13" t="s">
@@ -10206,10 +10236,10 @@
       <c r="E67" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="F67" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G67" s="13"/>
+      <c r="F67" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="58"/>
       <c r="H67" s="13" t="s">
         <v>24</v>
       </c>
@@ -10266,10 +10296,10 @@
       <c r="E68" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="F68" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G68" s="13"/>
+      <c r="F68" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" s="58"/>
       <c r="H68" s="13" t="s">
         <v>24</v>
       </c>
@@ -10326,10 +10356,10 @@
       <c r="E69" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="F69" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G69" s="13"/>
+      <c r="F69" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="58"/>
       <c r="H69" s="13" t="s">
         <v>24</v>
       </c>
@@ -10386,10 +10416,10 @@
       <c r="E70" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="F70" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G70" s="13"/>
+      <c r="F70" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="58"/>
       <c r="H70" s="13" t="s">
         <v>24</v>
       </c>
@@ -10446,10 +10476,10 @@
       <c r="E71" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="F71" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G71" s="13"/>
+      <c r="F71" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="58"/>
       <c r="H71" s="13" t="s">
         <v>24</v>
       </c>
@@ -10506,10 +10536,10 @@
       <c r="E72" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="F72" s="13" t="s">
+      <c r="F72" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H72" s="25" t="s">
@@ -10558,10 +10588,10 @@
       <c r="E73" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="F73" s="13" t="s">
+      <c r="F73" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G73" s="13" t="s">
+      <c r="G73" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H73" s="26" t="s">
@@ -10610,10 +10640,10 @@
       <c r="E74" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="F74" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G74" s="13"/>
+      <c r="F74" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="58"/>
       <c r="H74" s="25" t="s">
         <v>24</v>
       </c>
@@ -10670,10 +10700,10 @@
       <c r="E75" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="F75" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G75" s="13"/>
+      <c r="F75" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" s="58"/>
       <c r="H75" s="26" t="s">
         <v>24</v>
       </c>
@@ -10730,10 +10760,10 @@
       <c r="E76" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="F76" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G76" s="13"/>
+      <c r="F76" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" s="58"/>
       <c r="H76" s="25" t="s">
         <v>24</v>
       </c>
@@ -10790,10 +10820,10 @@
       <c r="E77" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="F77" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G77" s="13"/>
+      <c r="F77" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G77" s="58"/>
       <c r="H77" s="26" t="s">
         <v>24</v>
       </c>
@@ -10850,10 +10880,10 @@
       <c r="E78" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="F78" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G78" s="13"/>
+      <c r="F78" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="58"/>
       <c r="H78" s="25" t="s">
         <v>24</v>
       </c>
@@ -10910,10 +10940,10 @@
       <c r="E79" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="F79" s="13" t="s">
+      <c r="F79" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G79" s="13" t="s">
+      <c r="G79" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H79" s="26" t="s">
@@ -10962,10 +10992,10 @@
       <c r="E80" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="F80" s="13" t="s">
+      <c r="F80" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G80" s="13" t="s">
+      <c r="G80" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H80" s="25" t="s">
@@ -11014,10 +11044,10 @@
       <c r="E81" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="F81" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G81" s="13"/>
+      <c r="F81" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="58"/>
       <c r="H81" s="26" t="s">
         <v>24</v>
       </c>
@@ -11076,10 +11106,10 @@
       <c r="E82" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="F82" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G82" s="13"/>
+      <c r="F82" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G82" s="58"/>
       <c r="H82" s="25" t="s">
         <v>24</v>
       </c>
@@ -11138,10 +11168,10 @@
       <c r="E83" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="F83" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G83" s="13"/>
+      <c r="F83" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83" s="58"/>
       <c r="H83" s="26" t="s">
         <v>24</v>
       </c>
@@ -11198,10 +11228,10 @@
       <c r="E84" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="F84" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G84" s="13"/>
+      <c r="F84" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="58"/>
       <c r="H84" s="25" t="s">
         <v>24</v>
       </c>
@@ -11258,10 +11288,10 @@
       <c r="E85" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="F85" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G85" s="13"/>
+      <c r="F85" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="58"/>
       <c r="H85" s="26" t="s">
         <v>24</v>
       </c>
@@ -11320,10 +11350,10 @@
       <c r="E86" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="F86" s="13" t="s">
+      <c r="F86" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G86" s="13" t="s">
+      <c r="G86" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H86" s="13" t="s">
@@ -11372,10 +11402,10 @@
       <c r="E87" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F87" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G87" s="13" t="s">
+      <c r="G87" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H87" s="13" t="s">
@@ -11424,10 +11454,10 @@
       <c r="E88" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="F88" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G88" s="13"/>
+      <c r="F88" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G88" s="58"/>
       <c r="H88" s="13" t="s">
         <v>24</v>
       </c>
@@ -11486,10 +11516,10 @@
       <c r="E89" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="F89" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G89" s="13"/>
+      <c r="F89" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G89" s="58"/>
       <c r="H89" s="13" t="s">
         <v>24</v>
       </c>
@@ -11548,10 +11578,10 @@
       <c r="E90" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="F90" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G90" s="13"/>
+      <c r="F90" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="58"/>
       <c r="H90" s="13" t="s">
         <v>24</v>
       </c>
@@ -11608,10 +11638,10 @@
       <c r="E91" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="F91" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G91" s="13"/>
+      <c r="F91" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" s="58"/>
       <c r="H91" s="13" t="s">
         <v>24</v>
       </c>
@@ -11668,10 +11698,10 @@
       <c r="E92" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="F92" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G92" s="13"/>
+      <c r="F92" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" s="58"/>
       <c r="H92" s="13" t="s">
         <v>24</v>
       </c>
@@ -11728,10 +11758,10 @@
       <c r="E93" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="F93" s="13" t="s">
+      <c r="F93" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G93" s="13" t="s">
+      <c r="G93" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H93" s="13" t="s">
@@ -11780,10 +11810,10 @@
       <c r="E94" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="F94" s="13" t="s">
+      <c r="F94" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G94" s="13" t="s">
+      <c r="G94" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H94" s="13" t="s">
@@ -11832,10 +11862,10 @@
       <c r="E95" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="F95" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G95" s="13"/>
+      <c r="F95" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="58"/>
       <c r="H95" s="13" t="s">
         <v>24</v>
       </c>
@@ -11892,10 +11922,10 @@
       <c r="E96" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="F96" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G96" s="13"/>
+      <c r="F96" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="58"/>
       <c r="H96" s="13" t="s">
         <v>24</v>
       </c>
@@ -11952,10 +11982,10 @@
       <c r="E97" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="F97" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G97" s="13"/>
+      <c r="F97" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" s="58"/>
       <c r="H97" s="13" t="s">
         <v>24</v>
       </c>
@@ -12012,10 +12042,10 @@
       <c r="E98" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="F98" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G98" s="13"/>
+      <c r="F98" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="58"/>
       <c r="H98" s="13" t="s">
         <v>24</v>
       </c>
@@ -12072,10 +12102,10 @@
       <c r="E99" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="F99" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G99" s="13"/>
+      <c r="F99" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" s="58"/>
       <c r="H99" s="13" t="s">
         <v>24</v>
       </c>
@@ -12132,10 +12162,10 @@
       <c r="E100" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="F100" s="13" t="s">
+      <c r="F100" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G100" s="13" t="s">
+      <c r="G100" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H100" s="25" t="s">
@@ -12184,10 +12214,10 @@
       <c r="E101" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="F101" s="13" t="s">
+      <c r="F101" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H101" s="26" t="s">
@@ -12236,10 +12266,10 @@
       <c r="E102" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="F102" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G102" s="13"/>
+      <c r="F102" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" s="58"/>
       <c r="H102" s="25" t="s">
         <v>24</v>
       </c>
@@ -12298,10 +12328,10 @@
       <c r="E103" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="F103" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G103" s="13"/>
+      <c r="F103" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" s="58"/>
       <c r="H103" s="26" t="s">
         <v>24</v>
       </c>
@@ -12360,10 +12390,10 @@
       <c r="E104" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="F104" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G104" s="13"/>
+      <c r="F104" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G104" s="58"/>
       <c r="H104" s="25" t="s">
         <v>24</v>
       </c>
@@ -12420,10 +12450,10 @@
       <c r="E105" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="F105" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G105" s="13"/>
+      <c r="F105" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G105" s="58"/>
       <c r="H105" s="26" t="s">
         <v>24</v>
       </c>
@@ -12480,10 +12510,10 @@
       <c r="E106" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="F106" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G106" s="13"/>
+      <c r="F106" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" s="58"/>
       <c r="H106" s="25" t="s">
         <v>24</v>
       </c>
@@ -12542,10 +12572,10 @@
       <c r="E107" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="F107" s="13" t="s">
+      <c r="F107" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G107" s="13" t="s">
+      <c r="G107" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H107" s="26" t="s">
@@ -12594,10 +12624,10 @@
       <c r="E108" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="F108" s="13" t="s">
+      <c r="F108" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G108" s="13" t="s">
+      <c r="G108" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H108" s="25" t="s">
@@ -12646,10 +12676,10 @@
       <c r="E109" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="F109" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G109" s="13"/>
+      <c r="F109" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" s="58"/>
       <c r="H109" s="26" t="s">
         <v>24</v>
       </c>
@@ -12708,10 +12738,10 @@
       <c r="E110" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="F110" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G110" s="13"/>
+      <c r="F110" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G110" s="58"/>
       <c r="H110" s="25" t="s">
         <v>24</v>
       </c>
@@ -12770,10 +12800,10 @@
       <c r="E111" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="F111" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G111" s="13"/>
+      <c r="F111" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" s="58"/>
       <c r="H111" s="26" t="s">
         <v>24</v>
       </c>
@@ -12830,10 +12860,10 @@
       <c r="E112" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="F112" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G112" s="13"/>
+      <c r="F112" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G112" s="58"/>
       <c r="H112" s="25" t="s">
         <v>24</v>
       </c>
@@ -12890,10 +12920,10 @@
       <c r="E113" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="F113" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G113" s="13"/>
+      <c r="F113" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" s="58"/>
       <c r="H113" s="26" t="s">
         <v>24</v>
       </c>
@@ -12950,10 +12980,10 @@
       <c r="E114" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="F114" s="13" t="s">
+      <c r="F114" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G114" s="13" t="s">
+      <c r="G114" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H114" s="13" t="s">
@@ -13002,10 +13032,10 @@
       <c r="E115" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="F115" s="13" t="s">
+      <c r="F115" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G115" s="13" t="s">
+      <c r="G115" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H115" s="13" t="s">
@@ -13054,10 +13084,10 @@
       <c r="E116" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="F116" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G116" s="13"/>
+      <c r="F116" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" s="58"/>
       <c r="H116" s="13" t="s">
         <v>24</v>
       </c>
@@ -13114,10 +13144,10 @@
       <c r="E117" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="F117" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G117" s="13"/>
+      <c r="F117" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G117" s="58"/>
       <c r="H117" s="13" t="s">
         <v>24</v>
       </c>
@@ -13174,10 +13204,10 @@
       <c r="E118" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="F118" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G118" s="13"/>
+      <c r="F118" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" s="58"/>
       <c r="H118" s="13" t="s">
         <v>24</v>
       </c>
@@ -13234,10 +13264,10 @@
       <c r="E119" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="F119" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G119" s="13"/>
+      <c r="F119" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G119" s="58"/>
       <c r="H119" s="13" t="s">
         <v>24</v>
       </c>
@@ -13294,10 +13324,10 @@
       <c r="E120" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="F120" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G120" s="13"/>
+      <c r="F120" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G120" s="58"/>
       <c r="H120" s="13" t="s">
         <v>24</v>
       </c>
@@ -13354,10 +13384,10 @@
       <c r="E121" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="F121" s="13" t="s">
+      <c r="F121" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G121" s="13" t="s">
+      <c r="G121" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H121" s="13" t="s">
@@ -13406,10 +13436,10 @@
       <c r="E122" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="F122" s="13" t="s">
+      <c r="F122" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G122" s="13" t="s">
+      <c r="G122" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H122" s="13" t="s">
@@ -13458,10 +13488,10 @@
       <c r="E123" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="F123" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G123" s="13"/>
+      <c r="F123" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" s="58"/>
       <c r="H123" s="13" t="s">
         <v>24</v>
       </c>
@@ -13518,10 +13548,10 @@
       <c r="E124" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="F124" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G124" s="13"/>
+      <c r="F124" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G124" s="58"/>
       <c r="H124" s="13" t="s">
         <v>24</v>
       </c>
@@ -13578,10 +13608,10 @@
       <c r="E125" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="F125" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G125" s="13"/>
+      <c r="F125" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" s="58"/>
       <c r="H125" s="13" t="s">
         <v>24</v>
       </c>
@@ -13638,10 +13668,10 @@
       <c r="E126" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="F126" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G126" s="13"/>
+      <c r="F126" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G126" s="58"/>
       <c r="H126" s="13" t="s">
         <v>24</v>
       </c>
@@ -13698,10 +13728,10 @@
       <c r="E127" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="F127" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G127" s="13"/>
+      <c r="F127" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G127" s="58"/>
       <c r="H127" s="13" t="s">
         <v>24</v>
       </c>
@@ -13758,10 +13788,10 @@
       <c r="E128" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="F128" s="13" t="s">
+      <c r="F128" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G128" s="13" t="s">
+      <c r="G128" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H128" s="25" t="s">
@@ -13810,10 +13840,10 @@
       <c r="E129" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F129" s="13" t="s">
+      <c r="F129" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G129" s="13" t="s">
+      <c r="G129" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H129" s="26" t="s">
@@ -13862,10 +13892,10 @@
       <c r="E130" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="F130" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G130" s="13"/>
+      <c r="F130" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G130" s="58"/>
       <c r="H130" s="25" t="s">
         <v>24</v>
       </c>
@@ -13922,10 +13952,10 @@
       <c r="E131" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="F131" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G131" s="13"/>
+      <c r="F131" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G131" s="58"/>
       <c r="H131" s="26" t="s">
         <v>24</v>
       </c>
@@ -13982,10 +14012,10 @@
       <c r="E132" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="F132" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G132" s="13"/>
+      <c r="F132" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" s="58"/>
       <c r="H132" s="25" t="s">
         <v>24</v>
       </c>
@@ -14042,10 +14072,10 @@
       <c r="E133" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="F133" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G133" s="13"/>
+      <c r="F133" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G133" s="58"/>
       <c r="H133" s="26" t="s">
         <v>24</v>
       </c>
@@ -14102,10 +14132,10 @@
       <c r="E134" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="F134" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G134" s="13"/>
+      <c r="F134" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G134" s="58"/>
       <c r="H134" s="25" t="s">
         <v>24</v>
       </c>
@@ -14162,10 +14192,10 @@
       <c r="E135" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="F135" s="13" t="s">
+      <c r="F135" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G135" s="13" t="s">
+      <c r="G135" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H135" s="26" t="s">
@@ -14214,10 +14244,10 @@
       <c r="E136" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="F136" s="13" t="s">
+      <c r="F136" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G136" s="13" t="s">
+      <c r="G136" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H136" s="25" t="s">
@@ -14266,10 +14296,10 @@
       <c r="E137" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="F137" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G137" s="13"/>
+      <c r="F137" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G137" s="58"/>
       <c r="H137" s="26" t="s">
         <v>24</v>
       </c>
@@ -14326,10 +14356,10 @@
       <c r="E138" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="F138" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G138" s="13"/>
+      <c r="F138" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G138" s="58"/>
       <c r="H138" s="25" t="s">
         <v>24</v>
       </c>
@@ -14386,10 +14416,10 @@
       <c r="E139" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="F139" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G139" s="13"/>
+      <c r="F139" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G139" s="58"/>
       <c r="H139" s="26" t="s">
         <v>24</v>
       </c>
@@ -14446,10 +14476,10 @@
       <c r="E140" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="F140" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G140" s="13"/>
+      <c r="F140" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G140" s="58"/>
       <c r="H140" s="25" t="s">
         <v>24</v>
       </c>
@@ -14506,10 +14536,10 @@
       <c r="E141" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="F141" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G141" s="13"/>
+      <c r="F141" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G141" s="58"/>
       <c r="H141" s="26" t="s">
         <v>24</v>
       </c>
@@ -14566,10 +14596,10 @@
       <c r="E142" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="F142" s="13" t="s">
+      <c r="F142" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G142" s="13" t="s">
+      <c r="G142" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H142" s="13" t="s">
@@ -14618,10 +14648,10 @@
       <c r="E143" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="F143" s="13" t="s">
+      <c r="F143" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="G143" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H143" s="13" t="s">
@@ -14670,10 +14700,10 @@
       <c r="E144" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="F144" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G144" s="13"/>
+      <c r="F144" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G144" s="58"/>
       <c r="H144" s="13" t="s">
         <v>24</v>
       </c>
@@ -14730,10 +14760,10 @@
       <c r="E145" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="F145" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G145" s="13"/>
+      <c r="F145" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G145" s="58"/>
       <c r="H145" s="13" t="s">
         <v>24</v>
       </c>
@@ -14790,10 +14820,10 @@
       <c r="E146" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="F146" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G146" s="13"/>
+      <c r="F146" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G146" s="58"/>
       <c r="H146" s="13" t="s">
         <v>24</v>
       </c>
@@ -14850,10 +14880,10 @@
       <c r="E147" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="F147" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G147" s="13"/>
+      <c r="F147" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G147" s="58"/>
       <c r="H147" s="13" t="s">
         <v>24</v>
       </c>
@@ -14910,10 +14940,10 @@
       <c r="E148" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="F148" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G148" s="13"/>
+      <c r="F148" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G148" s="58"/>
       <c r="H148" s="13" t="s">
         <v>24</v>
       </c>
@@ -14970,10 +15000,10 @@
       <c r="E149" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="F149" s="13" t="s">
+      <c r="F149" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G149" s="13" t="s">
+      <c r="G149" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H149" s="13" t="s">
@@ -15022,10 +15052,10 @@
       <c r="E150" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="F150" s="13" t="s">
+      <c r="F150" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G150" s="13" t="s">
+      <c r="G150" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H150" s="13" t="s">
@@ -15074,10 +15104,10 @@
       <c r="E151" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="F151" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G151" s="13"/>
+      <c r="F151" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G151" s="58"/>
       <c r="H151" s="13" t="s">
         <v>24</v>
       </c>
@@ -15134,10 +15164,10 @@
       <c r="E152" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="F152" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G152" s="13"/>
+      <c r="F152" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G152" s="58"/>
       <c r="H152" s="13" t="s">
         <v>24</v>
       </c>
@@ -15194,10 +15224,10 @@
       <c r="E153" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="F153" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G153" s="13"/>
+      <c r="F153" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G153" s="58"/>
       <c r="H153" s="13" t="s">
         <v>24</v>
       </c>
@@ -15254,10 +15284,10 @@
       <c r="E154" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="F154" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G154" s="13"/>
+      <c r="F154" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G154" s="58"/>
       <c r="H154" s="13" t="s">
         <v>24</v>
       </c>
@@ -15314,10 +15344,10 @@
       <c r="E155" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="F155" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G155" s="13"/>
+      <c r="F155" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G155" s="58"/>
       <c r="H155" s="13" t="s">
         <v>24</v>
       </c>
@@ -15374,10 +15404,10 @@
       <c r="E156" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="F156" s="13" t="s">
+      <c r="F156" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G156" s="13" t="s">
+      <c r="G156" s="58" t="s">
         <v>88</v>
       </c>
       <c r="H156" s="25" t="s">
@@ -15426,10 +15456,10 @@
       <c r="E157" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="F157" s="13" t="s">
+      <c r="F157" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="G157" s="13" t="s">
+      <c r="G157" s="58" t="s">
         <v>110</v>
       </c>
       <c r="H157" s="26" t="s">
@@ -15478,10 +15508,10 @@
       <c r="E158" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="F158" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G158" s="13"/>
+      <c r="F158" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G158" s="58"/>
       <c r="H158" s="25" t="s">
         <v>24</v>
       </c>
@@ -15538,10 +15568,10 @@
       <c r="E159" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="F159" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G159" s="13"/>
+      <c r="F159" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G159" s="58"/>
       <c r="H159" s="26" t="s">
         <v>24</v>
       </c>
@@ -15598,10 +15628,10 @@
       <c r="E160" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="F160" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G160" s="13"/>
+      <c r="F160" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G160" s="58"/>
       <c r="H160" s="25" t="s">
         <v>24</v>
       </c>
@@ -15658,10 +15688,10 @@
       <c r="E161" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="F161" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G161" s="13"/>
+      <c r="F161" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G161" s="58"/>
       <c r="H161" s="26" t="s">
         <v>24</v>
       </c>
@@ -15718,10 +15748,10 @@
       <c r="E162" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="F162" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G162" s="13"/>
+      <c r="F162" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G162" s="58"/>
       <c r="H162" s="31" t="s">
         <v>24</v>
       </c>
@@ -15768,8 +15798,8 @@
       <c r="C163" s="13"/>
       <c r="D163" s="13"/>
       <c r="E163" s="13"/>
-      <c r="F163" s="13"/>
-      <c r="G163" s="13"/>
+      <c r="F163" s="58"/>
+      <c r="G163" s="58"/>
       <c r="H163" s="13"/>
       <c r="I163" s="25"/>
       <c r="J163" s="25"/>
@@ -15790,8 +15820,8 @@
       <c r="C164" s="13"/>
       <c r="D164" s="13"/>
       <c r="E164" s="13"/>
-      <c r="F164" s="13"/>
-      <c r="G164" s="13"/>
+      <c r="F164" s="58"/>
+      <c r="G164" s="58"/>
       <c r="H164" s="13"/>
       <c r="I164" s="26"/>
       <c r="J164" s="26"/>
@@ -15812,8 +15842,8 @@
       <c r="C165" s="13"/>
       <c r="D165" s="13"/>
       <c r="E165" s="13"/>
-      <c r="F165" s="13"/>
-      <c r="G165" s="13"/>
+      <c r="F165" s="58"/>
+      <c r="G165" s="58"/>
       <c r="H165" s="13"/>
       <c r="I165" s="25"/>
       <c r="J165" s="25"/>
@@ -15834,8 +15864,8 @@
       <c r="C166" s="13"/>
       <c r="D166" s="13"/>
       <c r="E166" s="13"/>
-      <c r="F166" s="13"/>
-      <c r="G166" s="13"/>
+      <c r="F166" s="58"/>
+      <c r="G166" s="58"/>
       <c r="H166" s="13"/>
       <c r="I166" s="26"/>
       <c r="J166" s="26"/>
@@ -15856,8 +15886,8 @@
       <c r="C167" s="13"/>
       <c r="D167" s="13"/>
       <c r="E167" s="13"/>
-      <c r="F167" s="13"/>
-      <c r="G167" s="13"/>
+      <c r="F167" s="58"/>
+      <c r="G167" s="58"/>
       <c r="H167" s="13"/>
       <c r="I167" s="25"/>
       <c r="J167" s="25"/>
@@ -15878,8 +15908,8 @@
       <c r="C168" s="13"/>
       <c r="D168" s="13"/>
       <c r="E168" s="13"/>
-      <c r="F168" s="13"/>
-      <c r="G168" s="13"/>
+      <c r="F168" s="58"/>
+      <c r="G168" s="58"/>
       <c r="H168" s="13"/>
       <c r="I168" s="26"/>
       <c r="J168" s="26"/>
@@ -15900,8 +15930,8 @@
       <c r="C169" s="13"/>
       <c r="D169" s="13"/>
       <c r="E169" s="13"/>
-      <c r="F169" s="13"/>
-      <c r="G169" s="13"/>
+      <c r="F169" s="58"/>
+      <c r="G169" s="58"/>
       <c r="H169" s="13"/>
       <c r="I169" s="31"/>
       <c r="J169" s="31"/>
@@ -15922,8 +15952,8 @@
       <c r="C170" s="13"/>
       <c r="D170" s="13"/>
       <c r="E170" s="13"/>
-      <c r="F170" s="13"/>
-      <c r="G170" s="13"/>
+      <c r="F170" s="58"/>
+      <c r="G170" s="58"/>
       <c r="H170" s="13"/>
       <c r="I170" s="25"/>
       <c r="J170" s="25"/>
@@ -15944,8 +15974,8 @@
       <c r="C171" s="13"/>
       <c r="D171" s="13"/>
       <c r="E171" s="13"/>
-      <c r="F171" s="13"/>
-      <c r="G171" s="13"/>
+      <c r="F171" s="58"/>
+      <c r="G171" s="58"/>
       <c r="H171" s="13"/>
       <c r="I171" s="26"/>
       <c r="J171" s="26"/>
@@ -15966,8 +15996,8 @@
       <c r="C172" s="13"/>
       <c r="D172" s="13"/>
       <c r="E172" s="13"/>
-      <c r="F172" s="13"/>
-      <c r="G172" s="13"/>
+      <c r="F172" s="58"/>
+      <c r="G172" s="58"/>
       <c r="H172" s="13"/>
       <c r="I172" s="25"/>
       <c r="J172" s="25"/>
@@ -15988,8 +16018,8 @@
       <c r="C173" s="13"/>
       <c r="D173" s="13"/>
       <c r="E173" s="13"/>
-      <c r="F173" s="13"/>
-      <c r="G173" s="13"/>
+      <c r="F173" s="58"/>
+      <c r="G173" s="58"/>
       <c r="H173" s="13"/>
       <c r="I173" s="26"/>
       <c r="J173" s="26"/>
@@ -16010,8 +16040,8 @@
       <c r="C174" s="13"/>
       <c r="D174" s="13"/>
       <c r="E174" s="13"/>
-      <c r="F174" s="13"/>
-      <c r="G174" s="13"/>
+      <c r="F174" s="58"/>
+      <c r="G174" s="58"/>
       <c r="H174" s="13"/>
       <c r="I174" s="25"/>
       <c r="J174" s="25"/>
@@ -16032,8 +16062,8 @@
       <c r="C175" s="13"/>
       <c r="D175" s="13"/>
       <c r="E175" s="13"/>
-      <c r="F175" s="13"/>
-      <c r="G175" s="13"/>
+      <c r="F175" s="58"/>
+      <c r="G175" s="58"/>
       <c r="H175" s="13"/>
       <c r="I175" s="26"/>
       <c r="J175" s="26"/>
@@ -16054,8 +16084,8 @@
       <c r="C176" s="13"/>
       <c r="D176" s="13"/>
       <c r="E176" s="13"/>
-      <c r="F176" s="13"/>
-      <c r="G176" s="13"/>
+      <c r="F176" s="58"/>
+      <c r="G176" s="58"/>
       <c r="H176" s="13"/>
       <c r="I176" s="31"/>
       <c r="J176" s="31"/>
@@ -16076,8 +16106,8 @@
       <c r="C177" s="13"/>
       <c r="D177" s="13"/>
       <c r="E177" s="13"/>
-      <c r="F177" s="13"/>
-      <c r="G177" s="13"/>
+      <c r="F177" s="58"/>
+      <c r="G177" s="58"/>
       <c r="H177" s="13"/>
       <c r="I177" s="13"/>
       <c r="J177" s="13"/>
@@ -16098,8 +16128,8 @@
       <c r="C178" s="13"/>
       <c r="D178" s="13"/>
       <c r="E178" s="13"/>
-      <c r="F178" s="13"/>
-      <c r="G178" s="13"/>
+      <c r="F178" s="58"/>
+      <c r="G178" s="58"/>
       <c r="H178" s="13"/>
       <c r="I178" s="13"/>
       <c r="J178" s="13"/>
@@ -16120,8 +16150,8 @@
       <c r="C179" s="13"/>
       <c r="D179" s="13"/>
       <c r="E179" s="13"/>
-      <c r="F179" s="13"/>
-      <c r="G179" s="13"/>
+      <c r="F179" s="58"/>
+      <c r="G179" s="58"/>
       <c r="H179" s="13"/>
       <c r="I179" s="13"/>
       <c r="J179" s="13"/>
@@ -16142,8 +16172,8 @@
       <c r="C180" s="13"/>
       <c r="D180" s="13"/>
       <c r="E180" s="13"/>
-      <c r="F180" s="13"/>
-      <c r="G180" s="13"/>
+      <c r="F180" s="58"/>
+      <c r="G180" s="58"/>
       <c r="H180" s="13"/>
       <c r="I180" s="13"/>
       <c r="J180" s="13"/>
@@ -16164,8 +16194,8 @@
       <c r="C181" s="13"/>
       <c r="D181" s="13"/>
       <c r="E181" s="13"/>
-      <c r="F181" s="13"/>
-      <c r="G181" s="13"/>
+      <c r="F181" s="58"/>
+      <c r="G181" s="58"/>
       <c r="H181" s="13"/>
       <c r="I181" s="13"/>
       <c r="J181" s="13"/>
@@ -16186,8 +16216,8 @@
       <c r="C182" s="13"/>
       <c r="D182" s="13"/>
       <c r="E182" s="13"/>
-      <c r="F182" s="13"/>
-      <c r="G182" s="13"/>
+      <c r="F182" s="58"/>
+      <c r="G182" s="58"/>
       <c r="H182" s="13"/>
       <c r="I182" s="13"/>
       <c r="J182" s="13"/>
@@ -16208,8 +16238,8 @@
       <c r="C183" s="13"/>
       <c r="D183" s="13"/>
       <c r="E183" s="13"/>
-      <c r="F183" s="13"/>
-      <c r="G183" s="13"/>
+      <c r="F183" s="58"/>
+      <c r="G183" s="58"/>
       <c r="H183" s="13"/>
       <c r="I183" s="13"/>
       <c r="J183" s="13"/>
@@ -16230,8 +16260,8 @@
       <c r="C184" s="13"/>
       <c r="D184" s="13"/>
       <c r="E184" s="13"/>
-      <c r="F184" s="13"/>
-      <c r="G184" s="13"/>
+      <c r="F184" s="58"/>
+      <c r="G184" s="58"/>
       <c r="H184" s="13"/>
       <c r="I184" s="13"/>
       <c r="J184" s="13"/>
@@ -16252,8 +16282,8 @@
       <c r="C185" s="13"/>
       <c r="D185" s="13"/>
       <c r="E185" s="13"/>
-      <c r="F185" s="13"/>
-      <c r="G185" s="13"/>
+      <c r="F185" s="58"/>
+      <c r="G185" s="58"/>
       <c r="H185" s="13"/>
       <c r="I185" s="13"/>
       <c r="J185" s="13"/>
@@ -16274,8 +16304,8 @@
       <c r="C186" s="13"/>
       <c r="D186" s="13"/>
       <c r="E186" s="13"/>
-      <c r="F186" s="13"/>
-      <c r="G186" s="13"/>
+      <c r="F186" s="58"/>
+      <c r="G186" s="58"/>
       <c r="H186" s="13"/>
       <c r="I186" s="13"/>
       <c r="J186" s="13"/>
@@ -16296,8 +16326,8 @@
       <c r="C187" s="13"/>
       <c r="D187" s="13"/>
       <c r="E187" s="13"/>
-      <c r="F187" s="13"/>
-      <c r="G187" s="13"/>
+      <c r="F187" s="58"/>
+      <c r="G187" s="58"/>
       <c r="H187" s="13"/>
       <c r="I187" s="13"/>
       <c r="J187" s="13"/>
@@ -16318,8 +16348,8 @@
       <c r="C188" s="13"/>
       <c r="D188" s="13"/>
       <c r="E188" s="13"/>
-      <c r="F188" s="13"/>
-      <c r="G188" s="13"/>
+      <c r="F188" s="58"/>
+      <c r="G188" s="58"/>
       <c r="H188" s="13"/>
       <c r="I188" s="13"/>
       <c r="J188" s="13"/>
@@ -16340,8 +16370,8 @@
       <c r="C189" s="13"/>
       <c r="D189" s="13"/>
       <c r="E189" s="13"/>
-      <c r="F189" s="13"/>
-      <c r="G189" s="13"/>
+      <c r="F189" s="58"/>
+      <c r="G189" s="58"/>
       <c r="H189" s="13"/>
       <c r="I189" s="13"/>
       <c r="J189" s="13"/>
@@ -16362,8 +16392,8 @@
       <c r="C190" s="13"/>
       <c r="D190" s="13"/>
       <c r="E190" s="13"/>
-      <c r="F190" s="13"/>
-      <c r="G190" s="13"/>
+      <c r="F190" s="58"/>
+      <c r="G190" s="58"/>
       <c r="H190" s="13"/>
       <c r="I190" s="13"/>
       <c r="J190" s="13"/>
@@ -16384,8 +16414,8 @@
       <c r="C191" s="13"/>
       <c r="D191" s="13"/>
       <c r="E191" s="13"/>
-      <c r="F191" s="13"/>
-      <c r="G191" s="13"/>
+      <c r="F191" s="58"/>
+      <c r="G191" s="58"/>
       <c r="H191" s="13"/>
       <c r="I191" s="13"/>
       <c r="J191" s="13"/>
@@ -16406,8 +16436,8 @@
       <c r="C192" s="13"/>
       <c r="D192" s="13"/>
       <c r="E192" s="13"/>
-      <c r="F192" s="13"/>
-      <c r="G192" s="13"/>
+      <c r="F192" s="58"/>
+      <c r="G192" s="58"/>
       <c r="H192" s="13"/>
       <c r="I192" s="13"/>
       <c r="J192" s="13"/>
@@ -16428,8 +16458,8 @@
       <c r="C193" s="13"/>
       <c r="D193" s="13"/>
       <c r="E193" s="13"/>
-      <c r="F193" s="13"/>
-      <c r="G193" s="13"/>
+      <c r="F193" s="58"/>
+      <c r="G193" s="58"/>
       <c r="H193" s="13"/>
       <c r="I193" s="13"/>
       <c r="J193" s="13"/>
@@ -16450,8 +16480,8 @@
       <c r="C194" s="13"/>
       <c r="D194" s="13"/>
       <c r="E194" s="13"/>
-      <c r="F194" s="13"/>
-      <c r="G194" s="13"/>
+      <c r="F194" s="58"/>
+      <c r="G194" s="58"/>
       <c r="H194" s="13"/>
       <c r="I194" s="13"/>
       <c r="J194" s="13"/>
@@ -16472,8 +16502,8 @@
       <c r="C195" s="13"/>
       <c r="D195" s="13"/>
       <c r="E195" s="13"/>
-      <c r="F195" s="13"/>
-      <c r="G195" s="13"/>
+      <c r="F195" s="58"/>
+      <c r="G195" s="58"/>
       <c r="H195" s="13"/>
       <c r="I195" s="13"/>
       <c r="J195" s="13"/>
@@ -16494,8 +16524,8 @@
       <c r="C196" s="13"/>
       <c r="D196" s="13"/>
       <c r="E196" s="13"/>
-      <c r="F196" s="13"/>
-      <c r="G196" s="13"/>
+      <c r="F196" s="58"/>
+      <c r="G196" s="58"/>
       <c r="H196" s="13"/>
       <c r="I196" s="13"/>
       <c r="J196" s="13"/>
@@ -16516,8 +16546,8 @@
       <c r="C197" s="13"/>
       <c r="D197" s="13"/>
       <c r="E197" s="13"/>
-      <c r="F197" s="13"/>
-      <c r="G197" s="13"/>
+      <c r="F197" s="58"/>
+      <c r="G197" s="58"/>
       <c r="H197" s="13"/>
       <c r="I197" s="13"/>
       <c r="J197" s="13"/>
@@ -16538,8 +16568,8 @@
       <c r="C198" s="13"/>
       <c r="D198" s="13"/>
       <c r="E198" s="13"/>
-      <c r="F198" s="13"/>
-      <c r="G198" s="13"/>
+      <c r="F198" s="58"/>
+      <c r="G198" s="58"/>
       <c r="H198" s="13"/>
       <c r="I198" s="13"/>
       <c r="J198" s="13"/>
@@ -16560,8 +16590,8 @@
       <c r="C199" s="13"/>
       <c r="D199" s="13"/>
       <c r="E199" s="13"/>
-      <c r="F199" s="13"/>
-      <c r="G199" s="13"/>
+      <c r="F199" s="58"/>
+      <c r="G199" s="58"/>
       <c r="H199" s="13"/>
       <c r="I199" s="13"/>
       <c r="J199" s="13"/>
@@ -16582,8 +16612,8 @@
       <c r="C200" s="13"/>
       <c r="D200" s="13"/>
       <c r="E200" s="13"/>
-      <c r="F200" s="13"/>
-      <c r="G200" s="13"/>
+      <c r="F200" s="58"/>
+      <c r="G200" s="58"/>
       <c r="H200" s="13"/>
       <c r="I200" s="13"/>
       <c r="J200" s="13"/>
@@ -16604,8 +16634,8 @@
       <c r="C201" s="13"/>
       <c r="D201" s="13"/>
       <c r="E201" s="13"/>
-      <c r="F201" s="13"/>
-      <c r="G201" s="13"/>
+      <c r="F201" s="58"/>
+      <c r="G201" s="58"/>
       <c r="H201" s="13"/>
       <c r="I201" s="13"/>
       <c r="J201" s="13"/>
@@ -16623,28 +16653,28 @@
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="M4:M8">
-    <cfRule type="duplicateValues" dxfId="9" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:M24 M32:M52 M60:M80 M88:M101 M109:M162">
-    <cfRule type="duplicateValues" dxfId="8" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:M29">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53:M57">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M81:M85">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M102:M106">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M177:M181">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M182:M186">
-    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="R4" r:id="rId1" xr:uid="{D9569CBD-1C1A-4EF0-9D90-B70EA928D150}"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D757572-C1F1-4BA0-99D4-D45A8475C7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAD1E99-123F-4510-A20F-492BEB56DCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6873,7 +6873,7 @@
         <v>474</v>
       </c>
       <c r="V9" s="13" t="s">
-        <v>110</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
@@ -6925,7 +6925,7 @@
         <v>474</v>
       </c>
       <c r="V10" s="13" t="s">
-        <v>88</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAD1E99-123F-4510-A20F-492BEB56DCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF4C10D-78D2-4330-ABDB-71265DE7AD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="478">
   <si>
     <t>Description</t>
   </si>
@@ -2412,6 +2412,12 @@
   </si>
   <si>
     <t>Hotspot Navigation</t>
+  </si>
+  <si>
+    <t>Check 21 Loading or no</t>
+  </si>
+  <si>
+    <t>"Hey, Hidden Slide 21"</t>
   </si>
 </sst>
 </file>
@@ -14225,7 +14231,7 @@
         <v>474</v>
       </c>
       <c r="V135" s="13" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
@@ -14277,7 +14283,7 @@
         <v>474</v>
       </c>
       <c r="V136" s="13" t="s">
-        <v>88</v>
+        <v>247</v>
       </c>
     </row>
     <row r="137" spans="1:22" ht="12.6" x14ac:dyDescent="0.4">
@@ -14330,7 +14336,7 @@
         <v>69</v>
       </c>
       <c r="S137" s="30" t="s">
-        <v>117</v>
+        <v>476</v>
       </c>
       <c r="T137" s="13" t="b">
         <v>1</v>
@@ -14389,8 +14395,8 @@
       <c r="R138" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="S138" s="29" t="s">
-        <v>118</v>
+      <c r="S138" s="30" t="s">
+        <v>476</v>
       </c>
       <c r="T138" s="13" t="b">
         <v>1</v>
@@ -14450,7 +14456,7 @@
         <v>69</v>
       </c>
       <c r="S139" s="30" t="s">
-        <v>120</v>
+        <v>476</v>
       </c>
       <c r="T139" s="13" t="b">
         <v>1</v>
@@ -14509,8 +14515,8 @@
       <c r="R140" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="S140" s="29" t="s">
-        <v>119</v>
+      <c r="S140" s="30" t="s">
+        <v>476</v>
       </c>
       <c r="T140" s="13" t="b">
         <v>1</v>
@@ -14570,7 +14576,7 @@
         <v>69</v>
       </c>
       <c r="S141" s="30" t="s">
-        <v>121</v>
+        <v>476</v>
       </c>
       <c r="T141" s="13" t="b">
         <v>1</v>
@@ -14734,7 +14740,7 @@
         <v>69</v>
       </c>
       <c r="S144" s="13" t="s">
-        <v>117</v>
+        <v>477</v>
       </c>
       <c r="T144" s="13" t="b">
         <v>1</v>
@@ -14794,7 +14800,7 @@
         <v>69</v>
       </c>
       <c r="S145" s="13" t="s">
-        <v>118</v>
+        <v>477</v>
       </c>
       <c r="T145" s="13" t="b">
         <v>1</v>
@@ -14854,7 +14860,7 @@
         <v>69</v>
       </c>
       <c r="S146" s="13" t="s">
-        <v>120</v>
+        <v>477</v>
       </c>
       <c r="T146" s="13" t="b">
         <v>1</v>
@@ -14914,7 +14920,7 @@
         <v>69</v>
       </c>
       <c r="S147" s="13" t="s">
-        <v>119</v>
+        <v>477</v>
       </c>
       <c r="T147" s="13" t="b">
         <v>1</v>
@@ -14974,7 +14980,7 @@
         <v>69</v>
       </c>
       <c r="S148" s="13" t="s">
-        <v>121</v>
+        <v>477</v>
       </c>
       <c r="T148" s="13" t="b">
         <v>1</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FD78BB-3090-4F22-926A-FFAFEF626998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E3C5DE-24E2-40E6-B632-1227B5D366C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="476">
   <si>
     <t>Description</t>
   </si>
@@ -2409,6 +2409,9 @@
   </si>
   <si>
     <t>"Hey, Hidden Slide 21"</t>
+  </si>
+  <si>
+    <t>[https://www.ikea.com/sa/en/images/products/varvial-fitted-sheet-blue__1243833_pe920981_s5.jpg],[https://www.ikea.com/sa/en/images/products/praktvial-bedspread-off-white__1249510_pe923370_s5.jpg],[https://i.imgur.com/mRdMBZA.png]</t>
   </si>
 </sst>
 </file>
@@ -2907,54 +2910,6 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF404040"/>
-        <name val="Inter"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF404040"/>
-        <name val="Inter"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF404040"/>
         <name val="Inter"/>
@@ -3376,6 +3331,54 @@
         <name val="Inter"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4033,46 +4036,46 @@
     <tableColumn id="1" xr3:uid="{8DAC3286-642C-4DB0-A8B8-5C7BF99FB11F}" name="SceneID" dataDxfId="37"/>
     <tableColumn id="19" xr3:uid="{79CDA865-39EA-4125-85E4-F3D78AC4893A}" name="Hotspot ID" dataDxfId="36"/>
     <tableColumn id="2" xr3:uid="{4BDAA051-81D1-400A-A39C-7D867ECB0341}" name="Hotspot Name" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{F981A75D-66D8-4E38-82C9-6DCD2B17FC3E}" name="Hotspot type" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{787CBE39-1923-41F6-9372-CA2D56C6E632}" name="Hotspot Navigation" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{878E0985-EA91-45B5-B984-8D637B8FAC1A}" name="StyleID/CustomCSS" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{5750A58C-6161-4401-AC72-9E158AEE5857}" name="Pitch" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{BE566E3E-5C22-4617-9723-BF12A43249DE}" name="Yaw" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{5A307C93-AF79-4FC7-8CD0-D327558EE7A8}" name="Rotation" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{CDA04002-4AE2-42E0-BE80-D1092B841D6F}" name="Custom Hotspot URL" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{B760F4E6-236A-47E6-B68A-77D0E77DEBE8}" name="Hotspot HoverImage URL" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{54ECD990-86C2-40C1-B48B-2D7A81FF92B9}" name="Title" dataDxfId="28"/>
-    <tableColumn id="12" xr3:uid="{945E3504-CBC4-4B71-87A6-409E0A7C093F}" name="Description" dataDxfId="27"/>
-    <tableColumn id="17" xr3:uid="{3055829F-DDE9-4492-B64F-EA9B27D86F0D}" name="SR Currancy Symbol image URL" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{37499370-9458-4DA7-9E1E-492AC195DCB2}" name="Price" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{51AF3A7A-9E37-4EC3-95E2-04EA97CB0A3F}" name="Avatar Image URL" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{62D296DE-BD87-415D-A7A9-7B26ADBEBF6D}" name="Voice over" dataDxfId="23"/>
-    <tableColumn id="18" xr3:uid="{48873D82-692C-4357-B503-4E9A267EC815}" name="Hotspot Hover Active" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{F981A75D-66D8-4E38-82C9-6DCD2B17FC3E}" name="Hotspot type" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{787CBE39-1923-41F6-9372-CA2D56C6E632}" name="Hotspot Navigation" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{878E0985-EA91-45B5-B984-8D637B8FAC1A}" name="StyleID/CustomCSS" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{5750A58C-6161-4401-AC72-9E158AEE5857}" name="Pitch" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{BE566E3E-5C22-4617-9723-BF12A43249DE}" name="Yaw" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{5A307C93-AF79-4FC7-8CD0-D327558EE7A8}" name="Rotation" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{CDA04002-4AE2-42E0-BE80-D1092B841D6F}" name="Custom Hotspot URL" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{B760F4E6-236A-47E6-B68A-77D0E77DEBE8}" name="Hotspot HoverImage URL" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{54ECD990-86C2-40C1-B48B-2D7A81FF92B9}" name="Title" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{945E3504-CBC4-4B71-87A6-409E0A7C093F}" name="Description" dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{3055829F-DDE9-4492-B64F-EA9B27D86F0D}" name="SR Currancy Symbol image URL" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{37499370-9458-4DA7-9E1E-492AC195DCB2}" name="Price" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{51AF3A7A-9E37-4EC3-95E2-04EA97CB0A3F}" name="Avatar Image URL" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{62D296DE-BD87-415D-A7A9-7B26ADBEBF6D}" name="Voice over" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{48873D82-692C-4357-B503-4E9A267EC815}" name="Hotspot Hover Active" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:E3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="17" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="15" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:B4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6477,8 +6480,8 @@
       <c r="L4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>140</v>
+      <c r="M4" s="16" t="s">
+        <v>475</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>108</v>
@@ -6537,7 +6540,7 @@
       <c r="L5" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="16" t="s">
         <v>141</v>
       </c>
       <c r="N5" s="13" t="s">
@@ -16037,10 +16040,11 @@
     <hyperlink ref="L33" r:id="rId148" xr:uid="{8D220609-2D34-48AD-A30F-42CE121090A0}"/>
     <hyperlink ref="S7" r:id="rId149" xr:uid="{E9C9AC5C-FB44-4DF1-9A5A-F63125F706C5}"/>
     <hyperlink ref="S11" r:id="rId150" xr:uid="{0C1812DF-CB74-4A1D-A893-DCD676F1D4E4}"/>
+    <hyperlink ref="M5" r:id="rId151" xr:uid="{1759D407-EB67-4B35-AE20-16AA58E37411}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId151"/>
+    <tablePart r:id="rId152"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E3C5DE-24E2-40E6-B632-1227B5D366C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B536C11-F5E3-4877-8334-423F7E77264A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="477">
   <si>
     <t>Description</t>
   </si>
@@ -2412,6 +2412,9 @@
   </si>
   <si>
     <t>[https://www.ikea.com/sa/en/images/products/varvial-fitted-sheet-blue__1243833_pe920981_s5.jpg],[https://www.ikea.com/sa/en/images/products/praktvial-bedspread-off-white__1249510_pe923370_s5.jpg],[https://i.imgur.com/mRdMBZA.png]</t>
+  </si>
+  <si>
+    <t>[https://images.homedepot-static.com/lifestyleimages/1024x682/85912049-ef4c-4208-94ba-7c4776a420290.jpeg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-3.jpg],https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-5.jpg]</t>
   </si>
 </sst>
 </file>
@@ -2808,7 +2811,17 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3993,89 +4006,89 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B3BD341F-A9EE-47D0-8C60-8860D1D4E7C2}" name="Table2" displayName="Table2" ref="A1:Z24" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B3BD341F-A9EE-47D0-8C60-8860D1D4E7C2}" name="Table2" displayName="Table2" ref="A1:Z24" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
   <autoFilter ref="A1:Z24" xr:uid="{B3BD341F-A9EE-47D0-8C60-8860D1D4E7C2}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{3F466341-C4E1-4EB6-AED5-B3FAB9FFDB04}" name="FloorGroupName" dataDxfId="67"/>
-    <tableColumn id="15" xr3:uid="{95822792-7ABB-423C-82E9-6D0F0DB26332}" name="Section2" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{F5DD3373-E684-418A-9C83-7C1DAF3E703C}" name="SceneID" dataDxfId="65"/>
-    <tableColumn id="16" xr3:uid="{C2E35991-5AAE-4454-B112-E210FA45B5B1}" name="Scene Order" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{1B214639-BDF9-4E07-8399-162C51178468}" name="SceneDisplayName" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{5C39FDEC-5B6B-4B37-A3D9-2FF0E84DB986}" name="PanoramaURL" dataDxfId="62" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{65443BFD-E63B-46ED-9BF9-60D1AEFBE995}" name="LogoURL" dataDxfId="61" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{479ED09E-25DD-46EC-B69E-1861960DEAC2}" name="Background music URL" dataDxfId="60" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{57935DA2-FBD2-4844-9037-7137E42964CE}" name="Background music Active" dataDxfId="59"/>
-    <tableColumn id="17" xr3:uid="{C4D373A5-CE54-491B-9807-1166BCDEB305}" name="Background Voice Over URL" dataDxfId="58" dataCellStyle="Hyperlink"/>
-    <tableColumn id="19" xr3:uid="{6234DADD-60C1-4FBC-8721-B0C377137173}" name="VC Actor Avatar URL" dataDxfId="57" dataCellStyle="Hyperlink"/>
-    <tableColumn id="20" xr3:uid="{F0BFA0EF-DF4E-4896-A5FE-58501F313D77}" name="VC Actor image BG Color" dataDxfId="56" dataCellStyle="Hyperlink"/>
-    <tableColumn id="18" xr3:uid="{F78E9396-7CBD-4F84-9A86-30BE5F251A4F}" name="Background Voice Over Active" dataDxfId="55" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{9659F453-2FDD-4F12-8239-DD98421E212B}" name="InitialPitch" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{CE8A6BA7-78A8-4B32-A5C9-820E789064BA}" name="InitialYaw" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{5EF27361-EA21-49B6-B21B-8017A9DE476E}" name="InitialZoom" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{F89939D0-37DB-4307-92F3-5C4A93A00D1C}" name="AutoRotate" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{841A2892-EB40-41E4-970A-069A5F80AE6F}" name="NorthOffset" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{7990DFCD-7C68-4753-865B-59877205AB47}" name="SceneID Active" dataDxfId="49"/>
-    <tableColumn id="21" xr3:uid="{A8F84F3B-00B3-4D3C-9D9A-1341A9EFEE4D}" name="Hotspot ID" dataDxfId="48"/>
-    <tableColumn id="22" xr3:uid="{D4B98C57-A117-462D-AE9B-DEC916B1362B}" name="Hotspot Active" dataDxfId="47"/>
-    <tableColumn id="23" xr3:uid="{81D4978B-66B3-415D-8A0B-3C39AEABC8F4}" name="Floor Map" dataDxfId="46"/>
-    <tableColumn id="26" xr3:uid="{9B34F8E8-0E7B-400B-82B0-9AB62121F087}" name="Floor map Details" dataDxfId="45"/>
-    <tableColumn id="24" xr3:uid="{9B53D36C-2C6E-4874-90BE-0AE384CE5D57}" name="Floor Map Active" dataDxfId="44"/>
-    <tableColumn id="25" xr3:uid="{35D08936-E73F-4BB6-8277-979FFFDB890C}" name="Get Pitch/Yaw Data" dataDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{73FDCD44-2E0B-408D-8C8B-526CF8AD1030}" name="Scen Identifier" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{3F466341-C4E1-4EB6-AED5-B3FAB9FFDB04}" name="FloorGroupName" dataDxfId="68"/>
+    <tableColumn id="15" xr3:uid="{95822792-7ABB-423C-82E9-6D0F0DB26332}" name="Section2" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{F5DD3373-E684-418A-9C83-7C1DAF3E703C}" name="SceneID" dataDxfId="66"/>
+    <tableColumn id="16" xr3:uid="{C2E35991-5AAE-4454-B112-E210FA45B5B1}" name="Scene Order" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{1B214639-BDF9-4E07-8399-162C51178468}" name="SceneDisplayName" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{5C39FDEC-5B6B-4B37-A3D9-2FF0E84DB986}" name="PanoramaURL" dataDxfId="63" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{65443BFD-E63B-46ED-9BF9-60D1AEFBE995}" name="LogoURL" dataDxfId="62" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{479ED09E-25DD-46EC-B69E-1861960DEAC2}" name="Background music URL" dataDxfId="61" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{57935DA2-FBD2-4844-9037-7137E42964CE}" name="Background music Active" dataDxfId="60"/>
+    <tableColumn id="17" xr3:uid="{C4D373A5-CE54-491B-9807-1166BCDEB305}" name="Background Voice Over URL" dataDxfId="59" dataCellStyle="Hyperlink"/>
+    <tableColumn id="19" xr3:uid="{6234DADD-60C1-4FBC-8721-B0C377137173}" name="VC Actor Avatar URL" dataDxfId="58" dataCellStyle="Hyperlink"/>
+    <tableColumn id="20" xr3:uid="{F0BFA0EF-DF4E-4896-A5FE-58501F313D77}" name="VC Actor image BG Color" dataDxfId="57" dataCellStyle="Hyperlink"/>
+    <tableColumn id="18" xr3:uid="{F78E9396-7CBD-4F84-9A86-30BE5F251A4F}" name="Background Voice Over Active" dataDxfId="56" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{9659F453-2FDD-4F12-8239-DD98421E212B}" name="InitialPitch" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{CE8A6BA7-78A8-4B32-A5C9-820E789064BA}" name="InitialYaw" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{5EF27361-EA21-49B6-B21B-8017A9DE476E}" name="InitialZoom" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{F89939D0-37DB-4307-92F3-5C4A93A00D1C}" name="AutoRotate" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{841A2892-EB40-41E4-970A-069A5F80AE6F}" name="NorthOffset" dataDxfId="51"/>
+    <tableColumn id="13" xr3:uid="{7990DFCD-7C68-4753-865B-59877205AB47}" name="SceneID Active" dataDxfId="50"/>
+    <tableColumn id="21" xr3:uid="{A8F84F3B-00B3-4D3C-9D9A-1341A9EFEE4D}" name="Hotspot ID" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{D4B98C57-A117-462D-AE9B-DEC916B1362B}" name="Hotspot Active" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{81D4978B-66B3-415D-8A0B-3C39AEABC8F4}" name="Floor Map" dataDxfId="47"/>
+    <tableColumn id="26" xr3:uid="{9B34F8E8-0E7B-400B-82B0-9AB62121F087}" name="Floor map Details" dataDxfId="46"/>
+    <tableColumn id="24" xr3:uid="{9B53D36C-2C6E-4874-90BE-0AE384CE5D57}" name="Floor Map Active" dataDxfId="45"/>
+    <tableColumn id="25" xr3:uid="{35D08936-E73F-4BB6-8277-979FFFDB890C}" name="Get Pitch/Yaw Data" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{73FDCD44-2E0B-408D-8C8B-526CF8AD1030}" name="Scen Identifier" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C481020-1612-4FDF-9B0C-75A16E8BD6EE}" name="Table1" displayName="Table1" ref="A1:T162" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C481020-1612-4FDF-9B0C-75A16E8BD6EE}" name="Table1" displayName="Table1" ref="A1:T162" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:T162" xr:uid="{1C481020-1612-4FDF-9B0C-75A16E8BD6EE}"/>
   <tableColumns count="20">
-    <tableColumn id="15" xr3:uid="{6C92FDC8-7FD4-4ED1-84DE-C73B1AEF49AA}" name="FloorID" dataDxfId="39"/>
-    <tableColumn id="20" xr3:uid="{D4590493-B9FB-4809-9262-EDF4D7F21ABC}" name="Scene Order" dataDxfId="38"/>
-    <tableColumn id="1" xr3:uid="{8DAC3286-642C-4DB0-A8B8-5C7BF99FB11F}" name="SceneID" dataDxfId="37"/>
-    <tableColumn id="19" xr3:uid="{79CDA865-39EA-4125-85E4-F3D78AC4893A}" name="Hotspot ID" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{4BDAA051-81D1-400A-A39C-7D867ECB0341}" name="Hotspot Name" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{F981A75D-66D8-4E38-82C9-6DCD2B17FC3E}" name="Hotspot type" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{787CBE39-1923-41F6-9372-CA2D56C6E632}" name="Hotspot Navigation" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{878E0985-EA91-45B5-B984-8D637B8FAC1A}" name="StyleID/CustomCSS" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{5750A58C-6161-4401-AC72-9E158AEE5857}" name="Pitch" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{BE566E3E-5C22-4617-9723-BF12A43249DE}" name="Yaw" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{5A307C93-AF79-4FC7-8CD0-D327558EE7A8}" name="Rotation" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{CDA04002-4AE2-42E0-BE80-D1092B841D6F}" name="Custom Hotspot URL" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{B760F4E6-236A-47E6-B68A-77D0E77DEBE8}" name="Hotspot HoverImage URL" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{54ECD990-86C2-40C1-B48B-2D7A81FF92B9}" name="Title" dataDxfId="26"/>
-    <tableColumn id="12" xr3:uid="{945E3504-CBC4-4B71-87A6-409E0A7C093F}" name="Description" dataDxfId="25"/>
-    <tableColumn id="17" xr3:uid="{3055829F-DDE9-4492-B64F-EA9B27D86F0D}" name="SR Currancy Symbol image URL" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{37499370-9458-4DA7-9E1E-492AC195DCB2}" name="Price" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{51AF3A7A-9E37-4EC3-95E2-04EA97CB0A3F}" name="Avatar Image URL" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{62D296DE-BD87-415D-A7A9-7B26ADBEBF6D}" name="Voice over" dataDxfId="21"/>
-    <tableColumn id="18" xr3:uid="{48873D82-692C-4357-B503-4E9A267EC815}" name="Hotspot Hover Active" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{6C92FDC8-7FD4-4ED1-84DE-C73B1AEF49AA}" name="FloorID" dataDxfId="40"/>
+    <tableColumn id="20" xr3:uid="{D4590493-B9FB-4809-9262-EDF4D7F21ABC}" name="Scene Order" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{8DAC3286-642C-4DB0-A8B8-5C7BF99FB11F}" name="SceneID" dataDxfId="38"/>
+    <tableColumn id="19" xr3:uid="{79CDA865-39EA-4125-85E4-F3D78AC4893A}" name="Hotspot ID" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{4BDAA051-81D1-400A-A39C-7D867ECB0341}" name="Hotspot Name" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{F981A75D-66D8-4E38-82C9-6DCD2B17FC3E}" name="Hotspot type" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{787CBE39-1923-41F6-9372-CA2D56C6E632}" name="Hotspot Navigation" dataDxfId="34"/>
+    <tableColumn id="14" xr3:uid="{878E0985-EA91-45B5-B984-8D637B8FAC1A}" name="StyleID/CustomCSS" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{5750A58C-6161-4401-AC72-9E158AEE5857}" name="Pitch" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{BE566E3E-5C22-4617-9723-BF12A43249DE}" name="Yaw" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{5A307C93-AF79-4FC7-8CD0-D327558EE7A8}" name="Rotation" dataDxfId="30"/>
+    <tableColumn id="16" xr3:uid="{CDA04002-4AE2-42E0-BE80-D1092B841D6F}" name="Custom Hotspot URL" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{B760F4E6-236A-47E6-B68A-77D0E77DEBE8}" name="Hotspot HoverImage URL" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{54ECD990-86C2-40C1-B48B-2D7A81FF92B9}" name="Title" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{945E3504-CBC4-4B71-87A6-409E0A7C093F}" name="Description" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{3055829F-DDE9-4492-B64F-EA9B27D86F0D}" name="SR Currancy Symbol image URL" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{37499370-9458-4DA7-9E1E-492AC195DCB2}" name="Price" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{51AF3A7A-9E37-4EC3-95E2-04EA97CB0A3F}" name="Avatar Image URL" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{62D296DE-BD87-415D-A7A9-7B26ADBEBF6D}" name="Voice over" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{48873D82-692C-4357-B503-4E9A267EC815}" name="Hotspot Hover Active" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A1:E3" xr:uid="{B3877FE7-10F8-47C2-9A2D-F16124172AF7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="15" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{7F04D01F-FFB6-4446-80B1-1E1109F1CC77}" name="FloorID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{D8967C29-E37C-4C91-8578-2B0335FAAD72}" name="FloorName" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{86218806-D26E-4D12-84C1-DF3205F3D3D2}" name="ThumbnailURL" dataDxfId="16" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{51DA99DE-2BCE-4472-8DFA-9B7A313CBD9F}" name="Order" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{919846AB-3552-48DA-97F3-A7CC50F58867}" name="Floor Thumb Active" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}" name="Table4" displayName="Table4" ref="A1:B4" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:B4" xr:uid="{2174795D-1356-4663-9B2E-C9CC7041F757}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{E6B3FDCD-EBB2-4CD5-A320-D45F8BCB7318}" name="StyleID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{2B3483AB-435E-499C-8675-560E5B48DE5F}" name="CSS Rules" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6231,7 +6244,7 @@
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{CD437926-0051-42E8-974D-E38762304209}"/>
@@ -6276,9 +6289,9 @@
     <col min="6" max="6" width="8.88671875" style="57"/>
     <col min="7" max="7" width="17.1640625" style="57" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.609375" customWidth="1"/>
-    <col min="12" max="12" width="58.94140625" customWidth="1"/>
-    <col min="13" max="13" width="24.1640625" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" customWidth="1"/>
+    <col min="13" max="13" width="34.0546875" customWidth="1"/>
+    <col min="14" max="14" width="17.21875" customWidth="1"/>
     <col min="15" max="15" width="22.77734375" customWidth="1"/>
     <col min="16" max="16" width="64.33203125" customWidth="1"/>
     <col min="17" max="17" width="8.109375" bestFit="1" customWidth="1"/>
@@ -6541,7 +6554,7 @@
         <v>136</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>141</v>
+        <v>476</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>109</v>
@@ -14982,7 +14995,9 @@
         <v>38</v>
       </c>
       <c r="L162" s="25"/>
-      <c r="M162" s="15"/>
+      <c r="M162" s="16" t="s">
+        <v>476</v>
+      </c>
       <c r="N162" s="31" t="s">
         <v>112</v>
       </c>
@@ -15866,28 +15881,31 @@
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="M4:M8">
-    <cfRule type="duplicateValues" dxfId="7" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M24 M32:M52 M60:M80 M88:M101 M109:M162">
-    <cfRule type="duplicateValues" dxfId="6" priority="27"/>
+  <conditionalFormatting sqref="M11:M24 M32:M52 M60:M80 M88:M101 M109:M161">
+    <cfRule type="duplicateValues" dxfId="7" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:M29">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M53:M57">
     <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M53:M57">
+  <conditionalFormatting sqref="M81:M85">
     <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M81:M85">
+  <conditionalFormatting sqref="M102:M106">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M102:M106">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M177:M181">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M182:M186">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M162">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="R4" r:id="rId1" xr:uid="{D9569CBD-1C1A-4EF0-9D90-B70EA928D150}"/>
@@ -16040,11 +16058,10 @@
     <hyperlink ref="L33" r:id="rId148" xr:uid="{8D220609-2D34-48AD-A30F-42CE121090A0}"/>
     <hyperlink ref="S7" r:id="rId149" xr:uid="{E9C9AC5C-FB44-4DF1-9A5A-F63125F706C5}"/>
     <hyperlink ref="S11" r:id="rId150" xr:uid="{0C1812DF-CB74-4A1D-A893-DCD676F1D4E4}"/>
-    <hyperlink ref="M5" r:id="rId151" xr:uid="{1759D407-EB67-4B35-AE20-16AA58E37411}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId152"/>
+    <tablePart r:id="rId151"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -703,7 +703,7 @@
     <t>https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
   </si>
   <si>
-    <t>[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-6.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-7.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-8.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-9.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg]</t>
+    <t>[https://www.ikea.com/us/en/home-design/images/graphics/dashboard/try-product-together.png],[https://cdn.apartmenttherapy.info/image/upload/v1554217999/at/house%20tours%20stock%20archive/7f6d6749cdc500dd3a8c93d2e1c6ad6aa7be7dec.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-2.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-3.jpg]</t>
   </si>
   <si>
     <t>Premium Beds</t>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE30429-82F3-42A9-8149-E8B02FB7B12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E9E68D-8A30-4A8E-B233-39965C752CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -8967,7 +8967,7 @@
     <col min="3" max="3" width="9.88671875" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
     <col min="7" max="7" width="17.109375" customWidth="1"/>
     <col min="8" max="8" width="17.609375" customWidth="1"/>
     <col min="9" max="11" width="8.609375" customWidth="1"/>
@@ -8983,7 +8983,7 @@
     <col min="21" max="26" width="8.609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
         <v>173</v>
       </c>
@@ -9077,7 +9077,7 @@
         <v>194</v>
       </c>
       <c r="I2" s="26">
-        <v>-24.61</v>
+        <v>-80.66</v>
       </c>
       <c r="J2" s="26">
         <v>176.91</v>
@@ -9123,7 +9123,7 @@
         <v>194</v>
       </c>
       <c r="I3" s="27">
-        <v>-11.7</v>
+        <v>-8.76</v>
       </c>
       <c r="J3" s="27">
         <v>-3.78</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E9E68D-8A30-4A8E-B233-39965C752CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C398B8-83D5-4D29-967D-1027C6A2F8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="403">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1292,6 +1292,9 @@
   </si>
   <si>
     <t>[A brief description for the product and service highlights for the 1],[Description for the product  title 2],[A brief description for the product and service highlights for the 3]</t>
+  </si>
+  <si>
+    <t>[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4]</t>
   </si>
 </sst>
 </file>
@@ -1559,7 +1562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1677,6 +1680,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9416,8 +9420,8 @@
       <c r="L8" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="M8" s="19" t="s">
-        <v>222</v>
+      <c r="M8" s="45" t="s">
+        <v>402</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>223</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C398B8-83D5-4D29-967D-1027C6A2F8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E64A0BF-087D-402D-A2D4-464F46A4E4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="404">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1294,7 +1294,10 @@
     <t>[A brief description for the product and service highlights for the 1],[Description for the product  title 2],[A brief description for the product and service highlights for the 3]</t>
   </si>
   <si>
-    <t>[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4]</t>
+    <t>Delay Hotspot Tour</t>
+  </si>
+  <si>
+    <t>[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4],[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4]</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1307,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1433,8 +1436,15 @@
       <color theme="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1463,6 +1473,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1559,10 +1575,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1681,8 +1698,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
@@ -1861,8 +1886,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:T162">
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:U162">
+  <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="FloorID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Scene Order"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="SceneID"/>
@@ -1883,6 +1908,7 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Avatar Image URL"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Voice over"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Hotspot Hover Active"/>
+    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour"/>
   </tableColumns>
   <tableStyleInfo name="2. Hotspots Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9048,7 +9074,9 @@
       <c r="T1" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="U1" s="25"/>
+      <c r="U1" s="47" t="s">
+        <v>402</v>
+      </c>
       <c r="V1" s="25"/>
       <c r="W1" s="25"/>
       <c r="X1" s="25"/>
@@ -9191,7 +9219,7 @@
       <c r="O4" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="48" t="s">
         <v>206</v>
       </c>
       <c r="Q4" s="3">
@@ -9205,6 +9233,9 @@
       </c>
       <c r="T4" s="3" t="b">
         <v>1</v>
+      </c>
+      <c r="U4" s="46">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -9266,6 +9297,9 @@
       <c r="T5" s="15" t="b">
         <v>0</v>
       </c>
+      <c r="U5" s="46">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
@@ -9326,6 +9360,9 @@
       <c r="T6" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="U6" s="46">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
@@ -9384,6 +9421,9 @@
       <c r="T7" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="U7" s="46">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
@@ -9421,7 +9461,7 @@
         <v>221</v>
       </c>
       <c r="M8" s="45" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>223</v>
@@ -9443,6 +9483,9 @@
       </c>
       <c r="T8" s="3" t="b">
         <v>1</v>
+      </c>
+      <c r="U8" s="46">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067C4D59-5A09-4B81-B730-8E88F3286B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A59B87-BB26-4895-8FF6-A66A9065F479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1293,10 +1293,18 @@
     <t>[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4],[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4]</t>
   </si>
   <si>
-    <t>[TitleBold: Title is here1A Description: A brief description for the product and service highlights for the 1 Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim ven],[TitleBold: Title is here1B Description: Description for the product  title 2],[A brief description for the product and service highlights for the 3]</t>
-  </si>
-  <si>
     <t>[TitleBold: Title is here 1 Description: Description of the card details if needed],[Title Bold: Title is here 1b Description: Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.],[TitleBold: Title is here 1c Description: Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.]</t>
+  </si>
+  <si>
+    <t>[TitleBold: Title is here1A Description: A brief description for the product and service highlights for the 1 Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim ven],[TitleBold: Title is here1B Description: Description for the product  title 2],[A brief description for the product and service highlights for the 3   commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.
+Lorem ipsum dolor sit amet, cons ectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat.
+Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.
+Lorem ipsum dolor sit amet, cons ectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat.
+Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.
+Lorem ipsum dolor sit amet, cons ectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat.
+Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.
+Lorem ipsum dolor sit amet, cons ectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat.
+Lorem ipsum dolor sit am]</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1580,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1699,6 +1707,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2310,7 +2321,7 @@
         <v>37</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="X2" s="11" t="b">
         <v>1</v>
@@ -9215,8 +9226,8 @@
       <c r="N4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>402</v>
+      <c r="O4" s="49" t="s">
+        <v>403</v>
       </c>
       <c r="P4" s="46" t="s">
         <v>205</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A59B87-BB26-4895-8FF6-A66A9065F479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8DDD1D-A2A7-42FD-8EAE-A9E81B101E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -1293,9 +1293,6 @@
     <t>[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4],[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4]</t>
   </si>
   <si>
-    <t>[TitleBold: Title is here 1 Description: Description of the card details if needed],[Title Bold: Title is here 1b Description: Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.],[TitleBold: Title is here 1c Description: Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.]</t>
-  </si>
-  <si>
     <t>[TitleBold: Title is here1A Description: A brief description for the product and service highlights for the 1 Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim ven],[TitleBold: Title is here1B Description: Description for the product  title 2],[A brief description for the product and service highlights for the 3   commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.
 Lorem ipsum dolor sit amet, cons ectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat.
 Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.
@@ -1305,6 +1302,9 @@
 Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.
 Lorem ipsum dolor sit amet, cons ectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat.
 Lorem ipsum dolor sit am]</t>
+  </si>
+  <si>
+    <t>[TitleBold: Title is here 1 Description: Description of the card details if needed],[TitleBold: Title is here 1b Description: Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.],[TitleBold: Title is here 1c Description: Lorem ipsum dolor sit amet, consectetuer adipiscing elit, sed diam nonummy nibh euismod tincidunt ut laoreet dolore magna aliquam erat volutpat. Ut wisi enim ad minim veniam, quis nostrud exerci tation ullamcorper suscipit lobortis nisl ut aliquip ex ea commodo consequat. Duis autem vel eum iriure dolor in hendrerit in vulputate velit esse molestie consequat, vel illum dolore eu feugiat nulla facilisis at vero eros et accumsan et iusto odio dignissim qui blandit praesent luptatum zzril delenit augue duis dolore te feugait nulla facilisi.]</t>
   </si>
 </sst>
 </file>
@@ -2321,7 +2321,7 @@
         <v>37</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="X2" s="11" t="b">
         <v>1</v>
@@ -9227,7 +9227,7 @@
         <v>203</v>
       </c>
       <c r="O4" s="49" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P4" s="46" t="s">
         <v>205</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8DDD1D-A2A7-42FD-8EAE-A9E81B101E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BF6BBE-BE8A-4064-8F04-EFACA73D8074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="404">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -9010,7 +9010,7 @@
     <col min="7" max="7" width="17.109375" customWidth="1"/>
     <col min="8" max="8" width="17.609375" customWidth="1"/>
     <col min="9" max="11" width="8.609375" customWidth="1"/>
-    <col min="12" max="12" width="10.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" customWidth="1"/>
     <col min="13" max="13" width="50.38671875" customWidth="1"/>
     <col min="14" max="14" width="17.21875" customWidth="1"/>
     <col min="15" max="15" width="22.71875" customWidth="1"/>
@@ -9393,7 +9393,9 @@
       <c r="F7" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="15" t="s">
+        <v>56</v>
+      </c>
       <c r="H7" s="3" t="s">
         <v>199</v>
       </c>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77F2B37-6351-40EE-A5C4-AE12E43D7B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7852EC48-370C-4506-81F8-A9C9AE6F227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1310,10 +1310,10 @@
     <t>PromotionURL</t>
   </si>
   <si>
-    <t>[True:https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[True:https://img.freepik.com/free-vector/realistic-vertical-sale-poster-template-with-photo_23-2149014882.jpg],[False:https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[True:https://img.freepik.com/free-vector/gradient-vertical-sale-poster-template-with-photo_23-2149051247.jpg]</t>
-  </si>
-  <si>
-    <t>[True:https://img.freepik.com/free-vector/gradient-vertical-sale-poster-template-with-photo_23-2149051247.jpg]</t>
+    <t>[https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://img.freepik.com/free-vector/realistic-vertical-sale-poster-template-with-photo_23-2149014882.jpg],[False:https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://img.freepik.com/free-vector/gradient-vertical-sale-poster-template-with-photo_23-2149051247.jpg]</t>
+  </si>
+  <si>
+    <t>[https://img.freepik.com/free-vector/gradient-vertical-sale-poster-template-with-photo_23-2149051247.jpg]</t>
   </si>
 </sst>
 </file>
@@ -4063,8 +4063,8 @@
       <c r="Y23" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="Z23" s="50" t="s">
-        <v>405</v>
+      <c r="Z23" t="s">
+        <v>406</v>
       </c>
       <c r="AA23" s="13">
         <v>45750</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7852EC48-370C-4506-81F8-A9C9AE6F227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0606DDCC-6898-4D8C-BA6B-509D866CCB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1310,10 +1310,10 @@
     <t>PromotionURL</t>
   </si>
   <si>
-    <t>[https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://img.freepik.com/free-vector/realistic-vertical-sale-poster-template-with-photo_23-2149014882.jpg],[False:https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://img.freepik.com/free-vector/gradient-vertical-sale-poster-template-with-photo_23-2149051247.jpg]</t>
-  </si>
-  <si>
     <t>[https://img.freepik.com/free-vector/gradient-vertical-sale-poster-template-with-photo_23-2149051247.jpg]</t>
+  </si>
+  <si>
+    <t>[https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4],[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4]</t>
   </si>
 </sst>
 </file>
@@ -2369,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="50" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA2" s="13">
         <v>45750</v>
@@ -2453,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="Z3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA3" s="13">
         <v>45750</v>
@@ -4064,7 +4064,7 @@
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA23" s="13">
         <v>45750</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0606DDCC-6898-4D8C-BA6B-509D866CCB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104C09B3-6030-40FF-87E3-9F60E5340B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -2191,11 +2191,11 @@
     <col min="6" max="6" width="28.27734375" customWidth="1"/>
     <col min="7" max="7" width="13.109375" customWidth="1"/>
     <col min="8" max="8" width="11.609375" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
     <col min="10" max="10" width="78.5" customWidth="1"/>
     <col min="11" max="11" width="16.5" customWidth="1"/>
     <col min="12" max="12" width="17.109375" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" customWidth="1"/>
     <col min="14" max="14" width="12.609375" customWidth="1"/>
     <col min="15" max="15" width="9.5" customWidth="1"/>
     <col min="16" max="17" width="8.609375" customWidth="1"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>199</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>199</v>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>199</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF74C5A3-E35C-4146-9702-EBAE4B2165D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A29E719-06B1-4DCC-AF92-4B7E945A023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9081,10 +9081,10 @@
     <col min="14" max="14" width="50.38671875" customWidth="1"/>
     <col min="15" max="15" width="17.21875" customWidth="1"/>
     <col min="16" max="16" width="22.71875" customWidth="1"/>
-    <col min="17" max="17" width="64.38671875" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.109375" customWidth="1"/>
     <col min="19" max="19" width="22.5" customWidth="1"/>
-    <col min="20" max="20" width="57.21875" customWidth="1"/>
+    <col min="20" max="20" width="20.0546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="23.109375" customWidth="1"/>
     <col min="22" max="22" width="8.609375" style="48" customWidth="1"/>
     <col min="23" max="27" width="8.609375" customWidth="1"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736DA131-72E1-4650-BE85-D297CC625B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532F9DBC-3EBC-4F79-8E35-ADB418DF1EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="408">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1314,6 +1314,9 @@
   </si>
   <si>
     <t>[https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4],[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4]</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4</t>
   </si>
 </sst>
 </file>
@@ -2324,7 +2327,7 @@
         <v>33</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>34</v>
+        <v>407</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>35</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532F9DBC-3EBC-4F79-8E35-ADB418DF1EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F032D56-BE1C-42BA-B59C-DF4BBE5876A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="407">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1314,9 +1314,6 @@
   </si>
   <si>
     <t>[https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4],[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4]</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4</t>
   </si>
 </sst>
 </file>
@@ -2196,7 +2193,7 @@
     <col min="8" max="8" width="11.609375" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
     <col min="10" max="10" width="78.5" customWidth="1"/>
-    <col min="11" max="11" width="16.5" customWidth="1"/>
+    <col min="11" max="11" width="39.44140625" customWidth="1"/>
     <col min="12" max="12" width="17.109375" customWidth="1"/>
     <col min="13" max="13" width="14.1640625" customWidth="1"/>
     <col min="14" max="14" width="12.609375" customWidth="1"/>
@@ -2326,9 +2323,7 @@
       <c r="J2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
         <v>35</v>
       </c>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F032D56-BE1C-42BA-B59C-DF4BBE5876A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5999E91-05B8-41F3-8E63-9CC457F25BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2328,7 +2328,7 @@
         <v>35</v>
       </c>
       <c r="M2" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="8">
         <v>-2.79</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5999E91-05B8-41F3-8E63-9CC457F25BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AABCA0-89A9-4927-8B75-74CDAB679C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="408">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1314,6 +1314,9 @@
   </si>
   <si>
     <t>[https://img.freepik.com/premium-vector/mega-sale-promotion-poster-template_693064-8.jpg],[https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg],[https://youtu.be/HCEOTyVooik?si=gzp8uopf_DOxihV4],[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4]</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4</t>
   </si>
 </sst>
 </file>
@@ -2323,12 +2326,14 @@
       <c r="J2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="6"/>
+      <c r="K2" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="L2" s="7" t="s">
         <v>35</v>
       </c>
       <c r="M2" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="8">
         <v>-2.79</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AABCA0-89A9-4927-8B75-74CDAB679C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0951A9E4-294C-4EC9-9C4E-B1C7F8A043EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -9084,7 +9084,7 @@
     <col min="15" max="15" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17.21875" customWidth="1"/>
     <col min="17" max="17" width="22.71875" customWidth="1"/>
-    <col min="18" max="18" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.609375" customWidth="1"/>
     <col min="19" max="19" width="20.21875" customWidth="1"/>
     <col min="20" max="20" width="22.5" customWidth="1"/>
     <col min="21" max="21" width="20.0546875" customWidth="1"/>
@@ -9308,8 +9308,8 @@
       <c r="Q4" s="3">
         <v>18</v>
       </c>
-      <c r="R4" s="19" t="s">
-        <v>34</v>
+      <c r="R4" s="6" t="s">
+        <v>407</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>206</v>
@@ -22210,113 +22210,112 @@
   <hyperlinks>
     <hyperlink ref="L4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="P4" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="R4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="L5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="R5" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="R6" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="S7" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="P11" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="R11" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="S11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="R12" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="R13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="L14" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="L15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="P18" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="R18" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="R19" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="R20" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="P25" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="R25" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="R26" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="R27" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="L28" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="L29" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="L32" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="P32" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="R32" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="L33" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="R33" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="R34" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="P39" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="R39" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="R40" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="R41" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="L42" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="L43" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="P46" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="R46" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="R47" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="R48" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="P53" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="R53" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="R54" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="R55" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="P60" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="R60" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="R61" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="R62" r:id="rId48" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="P67" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="R67" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="R68" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="R69" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="P74" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="R74" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="R75" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="R76" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="P81" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="R81" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="R82" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="R83" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="P88" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="R88" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="R89" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="R90" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="P95" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
-    <hyperlink ref="R95" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
-    <hyperlink ref="R96" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
-    <hyperlink ref="R97" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
-    <hyperlink ref="P102" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
-    <hyperlink ref="R102" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
-    <hyperlink ref="R103" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
-    <hyperlink ref="R104" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
-    <hyperlink ref="P109" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
-    <hyperlink ref="R109" r:id="rId74" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
-    <hyperlink ref="R110" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
-    <hyperlink ref="R111" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
-    <hyperlink ref="P116" r:id="rId77" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
-    <hyperlink ref="R116" r:id="rId78" xr:uid="{00000000-0004-0000-0100-00004D000000}"/>
-    <hyperlink ref="R117" r:id="rId79" xr:uid="{00000000-0004-0000-0100-00004E000000}"/>
-    <hyperlink ref="R118" r:id="rId80" xr:uid="{00000000-0004-0000-0100-00004F000000}"/>
-    <hyperlink ref="P123" r:id="rId81" xr:uid="{00000000-0004-0000-0100-000050000000}"/>
-    <hyperlink ref="R123" r:id="rId82" xr:uid="{00000000-0004-0000-0100-000051000000}"/>
-    <hyperlink ref="R124" r:id="rId83" xr:uid="{00000000-0004-0000-0100-000052000000}"/>
-    <hyperlink ref="R125" r:id="rId84" xr:uid="{00000000-0004-0000-0100-000053000000}"/>
-    <hyperlink ref="P130" r:id="rId85" xr:uid="{00000000-0004-0000-0100-000054000000}"/>
-    <hyperlink ref="R130" r:id="rId86" xr:uid="{00000000-0004-0000-0100-000055000000}"/>
-    <hyperlink ref="R131" r:id="rId87" xr:uid="{00000000-0004-0000-0100-000056000000}"/>
-    <hyperlink ref="R132" r:id="rId88" xr:uid="{00000000-0004-0000-0100-000057000000}"/>
-    <hyperlink ref="P137" r:id="rId89" xr:uid="{00000000-0004-0000-0100-000058000000}"/>
-    <hyperlink ref="R137" r:id="rId90" xr:uid="{00000000-0004-0000-0100-000059000000}"/>
-    <hyperlink ref="R138" r:id="rId91" xr:uid="{00000000-0004-0000-0100-00005A000000}"/>
-    <hyperlink ref="R139" r:id="rId92" xr:uid="{00000000-0004-0000-0100-00005B000000}"/>
-    <hyperlink ref="P144" r:id="rId93" xr:uid="{00000000-0004-0000-0100-00005C000000}"/>
-    <hyperlink ref="R144" r:id="rId94" xr:uid="{00000000-0004-0000-0100-00005D000000}"/>
-    <hyperlink ref="R145" r:id="rId95" xr:uid="{00000000-0004-0000-0100-00005E000000}"/>
-    <hyperlink ref="R146" r:id="rId96" xr:uid="{00000000-0004-0000-0100-00005F000000}"/>
-    <hyperlink ref="P151" r:id="rId97" xr:uid="{00000000-0004-0000-0100-000060000000}"/>
-    <hyperlink ref="R151" r:id="rId98" xr:uid="{00000000-0004-0000-0100-000061000000}"/>
-    <hyperlink ref="R152" r:id="rId99" xr:uid="{00000000-0004-0000-0100-000062000000}"/>
-    <hyperlink ref="R153" r:id="rId100" xr:uid="{00000000-0004-0000-0100-000063000000}"/>
-    <hyperlink ref="P158" r:id="rId101" xr:uid="{00000000-0004-0000-0100-000064000000}"/>
-    <hyperlink ref="R158" r:id="rId102" xr:uid="{00000000-0004-0000-0100-000065000000}"/>
-    <hyperlink ref="R159" r:id="rId103" xr:uid="{00000000-0004-0000-0100-000066000000}"/>
-    <hyperlink ref="R160" r:id="rId104" xr:uid="{00000000-0004-0000-0100-000067000000}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="R5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="R6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="S7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="P11" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="R11" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="S11" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="R12" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="R13" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="L14" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="L15" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="P18" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="R18" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="R19" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="R20" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="P25" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="R25" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="R26" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="R27" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="L28" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="L29" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="L32" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="P32" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="R32" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="L33" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="R33" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="R34" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="P39" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="R39" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="R40" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="R41" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="L42" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="L43" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="P46" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="R46" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="R47" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="R48" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="P53" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="R53" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="R54" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="R55" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="P60" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="R60" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="R61" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="R62" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="P67" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="R67" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="R68" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="R69" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="P74" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="R74" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="R75" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="R76" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="P81" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="R81" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="R82" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="R83" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="P88" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="R88" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="R89" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="R90" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="P95" r:id="rId64" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="R95" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
+    <hyperlink ref="R96" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
+    <hyperlink ref="R97" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
+    <hyperlink ref="P102" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
+    <hyperlink ref="R102" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
+    <hyperlink ref="R103" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
+    <hyperlink ref="R104" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
+    <hyperlink ref="P109" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
+    <hyperlink ref="R109" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
+    <hyperlink ref="R110" r:id="rId74" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
+    <hyperlink ref="R111" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
+    <hyperlink ref="P116" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
+    <hyperlink ref="R116" r:id="rId77" xr:uid="{00000000-0004-0000-0100-00004D000000}"/>
+    <hyperlink ref="R117" r:id="rId78" xr:uid="{00000000-0004-0000-0100-00004E000000}"/>
+    <hyperlink ref="R118" r:id="rId79" xr:uid="{00000000-0004-0000-0100-00004F000000}"/>
+    <hyperlink ref="P123" r:id="rId80" xr:uid="{00000000-0004-0000-0100-000050000000}"/>
+    <hyperlink ref="R123" r:id="rId81" xr:uid="{00000000-0004-0000-0100-000051000000}"/>
+    <hyperlink ref="R124" r:id="rId82" xr:uid="{00000000-0004-0000-0100-000052000000}"/>
+    <hyperlink ref="R125" r:id="rId83" xr:uid="{00000000-0004-0000-0100-000053000000}"/>
+    <hyperlink ref="P130" r:id="rId84" xr:uid="{00000000-0004-0000-0100-000054000000}"/>
+    <hyperlink ref="R130" r:id="rId85" xr:uid="{00000000-0004-0000-0100-000055000000}"/>
+    <hyperlink ref="R131" r:id="rId86" xr:uid="{00000000-0004-0000-0100-000056000000}"/>
+    <hyperlink ref="R132" r:id="rId87" xr:uid="{00000000-0004-0000-0100-000057000000}"/>
+    <hyperlink ref="P137" r:id="rId88" xr:uid="{00000000-0004-0000-0100-000058000000}"/>
+    <hyperlink ref="R137" r:id="rId89" xr:uid="{00000000-0004-0000-0100-000059000000}"/>
+    <hyperlink ref="R138" r:id="rId90" xr:uid="{00000000-0004-0000-0100-00005A000000}"/>
+    <hyperlink ref="R139" r:id="rId91" xr:uid="{00000000-0004-0000-0100-00005B000000}"/>
+    <hyperlink ref="P144" r:id="rId92" xr:uid="{00000000-0004-0000-0100-00005C000000}"/>
+    <hyperlink ref="R144" r:id="rId93" xr:uid="{00000000-0004-0000-0100-00005D000000}"/>
+    <hyperlink ref="R145" r:id="rId94" xr:uid="{00000000-0004-0000-0100-00005E000000}"/>
+    <hyperlink ref="R146" r:id="rId95" xr:uid="{00000000-0004-0000-0100-00005F000000}"/>
+    <hyperlink ref="P151" r:id="rId96" xr:uid="{00000000-0004-0000-0100-000060000000}"/>
+    <hyperlink ref="R151" r:id="rId97" xr:uid="{00000000-0004-0000-0100-000061000000}"/>
+    <hyperlink ref="R152" r:id="rId98" xr:uid="{00000000-0004-0000-0100-000062000000}"/>
+    <hyperlink ref="R153" r:id="rId99" xr:uid="{00000000-0004-0000-0100-000063000000}"/>
+    <hyperlink ref="P158" r:id="rId100" xr:uid="{00000000-0004-0000-0100-000064000000}"/>
+    <hyperlink ref="R158" r:id="rId101" xr:uid="{00000000-0004-0000-0100-000065000000}"/>
+    <hyperlink ref="R159" r:id="rId102" xr:uid="{00000000-0004-0000-0100-000066000000}"/>
+    <hyperlink ref="R160" r:id="rId103" xr:uid="{00000000-0004-0000-0100-000067000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId105"/>
+    <tablePart r:id="rId104"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30CDAAF-4408-4689-9146-B315C84F1A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE052ABD-22E2-4B1C-A324-315AED5C61FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9236,10 +9236,10 @@
         <v>193</v>
       </c>
       <c r="I3" s="27">
-        <v>-3.09</v>
+        <v>-13.36</v>
       </c>
       <c r="J3" s="27">
-        <v>-3.59</v>
+        <v>3.26</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>194</v>
@@ -9284,10 +9284,10 @@
         <v>193</v>
       </c>
       <c r="I4" s="27">
-        <v>-10.43</v>
+        <v>-23.71</v>
       </c>
       <c r="J4" s="27">
-        <v>-3.49</v>
+        <v>68.62</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>194</v>
@@ -9332,10 +9332,10 @@
         <v>193</v>
       </c>
       <c r="I5" s="27">
-        <v>-20.11</v>
+        <v>-13.75</v>
       </c>
       <c r="J5" s="27">
-        <v>-3.97</v>
+        <v>-147.05000000000001</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>194</v>
@@ -9380,10 +9380,10 @@
         <v>193</v>
       </c>
       <c r="I6" s="27">
-        <v>-42.23</v>
+        <v>-23.85</v>
       </c>
       <c r="J6" s="27">
-        <v>-5.5</v>
+        <v>76.88</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>194</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE052ABD-22E2-4B1C-A324-315AED5C61FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814FC527-FC32-4733-B90F-C1E8CF25544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9380,10 +9380,10 @@
         <v>193</v>
       </c>
       <c r="I6" s="27">
-        <v>-23.85</v>
+        <v>-47.17</v>
       </c>
       <c r="J6" s="27">
-        <v>76.88</v>
+        <v>-6.11</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>194</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814FC527-FC32-4733-B90F-C1E8CF25544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AA4E32-B2D4-48D7-9506-283FABF30BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9380,10 +9380,10 @@
         <v>193</v>
       </c>
       <c r="I6" s="27">
-        <v>-47.17</v>
+        <v>-49.99</v>
       </c>
       <c r="J6" s="27">
-        <v>-6.11</v>
+        <v>-4.3600000000000003</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>194</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AA4E32-B2D4-48D7-9506-283FABF30BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE044F06-B038-43CF-B5E0-B0825413946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="409">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1317,6 +1317,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4</t>
+  </si>
+  <si>
+    <t>Slide20</t>
   </si>
 </sst>
 </file>
@@ -9278,7 +9281,7 @@
         <v>191</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>193</v>
@@ -9326,7 +9329,7 @@
         <v>191</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>193</v>
@@ -9374,7 +9377,7 @@
         <v>191</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>196</v>
+        <v>408</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>193</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE044F06-B038-43CF-B5E0-B0825413946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB7A4D4-B2DC-473D-9F52-DF1459C7DF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="433">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1319,7 +1319,79 @@
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4</t>
   </si>
   <si>
-    <t>Slide20</t>
+    <t>Map Data</t>
+  </si>
+  <si>
+    <t>Show/ Hide Map and Grid</t>
+  </si>
+  <si>
+    <t>TRUE, Show</t>
+  </si>
+  <si>
+    <t>Show,X:1.5,Y:1,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:2,Y:2,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:3,Y:3,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:4.3,Y:4,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:5,Y:5,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:6,Y:6,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:7,Y:7,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:8,Y:8,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:9,Y:9,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:10,Y:10,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:11,Y:11,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:12,Y:12,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:13,Y:13,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:14,Y:14,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:15,Y:15,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:16,Y:16,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:17,Y:17,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:18,Y:18,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:19,Y:19,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:20,Y:20,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:15,Y:3,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:16,Y:20,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
 </sst>
 </file>
@@ -1902,8 +1974,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AA24">
-  <tableColumns count="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AC24">
+  <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="FloorGroupName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Section2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SceneID"/>
@@ -1931,6 +2003,8 @@
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Get Pitch/Yaw Data"/>
     <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="2"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Scen Identifier"/>
+    <tableColumn id="28" xr3:uid="{F3D3E641-7A49-4E3D-A155-18F57FACDDFD}" name="Map Data"/>
+    <tableColumn id="29" xr3:uid="{E29CD0D3-9DD4-4AE6-9A77-C8A7EC474374}" name="Show/ Hide Map and Grid"/>
   </tableColumns>
   <tableStyleInfo name="1. Scenes Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2186,7 +2260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1000"/>
+  <dimension ref="A1:AC1000"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -2213,9 +2287,10 @@
     <col min="23" max="23" width="30" customWidth="1"/>
     <col min="24" max="26" width="18.71875" customWidth="1"/>
     <col min="27" max="27" width="12.5" customWidth="1"/>
+    <col min="28" max="28" width="34.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2297,8 +2372,14 @@
       <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB1" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC1" s="50" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
@@ -2380,8 +2461,14 @@
       <c r="AA2" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB2" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
@@ -2464,8 +2551,14 @@
       <c r="AA3" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB3" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -2542,8 +2635,14 @@
       <c r="AA4" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB4" t="s">
+        <v>413</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -2621,8 +2720,14 @@
       <c r="AA5" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB5" t="s">
+        <v>414</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -2700,8 +2805,14 @@
       <c r="AA6" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB6" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -2779,8 +2890,14 @@
       <c r="AA7" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB7" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -2860,8 +2977,14 @@
       <c r="AA8" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB8" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -2941,8 +3064,14 @@
       <c r="AA9" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB9" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -3022,8 +3151,14 @@
       <c r="AA10" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB10" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -3101,8 +3236,14 @@
       <c r="AA11" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="12" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB11" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
@@ -3182,8 +3323,14 @@
       <c r="AA12" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB12" t="s">
+        <v>421</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
@@ -3263,8 +3410,14 @@
       <c r="AA13" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB13" t="s">
+        <v>422</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
@@ -3344,8 +3497,14 @@
       <c r="AA14" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB14" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
@@ -3425,8 +3584,14 @@
       <c r="AA15" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB15" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>118</v>
       </c>
@@ -3506,8 +3671,14 @@
       <c r="AA16" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB16" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>118</v>
       </c>
@@ -3587,8 +3758,14 @@
       <c r="AA17" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB17" t="s">
+        <v>426</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>118</v>
       </c>
@@ -3668,8 +3845,14 @@
       <c r="AA18" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB18" t="s">
+        <v>427</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>118</v>
       </c>
@@ -3749,8 +3932,14 @@
       <c r="AA19" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB19" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
         <v>118</v>
       </c>
@@ -3830,8 +4019,14 @@
       <c r="AA20" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB20" t="s">
+        <v>429</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>118</v>
       </c>
@@ -3911,8 +4106,14 @@
       <c r="AA21" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="22" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB21" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>118</v>
       </c>
@@ -3992,8 +4193,14 @@
       <c r="AA22" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB22" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>118</v>
       </c>
@@ -4075,8 +4282,14 @@
       <c r="AA23" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="24" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB23" t="s">
+        <v>431</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
         <v>118</v>
       </c>
@@ -4156,43 +4369,49 @@
       <c r="AA24" s="13">
         <v>45750</v>
       </c>
-    </row>
-    <row r="25" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB24" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D25" s="21"/>
       <c r="L25" s="21"/>
       <c r="N25" s="22"/>
     </row>
-    <row r="26" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D26" s="21"/>
       <c r="L26" s="21"/>
       <c r="N26" s="22"/>
     </row>
-    <row r="27" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D27" s="21"/>
       <c r="L27" s="21"/>
       <c r="N27" s="22"/>
     </row>
-    <row r="28" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D28" s="21"/>
       <c r="L28" s="21"/>
       <c r="N28" s="22"/>
     </row>
-    <row r="29" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D29" s="21"/>
       <c r="L29" s="21"/>
       <c r="N29" s="22"/>
     </row>
-    <row r="30" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D30" s="21"/>
       <c r="L30" s="21"/>
       <c r="N30" s="22"/>
     </row>
-    <row r="31" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D31" s="21"/>
       <c r="L31" s="21"/>
       <c r="N31" s="22"/>
     </row>
-    <row r="32" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D32" s="21"/>
       <c r="L32" s="21"/>
       <c r="N32" s="22"/>
@@ -9377,7 +9596,7 @@
         <v>191</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>408</v>
+        <v>151</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>193</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB7A4D4-B2DC-473D-9F52-DF1459C7DF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DE5267-C5AD-4333-90AA-ABE63133A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="431">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1322,36 +1322,15 @@
     <t>Map Data</t>
   </si>
   <si>
-    <t>Show/ Hide Map and Grid</t>
-  </si>
-  <si>
-    <t>TRUE, Show</t>
-  </si>
-  <si>
     <t>Show,X:1.5,Y:1,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
     <t>Hide,X:2,Y:2,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
-    <t>Show,X:3,Y:3,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:4.3,Y:4,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
     <t>Show,X:5,Y:5,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
-    <t>Show,X:6,Y:6,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:7,Y:7,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:8,Y:8,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
     <t>Show,X:9,Y:9,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
@@ -1361,37 +1340,52 @@
     <t>Show,X:11,Y:11,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
-    <t>Show,X:12,Y:12,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:13,Y:13,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
     <t>Show,X:14,Y:14,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
-    <t>Show,X:15,Y:15,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:16,Y:16,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:17,Y:17,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:18,Y:18,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:19,Y:19,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:20,Y:20,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:15,Y:3,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:16,Y:20,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+    <t>Hide,X:3,Y:3,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:4.3,Y:4,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:6,Y:6,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:7,Y:7,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:8,Y:8,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:12,Y:12,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:13,Y:13,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:15,Y:15,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Hide,X:16,Y:16,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Hide,X:17,Y:17,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Show,X:18,Y:18,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Hide,X:19,Y:19,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Hide,X:20,Y:20,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Show,X:15,Y:3,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Hide,X:16,Y:20,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1532,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1567,6 +1561,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1667,7 +1667,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1801,6 +1801,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1974,8 +1975,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AC24">
-  <tableColumns count="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AB24">
+  <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="FloorGroupName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Section2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SceneID"/>
@@ -2004,7 +2005,6 @@
     <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="2"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Scen Identifier"/>
     <tableColumn id="28" xr3:uid="{F3D3E641-7A49-4E3D-A155-18F57FACDDFD}" name="Map Data"/>
-    <tableColumn id="29" xr3:uid="{E29CD0D3-9DD4-4AE6-9A77-C8A7EC474374}" name="Show/ Hide Map and Grid"/>
   </tableColumns>
   <tableStyleInfo name="1. Scenes Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2260,7 +2260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1000"/>
+  <dimension ref="A1:AB1000"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -2287,10 +2287,10 @@
     <col min="23" max="23" width="30" customWidth="1"/>
     <col min="24" max="26" width="18.71875" customWidth="1"/>
     <col min="27" max="27" width="12.5" customWidth="1"/>
-    <col min="28" max="28" width="34.109375" customWidth="1"/>
+    <col min="28" max="28" width="65.0546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2375,11 +2375,8 @@
       <c r="AB1" t="s">
         <v>408</v>
       </c>
-      <c r="AC1" s="50" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
@@ -2462,13 +2459,10 @@
         <v>45750</v>
       </c>
       <c r="AB2" t="s">
-        <v>411</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
@@ -2552,13 +2546,10 @@
         <v>45750</v>
       </c>
       <c r="AB3" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -2636,13 +2627,10 @@
         <v>45750</v>
       </c>
       <c r="AB4" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -2721,13 +2709,10 @@
         <v>45750</v>
       </c>
       <c r="AB5" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -2806,13 +2791,10 @@
         <v>45750</v>
       </c>
       <c r="AB6" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -2891,13 +2873,10 @@
         <v>45750</v>
       </c>
       <c r="AB7" t="s">
-        <v>416</v>
-      </c>
-      <c r="AC7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -2978,13 +2957,10 @@
         <v>45750</v>
       </c>
       <c r="AB8" t="s">
-        <v>417</v>
-      </c>
-      <c r="AC8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -3065,13 +3041,10 @@
         <v>45750</v>
       </c>
       <c r="AB9" t="s">
-        <v>418</v>
-      </c>
-      <c r="AC9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -3152,13 +3125,10 @@
         <v>45750</v>
       </c>
       <c r="AB10" t="s">
-        <v>419</v>
-      </c>
-      <c r="AC10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -3237,13 +3207,10 @@
         <v>45750</v>
       </c>
       <c r="AB11" t="s">
-        <v>420</v>
-      </c>
-      <c r="AC11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
@@ -3324,13 +3291,10 @@
         <v>45750</v>
       </c>
       <c r="AB12" t="s">
-        <v>421</v>
-      </c>
-      <c r="AC12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
@@ -3411,13 +3375,10 @@
         <v>45750</v>
       </c>
       <c r="AB13" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
@@ -3498,13 +3459,10 @@
         <v>45750</v>
       </c>
       <c r="AB14" t="s">
-        <v>423</v>
-      </c>
-      <c r="AC14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
@@ -3585,13 +3543,10 @@
         <v>45750</v>
       </c>
       <c r="AB15" t="s">
-        <v>424</v>
-      </c>
-      <c r="AC15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>118</v>
       </c>
@@ -3671,14 +3626,11 @@
       <c r="AA16" s="13">
         <v>45750</v>
       </c>
-      <c r="AB16" t="s">
-        <v>425</v>
-      </c>
-      <c r="AC16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB16" s="51" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>118</v>
       </c>
@@ -3758,14 +3710,11 @@
       <c r="AA17" s="13">
         <v>45750</v>
       </c>
-      <c r="AB17" t="s">
-        <v>426</v>
-      </c>
-      <c r="AC17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB17" s="51" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>118</v>
       </c>
@@ -3845,14 +3794,11 @@
       <c r="AA18" s="13">
         <v>45750</v>
       </c>
-      <c r="AB18" t="s">
-        <v>427</v>
-      </c>
-      <c r="AC18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB18" s="51" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>118</v>
       </c>
@@ -3932,14 +3878,11 @@
       <c r="AA19" s="13">
         <v>45750</v>
       </c>
-      <c r="AB19" t="s">
-        <v>428</v>
-      </c>
-      <c r="AC19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB19" s="51" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
         <v>118</v>
       </c>
@@ -4019,14 +3962,11 @@
       <c r="AA20" s="13">
         <v>45750</v>
       </c>
-      <c r="AB20" t="s">
-        <v>429</v>
-      </c>
-      <c r="AC20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB20" s="51" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>118</v>
       </c>
@@ -4106,14 +4046,11 @@
       <c r="AA21" s="13">
         <v>45750</v>
       </c>
-      <c r="AB21" t="s">
-        <v>430</v>
-      </c>
-      <c r="AC21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB21" s="51" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>118</v>
       </c>
@@ -4193,14 +4130,11 @@
       <c r="AA22" s="13">
         <v>45750</v>
       </c>
-      <c r="AB22" t="s">
-        <v>428</v>
-      </c>
-      <c r="AC22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB22" s="51" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>118</v>
       </c>
@@ -4282,14 +4216,11 @@
       <c r="AA23" s="13">
         <v>45750</v>
       </c>
-      <c r="AB23" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AB23" s="51" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
         <v>118</v>
       </c>
@@ -4369,49 +4300,46 @@
       <c r="AA24" s="13">
         <v>45750</v>
       </c>
-      <c r="AB24" t="s">
-        <v>432</v>
-      </c>
-      <c r="AC24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB24" s="51" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D25" s="21"/>
       <c r="L25" s="21"/>
       <c r="N25" s="22"/>
     </row>
-    <row r="26" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D26" s="21"/>
       <c r="L26" s="21"/>
       <c r="N26" s="22"/>
     </row>
-    <row r="27" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D27" s="21"/>
       <c r="L27" s="21"/>
       <c r="N27" s="22"/>
     </row>
-    <row r="28" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D28" s="21"/>
       <c r="L28" s="21"/>
       <c r="N28" s="22"/>
     </row>
-    <row r="29" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D29" s="21"/>
       <c r="L29" s="21"/>
       <c r="N29" s="22"/>
     </row>
-    <row r="30" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D30" s="21"/>
       <c r="L30" s="21"/>
       <c r="N30" s="22"/>
     </row>
-    <row r="31" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D31" s="21"/>
       <c r="L31" s="21"/>
       <c r="N31" s="22"/>
     </row>
-    <row r="32" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D32" s="21"/>
       <c r="L32" s="21"/>
       <c r="N32" s="22"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DE5267-C5AD-4333-90AA-ABE63133A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD9E4DC-AC8E-4A1C-9B9C-F77BB6AA943B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="431">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1346,9 +1346,6 @@
     <t>Hide,X:3,Y:3,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
-    <t>Hide,X:4.3,Y:4,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
     <t>Hide,X:6,Y:6,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
   </si>
   <si>
@@ -1386,6 +1383,9 @@
   </si>
   <si>
     <t>Hide,X:16,Y:20,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Show,X:8,Y:18,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
   </si>
 </sst>
 </file>
@@ -2708,9 +2708,6 @@
       <c r="AA5" s="13">
         <v>45750</v>
       </c>
-      <c r="AB5" t="s">
-        <v>417</v>
-      </c>
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
@@ -2873,7 +2870,7 @@
         <v>45750</v>
       </c>
       <c r="AB7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2957,7 +2954,7 @@
         <v>45750</v>
       </c>
       <c r="AB8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3041,7 +3038,7 @@
         <v>45750</v>
       </c>
       <c r="AB9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3375,7 +3372,7 @@
         <v>45750</v>
       </c>
       <c r="AB13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3459,7 +3456,7 @@
         <v>45750</v>
       </c>
       <c r="AB14" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3627,7 +3624,7 @@
         <v>45750</v>
       </c>
       <c r="AB16" s="51" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3711,7 +3708,7 @@
         <v>45750</v>
       </c>
       <c r="AB17" s="51" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3795,7 +3792,7 @@
         <v>45750</v>
       </c>
       <c r="AB18" s="51" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3879,7 +3876,7 @@
         <v>45750</v>
       </c>
       <c r="AB19" s="51" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3963,7 +3960,7 @@
         <v>45750</v>
       </c>
       <c r="AB20" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -4047,7 +4044,7 @@
         <v>45750</v>
       </c>
       <c r="AB21" s="51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -4131,7 +4128,7 @@
         <v>45750</v>
       </c>
       <c r="AB22" s="51" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -4217,7 +4214,7 @@
         <v>45750</v>
       </c>
       <c r="AB23" s="51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4301,7 +4298,7 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD9E4DC-AC8E-4A1C-9B9C-F77BB6AA943B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C10760-D37F-4116-BC65-81D08E4FA16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="433">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1386,6 +1386,12 @@
   </si>
   <si>
     <t>Show,X:8,Y:18,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
+  </si>
+  <si>
+    <t>Top:200,https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg</t>
+  </si>
+  <si>
+    <t>Right:110,https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg</t>
   </si>
 </sst>
 </file>
@@ -1667,7 +1673,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1802,6 +1808,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9206,10 +9215,10 @@
     <hyperlink ref="J24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId19"/>
+  <pageSetup orientation="landscape" r:id="rId19"/>
+  <legacyDrawing r:id="rId20"/>
   <tableParts count="1">
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId21"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9581,8 +9590,8 @@
       <c r="K7" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L7" s="6" t="s">
-        <v>201</v>
+      <c r="L7" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="M7" s="19" t="s">
         <v>202</v>
@@ -9645,8 +9654,8 @@
       <c r="K8" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L8" s="6" t="s">
-        <v>201</v>
+      <c r="L8" s="46" t="s">
+        <v>432</v>
       </c>
       <c r="M8" s="28" t="s">
         <v>208</v>
@@ -22499,9 +22508,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L7" r:id="rId1" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="P7" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="L8" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="L8" r:id="rId3" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
     <hyperlink ref="R8" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
     <hyperlink ref="R9" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
     <hyperlink ref="S10" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
@@ -22604,9 +22613,9 @@
     <hyperlink ref="R163" r:id="rId103" xr:uid="{00000000-0004-0000-0100-000067000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId104"/>
   <tableParts count="1">
-    <tablePart r:id="rId104"/>
+    <tablePart r:id="rId105"/>
   </tableParts>
 </worksheet>
 </file>
@@ -23691,9 +23700,9 @@
     <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -24803,9 +24812,9 @@
     <row r="1000" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -25820,6 +25829,6 @@
     <row r="1000" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C10760-D37F-4116-BC65-81D08E4FA16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A48BC2-5D4F-4A5A-8689-F7F9EBE35A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="434">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -690,9 +690,6 @@
     <t>0°</t>
   </si>
   <si>
-    <t>https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg</t>
-  </si>
-  <si>
     <t>[https://www.ikea.com/sa/en/images/products/varvial-fitted-sheet-blue__1243833_pe920981_s5.jpg],[https://www.ikea.com/sa/en/images/products/praktvial-bedspread-off-white__1249510_pe923370_s5.jpg],[https://i.imgur.com/mRdMBZA.png]</t>
   </si>
   <si>
@@ -726,9 +723,6 @@
     <t>HS1 5</t>
   </si>
   <si>
-    <t>https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
-  </si>
-  <si>
     <t>[https://www.ikea.com/us/en/home-design/images/graphics/dashboard/try-product-together.png],[https://cdn.apartmenttherapy.info/image/upload/v1554217999/at/house%20tours%20stock%20archive/7f6d6749cdc500dd3a8c93d2e1c6ad6aa7be7dec.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-2.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-3.jpg]</t>
   </si>
   <si>
@@ -747,9 +741,6 @@
     <t>HS1 7</t>
   </si>
   <si>
-    <t>https://cdn-icons-png.freepik.com/512/9783/9783549.png</t>
-  </si>
-  <si>
     <t>https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg</t>
   </si>
   <si>
@@ -771,9 +762,6 @@
     <t>HS2 4</t>
   </si>
   <si>
-    <t>https://cdn-icons-png.freepik.com/512/16695/16695235.png</t>
-  </si>
-  <si>
     <t>https://i.pinimg.com/736x/cd/40/25/cd402521325c735c601f6de05fcf4f8d.jpg</t>
   </si>
   <si>
@@ -781,9 +769,6 @@
   </si>
   <si>
     <t>HS2 6</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png</t>
   </si>
   <si>
     <t>"Hey, Check this our Chair Collections"</t>
@@ -1392,6 +1377,24 @@
   </si>
   <si>
     <t>Right:110,https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg</t>
+  </si>
+  <si>
+    <t>Top:200,https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
+  </si>
+  <si>
+    <t>Top:200,https://cdn-icons-png.freepik.com/512/9783/9783549.png</t>
+  </si>
+  <si>
+    <t>Top:200,https://cdn-icons-png.freepik.com/512/16695/16695235.png</t>
+  </si>
+  <si>
+    <t>Top:200,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png</t>
+  </si>
+  <si>
+    <t>Bottom:50,https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
+  </si>
+  <si>
+    <t>Left:100,https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
   </si>
 </sst>
 </file>
@@ -2376,13 +2379,13 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2417,7 +2420,7 @@
         <v>33</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>35</v>
@@ -2453,7 +2456,7 @@
         <v>37</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="X2" s="11" t="b">
         <v>1</v>
@@ -2462,13 +2465,13 @@
         <v>1</v>
       </c>
       <c r="Z2" s="50" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AA2" s="13">
         <v>45750</v>
       </c>
       <c r="AB2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2549,13 +2552,13 @@
         <v>1</v>
       </c>
       <c r="Z3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AA3" s="13">
         <v>45750</v>
       </c>
       <c r="AB3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2636,7 +2639,7 @@
         <v>45750</v>
       </c>
       <c r="AB4" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2797,7 +2800,7 @@
         <v>45750</v>
       </c>
       <c r="AB6" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2879,7 +2882,7 @@
         <v>45750</v>
       </c>
       <c r="AB7" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2963,7 +2966,7 @@
         <v>45750</v>
       </c>
       <c r="AB8" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3047,7 +3050,7 @@
         <v>45750</v>
       </c>
       <c r="AB9" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3131,7 +3134,7 @@
         <v>45750</v>
       </c>
       <c r="AB10" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3213,7 +3216,7 @@
         <v>45750</v>
       </c>
       <c r="AB11" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3297,7 +3300,7 @@
         <v>45750</v>
       </c>
       <c r="AB12" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3381,7 +3384,7 @@
         <v>45750</v>
       </c>
       <c r="AB13" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3465,7 +3468,7 @@
         <v>45750</v>
       </c>
       <c r="AB14" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3549,7 +3552,7 @@
         <v>45750</v>
       </c>
       <c r="AB15" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3633,7 +3636,7 @@
         <v>45750</v>
       </c>
       <c r="AB16" s="51" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3717,7 +3720,7 @@
         <v>45750</v>
       </c>
       <c r="AB17" s="51" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3801,7 +3804,7 @@
         <v>45750</v>
       </c>
       <c r="AB18" s="51" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3885,7 +3888,7 @@
         <v>45750</v>
       </c>
       <c r="AB19" s="51" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3969,7 +3972,7 @@
         <v>45750</v>
       </c>
       <c r="AB20" s="51" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -4053,7 +4056,7 @@
         <v>45750</v>
       </c>
       <c r="AB21" s="51" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -4137,7 +4140,7 @@
         <v>45750</v>
       </c>
       <c r="AB22" s="51" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -4217,13 +4220,13 @@
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AA23" s="13">
         <v>45750</v>
       </c>
       <c r="AB23" s="51" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4307,7 +4310,7 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="51" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -9311,7 +9314,7 @@
         <v>188</v>
       </c>
       <c r="U1" s="47" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="V1" s="25"/>
       <c r="W1" s="25"/>
@@ -9591,28 +9594,28 @@
         <v>200</v>
       </c>
       <c r="L7" s="52" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="M7" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="O7" s="49" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="P7" s="46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q7" s="3">
         <v>18</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T7" s="3" t="b">
         <v>1</v>
@@ -9636,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>198</v>
@@ -9655,19 +9658,19 @@
         <v>200</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="M8" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q8" s="3">
         <v>22.5</v>
@@ -9676,7 +9679,7 @@
         <v>34</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T8" s="15" t="b">
         <v>0</v>
@@ -9700,7 +9703,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>198</v>
@@ -9718,20 +9721,20 @@
       <c r="K9" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="52" t="s">
+        <v>433</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="M9" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="O9" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P9" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q9" s="3">
         <v>32.799999999999997</v>
@@ -9740,7 +9743,7 @@
         <v>34</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T9" s="3" t="b">
         <v>1</v>
@@ -9764,7 +9767,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>198</v>
@@ -9784,18 +9787,18 @@
       <c r="K10" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>213</v>
+      <c r="L10" s="52" t="s">
+        <v>432</v>
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O10" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P10" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q10" s="3">
         <v>40</v>
@@ -9828,7 +9831,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>198</v>
@@ -9846,20 +9849,20 @@
       <c r="K11" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>220</v>
+      <c r="L11" s="52" t="s">
+        <v>429</v>
       </c>
       <c r="M11" s="45" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P11" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q11" s="3">
         <v>100</v>
@@ -9868,7 +9871,7 @@
         <v>34</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T11" s="3" t="b">
         <v>1</v>
@@ -9892,7 +9895,7 @@
         <v>42</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>191</v>
@@ -9940,7 +9943,7 @@
         <v>42</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>191</v>
@@ -9988,7 +9991,7 @@
         <v>42</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>198</v>
@@ -10006,20 +10009,20 @@
       <c r="K14" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>220</v>
+      <c r="L14" s="52" t="s">
+        <v>429</v>
       </c>
       <c r="M14" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q14" s="3">
         <v>18</v>
@@ -10050,7 +10053,7 @@
         <v>42</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>198</v>
@@ -10068,20 +10071,20 @@
       <c r="K15" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>228</v>
+      <c r="L15" s="52" t="s">
+        <v>430</v>
       </c>
       <c r="M15" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="N15" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q15" s="3">
         <v>15.82</v>
@@ -10090,7 +10093,7 @@
         <v>34</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T15" s="3" t="b">
         <v>1</v>
@@ -10112,7 +10115,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>198</v>
@@ -10130,18 +10133,18 @@
       <c r="K16" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>228</v>
+      <c r="L16" s="52" t="s">
+        <v>430</v>
       </c>
       <c r="M16" s="19"/>
       <c r="N16" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q16" s="3">
         <v>45.65</v>
@@ -10150,7 +10153,7 @@
         <v>34</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T16" s="3" t="b">
         <v>1</v>
@@ -10172,7 +10175,7 @@
         <v>42</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>198</v>
@@ -10190,18 +10193,18 @@
       <c r="K17" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>232</v>
+      <c r="L17" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="M17" s="19"/>
       <c r="N17" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O17" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P17" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q17" s="3">
         <v>40</v>
@@ -10210,7 +10213,7 @@
         <v>34</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T17" s="3" t="b">
         <v>1</v>
@@ -10232,7 +10235,7 @@
         <v>42</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>198</v>
@@ -10250,18 +10253,18 @@
       <c r="K18" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L18" s="6" t="s">
-        <v>232</v>
+      <c r="L18" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q18" s="3">
         <v>100</v>
@@ -10270,7 +10273,7 @@
         <v>34</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T18" s="3" t="b">
         <v>1</v>
@@ -10292,7 +10295,7 @@
         <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>191</v>
@@ -10340,7 +10343,7 @@
         <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>191</v>
@@ -10388,7 +10391,7 @@
         <v>48</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>198</v>
@@ -10409,13 +10412,13 @@
       <c r="L21" s="3"/>
       <c r="M21" s="19"/>
       <c r="N21" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q21" s="26">
         <v>18</v>
@@ -10424,7 +10427,7 @@
         <v>34</v>
       </c>
       <c r="S21" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T21" s="3" t="b">
         <v>1</v>
@@ -10446,7 +10449,7 @@
         <v>48</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>198</v>
@@ -10467,13 +10470,13 @@
       <c r="L22" s="3"/>
       <c r="M22" s="19"/>
       <c r="N22" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q22" s="27">
         <v>22</v>
@@ -10482,7 +10485,7 @@
         <v>34</v>
       </c>
       <c r="S22" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T22" s="3" t="b">
         <v>1</v>
@@ -10504,7 +10507,7 @@
         <v>48</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>198</v>
@@ -10525,13 +10528,13 @@
       <c r="L23" s="3"/>
       <c r="M23" s="19"/>
       <c r="N23" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P23" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P23" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q23" s="26">
         <v>32</v>
@@ -10540,7 +10543,7 @@
         <v>34</v>
       </c>
       <c r="S23" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T23" s="3" t="b">
         <v>1</v>
@@ -10562,7 +10565,7 @@
         <v>48</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>198</v>
@@ -10583,13 +10586,13 @@
       <c r="L24" s="3"/>
       <c r="M24" s="19"/>
       <c r="N24" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O24" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P24" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q24" s="27">
         <v>40</v>
@@ -10598,7 +10601,7 @@
         <v>34</v>
       </c>
       <c r="S24" s="31" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T24" s="3" t="b">
         <v>1</v>
@@ -10620,7 +10623,7 @@
         <v>48</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>198</v>
@@ -10638,18 +10641,18 @@
       <c r="K25" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>220</v>
+      <c r="L25" s="52" t="s">
+        <v>429</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P25" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P25" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q25" s="26">
         <v>100</v>
@@ -10658,7 +10661,7 @@
         <v>34</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T25" s="3" t="b">
         <v>1</v>
@@ -10680,7 +10683,7 @@
         <v>54</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>191</v>
@@ -10728,7 +10731,7 @@
         <v>54</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>191</v>
@@ -10776,7 +10779,7 @@
         <v>54</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>198</v>
@@ -10796,16 +10799,16 @@
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="N28" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O28" s="3" t="s">
+      <c r="P28" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q28" s="27">
         <v>18</v>
@@ -10814,7 +10817,7 @@
         <v>34</v>
       </c>
       <c r="S28" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T28" s="3" t="b">
         <v>1</v>
@@ -10836,7 +10839,7 @@
         <v>54</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>198</v>
@@ -10856,16 +10859,16 @@
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="19" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N29" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P29" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q29" s="26">
         <v>22</v>
@@ -10874,7 +10877,7 @@
         <v>34</v>
       </c>
       <c r="S29" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T29" s="3" t="b">
         <v>1</v>
@@ -10896,7 +10899,7 @@
         <v>54</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>198</v>
@@ -10917,13 +10920,13 @@
       <c r="L30" s="3"/>
       <c r="M30" s="19"/>
       <c r="N30" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O30" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q30" s="27">
         <v>32</v>
@@ -10932,7 +10935,7 @@
         <v>34</v>
       </c>
       <c r="S30" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T30" s="3" t="b">
         <v>1</v>
@@ -10954,7 +10957,7 @@
         <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>198</v>
@@ -10972,18 +10975,18 @@
       <c r="K31" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="L31" s="6" t="s">
-        <v>232</v>
+      <c r="L31" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="M31" s="19"/>
       <c r="N31" s="34" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O31" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P31" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q31" s="29">
         <v>40</v>
@@ -10992,7 +10995,7 @@
         <v>34</v>
       </c>
       <c r="S31" s="35" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T31" s="3" t="b">
         <v>1</v>
@@ -11014,7 +11017,7 @@
         <v>54</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>198</v>
@@ -11032,20 +11035,20 @@
       <c r="K32" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L32" s="6" t="s">
-        <v>232</v>
+      <c r="L32" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="M32" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N32" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q32" s="27">
         <v>100</v>
@@ -11054,7 +11057,7 @@
         <v>34</v>
       </c>
       <c r="S32" s="31" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T32" s="3" t="b">
         <v>1</v>
@@ -11076,7 +11079,7 @@
         <v>59</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>191</v>
@@ -11124,7 +11127,7 @@
         <v>59</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>191</v>
@@ -11172,7 +11175,7 @@
         <v>59</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>198</v>
@@ -11190,20 +11193,20 @@
       <c r="K35" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L35" s="6" t="s">
-        <v>201</v>
+      <c r="L35" s="52" t="s">
+        <v>426</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N35" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O35" s="3" t="s">
+      <c r="P35" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P35" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q35" s="3">
         <v>18</v>
@@ -11212,7 +11215,7 @@
         <v>34</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T35" s="3" t="b">
         <v>1</v>
@@ -11234,7 +11237,7 @@
         <v>59</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>198</v>
@@ -11252,20 +11255,20 @@
       <c r="K36" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="L36" s="6" t="s">
-        <v>201</v>
+      <c r="L36" s="52" t="s">
+        <v>426</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="N36" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P36" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q36" s="3">
         <v>22</v>
@@ -11274,7 +11277,7 @@
         <v>34</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T36" s="3" t="b">
         <v>1</v>
@@ -11296,7 +11299,7 @@
         <v>59</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>198</v>
@@ -11314,18 +11317,18 @@
       <c r="K37" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L37" s="6" t="s">
-        <v>213</v>
+      <c r="L37" s="52" t="s">
+        <v>428</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O37" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P37" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P37" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q37" s="3">
         <v>32</v>
@@ -11334,7 +11337,7 @@
         <v>34</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T37" s="3" t="b">
         <v>1</v>
@@ -11356,7 +11359,7 @@
         <v>59</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>198</v>
@@ -11374,18 +11377,18 @@
       <c r="K38" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>213</v>
+      <c r="L38" s="52" t="s">
+        <v>428</v>
       </c>
       <c r="M38" s="19"/>
       <c r="N38" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O38" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P38" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q38" s="3">
         <v>40</v>
@@ -11394,7 +11397,7 @@
         <v>34</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T38" s="3" t="b">
         <v>1</v>
@@ -11416,7 +11419,7 @@
         <v>59</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>198</v>
@@ -11434,18 +11437,18 @@
       <c r="K39" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L39" s="6" t="s">
-        <v>220</v>
+      <c r="L39" s="52" t="s">
+        <v>429</v>
       </c>
       <c r="M39" s="19"/>
       <c r="N39" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O39" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P39" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P39" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q39" s="3">
         <v>100</v>
@@ -11454,7 +11457,7 @@
         <v>34</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T39" s="3" t="b">
         <v>1</v>
@@ -11476,7 +11479,7 @@
         <v>69</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>191</v>
@@ -11524,7 +11527,7 @@
         <v>69</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>191</v>
@@ -11572,7 +11575,7 @@
         <v>69</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>198</v>
@@ -11590,18 +11593,18 @@
       <c r="K42" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L42" s="6" t="s">
-        <v>220</v>
+      <c r="L42" s="52" t="s">
+        <v>429</v>
       </c>
       <c r="M42" s="19"/>
       <c r="N42" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O42" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O42" s="3" t="s">
+      <c r="P42" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q42" s="3">
         <v>18</v>
@@ -11610,7 +11613,7 @@
         <v>34</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T42" s="3" t="b">
         <v>1</v>
@@ -11632,7 +11635,7 @@
         <v>69</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>198</v>
@@ -11650,18 +11653,18 @@
       <c r="K43" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>228</v>
+      <c r="L43" s="52" t="s">
+        <v>430</v>
       </c>
       <c r="M43" s="19"/>
       <c r="N43" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P43" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q43" s="3">
         <v>22</v>
@@ -11670,7 +11673,7 @@
         <v>34</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T43" s="3" t="b">
         <v>1</v>
@@ -11692,7 +11695,7 @@
         <v>69</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>198</v>
@@ -11710,18 +11713,18 @@
       <c r="K44" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L44" s="6" t="s">
-        <v>228</v>
+      <c r="L44" s="52" t="s">
+        <v>430</v>
       </c>
       <c r="M44" s="19"/>
       <c r="N44" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O44" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q44" s="3">
         <v>32</v>
@@ -11730,7 +11733,7 @@
         <v>34</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T44" s="3" t="b">
         <v>1</v>
@@ -11752,7 +11755,7 @@
         <v>69</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>198</v>
@@ -11770,18 +11773,18 @@
       <c r="K45" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="L45" s="6" t="s">
-        <v>232</v>
+      <c r="L45" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="M45" s="19"/>
       <c r="N45" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O45" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P45" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P45" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q45" s="3">
         <v>40</v>
@@ -11790,7 +11793,7 @@
         <v>34</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T45" s="3" t="b">
         <v>1</v>
@@ -11812,7 +11815,7 @@
         <v>69</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>198</v>
@@ -11830,18 +11833,18 @@
       <c r="K46" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="L46" s="6" t="s">
-        <v>232</v>
+      <c r="L46" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="M46" s="19"/>
       <c r="N46" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O46" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P46" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q46" s="3">
         <v>100</v>
@@ -11850,7 +11853,7 @@
         <v>34</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T46" s="3" t="b">
         <v>1</v>
@@ -11872,7 +11875,7 @@
         <v>75</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>191</v>
@@ -11920,7 +11923,7 @@
         <v>75</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>191</v>
@@ -11968,7 +11971,7 @@
         <v>75</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>198</v>
@@ -11989,13 +11992,13 @@
       <c r="L49" s="26"/>
       <c r="M49" s="19"/>
       <c r="N49" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O49" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O49" s="3" t="s">
+      <c r="P49" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P49" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q49" s="26">
         <v>18</v>
@@ -12004,7 +12007,7 @@
         <v>34</v>
       </c>
       <c r="S49" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T49" s="3" t="b">
         <v>1</v>
@@ -12026,7 +12029,7 @@
         <v>75</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>198</v>
@@ -12047,13 +12050,13 @@
       <c r="L50" s="26"/>
       <c r="M50" s="19"/>
       <c r="N50" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P50" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P50" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q50" s="27">
         <v>22</v>
@@ -12062,7 +12065,7 @@
         <v>34</v>
       </c>
       <c r="S50" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T50" s="3" t="b">
         <v>1</v>
@@ -12084,7 +12087,7 @@
         <v>75</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>198</v>
@@ -12105,13 +12108,13 @@
       <c r="L51" s="26"/>
       <c r="M51" s="19"/>
       <c r="N51" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O51" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P51" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P51" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q51" s="26">
         <v>32</v>
@@ -12120,7 +12123,7 @@
         <v>34</v>
       </c>
       <c r="S51" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T51" s="3" t="b">
         <v>1</v>
@@ -12142,7 +12145,7 @@
         <v>75</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>198</v>
@@ -12163,13 +12166,13 @@
       <c r="L52" s="26"/>
       <c r="M52" s="19"/>
       <c r="N52" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O52" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q52" s="27">
         <v>40</v>
@@ -12178,7 +12181,7 @@
         <v>34</v>
       </c>
       <c r="S52" s="31" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T52" s="3" t="b">
         <v>1</v>
@@ -12200,7 +12203,7 @@
         <v>75</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>198</v>
@@ -12221,13 +12224,13 @@
       <c r="L53" s="26"/>
       <c r="M53" s="19"/>
       <c r="N53" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O53" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P53" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P53" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q53" s="26">
         <v>100</v>
@@ -12236,7 +12239,7 @@
         <v>34</v>
       </c>
       <c r="S53" s="30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T53" s="3" t="b">
         <v>1</v>
@@ -12258,7 +12261,7 @@
         <v>83</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>191</v>
@@ -12306,7 +12309,7 @@
         <v>83</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>191</v>
@@ -12354,7 +12357,7 @@
         <v>83</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>198</v>
@@ -12374,16 +12377,16 @@
       </c>
       <c r="L56" s="26"/>
       <c r="M56" s="19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="N56" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O56" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O56" s="3" t="s">
+      <c r="P56" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q56" s="27">
         <v>18</v>
@@ -12392,7 +12395,7 @@
         <v>34</v>
       </c>
       <c r="S56" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T56" s="3" t="b">
         <v>1</v>
@@ -12414,7 +12417,7 @@
         <v>83</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>198</v>
@@ -12434,16 +12437,16 @@
       </c>
       <c r="L57" s="26"/>
       <c r="M57" s="19" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N57" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P57" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q57" s="26">
         <v>22</v>
@@ -12452,7 +12455,7 @@
         <v>34</v>
       </c>
       <c r="S57" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T57" s="3" t="b">
         <v>1</v>
@@ -12474,7 +12477,7 @@
         <v>83</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>198</v>
@@ -12495,13 +12498,13 @@
       <c r="L58" s="26"/>
       <c r="M58" s="19"/>
       <c r="N58" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O58" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q58" s="27">
         <v>32</v>
@@ -12510,7 +12513,7 @@
         <v>34</v>
       </c>
       <c r="S58" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T58" s="3" t="b">
         <v>1</v>
@@ -12532,7 +12535,7 @@
         <v>83</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>198</v>
@@ -12553,13 +12556,13 @@
       <c r="L59" s="26"/>
       <c r="M59" s="19"/>
       <c r="N59" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O59" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P59" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P59" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q59" s="26">
         <v>40</v>
@@ -12568,7 +12571,7 @@
         <v>34</v>
       </c>
       <c r="S59" s="30" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T59" s="3" t="b">
         <v>1</v>
@@ -12590,7 +12593,7 @@
         <v>83</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>198</v>
@@ -12610,16 +12613,16 @@
       </c>
       <c r="L60" s="26"/>
       <c r="M60" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N60" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O60" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q60" s="27">
         <v>100</v>
@@ -12628,7 +12631,7 @@
         <v>34</v>
       </c>
       <c r="S60" s="31" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T60" s="3" t="b">
         <v>1</v>
@@ -12650,7 +12653,7 @@
         <v>89</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>191</v>
@@ -12698,7 +12701,7 @@
         <v>89</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>191</v>
@@ -12746,7 +12749,7 @@
         <v>89</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>198</v>
@@ -12766,16 +12769,16 @@
       </c>
       <c r="L63" s="26"/>
       <c r="M63" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N63" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O63" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O63" s="3" t="s">
+      <c r="P63" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P63" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q63" s="3">
         <v>18</v>
@@ -12784,7 +12787,7 @@
         <v>34</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T63" s="3" t="b">
         <v>1</v>
@@ -12806,7 +12809,7 @@
         <v>89</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>198</v>
@@ -12826,16 +12829,16 @@
       </c>
       <c r="L64" s="26"/>
       <c r="M64" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="N64" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P64" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q64" s="3">
         <v>22</v>
@@ -12844,7 +12847,7 @@
         <v>34</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T64" s="3" t="b">
         <v>1</v>
@@ -12866,7 +12869,7 @@
         <v>89</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>198</v>
@@ -12887,13 +12890,13 @@
       <c r="L65" s="26"/>
       <c r="M65" s="19"/>
       <c r="N65" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O65" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P65" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P65" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q65" s="3">
         <v>32</v>
@@ -12902,7 +12905,7 @@
         <v>34</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T65" s="3" t="b">
         <v>1</v>
@@ -12924,7 +12927,7 @@
         <v>89</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>198</v>
@@ -12945,13 +12948,13 @@
       <c r="L66" s="26"/>
       <c r="M66" s="19"/>
       <c r="N66" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O66" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q66" s="3">
         <v>40</v>
@@ -12960,7 +12963,7 @@
         <v>34</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T66" s="3" t="b">
         <v>1</v>
@@ -12982,7 +12985,7 @@
         <v>89</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>198</v>
@@ -13003,13 +13006,13 @@
       <c r="L67" s="26"/>
       <c r="M67" s="19"/>
       <c r="N67" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O67" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P67" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P67" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q67" s="3">
         <v>100</v>
@@ -13018,7 +13021,7 @@
         <v>34</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T67" s="3" t="b">
         <v>1</v>
@@ -13040,7 +13043,7 @@
         <v>94</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>191</v>
@@ -13088,7 +13091,7 @@
         <v>94</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>191</v>
@@ -13136,7 +13139,7 @@
         <v>94</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>198</v>
@@ -13157,13 +13160,13 @@
       <c r="L70" s="26"/>
       <c r="M70" s="19"/>
       <c r="N70" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O70" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O70" s="3" t="s">
+      <c r="P70" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q70" s="3">
         <v>18</v>
@@ -13172,7 +13175,7 @@
         <v>34</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T70" s="3" t="b">
         <v>1</v>
@@ -13194,7 +13197,7 @@
         <v>94</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>198</v>
@@ -13215,13 +13218,13 @@
       <c r="L71" s="26"/>
       <c r="M71" s="19"/>
       <c r="N71" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P71" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q71" s="3">
         <v>22</v>
@@ -13230,7 +13233,7 @@
         <v>34</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T71" s="3" t="b">
         <v>1</v>
@@ -13252,7 +13255,7 @@
         <v>94</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>198</v>
@@ -13273,13 +13276,13 @@
       <c r="L72" s="26"/>
       <c r="M72" s="19"/>
       <c r="N72" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O72" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q72" s="3">
         <v>32</v>
@@ -13288,7 +13291,7 @@
         <v>34</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T72" s="3" t="b">
         <v>1</v>
@@ -13310,7 +13313,7 @@
         <v>94</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>198</v>
@@ -13331,13 +13334,13 @@
       <c r="L73" s="26"/>
       <c r="M73" s="19"/>
       <c r="N73" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O73" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P73" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P73" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q73" s="3">
         <v>40</v>
@@ -13346,7 +13349,7 @@
         <v>34</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T73" s="3" t="b">
         <v>1</v>
@@ -13368,7 +13371,7 @@
         <v>94</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>198</v>
@@ -13389,13 +13392,13 @@
       <c r="L74" s="26"/>
       <c r="M74" s="19"/>
       <c r="N74" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O74" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q74" s="3">
         <v>100</v>
@@ -13404,7 +13407,7 @@
         <v>34</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T74" s="3" t="b">
         <v>1</v>
@@ -13426,7 +13429,7 @@
         <v>99</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>191</v>
@@ -13474,7 +13477,7 @@
         <v>99</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>191</v>
@@ -13522,7 +13525,7 @@
         <v>99</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>198</v>
@@ -13543,13 +13546,13 @@
       <c r="L77" s="26"/>
       <c r="M77" s="19"/>
       <c r="N77" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O77" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O77" s="3" t="s">
+      <c r="P77" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P77" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q77" s="26">
         <v>18</v>
@@ -13558,7 +13561,7 @@
         <v>34</v>
       </c>
       <c r="S77" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T77" s="3" t="b">
         <v>1</v>
@@ -13580,7 +13583,7 @@
         <v>99</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>198</v>
@@ -13601,13 +13604,13 @@
       <c r="L78" s="26"/>
       <c r="M78" s="19"/>
       <c r="N78" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P78" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P78" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q78" s="27">
         <v>22</v>
@@ -13616,7 +13619,7 @@
         <v>34</v>
       </c>
       <c r="S78" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T78" s="3" t="b">
         <v>1</v>
@@ -13638,7 +13641,7 @@
         <v>99</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>198</v>
@@ -13659,13 +13662,13 @@
       <c r="L79" s="26"/>
       <c r="M79" s="19"/>
       <c r="N79" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O79" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P79" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P79" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q79" s="26">
         <v>32</v>
@@ -13674,7 +13677,7 @@
         <v>34</v>
       </c>
       <c r="S79" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T79" s="3" t="b">
         <v>1</v>
@@ -13696,7 +13699,7 @@
         <v>99</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>198</v>
@@ -13717,13 +13720,13 @@
       <c r="L80" s="26"/>
       <c r="M80" s="19"/>
       <c r="N80" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O80" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q80" s="27">
         <v>40</v>
@@ -13732,7 +13735,7 @@
         <v>34</v>
       </c>
       <c r="S80" s="31" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T80" s="3" t="b">
         <v>1</v>
@@ -13754,7 +13757,7 @@
         <v>99</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>198</v>
@@ -13775,13 +13778,13 @@
       <c r="L81" s="26"/>
       <c r="M81" s="19"/>
       <c r="N81" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O81" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P81" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P81" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q81" s="26">
         <v>100</v>
@@ -13790,7 +13793,7 @@
         <v>34</v>
       </c>
       <c r="S81" s="30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T81" s="3" t="b">
         <v>1</v>
@@ -13812,7 +13815,7 @@
         <v>106</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>191</v>
@@ -13860,7 +13863,7 @@
         <v>106</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>191</v>
@@ -13908,7 +13911,7 @@
         <v>106</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>198</v>
@@ -13928,16 +13931,16 @@
       </c>
       <c r="L84" s="26"/>
       <c r="M84" s="19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="N84" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O84" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O84" s="3" t="s">
+      <c r="P84" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q84" s="27">
         <v>18</v>
@@ -13946,7 +13949,7 @@
         <v>34</v>
       </c>
       <c r="S84" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T84" s="3" t="b">
         <v>1</v>
@@ -13968,7 +13971,7 @@
         <v>106</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>198</v>
@@ -13988,16 +13991,16 @@
       </c>
       <c r="L85" s="26"/>
       <c r="M85" s="19" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N85" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P85" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O85" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P85" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q85" s="26">
         <v>22</v>
@@ -14006,7 +14009,7 @@
         <v>34</v>
       </c>
       <c r="S85" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T85" s="3" t="b">
         <v>1</v>
@@ -14028,7 +14031,7 @@
         <v>106</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>198</v>
@@ -14049,13 +14052,13 @@
       <c r="L86" s="26"/>
       <c r="M86" s="19"/>
       <c r="N86" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O86" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q86" s="27">
         <v>32</v>
@@ -14064,7 +14067,7 @@
         <v>34</v>
       </c>
       <c r="S86" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T86" s="3" t="b">
         <v>1</v>
@@ -14086,7 +14089,7 @@
         <v>106</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>198</v>
@@ -14107,13 +14110,13 @@
       <c r="L87" s="26"/>
       <c r="M87" s="19"/>
       <c r="N87" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O87" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P87" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q87" s="26">
         <v>40</v>
@@ -14122,7 +14125,7 @@
         <v>34</v>
       </c>
       <c r="S87" s="30" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T87" s="3" t="b">
         <v>1</v>
@@ -14144,7 +14147,7 @@
         <v>106</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>198</v>
@@ -14164,16 +14167,16 @@
       </c>
       <c r="L88" s="26"/>
       <c r="M88" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N88" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O88" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q88" s="27">
         <v>100</v>
@@ -14182,7 +14185,7 @@
         <v>34</v>
       </c>
       <c r="S88" s="31" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T88" s="3" t="b">
         <v>1</v>
@@ -14204,7 +14207,7 @@
         <v>111</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>191</v>
@@ -14252,7 +14255,7 @@
         <v>111</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>191</v>
@@ -14300,7 +14303,7 @@
         <v>111</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>198</v>
@@ -14320,16 +14323,16 @@
       </c>
       <c r="L91" s="26"/>
       <c r="M91" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N91" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O91" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O91" s="3" t="s">
+      <c r="P91" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q91" s="3">
         <v>18</v>
@@ -14338,7 +14341,7 @@
         <v>34</v>
       </c>
       <c r="S91" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T91" s="3" t="b">
         <v>1</v>
@@ -14360,7 +14363,7 @@
         <v>111</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>198</v>
@@ -14380,16 +14383,16 @@
       </c>
       <c r="L92" s="26"/>
       <c r="M92" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="N92" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P92" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O92" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q92" s="3">
         <v>22</v>
@@ -14398,7 +14401,7 @@
         <v>34</v>
       </c>
       <c r="S92" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T92" s="3" t="b">
         <v>1</v>
@@ -14420,7 +14423,7 @@
         <v>111</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>198</v>
@@ -14441,13 +14444,13 @@
       <c r="L93" s="26"/>
       <c r="M93" s="19"/>
       <c r="N93" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O93" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P93" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q93" s="3">
         <v>32</v>
@@ -14456,7 +14459,7 @@
         <v>34</v>
       </c>
       <c r="S93" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T93" s="3" t="b">
         <v>1</v>
@@ -14478,7 +14481,7 @@
         <v>111</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>198</v>
@@ -14499,13 +14502,13 @@
       <c r="L94" s="26"/>
       <c r="M94" s="19"/>
       <c r="N94" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O94" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q94" s="3">
         <v>40</v>
@@ -14514,7 +14517,7 @@
         <v>34</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T94" s="3" t="b">
         <v>1</v>
@@ -14536,7 +14539,7 @@
         <v>111</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>198</v>
@@ -14557,13 +14560,13 @@
       <c r="L95" s="26"/>
       <c r="M95" s="19"/>
       <c r="N95" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O95" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P95" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P95" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q95" s="3">
         <v>100</v>
@@ -14572,7 +14575,7 @@
         <v>34</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T95" s="3" t="b">
         <v>1</v>
@@ -14594,7 +14597,7 @@
         <v>116</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>191</v>
@@ -14642,7 +14645,7 @@
         <v>116</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>191</v>
@@ -14690,7 +14693,7 @@
         <v>116</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>198</v>
@@ -14711,13 +14714,13 @@
       <c r="L98" s="26"/>
       <c r="M98" s="19"/>
       <c r="N98" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O98" s="3" t="s">
+      <c r="P98" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q98" s="3">
         <v>18</v>
@@ -14726,7 +14729,7 @@
         <v>34</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T98" s="3" t="b">
         <v>1</v>
@@ -14748,7 +14751,7 @@
         <v>116</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>198</v>
@@ -14769,13 +14772,13 @@
       <c r="L99" s="26"/>
       <c r="M99" s="19"/>
       <c r="N99" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P99" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O99" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q99" s="3">
         <v>22</v>
@@ -14784,7 +14787,7 @@
         <v>34</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T99" s="3" t="b">
         <v>1</v>
@@ -14806,7 +14809,7 @@
         <v>116</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>198</v>
@@ -14827,13 +14830,13 @@
       <c r="L100" s="26"/>
       <c r="M100" s="19"/>
       <c r="N100" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O100" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q100" s="3">
         <v>32</v>
@@ -14842,7 +14845,7 @@
         <v>34</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T100" s="3" t="b">
         <v>1</v>
@@ -14864,7 +14867,7 @@
         <v>116</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>198</v>
@@ -14885,13 +14888,13 @@
       <c r="L101" s="26"/>
       <c r="M101" s="19"/>
       <c r="N101" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O101" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P101" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P101" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q101" s="3">
         <v>40</v>
@@ -14900,7 +14903,7 @@
         <v>34</v>
       </c>
       <c r="S101" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T101" s="3" t="b">
         <v>1</v>
@@ -14922,7 +14925,7 @@
         <v>116</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>198</v>
@@ -14943,13 +14946,13 @@
       <c r="L102" s="26"/>
       <c r="M102" s="19"/>
       <c r="N102" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P102" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q102" s="3">
         <v>100</v>
@@ -14958,7 +14961,7 @@
         <v>34</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T102" s="3" t="b">
         <v>1</v>
@@ -14968,7 +14971,7 @@
     </row>
     <row r="103" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B103" s="8">
         <v>15</v>
@@ -14980,7 +14983,7 @@
         <v>122</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>191</v>
@@ -15016,7 +15019,7 @@
     </row>
     <row r="104" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B104" s="8">
         <v>15</v>
@@ -15028,7 +15031,7 @@
         <v>122</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>191</v>
@@ -15064,7 +15067,7 @@
     </row>
     <row r="105" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B105" s="8">
         <v>15</v>
@@ -15076,7 +15079,7 @@
         <v>122</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>198</v>
@@ -15096,16 +15099,16 @@
       </c>
       <c r="L105" s="26"/>
       <c r="M105" s="19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="N105" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O105" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O105" s="3" t="s">
+      <c r="P105" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P105" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q105" s="26">
         <v>18</v>
@@ -15114,7 +15117,7 @@
         <v>34</v>
       </c>
       <c r="S105" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T105" s="3" t="b">
         <v>1</v>
@@ -15124,7 +15127,7 @@
     </row>
     <row r="106" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B106" s="8">
         <v>15</v>
@@ -15136,7 +15139,7 @@
         <v>122</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>198</v>
@@ -15156,16 +15159,16 @@
       </c>
       <c r="L106" s="26"/>
       <c r="M106" s="19" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N106" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P106" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O106" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P106" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q106" s="27">
         <v>22</v>
@@ -15174,7 +15177,7 @@
         <v>34</v>
       </c>
       <c r="S106" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T106" s="3" t="b">
         <v>1</v>
@@ -15184,7 +15187,7 @@
     </row>
     <row r="107" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B107" s="8">
         <v>15</v>
@@ -15196,7 +15199,7 @@
         <v>122</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>198</v>
@@ -15217,13 +15220,13 @@
       <c r="L107" s="26"/>
       <c r="M107" s="19"/>
       <c r="N107" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O107" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P107" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q107" s="26">
         <v>32</v>
@@ -15232,7 +15235,7 @@
         <v>34</v>
       </c>
       <c r="S107" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T107" s="3" t="b">
         <v>1</v>
@@ -15242,7 +15245,7 @@
     </row>
     <row r="108" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B108" s="8">
         <v>15</v>
@@ -15254,7 +15257,7 @@
         <v>122</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>198</v>
@@ -15275,13 +15278,13 @@
       <c r="L108" s="26"/>
       <c r="M108" s="19"/>
       <c r="N108" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O108" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q108" s="27">
         <v>40</v>
@@ -15290,7 +15293,7 @@
         <v>34</v>
       </c>
       <c r="S108" s="31" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T108" s="3" t="b">
         <v>1</v>
@@ -15300,7 +15303,7 @@
     </row>
     <row r="109" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B109" s="8">
         <v>15</v>
@@ -15312,7 +15315,7 @@
         <v>122</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>198</v>
@@ -15332,16 +15335,16 @@
       </c>
       <c r="L109" s="26"/>
       <c r="M109" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N109" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O109" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P109" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q109" s="26">
         <v>100</v>
@@ -15350,7 +15353,7 @@
         <v>34</v>
       </c>
       <c r="S109" s="30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T109" s="3" t="b">
         <v>1</v>
@@ -15360,7 +15363,7 @@
     </row>
     <row r="110" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B110" s="8">
         <v>16</v>
@@ -15372,7 +15375,7 @@
         <v>128</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>191</v>
@@ -15408,7 +15411,7 @@
     </row>
     <row r="111" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B111" s="8">
         <v>16</v>
@@ -15420,7 +15423,7 @@
         <v>128</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>191</v>
@@ -15456,7 +15459,7 @@
     </row>
     <row r="112" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B112" s="8">
         <v>16</v>
@@ -15468,7 +15471,7 @@
         <v>128</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>198</v>
@@ -15488,16 +15491,16 @@
       </c>
       <c r="L112" s="26"/>
       <c r="M112" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N112" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O112" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O112" s="3" t="s">
+      <c r="P112" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q112" s="27">
         <v>18</v>
@@ -15506,7 +15509,7 @@
         <v>34</v>
       </c>
       <c r="S112" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T112" s="3" t="b">
         <v>1</v>
@@ -15516,7 +15519,7 @@
     </row>
     <row r="113" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B113" s="8">
         <v>16</v>
@@ -15528,7 +15531,7 @@
         <v>128</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>198</v>
@@ -15548,16 +15551,16 @@
       </c>
       <c r="L113" s="26"/>
       <c r="M113" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="N113" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P113" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O113" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P113" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q113" s="26">
         <v>22</v>
@@ -15566,7 +15569,7 @@
         <v>34</v>
       </c>
       <c r="S113" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T113" s="3" t="b">
         <v>1</v>
@@ -15576,7 +15579,7 @@
     </row>
     <row r="114" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B114" s="8">
         <v>16</v>
@@ -15588,7 +15591,7 @@
         <v>128</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>198</v>
@@ -15609,13 +15612,13 @@
       <c r="L114" s="26"/>
       <c r="M114" s="19"/>
       <c r="N114" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O114" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P114" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q114" s="27">
         <v>32</v>
@@ -15624,7 +15627,7 @@
         <v>34</v>
       </c>
       <c r="S114" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T114" s="3" t="b">
         <v>1</v>
@@ -15634,7 +15637,7 @@
     </row>
     <row r="115" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B115" s="8">
         <v>16</v>
@@ -15646,7 +15649,7 @@
         <v>128</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>198</v>
@@ -15667,13 +15670,13 @@
       <c r="L115" s="26"/>
       <c r="M115" s="19"/>
       <c r="N115" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O115" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P115" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P115" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q115" s="26">
         <v>40</v>
@@ -15682,7 +15685,7 @@
         <v>34</v>
       </c>
       <c r="S115" s="30" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T115" s="3" t="b">
         <v>1</v>
@@ -15692,7 +15695,7 @@
     </row>
     <row r="116" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B116" s="8">
         <v>16</v>
@@ -15704,7 +15707,7 @@
         <v>128</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>198</v>
@@ -15725,13 +15728,13 @@
       <c r="L116" s="26"/>
       <c r="M116" s="19"/>
       <c r="N116" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O116" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q116" s="27">
         <v>100</v>
@@ -15740,7 +15743,7 @@
         <v>34</v>
       </c>
       <c r="S116" s="31" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T116" s="3" t="b">
         <v>1</v>
@@ -15750,7 +15753,7 @@
     </row>
     <row r="117" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B117" s="8">
         <v>17</v>
@@ -15762,7 +15765,7 @@
         <v>133</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>191</v>
@@ -15798,7 +15801,7 @@
     </row>
     <row r="118" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B118" s="8">
         <v>17</v>
@@ -15810,7 +15813,7 @@
         <v>133</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>191</v>
@@ -15846,7 +15849,7 @@
     </row>
     <row r="119" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B119" s="8">
         <v>17</v>
@@ -15858,7 +15861,7 @@
         <v>133</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>198</v>
@@ -15879,13 +15882,13 @@
       <c r="L119" s="26"/>
       <c r="M119" s="19"/>
       <c r="N119" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O119" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O119" s="3" t="s">
+      <c r="P119" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P119" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q119" s="3">
         <v>18</v>
@@ -15894,7 +15897,7 @@
         <v>34</v>
       </c>
       <c r="S119" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T119" s="3" t="b">
         <v>1</v>
@@ -15904,7 +15907,7 @@
     </row>
     <row r="120" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B120" s="8">
         <v>17</v>
@@ -15916,7 +15919,7 @@
         <v>133</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>198</v>
@@ -15937,13 +15940,13 @@
       <c r="L120" s="26"/>
       <c r="M120" s="19"/>
       <c r="N120" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P120" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O120" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P120" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q120" s="3">
         <v>22</v>
@@ -15952,7 +15955,7 @@
         <v>34</v>
       </c>
       <c r="S120" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T120" s="3" t="b">
         <v>1</v>
@@ -15962,7 +15965,7 @@
     </row>
     <row r="121" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B121" s="8">
         <v>17</v>
@@ -15974,7 +15977,7 @@
         <v>133</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>198</v>
@@ -15995,13 +15998,13 @@
       <c r="L121" s="26"/>
       <c r="M121" s="19"/>
       <c r="N121" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O121" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P121" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P121" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q121" s="3">
         <v>32</v>
@@ -16010,7 +16013,7 @@
         <v>34</v>
       </c>
       <c r="S121" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T121" s="3" t="b">
         <v>1</v>
@@ -16020,7 +16023,7 @@
     </row>
     <row r="122" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B122" s="8">
         <v>17</v>
@@ -16032,7 +16035,7 @@
         <v>133</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>198</v>
@@ -16053,13 +16056,13 @@
       <c r="L122" s="26"/>
       <c r="M122" s="19"/>
       <c r="N122" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O122" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P122" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q122" s="3">
         <v>40</v>
@@ -16068,7 +16071,7 @@
         <v>34</v>
       </c>
       <c r="S122" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T122" s="3" t="b">
         <v>1</v>
@@ -16078,7 +16081,7 @@
     </row>
     <row r="123" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B123" s="8">
         <v>17</v>
@@ -16090,7 +16093,7 @@
         <v>133</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>198</v>
@@ -16111,13 +16114,13 @@
       <c r="L123" s="26"/>
       <c r="M123" s="19"/>
       <c r="N123" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O123" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P123" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P123" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q123" s="3">
         <v>100</v>
@@ -16126,7 +16129,7 @@
         <v>34</v>
       </c>
       <c r="S123" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T123" s="3" t="b">
         <v>1</v>
@@ -16136,7 +16139,7 @@
     </row>
     <row r="124" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B124" s="8">
         <v>18</v>
@@ -16148,7 +16151,7 @@
         <v>142</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>191</v>
@@ -16184,7 +16187,7 @@
     </row>
     <row r="125" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B125" s="8">
         <v>18</v>
@@ -16196,7 +16199,7 @@
         <v>142</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>191</v>
@@ -16232,7 +16235,7 @@
     </row>
     <row r="126" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B126" s="8">
         <v>18</v>
@@ -16244,7 +16247,7 @@
         <v>142</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>198</v>
@@ -16265,13 +16268,13 @@
       <c r="L126" s="26"/>
       <c r="M126" s="19"/>
       <c r="N126" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O126" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O126" s="3" t="s">
+      <c r="P126" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q126" s="3">
         <v>18</v>
@@ -16280,7 +16283,7 @@
         <v>34</v>
       </c>
       <c r="S126" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T126" s="3" t="b">
         <v>1</v>
@@ -16290,7 +16293,7 @@
     </row>
     <row r="127" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B127" s="8">
         <v>18</v>
@@ -16302,7 +16305,7 @@
         <v>142</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>198</v>
@@ -16323,13 +16326,13 @@
       <c r="L127" s="26"/>
       <c r="M127" s="19"/>
       <c r="N127" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O127" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P127" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O127" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P127" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q127" s="3">
         <v>22</v>
@@ -16338,7 +16341,7 @@
         <v>34</v>
       </c>
       <c r="S127" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T127" s="3" t="b">
         <v>1</v>
@@ -16348,7 +16351,7 @@
     </row>
     <row r="128" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B128" s="8">
         <v>18</v>
@@ -16360,7 +16363,7 @@
         <v>142</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>198</v>
@@ -16381,13 +16384,13 @@
       <c r="L128" s="26"/>
       <c r="M128" s="19"/>
       <c r="N128" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O128" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P128" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q128" s="3">
         <v>32</v>
@@ -16396,7 +16399,7 @@
         <v>34</v>
       </c>
       <c r="S128" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T128" s="3" t="b">
         <v>1</v>
@@ -16406,7 +16409,7 @@
     </row>
     <row r="129" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B129" s="8">
         <v>18</v>
@@ -16418,7 +16421,7 @@
         <v>142</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>198</v>
@@ -16439,13 +16442,13 @@
       <c r="L129" s="26"/>
       <c r="M129" s="19"/>
       <c r="N129" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O129" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P129" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P129" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q129" s="3">
         <v>40</v>
@@ -16454,7 +16457,7 @@
         <v>34</v>
       </c>
       <c r="S129" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T129" s="3" t="b">
         <v>1</v>
@@ -16464,7 +16467,7 @@
     </row>
     <row r="130" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B130" s="8">
         <v>18</v>
@@ -16476,7 +16479,7 @@
         <v>142</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>198</v>
@@ -16497,13 +16500,13 @@
       <c r="L130" s="26"/>
       <c r="M130" s="19"/>
       <c r="N130" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O130" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P130" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q130" s="3">
         <v>100</v>
@@ -16512,7 +16515,7 @@
         <v>34</v>
       </c>
       <c r="S130" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T130" s="3" t="b">
         <v>1</v>
@@ -16522,7 +16525,7 @@
     </row>
     <row r="131" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B131" s="8">
         <v>19</v>
@@ -16534,7 +16537,7 @@
         <v>149</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>191</v>
@@ -16570,7 +16573,7 @@
     </row>
     <row r="132" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B132" s="8">
         <v>19</v>
@@ -16582,7 +16585,7 @@
         <v>149</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>191</v>
@@ -16618,7 +16621,7 @@
     </row>
     <row r="133" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B133" s="8">
         <v>19</v>
@@ -16630,7 +16633,7 @@
         <v>149</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>198</v>
@@ -16651,13 +16654,13 @@
       <c r="L133" s="26"/>
       <c r="M133" s="19"/>
       <c r="N133" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O133" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O133" s="3" t="s">
+      <c r="P133" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P133" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q133" s="26">
         <v>18</v>
@@ -16666,7 +16669,7 @@
         <v>34</v>
       </c>
       <c r="S133" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T133" s="3" t="b">
         <v>1</v>
@@ -16676,7 +16679,7 @@
     </row>
     <row r="134" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B134" s="8">
         <v>19</v>
@@ -16688,7 +16691,7 @@
         <v>149</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>198</v>
@@ -16709,13 +16712,13 @@
       <c r="L134" s="26"/>
       <c r="M134" s="19"/>
       <c r="N134" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P134" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O134" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P134" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q134" s="27">
         <v>22</v>
@@ -16724,7 +16727,7 @@
         <v>34</v>
       </c>
       <c r="S134" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T134" s="3" t="b">
         <v>1</v>
@@ -16734,7 +16737,7 @@
     </row>
     <row r="135" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B135" s="8">
         <v>19</v>
@@ -16746,7 +16749,7 @@
         <v>149</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>198</v>
@@ -16767,13 +16770,13 @@
       <c r="L135" s="26"/>
       <c r="M135" s="19"/>
       <c r="N135" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O135" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P135" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P135" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q135" s="26">
         <v>32</v>
@@ -16782,7 +16785,7 @@
         <v>34</v>
       </c>
       <c r="S135" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T135" s="3" t="b">
         <v>1</v>
@@ -16792,7 +16795,7 @@
     </row>
     <row r="136" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B136" s="8">
         <v>19</v>
@@ -16804,7 +16807,7 @@
         <v>149</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>198</v>
@@ -16825,13 +16828,13 @@
       <c r="L136" s="26"/>
       <c r="M136" s="19"/>
       <c r="N136" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O136" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P136" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q136" s="27">
         <v>40</v>
@@ -16840,7 +16843,7 @@
         <v>34</v>
       </c>
       <c r="S136" s="31" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T136" s="3" t="b">
         <v>1</v>
@@ -16850,7 +16853,7 @@
     </row>
     <row r="137" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B137" s="8">
         <v>19</v>
@@ -16862,7 +16865,7 @@
         <v>149</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>198</v>
@@ -16883,13 +16886,13 @@
       <c r="L137" s="26"/>
       <c r="M137" s="19"/>
       <c r="N137" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O137" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P137" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P137" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q137" s="26">
         <v>100</v>
@@ -16898,7 +16901,7 @@
         <v>34</v>
       </c>
       <c r="S137" s="30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T137" s="3" t="b">
         <v>1</v>
@@ -16908,7 +16911,7 @@
     </row>
     <row r="138" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B138" s="8">
         <v>20</v>
@@ -16920,7 +16923,7 @@
         <v>154</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>191</v>
@@ -16956,7 +16959,7 @@
     </row>
     <row r="139" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B139" s="8">
         <v>20</v>
@@ -16968,7 +16971,7 @@
         <v>154</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>191</v>
@@ -17004,7 +17007,7 @@
     </row>
     <row r="140" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B140" s="8">
         <v>20</v>
@@ -17016,7 +17019,7 @@
         <v>154</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>198</v>
@@ -17037,13 +17040,13 @@
       <c r="L140" s="26"/>
       <c r="M140" s="19"/>
       <c r="N140" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O140" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O140" s="3" t="s">
+      <c r="P140" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q140" s="27">
         <v>18</v>
@@ -17052,7 +17055,7 @@
         <v>34</v>
       </c>
       <c r="S140" s="31" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="T140" s="3" t="b">
         <v>1</v>
@@ -17062,7 +17065,7 @@
     </row>
     <row r="141" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B141" s="8">
         <v>20</v>
@@ -17074,7 +17077,7 @@
         <v>154</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>198</v>
@@ -17095,13 +17098,13 @@
       <c r="L141" s="26"/>
       <c r="M141" s="19"/>
       <c r="N141" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P141" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O141" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P141" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q141" s="26">
         <v>22</v>
@@ -17110,7 +17113,7 @@
         <v>34</v>
       </c>
       <c r="S141" s="31" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="T141" s="3" t="b">
         <v>1</v>
@@ -17120,7 +17123,7 @@
     </row>
     <row r="142" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B142" s="8">
         <v>20</v>
@@ -17132,7 +17135,7 @@
         <v>154</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>198</v>
@@ -17153,13 +17156,13 @@
       <c r="L142" s="26"/>
       <c r="M142" s="19"/>
       <c r="N142" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O142" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P142" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P142" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q142" s="27">
         <v>32</v>
@@ -17168,7 +17171,7 @@
         <v>34</v>
       </c>
       <c r="S142" s="31" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="T142" s="3" t="b">
         <v>1</v>
@@ -17178,7 +17181,7 @@
     </row>
     <row r="143" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B143" s="8">
         <v>20</v>
@@ -17190,7 +17193,7 @@
         <v>154</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>198</v>
@@ -17211,13 +17214,13 @@
       <c r="L143" s="26"/>
       <c r="M143" s="19"/>
       <c r="N143" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O143" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P143" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P143" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q143" s="26">
         <v>40</v>
@@ -17226,7 +17229,7 @@
         <v>34</v>
       </c>
       <c r="S143" s="31" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="T143" s="3" t="b">
         <v>1</v>
@@ -17236,7 +17239,7 @@
     </row>
     <row r="144" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B144" s="8">
         <v>20</v>
@@ -17248,7 +17251,7 @@
         <v>154</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>198</v>
@@ -17269,13 +17272,13 @@
       <c r="L144" s="26"/>
       <c r="M144" s="19"/>
       <c r="N144" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O144" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P144" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P144" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q144" s="27">
         <v>100</v>
@@ -17284,7 +17287,7 @@
         <v>34</v>
       </c>
       <c r="S144" s="31" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="T144" s="3" t="b">
         <v>1</v>
@@ -17294,7 +17297,7 @@
     </row>
     <row r="145" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B145" s="8">
         <v>21</v>
@@ -17306,7 +17309,7 @@
         <v>159</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>191</v>
@@ -17342,7 +17345,7 @@
     </row>
     <row r="146" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B146" s="8">
         <v>21</v>
@@ -17354,7 +17357,7 @@
         <v>159</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>191</v>
@@ -17390,7 +17393,7 @@
     </row>
     <row r="147" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B147" s="8">
         <v>21</v>
@@ -17402,7 +17405,7 @@
         <v>159</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>198</v>
@@ -17423,13 +17426,13 @@
       <c r="L147" s="26"/>
       <c r="M147" s="19"/>
       <c r="N147" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O147" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O147" s="3" t="s">
+      <c r="P147" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P147" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q147" s="3">
         <v>18</v>
@@ -17438,7 +17441,7 @@
         <v>34</v>
       </c>
       <c r="S147" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="T147" s="3" t="b">
         <v>1</v>
@@ -17448,7 +17451,7 @@
     </row>
     <row r="148" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B148" s="8">
         <v>21</v>
@@ -17460,7 +17463,7 @@
         <v>159</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>198</v>
@@ -17481,13 +17484,13 @@
       <c r="L148" s="26"/>
       <c r="M148" s="19"/>
       <c r="N148" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O148" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P148" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O148" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P148" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q148" s="3">
         <v>22</v>
@@ -17496,7 +17499,7 @@
         <v>34</v>
       </c>
       <c r="S148" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="T148" s="3" t="b">
         <v>1</v>
@@ -17506,7 +17509,7 @@
     </row>
     <row r="149" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B149" s="8">
         <v>21</v>
@@ -17518,7 +17521,7 @@
         <v>159</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>198</v>
@@ -17539,13 +17542,13 @@
       <c r="L149" s="26"/>
       <c r="M149" s="19"/>
       <c r="N149" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O149" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P149" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P149" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q149" s="3">
         <v>32</v>
@@ -17554,7 +17557,7 @@
         <v>34</v>
       </c>
       <c r="S149" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="T149" s="3" t="b">
         <v>1</v>
@@ -17564,7 +17567,7 @@
     </row>
     <row r="150" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B150" s="8">
         <v>21</v>
@@ -17576,7 +17579,7 @@
         <v>159</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>198</v>
@@ -17597,13 +17600,13 @@
       <c r="L150" s="26"/>
       <c r="M150" s="19"/>
       <c r="N150" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O150" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P150" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P150" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q150" s="3">
         <v>40</v>
@@ -17612,7 +17615,7 @@
         <v>34</v>
       </c>
       <c r="S150" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="T150" s="3" t="b">
         <v>1</v>
@@ -17622,7 +17625,7 @@
     </row>
     <row r="151" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B151" s="8">
         <v>21</v>
@@ -17634,7 +17637,7 @@
         <v>159</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>198</v>
@@ -17655,13 +17658,13 @@
       <c r="L151" s="26"/>
       <c r="M151" s="19"/>
       <c r="N151" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O151" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P151" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P151" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q151" s="3">
         <v>100</v>
@@ -17670,7 +17673,7 @@
         <v>34</v>
       </c>
       <c r="S151" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="T151" s="3" t="b">
         <v>1</v>
@@ -17680,7 +17683,7 @@
     </row>
     <row r="152" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B152" s="8">
         <v>22</v>
@@ -17692,7 +17695,7 @@
         <v>164</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>191</v>
@@ -17728,7 +17731,7 @@
     </row>
     <row r="153" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B153" s="8">
         <v>22</v>
@@ -17740,7 +17743,7 @@
         <v>164</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>191</v>
@@ -17776,7 +17779,7 @@
     </row>
     <row r="154" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B154" s="8">
         <v>22</v>
@@ -17788,7 +17791,7 @@
         <v>164</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>198</v>
@@ -17809,13 +17812,13 @@
       <c r="L154" s="26"/>
       <c r="M154" s="19"/>
       <c r="N154" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O154" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O154" s="3" t="s">
+      <c r="P154" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P154" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q154" s="3">
         <v>18</v>
@@ -17824,7 +17827,7 @@
         <v>34</v>
       </c>
       <c r="S154" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T154" s="3" t="b">
         <v>1</v>
@@ -17834,7 +17837,7 @@
     </row>
     <row r="155" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B155" s="8">
         <v>22</v>
@@ -17846,7 +17849,7 @@
         <v>164</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>198</v>
@@ -17867,13 +17870,13 @@
       <c r="L155" s="26"/>
       <c r="M155" s="19"/>
       <c r="N155" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O155" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P155" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O155" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P155" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q155" s="3">
         <v>22</v>
@@ -17882,7 +17885,7 @@
         <v>34</v>
       </c>
       <c r="S155" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T155" s="3" t="b">
         <v>1</v>
@@ -17892,7 +17895,7 @@
     </row>
     <row r="156" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B156" s="8">
         <v>22</v>
@@ -17904,7 +17907,7 @@
         <v>164</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>198</v>
@@ -17925,13 +17928,13 @@
       <c r="L156" s="26"/>
       <c r="M156" s="19"/>
       <c r="N156" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O156" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P156" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P156" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q156" s="3">
         <v>32</v>
@@ -17940,7 +17943,7 @@
         <v>34</v>
       </c>
       <c r="S156" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T156" s="3" t="b">
         <v>1</v>
@@ -17950,7 +17953,7 @@
     </row>
     <row r="157" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B157" s="8">
         <v>22</v>
@@ -17962,7 +17965,7 @@
         <v>164</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>198</v>
@@ -17983,13 +17986,13 @@
       <c r="L157" s="26"/>
       <c r="M157" s="19"/>
       <c r="N157" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O157" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P157" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P157" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q157" s="3">
         <v>40</v>
@@ -17998,7 +18001,7 @@
         <v>34</v>
       </c>
       <c r="S157" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T157" s="3" t="b">
         <v>1</v>
@@ -18008,7 +18011,7 @@
     </row>
     <row r="158" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B158" s="8">
         <v>22</v>
@@ -18020,7 +18023,7 @@
         <v>164</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>198</v>
@@ -18041,13 +18044,13 @@
       <c r="L158" s="26"/>
       <c r="M158" s="19"/>
       <c r="N158" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O158" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P158" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P158" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q158" s="3">
         <v>100</v>
@@ -18056,7 +18059,7 @@
         <v>34</v>
       </c>
       <c r="S158" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T158" s="3" t="b">
         <v>1</v>
@@ -18066,7 +18069,7 @@
     </row>
     <row r="159" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B159" s="8">
         <v>23</v>
@@ -18078,7 +18081,7 @@
         <v>170</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>191</v>
@@ -18114,7 +18117,7 @@
     </row>
     <row r="160" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B160" s="8">
         <v>23</v>
@@ -18126,7 +18129,7 @@
         <v>170</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>191</v>
@@ -18162,7 +18165,7 @@
     </row>
     <row r="161" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B161" s="8">
         <v>23</v>
@@ -18174,7 +18177,7 @@
         <v>170</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>198</v>
@@ -18195,13 +18198,13 @@
       <c r="L161" s="26"/>
       <c r="M161" s="19"/>
       <c r="N161" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O161" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O161" s="3" t="s">
+      <c r="P161" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P161" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q161" s="26">
         <v>18</v>
@@ -18210,7 +18213,7 @@
         <v>34</v>
       </c>
       <c r="S161" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T161" s="3" t="b">
         <v>1</v>
@@ -18220,7 +18223,7 @@
     </row>
     <row r="162" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B162" s="8">
         <v>23</v>
@@ -18232,7 +18235,7 @@
         <v>170</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>198</v>
@@ -18253,13 +18256,13 @@
       <c r="L162" s="26"/>
       <c r="M162" s="19"/>
       <c r="N162" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O162" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P162" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O162" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P162" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="Q162" s="27">
         <v>22</v>
@@ -18268,7 +18271,7 @@
         <v>34</v>
       </c>
       <c r="S162" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T162" s="3" t="b">
         <v>1</v>
@@ -18278,7 +18281,7 @@
     </row>
     <row r="163" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B163" s="8">
         <v>23</v>
@@ -18290,7 +18293,7 @@
         <v>170</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>198</v>
@@ -18311,13 +18314,13 @@
       <c r="L163" s="26"/>
       <c r="M163" s="19"/>
       <c r="N163" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O163" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P163" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P163" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q163" s="26">
         <v>32</v>
@@ -18326,7 +18329,7 @@
         <v>34</v>
       </c>
       <c r="S163" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T163" s="3" t="b">
         <v>1</v>
@@ -18336,7 +18339,7 @@
     </row>
     <row r="164" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B164" s="8">
         <v>23</v>
@@ -18348,7 +18351,7 @@
         <v>170</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>198</v>
@@ -18369,13 +18372,13 @@
       <c r="L164" s="26"/>
       <c r="M164" s="19"/>
       <c r="N164" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O164" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P164" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P164" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q164" s="27">
         <v>40</v>
@@ -18384,7 +18387,7 @@
         <v>34</v>
       </c>
       <c r="S164" s="31" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T164" s="3" t="b">
         <v>1</v>
@@ -18394,7 +18397,7 @@
     </row>
     <row r="165" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B165" s="8">
         <v>23</v>
@@ -18406,7 +18409,7 @@
         <v>170</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>198</v>
@@ -18426,16 +18429,16 @@
       </c>
       <c r="L165" s="26"/>
       <c r="M165" s="19" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="N165" s="29" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O165" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P165" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P165" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q165" s="29">
         <v>100</v>
@@ -18444,7 +18447,7 @@
         <v>34</v>
       </c>
       <c r="S165" s="35" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T165" s="3" t="b">
         <v>1</v>
@@ -22519,8 +22522,8 @@
     <hyperlink ref="S14" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
     <hyperlink ref="R15" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
     <hyperlink ref="R16" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="L17" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="L18" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="L17" r:id="rId12" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="L18" r:id="rId13" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
     <hyperlink ref="P21" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
     <hyperlink ref="R21" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
     <hyperlink ref="R22" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
@@ -22529,20 +22532,20 @@
     <hyperlink ref="R28" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
     <hyperlink ref="R29" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
     <hyperlink ref="R30" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="L31" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="L32" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="L35" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="L31" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="L32" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="L35" r:id="rId24" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
     <hyperlink ref="P35" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
     <hyperlink ref="R35" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="L36" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="L36" r:id="rId27" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
     <hyperlink ref="R36" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
     <hyperlink ref="R37" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
     <hyperlink ref="P42" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
     <hyperlink ref="R42" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
     <hyperlink ref="R43" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
     <hyperlink ref="R44" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="L45" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="L46" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="L45" r:id="rId34" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="L46" r:id="rId35" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
     <hyperlink ref="P49" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
     <hyperlink ref="R49" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
     <hyperlink ref="R50" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
@@ -22638,16 +22641,16 @@
         <v>172</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="F1" s="40"/>
     </row>
@@ -22659,7 +22662,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D2" s="41">
         <v>1</v>
@@ -22671,13 +22674,13 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="41" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B3" s="41" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D3" s="41">
         <v>2</v>
@@ -23719,10 +23722,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="39" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -23734,7 +23737,7 @@
         <v>199</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -23746,7 +23749,7 @@
         <v>193</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="40"/>
@@ -23755,10 +23758,10 @@
     </row>
     <row r="4" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="41" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309C2E94-5E7B-4F6F-A7D4-0925AA0E26EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76C1017-5D99-46E1-8C01-9A21ACC80453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1391,10 +1391,10 @@
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0072.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0071.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0071B.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0041.jpg</t>
   </si>
 </sst>
 </file>
@@ -2494,7 +2494,7 @@
         <v>38</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>30</v>
@@ -2581,7 +2581,7 @@
         <v>43</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>30</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7CE80F5-ABFA-4297-8A17-4389E462E580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AF2B25-25CB-466E-A8D3-9537D5A13E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2444,7 +2444,7 @@
         <v>176.61</v>
       </c>
       <c r="P2" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>
@@ -2531,7 +2531,7 @@
         <v>171.97</v>
       </c>
       <c r="P3" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q3" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AF2B25-25CB-466E-A8D3-9537D5A13E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7D75A-3BCD-47E7-8476-A3F543D83D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="438">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1325,9 +1325,6 @@
     <t>Left:100,https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0041.jpg</t>
-  </si>
-  <si>
     <t>GF 5K</t>
   </si>
   <si>
@@ -1410,9 +1407,6 @@
   </si>
   <si>
     <t>Slide-28 HS</t>
-  </si>
-  <si>
-    <t>Slide-29 HS</t>
   </si>
 </sst>
 </file>
@@ -1996,7 +1990,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AB30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AB29">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="FloorGroupName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Section2"/>
@@ -2281,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AB999"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -2414,7 +2408,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>30</v>
@@ -2438,13 +2432,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="7">
-        <v>-2.79</v>
+        <v>-3.11</v>
       </c>
       <c r="O2" s="8">
-        <v>176.61</v>
+        <v>-42.67</v>
       </c>
       <c r="P2" s="3">
-        <v>80</v>
+        <v>-100</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>
@@ -2744,7 +2738,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F6" s="51" t="s">
         <v>415</v>
@@ -4255,7 +4249,7 @@
         <v>144</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>30</v>
@@ -4339,7 +4333,7 @@
         <v>144</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I25" s="3" t="b">
         <v>1</v>
@@ -4375,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U25" s="9" t="b">
         <v>1</v>
@@ -4417,7 +4411,7 @@
         <v>144</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I26" s="3" t="b">
         <v>1</v>
@@ -4453,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U26" s="9" t="b">
         <v>1</v>
@@ -4495,7 +4489,7 @@
         <v>144</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I27" s="3" t="b">
         <v>1</v>
@@ -4531,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U27" s="9" t="b">
         <v>1</v>
@@ -4573,7 +4567,7 @@
         <v>144</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I28" s="3" t="b">
         <v>1</v>
@@ -4609,7 +4603,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="U28" s="9" t="b">
         <v>1</v>
@@ -4651,7 +4645,7 @@
         <v>144</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I29" s="3" t="b">
         <v>1</v>
@@ -4687,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="U29" s="9" t="b">
         <v>1</v>
@@ -4712,83 +4706,10 @@
         <v>400</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" s="4">
-        <v>29</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F30" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="I30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="M30" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N30" s="7">
-        <v>1</v>
-      </c>
-      <c r="O30" s="3">
-        <v>-7.6</v>
-      </c>
-      <c r="P30" s="3">
-        <v>90</v>
-      </c>
-      <c r="Q30" s="3">
-        <v>-2</v>
-      </c>
-      <c r="R30" s="3">
-        <v>0</v>
-      </c>
-      <c r="S30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="T30" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="U30" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V30" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="W30" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="X30" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="12">
-        <v>45750</v>
-      </c>
-      <c r="AB30" s="49" t="s">
-        <v>400</v>
-      </c>
+    <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="N30" s="20"/>
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D31" s="19"/>
@@ -9634,65 +9555,41 @@
       <c r="D999" s="19"/>
       <c r="L999" s="19"/>
       <c r="N999" s="20"/>
-    </row>
-    <row r="1000" spans="4:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D1000" s="19"/>
-      <c r="L1000" s="19"/>
-      <c r="N1000" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="H2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="J2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="J5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="J16" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="J18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G24" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H24" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="J24" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F3" r:id="rId13" xr:uid="{AC4D3CDF-D829-4FC6-B8CF-8BF3FBC2C38E}"/>
-    <hyperlink ref="F4" r:id="rId14" xr:uid="{1C1C4470-7349-4662-88CB-ED26E50E4B09}"/>
-    <hyperlink ref="F5" r:id="rId15" xr:uid="{A5C96526-255F-44A2-ABC1-5E6C7B0850EB}"/>
-    <hyperlink ref="F6" r:id="rId16" xr:uid="{2591374B-F1B5-447D-B127-FF2E2B794BBF}"/>
-    <hyperlink ref="F7" r:id="rId17" xr:uid="{DADC9C74-62E2-4616-8584-612682BADE2B}"/>
-    <hyperlink ref="F8" r:id="rId18" xr:uid="{F35848CD-FB13-4D8B-A6DE-79DF3A60D870}"/>
-    <hyperlink ref="F9" r:id="rId19" xr:uid="{428674A9-CCE0-41E4-BDAE-0DF12476656A}"/>
-    <hyperlink ref="F10" r:id="rId20" xr:uid="{193D55CE-CA86-4D5B-94F3-F4A9F36709F2}"/>
-    <hyperlink ref="F11" r:id="rId21" xr:uid="{7885F5E6-8EBB-41B4-96E1-3D89709CC736}"/>
-    <hyperlink ref="F12" r:id="rId22" xr:uid="{99B3EEA5-4A57-4D44-886F-6E3AC8A49D06}"/>
-    <hyperlink ref="F13" r:id="rId23" xr:uid="{DE917D8C-5EFB-4D6B-A455-4507BB392F3E}"/>
-    <hyperlink ref="F14" r:id="rId24" xr:uid="{57E08804-520E-496A-BDBE-C1919AB83F88}"/>
-    <hyperlink ref="F15" r:id="rId25" xr:uid="{B2488705-726C-4D0E-B98F-5453571B1143}"/>
-    <hyperlink ref="F16" r:id="rId26" xr:uid="{903D5D58-A572-42BB-A8B7-1F945730E5A6}"/>
-    <hyperlink ref="F17" r:id="rId27" xr:uid="{0602C901-D7F9-41D1-9CB6-12B6BF655F9D}"/>
-    <hyperlink ref="F18" r:id="rId28" xr:uid="{1DC742F4-E7ED-4072-9E92-14D29CF94F43}"/>
-    <hyperlink ref="F19" r:id="rId29" xr:uid="{C27715D6-9915-44C2-809D-405D2C8414AA}"/>
-    <hyperlink ref="F20" r:id="rId30" xr:uid="{05A83B5C-E1E4-48D8-8C6D-D6F6138E7892}"/>
-    <hyperlink ref="F21:F24" r:id="rId31" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0060.jpg" xr:uid="{BCEE8204-006A-41FF-A0A8-78044038D324}"/>
-    <hyperlink ref="F21" r:id="rId32" xr:uid="{CBC7E2D7-F3DE-4E1F-9BF9-D5EB316FC22B}"/>
-    <hyperlink ref="F22" r:id="rId33" xr:uid="{DE306989-27FB-48EC-BE33-1A0A9B4E9B86}"/>
-    <hyperlink ref="F23" r:id="rId34" xr:uid="{1EEF4534-9F54-465D-ADF9-C23A3493A43B}"/>
-    <hyperlink ref="F24" r:id="rId35" xr:uid="{B24DD1E7-5E0A-4927-A628-BF7441D0E318}"/>
-    <hyperlink ref="F25:F30" r:id="rId36" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0060.jpg" xr:uid="{DA75A68D-88D2-4F5E-A82A-ED8775684893}"/>
-    <hyperlink ref="J25" r:id="rId37" xr:uid="{F960863E-86E7-4345-B88E-5019116B0B01}"/>
-    <hyperlink ref="J26" r:id="rId38" xr:uid="{745D9AE7-CECD-46B7-97F0-0FAE4EED1D50}"/>
-    <hyperlink ref="J27" r:id="rId39" xr:uid="{F5AA404F-4C7B-4FDF-90D4-7773184A98F4}"/>
-    <hyperlink ref="J28" r:id="rId40" xr:uid="{B051E4E2-084B-406C-9635-09A660418534}"/>
-    <hyperlink ref="J29" r:id="rId41" xr:uid="{44E8095E-75EC-488A-8C47-2DC3C0A76D3D}"/>
-    <hyperlink ref="J30" r:id="rId42" xr:uid="{FE29F3C4-5546-47C1-A2CD-D954A7DB7B43}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="J5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="J16" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="J18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="H19" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="G24" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="H24" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F25:F29" r:id="rId12" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0060.jpg" xr:uid="{DA75A68D-88D2-4F5E-A82A-ED8775684893}"/>
+    <hyperlink ref="J25" r:id="rId13" xr:uid="{F960863E-86E7-4345-B88E-5019116B0B01}"/>
+    <hyperlink ref="J26" r:id="rId14" xr:uid="{745D9AE7-CECD-46B7-97F0-0FAE4EED1D50}"/>
+    <hyperlink ref="J27" r:id="rId15" xr:uid="{F5AA404F-4C7B-4FDF-90D4-7773184A98F4}"/>
+    <hyperlink ref="J28" r:id="rId16" xr:uid="{B051E4E2-084B-406C-9635-09A660418534}"/>
+    <hyperlink ref="J29" r:id="rId17" xr:uid="{44E8095E-75EC-488A-8C47-2DC3C0A76D3D}"/>
+    <hyperlink ref="F2" r:id="rId18" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{AB270BCF-1AA8-47FF-80FE-D009D633004B}"/>
+    <hyperlink ref="F3" r:id="rId19" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{47FBFB10-469E-4D20-8994-30086370DC3C}"/>
+    <hyperlink ref="F4" r:id="rId20" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{775F0E26-CD14-4782-A41D-86E840A47733}"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{79D8803E-F4DB-4B83-9B31-6B894F862571}"/>
+    <hyperlink ref="F6" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{2E4EBD61-5141-4E51-8166-1336E6629FA8}"/>
+    <hyperlink ref="F7" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{9AC10286-297E-4D90-8F31-DB00820E07A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId43"/>
-  <legacyDrawing r:id="rId44"/>
+  <pageSetup orientation="landscape" r:id="rId24"/>
+  <legacyDrawing r:id="rId25"/>
   <tableParts count="1">
-    <tablePart r:id="rId45"/>
+    <tablePart r:id="rId26"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7D75A-3BCD-47E7-8476-A3F543D83D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154795DD-00DC-465D-AFCD-382A398E93BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2432,10 +2432,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="7">
-        <v>-3.11</v>
+        <v>0.88</v>
       </c>
       <c r="O2" s="8">
-        <v>-42.67</v>
+        <v>2.15</v>
       </c>
       <c r="P2" s="3">
         <v>-100</v>
@@ -2518,11 +2518,10 @@
         <v>1</v>
       </c>
       <c r="N3" s="7">
-        <f>--7.17</f>
-        <v>7.17</v>
+        <v>-8.27</v>
       </c>
       <c r="O3" s="8">
-        <v>171.97</v>
+        <v>-47.28</v>
       </c>
       <c r="P3" s="3">
         <v>80</v>
@@ -2605,10 +2604,10 @@
         <v>1</v>
       </c>
       <c r="N4" s="7">
-        <v>-2.79</v>
+        <v>-10.69</v>
       </c>
       <c r="O4" s="8">
-        <v>176.61</v>
+        <v>-43.36</v>
       </c>
       <c r="P4" s="3">
         <v>100</v>
@@ -2686,10 +2685,10 @@
         <v>1</v>
       </c>
       <c r="N5" s="7">
-        <v>-2.79</v>
+        <v>-3.41</v>
       </c>
       <c r="O5" s="8">
-        <v>176.61</v>
+        <v>-4.79</v>
       </c>
       <c r="P5" s="3">
         <v>100</v>
@@ -2765,10 +2764,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="7">
-        <v>-2.79</v>
+        <v>-1.04</v>
       </c>
       <c r="O6" s="8">
-        <v>176.61</v>
+        <v>15.52</v>
       </c>
       <c r="P6" s="3">
         <v>100</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154795DD-00DC-465D-AFCD-382A398E93BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B27A25-3E2D-4E8D-BBA3-06431D698464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>-100</v>
+        <v>180</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>
@@ -2524,7 +2524,7 @@
         <v>-47.28</v>
       </c>
       <c r="P3" s="3">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="Q3" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B27A25-3E2D-4E8D-BBA3-06431D698464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC64512-846B-4231-862F-D4D44E02E0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>
@@ -2524,7 +2524,7 @@
         <v>-47.28</v>
       </c>
       <c r="P3" s="3">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="Q3" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC64512-846B-4231-862F-D4D44E02E0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E87871D-95BA-4D9B-AD2E-21361F4E9D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E87871D-95BA-4D9B-AD2E-21361F4E9D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DA4758-78DB-4635-ADFE-3A26176399A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DA4758-78DB-4635-ADFE-3A26176399A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F8A913-C7EB-475A-8B0C-D250E3BC6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F8A913-C7EB-475A-8B0C-D250E3BC6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB150435-E8CA-41FB-80B3-70FCC97FA6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB150435-E8CA-41FB-80B3-70FCC97FA6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AC9B44-3B7B-4C18-9743-F5CCF217C0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AC9B44-3B7B-4C18-9743-F5CCF217C0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E922BA-51DE-47AC-9DE3-0FFDD03ECFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E922BA-51DE-47AC-9DE3-0FFDD03ECFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C3AF50-B3C7-464C-80E8-CEC1F54AEC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C3AF50-B3C7-464C-80E8-CEC1F54AEC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D13F85C-30AF-4F2E-8049-566BA81E1242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D13F85C-30AF-4F2E-8049-566BA81E1242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8A630A-BA45-418C-97E7-B85F169DCB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8A630A-BA45-418C-97E7-B85F169DCB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16C76DC-3600-45D8-BBA3-B6A8004BF152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2518,10 +2518,10 @@
         <v>1</v>
       </c>
       <c r="N3" s="7">
-        <v>-8.27</v>
+        <v>-2.33</v>
       </c>
       <c r="O3" s="8">
-        <v>-47.28</v>
+        <v>-116.05</v>
       </c>
       <c r="P3" s="3">
         <v>120</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16C76DC-3600-45D8-BBA3-B6A8004BF152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C51849-3DC1-40D4-83DA-50B357B76173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="458">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1407,6 +1407,66 @@
   </si>
   <si>
     <t>Slide-28 HS</t>
+  </si>
+  <si>
+    <t>Slide-29 HS</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0045.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0065.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0067.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0068.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0069.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0070.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0064.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0071.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0072.jpg</t>
+  </si>
+  <si>
+    <t>Slide-30 HS</t>
+  </si>
+  <si>
+    <t>Slide-31 HS</t>
+  </si>
+  <si>
+    <t>Slide-24</t>
+  </si>
+  <si>
+    <t>Slide-25</t>
+  </si>
+  <si>
+    <t>Slide-26</t>
+  </si>
+  <si>
+    <t>Slide-27</t>
+  </si>
+  <si>
+    <t>Slide-28</t>
+  </si>
+  <si>
+    <t>Slide-29</t>
+  </si>
+  <si>
+    <t>Slide-30</t>
+  </si>
+  <si>
+    <t>Slide-31</t>
   </si>
 </sst>
 </file>
@@ -1990,7 +2050,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AB29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AB32">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="FloorGroupName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Section2"/>
@@ -2661,7 +2721,7 @@
         <v>48</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>30</v>
@@ -2740,7 +2800,7 @@
         <v>410</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>30</v>
@@ -2822,7 +2882,7 @@
         <v>57</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -2904,7 +2964,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>30</v>
@@ -2988,7 +3048,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>30</v>
@@ -3072,7 +3132,7 @@
         <v>77</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>30</v>
@@ -3156,7 +3216,7 @@
         <v>82</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>30</v>
@@ -3238,7 +3298,7 @@
         <v>86</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>30</v>
@@ -3322,7 +3382,7 @@
         <v>92</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>30</v>
@@ -3406,7 +3466,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>30</v>
@@ -3490,7 +3550,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>30</v>
@@ -3574,7 +3634,7 @@
         <v>105</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>30</v>
@@ -3658,7 +3718,7 @@
         <v>110</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>30</v>
@@ -3742,7 +3802,7 @@
         <v>114</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>30</v>
@@ -3826,7 +3886,7 @@
         <v>119</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>30</v>
@@ -3910,7 +3970,7 @@
         <v>126</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>30</v>
@@ -3994,7 +4054,7 @@
         <v>132</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>30</v>
@@ -4078,7 +4138,7 @@
         <v>136</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>30</v>
@@ -4162,7 +4222,7 @@
         <v>140</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>30</v>
@@ -4248,7 +4308,7 @@
         <v>144</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>30</v>
@@ -4323,7 +4383,7 @@
         <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>143</v>
+        <v>450</v>
       </c>
       <c r="D25" s="4">
         <v>24</v>
@@ -4332,7 +4392,7 @@
         <v>144</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="I25" s="3" t="b">
         <v>1</v>
@@ -4377,7 +4437,7 @@
         <v>107</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="X25" s="10" t="b">
         <v>1</v>
@@ -4401,7 +4461,7 @@
         <v>117</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>451</v>
       </c>
       <c r="D26" s="4">
         <v>25</v>
@@ -4455,7 +4515,7 @@
         <v>107</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="X26" s="10" t="b">
         <v>1</v>
@@ -4479,7 +4539,7 @@
         <v>117</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>143</v>
+        <v>452</v>
       </c>
       <c r="D27" s="4">
         <v>26</v>
@@ -4488,7 +4548,7 @@
         <v>144</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="I27" s="3" t="b">
         <v>1</v>
@@ -4533,7 +4593,7 @@
         <v>107</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="X27" s="10" t="b">
         <v>1</v>
@@ -4557,7 +4617,7 @@
         <v>117</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>143</v>
+        <v>453</v>
       </c>
       <c r="D28" s="4">
         <v>27</v>
@@ -4566,7 +4626,7 @@
         <v>144</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="I28" s="3" t="b">
         <v>1</v>
@@ -4611,7 +4671,7 @@
         <v>107</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="X28" s="10" t="b">
         <v>1</v>
@@ -4635,7 +4695,7 @@
         <v>117</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>143</v>
+        <v>454</v>
       </c>
       <c r="D29" s="4">
         <v>28</v>
@@ -4644,7 +4704,7 @@
         <v>144</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="I29" s="3" t="b">
         <v>1</v>
@@ -4689,7 +4749,7 @@
         <v>107</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="X29" s="10" t="b">
         <v>1</v>
@@ -4705,20 +4765,239 @@
         <v>400</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="N30" s="20"/>
-    </row>
-    <row r="31" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="N31" s="20"/>
-    </row>
-    <row r="32" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="N32" s="20"/>
+    <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D30" s="4">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>444</v>
+      </c>
+      <c r="I30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M30" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" s="7">
+        <v>1</v>
+      </c>
+      <c r="O30" s="3">
+        <v>-7.6</v>
+      </c>
+      <c r="P30" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>-2</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="U30" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="W30" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="X30" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="12">
+        <v>45750</v>
+      </c>
+      <c r="AB30" s="49" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D31" s="4">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="I31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M31" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" s="7">
+        <v>1</v>
+      </c>
+      <c r="O31" s="3">
+        <v>-7.6</v>
+      </c>
+      <c r="P31" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>-2</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="U31" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="W31" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="X31" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="12">
+        <v>45750</v>
+      </c>
+      <c r="AB31" s="49" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D32" s="4">
+        <v>31</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="I32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M32" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" s="7">
+        <v>1</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-7.6</v>
+      </c>
+      <c r="P32" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-2</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="U32" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="W32" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="X32" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="12">
+        <v>45750</v>
+      </c>
+      <c r="AB32" s="49" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="33" spans="4:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D33" s="19"/>
@@ -9571,24 +9850,35 @@
     <hyperlink ref="G24" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="H24" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="J24" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F25:F29" r:id="rId12" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0060.jpg" xr:uid="{DA75A68D-88D2-4F5E-A82A-ED8775684893}"/>
-    <hyperlink ref="J25" r:id="rId13" xr:uid="{F960863E-86E7-4345-B88E-5019116B0B01}"/>
-    <hyperlink ref="J26" r:id="rId14" xr:uid="{745D9AE7-CECD-46B7-97F0-0FAE4EED1D50}"/>
-    <hyperlink ref="J27" r:id="rId15" xr:uid="{F5AA404F-4C7B-4FDF-90D4-7773184A98F4}"/>
-    <hyperlink ref="J28" r:id="rId16" xr:uid="{B051E4E2-084B-406C-9635-09A660418534}"/>
-    <hyperlink ref="J29" r:id="rId17" xr:uid="{44E8095E-75EC-488A-8C47-2DC3C0A76D3D}"/>
-    <hyperlink ref="F2" r:id="rId18" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{AB270BCF-1AA8-47FF-80FE-D009D633004B}"/>
-    <hyperlink ref="F3" r:id="rId19" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{47FBFB10-469E-4D20-8994-30086370DC3C}"/>
-    <hyperlink ref="F4" r:id="rId20" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{775F0E26-CD14-4782-A41D-86E840A47733}"/>
-    <hyperlink ref="F5" r:id="rId21" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{79D8803E-F4DB-4B83-9B31-6B894F862571}"/>
-    <hyperlink ref="F6" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{2E4EBD61-5141-4E51-8166-1336E6629FA8}"/>
-    <hyperlink ref="F7" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{9AC10286-297E-4D90-8F31-DB00820E07A5}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{F960863E-86E7-4345-B88E-5019116B0B01}"/>
+    <hyperlink ref="J26" r:id="rId13" xr:uid="{745D9AE7-CECD-46B7-97F0-0FAE4EED1D50}"/>
+    <hyperlink ref="J27" r:id="rId14" xr:uid="{F5AA404F-4C7B-4FDF-90D4-7773184A98F4}"/>
+    <hyperlink ref="J28" r:id="rId15" xr:uid="{B051E4E2-084B-406C-9635-09A660418534}"/>
+    <hyperlink ref="J29" r:id="rId16" xr:uid="{44E8095E-75EC-488A-8C47-2DC3C0A76D3D}"/>
+    <hyperlink ref="F2" r:id="rId17" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{AB270BCF-1AA8-47FF-80FE-D009D633004B}"/>
+    <hyperlink ref="F3" r:id="rId18" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{47FBFB10-469E-4D20-8994-30086370DC3C}"/>
+    <hyperlink ref="F4" r:id="rId19" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{775F0E26-CD14-4782-A41D-86E840A47733}"/>
+    <hyperlink ref="F5" r:id="rId20" xr:uid="{79D8803E-F4DB-4B83-9B31-6B894F862571}"/>
+    <hyperlink ref="F26:F30" r:id="rId21" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{9925964D-A310-4E0E-83D1-2E78BC1F9E05}"/>
+    <hyperlink ref="F24" r:id="rId22" xr:uid="{7B7EBC07-2945-492E-AE24-510C2E19B39A}"/>
+    <hyperlink ref="F25" r:id="rId23" xr:uid="{A8B05568-F5A9-40CF-8EB5-0ACED574744B}"/>
+    <hyperlink ref="F26" r:id="rId24" xr:uid="{D08F559C-D83F-4F29-8262-D2CBE4D8264A}"/>
+    <hyperlink ref="F27" r:id="rId25" xr:uid="{48C4DE9F-7DB5-4F99-9356-A53636AF67E5}"/>
+    <hyperlink ref="F28" r:id="rId26" xr:uid="{977B2D9E-24F5-49C1-A5F1-263F23523C7E}"/>
+    <hyperlink ref="F29" r:id="rId27" xr:uid="{95C2D657-DCFA-4D15-8113-AE87DB68103A}"/>
+    <hyperlink ref="F30" r:id="rId28" xr:uid="{8D33B9E3-91BF-4D92-AAC9-2AB8431FCAD1}"/>
+    <hyperlink ref="F31:F32" r:id="rId29" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3" xr:uid="{1C5F36D1-692B-46B6-993A-B7C5F3D75771}"/>
+    <hyperlink ref="F31" r:id="rId30" xr:uid="{F1779D11-57B5-4C9B-A925-6D91872B27CF}"/>
+    <hyperlink ref="F32" r:id="rId31" xr:uid="{307BE293-E318-4A53-B4F6-52FD11E0187F}"/>
+    <hyperlink ref="J30" r:id="rId32" xr:uid="{4145FA64-3FE7-4A35-8775-B79866B9FA60}"/>
+    <hyperlink ref="J31" r:id="rId33" xr:uid="{CF4E9A91-67F0-423E-BCEC-C74885AF5BC9}"/>
+    <hyperlink ref="J32" r:id="rId34" xr:uid="{ECDBC281-C876-447B-A095-FEDCE057629B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId24"/>
-  <legacyDrawing r:id="rId25"/>
+  <pageSetup orientation="landscape" r:id="rId35"/>
+  <legacyDrawing r:id="rId36"/>
   <tableParts count="1">
-    <tablePart r:id="rId26"/>
+    <tablePart r:id="rId37"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9715,10 +10005,10 @@
         <v>169</v>
       </c>
       <c r="I2" s="24">
-        <v>-80.66</v>
+        <v>-18.66</v>
       </c>
       <c r="J2" s="24">
-        <v>176.91</v>
+        <v>3.6</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>170</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027BA1D0-801F-43A3-8F9B-3A5731FD555C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDF8C4A-C4C1-4D32-BB20-8B6CEECF3EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="2. Hotspots Sheet" sheetId="2" r:id="rId2"/>
-    <sheet name="3. Floors Sheet" sheetId="3" r:id="rId3"/>
-    <sheet name="4. Styles Sheet (Custom CSS)" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="3. Hotspot Datas" sheetId="5" r:id="rId3"/>
+    <sheet name="4. Floors Sheet" sheetId="3" r:id="rId4"/>
+    <sheet name="5. Styles Sheet (Custom CSS)" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="461">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1473,6 +1473,9 @@
   </si>
   <si>
     <t>Top:50,https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
+  </si>
+  <si>
+    <t>SL#</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1616,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1648,6 +1651,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor theme="9"/>
       </patternFill>
     </fill>
   </fills>
@@ -1748,7 +1757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1881,6 +1890,64 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10000,9 +10067,7 @@
       <c r="D2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>166</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>167</v>
       </c>
@@ -10048,9 +10113,7 @@
       <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
         <v>167</v>
       </c>
@@ -10096,9 +10159,7 @@
       <c r="D4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
         <v>167</v>
       </c>
@@ -10144,9 +10205,7 @@
       <c r="D5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>173</v>
-      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
         <v>174</v>
       </c>
@@ -10208,9 +10267,7 @@
       <c r="D6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>182</v>
-      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
         <v>174</v>
       </c>
@@ -10272,9 +10329,7 @@
       <c r="D7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>187</v>
-      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
         <v>174</v>
       </c>
@@ -10336,9 +10391,7 @@
       <c r="D8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>191</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
         <v>174</v>
       </c>
@@ -10398,9 +10451,7 @@
       <c r="D9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
         <v>174</v>
       </c>
@@ -23192,6 +23243,4238 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J163"/>
+  <sheetFormatPr defaultColWidth="7.609375" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7.609375" style="55"/>
+    <col min="2" max="2" width="15.38671875" customWidth="1"/>
+    <col min="3" max="3" width="22.609375" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="5" max="5" width="23.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="27.0546875" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" customWidth="1"/>
+    <col min="9" max="9" width="62.71875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="66.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A1" s="55" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A2" s="55">
+        <v>1</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="3" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A3" s="55">
+        <v>2</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+    </row>
+    <row r="4" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A4" s="55">
+        <v>3</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A5" s="55">
+        <v>4</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>456</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>373</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="54">
+        <v>18</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>378</v>
+      </c>
+      <c r="J5" s="54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A6" s="55">
+        <v>5</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>402</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H6" s="53">
+        <v>22.5</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A7" s="55">
+        <v>6</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>457</v>
+      </c>
+      <c r="D7" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" s="54">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A8" s="55">
+        <v>7</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>459</v>
+      </c>
+      <c r="D8" s="61"/>
+      <c r="E8" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H8" s="53">
+        <v>40</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="63" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A9" s="55">
+        <v>8</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>372</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="54">
+        <v>100</v>
+      </c>
+      <c r="I9" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A10" s="55">
+        <v>9</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+    </row>
+    <row r="11" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A11" s="55">
+        <v>10</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A12" s="55">
+        <v>11</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>404</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="53">
+        <v>18</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="63" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A13" s="55">
+        <v>12</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>405</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H13" s="54">
+        <v>15.82</v>
+      </c>
+      <c r="I13" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A14" s="55">
+        <v>13</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>405</v>
+      </c>
+      <c r="D14" s="61"/>
+      <c r="E14" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H14" s="53">
+        <v>45.65</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A15" s="55">
+        <v>14</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>406</v>
+      </c>
+      <c r="D15" s="57"/>
+      <c r="E15" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H15" s="54">
+        <v>40</v>
+      </c>
+      <c r="I15" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A16" s="55">
+        <v>15</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>406</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H16" s="53">
+        <v>100</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A17" s="55">
+        <v>16</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" s="54"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="65"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A18" s="55">
+        <v>17</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="53"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="65"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A19" s="55">
+        <v>18</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="54"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G19" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H19" s="64">
+        <v>18</v>
+      </c>
+      <c r="I19" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A20" s="55">
+        <v>19</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="53"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" s="64">
+        <v>22</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A21" s="55">
+        <v>20</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="54"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F21" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G21" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H21" s="64">
+        <v>32</v>
+      </c>
+      <c r="I21" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A22" s="55">
+        <v>21</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" s="53"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G22" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="64">
+        <v>40</v>
+      </c>
+      <c r="I22" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A23" s="55">
+        <v>22</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D23" s="57"/>
+      <c r="E23" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G23" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="64">
+        <v>100</v>
+      </c>
+      <c r="I23" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A24" s="55">
+        <v>23</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C24" s="53"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="65"/>
+    </row>
+    <row r="25" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A25" s="55">
+        <v>24</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="65"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A26" s="55">
+        <v>25</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" s="53"/>
+      <c r="D26" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G26" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="64">
+        <v>18</v>
+      </c>
+      <c r="I26" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A27" s="55">
+        <v>26</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C27" s="54"/>
+      <c r="D27" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="64">
+        <v>22</v>
+      </c>
+      <c r="I27" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A28" s="55">
+        <v>27</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="C28" s="53"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="64">
+        <v>32</v>
+      </c>
+      <c r="I28" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A29" s="55">
+        <v>28</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>220</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>406</v>
+      </c>
+      <c r="D29" s="57"/>
+      <c r="E29" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G29" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" s="70">
+        <v>40</v>
+      </c>
+      <c r="I29" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A30" s="55">
+        <v>29</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>406</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G30" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H30" s="64">
+        <v>100</v>
+      </c>
+      <c r="I30" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A31" s="55">
+        <v>30</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="54"/>
+    </row>
+    <row r="32" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A32" s="55">
+        <v>31</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="53"/>
+    </row>
+    <row r="33" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A33" s="55">
+        <v>32</v>
+      </c>
+      <c r="B33" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="D33" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G33" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="54">
+        <v>18</v>
+      </c>
+      <c r="I33" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A34" s="55">
+        <v>33</v>
+      </c>
+      <c r="B34" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" s="63" t="s">
+        <v>402</v>
+      </c>
+      <c r="D34" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G34" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H34" s="53">
+        <v>22</v>
+      </c>
+      <c r="I34" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J34" s="53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A35" s="55">
+        <v>34</v>
+      </c>
+      <c r="B35" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>403</v>
+      </c>
+      <c r="D35" s="57"/>
+      <c r="E35" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G35" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H35" s="54">
+        <v>32</v>
+      </c>
+      <c r="I35" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A36" s="55">
+        <v>35</v>
+      </c>
+      <c r="B36" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>403</v>
+      </c>
+      <c r="D36" s="61"/>
+      <c r="E36" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G36" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H36" s="53">
+        <v>40</v>
+      </c>
+      <c r="I36" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A37" s="55">
+        <v>36</v>
+      </c>
+      <c r="B37" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D37" s="57"/>
+      <c r="E37" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="F37" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G37" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H37" s="54">
+        <v>100</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A38" s="55">
+        <v>37</v>
+      </c>
+      <c r="B38" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" s="53"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="53"/>
+    </row>
+    <row r="39" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A39" s="55">
+        <v>38</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="54"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="54"/>
+    </row>
+    <row r="40" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A40" s="55">
+        <v>39</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="63" t="s">
+        <v>404</v>
+      </c>
+      <c r="D40" s="61"/>
+      <c r="E40" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G40" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H40" s="53">
+        <v>18</v>
+      </c>
+      <c r="I40" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A41" s="55">
+        <v>40</v>
+      </c>
+      <c r="B41" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="56" t="s">
+        <v>405</v>
+      </c>
+      <c r="D41" s="57"/>
+      <c r="E41" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F41" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G41" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H41" s="54">
+        <v>22</v>
+      </c>
+      <c r="I41" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J41" s="54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A42" s="55">
+        <v>41</v>
+      </c>
+      <c r="B42" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42" s="63" t="s">
+        <v>405</v>
+      </c>
+      <c r="D42" s="61"/>
+      <c r="E42" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F42" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G42" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H42" s="53">
+        <v>32</v>
+      </c>
+      <c r="I42" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J42" s="53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A43" s="55">
+        <v>42</v>
+      </c>
+      <c r="B43" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="C43" s="56" t="s">
+        <v>406</v>
+      </c>
+      <c r="D43" s="57"/>
+      <c r="E43" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G43" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43" s="54">
+        <v>40</v>
+      </c>
+      <c r="I43" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" s="54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A44" s="55">
+        <v>43</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="C44" s="63" t="s">
+        <v>406</v>
+      </c>
+      <c r="D44" s="61"/>
+      <c r="E44" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F44" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G44" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H44" s="53">
+        <v>100</v>
+      </c>
+      <c r="I44" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A45" s="55">
+        <v>44</v>
+      </c>
+      <c r="B45" s="54" t="s">
+        <v>236</v>
+      </c>
+      <c r="C45" s="64"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="65"/>
+    </row>
+    <row r="46" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A46" s="55">
+        <v>45</v>
+      </c>
+      <c r="B46" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" s="64"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="65"/>
+    </row>
+    <row r="47" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A47" s="55">
+        <v>46</v>
+      </c>
+      <c r="B47" s="54" t="s">
+        <v>238</v>
+      </c>
+      <c r="C47" s="64"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F47" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G47" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H47" s="64">
+        <v>18</v>
+      </c>
+      <c r="I47" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A48" s="55">
+        <v>47</v>
+      </c>
+      <c r="B48" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="C48" s="64"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G48" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H48" s="64">
+        <v>22</v>
+      </c>
+      <c r="I48" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A49" s="55">
+        <v>48</v>
+      </c>
+      <c r="B49" s="54" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" s="64"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F49" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G49" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H49" s="64">
+        <v>32</v>
+      </c>
+      <c r="I49" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A50" s="55">
+        <v>49</v>
+      </c>
+      <c r="B50" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="64"/>
+      <c r="D50" s="61"/>
+      <c r="E50" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G50" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H50" s="64">
+        <v>40</v>
+      </c>
+      <c r="I50" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J50" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A51" s="55">
+        <v>50</v>
+      </c>
+      <c r="B51" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C51" s="64"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F51" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G51" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H51" s="64">
+        <v>100</v>
+      </c>
+      <c r="I51" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J51" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A52" s="55">
+        <v>51</v>
+      </c>
+      <c r="B52" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="C52" s="64"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="64"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="65"/>
+    </row>
+    <row r="53" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A53" s="55">
+        <v>52</v>
+      </c>
+      <c r="B53" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="C53" s="64"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="64"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="65"/>
+    </row>
+    <row r="54" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A54" s="55">
+        <v>53</v>
+      </c>
+      <c r="B54" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C54" s="64"/>
+      <c r="D54" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="E54" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F54" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G54" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" s="64">
+        <v>18</v>
+      </c>
+      <c r="I54" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J54" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A55" s="55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="C55" s="64"/>
+      <c r="D55" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G55" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H55" s="64">
+        <v>22</v>
+      </c>
+      <c r="I55" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J55" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A56" s="55">
+        <v>55</v>
+      </c>
+      <c r="B56" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="C56" s="64"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G56" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H56" s="64">
+        <v>32</v>
+      </c>
+      <c r="I56" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J56" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A57" s="55">
+        <v>56</v>
+      </c>
+      <c r="B57" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="C57" s="64"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="F57" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G57" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H57" s="64">
+        <v>40</v>
+      </c>
+      <c r="I57" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J57" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A58" s="55">
+        <v>57</v>
+      </c>
+      <c r="B58" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="C58" s="64"/>
+      <c r="D58" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E58" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F58" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G58" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H58" s="64">
+        <v>100</v>
+      </c>
+      <c r="I58" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A59" s="55">
+        <v>58</v>
+      </c>
+      <c r="B59" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="C59" s="64"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54"/>
+      <c r="I59" s="64"/>
+      <c r="J59" s="54"/>
+    </row>
+    <row r="60" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A60" s="55">
+        <v>59</v>
+      </c>
+      <c r="B60" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="C60" s="64"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="64"/>
+      <c r="J60" s="53"/>
+    </row>
+    <row r="61" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A61" s="55">
+        <v>60</v>
+      </c>
+      <c r="B61" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="C61" s="64"/>
+      <c r="D61" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E61" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="F61" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G61" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H61" s="54">
+        <v>18</v>
+      </c>
+      <c r="I61" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J61" s="54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A62" s="55">
+        <v>61</v>
+      </c>
+      <c r="B62" s="53" t="s">
+        <v>253</v>
+      </c>
+      <c r="C62" s="64"/>
+      <c r="D62" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E62" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F62" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G62" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H62" s="53">
+        <v>22</v>
+      </c>
+      <c r="I62" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J62" s="53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A63" s="55">
+        <v>62</v>
+      </c>
+      <c r="B63" s="54" t="s">
+        <v>254</v>
+      </c>
+      <c r="C63" s="64"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F63" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G63" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H63" s="54">
+        <v>32</v>
+      </c>
+      <c r="I63" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J63" s="54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A64" s="55">
+        <v>63</v>
+      </c>
+      <c r="B64" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="C64" s="64"/>
+      <c r="D64" s="61"/>
+      <c r="E64" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F64" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G64" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H64" s="53">
+        <v>40</v>
+      </c>
+      <c r="I64" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J64" s="53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A65" s="55">
+        <v>64</v>
+      </c>
+      <c r="B65" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="C65" s="64"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="F65" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G65" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H65" s="54">
+        <v>100</v>
+      </c>
+      <c r="I65" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J65" s="54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A66" s="55">
+        <v>65</v>
+      </c>
+      <c r="B66" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="C66" s="64"/>
+      <c r="D66" s="61"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="53"/>
+    </row>
+    <row r="67" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A67" s="55">
+        <v>66</v>
+      </c>
+      <c r="B67" s="54" t="s">
+        <v>258</v>
+      </c>
+      <c r="C67" s="64"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="67"/>
+      <c r="J67" s="54"/>
+    </row>
+    <row r="68" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A68" s="55">
+        <v>67</v>
+      </c>
+      <c r="B68" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="C68" s="64"/>
+      <c r="D68" s="61"/>
+      <c r="E68" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="F68" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G68" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H68" s="53">
+        <v>18</v>
+      </c>
+      <c r="I68" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J68" s="53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A69" s="55">
+        <v>68</v>
+      </c>
+      <c r="B69" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="C69" s="64"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F69" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G69" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H69" s="54">
+        <v>22</v>
+      </c>
+      <c r="I69" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J69" s="54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A70" s="55">
+        <v>69</v>
+      </c>
+      <c r="B70" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="C70" s="64"/>
+      <c r="D70" s="61"/>
+      <c r="E70" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F70" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G70" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H70" s="53">
+        <v>32</v>
+      </c>
+      <c r="I70" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J70" s="53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A71" s="55">
+        <v>70</v>
+      </c>
+      <c r="B71" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="C71" s="64"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F71" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G71" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H71" s="54">
+        <v>40</v>
+      </c>
+      <c r="I71" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J71" s="54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A72" s="55">
+        <v>71</v>
+      </c>
+      <c r="B72" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="C72" s="64"/>
+      <c r="D72" s="61"/>
+      <c r="E72" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F72" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G72" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H72" s="53">
+        <v>100</v>
+      </c>
+      <c r="I72" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J72" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A73" s="55">
+        <v>72</v>
+      </c>
+      <c r="B73" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C73" s="64"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="64"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="64"/>
+      <c r="I73" s="64"/>
+      <c r="J73" s="65"/>
+    </row>
+    <row r="74" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A74" s="55">
+        <v>73</v>
+      </c>
+      <c r="B74" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="C74" s="64"/>
+      <c r="D74" s="61"/>
+      <c r="E74" s="64"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="64"/>
+      <c r="I74" s="64"/>
+      <c r="J74" s="65"/>
+    </row>
+    <row r="75" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A75" s="55">
+        <v>74</v>
+      </c>
+      <c r="B75" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="C75" s="64"/>
+      <c r="D75" s="57"/>
+      <c r="E75" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F75" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G75" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H75" s="64">
+        <v>18</v>
+      </c>
+      <c r="I75" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J75" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A76" s="55">
+        <v>75</v>
+      </c>
+      <c r="B76" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="C76" s="64"/>
+      <c r="D76" s="61"/>
+      <c r="E76" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F76" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G76" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H76" s="64">
+        <v>22</v>
+      </c>
+      <c r="I76" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J76" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A77" s="55">
+        <v>76</v>
+      </c>
+      <c r="B77" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="C77" s="64"/>
+      <c r="D77" s="57"/>
+      <c r="E77" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F77" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G77" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H77" s="64">
+        <v>32</v>
+      </c>
+      <c r="I77" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J77" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A78" s="55">
+        <v>77</v>
+      </c>
+      <c r="B78" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="C78" s="64"/>
+      <c r="D78" s="61"/>
+      <c r="E78" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="F78" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G78" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H78" s="64">
+        <v>40</v>
+      </c>
+      <c r="I78" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J78" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A79" s="55">
+        <v>78</v>
+      </c>
+      <c r="B79" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="C79" s="64"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F79" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G79" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H79" s="64">
+        <v>100</v>
+      </c>
+      <c r="I79" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J79" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A80" s="55">
+        <v>79</v>
+      </c>
+      <c r="B80" s="53" t="s">
+        <v>271</v>
+      </c>
+      <c r="C80" s="64"/>
+      <c r="D80" s="61"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="64"/>
+      <c r="J80" s="65"/>
+    </row>
+    <row r="81" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A81" s="55">
+        <v>80</v>
+      </c>
+      <c r="B81" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="C81" s="64"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="54"/>
+      <c r="H81" s="64"/>
+      <c r="I81" s="67"/>
+      <c r="J81" s="65"/>
+    </row>
+    <row r="82" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A82" s="55">
+        <v>81</v>
+      </c>
+      <c r="B82" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="C82" s="64"/>
+      <c r="D82" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="E82" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F82" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G82" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H82" s="64">
+        <v>18</v>
+      </c>
+      <c r="I82" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J82" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A83" s="55">
+        <v>82</v>
+      </c>
+      <c r="B83" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="C83" s="64"/>
+      <c r="D83" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="E83" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="F83" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G83" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H83" s="64">
+        <v>22</v>
+      </c>
+      <c r="I83" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J83" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A84" s="55">
+        <v>83</v>
+      </c>
+      <c r="B84" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="C84" s="64"/>
+      <c r="D84" s="61"/>
+      <c r="E84" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F84" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G84" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H84" s="64">
+        <v>32</v>
+      </c>
+      <c r="I84" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J84" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A85" s="55">
+        <v>84</v>
+      </c>
+      <c r="B85" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="C85" s="64"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="F85" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G85" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H85" s="64">
+        <v>40</v>
+      </c>
+      <c r="I85" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J85" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A86" s="55">
+        <v>85</v>
+      </c>
+      <c r="B86" s="53" t="s">
+        <v>277</v>
+      </c>
+      <c r="C86" s="64"/>
+      <c r="D86" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E86" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F86" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G86" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H86" s="64">
+        <v>100</v>
+      </c>
+      <c r="I86" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J86" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A87" s="55">
+        <v>86</v>
+      </c>
+      <c r="B87" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="C87" s="64"/>
+      <c r="D87" s="54"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="54"/>
+      <c r="I87" s="54"/>
+      <c r="J87" s="54"/>
+    </row>
+    <row r="88" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A88" s="55">
+        <v>87</v>
+      </c>
+      <c r="B88" s="53" t="s">
+        <v>279</v>
+      </c>
+      <c r="C88" s="64"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
+      <c r="J88" s="53"/>
+    </row>
+    <row r="89" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A89" s="55">
+        <v>88</v>
+      </c>
+      <c r="B89" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="C89" s="64"/>
+      <c r="D89" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E89" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="F89" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G89" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H89" s="54">
+        <v>18</v>
+      </c>
+      <c r="I89" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J89" s="54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A90" s="55">
+        <v>89</v>
+      </c>
+      <c r="B90" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="C90" s="64"/>
+      <c r="D90" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E90" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F90" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G90" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H90" s="53">
+        <v>22</v>
+      </c>
+      <c r="I90" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J90" s="53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A91" s="55">
+        <v>90</v>
+      </c>
+      <c r="B91" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="C91" s="64"/>
+      <c r="D91" s="57"/>
+      <c r="E91" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F91" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G91" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H91" s="54">
+        <v>32</v>
+      </c>
+      <c r="I91" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J91" s="54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A92" s="55">
+        <v>91</v>
+      </c>
+      <c r="B92" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="C92" s="64"/>
+      <c r="D92" s="61"/>
+      <c r="E92" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F92" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G92" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H92" s="53">
+        <v>40</v>
+      </c>
+      <c r="I92" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J92" s="53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A93" s="55">
+        <v>92</v>
+      </c>
+      <c r="B93" s="54" t="s">
+        <v>284</v>
+      </c>
+      <c r="C93" s="64"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="F93" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G93" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H93" s="54">
+        <v>100</v>
+      </c>
+      <c r="I93" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J93" s="54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A94" s="55">
+        <v>93</v>
+      </c>
+      <c r="B94" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="C94" s="64"/>
+      <c r="D94" s="61"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="53"/>
+      <c r="J94" s="53"/>
+    </row>
+    <row r="95" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A95" s="55">
+        <v>94</v>
+      </c>
+      <c r="B95" s="54" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" s="64"/>
+      <c r="D95" s="57"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="54"/>
+      <c r="I95" s="54"/>
+      <c r="J95" s="54"/>
+    </row>
+    <row r="96" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A96" s="55">
+        <v>95</v>
+      </c>
+      <c r="B96" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="C96" s="64"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="F96" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G96" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H96" s="53">
+        <v>18</v>
+      </c>
+      <c r="I96" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J96" s="53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A97" s="55">
+        <v>96</v>
+      </c>
+      <c r="B97" s="54" t="s">
+        <v>288</v>
+      </c>
+      <c r="C97" s="64"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F97" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G97" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H97" s="54">
+        <v>22</v>
+      </c>
+      <c r="I97" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J97" s="54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A98" s="55">
+        <v>97</v>
+      </c>
+      <c r="B98" s="53" t="s">
+        <v>289</v>
+      </c>
+      <c r="C98" s="64"/>
+      <c r="D98" s="61"/>
+      <c r="E98" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F98" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G98" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H98" s="53">
+        <v>32</v>
+      </c>
+      <c r="I98" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J98" s="53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A99" s="55">
+        <v>98</v>
+      </c>
+      <c r="B99" s="54" t="s">
+        <v>290</v>
+      </c>
+      <c r="C99" s="64"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F99" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G99" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H99" s="54">
+        <v>40</v>
+      </c>
+      <c r="I99" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J99" s="54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A100" s="55">
+        <v>99</v>
+      </c>
+      <c r="B100" s="53" t="s">
+        <v>291</v>
+      </c>
+      <c r="C100" s="64"/>
+      <c r="D100" s="61"/>
+      <c r="E100" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F100" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G100" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H100" s="53">
+        <v>100</v>
+      </c>
+      <c r="I100" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J100" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A101" s="55">
+        <v>100</v>
+      </c>
+      <c r="B101" s="54" t="s">
+        <v>293</v>
+      </c>
+      <c r="C101" s="64"/>
+      <c r="D101" s="57"/>
+      <c r="E101" s="64"/>
+      <c r="F101" s="54"/>
+      <c r="G101" s="54"/>
+      <c r="H101" s="64"/>
+      <c r="I101" s="64"/>
+      <c r="J101" s="65"/>
+    </row>
+    <row r="102" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A102" s="55">
+        <v>101</v>
+      </c>
+      <c r="B102" s="53" t="s">
+        <v>294</v>
+      </c>
+      <c r="C102" s="64"/>
+      <c r="D102" s="61"/>
+      <c r="E102" s="64"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="64"/>
+      <c r="I102" s="64"/>
+      <c r="J102" s="65"/>
+    </row>
+    <row r="103" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A103" s="55">
+        <v>102</v>
+      </c>
+      <c r="B103" s="54" t="s">
+        <v>295</v>
+      </c>
+      <c r="C103" s="64"/>
+      <c r="D103" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="E103" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F103" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G103" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H103" s="64">
+        <v>18</v>
+      </c>
+      <c r="I103" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J103" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A104" s="55">
+        <v>103</v>
+      </c>
+      <c r="B104" s="53" t="s">
+        <v>296</v>
+      </c>
+      <c r="C104" s="64"/>
+      <c r="D104" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="E104" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F104" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G104" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H104" s="64">
+        <v>22</v>
+      </c>
+      <c r="I104" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J104" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A105" s="55">
+        <v>104</v>
+      </c>
+      <c r="B105" s="54" t="s">
+        <v>297</v>
+      </c>
+      <c r="C105" s="64"/>
+      <c r="D105" s="57"/>
+      <c r="E105" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F105" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G105" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H105" s="64">
+        <v>32</v>
+      </c>
+      <c r="I105" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J105" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A106" s="55">
+        <v>105</v>
+      </c>
+      <c r="B106" s="53" t="s">
+        <v>298</v>
+      </c>
+      <c r="C106" s="64"/>
+      <c r="D106" s="61"/>
+      <c r="E106" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="F106" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G106" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H106" s="64">
+        <v>40</v>
+      </c>
+      <c r="I106" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J106" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A107" s="55">
+        <v>106</v>
+      </c>
+      <c r="B107" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="C107" s="64"/>
+      <c r="D107" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E107" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F107" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G107" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H107" s="64">
+        <v>100</v>
+      </c>
+      <c r="I107" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J107" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A108" s="55">
+        <v>107</v>
+      </c>
+      <c r="B108" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="C108" s="64"/>
+      <c r="D108" s="53"/>
+      <c r="E108" s="64"/>
+      <c r="F108" s="53"/>
+      <c r="G108" s="53"/>
+      <c r="H108" s="64"/>
+      <c r="I108" s="64"/>
+      <c r="J108" s="65"/>
+    </row>
+    <row r="109" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A109" s="55">
+        <v>108</v>
+      </c>
+      <c r="B109" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="C109" s="64"/>
+      <c r="D109" s="54"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="54"/>
+      <c r="H109" s="64"/>
+      <c r="I109" s="67"/>
+      <c r="J109" s="65"/>
+    </row>
+    <row r="110" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A110" s="55">
+        <v>109</v>
+      </c>
+      <c r="B110" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" s="64"/>
+      <c r="D110" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E110" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F110" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G110" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H110" s="64">
+        <v>18</v>
+      </c>
+      <c r="I110" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J110" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A111" s="55">
+        <v>110</v>
+      </c>
+      <c r="B111" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="C111" s="64"/>
+      <c r="D111" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E111" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="F111" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G111" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H111" s="64">
+        <v>22</v>
+      </c>
+      <c r="I111" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J111" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A112" s="55">
+        <v>111</v>
+      </c>
+      <c r="B112" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="C112" s="64"/>
+      <c r="D112" s="61"/>
+      <c r="E112" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F112" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G112" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H112" s="64">
+        <v>32</v>
+      </c>
+      <c r="I112" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J112" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A113" s="55">
+        <v>112</v>
+      </c>
+      <c r="B113" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="C113" s="64"/>
+      <c r="D113" s="57"/>
+      <c r="E113" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="F113" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G113" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H113" s="64">
+        <v>40</v>
+      </c>
+      <c r="I113" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J113" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A114" s="55">
+        <v>113</v>
+      </c>
+      <c r="B114" s="53" t="s">
+        <v>306</v>
+      </c>
+      <c r="C114" s="64"/>
+      <c r="D114" s="61"/>
+      <c r="E114" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F114" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G114" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H114" s="64">
+        <v>100</v>
+      </c>
+      <c r="I114" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J114" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A115" s="55">
+        <v>114</v>
+      </c>
+      <c r="B115" s="54" t="s">
+        <v>307</v>
+      </c>
+      <c r="C115" s="64"/>
+      <c r="D115" s="57"/>
+      <c r="E115" s="54"/>
+      <c r="F115" s="54"/>
+      <c r="G115" s="54"/>
+      <c r="H115" s="54"/>
+      <c r="I115" s="64"/>
+      <c r="J115" s="54"/>
+    </row>
+    <row r="116" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A116" s="55">
+        <v>115</v>
+      </c>
+      <c r="B116" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="C116" s="64"/>
+      <c r="D116" s="61"/>
+      <c r="E116" s="53"/>
+      <c r="F116" s="53"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="53"/>
+      <c r="I116" s="64"/>
+      <c r="J116" s="53"/>
+    </row>
+    <row r="117" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A117" s="55">
+        <v>116</v>
+      </c>
+      <c r="B117" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="C117" s="64"/>
+      <c r="D117" s="57"/>
+      <c r="E117" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="F117" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G117" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H117" s="54">
+        <v>18</v>
+      </c>
+      <c r="I117" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J117" s="54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A118" s="55">
+        <v>117</v>
+      </c>
+      <c r="B118" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="C118" s="64"/>
+      <c r="D118" s="61"/>
+      <c r="E118" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F118" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G118" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H118" s="53">
+        <v>22</v>
+      </c>
+      <c r="I118" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J118" s="53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A119" s="55">
+        <v>118</v>
+      </c>
+      <c r="B119" s="54" t="s">
+        <v>311</v>
+      </c>
+      <c r="C119" s="64"/>
+      <c r="D119" s="57"/>
+      <c r="E119" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F119" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G119" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H119" s="54">
+        <v>32</v>
+      </c>
+      <c r="I119" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J119" s="54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A120" s="55">
+        <v>119</v>
+      </c>
+      <c r="B120" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="C120" s="64"/>
+      <c r="D120" s="61"/>
+      <c r="E120" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F120" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G120" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H120" s="53">
+        <v>40</v>
+      </c>
+      <c r="I120" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J120" s="53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A121" s="55">
+        <v>120</v>
+      </c>
+      <c r="B121" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="C121" s="64"/>
+      <c r="D121" s="57"/>
+      <c r="E121" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="F121" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G121" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H121" s="54">
+        <v>100</v>
+      </c>
+      <c r="I121" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J121" s="54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A122" s="55">
+        <v>121</v>
+      </c>
+      <c r="B122" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="C122" s="64"/>
+      <c r="D122" s="61"/>
+      <c r="E122" s="53"/>
+      <c r="F122" s="53"/>
+      <c r="G122" s="53"/>
+      <c r="H122" s="53"/>
+      <c r="I122" s="64"/>
+      <c r="J122" s="53"/>
+    </row>
+    <row r="123" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A123" s="55">
+        <v>122</v>
+      </c>
+      <c r="B123" s="54" t="s">
+        <v>315</v>
+      </c>
+      <c r="C123" s="64"/>
+      <c r="D123" s="57"/>
+      <c r="E123" s="54"/>
+      <c r="F123" s="54"/>
+      <c r="G123" s="54"/>
+      <c r="H123" s="54"/>
+      <c r="I123" s="67"/>
+      <c r="J123" s="54"/>
+    </row>
+    <row r="124" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A124" s="55">
+        <v>123</v>
+      </c>
+      <c r="B124" s="53" t="s">
+        <v>316</v>
+      </c>
+      <c r="C124" s="64"/>
+      <c r="D124" s="61"/>
+      <c r="E124" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="F124" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G124" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H124" s="53">
+        <v>18</v>
+      </c>
+      <c r="I124" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J124" s="53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A125" s="55">
+        <v>124</v>
+      </c>
+      <c r="B125" s="54" t="s">
+        <v>317</v>
+      </c>
+      <c r="C125" s="64"/>
+      <c r="D125" s="57"/>
+      <c r="E125" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F125" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G125" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H125" s="54">
+        <v>22</v>
+      </c>
+      <c r="I125" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J125" s="54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A126" s="55">
+        <v>125</v>
+      </c>
+      <c r="B126" s="53" t="s">
+        <v>318</v>
+      </c>
+      <c r="C126" s="64"/>
+      <c r="D126" s="61"/>
+      <c r="E126" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F126" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G126" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H126" s="53">
+        <v>32</v>
+      </c>
+      <c r="I126" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J126" s="53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A127" s="55">
+        <v>126</v>
+      </c>
+      <c r="B127" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="C127" s="64"/>
+      <c r="D127" s="57"/>
+      <c r="E127" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F127" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G127" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H127" s="54">
+        <v>40</v>
+      </c>
+      <c r="I127" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J127" s="54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A128" s="55">
+        <v>127</v>
+      </c>
+      <c r="B128" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="C128" s="64"/>
+      <c r="D128" s="61"/>
+      <c r="E128" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F128" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G128" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H128" s="53">
+        <v>100</v>
+      </c>
+      <c r="I128" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J128" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A129" s="55">
+        <v>128</v>
+      </c>
+      <c r="B129" s="54" t="s">
+        <v>321</v>
+      </c>
+      <c r="C129" s="64"/>
+      <c r="D129" s="57"/>
+      <c r="E129" s="64"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="54"/>
+      <c r="H129" s="64"/>
+      <c r="I129" s="54"/>
+      <c r="J129" s="65"/>
+    </row>
+    <row r="130" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A130" s="55">
+        <v>129</v>
+      </c>
+      <c r="B130" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="C130" s="64"/>
+      <c r="D130" s="61"/>
+      <c r="E130" s="64"/>
+      <c r="F130" s="53"/>
+      <c r="G130" s="53"/>
+      <c r="H130" s="64"/>
+      <c r="I130" s="53"/>
+      <c r="J130" s="65"/>
+    </row>
+    <row r="131" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A131" s="55">
+        <v>130</v>
+      </c>
+      <c r="B131" s="54" t="s">
+        <v>323</v>
+      </c>
+      <c r="C131" s="64"/>
+      <c r="D131" s="57"/>
+      <c r="E131" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F131" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G131" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H131" s="64">
+        <v>18</v>
+      </c>
+      <c r="I131" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J131" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A132" s="55">
+        <v>131</v>
+      </c>
+      <c r="B132" s="53" t="s">
+        <v>324</v>
+      </c>
+      <c r="C132" s="64"/>
+      <c r="D132" s="61"/>
+      <c r="E132" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F132" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G132" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H132" s="64">
+        <v>22</v>
+      </c>
+      <c r="I132" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J132" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A133" s="55">
+        <v>132</v>
+      </c>
+      <c r="B133" s="54" t="s">
+        <v>325</v>
+      </c>
+      <c r="C133" s="64"/>
+      <c r="D133" s="57"/>
+      <c r="E133" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F133" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G133" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H133" s="64">
+        <v>32</v>
+      </c>
+      <c r="I133" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J133" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A134" s="55">
+        <v>133</v>
+      </c>
+      <c r="B134" s="53" t="s">
+        <v>326</v>
+      </c>
+      <c r="C134" s="64"/>
+      <c r="D134" s="61"/>
+      <c r="E134" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="F134" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G134" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H134" s="64">
+        <v>40</v>
+      </c>
+      <c r="I134" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J134" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A135" s="55">
+        <v>134</v>
+      </c>
+      <c r="B135" s="54" t="s">
+        <v>327</v>
+      </c>
+      <c r="C135" s="64"/>
+      <c r="D135" s="57"/>
+      <c r="E135" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F135" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G135" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H135" s="64">
+        <v>100</v>
+      </c>
+      <c r="I135" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J135" s="65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A136" s="55">
+        <v>135</v>
+      </c>
+      <c r="B136" s="53" t="s">
+        <v>328</v>
+      </c>
+      <c r="C136" s="64"/>
+      <c r="D136" s="61"/>
+      <c r="E136" s="64"/>
+      <c r="F136" s="53"/>
+      <c r="G136" s="53"/>
+      <c r="H136" s="64"/>
+      <c r="I136" s="53"/>
+      <c r="J136" s="65"/>
+    </row>
+    <row r="137" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A137" s="55">
+        <v>136</v>
+      </c>
+      <c r="B137" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="C137" s="64"/>
+      <c r="D137" s="57"/>
+      <c r="E137" s="67"/>
+      <c r="F137" s="54"/>
+      <c r="G137" s="54"/>
+      <c r="H137" s="64"/>
+      <c r="I137" s="54"/>
+      <c r="J137" s="65"/>
+    </row>
+    <row r="138" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A138" s="55">
+        <v>137</v>
+      </c>
+      <c r="B138" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="C138" s="64"/>
+      <c r="D138" s="61"/>
+      <c r="E138" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F138" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G138" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H138" s="64">
+        <v>18</v>
+      </c>
+      <c r="I138" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J138" s="65" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A139" s="55">
+        <v>138</v>
+      </c>
+      <c r="B139" s="54" t="s">
+        <v>332</v>
+      </c>
+      <c r="C139" s="64"/>
+      <c r="D139" s="57"/>
+      <c r="E139" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="F139" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G139" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H139" s="64">
+        <v>22</v>
+      </c>
+      <c r="I139" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J139" s="73" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A140" s="55">
+        <v>139</v>
+      </c>
+      <c r="B140" s="53" t="s">
+        <v>333</v>
+      </c>
+      <c r="C140" s="64"/>
+      <c r="D140" s="61"/>
+      <c r="E140" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F140" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G140" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H140" s="64">
+        <v>32</v>
+      </c>
+      <c r="I140" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J140" s="65" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A141" s="55">
+        <v>140</v>
+      </c>
+      <c r="B141" s="54" t="s">
+        <v>334</v>
+      </c>
+      <c r="C141" s="64"/>
+      <c r="D141" s="57"/>
+      <c r="E141" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="F141" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G141" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H141" s="64">
+        <v>40</v>
+      </c>
+      <c r="I141" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J141" s="73" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A142" s="55">
+        <v>141</v>
+      </c>
+      <c r="B142" s="53" t="s">
+        <v>335</v>
+      </c>
+      <c r="C142" s="64"/>
+      <c r="D142" s="61"/>
+      <c r="E142" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F142" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G142" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H142" s="64">
+        <v>100</v>
+      </c>
+      <c r="I142" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J142" s="65" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A143" s="55">
+        <v>142</v>
+      </c>
+      <c r="B143" s="54" t="s">
+        <v>336</v>
+      </c>
+      <c r="C143" s="64"/>
+      <c r="D143" s="57"/>
+      <c r="E143" s="54"/>
+      <c r="F143" s="54"/>
+      <c r="G143" s="54"/>
+      <c r="H143" s="54"/>
+      <c r="I143" s="64"/>
+      <c r="J143" s="54"/>
+    </row>
+    <row r="144" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A144" s="55">
+        <v>143</v>
+      </c>
+      <c r="B144" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="C144" s="64"/>
+      <c r="D144" s="61"/>
+      <c r="E144" s="53"/>
+      <c r="F144" s="53"/>
+      <c r="G144" s="53"/>
+      <c r="H144" s="53"/>
+      <c r="I144" s="64"/>
+      <c r="J144" s="53"/>
+    </row>
+    <row r="145" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A145" s="55">
+        <v>144</v>
+      </c>
+      <c r="B145" s="54" t="s">
+        <v>338</v>
+      </c>
+      <c r="C145" s="64"/>
+      <c r="D145" s="57"/>
+      <c r="E145" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="F145" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G145" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H145" s="54">
+        <v>18</v>
+      </c>
+      <c r="I145" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J145" s="54" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A146" s="55">
+        <v>145</v>
+      </c>
+      <c r="B146" s="53" t="s">
+        <v>340</v>
+      </c>
+      <c r="C146" s="64"/>
+      <c r="D146" s="61"/>
+      <c r="E146" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F146" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G146" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H146" s="53">
+        <v>22</v>
+      </c>
+      <c r="I146" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J146" s="53" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A147" s="55">
+        <v>146</v>
+      </c>
+      <c r="B147" s="54" t="s">
+        <v>341</v>
+      </c>
+      <c r="C147" s="64"/>
+      <c r="D147" s="57"/>
+      <c r="E147" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F147" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G147" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H147" s="54">
+        <v>32</v>
+      </c>
+      <c r="I147" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J147" s="54" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A148" s="55">
+        <v>147</v>
+      </c>
+      <c r="B148" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="C148" s="64"/>
+      <c r="D148" s="61"/>
+      <c r="E148" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F148" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G148" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H148" s="53">
+        <v>40</v>
+      </c>
+      <c r="I148" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J148" s="53" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A149" s="55">
+        <v>148</v>
+      </c>
+      <c r="B149" s="54" t="s">
+        <v>343</v>
+      </c>
+      <c r="C149" s="64"/>
+      <c r="D149" s="57"/>
+      <c r="E149" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="F149" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G149" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H149" s="54">
+        <v>100</v>
+      </c>
+      <c r="I149" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J149" s="54" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A150" s="55">
+        <v>149</v>
+      </c>
+      <c r="B150" s="53" t="s">
+        <v>344</v>
+      </c>
+      <c r="C150" s="64"/>
+      <c r="D150" s="61"/>
+      <c r="E150" s="53"/>
+      <c r="F150" s="53"/>
+      <c r="G150" s="53"/>
+      <c r="H150" s="53"/>
+      <c r="I150" s="64"/>
+      <c r="J150" s="53"/>
+    </row>
+    <row r="151" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A151" s="55">
+        <v>150</v>
+      </c>
+      <c r="B151" s="54" t="s">
+        <v>345</v>
+      </c>
+      <c r="C151" s="64"/>
+      <c r="D151" s="57"/>
+      <c r="E151" s="54"/>
+      <c r="F151" s="54"/>
+      <c r="G151" s="54"/>
+      <c r="H151" s="54"/>
+      <c r="I151" s="67"/>
+      <c r="J151" s="54"/>
+    </row>
+    <row r="152" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A152" s="55">
+        <v>151</v>
+      </c>
+      <c r="B152" s="53" t="s">
+        <v>346</v>
+      </c>
+      <c r="C152" s="64"/>
+      <c r="D152" s="61"/>
+      <c r="E152" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="F152" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G152" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H152" s="53">
+        <v>18</v>
+      </c>
+      <c r="I152" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J152" s="53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A153" s="55">
+        <v>152</v>
+      </c>
+      <c r="B153" s="54" t="s">
+        <v>347</v>
+      </c>
+      <c r="C153" s="64"/>
+      <c r="D153" s="57"/>
+      <c r="E153" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F153" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G153" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H153" s="54">
+        <v>22</v>
+      </c>
+      <c r="I153" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J153" s="54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A154" s="55">
+        <v>153</v>
+      </c>
+      <c r="B154" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="C154" s="64"/>
+      <c r="D154" s="61"/>
+      <c r="E154" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F154" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G154" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H154" s="53">
+        <v>32</v>
+      </c>
+      <c r="I154" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J154" s="53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A155" s="55">
+        <v>154</v>
+      </c>
+      <c r="B155" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="C155" s="64"/>
+      <c r="D155" s="57"/>
+      <c r="E155" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F155" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G155" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H155" s="54">
+        <v>40</v>
+      </c>
+      <c r="I155" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J155" s="54" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A156" s="55">
+        <v>155</v>
+      </c>
+      <c r="B156" s="53" t="s">
+        <v>350</v>
+      </c>
+      <c r="C156" s="64"/>
+      <c r="D156" s="61"/>
+      <c r="E156" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F156" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G156" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H156" s="53">
+        <v>100</v>
+      </c>
+      <c r="I156" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J156" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A157" s="55">
+        <v>156</v>
+      </c>
+      <c r="B157" s="54" t="s">
+        <v>351</v>
+      </c>
+      <c r="C157" s="64"/>
+      <c r="D157" s="57"/>
+      <c r="E157" s="64"/>
+      <c r="F157" s="54"/>
+      <c r="G157" s="54"/>
+      <c r="H157" s="64"/>
+      <c r="I157" s="64"/>
+      <c r="J157" s="65"/>
+    </row>
+    <row r="158" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A158" s="55">
+        <v>157</v>
+      </c>
+      <c r="B158" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="C158" s="64"/>
+      <c r="D158" s="61"/>
+      <c r="E158" s="64"/>
+      <c r="F158" s="53"/>
+      <c r="G158" s="53"/>
+      <c r="H158" s="64"/>
+      <c r="I158" s="64"/>
+      <c r="J158" s="65"/>
+    </row>
+    <row r="159" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A159" s="55">
+        <v>158</v>
+      </c>
+      <c r="B159" s="54" t="s">
+        <v>353</v>
+      </c>
+      <c r="C159" s="64"/>
+      <c r="D159" s="57"/>
+      <c r="E159" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F159" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G159" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H159" s="64">
+        <v>18</v>
+      </c>
+      <c r="I159" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J159" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A160" s="55">
+        <v>159</v>
+      </c>
+      <c r="B160" s="53" t="s">
+        <v>354</v>
+      </c>
+      <c r="C160" s="64"/>
+      <c r="D160" s="61"/>
+      <c r="E160" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F160" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G160" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H160" s="64">
+        <v>22</v>
+      </c>
+      <c r="I160" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J160" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A161" s="55">
+        <v>160</v>
+      </c>
+      <c r="B161" s="54" t="s">
+        <v>355</v>
+      </c>
+      <c r="C161" s="64"/>
+      <c r="D161" s="57"/>
+      <c r="E161" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F161" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G161" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H161" s="64">
+        <v>32</v>
+      </c>
+      <c r="I161" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J161" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A162" s="55">
+        <v>161</v>
+      </c>
+      <c r="B162" s="53" t="s">
+        <v>356</v>
+      </c>
+      <c r="C162" s="64"/>
+      <c r="D162" s="61"/>
+      <c r="E162" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="F162" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G162" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H162" s="64">
+        <v>40</v>
+      </c>
+      <c r="I162" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J162" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A163" s="55">
+        <v>162</v>
+      </c>
+      <c r="B163" s="54" t="s">
+        <v>357</v>
+      </c>
+      <c r="C163" s="64"/>
+      <c r="D163" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="E163" s="70" t="s">
+        <v>195</v>
+      </c>
+      <c r="F163" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G163" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H163" s="70">
+        <v>100</v>
+      </c>
+      <c r="I163" s="70" t="s">
+        <v>33</v>
+      </c>
+      <c r="J163" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{6339E7B0-DD91-43F9-9AA6-7575AE99BA81}"/>
+    <hyperlink ref="G5" r:id="rId2" xr:uid="{DC80D7AF-69FB-4AAA-9743-02E8CB5F9079}"/>
+    <hyperlink ref="C6" r:id="rId3" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{A36D2DA1-4E0F-463F-BD52-823614E6F14F}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{738B9507-8B22-40D6-BDF3-FFDA91DE87D0}"/>
+    <hyperlink ref="I7" r:id="rId5" xr:uid="{2CF77598-3EF2-4C04-B577-6076A34E9EE1}"/>
+    <hyperlink ref="J8" r:id="rId6" xr:uid="{3AEABC4D-2D5C-4B33-A11F-9E6767FF7514}"/>
+    <hyperlink ref="G12" r:id="rId7" xr:uid="{64D354CE-3A49-4217-ACF2-71251338491D}"/>
+    <hyperlink ref="I12" r:id="rId8" xr:uid="{44D7D327-4162-41F1-A693-DB31C169FEFD}"/>
+    <hyperlink ref="J12" r:id="rId9" xr:uid="{01FFD6B0-7C64-48E1-85C5-C64A49956307}"/>
+    <hyperlink ref="I13" r:id="rId10" xr:uid="{41651FDF-D68A-4A66-81C6-6AD85DE23FD9}"/>
+    <hyperlink ref="I14" r:id="rId11" xr:uid="{7A5E544D-B0DA-4DF2-B0C0-212A31F2A80F}"/>
+    <hyperlink ref="C15" r:id="rId12" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{5BC5963B-3916-439B-9D2F-5531AB6E9425}"/>
+    <hyperlink ref="C16" r:id="rId13" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{2E3C5B4A-D7B4-4F34-832E-7B28AE6A218C}"/>
+    <hyperlink ref="G19" r:id="rId14" xr:uid="{8B42E5A2-C150-46E6-B84A-DA0391FFA844}"/>
+    <hyperlink ref="I19" r:id="rId15" xr:uid="{790A0EE4-1017-405C-8848-CC0D9825D731}"/>
+    <hyperlink ref="I20" r:id="rId16" xr:uid="{764E6654-EFE2-4BA2-88CA-00AE8F329884}"/>
+    <hyperlink ref="I21" r:id="rId17" xr:uid="{4010C3DF-3FB7-46B2-B628-F824ED91569E}"/>
+    <hyperlink ref="G26" r:id="rId18" xr:uid="{4B3272BE-97BD-4CC8-BF98-44DD196E5699}"/>
+    <hyperlink ref="I26" r:id="rId19" xr:uid="{7086DBCC-8681-4066-9B71-B7DF4F3E2D30}"/>
+    <hyperlink ref="I27" r:id="rId20" xr:uid="{7FEAFFCA-16F0-4E78-91E4-FD82A1D3B0C4}"/>
+    <hyperlink ref="I28" r:id="rId21" xr:uid="{F20DF1DC-2961-454E-911C-ABF0A6E1F404}"/>
+    <hyperlink ref="C29" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{EA695AE7-AC33-45C1-9A23-9E4D47F22F81}"/>
+    <hyperlink ref="C30" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{BDD9060C-BB64-40F9-9378-CACE644C50DE}"/>
+    <hyperlink ref="C33" r:id="rId24" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{E5AEA5DE-3C90-4E47-B35F-AB8EFF4B4953}"/>
+    <hyperlink ref="G33" r:id="rId25" xr:uid="{714BB29E-4767-4E98-A6BF-5E37049886D7}"/>
+    <hyperlink ref="I33" r:id="rId26" xr:uid="{480CD544-5AF8-4465-8A74-C2E6369717B6}"/>
+    <hyperlink ref="C34" r:id="rId27" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{08323F9D-CA33-4346-B21A-C3B9D7BB7B7E}"/>
+    <hyperlink ref="I34" r:id="rId28" xr:uid="{2B960E4C-FE40-4CB6-BDDD-28A72E609F04}"/>
+    <hyperlink ref="I35" r:id="rId29" xr:uid="{E942CEC3-BF23-40D4-84D3-6A430C7B9E61}"/>
+    <hyperlink ref="G40" r:id="rId30" xr:uid="{7E935DD9-45FE-4501-BD0A-38D296B887E2}"/>
+    <hyperlink ref="I40" r:id="rId31" xr:uid="{77AB3D35-170E-4247-A38A-EE471314CF0F}"/>
+    <hyperlink ref="I41" r:id="rId32" xr:uid="{5C869B45-777D-436F-94DA-754D39F132EE}"/>
+    <hyperlink ref="I42" r:id="rId33" xr:uid="{B57EF70C-5460-4D80-A9E9-485C86A20447}"/>
+    <hyperlink ref="C43" r:id="rId34" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{14A5DB0A-BDA8-453F-B7D7-995AC70125A2}"/>
+    <hyperlink ref="C44" r:id="rId35" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{D772ABD5-5C69-4241-9029-7289F0BECD9E}"/>
+    <hyperlink ref="G47" r:id="rId36" xr:uid="{8FF3EFF4-4D50-425D-932F-E1369AFEF777}"/>
+    <hyperlink ref="I47" r:id="rId37" xr:uid="{2BCC0DF4-8B48-45D2-B2C3-877CDAF78588}"/>
+    <hyperlink ref="I48" r:id="rId38" xr:uid="{E4EC3E67-3D68-4B94-A561-7852D77FA6B3}"/>
+    <hyperlink ref="I49" r:id="rId39" xr:uid="{894ECB8E-FED0-43E2-9442-4B7F0F4A4295}"/>
+    <hyperlink ref="G54" r:id="rId40" xr:uid="{A803117E-054D-4B80-B016-B1B408547039}"/>
+    <hyperlink ref="I54" r:id="rId41" xr:uid="{BBDFEADA-9ABF-4070-A8DC-9D37D81222DF}"/>
+    <hyperlink ref="I55" r:id="rId42" xr:uid="{6F7A7C4C-4B7F-4891-B1F2-86BF8CF3E072}"/>
+    <hyperlink ref="I56" r:id="rId43" xr:uid="{E1C32555-4E1D-48FE-BC03-4661D89A7E35}"/>
+    <hyperlink ref="G61" r:id="rId44" xr:uid="{C63F87E6-57BC-48A6-8F09-DBC79C019A3F}"/>
+    <hyperlink ref="I61" r:id="rId45" xr:uid="{5689483F-1D81-4FD9-BD8B-31971ECBC639}"/>
+    <hyperlink ref="I62" r:id="rId46" xr:uid="{A3C4379E-4546-4AB9-9F7C-17AEBB2D66EB}"/>
+    <hyperlink ref="I63" r:id="rId47" xr:uid="{99DAA9E1-1FD4-4ADD-AB38-89706B720FBC}"/>
+    <hyperlink ref="G68" r:id="rId48" xr:uid="{E8E2FDA9-1E27-4FFB-804B-E0E26D30C7B4}"/>
+    <hyperlink ref="I68" r:id="rId49" xr:uid="{A31F79E9-5729-42B1-A972-4705B82BC49E}"/>
+    <hyperlink ref="I69" r:id="rId50" xr:uid="{B806E230-0F56-4A86-B12E-028E47C6DD6D}"/>
+    <hyperlink ref="I70" r:id="rId51" xr:uid="{4AFCC2FC-35BD-4D88-97D1-2D44E1CAAE61}"/>
+    <hyperlink ref="G75" r:id="rId52" xr:uid="{0990E094-1F39-4D06-A0D8-22C0F7201B9C}"/>
+    <hyperlink ref="I75" r:id="rId53" xr:uid="{53E99039-F506-4BBD-A687-513FE8545B0D}"/>
+    <hyperlink ref="I76" r:id="rId54" xr:uid="{1B8C272C-08D5-41FB-8D44-080496BF0EB1}"/>
+    <hyperlink ref="I77" r:id="rId55" xr:uid="{A6542184-9324-45AC-B0D7-69BA78875B9B}"/>
+    <hyperlink ref="G82" r:id="rId56" xr:uid="{BF86F5E8-DA74-4E10-9951-1F875903173A}"/>
+    <hyperlink ref="I82" r:id="rId57" xr:uid="{3404AB7B-D524-48E9-8BAB-B50B8F859456}"/>
+    <hyperlink ref="I83" r:id="rId58" xr:uid="{0BB43E61-5E6E-4DE7-AF56-E0CA3CE9C187}"/>
+    <hyperlink ref="I84" r:id="rId59" xr:uid="{D8937785-EF82-4F4E-95B5-66BC812D30AC}"/>
+    <hyperlink ref="G89" r:id="rId60" xr:uid="{A923791D-1299-4889-942D-7D3AF55335F8}"/>
+    <hyperlink ref="I89" r:id="rId61" xr:uid="{BA71708A-6D63-4358-A02C-BCC88DD28EE8}"/>
+    <hyperlink ref="I90" r:id="rId62" xr:uid="{DA4D5762-9F65-4266-8FF7-F719F27D5CD3}"/>
+    <hyperlink ref="I91" r:id="rId63" xr:uid="{58583291-A2B1-45EA-83D6-A283D0008EAE}"/>
+    <hyperlink ref="G96" r:id="rId64" xr:uid="{56CF3933-6DEA-4996-9020-35D620448BC7}"/>
+    <hyperlink ref="I96" r:id="rId65" xr:uid="{99F25E62-73B8-4C56-A75D-E3F4E24D1687}"/>
+    <hyperlink ref="I97" r:id="rId66" xr:uid="{A0A7A319-6E6A-48E1-97F1-4894965BDFB1}"/>
+    <hyperlink ref="I98" r:id="rId67" xr:uid="{8E4979CA-C5BB-4B78-B07A-E4DA6A86A294}"/>
+    <hyperlink ref="G103" r:id="rId68" xr:uid="{8B75C1BC-97B0-48EF-A7CC-5658C82397E4}"/>
+    <hyperlink ref="I103" r:id="rId69" xr:uid="{277C068A-603E-4C7F-AEEA-00F62CCE6E41}"/>
+    <hyperlink ref="I104" r:id="rId70" xr:uid="{EEDD0E31-A2BA-43EB-A7ED-4D2185D47C1A}"/>
+    <hyperlink ref="I105" r:id="rId71" xr:uid="{2F6FF619-958E-4834-81A8-4E13FA58E8FC}"/>
+    <hyperlink ref="G110" r:id="rId72" xr:uid="{185B1B4F-2099-401A-B33B-0C459ECF3654}"/>
+    <hyperlink ref="I110" r:id="rId73" xr:uid="{DDDA7BC3-1B41-43EB-A726-40B7272CE2F4}"/>
+    <hyperlink ref="I111" r:id="rId74" xr:uid="{CDC4CCA1-F9D9-43AB-9CA3-5C55AA8D916A}"/>
+    <hyperlink ref="I112" r:id="rId75" xr:uid="{1B81F8D1-E118-4A3E-94BF-B73CA6B2A3D0}"/>
+    <hyperlink ref="G117" r:id="rId76" xr:uid="{64878FCB-B8AB-481A-91E6-4431E489DF18}"/>
+    <hyperlink ref="I117" r:id="rId77" xr:uid="{45601091-B19D-4E23-A8FE-88288CA6016C}"/>
+    <hyperlink ref="I118" r:id="rId78" xr:uid="{B26A1F7D-4109-496C-95F5-2EFCC4D7EB89}"/>
+    <hyperlink ref="I119" r:id="rId79" xr:uid="{768B1FB7-B6AF-44ED-9ED7-374FAEBD3918}"/>
+    <hyperlink ref="G124" r:id="rId80" xr:uid="{6B170C46-A794-466B-9062-FAE1E547A089}"/>
+    <hyperlink ref="I124" r:id="rId81" xr:uid="{F577E69E-0A52-4E52-B80C-F8FCBF2A58DA}"/>
+    <hyperlink ref="I125" r:id="rId82" xr:uid="{DC8A9405-1319-408E-8957-B75568F6E188}"/>
+    <hyperlink ref="I126" r:id="rId83" xr:uid="{C5F11A2B-562F-4144-9B91-61E039731DD2}"/>
+    <hyperlink ref="G131" r:id="rId84" xr:uid="{478E9943-0227-40B0-9DB5-BB4CFF1DBE04}"/>
+    <hyperlink ref="I131" r:id="rId85" xr:uid="{1EFAAB46-6634-4097-ADC4-67185B20BAAF}"/>
+    <hyperlink ref="I132" r:id="rId86" xr:uid="{FC01E5F9-5C71-4278-8F2B-E44C1875A79A}"/>
+    <hyperlink ref="I133" r:id="rId87" xr:uid="{DE21D0B5-B4E7-454F-A0E2-BFC40F5BE658}"/>
+    <hyperlink ref="G138" r:id="rId88" xr:uid="{475D2958-C5A6-4BA7-860A-07231330A2A0}"/>
+    <hyperlink ref="I138" r:id="rId89" xr:uid="{718AD3B3-D45D-4AE4-896C-7D6B0ACBFFF4}"/>
+    <hyperlink ref="I139" r:id="rId90" xr:uid="{C09E5E99-0239-4341-9506-14D8AE30DC86}"/>
+    <hyperlink ref="I140" r:id="rId91" xr:uid="{7ACB77E7-EB5B-4EAE-B6B8-441CE1C371B3}"/>
+    <hyperlink ref="G145" r:id="rId92" xr:uid="{6B807B5F-01BB-4B26-AA75-D1293E103DE9}"/>
+    <hyperlink ref="I145" r:id="rId93" xr:uid="{51EDD7B2-1E1D-42E9-822A-918C1FC28A26}"/>
+    <hyperlink ref="I146" r:id="rId94" xr:uid="{1B206152-46CB-46D4-B596-B6D0A135A4CC}"/>
+    <hyperlink ref="I147" r:id="rId95" xr:uid="{31129E15-FE4F-4038-A733-5AA9071449F1}"/>
+    <hyperlink ref="G152" r:id="rId96" xr:uid="{3616167C-4414-4250-9B79-0A8D4183D87D}"/>
+    <hyperlink ref="I152" r:id="rId97" xr:uid="{F71DA604-08F7-43E1-B861-5177D8F1F657}"/>
+    <hyperlink ref="I153" r:id="rId98" xr:uid="{F44D8F46-5FA4-4A8F-90C8-7E1E85DD949A}"/>
+    <hyperlink ref="I154" r:id="rId99" xr:uid="{F5D319DD-3210-4B57-ADF8-21B97A9B0B46}"/>
+    <hyperlink ref="G159" r:id="rId100" xr:uid="{6E31B056-8F46-4D10-B521-AB5F56FBA945}"/>
+    <hyperlink ref="I159" r:id="rId101" xr:uid="{EA280733-544C-4343-BE1F-31165842B53B}"/>
+    <hyperlink ref="I160" r:id="rId102" xr:uid="{9D9FA1DD-EB56-4044-965A-24932626784C}"/>
+    <hyperlink ref="I161" r:id="rId103" xr:uid="{451461BD-A866-4D85-8D3C-9DACB55ADEE8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId104"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -24278,7 +28561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -25388,1018 +29671,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A1000"/>
-  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="26" width="21.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="3" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="5" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="6" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="7" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="8" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="9" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="10" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="11" ht="29.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" ht="27.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="16" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="17" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="18" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" ht="32.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="20" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="26" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="27" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="28" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="33" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="43" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="65" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="66" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="67" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="68" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="69" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="70" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="71" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="72" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="73" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="74" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="75" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="76" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="77" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="78" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="79" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="80" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="81" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="82" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="83" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="84" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="85" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="86" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="87" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="88" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="89" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="90" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="91" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="92" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="93" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="94" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="95" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="96" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="97" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="98" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="99" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="100" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="101" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="102" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="103" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="104" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="105" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="106" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="107" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="108" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="109" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="110" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="111" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="112" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="114" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="115" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="116" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="117" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="118" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="119" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="120" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="121" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="122" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="123" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="124" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="125" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="126" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="127" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="128" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="129" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="130" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="131" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="132" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="133" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="134" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="135" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="136" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="137" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="138" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="139" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="140" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="141" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="142" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="143" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="144" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="145" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="146" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="147" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="148" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="149" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="150" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="151" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="152" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="153" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="154" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="155" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="156" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="157" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="158" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="159" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="160" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="161" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="162" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="163" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="164" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="165" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="166" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="167" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="168" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="169" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="170" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="171" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="172" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="173" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="174" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="175" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="176" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="177" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="178" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="179" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="181" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="182" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="183" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="184" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="185" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="186" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="187" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="188" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="189" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="190" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="191" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="192" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="193" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="194" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="195" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="196" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="197" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="198" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="199" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="200" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="201" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="202" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="203" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="204" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="205" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="206" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="207" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="208" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="209" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="210" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="211" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="212" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="213" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="214" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="215" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="216" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="217" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="218" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="219" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="220" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="221" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="222" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="223" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="224" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="225" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="226" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="227" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="228" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="229" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="230" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="231" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="232" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="233" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="234" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="235" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="236" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="237" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="238" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="239" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="240" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="241" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="242" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="243" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="244" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="245" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="246" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="247" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="248" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="249" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="250" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="251" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="252" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="253" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="254" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="255" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="256" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="257" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="258" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="259" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="260" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="261" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="262" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="263" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="264" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="265" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="266" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="267" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="268" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="269" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="270" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="271" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="272" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="273" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="274" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="275" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="276" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="277" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="278" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="279" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="280" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="281" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="282" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="283" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="284" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="285" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="286" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="287" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="288" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="289" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="290" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="291" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="292" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="293" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="294" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="295" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="296" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="297" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="298" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="299" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="300" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="301" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="302" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="303" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="304" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="305" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="306" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="307" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="308" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="309" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="310" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="311" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="312" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="313" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="314" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="315" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="316" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="317" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="318" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="319" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="320" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="321" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="322" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="323" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="324" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="325" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="326" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="327" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="328" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="329" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="330" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="331" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="332" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="333" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="334" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="335" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="336" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="337" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="338" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="339" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="340" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="341" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="342" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="343" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="344" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="345" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="346" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="347" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="348" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="349" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="350" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="351" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="352" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="353" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="354" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="355" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="356" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="357" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="358" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="359" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="360" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="361" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="362" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="363" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="364" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="365" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="366" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="367" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="368" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="369" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="370" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="371" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="372" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="373" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="374" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="375" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="376" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="377" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="378" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="379" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="380" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="381" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="382" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="383" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="384" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="385" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="386" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="387" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="388" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="389" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="390" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="391" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="392" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="393" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="394" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="395" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="396" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="397" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="398" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="399" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="400" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="401" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="402" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="403" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="404" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="405" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="406" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="407" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="408" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="409" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="410" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="411" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="412" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="413" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="414" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="415" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="416" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="417" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="418" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="419" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="420" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="421" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="422" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="423" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="424" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="425" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="426" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="427" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="428" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="429" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="430" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="431" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="432" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="433" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="434" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="435" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="436" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="437" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="438" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="439" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="440" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="441" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="442" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="443" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="444" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="445" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="446" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="447" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="448" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="449" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="450" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="451" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="452" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="453" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="454" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="455" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="456" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="457" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="458" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="459" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="460" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="461" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="462" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="463" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="464" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="465" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="466" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="467" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="468" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="469" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="470" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="471" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="472" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="473" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="474" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="475" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="476" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="477" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="478" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="479" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="480" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="481" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="482" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="483" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="484" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="485" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="486" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="487" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="488" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="489" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="490" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="491" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="492" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="493" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="494" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="495" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="496" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="497" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="498" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="499" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="500" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="501" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="502" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="503" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="504" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="505" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="506" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="507" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="508" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="509" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="510" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="511" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="512" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="513" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="514" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="515" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="516" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="517" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="518" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="519" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="520" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="521" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="522" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="523" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="524" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="525" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="526" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="527" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="528" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="529" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="530" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="531" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="532" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="533" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="534" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="535" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="536" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="537" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="538" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="539" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="540" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="541" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="542" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="543" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="544" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="545" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="546" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="547" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="548" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="549" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="550" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="551" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="552" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="553" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="554" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="555" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="556" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="557" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="558" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="559" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="560" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="561" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="562" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="563" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="564" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="565" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="566" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="567" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="568" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="569" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="570" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="571" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="572" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="573" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="574" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="575" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="576" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="577" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="578" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="579" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="580" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="581" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="582" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="583" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="584" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="585" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="586" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="587" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="588" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="589" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="590" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="591" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="592" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="593" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="594" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="595" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="596" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="597" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="598" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="599" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="600" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="601" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="602" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="603" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="604" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="605" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="606" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="607" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="608" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="609" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="610" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="611" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="612" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="613" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="614" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="615" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="616" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="617" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="618" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="619" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="620" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="621" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="622" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="623" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="624" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="625" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="626" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="627" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="628" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="629" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="630" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="631" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="632" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="633" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="634" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="635" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="636" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="637" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="638" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="639" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="640" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="641" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="642" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="643" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="644" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="645" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="646" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="647" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="648" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="649" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="650" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="651" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="652" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="653" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="654" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="655" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="656" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="657" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="658" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="659" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="660" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="661" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="662" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="663" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="664" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="665" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="666" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="667" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="668" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="669" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="670" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="671" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="672" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="673" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="674" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="675" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="676" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="677" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="678" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="679" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="680" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="681" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="682" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="683" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="684" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="685" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="686" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="687" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="688" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="689" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="690" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="691" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="692" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="693" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="694" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="695" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="696" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="697" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="698" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="699" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="700" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="701" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="702" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="703" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="704" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="705" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="706" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="707" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="708" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="709" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="710" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="711" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="712" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="713" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="714" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="715" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="716" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="717" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="718" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="719" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="720" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="721" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="722" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="723" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="724" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="725" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="726" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="727" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="728" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="729" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="730" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="731" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="732" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="733" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="734" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="735" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="736" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="737" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="738" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="739" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="740" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="741" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="742" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="743" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="744" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="745" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="746" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="747" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="748" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="749" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="750" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="751" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="752" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="753" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="754" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="755" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="756" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="757" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="758" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="759" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="760" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="761" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="762" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="763" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="764" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="765" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="766" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="767" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="768" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="769" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="770" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="771" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="772" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="773" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="774" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="775" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="776" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="777" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="778" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="779" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="780" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="781" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="782" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="783" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="784" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="785" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="786" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="787" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="788" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="789" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="790" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="791" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="792" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="793" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="794" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="795" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="796" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="797" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="798" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="799" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="800" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="801" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="802" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="803" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="804" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="805" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="806" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="807" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="808" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="809" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="810" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="811" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="812" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="813" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="814" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="815" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="816" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="817" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="818" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="819" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="820" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="821" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="822" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="823" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="824" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="825" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="826" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="827" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="828" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="829" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="830" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="831" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="832" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="833" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="834" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="835" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="836" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="837" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="838" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="839" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="840" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="841" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="842" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="843" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="844" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="845" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="846" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="847" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="848" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="849" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="850" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="851" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="852" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="853" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="854" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="855" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="856" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="857" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="858" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="859" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="860" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="861" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="862" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="863" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="864" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="865" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="866" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="867" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="868" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="869" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="870" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="871" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="872" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="873" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="874" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="875" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="876" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="877" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="878" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="879" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="880" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="881" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="882" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="883" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="884" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="885" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="886" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="887" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="888" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="889" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="890" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="891" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="892" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="893" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="894" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="895" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="896" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="897" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="898" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="899" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="900" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="901" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="902" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="903" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="904" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="905" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="906" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="907" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="908" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="909" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="910" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="911" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="912" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="913" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="914" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="915" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="916" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="917" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="918" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="919" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="920" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="921" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="922" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="923" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="924" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="925" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="926" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="927" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="928" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="929" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="930" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="931" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="932" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="933" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="934" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="935" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="936" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="937" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="938" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="939" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="940" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="941" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="942" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="943" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="944" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="945" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="946" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="947" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="948" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="949" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="950" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="951" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="952" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="953" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="954" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="955" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="956" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="957" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="958" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="959" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="960" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="961" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="962" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="963" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="964" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="965" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="966" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="967" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="968" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="969" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="970" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="971" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="972" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="973" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="974" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="975" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="976" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="977" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="978" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="979" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="980" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="981" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="982" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="983" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="984" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="985" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="986" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="987" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="988" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="989" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="990" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="991" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="992" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="993" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="994" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="995" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="996" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="997" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="998" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="999" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="1000" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>
--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4810BA99-4C05-444E-BDDD-A84A99A2D6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6941342D-8BC9-42FE-B3B5-00B56263A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="331">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1074,6 +1074,18 @@
   </si>
   <si>
     <t>Slide-32 HS</t>
+  </si>
+  <si>
+    <t>https://www.extra.com/en-sa/accessories/electrical/lights/c/6-633-18/facet/?q=%3Arelevance%3Atype%3APRODUCT&amp;text=&amp;pg=1&amp;pageSize=24&amp;sort=relevance check this link,</t>
+  </si>
+  <si>
+    <t>https://www.extra.com/en-sa/small-appliances/home-environment-care/air-treatment/c/5-503-16/facet/?q=%3Arelevance%3Atype%3APRODUCT&amp;text=&amp;pg=1&amp;pageSize=24&amp;sort=relevance</t>
+  </si>
+  <si>
+    <t>https://www.extra.com/en-sa/search/?q=scent+diffusers%3Arelevance%3Atype%3APRODUCT&amp;text=scent+diffusers&amp;pg=1&amp;pageSize=24&amp;sort=relevance</t>
+  </si>
+  <si>
+    <t>https://www.extra.com/en-sa/search/?q=RAFEED+LED+Bulb%3Arelevance%3Atype%3APRODUCT&amp;text=RAFEED+LED+Bulb&amp;pg=1&amp;pageSize=24&amp;sort=relevance</t>
   </si>
 </sst>
 </file>
@@ -9556,9 +9568,7 @@
       <c r="D2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>296</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>166</v>
       </c>
@@ -9596,9 +9606,7 @@
       <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>297</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
         <v>166</v>
       </c>
@@ -9636,9 +9644,7 @@
       <c r="D4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>298</v>
-      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
         <v>166</v>
       </c>
@@ -9876,9 +9882,7 @@
       <c r="D10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>304</v>
-      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
         <v>166</v>
       </c>
@@ -9916,9 +9920,7 @@
       <c r="D11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>305</v>
-      </c>
+      <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
         <v>166</v>
       </c>
@@ -10146,9 +10148,7 @@
       <c r="D17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>311</v>
-      </c>
+      <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
         <v>166</v>
       </c>
@@ -10186,9 +10186,7 @@
       <c r="D18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>312</v>
-      </c>
+      <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
         <v>166</v>
       </c>
@@ -10416,9 +10414,7 @@
       <c r="D24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>318</v>
-      </c>
+      <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
         <v>166</v>
       </c>
@@ -10456,9 +10452,7 @@
       <c r="D25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>319</v>
-      </c>
+      <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
         <v>166</v>
       </c>
@@ -10686,9 +10680,7 @@
       <c r="D31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>296</v>
-      </c>
+      <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
         <v>166</v>
       </c>
@@ -10726,9 +10718,7 @@
       <c r="D32" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>297</v>
-      </c>
+      <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
         <v>166</v>
       </c>
@@ -10956,9 +10946,7 @@
       <c r="D38" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>303</v>
-      </c>
+      <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
         <v>166</v>
       </c>
@@ -10996,9 +10984,7 @@
       <c r="D39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>304</v>
-      </c>
+      <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
         <v>166</v>
       </c>
@@ -20950,7 +20936,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="7.609375" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.609375" style="43"/>
@@ -20961,11 +20947,11 @@
     <col min="6" max="6" width="25.83203125" customWidth="1"/>
     <col min="7" max="7" width="27.0546875" customWidth="1"/>
     <col min="8" max="8" width="10.109375" customWidth="1"/>
-    <col min="9" max="9" width="62.71875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.6640625" customWidth="1"/>
     <col min="10" max="10" width="66.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="25.2" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>295</v>
       </c>
@@ -20997,780 +20983,696 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A2" s="43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>296</v>
-      </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-    </row>
-    <row r="3" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+        <v>299</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>174</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="42">
+        <v>18</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="J2" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="K2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A3" s="43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>297</v>
-      </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-    </row>
-    <row r="4" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+        <v>300</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="H3" s="41">
+        <v>22.5</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="K3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A4" s="43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>298</v>
-      </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+        <v>301</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H4" s="42">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="K4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A5" s="43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>174</v>
-      </c>
-      <c r="E5" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="41">
+        <v>40</v>
+      </c>
+      <c r="I5" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A6" s="43">
+        <v>8</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" s="42">
+        <v>100</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="K6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A7" s="43">
+        <v>11</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="42" t="s">
-        <v>209</v>
-      </c>
-      <c r="G5" s="46" t="s">
+      <c r="F7" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H7" s="41">
         <v>18</v>
       </c>
-      <c r="I5" s="44" t="s">
-        <v>214</v>
-      </c>
-      <c r="J5" s="42" t="s">
+      <c r="I7" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A8" s="43">
+        <v>12</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="H8" s="42">
+        <v>15.82</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="K8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A9" s="43">
+        <v>13</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="41">
+        <v>45.65</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="K9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A10" s="43">
+        <v>14</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="45"/>
+      <c r="E10" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="42">
+        <v>40</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="K10" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A11" s="43">
+        <v>15</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="41">
+        <v>100</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="K11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A12" s="43">
+        <v>18</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="52">
+        <v>18</v>
+      </c>
+      <c r="I12" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="53" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A6" s="43">
-        <v>5</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>300</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="41" t="s">
+      <c r="K12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A13" s="43">
+        <v>19</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="52" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F13" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G13" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="H6" s="41">
-        <v>22.5</v>
-      </c>
-      <c r="I6" s="49" t="s">
+      <c r="H13" s="52">
+        <v>22</v>
+      </c>
+      <c r="I13" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="41" t="s">
+      <c r="J13" s="53" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A7" s="43">
-        <v>6</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>301</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="42" t="s">
+      <c r="K13" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A14" s="43">
+        <v>20</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F14" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G7" s="44" t="s">
+      <c r="G14" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="42">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="I7" s="45" t="s">
+      <c r="H14" s="52">
+        <v>32</v>
+      </c>
+      <c r="I14" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="J14" s="53" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A8" s="43">
-        <v>7</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>302</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>294</v>
-      </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="41" t="s">
+      <c r="K14" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A15" s="43">
+        <v>21</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F15" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G15" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H15" s="52">
         <v>40</v>
       </c>
-      <c r="I8" s="49" t="s">
+      <c r="I15" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A9" s="43">
-        <v>8</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="E9" s="42" t="s">
+      <c r="J15" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="K15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A16" s="43">
+        <v>22</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="45"/>
+      <c r="E16" s="52" t="s">
         <v>188</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F16" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G9" s="44" t="s">
+      <c r="G16" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H16" s="52">
         <v>100</v>
       </c>
-      <c r="I9" s="45" t="s">
+      <c r="I16" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="J16" s="53" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A10" s="43">
-        <v>9</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-    </row>
-    <row r="11" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A11" s="43">
-        <v>10</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-    </row>
-    <row r="12" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A12" s="43">
-        <v>11</v>
-      </c>
-      <c r="B12" s="41" t="s">
-        <v>306</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>239</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="K16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A17" s="43">
+        <v>25</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="52" t="s">
         <v>175</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F17" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G17" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H17" s="52">
         <v>18</v>
       </c>
-      <c r="I12" s="49" t="s">
+      <c r="I17" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A13" s="43">
-        <v>12</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="C13" s="44" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="42" t="s">
+      <c r="J17" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="K17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A18" s="43">
+        <v>26</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="55" t="s">
         <v>180</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F18" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G18" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="H13" s="42">
-        <v>15.82</v>
-      </c>
-      <c r="I13" s="45" t="s">
+      <c r="H18" s="52">
+        <v>22</v>
+      </c>
+      <c r="I18" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="42" t="s">
+      <c r="J18" s="53" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A14" s="43">
-        <v>13</v>
-      </c>
-      <c r="B14" s="41" t="s">
-        <v>308</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="41" t="s">
+      <c r="K18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="A19" s="43">
+        <v>27</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>322</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F19" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G14" s="51" t="s">
+      <c r="G19" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="H14" s="41">
-        <v>45.65</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="41" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A15" s="43">
-        <v>14</v>
-      </c>
-      <c r="B15" s="41" t="s">
-        <v>309</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="42">
-        <v>40</v>
-      </c>
-      <c r="I15" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A16" s="43">
-        <v>15</v>
-      </c>
-      <c r="B16" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="F16" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="G16" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="41">
-        <v>100</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="41" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A17" s="43">
-        <v>16</v>
-      </c>
-      <c r="B17" s="41" t="s">
-        <v>311</v>
-      </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="53"/>
-    </row>
-    <row r="18" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A18" s="43">
-        <v>17</v>
-      </c>
-      <c r="B18" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="53"/>
-    </row>
-    <row r="19" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A19" s="43">
-        <v>18</v>
-      </c>
-      <c r="B19" s="41" t="s">
-        <v>313</v>
-      </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="F19" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="G19" s="44" t="s">
-        <v>177</v>
-      </c>
       <c r="H19" s="52">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I19" s="54" t="s">
         <v>33</v>
       </c>
       <c r="J19" s="53" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+        <v>185</v>
+      </c>
+      <c r="K19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A20" s="43">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>314</v>
-      </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="F20" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="D20" s="45"/>
+      <c r="E20" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G20" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="H20" s="52">
-        <v>22</v>
-      </c>
-      <c r="I20" s="54" t="s">
+      <c r="G20" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="58">
+        <v>40</v>
+      </c>
+      <c r="I20" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="53" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
+      <c r="J20" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="K20" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
       <c r="A21" s="43">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>315</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="45"/>
+        <v>324</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>187</v>
+      </c>
       <c r="E21" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="F21" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="G21" s="44" t="s">
+      <c r="G21" s="51" t="s">
         <v>177</v>
       </c>
       <c r="H21" s="52">
-        <v>32</v>
-      </c>
-      <c r="I21" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="I21" s="52" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="53" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A22" s="43">
-        <v>21</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>316</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="G22" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="52">
-        <v>40</v>
-      </c>
-      <c r="I22" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="53" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A23" s="43">
-        <v>22</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>317</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="H23" s="52">
-        <v>100</v>
-      </c>
-      <c r="I23" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="53" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A24" s="43">
-        <v>23</v>
-      </c>
-      <c r="B24" s="41" t="s">
-        <v>318</v>
-      </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="53"/>
-    </row>
-    <row r="25" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A25" s="43">
-        <v>24</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>319</v>
-      </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="53"/>
-    </row>
-    <row r="26" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A26" s="43">
-        <v>25</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="E26" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="G26" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="52">
-        <v>18</v>
-      </c>
-      <c r="I26" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A27" s="43">
-        <v>26</v>
-      </c>
-      <c r="B27" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" s="52">
-        <v>22</v>
-      </c>
-      <c r="I27" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="53" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A28" s="43">
-        <v>27</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>322</v>
-      </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="F28" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="G28" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="52">
-        <v>32</v>
-      </c>
-      <c r="I28" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A29" s="43">
-        <v>28</v>
-      </c>
-      <c r="B29" s="41" t="s">
-        <v>323</v>
-      </c>
-      <c r="C29" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="F29" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="G29" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="58">
-        <v>40</v>
-      </c>
-      <c r="I29" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="27" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="12.6" x14ac:dyDescent="0.4">
-      <c r="A30" s="43">
-        <v>29</v>
-      </c>
-      <c r="B30" s="41" t="s">
-        <v>324</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="D30" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="E30" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="F30" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="G30" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="52">
-        <v>100</v>
-      </c>
-      <c r="I30" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="53" t="s">
-        <v>189</v>
+      <c r="K21" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{6339E7B0-DD91-43F9-9AA6-7575AE99BA81}"/>
-    <hyperlink ref="G5" r:id="rId2" xr:uid="{DC80D7AF-69FB-4AAA-9743-02E8CB5F9079}"/>
-    <hyperlink ref="C6" r:id="rId3" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{A36D2DA1-4E0F-463F-BD52-823614E6F14F}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{738B9507-8B22-40D6-BDF3-FFDA91DE87D0}"/>
-    <hyperlink ref="I7" r:id="rId5" xr:uid="{2CF77598-3EF2-4C04-B577-6076A34E9EE1}"/>
-    <hyperlink ref="J8" r:id="rId6" xr:uid="{3AEABC4D-2D5C-4B33-A11F-9E6767FF7514}"/>
-    <hyperlink ref="G12" r:id="rId7" xr:uid="{64D354CE-3A49-4217-ACF2-71251338491D}"/>
-    <hyperlink ref="I12" r:id="rId8" xr:uid="{44D7D327-4162-41F1-A693-DB31C169FEFD}"/>
-    <hyperlink ref="J12" r:id="rId9" xr:uid="{01FFD6B0-7C64-48E1-85C5-C64A49956307}"/>
-    <hyperlink ref="I13" r:id="rId10" xr:uid="{41651FDF-D68A-4A66-81C6-6AD85DE23FD9}"/>
-    <hyperlink ref="I14" r:id="rId11" xr:uid="{7A5E544D-B0DA-4DF2-B0C0-212A31F2A80F}"/>
-    <hyperlink ref="C15" r:id="rId12" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{5BC5963B-3916-439B-9D2F-5531AB6E9425}"/>
-    <hyperlink ref="C16" r:id="rId13" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{2E3C5B4A-D7B4-4F34-832E-7B28AE6A218C}"/>
-    <hyperlink ref="G19" r:id="rId14" xr:uid="{8B42E5A2-C150-46E6-B84A-DA0391FFA844}"/>
-    <hyperlink ref="I19" r:id="rId15" xr:uid="{790A0EE4-1017-405C-8848-CC0D9825D731}"/>
-    <hyperlink ref="I20" r:id="rId16" xr:uid="{764E6654-EFE2-4BA2-88CA-00AE8F329884}"/>
-    <hyperlink ref="I21" r:id="rId17" xr:uid="{4010C3DF-3FB7-46B2-B628-F824ED91569E}"/>
-    <hyperlink ref="G26" r:id="rId18" xr:uid="{4B3272BE-97BD-4CC8-BF98-44DD196E5699}"/>
-    <hyperlink ref="I26" r:id="rId19" xr:uid="{7086DBCC-8681-4066-9B71-B7DF4F3E2D30}"/>
-    <hyperlink ref="I27" r:id="rId20" xr:uid="{7FEAFFCA-16F0-4E78-91E4-FD82A1D3B0C4}"/>
-    <hyperlink ref="I28" r:id="rId21" xr:uid="{F20DF1DC-2961-454E-911C-ABF0A6E1F404}"/>
-    <hyperlink ref="C29" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{EA695AE7-AC33-45C1-9A23-9E4D47F22F81}"/>
-    <hyperlink ref="C30" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{BDD9060C-BB64-40F9-9378-CACE644C50DE}"/>
+    <hyperlink ref="C2" r:id="rId1" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{6339E7B0-DD91-43F9-9AA6-7575AE99BA81}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{DC80D7AF-69FB-4AAA-9743-02E8CB5F9079}"/>
+    <hyperlink ref="C3" r:id="rId3" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{A36D2DA1-4E0F-463F-BD52-823614E6F14F}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{738B9507-8B22-40D6-BDF3-FFDA91DE87D0}"/>
+    <hyperlink ref="I4" r:id="rId5" xr:uid="{2CF77598-3EF2-4C04-B577-6076A34E9EE1}"/>
+    <hyperlink ref="J5" r:id="rId6" xr:uid="{3AEABC4D-2D5C-4B33-A11F-9E6767FF7514}"/>
+    <hyperlink ref="G7" r:id="rId7" xr:uid="{64D354CE-3A49-4217-ACF2-71251338491D}"/>
+    <hyperlink ref="I7" r:id="rId8" xr:uid="{44D7D327-4162-41F1-A693-DB31C169FEFD}"/>
+    <hyperlink ref="J7" r:id="rId9" xr:uid="{01FFD6B0-7C64-48E1-85C5-C64A49956307}"/>
+    <hyperlink ref="I8" r:id="rId10" xr:uid="{41651FDF-D68A-4A66-81C6-6AD85DE23FD9}"/>
+    <hyperlink ref="I9" r:id="rId11" xr:uid="{7A5E544D-B0DA-4DF2-B0C0-212A31F2A80F}"/>
+    <hyperlink ref="C10" r:id="rId12" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{5BC5963B-3916-439B-9D2F-5531AB6E9425}"/>
+    <hyperlink ref="C11" r:id="rId13" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{2E3C5B4A-D7B4-4F34-832E-7B28AE6A218C}"/>
+    <hyperlink ref="G12" r:id="rId14" xr:uid="{8B42E5A2-C150-46E6-B84A-DA0391FFA844}"/>
+    <hyperlink ref="I12" r:id="rId15" xr:uid="{790A0EE4-1017-405C-8848-CC0D9825D731}"/>
+    <hyperlink ref="I13" r:id="rId16" xr:uid="{764E6654-EFE2-4BA2-88CA-00AE8F329884}"/>
+    <hyperlink ref="I14" r:id="rId17" xr:uid="{4010C3DF-3FB7-46B2-B628-F824ED91569E}"/>
+    <hyperlink ref="G17" r:id="rId18" xr:uid="{4B3272BE-97BD-4CC8-BF98-44DD196E5699}"/>
+    <hyperlink ref="I17" r:id="rId19" xr:uid="{7086DBCC-8681-4066-9B71-B7DF4F3E2D30}"/>
+    <hyperlink ref="I18" r:id="rId20" xr:uid="{7FEAFFCA-16F0-4E78-91E4-FD82A1D3B0C4}"/>
+    <hyperlink ref="I19" r:id="rId21" xr:uid="{F20DF1DC-2961-454E-911C-ABF0A6E1F404}"/>
+    <hyperlink ref="C20" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{EA695AE7-AC33-45C1-9A23-9E4D47F22F81}"/>
+    <hyperlink ref="C21" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{BDD9060C-BB64-40F9-9378-CACE644C50DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId24"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6941342D-8BC9-42FE-B3B5-00B56263A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62077FD-41F3-489F-B505-A23E8CB3D009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="337">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1007,67 +1007,13 @@
     <t>HS1-08</t>
   </si>
   <si>
-    <t>HS2-01</t>
-  </si>
-  <si>
-    <t>HS2-02</t>
-  </si>
-  <si>
-    <t>HS2-03</t>
-  </si>
-  <si>
-    <t>HS2-04</t>
-  </si>
-  <si>
-    <t>HS2-05</t>
-  </si>
-  <si>
     <t>HS2-06</t>
   </si>
   <si>
     <t>HS2-07</t>
   </si>
   <si>
-    <t>HS3-01</t>
-  </si>
-  <si>
-    <t>HS3-02</t>
-  </si>
-  <si>
-    <t>HS3-03</t>
-  </si>
-  <si>
-    <t>HS3-04</t>
-  </si>
-  <si>
-    <t>HS3-05</t>
-  </si>
-  <si>
-    <t>HS3-06</t>
-  </si>
-  <si>
-    <t>HS3-07</t>
-  </si>
-  <si>
-    <t>HS4-01</t>
-  </si>
-  <si>
-    <t>HS4-02</t>
-  </si>
-  <si>
-    <t>HS4-03</t>
-  </si>
-  <si>
-    <t>HS4-04</t>
-  </si>
-  <si>
-    <t>HS4-05</t>
-  </si>
-  <si>
-    <t>HS4-06</t>
-  </si>
-  <si>
-    <t>HS4-07</t>
+    <t>HS2-08</t>
   </si>
   <si>
     <t>Slide-32</t>
@@ -1086,6 +1032,78 @@
   </si>
   <si>
     <t>https://www.extra.com/en-sa/search/?q=RAFEED+LED+Bulb%3Arelevance%3Atype%3APRODUCT&amp;text=RAFEED+LED+Bulb&amp;pg=1&amp;pageSize=24&amp;sort=relevance</t>
+  </si>
+  <si>
+    <t>HS1-09</t>
+  </si>
+  <si>
+    <t>HS1-10</t>
+  </si>
+  <si>
+    <t>HS1-11</t>
+  </si>
+  <si>
+    <t>HS1-12</t>
+  </si>
+  <si>
+    <t>HS1-13</t>
+  </si>
+  <si>
+    <t>HS1-14</t>
+  </si>
+  <si>
+    <t>HS1-15</t>
+  </si>
+  <si>
+    <t>HS1-16</t>
+  </si>
+  <si>
+    <t>HS1-17</t>
+  </si>
+  <si>
+    <t>HS1-18</t>
+  </si>
+  <si>
+    <t>HS1-19</t>
+  </si>
+  <si>
+    <t>HS1-20</t>
+  </si>
+  <si>
+    <t>HS2-09</t>
+  </si>
+  <si>
+    <t>HS2-10</t>
+  </si>
+  <si>
+    <t>HS3-11</t>
+  </si>
+  <si>
+    <t>HS4-17</t>
+  </si>
+  <si>
+    <t>HS3-12</t>
+  </si>
+  <si>
+    <t>HS3-13</t>
+  </si>
+  <si>
+    <t>HS3-14</t>
+  </si>
+  <si>
+    <t>HS3-15</t>
+  </si>
+  <si>
+    <t>HS4-16</t>
+  </si>
+  <si>
+    <t>HS4-18</t>
+  </si>
+  <si>
+    <t>HS4-19</t>
+  </si>
+  <si>
+    <t>HS4-20</t>
   </si>
 </sst>
 </file>
@@ -9683,7 +9701,7 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>171</v>
@@ -9723,7 +9741,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>171</v>
@@ -9763,7 +9781,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>171</v>
@@ -9803,7 +9821,7 @@
         <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>171</v>
@@ -9843,7 +9861,7 @@
         <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>171</v>
@@ -9959,7 +9977,7 @@
         <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>171</v>
@@ -9997,7 +10015,7 @@
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>171</v>
@@ -10035,7 +10053,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>171</v>
@@ -10073,7 +10091,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>171</v>
@@ -10111,7 +10129,7 @@
         <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>171</v>
@@ -10225,7 +10243,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>171</v>
@@ -10263,7 +10281,7 @@
         <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>171</v>
@@ -10301,7 +10319,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>171</v>
@@ -10339,7 +10357,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>171</v>
@@ -10377,7 +10395,7 @@
         <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>171</v>
@@ -10491,7 +10509,7 @@
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>171</v>
@@ -10529,7 +10547,7 @@
         <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>171</v>
@@ -10567,7 +10585,7 @@
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>171</v>
@@ -10605,7 +10623,7 @@
         <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>171</v>
@@ -10643,7 +10661,7 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>171</v>
@@ -10757,7 +10775,7 @@
         <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>171</v>
@@ -10795,7 +10813,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>171</v>
@@ -10833,7 +10851,7 @@
         <v>53</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>171</v>
@@ -10871,7 +10889,7 @@
         <v>53</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>171</v>
@@ -10909,7 +10927,7 @@
         <v>53</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>171</v>
@@ -11023,7 +11041,7 @@
         <v>62</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>171</v>
@@ -11061,7 +11079,7 @@
         <v>62</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>171</v>
@@ -11099,7 +11117,7 @@
         <v>62</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>171</v>
@@ -11137,7 +11155,7 @@
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>171</v>
@@ -11175,7 +11193,7 @@
         <v>62</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>171</v>
@@ -11212,9 +11230,7 @@
       <c r="D45" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>310</v>
-      </c>
+      <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
         <v>166</v>
       </c>
@@ -11252,9 +11268,7 @@
       <c r="D46" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>311</v>
-      </c>
+      <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
         <v>166</v>
       </c>
@@ -11293,7 +11307,7 @@
         <v>67</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>171</v>
@@ -11331,7 +11345,7 @@
         <v>67</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>171</v>
@@ -11369,7 +11383,7 @@
         <v>67</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>171</v>
@@ -11407,7 +11421,7 @@
         <v>67</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>171</v>
@@ -11445,7 +11459,7 @@
         <v>67</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>171</v>
@@ -11482,9 +11496,7 @@
       <c r="D52" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>317</v>
-      </c>
+      <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
         <v>166</v>
       </c>
@@ -11522,9 +11534,7 @@
       <c r="D53" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>318</v>
-      </c>
+      <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
         <v>166</v>
       </c>
@@ -11563,7 +11573,7 @@
         <v>74</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>171</v>
@@ -11601,7 +11611,7 @@
         <v>74</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>171</v>
@@ -11639,7 +11649,7 @@
         <v>74</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>171</v>
@@ -11677,7 +11687,7 @@
         <v>74</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>171</v>
@@ -11715,7 +11725,7 @@
         <v>74</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>171</v>
@@ -11752,9 +11762,7 @@
       <c r="D59" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>324</v>
-      </c>
+      <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
         <v>166</v>
       </c>
@@ -11792,9 +11800,7 @@
       <c r="D60" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>296</v>
-      </c>
+      <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
         <v>166</v>
       </c>
@@ -11833,7 +11839,7 @@
         <v>79</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>171</v>
@@ -11871,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>171</v>
@@ -11909,7 +11915,7 @@
         <v>79</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>171</v>
@@ -11947,7 +11953,7 @@
         <v>79</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>171</v>
@@ -11985,7 +11991,7 @@
         <v>79</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>171</v>
@@ -12022,9 +12028,7 @@
       <c r="D66" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>302</v>
-      </c>
+      <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
         <v>166</v>
       </c>
@@ -12062,9 +12066,7 @@
       <c r="D67" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>303</v>
-      </c>
+      <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
         <v>166</v>
       </c>
@@ -12217,7 +12219,7 @@
         <v>83</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>171</v>
@@ -12255,7 +12257,7 @@
         <v>83</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>171</v>
@@ -12292,9 +12294,7 @@
       <c r="D73" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>309</v>
-      </c>
+      <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
         <v>166</v>
       </c>
@@ -12332,9 +12332,7 @@
       <c r="D74" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>310</v>
-      </c>
+      <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
         <v>166</v>
       </c>
@@ -12373,7 +12371,7 @@
         <v>87</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>171</v>
@@ -12411,7 +12409,7 @@
         <v>87</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>171</v>
@@ -12449,7 +12447,7 @@
         <v>87</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>171</v>
@@ -12487,7 +12485,7 @@
         <v>87</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>171</v>
@@ -12525,7 +12523,7 @@
         <v>87</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>171</v>
@@ -12562,9 +12560,7 @@
       <c r="D80" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>316</v>
-      </c>
+      <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>166</v>
       </c>
@@ -12602,9 +12598,7 @@
       <c r="D81" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>317</v>
-      </c>
+      <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
         <v>166</v>
       </c>
@@ -12643,7 +12637,7 @@
         <v>93</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>171</v>
@@ -12681,7 +12675,7 @@
         <v>93</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>171</v>
@@ -12719,7 +12713,7 @@
         <v>93</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>171</v>
@@ -12757,7 +12751,7 @@
         <v>93</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>171</v>
@@ -12795,7 +12789,7 @@
         <v>93</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>171</v>
@@ -12832,9 +12826,7 @@
       <c r="D87" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>323</v>
-      </c>
+      <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
         <v>166</v>
       </c>
@@ -12872,9 +12864,7 @@
       <c r="D88" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>324</v>
-      </c>
+      <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
         <v>166</v>
       </c>
@@ -13102,9 +13092,7 @@
       <c r="D94" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>301</v>
-      </c>
+      <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
         <v>166</v>
       </c>
@@ -13142,9 +13130,7 @@
       <c r="D95" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>302</v>
-      </c>
+      <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
         <v>166</v>
       </c>
@@ -13183,7 +13169,7 @@
         <v>101</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>171</v>
@@ -13221,7 +13207,7 @@
         <v>101</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>171</v>
@@ -13259,7 +13245,7 @@
         <v>101</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>171</v>
@@ -13297,7 +13283,7 @@
         <v>101</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>171</v>
@@ -13335,7 +13321,7 @@
         <v>101</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>171</v>
@@ -13372,9 +13358,7 @@
       <c r="D101" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>308</v>
-      </c>
+      <c r="E101" s="3"/>
       <c r="F101" s="3" t="s">
         <v>166</v>
       </c>
@@ -13412,9 +13396,7 @@
       <c r="D102" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>309</v>
-      </c>
+      <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
         <v>166</v>
       </c>
@@ -13453,7 +13435,7 @@
         <v>106</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>171</v>
@@ -13491,7 +13473,7 @@
         <v>106</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>171</v>
@@ -13529,7 +13511,7 @@
         <v>106</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>171</v>
@@ -13567,7 +13549,7 @@
         <v>106</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>171</v>
@@ -13605,7 +13587,7 @@
         <v>106</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>171</v>
@@ -13642,9 +13624,7 @@
       <c r="D108" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>315</v>
-      </c>
+      <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
         <v>166</v>
       </c>
@@ -13682,9 +13662,7 @@
       <c r="D109" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E109" s="3" t="s">
-        <v>316</v>
-      </c>
+      <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
         <v>166</v>
       </c>
@@ -13723,7 +13701,7 @@
         <v>111</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>171</v>
@@ -13761,7 +13739,7 @@
         <v>111</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>171</v>
@@ -13799,7 +13777,7 @@
         <v>111</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>171</v>
@@ -13837,7 +13815,7 @@
         <v>111</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>171</v>
@@ -13875,7 +13853,7 @@
         <v>111</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>171</v>
@@ -13912,9 +13890,7 @@
       <c r="D115" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E115" s="3" t="s">
-        <v>322</v>
-      </c>
+      <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
         <v>166</v>
       </c>
@@ -13952,9 +13928,7 @@
       <c r="D116" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>323</v>
-      </c>
+      <c r="E116" s="3"/>
       <c r="F116" s="3" t="s">
         <v>166</v>
       </c>
@@ -13993,7 +13967,7 @@
         <v>115</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>171</v>
@@ -14031,7 +14005,7 @@
         <v>115</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>171</v>
@@ -14069,7 +14043,7 @@
         <v>115</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>171</v>
@@ -14107,7 +14081,7 @@
         <v>115</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>171</v>
@@ -14145,7 +14119,7 @@
         <v>115</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>171</v>
@@ -14182,9 +14156,7 @@
       <c r="D122" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E122" s="3" t="s">
-        <v>300</v>
-      </c>
+      <c r="E122" s="3"/>
       <c r="F122" s="3" t="s">
         <v>166</v>
       </c>
@@ -14222,9 +14194,7 @@
       <c r="D123" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E123" s="3" t="s">
-        <v>301</v>
-      </c>
+      <c r="E123" s="3"/>
       <c r="F123" s="3" t="s">
         <v>166</v>
       </c>
@@ -14263,7 +14233,7 @@
         <v>123</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>171</v>
@@ -14301,7 +14271,7 @@
         <v>123</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>171</v>
@@ -14339,7 +14309,7 @@
         <v>123</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>171</v>
@@ -14377,7 +14347,7 @@
         <v>123</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>171</v>
@@ -14415,7 +14385,7 @@
         <v>123</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>171</v>
@@ -14452,9 +14422,7 @@
       <c r="D129" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E129" s="3" t="s">
-        <v>307</v>
-      </c>
+      <c r="E129" s="3"/>
       <c r="F129" s="3" t="s">
         <v>166</v>
       </c>
@@ -14492,9 +14460,7 @@
       <c r="D130" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E130" s="3" t="s">
-        <v>308</v>
-      </c>
+      <c r="E130" s="3"/>
       <c r="F130" s="3" t="s">
         <v>166</v>
       </c>
@@ -14533,7 +14499,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>171</v>
@@ -14571,7 +14537,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>171</v>
@@ -14609,7 +14575,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>171</v>
@@ -14647,7 +14613,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>171</v>
@@ -14685,7 +14651,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>171</v>
@@ -14722,9 +14688,7 @@
       <c r="D136" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E136" s="3" t="s">
-        <v>314</v>
-      </c>
+      <c r="E136" s="3"/>
       <c r="F136" s="3" t="s">
         <v>166</v>
       </c>
@@ -14762,9 +14726,7 @@
       <c r="D137" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E137" s="3" t="s">
-        <v>315</v>
-      </c>
+      <c r="E137" s="3"/>
       <c r="F137" s="3" t="s">
         <v>166</v>
       </c>
@@ -14803,7 +14765,7 @@
         <v>133</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>171</v>
@@ -14841,7 +14803,7 @@
         <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>171</v>
@@ -14879,7 +14841,7 @@
         <v>133</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>171</v>
@@ -14917,7 +14879,7 @@
         <v>133</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>171</v>
@@ -14955,7 +14917,7 @@
         <v>133</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>171</v>
@@ -14992,9 +14954,7 @@
       <c r="D143" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E143" s="3" t="s">
-        <v>321</v>
-      </c>
+      <c r="E143" s="3"/>
       <c r="F143" s="3" t="s">
         <v>166</v>
       </c>
@@ -15032,9 +14992,7 @@
       <c r="D144" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E144" s="3" t="s">
-        <v>322</v>
-      </c>
+      <c r="E144" s="3"/>
       <c r="F144" s="3" t="s">
         <v>166</v>
       </c>
@@ -15073,7 +15031,7 @@
         <v>137</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>171</v>
@@ -15111,7 +15069,7 @@
         <v>137</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>171</v>
@@ -15149,7 +15107,7 @@
         <v>137</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>171</v>
@@ -15187,7 +15145,7 @@
         <v>137</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>171</v>
@@ -15225,7 +15183,7 @@
         <v>137</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>171</v>
@@ -15262,9 +15220,7 @@
       <c r="D150" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E150" s="3" t="s">
-        <v>299</v>
-      </c>
+      <c r="E150" s="3"/>
       <c r="F150" s="3" t="s">
         <v>166</v>
       </c>
@@ -15302,9 +15258,7 @@
       <c r="D151" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E151" s="3" t="s">
-        <v>300</v>
-      </c>
+      <c r="E151" s="3"/>
       <c r="F151" s="3" t="s">
         <v>166</v>
       </c>
@@ -15343,7 +15297,7 @@
         <v>141</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>171</v>
@@ -15381,7 +15335,7 @@
         <v>141</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>171</v>
@@ -15419,7 +15373,7 @@
         <v>141</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>171</v>
@@ -15457,7 +15411,7 @@
         <v>141</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>171</v>
@@ -15495,7 +15449,7 @@
         <v>141</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>171</v>
@@ -15532,9 +15486,7 @@
       <c r="D157" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E157" s="3" t="s">
-        <v>306</v>
-      </c>
+      <c r="E157" s="3"/>
       <c r="F157" s="3" t="s">
         <v>166</v>
       </c>
@@ -15572,9 +15524,7 @@
       <c r="D158" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E158" s="3" t="s">
-        <v>307</v>
-      </c>
+      <c r="E158" s="3"/>
       <c r="F158" s="3" t="s">
         <v>166</v>
       </c>
@@ -15613,7 +15563,7 @@
         <v>146</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>171</v>
@@ -15651,7 +15601,7 @@
         <v>146</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>171</v>
@@ -15689,7 +15639,7 @@
         <v>146</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>171</v>
@@ -15727,7 +15677,7 @@
         <v>146</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>171</v>
@@ -15765,7 +15715,7 @@
         <v>146</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>171</v>
@@ -15802,9 +15752,7 @@
       <c r="D164" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E164" s="3" t="s">
-        <v>313</v>
-      </c>
+      <c r="E164" s="3"/>
       <c r="F164" s="3" t="s">
         <v>166</v>
       </c>
@@ -15842,9 +15790,7 @@
       <c r="D165" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E165" s="3" t="s">
-        <v>314</v>
-      </c>
+      <c r="E165" s="3"/>
       <c r="F165" s="3" t="s">
         <v>166</v>
       </c>
@@ -15883,7 +15829,7 @@
         <v>263</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>171</v>
@@ -15921,7 +15867,7 @@
         <v>263</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>171</v>
@@ -15959,7 +15905,7 @@
         <v>263</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>171</v>
@@ -15997,7 +15943,7 @@
         <v>263</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>171</v>
@@ -16035,7 +15981,7 @@
         <v>263</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>171</v>
@@ -16072,9 +16018,7 @@
       <c r="D171" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E171" s="3" t="s">
-        <v>320</v>
-      </c>
+      <c r="E171" s="3"/>
       <c r="F171" s="3" t="s">
         <v>166</v>
       </c>
@@ -16112,9 +16056,7 @@
       <c r="D172" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E172" s="3" t="s">
-        <v>321</v>
-      </c>
+      <c r="E172" s="3"/>
       <c r="F172" s="3" t="s">
         <v>166</v>
       </c>
@@ -16153,7 +16095,7 @@
         <v>264</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>171</v>
@@ -16191,7 +16133,7 @@
         <v>264</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>171</v>
@@ -16229,7 +16171,7 @@
         <v>264</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>171</v>
@@ -16267,7 +16209,7 @@
         <v>264</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>171</v>
@@ -16305,7 +16247,7 @@
         <v>264</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>171</v>
@@ -16342,9 +16284,7 @@
       <c r="D178" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E178" s="3" t="s">
-        <v>298</v>
-      </c>
+      <c r="E178" s="3"/>
       <c r="F178" s="3" t="s">
         <v>166</v>
       </c>
@@ -16382,9 +16322,7 @@
       <c r="D179" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E179" s="3" t="s">
-        <v>299</v>
-      </c>
+      <c r="E179" s="3"/>
       <c r="F179" s="3" t="s">
         <v>166</v>
       </c>
@@ -16423,7 +16361,7 @@
         <v>265</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>171</v>
@@ -16461,7 +16399,7 @@
         <v>265</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>171</v>
@@ -16499,7 +16437,7 @@
         <v>265</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>171</v>
@@ -16537,7 +16475,7 @@
         <v>265</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>171</v>
@@ -16575,7 +16513,7 @@
         <v>265</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>171</v>
@@ -16612,9 +16550,7 @@
       <c r="D185" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E185" s="3" t="s">
-        <v>305</v>
-      </c>
+      <c r="E185" s="3"/>
       <c r="F185" s="3" t="s">
         <v>166</v>
       </c>
@@ -16652,9 +16588,7 @@
       <c r="D186" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E186" s="3" t="s">
-        <v>306</v>
-      </c>
+      <c r="E186" s="3"/>
       <c r="F186" s="3" t="s">
         <v>166</v>
       </c>
@@ -16693,7 +16627,7 @@
         <v>266</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>171</v>
@@ -16731,7 +16665,7 @@
         <v>266</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>171</v>
@@ -16769,7 +16703,7 @@
         <v>266</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>171</v>
@@ -16807,7 +16741,7 @@
         <v>266</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>171</v>
@@ -16845,7 +16779,7 @@
         <v>266</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>171</v>
@@ -16882,9 +16816,7 @@
       <c r="D192" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E192" s="3" t="s">
-        <v>312</v>
-      </c>
+      <c r="E192" s="3"/>
       <c r="F192" s="3" t="s">
         <v>166</v>
       </c>
@@ -16922,9 +16854,7 @@
       <c r="D193" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E193" s="3" t="s">
-        <v>313</v>
-      </c>
+      <c r="E193" s="3"/>
       <c r="F193" s="3" t="s">
         <v>166</v>
       </c>
@@ -16963,7 +16893,7 @@
         <v>267</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>171</v>
@@ -17001,7 +16931,7 @@
         <v>267</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>171</v>
@@ -17039,7 +16969,7 @@
         <v>267</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>171</v>
@@ -17077,7 +17007,7 @@
         <v>267</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>171</v>
@@ -17115,7 +17045,7 @@
         <v>267</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>171</v>
@@ -17152,9 +17082,7 @@
       <c r="D199" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E199" s="3" t="s">
-        <v>319</v>
-      </c>
+      <c r="E199" s="3"/>
       <c r="F199" s="3" t="s">
         <v>166</v>
       </c>
@@ -17192,9 +17120,7 @@
       <c r="D200" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E200" s="3" t="s">
-        <v>320</v>
-      </c>
+      <c r="E200" s="3"/>
       <c r="F200" s="3" t="s">
         <v>166</v>
       </c>
@@ -17233,7 +17159,7 @@
         <v>268</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>171</v>
@@ -17271,7 +17197,7 @@
         <v>268</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>171</v>
@@ -17309,7 +17235,7 @@
         <v>268</v>
       </c>
       <c r="E203" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>171</v>
@@ -17346,7 +17272,7 @@
         <v>268</v>
       </c>
       <c r="E204" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>171</v>
@@ -17383,7 +17309,7 @@
         <v>268</v>
       </c>
       <c r="E205" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>171</v>
@@ -17419,9 +17345,6 @@
       <c r="D206" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E206" t="s">
-        <v>297</v>
-      </c>
       <c r="F206" s="3" t="s">
         <v>166</v>
       </c>
@@ -17458,9 +17381,6 @@
       <c r="D207" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E207" t="s">
-        <v>298</v>
-      </c>
       <c r="F207" s="3" t="s">
         <v>166</v>
       </c>
@@ -17498,7 +17418,7 @@
         <v>278</v>
       </c>
       <c r="E208" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>171</v>
@@ -17535,7 +17455,7 @@
         <v>278</v>
       </c>
       <c r="E209" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>171</v>
@@ -17572,7 +17492,7 @@
         <v>278</v>
       </c>
       <c r="E210" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>171</v>
@@ -17609,7 +17529,7 @@
         <v>278</v>
       </c>
       <c r="E211" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>171</v>
@@ -17646,7 +17566,7 @@
         <v>278</v>
       </c>
       <c r="E212" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>171</v>
@@ -17682,9 +17602,6 @@
       <c r="D213" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E213" t="s">
-        <v>304</v>
-      </c>
       <c r="F213" s="3" t="s">
         <v>166</v>
       </c>
@@ -17721,9 +17638,6 @@
       <c r="D214" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="E214" t="s">
-        <v>305</v>
-      </c>
       <c r="F214" s="3" t="s">
         <v>166</v>
       </c>
@@ -17761,7 +17675,7 @@
         <v>279</v>
       </c>
       <c r="E215" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>171</v>
@@ -17798,7 +17712,7 @@
         <v>279</v>
       </c>
       <c r="E216" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>171</v>
@@ -17835,7 +17749,7 @@
         <v>279</v>
       </c>
       <c r="E217" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>171</v>
@@ -17872,7 +17786,7 @@
         <v>279</v>
       </c>
       <c r="E218" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>171</v>
@@ -17909,7 +17823,7 @@
         <v>279</v>
       </c>
       <c r="E219" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>171</v>
@@ -17945,9 +17859,6 @@
       <c r="D220" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="E220" t="s">
-        <v>311</v>
-      </c>
       <c r="F220" s="3" t="s">
         <v>166</v>
       </c>
@@ -17979,13 +17890,10 @@
         <v>32</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="E221" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>166</v>
@@ -18018,13 +17926,13 @@
         <v>32</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="E222" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>171</v>
@@ -18055,13 +17963,13 @@
         <v>32</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="E223" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>171</v>
@@ -18092,13 +18000,13 @@
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="E224" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>171</v>
@@ -18129,13 +18037,13 @@
         <v>32</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="E225" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>171</v>
@@ -18166,13 +18074,13 @@
         <v>32</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="E226" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>171</v>
@@ -20988,7 +20896,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>291</v>
@@ -21015,7 +20923,7 @@
         <v>178</v>
       </c>
       <c r="K2" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21023,7 +20931,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C3" s="47" t="s">
         <v>238</v>
@@ -21050,7 +20958,7 @@
         <v>182</v>
       </c>
       <c r="K3" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21058,7 +20966,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>292</v>
@@ -21085,7 +20993,7 @@
         <v>185</v>
       </c>
       <c r="K4" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21093,7 +21001,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>294</v>
@@ -21118,7 +21026,7 @@
         <v>49</v>
       </c>
       <c r="K5" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21126,7 +21034,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C6" s="44" t="s">
         <v>293</v>
@@ -21153,7 +21061,7 @@
         <v>189</v>
       </c>
       <c r="K6" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21161,7 +21069,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>239</v>
@@ -21188,7 +21096,7 @@
         <v>49</v>
       </c>
       <c r="K7" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21196,7 +21104,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>240</v>
@@ -21223,7 +21131,7 @@
         <v>182</v>
       </c>
       <c r="K8" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21231,7 +21139,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>240</v>
@@ -21256,7 +21164,7 @@
         <v>185</v>
       </c>
       <c r="K9" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21264,7 +21172,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C10" s="44" t="s">
         <v>241</v>
@@ -21289,7 +21197,7 @@
         <v>191</v>
       </c>
       <c r="K10" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21297,7 +21205,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>241</v>
@@ -21322,7 +21230,7 @@
         <v>189</v>
       </c>
       <c r="K11" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21330,7 +21238,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="45"/>
@@ -21353,7 +21261,7 @@
         <v>178</v>
       </c>
       <c r="K12" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21361,7 +21269,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="49"/>
@@ -21384,7 +21292,7 @@
         <v>182</v>
       </c>
       <c r="K13" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21392,7 +21300,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="45"/>
@@ -21415,7 +21323,7 @@
         <v>185</v>
       </c>
       <c r="K14" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21423,7 +21331,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="49"/>
@@ -21446,7 +21354,7 @@
         <v>191</v>
       </c>
       <c r="K15" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21454,7 +21362,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C16" s="44" t="s">
         <v>239</v>
@@ -21479,7 +21387,7 @@
         <v>189</v>
       </c>
       <c r="K16" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21512,7 +21420,7 @@
         <v>178</v>
       </c>
       <c r="K17" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21545,7 +21453,7 @@
         <v>182</v>
       </c>
       <c r="K18" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21576,7 +21484,7 @@
         <v>185</v>
       </c>
       <c r="K19" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21609,7 +21517,7 @@
         <v>191</v>
       </c>
       <c r="K20" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21644,7 +21552,7 @@
         <v>189</v>
       </c>
       <c r="K21" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62077FD-41F3-489F-B505-A23E8CB3D009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E90786-1F3E-4ED5-846A-64024C1CD4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="338">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1104,6 +1104,9 @@
   </si>
   <si>
     <t>HS4-20</t>
+  </si>
+  <si>
+    <t>Shop Now i-frame</t>
   </si>
 </sst>
 </file>
@@ -20857,6 +20860,7 @@
     <col min="8" max="8" width="10.109375" customWidth="1"/>
     <col min="9" max="9" width="29.6640625" customWidth="1"/>
     <col min="10" max="10" width="66.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="80.0546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.2" x14ac:dyDescent="0.4">
@@ -20889,6 +20893,9 @@
       </c>
       <c r="J1" s="40" t="s">
         <v>163</v>
+      </c>
+      <c r="K1" s="40" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E90786-1F3E-4ED5-846A-64024C1CD4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84728220-31FF-4243-8DB2-41AAB5980CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20860,7 +20860,7 @@
     <col min="8" max="8" width="10.109375" customWidth="1"/>
     <col min="9" max="9" width="29.6640625" customWidth="1"/>
     <col min="10" max="10" width="66.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="80.0546875" customWidth="1"/>
+    <col min="11" max="11" width="156.609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.2" x14ac:dyDescent="0.4">

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84728220-31FF-4243-8DB2-41AAB5980CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6883173F-C73F-48B9-9EE6-BA379539C376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6883173F-C73F-48B9-9EE6-BA379539C376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3328CC3E-8416-492D-B054-23C98E3A786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1022,9 +1022,6 @@
     <t>Slide-32 HS</t>
   </si>
   <si>
-    <t>https://www.extra.com/en-sa/accessories/electrical/lights/c/6-633-18/facet/?q=%3Arelevance%3Atype%3APRODUCT&amp;text=&amp;pg=1&amp;pageSize=24&amp;sort=relevance check this link,</t>
-  </si>
-  <si>
     <t>https://www.extra.com/en-sa/small-appliances/home-environment-care/air-treatment/c/5-503-16/facet/?q=%3Arelevance%3Atype%3APRODUCT&amp;text=&amp;pg=1&amp;pageSize=24&amp;sort=relevance</t>
   </si>
   <si>
@@ -1107,6 +1104,9 @@
   </si>
   <si>
     <t>Shop Now i-frame</t>
+  </si>
+  <si>
+    <t>https://www.extra.com/en-sa/accessories/electrical/lights/c/6-633-18/facet/?q=%3Arelevance%3Atype%3APRODUCT&amp;text=&amp;pg=1&amp;pageSize=24&amp;sort=relevance</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1356,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1512,6 +1512,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10094,7 +10095,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>171</v>
@@ -10132,7 +10133,7 @@
         <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>171</v>
@@ -10246,7 +10247,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>171</v>
@@ -10284,7 +10285,7 @@
         <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>171</v>
@@ -10322,7 +10323,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>171</v>
@@ -10360,7 +10361,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>171</v>
@@ -10398,7 +10399,7 @@
         <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>171</v>
@@ -10512,7 +10513,7 @@
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>171</v>
@@ -10550,7 +10551,7 @@
         <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>171</v>
@@ -10588,7 +10589,7 @@
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>171</v>
@@ -10626,7 +10627,7 @@
         <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>171</v>
@@ -10664,7 +10665,7 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>171</v>
@@ -11158,7 +11159,7 @@
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>171</v>
@@ -11196,7 +11197,7 @@
         <v>62</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>171</v>
@@ -11310,7 +11311,7 @@
         <v>67</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>171</v>
@@ -11348,7 +11349,7 @@
         <v>67</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>171</v>
@@ -11386,7 +11387,7 @@
         <v>67</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>171</v>
@@ -11424,7 +11425,7 @@
         <v>67</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>171</v>
@@ -11462,7 +11463,7 @@
         <v>67</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>171</v>
@@ -11576,7 +11577,7 @@
         <v>74</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>171</v>
@@ -11614,7 +11615,7 @@
         <v>74</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>171</v>
@@ -11652,7 +11653,7 @@
         <v>74</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>171</v>
@@ -11690,7 +11691,7 @@
         <v>74</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>171</v>
@@ -11728,7 +11729,7 @@
         <v>74</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>171</v>
@@ -12222,7 +12223,7 @@
         <v>83</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>171</v>
@@ -12260,7 +12261,7 @@
         <v>83</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>171</v>
@@ -12374,7 +12375,7 @@
         <v>87</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>171</v>
@@ -12412,7 +12413,7 @@
         <v>87</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>171</v>
@@ -12450,7 +12451,7 @@
         <v>87</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>171</v>
@@ -12488,7 +12489,7 @@
         <v>87</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>171</v>
@@ -12526,7 +12527,7 @@
         <v>87</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>171</v>
@@ -12640,7 +12641,7 @@
         <v>93</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>171</v>
@@ -12678,7 +12679,7 @@
         <v>93</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>171</v>
@@ -12716,7 +12717,7 @@
         <v>93</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>171</v>
@@ -12754,7 +12755,7 @@
         <v>93</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>171</v>
@@ -12792,7 +12793,7 @@
         <v>93</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>171</v>
@@ -13286,7 +13287,7 @@
         <v>101</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>171</v>
@@ -13324,7 +13325,7 @@
         <v>101</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>171</v>
@@ -13438,7 +13439,7 @@
         <v>106</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>171</v>
@@ -13476,7 +13477,7 @@
         <v>106</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>171</v>
@@ -13514,7 +13515,7 @@
         <v>106</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>171</v>
@@ -13552,7 +13553,7 @@
         <v>106</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>171</v>
@@ -13590,7 +13591,7 @@
         <v>106</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>171</v>
@@ -13704,7 +13705,7 @@
         <v>111</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>171</v>
@@ -13742,7 +13743,7 @@
         <v>111</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>171</v>
@@ -13780,7 +13781,7 @@
         <v>111</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>171</v>
@@ -13818,7 +13819,7 @@
         <v>111</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>171</v>
@@ -13856,7 +13857,7 @@
         <v>111</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>171</v>
@@ -14350,7 +14351,7 @@
         <v>123</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>171</v>
@@ -14388,7 +14389,7 @@
         <v>123</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>171</v>
@@ -14502,7 +14503,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>171</v>
@@ -14540,7 +14541,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>171</v>
@@ -14578,7 +14579,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>171</v>
@@ -14616,7 +14617,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>171</v>
@@ -14654,7 +14655,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>171</v>
@@ -14768,7 +14769,7 @@
         <v>133</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>171</v>
@@ -14806,7 +14807,7 @@
         <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>171</v>
@@ -14844,7 +14845,7 @@
         <v>133</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>171</v>
@@ -14882,7 +14883,7 @@
         <v>133</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>171</v>
@@ -14920,7 +14921,7 @@
         <v>133</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>171</v>
@@ -15414,7 +15415,7 @@
         <v>141</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>171</v>
@@ -15452,7 +15453,7 @@
         <v>141</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>171</v>
@@ -15566,7 +15567,7 @@
         <v>146</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>171</v>
@@ -15604,7 +15605,7 @@
         <v>146</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>171</v>
@@ -15642,7 +15643,7 @@
         <v>146</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>171</v>
@@ -15680,7 +15681,7 @@
         <v>146</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>171</v>
@@ -15718,7 +15719,7 @@
         <v>146</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>171</v>
@@ -15832,7 +15833,7 @@
         <v>263</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>171</v>
@@ -15870,7 +15871,7 @@
         <v>263</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>171</v>
@@ -15908,7 +15909,7 @@
         <v>263</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>171</v>
@@ -15946,7 +15947,7 @@
         <v>263</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>171</v>
@@ -15984,7 +15985,7 @@
         <v>263</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>171</v>
@@ -16478,7 +16479,7 @@
         <v>265</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>171</v>
@@ -16516,7 +16517,7 @@
         <v>265</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>171</v>
@@ -16630,7 +16631,7 @@
         <v>266</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>171</v>
@@ -16668,7 +16669,7 @@
         <v>266</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>171</v>
@@ -16706,7 +16707,7 @@
         <v>266</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>171</v>
@@ -16744,7 +16745,7 @@
         <v>266</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>171</v>
@@ -16782,7 +16783,7 @@
         <v>266</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>171</v>
@@ -16896,7 +16897,7 @@
         <v>267</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>171</v>
@@ -16934,7 +16935,7 @@
         <v>267</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>171</v>
@@ -16972,7 +16973,7 @@
         <v>267</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>171</v>
@@ -17010,7 +17011,7 @@
         <v>267</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>171</v>
@@ -17048,7 +17049,7 @@
         <v>267</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>171</v>
@@ -17532,7 +17533,7 @@
         <v>278</v>
       </c>
       <c r="E211" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>171</v>
@@ -17569,7 +17570,7 @@
         <v>278</v>
       </c>
       <c r="E212" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>171</v>
@@ -17678,7 +17679,7 @@
         <v>279</v>
       </c>
       <c r="E215" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>171</v>
@@ -17715,7 +17716,7 @@
         <v>279</v>
       </c>
       <c r="E216" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>171</v>
@@ -17752,7 +17753,7 @@
         <v>279</v>
       </c>
       <c r="E217" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>171</v>
@@ -17789,7 +17790,7 @@
         <v>279</v>
       </c>
       <c r="E218" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>171</v>
@@ -17826,7 +17827,7 @@
         <v>279</v>
       </c>
       <c r="E219" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>171</v>
@@ -17935,7 +17936,7 @@
         <v>308</v>
       </c>
       <c r="E222" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>171</v>
@@ -17972,7 +17973,7 @@
         <v>308</v>
       </c>
       <c r="E223" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>171</v>
@@ -18009,7 +18010,7 @@
         <v>308</v>
       </c>
       <c r="E224" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>171</v>
@@ -18046,7 +18047,7 @@
         <v>308</v>
       </c>
       <c r="E225" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>171</v>
@@ -18083,7 +18084,7 @@
         <v>308</v>
       </c>
       <c r="E226" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>171</v>
@@ -20895,7 +20896,7 @@
         <v>163</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20929,8 +20930,8 @@
       <c r="J2" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="K2" t="s">
-        <v>309</v>
+      <c r="K2" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20964,8 +20965,8 @@
       <c r="J3" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="K3" t="s">
-        <v>310</v>
+      <c r="K3" s="59" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20999,8 +21000,8 @@
       <c r="J4" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="K4" t="s">
-        <v>311</v>
+      <c r="K4" s="59" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21032,8 +21033,8 @@
       <c r="J5" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="K5" t="s">
-        <v>312</v>
+      <c r="K5" s="59" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21067,8 +21068,8 @@
       <c r="J6" s="42" t="s">
         <v>189</v>
       </c>
-      <c r="K6" t="s">
-        <v>309</v>
+      <c r="K6" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21102,8 +21103,8 @@
       <c r="J7" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="K7" t="s">
-        <v>309</v>
+      <c r="K7" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21137,8 +21138,8 @@
       <c r="J8" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="K8" t="s">
-        <v>310</v>
+      <c r="K8" s="59" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21170,8 +21171,8 @@
       <c r="J9" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="K9" t="s">
-        <v>311</v>
+      <c r="K9" s="59" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21179,7 +21180,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C10" s="44" t="s">
         <v>241</v>
@@ -21203,8 +21204,8 @@
       <c r="J10" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="K10" t="s">
-        <v>312</v>
+      <c r="K10" s="59" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21212,7 +21213,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>241</v>
@@ -21236,8 +21237,8 @@
       <c r="J11" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="K11" t="s">
-        <v>309</v>
+      <c r="K11" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21245,7 +21246,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="45"/>
@@ -21267,8 +21268,8 @@
       <c r="J12" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="K12" t="s">
-        <v>309</v>
+      <c r="K12" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21276,7 +21277,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="49"/>
@@ -21298,8 +21299,8 @@
       <c r="J13" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="K13" t="s">
-        <v>310</v>
+      <c r="K13" s="59" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21307,7 +21308,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="45"/>
@@ -21329,8 +21330,8 @@
       <c r="J14" s="53" t="s">
         <v>185</v>
       </c>
-      <c r="K14" t="s">
-        <v>311</v>
+      <c r="K14" s="59" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21338,7 +21339,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="49"/>
@@ -21360,8 +21361,8 @@
       <c r="J15" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="K15" t="s">
-        <v>312</v>
+      <c r="K15" s="59" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21369,7 +21370,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C16" s="44" t="s">
         <v>239</v>
@@ -21393,8 +21394,8 @@
       <c r="J16" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="K16" t="s">
-        <v>309</v>
+      <c r="K16" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21402,7 +21403,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
@@ -21426,8 +21427,8 @@
       <c r="J17" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="K17" t="s">
-        <v>309</v>
+      <c r="K17" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21435,7 +21436,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="45" t="s">
@@ -21459,8 +21460,8 @@
       <c r="J18" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="K18" t="s">
-        <v>310</v>
+      <c r="K18" s="59" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21468,7 +21469,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="49"/>
@@ -21490,8 +21491,8 @@
       <c r="J19" s="53" t="s">
         <v>185</v>
       </c>
-      <c r="K19" t="s">
-        <v>311</v>
+      <c r="K19" s="59" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21499,7 +21500,7 @@
         <v>28</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C20" s="44" t="s">
         <v>241</v>
@@ -21523,8 +21524,8 @@
       <c r="J20" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="K20" t="s">
-        <v>312</v>
+      <c r="K20" s="59" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21532,7 +21533,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C21" s="51" t="s">
         <v>241</v>
@@ -21558,8 +21559,8 @@
       <c r="J21" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="K21" t="s">
-        <v>309</v>
+      <c r="K21" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -21588,9 +21589,29 @@
     <hyperlink ref="I19" r:id="rId21" xr:uid="{F20DF1DC-2961-454E-911C-ABF0A6E1F404}"/>
     <hyperlink ref="C20" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{EA695AE7-AC33-45C1-9A23-9E4D47F22F81}"/>
     <hyperlink ref="C21" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{BDD9060C-BB64-40F9-9378-CACE644C50DE}"/>
+    <hyperlink ref="K2" r:id="rId24" xr:uid="{A87BB04B-B72D-4A86-BEEA-8BA449F0988B}"/>
+    <hyperlink ref="K6" r:id="rId25" xr:uid="{00FB0EE0-C588-4769-B7E3-0083DFEF0525}"/>
+    <hyperlink ref="K7" r:id="rId26" xr:uid="{9CB4FD52-CAD2-4D4D-9553-FDF72B33FAA8}"/>
+    <hyperlink ref="K11" r:id="rId27" xr:uid="{4DB6892B-6CE5-4368-A6BD-DDEB6A532751}"/>
+    <hyperlink ref="K12" r:id="rId28" xr:uid="{DD34B684-CBEC-4F40-87F6-5D309BEDC549}"/>
+    <hyperlink ref="K16" r:id="rId29" xr:uid="{8FF887A0-CF88-4749-BA71-98E8CEEE39C4}"/>
+    <hyperlink ref="K17" r:id="rId30" xr:uid="{95FA9265-3417-430B-A82F-1851ABDA5322}"/>
+    <hyperlink ref="K21" r:id="rId31" xr:uid="{DD9C60D6-CB3B-4465-9F2F-A85C47AA31AC}"/>
+    <hyperlink ref="K3" r:id="rId32" xr:uid="{4B8525E2-3D2C-4F11-8FF2-F397CFE942BF}"/>
+    <hyperlink ref="K4" r:id="rId33" xr:uid="{59A3D8FA-E4B4-4B4A-A777-1FAE6B4BB057}"/>
+    <hyperlink ref="K5" r:id="rId34" xr:uid="{7E30C704-B4A9-4E96-9539-437889F395BC}"/>
+    <hyperlink ref="K8" r:id="rId35" xr:uid="{8DF7CB57-71D4-4D40-AA53-99108D3FB1F7}"/>
+    <hyperlink ref="K9" r:id="rId36" xr:uid="{3611887B-2A5C-4BAD-B0F9-416880C50ABD}"/>
+    <hyperlink ref="K10" r:id="rId37" xr:uid="{AFC04322-530D-40D9-80C5-FD9B4B5813C3}"/>
+    <hyperlink ref="K13" r:id="rId38" xr:uid="{16FD737E-DCEA-48E3-BE2A-EBE2DD34E23C}"/>
+    <hyperlink ref="K14" r:id="rId39" xr:uid="{2782968C-4C7B-4AB3-81E0-06C30BC00D06}"/>
+    <hyperlink ref="K15" r:id="rId40" xr:uid="{9866D5BE-5EB5-4F6F-8BB0-6B529FC2D49E}"/>
+    <hyperlink ref="K18" r:id="rId41" xr:uid="{BFA9A033-AABB-4EA6-AA1E-7D3026867594}"/>
+    <hyperlink ref="K19" r:id="rId42" xr:uid="{D15E29DE-9055-4D1E-A061-94CD9CD385A7}"/>
+    <hyperlink ref="K20" r:id="rId43" xr:uid="{21E0BFBF-876B-451F-A4D6-CEF3E93F675C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId24"/>
+  <pageSetup orientation="landscape" r:id="rId44"/>
 </worksheet>
 </file>
 

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3328CC3E-8416-492D-B054-23C98E3A786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A5CE5D-E5E6-4804-B249-24EBF073993B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="338">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -9590,7 +9590,9 @@
       <c r="D2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>166</v>
       </c>
@@ -9628,7 +9630,9 @@
       <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>166</v>
       </c>
@@ -9666,7 +9670,9 @@
       <c r="D4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="F4" s="3" t="s">
         <v>166</v>
       </c>
@@ -9705,7 +9711,7 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>171</v>
@@ -9745,7 +9751,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>171</v>
@@ -9785,7 +9791,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>171</v>
@@ -9825,7 +9831,7 @@
         <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>171</v>
@@ -9865,7 +9871,7 @@
         <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>171</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A5CE5D-E5E6-4804-B249-24EBF073993B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4417440-3DDA-42DE-9899-8E53FE343FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="346">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -585,6 +585,9 @@
     <t>GF</t>
   </si>
   <si>
+    <t>HS1 1</t>
+  </si>
+  <si>
     <t>navigation</t>
   </si>
   <si>
@@ -597,9 +600,15 @@
     <t>45°</t>
   </si>
   <si>
+    <t>HS1 2</t>
+  </si>
+  <si>
     <t>Previous</t>
   </si>
   <si>
+    <t>HS1 3</t>
+  </si>
+  <si>
     <t>info</t>
   </si>
   <si>
@@ -624,6 +633,9 @@
     <t>"Hey, Check this our new premium collections of the Safas"</t>
   </si>
   <si>
+    <t>HS1 4</t>
+  </si>
+  <si>
     <t>[https://images.homedepot-static.com/lifestyleimages/1024x682/85912049-ef4c-4208-94ba-7c4776a420290.jpeg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-3.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-5.jpg]</t>
   </si>
   <si>
@@ -636,6 +648,9 @@
     <t>"Hey, Check this our new premium collections of the Tables"</t>
   </si>
   <si>
+    <t>HS1 5</t>
+  </si>
+  <si>
     <t>[https://www.ikea.com/us/en/home-design/images/graphics/dashboard/try-product-together.png],[https://cdn.apartmenttherapy.info/image/upload/v1554217999/at/house%20tours%20stock%20archive/7f6d6749cdc500dd3a8c93d2e1c6ad6aa7be7dec.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-2.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-3.jpg]</t>
   </si>
   <si>
@@ -645,7 +660,13 @@
     <t>"Hey, Check this our new premium collections of the Beds"</t>
   </si>
   <si>
+    <t>HS1 6</t>
+  </si>
+  <si>
     <t>Premium Chairs</t>
+  </si>
+  <si>
+    <t>HS1 7</t>
   </si>
   <si>
     <t>https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg</t>
@@ -981,6 +1002,9 @@
   </si>
   <si>
     <t>SL#</t>
+  </si>
+  <si>
+    <t>HS1 8</t>
   </si>
   <si>
     <t>HS1-01</t>
@@ -2070,13 +2094,13 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2096,7 +2120,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>30</v>
@@ -2111,7 +2135,7 @@
         <v>32</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>34</v>
@@ -2147,7 +2171,7 @@
         <v>36</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="X2" s="10" t="b">
         <v>1</v>
@@ -2156,13 +2180,13 @@
         <v>1</v>
       </c>
       <c r="Z2" s="37" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
       </c>
       <c r="AB2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2182,7 +2206,7 @@
         <v>38</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>30</v>
@@ -2242,13 +2266,13 @@
         <v>1</v>
       </c>
       <c r="Z3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
       </c>
       <c r="AB3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2268,7 +2292,7 @@
         <v>43</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>30</v>
@@ -2329,7 +2353,7 @@
         <v>45750</v>
       </c>
       <c r="AB4" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2349,7 +2373,7 @@
         <v>48</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>30</v>
@@ -2425,10 +2449,10 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>30</v>
@@ -2490,7 +2514,7 @@
         <v>45750</v>
       </c>
       <c r="AB6" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2510,7 +2534,7 @@
         <v>57</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -2572,7 +2596,7 @@
         <v>45750</v>
       </c>
       <c r="AB7" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2592,7 +2616,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>30</v>
@@ -2656,7 +2680,7 @@
         <v>45750</v>
       </c>
       <c r="AB8" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2676,7 +2700,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>30</v>
@@ -2740,7 +2764,7 @@
         <v>45750</v>
       </c>
       <c r="AB9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2760,7 +2784,7 @@
         <v>77</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>30</v>
@@ -2824,7 +2848,7 @@
         <v>45750</v>
       </c>
       <c r="AB10" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2844,7 +2868,7 @@
         <v>82</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>30</v>
@@ -2906,7 +2930,7 @@
         <v>45750</v>
       </c>
       <c r="AB11" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2926,7 +2950,7 @@
         <v>86</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>30</v>
@@ -2990,7 +3014,7 @@
         <v>45750</v>
       </c>
       <c r="AB12" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3010,7 +3034,7 @@
         <v>92</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>30</v>
@@ -3074,7 +3098,7 @@
         <v>45750</v>
       </c>
       <c r="AB13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3094,7 +3118,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>30</v>
@@ -3158,7 +3182,7 @@
         <v>45750</v>
       </c>
       <c r="AB14" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3178,7 +3202,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>30</v>
@@ -3242,7 +3266,7 @@
         <v>45750</v>
       </c>
       <c r="AB15" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3262,7 +3286,7 @@
         <v>105</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>30</v>
@@ -3326,7 +3350,7 @@
         <v>45750</v>
       </c>
       <c r="AB16" s="38" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3346,7 +3370,7 @@
         <v>110</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>30</v>
@@ -3410,7 +3434,7 @@
         <v>45750</v>
       </c>
       <c r="AB17" s="38" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3430,7 +3454,7 @@
         <v>114</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>30</v>
@@ -3494,7 +3518,7 @@
         <v>45750</v>
       </c>
       <c r="AB18" s="38" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3514,7 +3538,7 @@
         <v>119</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>30</v>
@@ -3578,7 +3602,7 @@
         <v>45750</v>
       </c>
       <c r="AB19" s="38" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3598,7 +3622,7 @@
         <v>126</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>30</v>
@@ -3662,7 +3686,7 @@
         <v>45750</v>
       </c>
       <c r="AB20" s="38" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3682,7 +3706,7 @@
         <v>132</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>30</v>
@@ -3746,7 +3770,7 @@
         <v>45750</v>
       </c>
       <c r="AB21" s="38" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3766,7 +3790,7 @@
         <v>136</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>30</v>
@@ -3830,7 +3854,7 @@
         <v>45750</v>
       </c>
       <c r="AB22" s="38" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3850,7 +3874,7 @@
         <v>140</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>30</v>
@@ -3910,13 +3934,13 @@
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AA23" s="12">
         <v>45750</v>
       </c>
       <c r="AB23" s="38" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -3936,7 +3960,7 @@
         <v>144</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>30</v>
@@ -4000,7 +4024,7 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4011,7 +4035,7 @@
         <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D25" s="4">
         <v>24</v>
@@ -4020,7 +4044,7 @@
         <v>144</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="I25" s="3" t="b">
         <v>1</v>
@@ -4056,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="U25" s="9" t="b">
         <v>1</v>
@@ -4078,7 +4102,7 @@
         <v>45750</v>
       </c>
       <c r="AB25" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4089,7 +4113,7 @@
         <v>117</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D26" s="4">
         <v>25</v>
@@ -4098,7 +4122,7 @@
         <v>144</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I26" s="3" t="b">
         <v>1</v>
@@ -4134,7 +4158,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="U26" s="9" t="b">
         <v>1</v>
@@ -4156,7 +4180,7 @@
         <v>45750</v>
       </c>
       <c r="AB26" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4167,7 +4191,7 @@
         <v>117</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D27" s="4">
         <v>26</v>
@@ -4176,7 +4200,7 @@
         <v>144</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="I27" s="3" t="b">
         <v>1</v>
@@ -4212,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="U27" s="9" t="b">
         <v>1</v>
@@ -4234,7 +4258,7 @@
         <v>45750</v>
       </c>
       <c r="AB27" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4245,7 +4269,7 @@
         <v>117</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D28" s="4">
         <v>27</v>
@@ -4254,7 +4278,7 @@
         <v>144</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="I28" s="3" t="b">
         <v>1</v>
@@ -4290,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="U28" s="9" t="b">
         <v>1</v>
@@ -4312,7 +4336,7 @@
         <v>45750</v>
       </c>
       <c r="AB28" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4323,7 +4347,7 @@
         <v>117</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D29" s="4">
         <v>28</v>
@@ -4332,7 +4356,7 @@
         <v>144</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="I29" s="3" t="b">
         <v>1</v>
@@ -4368,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="U29" s="9" t="b">
         <v>1</v>
@@ -4390,7 +4414,7 @@
         <v>45750</v>
       </c>
       <c r="AB29" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4401,7 +4425,7 @@
         <v>117</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D30" s="4">
         <v>29</v>
@@ -4410,7 +4434,7 @@
         <v>144</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="I30" s="3" t="b">
         <v>1</v>
@@ -4446,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="U30" s="9" t="b">
         <v>1</v>
@@ -4468,7 +4492,7 @@
         <v>45750</v>
       </c>
       <c r="AB30" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4479,7 +4503,7 @@
         <v>117</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D31" s="4">
         <v>30</v>
@@ -4488,7 +4512,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="39" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="I31" s="3" t="b">
         <v>1</v>
@@ -4524,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="U31" s="9" t="b">
         <v>1</v>
@@ -4546,7 +4570,7 @@
         <v>45750</v>
       </c>
       <c r="AB31" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4557,7 +4581,7 @@
         <v>117</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D32" s="4">
         <v>31</v>
@@ -4566,7 +4590,7 @@
         <v>144</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="I32" s="3" t="b">
         <v>1</v>
@@ -4602,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="U32" s="9" t="b">
         <v>1</v>
@@ -4624,7 +4648,7 @@
         <v>45750</v>
       </c>
       <c r="AB32" s="38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="4:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -9570,7 +9594,7 @@
         <v>164</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
@@ -9591,16 +9615,16 @@
         <v>35</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>296</v>
+        <v>166</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I2" s="23">
         <v>-18.66</v>
@@ -9609,7 +9633,7 @@
         <v>3.6</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L2" s="3" t="b">
         <v>1</v>
@@ -9631,16 +9655,16 @@
         <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I3" s="24">
         <v>-17.899999999999999</v>
@@ -9649,7 +9673,7 @@
         <v>80.739999999999995</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L3" s="3" t="b">
         <v>1</v>
@@ -9671,16 +9695,16 @@
         <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>298</v>
+        <v>173</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I4" s="24">
         <v>-6.94</v>
@@ -9689,7 +9713,7 @@
         <v>77.06</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L4" s="3" t="b">
         <v>1</v>
@@ -9711,14 +9735,14 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I5" s="23">
         <v>13.3</v>
@@ -9727,7 +9751,7 @@
         <v>-50.58</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L5" s="3" t="b">
         <v>1</v>
@@ -9751,14 +9775,14 @@
         <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>300</v>
+        <v>187</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I6" s="24">
         <v>-12.48</v>
@@ -9767,7 +9791,7 @@
         <v>-13.11</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L6" s="13" t="b">
         <v>0</v>
@@ -9791,14 +9815,14 @@
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>301</v>
+        <v>191</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I7" s="23">
         <v>-17.02</v>
@@ -9807,7 +9831,7 @@
         <v>17.059999999999999</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L7" s="3" t="b">
         <v>1</v>
@@ -9831,14 +9855,14 @@
         <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>302</v>
+        <v>193</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I8" s="24">
         <v>-9.15</v>
@@ -9847,7 +9871,7 @@
         <v>49.78</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L8" s="3" t="b">
         <v>1</v>
@@ -9874,11 +9898,11 @@
         <v>303</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I9" s="25">
         <v>35.43</v>
@@ -9887,7 +9911,7 @@
         <v>63.03</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L9" s="3" t="b">
         <v>1</v>
@@ -9912,13 +9936,13 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I10" s="23">
         <v>-24.61</v>
@@ -9927,7 +9951,7 @@
         <v>176.91</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L10" s="3" t="b">
         <v>1</v>
@@ -9950,13 +9974,13 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I11" s="24">
         <v>-11.7</v>
@@ -9965,7 +9989,7 @@
         <v>-3.78</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L11" s="3" t="b">
         <v>1</v>
@@ -9987,14 +10011,14 @@
         <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I12" s="23">
         <v>-0.74</v>
@@ -10003,7 +10027,7 @@
         <v>112.77</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L12" s="3" t="b">
         <v>1</v>
@@ -10025,14 +10049,14 @@
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I13" s="24">
         <v>10.43</v>
@@ -10041,7 +10065,7 @@
         <v>170.31</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L13" s="3" t="b">
         <v>1</v>
@@ -10063,14 +10087,14 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I14" s="23">
         <v>26.8</v>
@@ -10079,7 +10103,7 @@
         <v>-136.21</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L14" s="3" t="b">
         <v>1</v>
@@ -10101,14 +10125,14 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I15" s="24">
         <v>65.44</v>
@@ -10117,7 +10141,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L15" s="3" t="b">
         <v>1</v>
@@ -10139,14 +10163,14 @@
         <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I16" s="25">
         <v>58.71</v>
@@ -10155,7 +10179,7 @@
         <v>-1.51</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L16" s="3" t="b">
         <v>1</v>
@@ -10178,13 +10202,13 @@
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I17" s="23">
         <v>-24.61</v>
@@ -10193,7 +10217,7 @@
         <v>176.91</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L17" s="3" t="b">
         <v>1</v>
@@ -10216,13 +10240,13 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I18" s="24">
         <v>-11.7</v>
@@ -10231,7 +10255,7 @@
         <v>-3.78</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L18" s="3" t="b">
         <v>1</v>
@@ -10253,14 +10277,14 @@
         <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I19" s="23">
         <v>-0.74</v>
@@ -10269,7 +10293,7 @@
         <v>112.77</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L19" s="3" t="b">
         <v>1</v>
@@ -10291,14 +10315,14 @@
         <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I20" s="24">
         <v>10.43</v>
@@ -10307,7 +10331,7 @@
         <v>170.31</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L20" s="3" t="b">
         <v>1</v>
@@ -10329,14 +10353,14 @@
         <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I21" s="23">
         <v>26.8</v>
@@ -10345,7 +10369,7 @@
         <v>-136.21</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L21" s="3" t="b">
         <v>1</v>
@@ -10367,14 +10391,14 @@
         <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I22" s="24">
         <v>65.44</v>
@@ -10383,7 +10407,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L22" s="3" t="b">
         <v>1</v>
@@ -10405,14 +10429,14 @@
         <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I23" s="25">
         <v>58.71</v>
@@ -10421,7 +10445,7 @@
         <v>-1.51</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L23" s="3" t="b">
         <v>1</v>
@@ -10444,13 +10468,13 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I24" s="23">
         <v>-24.61</v>
@@ -10459,7 +10483,7 @@
         <v>176.91</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L24" s="3" t="b">
         <v>1</v>
@@ -10482,13 +10506,13 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I25" s="24">
         <v>-11.7</v>
@@ -10497,7 +10521,7 @@
         <v>-3.78</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L25" s="3" t="b">
         <v>1</v>
@@ -10519,14 +10543,14 @@
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I26" s="23">
         <v>-0.74</v>
@@ -10535,7 +10559,7 @@
         <v>112.77</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L26" s="3" t="b">
         <v>1</v>
@@ -10557,14 +10581,14 @@
         <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I27" s="24">
         <v>10.43</v>
@@ -10573,7 +10597,7 @@
         <v>170.31</v>
       </c>
       <c r="K27" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L27" s="3" t="b">
         <v>1</v>
@@ -10595,14 +10619,14 @@
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I28" s="23">
         <v>26.8</v>
@@ -10611,7 +10635,7 @@
         <v>-136.21</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L28" s="3" t="b">
         <v>1</v>
@@ -10633,14 +10657,14 @@
         <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I29" s="24">
         <v>65.44</v>
@@ -10649,7 +10673,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K29" s="26" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L29" s="3" t="b">
         <v>1</v>
@@ -10671,14 +10695,14 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I30" s="25">
         <v>58.71</v>
@@ -10687,7 +10711,7 @@
         <v>-1.51</v>
       </c>
       <c r="K30" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L30" s="3" t="b">
         <v>1</v>
@@ -10710,13 +10734,13 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I31" s="23">
         <v>-24.61</v>
@@ -10725,7 +10749,7 @@
         <v>176.91</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L31" s="3" t="b">
         <v>1</v>
@@ -10748,13 +10772,13 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I32" s="24">
         <v>-11.7</v>
@@ -10763,7 +10787,7 @@
         <v>-3.78</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L32" s="3" t="b">
         <v>1</v>
@@ -10785,14 +10809,14 @@
         <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I33" s="23">
         <v>-0.74</v>
@@ -10801,7 +10825,7 @@
         <v>112.77</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L33" s="3" t="b">
         <v>1</v>
@@ -10823,14 +10847,14 @@
         <v>53</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I34" s="24">
         <v>10.43</v>
@@ -10839,7 +10863,7 @@
         <v>170.31</v>
       </c>
       <c r="K34" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L34" s="3" t="b">
         <v>1</v>
@@ -10861,14 +10885,14 @@
         <v>53</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I35" s="23">
         <v>26.8</v>
@@ -10877,7 +10901,7 @@
         <v>-136.21</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L35" s="3" t="b">
         <v>1</v>
@@ -10899,14 +10923,14 @@
         <v>53</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I36" s="24">
         <v>65.44</v>
@@ -10915,7 +10939,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K36" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L36" s="3" t="b">
         <v>1</v>
@@ -10937,14 +10961,14 @@
         <v>53</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I37" s="25">
         <v>58.71</v>
@@ -10953,7 +10977,7 @@
         <v>-1.51</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L37" s="3" t="b">
         <v>1</v>
@@ -10976,13 +11000,13 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I38" s="23">
         <v>-24.61</v>
@@ -10991,7 +11015,7 @@
         <v>176.91</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L38" s="3" t="b">
         <v>1</v>
@@ -11014,13 +11038,13 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I39" s="24">
         <v>-11.7</v>
@@ -11029,7 +11053,7 @@
         <v>-3.78</v>
       </c>
       <c r="K39" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L39" s="3" t="b">
         <v>1</v>
@@ -11051,14 +11075,14 @@
         <v>62</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I40" s="23">
         <v>-0.74</v>
@@ -11067,7 +11091,7 @@
         <v>112.77</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L40" s="3" t="b">
         <v>1</v>
@@ -11089,14 +11113,14 @@
         <v>62</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I41" s="24">
         <v>10.43</v>
@@ -11105,7 +11129,7 @@
         <v>170.31</v>
       </c>
       <c r="K41" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L41" s="3" t="b">
         <v>1</v>
@@ -11127,14 +11151,14 @@
         <v>62</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I42" s="23">
         <v>26.8</v>
@@ -11143,7 +11167,7 @@
         <v>-136.21</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L42" s="3" t="b">
         <v>1</v>
@@ -11165,14 +11189,14 @@
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I43" s="24">
         <v>65.44</v>
@@ -11181,7 +11205,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K43" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L43" s="3" t="b">
         <v>1</v>
@@ -11203,14 +11227,14 @@
         <v>62</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I44" s="25">
         <v>58.71</v>
@@ -11219,7 +11243,7 @@
         <v>-1.51</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L44" s="3" t="b">
         <v>1</v>
@@ -11242,13 +11266,13 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I45" s="23">
         <v>-24.61</v>
@@ -11257,7 +11281,7 @@
         <v>176.91</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L45" s="3" t="b">
         <v>1</v>
@@ -11280,13 +11304,13 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" s="24">
         <v>-11.7</v>
@@ -11295,7 +11319,7 @@
         <v>-3.78</v>
       </c>
       <c r="K46" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L46" s="3" t="b">
         <v>1</v>
@@ -11317,14 +11341,14 @@
         <v>67</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I47" s="23">
         <v>-0.74</v>
@@ -11333,7 +11357,7 @@
         <v>112.77</v>
       </c>
       <c r="K47" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L47" s="3" t="b">
         <v>1</v>
@@ -11355,14 +11379,14 @@
         <v>67</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I48" s="24">
         <v>10.43</v>
@@ -11371,7 +11395,7 @@
         <v>170.31</v>
       </c>
       <c r="K48" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L48" s="3" t="b">
         <v>1</v>
@@ -11393,14 +11417,14 @@
         <v>67</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I49" s="23">
         <v>26.8</v>
@@ -11409,7 +11433,7 @@
         <v>-136.21</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L49" s="3" t="b">
         <v>1</v>
@@ -11431,14 +11455,14 @@
         <v>67</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I50" s="24">
         <v>65.44</v>
@@ -11447,7 +11471,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K50" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L50" s="3" t="b">
         <v>1</v>
@@ -11469,14 +11493,14 @@
         <v>67</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I51" s="25">
         <v>58.71</v>
@@ -11485,7 +11509,7 @@
         <v>-1.51</v>
       </c>
       <c r="K51" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L51" s="3" t="b">
         <v>1</v>
@@ -11508,13 +11532,13 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I52" s="23">
         <v>-15.9</v>
@@ -11523,7 +11547,7 @@
         <v>100.17</v>
       </c>
       <c r="K52" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L52" s="3" t="b">
         <v>1</v>
@@ -11546,13 +11570,13 @@
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I53" s="24">
         <v>-7.08</v>
@@ -11561,7 +11585,7 @@
         <v>-86.86</v>
       </c>
       <c r="K53" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L53" s="3" t="b">
         <v>1</v>
@@ -11583,14 +11607,14 @@
         <v>74</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I54" s="23">
         <v>-0.74</v>
@@ -11599,7 +11623,7 @@
         <v>112.77</v>
       </c>
       <c r="K54" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L54" s="3" t="b">
         <v>1</v>
@@ -11621,14 +11645,14 @@
         <v>74</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I55" s="24">
         <v>10.43</v>
@@ -11637,7 +11661,7 @@
         <v>170.31</v>
       </c>
       <c r="K55" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L55" s="3" t="b">
         <v>1</v>
@@ -11659,14 +11683,14 @@
         <v>74</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I56" s="23">
         <v>26.8</v>
@@ -11675,7 +11699,7 @@
         <v>-136.21</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L56" s="3" t="b">
         <v>1</v>
@@ -11697,14 +11721,14 @@
         <v>74</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I57" s="24">
         <v>65.44</v>
@@ -11713,7 +11737,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K57" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L57" s="3" t="b">
         <v>1</v>
@@ -11735,14 +11759,14 @@
         <v>74</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I58" s="25">
         <v>58.71</v>
@@ -11751,7 +11775,7 @@
         <v>-1.51</v>
       </c>
       <c r="K58" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L58" s="3" t="b">
         <v>1</v>
@@ -11774,13 +11798,13 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I59" s="23">
         <v>-24.61</v>
@@ -11789,7 +11813,7 @@
         <v>176.91</v>
       </c>
       <c r="K59" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L59" s="3" t="b">
         <v>1</v>
@@ -11812,13 +11836,13 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I60" s="24">
         <v>-11.7</v>
@@ -11827,7 +11851,7 @@
         <v>-3.78</v>
       </c>
       <c r="K60" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L60" s="3" t="b">
         <v>1</v>
@@ -11849,14 +11873,14 @@
         <v>79</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I61" s="23">
         <v>-0.74</v>
@@ -11865,7 +11889,7 @@
         <v>112.77</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L61" s="3" t="b">
         <v>1</v>
@@ -11887,14 +11911,14 @@
         <v>79</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I62" s="24">
         <v>10.43</v>
@@ -11903,7 +11927,7 @@
         <v>170.31</v>
       </c>
       <c r="K62" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L62" s="3" t="b">
         <v>1</v>
@@ -11925,14 +11949,14 @@
         <v>79</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I63" s="23">
         <v>26.8</v>
@@ -11941,7 +11965,7 @@
         <v>-136.21</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L63" s="3" t="b">
         <v>1</v>
@@ -11963,14 +11987,14 @@
         <v>79</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I64" s="24">
         <v>65.44</v>
@@ -11979,7 +12003,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K64" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L64" s="3" t="b">
         <v>1</v>
@@ -12001,14 +12025,14 @@
         <v>79</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I65" s="25">
         <v>58.71</v>
@@ -12017,7 +12041,7 @@
         <v>-1.51</v>
       </c>
       <c r="K65" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L65" s="3" t="b">
         <v>1</v>
@@ -12040,13 +12064,13 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I66" s="23">
         <v>-24.61</v>
@@ -12055,7 +12079,7 @@
         <v>176.91</v>
       </c>
       <c r="K66" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L66" s="3" t="b">
         <v>1</v>
@@ -12078,13 +12102,13 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I67" s="24">
         <v>-11.7</v>
@@ -12093,7 +12117,7 @@
         <v>-3.78</v>
       </c>
       <c r="K67" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L67" s="3" t="b">
         <v>1</v>
@@ -12115,14 +12139,14 @@
         <v>83</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I68" s="23">
         <v>-0.74</v>
@@ -12131,7 +12155,7 @@
         <v>112.77</v>
       </c>
       <c r="K68" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L68" s="3" t="b">
         <v>1</v>
@@ -12153,14 +12177,14 @@
         <v>83</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I69" s="24">
         <v>10.43</v>
@@ -12169,7 +12193,7 @@
         <v>170.31</v>
       </c>
       <c r="K69" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L69" s="3" t="b">
         <v>1</v>
@@ -12191,14 +12215,14 @@
         <v>83</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I70" s="23">
         <v>26.8</v>
@@ -12207,7 +12231,7 @@
         <v>-136.21</v>
       </c>
       <c r="K70" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L70" s="3" t="b">
         <v>1</v>
@@ -12229,14 +12253,14 @@
         <v>83</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I71" s="24">
         <v>65.44</v>
@@ -12245,7 +12269,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K71" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L71" s="3" t="b">
         <v>1</v>
@@ -12267,14 +12291,14 @@
         <v>83</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I72" s="25">
         <v>58.71</v>
@@ -12283,7 +12307,7 @@
         <v>-1.51</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L72" s="3" t="b">
         <v>1</v>
@@ -12306,13 +12330,13 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H73" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I73" s="23">
         <v>-24.61</v>
@@ -12321,7 +12345,7 @@
         <v>176.91</v>
       </c>
       <c r="K73" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L73" s="3" t="b">
         <v>1</v>
@@ -12344,13 +12368,13 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I74" s="24">
         <v>-11.7</v>
@@ -12359,7 +12383,7 @@
         <v>-3.78</v>
       </c>
       <c r="K74" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L74" s="3" t="b">
         <v>1</v>
@@ -12381,14 +12405,14 @@
         <v>87</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I75" s="23">
         <v>-0.74</v>
@@ -12397,7 +12421,7 @@
         <v>112.77</v>
       </c>
       <c r="K75" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L75" s="3" t="b">
         <v>1</v>
@@ -12419,14 +12443,14 @@
         <v>87</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I76" s="24">
         <v>10.43</v>
@@ -12435,7 +12459,7 @@
         <v>170.31</v>
       </c>
       <c r="K76" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L76" s="3" t="b">
         <v>1</v>
@@ -12457,14 +12481,14 @@
         <v>87</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I77" s="23">
         <v>26.8</v>
@@ -12473,7 +12497,7 @@
         <v>-136.21</v>
       </c>
       <c r="K77" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L77" s="3" t="b">
         <v>1</v>
@@ -12495,14 +12519,14 @@
         <v>87</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I78" s="24">
         <v>65.44</v>
@@ -12511,7 +12535,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K78" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L78" s="3" t="b">
         <v>1</v>
@@ -12533,14 +12557,14 @@
         <v>87</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I79" s="25">
         <v>58.71</v>
@@ -12549,7 +12573,7 @@
         <v>-1.51</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L79" s="3" t="b">
         <v>1</v>
@@ -12572,13 +12596,13 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I80" s="23">
         <v>-24.61</v>
@@ -12587,7 +12611,7 @@
         <v>176.91</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L80" s="3" t="b">
         <v>1</v>
@@ -12610,13 +12634,13 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I81" s="24">
         <v>-11.7</v>
@@ -12625,7 +12649,7 @@
         <v>-3.78</v>
       </c>
       <c r="K81" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L81" s="3" t="b">
         <v>1</v>
@@ -12647,14 +12671,14 @@
         <v>93</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I82" s="23">
         <v>-0.74</v>
@@ -12663,7 +12687,7 @@
         <v>112.77</v>
       </c>
       <c r="K82" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L82" s="3" t="b">
         <v>1</v>
@@ -12685,14 +12709,14 @@
         <v>93</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I83" s="24">
         <v>10.43</v>
@@ -12701,7 +12725,7 @@
         <v>170.31</v>
       </c>
       <c r="K83" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L83" s="3" t="b">
         <v>1</v>
@@ -12723,14 +12747,14 @@
         <v>93</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I84" s="23">
         <v>26.8</v>
@@ -12739,7 +12763,7 @@
         <v>-136.21</v>
       </c>
       <c r="K84" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L84" s="3" t="b">
         <v>1</v>
@@ -12761,14 +12785,14 @@
         <v>93</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I85" s="24">
         <v>65.44</v>
@@ -12777,7 +12801,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K85" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L85" s="3" t="b">
         <v>1</v>
@@ -12799,14 +12823,14 @@
         <v>93</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I86" s="25">
         <v>58.71</v>
@@ -12815,7 +12839,7 @@
         <v>-1.51</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L86" s="3" t="b">
         <v>1</v>
@@ -12838,13 +12862,13 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I87" s="23">
         <v>-24.61</v>
@@ -12853,7 +12877,7 @@
         <v>176.91</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L87" s="3" t="b">
         <v>1</v>
@@ -12876,13 +12900,13 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I88" s="24">
         <v>-11.7</v>
@@ -12891,7 +12915,7 @@
         <v>-3.78</v>
       </c>
       <c r="K88" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L88" s="3" t="b">
         <v>1</v>
@@ -12913,14 +12937,14 @@
         <v>97</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I89" s="23">
         <v>-0.74</v>
@@ -12929,7 +12953,7 @@
         <v>112.77</v>
       </c>
       <c r="K89" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L89" s="3" t="b">
         <v>1</v>
@@ -12951,14 +12975,14 @@
         <v>97</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I90" s="24">
         <v>10.43</v>
@@ -12967,7 +12991,7 @@
         <v>170.31</v>
       </c>
       <c r="K90" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L90" s="3" t="b">
         <v>1</v>
@@ -12989,14 +13013,14 @@
         <v>97</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I91" s="23">
         <v>26.8</v>
@@ -13005,7 +13029,7 @@
         <v>-136.21</v>
       </c>
       <c r="K91" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L91" s="3" t="b">
         <v>1</v>
@@ -13027,14 +13051,14 @@
         <v>97</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I92" s="24">
         <v>65.44</v>
@@ -13043,7 +13067,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K92" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L92" s="3" t="b">
         <v>1</v>
@@ -13065,14 +13089,14 @@
         <v>97</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I93" s="25">
         <v>58.71</v>
@@ -13081,7 +13105,7 @@
         <v>-1.51</v>
       </c>
       <c r="K93" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L93" s="3" t="b">
         <v>1</v>
@@ -13104,13 +13128,13 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I94" s="23">
         <v>-24.61</v>
@@ -13119,7 +13143,7 @@
         <v>176.91</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L94" s="3" t="b">
         <v>1</v>
@@ -13142,13 +13166,13 @@
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I95" s="24">
         <v>-11.7</v>
@@ -13157,7 +13181,7 @@
         <v>-3.78</v>
       </c>
       <c r="K95" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L95" s="3" t="b">
         <v>1</v>
@@ -13179,14 +13203,14 @@
         <v>101</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I96" s="23">
         <v>-0.74</v>
@@ -13195,7 +13219,7 @@
         <v>112.77</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L96" s="3" t="b">
         <v>1</v>
@@ -13217,14 +13241,14 @@
         <v>101</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I97" s="24">
         <v>10.43</v>
@@ -13233,7 +13257,7 @@
         <v>170.31</v>
       </c>
       <c r="K97" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L97" s="3" t="b">
         <v>1</v>
@@ -13255,14 +13279,14 @@
         <v>101</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I98" s="23">
         <v>26.8</v>
@@ -13271,7 +13295,7 @@
         <v>-136.21</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L98" s="3" t="b">
         <v>1</v>
@@ -13293,14 +13317,14 @@
         <v>101</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I99" s="24">
         <v>65.44</v>
@@ -13309,7 +13333,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K99" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L99" s="3" t="b">
         <v>1</v>
@@ -13331,14 +13355,14 @@
         <v>101</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I100" s="25">
         <v>58.71</v>
@@ -13347,7 +13371,7 @@
         <v>-1.51</v>
       </c>
       <c r="K100" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L100" s="3" t="b">
         <v>1</v>
@@ -13357,7 +13381,7 @@
     </row>
     <row r="101" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B101" s="7">
         <v>15</v>
@@ -13370,13 +13394,13 @@
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H101" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I101" s="23">
         <v>-24.61</v>
@@ -13385,7 +13409,7 @@
         <v>176.91</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L101" s="3" t="b">
         <v>1</v>
@@ -13395,7 +13419,7 @@
     </row>
     <row r="102" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B102" s="7">
         <v>15</v>
@@ -13408,13 +13432,13 @@
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I102" s="24">
         <v>-11.7</v>
@@ -13423,7 +13447,7 @@
         <v>-3.78</v>
       </c>
       <c r="K102" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L102" s="3" t="b">
         <v>1</v>
@@ -13433,7 +13457,7 @@
     </row>
     <row r="103" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B103" s="7">
         <v>15</v>
@@ -13445,14 +13469,14 @@
         <v>106</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I103" s="23">
         <v>-0.74</v>
@@ -13461,7 +13485,7 @@
         <v>112.77</v>
       </c>
       <c r="K103" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L103" s="3" t="b">
         <v>1</v>
@@ -13471,7 +13495,7 @@
     </row>
     <row r="104" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B104" s="7">
         <v>15</v>
@@ -13483,14 +13507,14 @@
         <v>106</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I104" s="24">
         <v>10.43</v>
@@ -13499,7 +13523,7 @@
         <v>170.31</v>
       </c>
       <c r="K104" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L104" s="3" t="b">
         <v>1</v>
@@ -13509,7 +13533,7 @@
     </row>
     <row r="105" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B105" s="7">
         <v>15</v>
@@ -13521,14 +13545,14 @@
         <v>106</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I105" s="23">
         <v>26.8</v>
@@ -13537,7 +13561,7 @@
         <v>-136.21</v>
       </c>
       <c r="K105" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L105" s="3" t="b">
         <v>1</v>
@@ -13547,7 +13571,7 @@
     </row>
     <row r="106" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B106" s="7">
         <v>15</v>
@@ -13559,14 +13583,14 @@
         <v>106</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I106" s="24">
         <v>65.44</v>
@@ -13575,7 +13599,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K106" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L106" s="3" t="b">
         <v>1</v>
@@ -13585,7 +13609,7 @@
     </row>
     <row r="107" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B107" s="7">
         <v>15</v>
@@ -13597,14 +13621,14 @@
         <v>106</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I107" s="25">
         <v>58.71</v>
@@ -13613,7 +13637,7 @@
         <v>-1.51</v>
       </c>
       <c r="K107" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L107" s="3" t="b">
         <v>1</v>
@@ -13623,7 +13647,7 @@
     </row>
     <row r="108" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B108" s="7">
         <v>16</v>
@@ -13636,13 +13660,13 @@
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H108" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I108" s="23">
         <v>-24.61</v>
@@ -13651,7 +13675,7 @@
         <v>176.91</v>
       </c>
       <c r="K108" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L108" s="3" t="b">
         <v>1</v>
@@ -13661,7 +13685,7 @@
     </row>
     <row r="109" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B109" s="7">
         <v>16</v>
@@ -13674,13 +13698,13 @@
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H109" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I109" s="24">
         <v>-11.7</v>
@@ -13689,7 +13713,7 @@
         <v>-3.78</v>
       </c>
       <c r="K109" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L109" s="3" t="b">
         <v>1</v>
@@ -13699,7 +13723,7 @@
     </row>
     <row r="110" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B110" s="7">
         <v>16</v>
@@ -13711,14 +13735,14 @@
         <v>111</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I110" s="23">
         <v>-0.74</v>
@@ -13727,7 +13751,7 @@
         <v>112.77</v>
       </c>
       <c r="K110" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L110" s="3" t="b">
         <v>1</v>
@@ -13737,7 +13761,7 @@
     </row>
     <row r="111" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B111" s="7">
         <v>16</v>
@@ -13749,14 +13773,14 @@
         <v>111</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I111" s="24">
         <v>10.43</v>
@@ -13765,7 +13789,7 @@
         <v>170.31</v>
       </c>
       <c r="K111" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L111" s="3" t="b">
         <v>1</v>
@@ -13775,7 +13799,7 @@
     </row>
     <row r="112" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B112" s="7">
         <v>16</v>
@@ -13787,14 +13811,14 @@
         <v>111</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I112" s="23">
         <v>26.8</v>
@@ -13803,7 +13827,7 @@
         <v>-136.21</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L112" s="3" t="b">
         <v>1</v>
@@ -13813,7 +13837,7 @@
     </row>
     <row r="113" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B113" s="7">
         <v>16</v>
@@ -13825,14 +13849,14 @@
         <v>111</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I113" s="24">
         <v>65.44</v>
@@ -13841,7 +13865,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K113" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L113" s="3" t="b">
         <v>1</v>
@@ -13851,7 +13875,7 @@
     </row>
     <row r="114" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B114" s="7">
         <v>16</v>
@@ -13863,14 +13887,14 @@
         <v>111</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I114" s="25">
         <v>58.71</v>
@@ -13879,7 +13903,7 @@
         <v>-1.51</v>
       </c>
       <c r="K114" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L114" s="3" t="b">
         <v>1</v>
@@ -13889,7 +13913,7 @@
     </row>
     <row r="115" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B115" s="7">
         <v>17</v>
@@ -13902,13 +13926,13 @@
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I115" s="23">
         <v>-24.61</v>
@@ -13917,7 +13941,7 @@
         <v>176.91</v>
       </c>
       <c r="K115" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L115" s="3" t="b">
         <v>1</v>
@@ -13927,7 +13951,7 @@
     </row>
     <row r="116" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B116" s="7">
         <v>17</v>
@@ -13940,13 +13964,13 @@
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I116" s="24">
         <v>-11.7</v>
@@ -13955,7 +13979,7 @@
         <v>-3.78</v>
       </c>
       <c r="K116" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L116" s="3" t="b">
         <v>1</v>
@@ -13965,7 +13989,7 @@
     </row>
     <row r="117" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B117" s="7">
         <v>17</v>
@@ -13977,14 +14001,14 @@
         <v>115</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I117" s="23">
         <v>-0.74</v>
@@ -13993,7 +14017,7 @@
         <v>112.77</v>
       </c>
       <c r="K117" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L117" s="3" t="b">
         <v>1</v>
@@ -14003,7 +14027,7 @@
     </row>
     <row r="118" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B118" s="7">
         <v>17</v>
@@ -14015,14 +14039,14 @@
         <v>115</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I118" s="24">
         <v>10.43</v>
@@ -14031,7 +14055,7 @@
         <v>170.31</v>
       </c>
       <c r="K118" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L118" s="3" t="b">
         <v>1</v>
@@ -14041,7 +14065,7 @@
     </row>
     <row r="119" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B119" s="7">
         <v>17</v>
@@ -14053,14 +14077,14 @@
         <v>115</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I119" s="23">
         <v>26.8</v>
@@ -14069,7 +14093,7 @@
         <v>-136.21</v>
       </c>
       <c r="K119" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L119" s="3" t="b">
         <v>1</v>
@@ -14079,7 +14103,7 @@
     </row>
     <row r="120" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B120" s="7">
         <v>17</v>
@@ -14091,14 +14115,14 @@
         <v>115</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I120" s="24">
         <v>65.44</v>
@@ -14107,7 +14131,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K120" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L120" s="3" t="b">
         <v>1</v>
@@ -14117,7 +14141,7 @@
     </row>
     <row r="121" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B121" s="7">
         <v>17</v>
@@ -14129,14 +14153,14 @@
         <v>115</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I121" s="25">
         <v>58.71</v>
@@ -14145,7 +14169,7 @@
         <v>-1.51</v>
       </c>
       <c r="K121" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L121" s="3" t="b">
         <v>1</v>
@@ -14155,7 +14179,7 @@
     </row>
     <row r="122" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B122" s="7">
         <v>18</v>
@@ -14168,13 +14192,13 @@
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I122" s="23">
         <v>-24.61</v>
@@ -14183,7 +14207,7 @@
         <v>176.91</v>
       </c>
       <c r="K122" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L122" s="3" t="b">
         <v>1</v>
@@ -14193,7 +14217,7 @@
     </row>
     <row r="123" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B123" s="7">
         <v>18</v>
@@ -14206,13 +14230,13 @@
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I123" s="24">
         <v>-11.7</v>
@@ -14221,7 +14245,7 @@
         <v>-3.78</v>
       </c>
       <c r="K123" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L123" s="3" t="b">
         <v>1</v>
@@ -14231,7 +14255,7 @@
     </row>
     <row r="124" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B124" s="7">
         <v>18</v>
@@ -14243,14 +14267,14 @@
         <v>123</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I124" s="23">
         <v>-0.74</v>
@@ -14259,7 +14283,7 @@
         <v>112.77</v>
       </c>
       <c r="K124" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L124" s="3" t="b">
         <v>1</v>
@@ -14269,7 +14293,7 @@
     </row>
     <row r="125" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B125" s="7">
         <v>18</v>
@@ -14281,14 +14305,14 @@
         <v>123</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I125" s="24">
         <v>10.43</v>
@@ -14297,7 +14321,7 @@
         <v>170.31</v>
       </c>
       <c r="K125" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L125" s="3" t="b">
         <v>1</v>
@@ -14307,7 +14331,7 @@
     </row>
     <row r="126" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B126" s="7">
         <v>18</v>
@@ -14319,14 +14343,14 @@
         <v>123</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I126" s="23">
         <v>26.8</v>
@@ -14335,7 +14359,7 @@
         <v>-136.21</v>
       </c>
       <c r="K126" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L126" s="3" t="b">
         <v>1</v>
@@ -14345,7 +14369,7 @@
     </row>
     <row r="127" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B127" s="7">
         <v>18</v>
@@ -14357,14 +14381,14 @@
         <v>123</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I127" s="24">
         <v>65.44</v>
@@ -14373,7 +14397,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K127" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L127" s="3" t="b">
         <v>1</v>
@@ -14383,7 +14407,7 @@
     </row>
     <row r="128" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B128" s="7">
         <v>18</v>
@@ -14395,14 +14419,14 @@
         <v>123</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G128" s="3"/>
       <c r="H128" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I128" s="25">
         <v>58.71</v>
@@ -14411,7 +14435,7 @@
         <v>-1.51</v>
       </c>
       <c r="K128" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L128" s="3" t="b">
         <v>1</v>
@@ -14421,7 +14445,7 @@
     </row>
     <row r="129" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B129" s="7">
         <v>19</v>
@@ -14434,13 +14458,13 @@
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H129" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I129" s="23">
         <v>-24.61</v>
@@ -14449,7 +14473,7 @@
         <v>176.91</v>
       </c>
       <c r="K129" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L129" s="3" t="b">
         <v>1</v>
@@ -14459,7 +14483,7 @@
     </row>
     <row r="130" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B130" s="7">
         <v>19</v>
@@ -14472,13 +14496,13 @@
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H130" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I130" s="24">
         <v>-11.7</v>
@@ -14487,7 +14511,7 @@
         <v>-3.78</v>
       </c>
       <c r="K130" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L130" s="3" t="b">
         <v>1</v>
@@ -14497,7 +14521,7 @@
     </row>
     <row r="131" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B131" s="7">
         <v>19</v>
@@ -14509,14 +14533,14 @@
         <v>129</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G131" s="3"/>
       <c r="H131" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I131" s="23">
         <v>-0.74</v>
@@ -14525,7 +14549,7 @@
         <v>112.77</v>
       </c>
       <c r="K131" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L131" s="3" t="b">
         <v>1</v>
@@ -14535,7 +14559,7 @@
     </row>
     <row r="132" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B132" s="7">
         <v>19</v>
@@ -14547,14 +14571,14 @@
         <v>129</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I132" s="24">
         <v>10.43</v>
@@ -14563,7 +14587,7 @@
         <v>170.31</v>
       </c>
       <c r="K132" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L132" s="3" t="b">
         <v>1</v>
@@ -14573,7 +14597,7 @@
     </row>
     <row r="133" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B133" s="7">
         <v>19</v>
@@ -14585,14 +14609,14 @@
         <v>129</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I133" s="23">
         <v>26.8</v>
@@ -14601,7 +14625,7 @@
         <v>-136.21</v>
       </c>
       <c r="K133" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L133" s="3" t="b">
         <v>1</v>
@@ -14611,7 +14635,7 @@
     </row>
     <row r="134" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B134" s="7">
         <v>19</v>
@@ -14623,14 +14647,14 @@
         <v>129</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G134" s="3"/>
       <c r="H134" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I134" s="24">
         <v>65.44</v>
@@ -14639,7 +14663,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K134" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L134" s="3" t="b">
         <v>1</v>
@@ -14649,7 +14673,7 @@
     </row>
     <row r="135" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B135" s="7">
         <v>19</v>
@@ -14661,14 +14685,14 @@
         <v>129</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G135" s="3"/>
       <c r="H135" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I135" s="25">
         <v>58.71</v>
@@ -14677,7 +14701,7 @@
         <v>-1.51</v>
       </c>
       <c r="K135" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L135" s="3" t="b">
         <v>1</v>
@@ -14687,7 +14711,7 @@
     </row>
     <row r="136" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B136" s="7">
         <v>20</v>
@@ -14700,13 +14724,13 @@
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H136" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I136" s="23">
         <v>-24.61</v>
@@ -14715,7 +14739,7 @@
         <v>176.91</v>
       </c>
       <c r="K136" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L136" s="3" t="b">
         <v>1</v>
@@ -14725,7 +14749,7 @@
     </row>
     <row r="137" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B137" s="7">
         <v>20</v>
@@ -14738,13 +14762,13 @@
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H137" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I137" s="24">
         <v>-11.7</v>
@@ -14753,7 +14777,7 @@
         <v>-3.78</v>
       </c>
       <c r="K137" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L137" s="3" t="b">
         <v>1</v>
@@ -14763,7 +14787,7 @@
     </row>
     <row r="138" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B138" s="7">
         <v>20</v>
@@ -14775,14 +14799,14 @@
         <v>133</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I138" s="23">
         <v>-0.74</v>
@@ -14791,7 +14815,7 @@
         <v>112.77</v>
       </c>
       <c r="K138" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L138" s="3" t="b">
         <v>1</v>
@@ -14801,7 +14825,7 @@
     </row>
     <row r="139" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B139" s="7">
         <v>20</v>
@@ -14813,14 +14837,14 @@
         <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I139" s="24">
         <v>10.43</v>
@@ -14829,7 +14853,7 @@
         <v>170.31</v>
       </c>
       <c r="K139" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L139" s="3" t="b">
         <v>1</v>
@@ -14839,7 +14863,7 @@
     </row>
     <row r="140" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B140" s="7">
         <v>20</v>
@@ -14851,14 +14875,14 @@
         <v>133</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I140" s="23">
         <v>26.8</v>
@@ -14867,7 +14891,7 @@
         <v>-136.21</v>
       </c>
       <c r="K140" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L140" s="3" t="b">
         <v>1</v>
@@ -14877,7 +14901,7 @@
     </row>
     <row r="141" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B141" s="7">
         <v>20</v>
@@ -14889,14 +14913,14 @@
         <v>133</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I141" s="24">
         <v>65.44</v>
@@ -14905,7 +14929,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K141" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L141" s="3" t="b">
         <v>1</v>
@@ -14915,7 +14939,7 @@
     </row>
     <row r="142" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B142" s="7">
         <v>20</v>
@@ -14927,14 +14951,14 @@
         <v>133</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G142" s="3"/>
       <c r="H142" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I142" s="25">
         <v>58.71</v>
@@ -14943,7 +14967,7 @@
         <v>-1.51</v>
       </c>
       <c r="K142" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L142" s="3" t="b">
         <v>1</v>
@@ -14953,7 +14977,7 @@
     </row>
     <row r="143" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B143" s="7">
         <v>21</v>
@@ -14966,13 +14990,13 @@
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I143" s="23">
         <v>-24.61</v>
@@ -14981,7 +15005,7 @@
         <v>176.91</v>
       </c>
       <c r="K143" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L143" s="3" t="b">
         <v>1</v>
@@ -14991,7 +15015,7 @@
     </row>
     <row r="144" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B144" s="7">
         <v>21</v>
@@ -15004,13 +15028,13 @@
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I144" s="24">
         <v>-11.7</v>
@@ -15019,7 +15043,7 @@
         <v>-3.78</v>
       </c>
       <c r="K144" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L144" s="3" t="b">
         <v>1</v>
@@ -15029,7 +15053,7 @@
     </row>
     <row r="145" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B145" s="7">
         <v>21</v>
@@ -15041,14 +15065,14 @@
         <v>137</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I145" s="23">
         <v>-0.74</v>
@@ -15057,7 +15081,7 @@
         <v>112.77</v>
       </c>
       <c r="K145" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L145" s="3" t="b">
         <v>1</v>
@@ -15067,7 +15091,7 @@
     </row>
     <row r="146" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B146" s="7">
         <v>21</v>
@@ -15079,14 +15103,14 @@
         <v>137</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G146" s="3"/>
       <c r="H146" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I146" s="24">
         <v>10.43</v>
@@ -15095,7 +15119,7 @@
         <v>170.31</v>
       </c>
       <c r="K146" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L146" s="3" t="b">
         <v>1</v>
@@ -15105,7 +15129,7 @@
     </row>
     <row r="147" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B147" s="7">
         <v>21</v>
@@ -15117,14 +15141,14 @@
         <v>137</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G147" s="3"/>
       <c r="H147" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I147" s="23">
         <v>26.8</v>
@@ -15133,7 +15157,7 @@
         <v>-136.21</v>
       </c>
       <c r="K147" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L147" s="3" t="b">
         <v>1</v>
@@ -15143,7 +15167,7 @@
     </row>
     <row r="148" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B148" s="7">
         <v>21</v>
@@ -15155,14 +15179,14 @@
         <v>137</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I148" s="24">
         <v>65.44</v>
@@ -15171,7 +15195,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K148" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L148" s="3" t="b">
         <v>1</v>
@@ -15181,7 +15205,7 @@
     </row>
     <row r="149" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B149" s="7">
         <v>21</v>
@@ -15193,14 +15217,14 @@
         <v>137</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I149" s="25">
         <v>58.71</v>
@@ -15209,7 +15233,7 @@
         <v>-1.51</v>
       </c>
       <c r="K149" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L149" s="3" t="b">
         <v>1</v>
@@ -15219,7 +15243,7 @@
     </row>
     <row r="150" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B150" s="7">
         <v>22</v>
@@ -15232,13 +15256,13 @@
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I150" s="23">
         <v>-24.61</v>
@@ -15247,7 +15271,7 @@
         <v>176.91</v>
       </c>
       <c r="K150" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L150" s="3" t="b">
         <v>1</v>
@@ -15257,7 +15281,7 @@
     </row>
     <row r="151" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B151" s="7">
         <v>22</v>
@@ -15270,13 +15294,13 @@
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I151" s="24">
         <v>-11.7</v>
@@ -15285,7 +15309,7 @@
         <v>-3.78</v>
       </c>
       <c r="K151" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L151" s="3" t="b">
         <v>1</v>
@@ -15295,7 +15319,7 @@
     </row>
     <row r="152" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B152" s="7">
         <v>22</v>
@@ -15307,14 +15331,14 @@
         <v>141</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G152" s="3"/>
       <c r="H152" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I152" s="23">
         <v>-0.74</v>
@@ -15323,7 +15347,7 @@
         <v>112.77</v>
       </c>
       <c r="K152" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L152" s="3" t="b">
         <v>1</v>
@@ -15333,7 +15357,7 @@
     </row>
     <row r="153" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B153" s="7">
         <v>22</v>
@@ -15345,14 +15369,14 @@
         <v>141</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G153" s="3"/>
       <c r="H153" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I153" s="24">
         <v>10.43</v>
@@ -15361,7 +15385,7 @@
         <v>170.31</v>
       </c>
       <c r="K153" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L153" s="3" t="b">
         <v>1</v>
@@ -15371,7 +15395,7 @@
     </row>
     <row r="154" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B154" s="7">
         <v>22</v>
@@ -15383,14 +15407,14 @@
         <v>141</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G154" s="3"/>
       <c r="H154" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I154" s="23">
         <v>26.8</v>
@@ -15399,7 +15423,7 @@
         <v>-136.21</v>
       </c>
       <c r="K154" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L154" s="3" t="b">
         <v>1</v>
@@ -15409,7 +15433,7 @@
     </row>
     <row r="155" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B155" s="7">
         <v>22</v>
@@ -15421,14 +15445,14 @@
         <v>141</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G155" s="3"/>
       <c r="H155" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I155" s="24">
         <v>65.44</v>
@@ -15437,7 +15461,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K155" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L155" s="3" t="b">
         <v>1</v>
@@ -15447,7 +15471,7 @@
     </row>
     <row r="156" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B156" s="7">
         <v>22</v>
@@ -15459,14 +15483,14 @@
         <v>141</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G156" s="3"/>
       <c r="H156" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I156" s="25">
         <v>58.71</v>
@@ -15475,7 +15499,7 @@
         <v>-1.51</v>
       </c>
       <c r="K156" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L156" s="3" t="b">
         <v>1</v>
@@ -15485,7 +15509,7 @@
     </row>
     <row r="157" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B157" s="7">
         <v>23</v>
@@ -15498,13 +15522,13 @@
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H157" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I157" s="23">
         <v>-24.61</v>
@@ -15513,7 +15537,7 @@
         <v>176.91</v>
       </c>
       <c r="K157" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L157" s="3" t="b">
         <v>1</v>
@@ -15523,7 +15547,7 @@
     </row>
     <row r="158" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B158" s="7">
         <v>23</v>
@@ -15536,13 +15560,13 @@
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H158" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I158" s="24">
         <v>-11.7</v>
@@ -15551,7 +15575,7 @@
         <v>-3.78</v>
       </c>
       <c r="K158" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L158" s="3" t="b">
         <v>1</v>
@@ -15561,7 +15585,7 @@
     </row>
     <row r="159" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B159" s="7">
         <v>23</v>
@@ -15573,14 +15597,14 @@
         <v>146</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G159" s="3"/>
       <c r="H159" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I159" s="23">
         <v>-0.74</v>
@@ -15589,7 +15613,7 @@
         <v>112.77</v>
       </c>
       <c r="K159" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L159" s="3" t="b">
         <v>1</v>
@@ -15599,7 +15623,7 @@
     </row>
     <row r="160" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B160" s="7">
         <v>23</v>
@@ -15611,14 +15635,14 @@
         <v>146</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G160" s="3"/>
       <c r="H160" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I160" s="24">
         <v>10.43</v>
@@ -15627,7 +15651,7 @@
         <v>170.31</v>
       </c>
       <c r="K160" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L160" s="3" t="b">
         <v>1</v>
@@ -15637,7 +15661,7 @@
     </row>
     <row r="161" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B161" s="7">
         <v>23</v>
@@ -15649,14 +15673,14 @@
         <v>146</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G161" s="3"/>
       <c r="H161" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I161" s="23">
         <v>26.8</v>
@@ -15665,7 +15689,7 @@
         <v>-136.21</v>
       </c>
       <c r="K161" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L161" s="3" t="b">
         <v>1</v>
@@ -15675,7 +15699,7 @@
     </row>
     <row r="162" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B162" s="7">
         <v>23</v>
@@ -15687,14 +15711,14 @@
         <v>146</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G162" s="3"/>
       <c r="H162" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I162" s="24">
         <v>65.44</v>
@@ -15703,7 +15727,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K162" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L162" s="3" t="b">
         <v>1</v>
@@ -15713,7 +15737,7 @@
     </row>
     <row r="163" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B163" s="7">
         <v>23</v>
@@ -15725,14 +15749,14 @@
         <v>146</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G163" s="3"/>
       <c r="H163" s="25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I163" s="25">
         <v>58.71</v>
@@ -15741,7 +15765,7 @@
         <v>-1.51</v>
       </c>
       <c r="K163" s="25" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L163" s="3" t="b">
         <v>1</v>
@@ -15751,26 +15775,26 @@
     </row>
     <row r="164" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B164" s="7">
         <v>24</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H164" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I164" s="23">
         <v>-24.61</v>
@@ -15779,7 +15803,7 @@
         <v>176.91</v>
       </c>
       <c r="K164" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L164" s="3" t="b">
         <v>1</v>
@@ -15789,26 +15813,26 @@
     </row>
     <row r="165" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B165" s="7">
         <v>24</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H165" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I165" s="24">
         <v>-11.7</v>
@@ -15817,7 +15841,7 @@
         <v>-3.78</v>
       </c>
       <c r="K165" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L165" s="3" t="b">
         <v>1</v>
@@ -15827,26 +15851,26 @@
     </row>
     <row r="166" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B166" s="7">
         <v>24</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G166" s="3"/>
       <c r="H166" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I166" s="23">
         <v>-0.74</v>
@@ -15855,7 +15879,7 @@
         <v>112.77</v>
       </c>
       <c r="K166" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L166" s="3" t="b">
         <v>1</v>
@@ -15865,26 +15889,26 @@
     </row>
     <row r="167" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B167" s="7">
         <v>24</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G167" s="3"/>
       <c r="H167" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I167" s="24">
         <v>10.43</v>
@@ -15893,7 +15917,7 @@
         <v>170.31</v>
       </c>
       <c r="K167" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L167" s="3" t="b">
         <v>1</v>
@@ -15903,26 +15927,26 @@
     </row>
     <row r="168" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B168" s="7">
         <v>24</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G168" s="3"/>
       <c r="H168" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I168" s="23">
         <v>26.8</v>
@@ -15931,7 +15955,7 @@
         <v>-136.21</v>
       </c>
       <c r="K168" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L168" s="3" t="b">
         <v>1</v>
@@ -15941,26 +15965,26 @@
     </row>
     <row r="169" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B169" s="7">
         <v>24</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G169" s="3"/>
       <c r="H169" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I169" s="24">
         <v>65.44</v>
@@ -15969,7 +15993,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K169" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L169" s="3" t="b">
         <v>1</v>
@@ -15979,26 +16003,26 @@
     </row>
     <row r="170" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B170" s="7">
         <v>24</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G170" s="3"/>
       <c r="H170" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I170" s="25">
         <v>58.71</v>
@@ -16007,7 +16031,7 @@
         <v>-1.51</v>
       </c>
       <c r="K170" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L170" s="3" t="b">
         <v>1</v>
@@ -16017,26 +16041,26 @@
     </row>
     <row r="171" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B171" s="7">
         <v>25</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E171" s="3"/>
       <c r="F171" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I171" s="23">
         <v>-24.61</v>
@@ -16045,7 +16069,7 @@
         <v>176.91</v>
       </c>
       <c r="K171" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L171" s="3" t="b">
         <v>1</v>
@@ -16055,26 +16079,26 @@
     </row>
     <row r="172" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B172" s="7">
         <v>25</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I172" s="24">
         <v>-11.7</v>
@@ -16083,7 +16107,7 @@
         <v>-3.78</v>
       </c>
       <c r="K172" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L172" s="3" t="b">
         <v>1</v>
@@ -16093,26 +16117,26 @@
     </row>
     <row r="173" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B173" s="7">
         <v>25</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G173" s="3"/>
       <c r="H173" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I173" s="23">
         <v>-0.74</v>
@@ -16121,7 +16145,7 @@
         <v>112.77</v>
       </c>
       <c r="K173" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L173" s="3" t="b">
         <v>1</v>
@@ -16131,26 +16155,26 @@
     </row>
     <row r="174" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B174" s="7">
         <v>25</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G174" s="3"/>
       <c r="H174" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I174" s="24">
         <v>10.43</v>
@@ -16159,7 +16183,7 @@
         <v>170.31</v>
       </c>
       <c r="K174" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L174" s="3" t="b">
         <v>1</v>
@@ -16169,26 +16193,26 @@
     </row>
     <row r="175" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B175" s="7">
         <v>25</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G175" s="3"/>
       <c r="H175" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I175" s="23">
         <v>26.8</v>
@@ -16197,7 +16221,7 @@
         <v>-136.21</v>
       </c>
       <c r="K175" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L175" s="3" t="b">
         <v>1</v>
@@ -16207,26 +16231,26 @@
     </row>
     <row r="176" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B176" s="7">
         <v>25</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G176" s="3"/>
       <c r="H176" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I176" s="24">
         <v>65.44</v>
@@ -16235,7 +16259,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K176" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L176" s="3" t="b">
         <v>1</v>
@@ -16245,26 +16269,26 @@
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B177" s="7">
         <v>25</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G177" s="3"/>
       <c r="H177" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I177" s="25">
         <v>58.71</v>
@@ -16273,7 +16297,7 @@
         <v>-1.51</v>
       </c>
       <c r="K177" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L177" s="3" t="b">
         <v>1</v>
@@ -16283,26 +16307,26 @@
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B178" s="7">
         <v>25</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E178" s="3"/>
       <c r="F178" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I178" s="23">
         <v>-24.61</v>
@@ -16311,7 +16335,7 @@
         <v>176.91</v>
       </c>
       <c r="K178" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L178" s="3" t="b">
         <v>1</v>
@@ -16321,26 +16345,26 @@
     </row>
     <row r="179" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B179" s="7">
         <v>26</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E179" s="3"/>
       <c r="F179" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I179" s="24">
         <v>-11.7</v>
@@ -16349,7 +16373,7 @@
         <v>-3.78</v>
       </c>
       <c r="K179" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L179" s="3" t="b">
         <v>1</v>
@@ -16359,26 +16383,26 @@
     </row>
     <row r="180" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B180" s="7">
         <v>26</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G180" s="3"/>
       <c r="H180" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I180" s="23">
         <v>-0.74</v>
@@ -16387,7 +16411,7 @@
         <v>112.77</v>
       </c>
       <c r="K180" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L180" s="3" t="b">
         <v>1</v>
@@ -16397,26 +16421,26 @@
     </row>
     <row r="181" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B181" s="7">
         <v>26</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G181" s="3"/>
       <c r="H181" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I181" s="24">
         <v>10.43</v>
@@ -16425,7 +16449,7 @@
         <v>170.31</v>
       </c>
       <c r="K181" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L181" s="3" t="b">
         <v>1</v>
@@ -16435,26 +16459,26 @@
     </row>
     <row r="182" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B182" s="7">
         <v>26</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G182" s="3"/>
       <c r="H182" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I182" s="23">
         <v>26.8</v>
@@ -16463,7 +16487,7 @@
         <v>-136.21</v>
       </c>
       <c r="K182" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L182" s="3" t="b">
         <v>1</v>
@@ -16473,26 +16497,26 @@
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B183" s="7">
         <v>26</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G183" s="3"/>
       <c r="H183" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I183" s="24">
         <v>65.44</v>
@@ -16501,7 +16525,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K183" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L183" s="3" t="b">
         <v>1</v>
@@ -16511,26 +16535,26 @@
     </row>
     <row r="184" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B184" s="7">
         <v>26</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G184" s="3"/>
       <c r="H184" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I184" s="25">
         <v>58.71</v>
@@ -16539,7 +16563,7 @@
         <v>-1.51</v>
       </c>
       <c r="K184" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L184" s="3" t="b">
         <v>1</v>
@@ -16549,26 +16573,26 @@
     </row>
     <row r="185" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B185" s="7">
         <v>26</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E185" s="3"/>
       <c r="F185" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H185" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I185" s="23">
         <v>-24.61</v>
@@ -16577,7 +16601,7 @@
         <v>176.91</v>
       </c>
       <c r="K185" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L185" s="3" t="b">
         <v>1</v>
@@ -16587,26 +16611,26 @@
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B186" s="7">
         <v>27</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E186" s="3"/>
       <c r="F186" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H186" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I186" s="24">
         <v>-11.7</v>
@@ -16615,7 +16639,7 @@
         <v>-3.78</v>
       </c>
       <c r="K186" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L186" s="3" t="b">
         <v>1</v>
@@ -16625,26 +16649,26 @@
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B187" s="7">
         <v>27</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G187" s="3"/>
       <c r="H187" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I187" s="23">
         <v>-0.74</v>
@@ -16653,7 +16677,7 @@
         <v>112.77</v>
       </c>
       <c r="K187" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L187" s="3" t="b">
         <v>1</v>
@@ -16663,26 +16687,26 @@
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B188" s="7">
         <v>27</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G188" s="3"/>
       <c r="H188" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I188" s="24">
         <v>10.43</v>
@@ -16691,7 +16715,7 @@
         <v>170.31</v>
       </c>
       <c r="K188" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L188" s="3" t="b">
         <v>1</v>
@@ -16701,26 +16725,26 @@
     </row>
     <row r="189" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B189" s="7">
         <v>27</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G189" s="3"/>
       <c r="H189" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I189" s="23">
         <v>26.8</v>
@@ -16729,7 +16753,7 @@
         <v>-136.21</v>
       </c>
       <c r="K189" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L189" s="3" t="b">
         <v>1</v>
@@ -16739,26 +16763,26 @@
     </row>
     <row r="190" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B190" s="7">
         <v>27</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G190" s="3"/>
       <c r="H190" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I190" s="24">
         <v>65.44</v>
@@ -16767,7 +16791,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K190" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L190" s="3" t="b">
         <v>1</v>
@@ -16777,26 +16801,26 @@
     </row>
     <row r="191" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B191" s="7">
         <v>27</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G191" s="3"/>
       <c r="H191" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I191" s="25">
         <v>58.71</v>
@@ -16805,7 +16829,7 @@
         <v>-1.51</v>
       </c>
       <c r="K191" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L191" s="3" t="b">
         <v>1</v>
@@ -16815,26 +16839,26 @@
     </row>
     <row r="192" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B192" s="7">
         <v>27</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E192" s="3"/>
       <c r="F192" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H192" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I192" s="23">
         <v>-24.61</v>
@@ -16843,7 +16867,7 @@
         <v>176.91</v>
       </c>
       <c r="K192" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L192" s="3" t="b">
         <v>1</v>
@@ -16853,26 +16877,26 @@
     </row>
     <row r="193" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B193" s="7">
         <v>28</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E193" s="3"/>
       <c r="F193" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H193" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I193" s="24">
         <v>-11.7</v>
@@ -16881,7 +16905,7 @@
         <v>-3.78</v>
       </c>
       <c r="K193" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L193" s="3" t="b">
         <v>1</v>
@@ -16891,26 +16915,26 @@
     </row>
     <row r="194" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B194" s="7">
         <v>28</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G194" s="3"/>
       <c r="H194" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I194" s="23">
         <v>-0.74</v>
@@ -16919,7 +16943,7 @@
         <v>112.77</v>
       </c>
       <c r="K194" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L194" s="3" t="b">
         <v>1</v>
@@ -16929,26 +16953,26 @@
     </row>
     <row r="195" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B195" s="7">
         <v>28</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G195" s="3"/>
       <c r="H195" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I195" s="24">
         <v>10.43</v>
@@ -16957,7 +16981,7 @@
         <v>170.31</v>
       </c>
       <c r="K195" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L195" s="3" t="b">
         <v>1</v>
@@ -16967,26 +16991,26 @@
     </row>
     <row r="196" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B196" s="7">
         <v>28</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G196" s="3"/>
       <c r="H196" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I196" s="23">
         <v>26.8</v>
@@ -16995,7 +17019,7 @@
         <v>-136.21</v>
       </c>
       <c r="K196" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L196" s="3" t="b">
         <v>1</v>
@@ -17005,26 +17029,26 @@
     </row>
     <row r="197" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B197" s="7">
         <v>28</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G197" s="3"/>
       <c r="H197" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I197" s="24">
         <v>65.44</v>
@@ -17033,7 +17057,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K197" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L197" s="3" t="b">
         <v>1</v>
@@ -17043,26 +17067,26 @@
     </row>
     <row r="198" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B198" s="7">
         <v>28</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I198" s="25">
         <v>58.71</v>
@@ -17071,7 +17095,7 @@
         <v>-1.51</v>
       </c>
       <c r="K198" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L198" s="3" t="b">
         <v>1</v>
@@ -17081,26 +17105,26 @@
     </row>
     <row r="199" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B199" s="7">
         <v>28</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E199" s="3"/>
       <c r="F199" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I199" s="23">
         <v>-24.61</v>
@@ -17109,7 +17133,7 @@
         <v>176.91</v>
       </c>
       <c r="K199" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L199" s="3" t="b">
         <v>1</v>
@@ -17119,26 +17143,26 @@
     </row>
     <row r="200" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B200" s="7">
         <v>29</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E200" s="3"/>
       <c r="F200" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I200" s="24">
         <v>-11.7</v>
@@ -17147,7 +17171,7 @@
         <v>-3.78</v>
       </c>
       <c r="K200" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L200" s="3" t="b">
         <v>1</v>
@@ -17157,26 +17181,26 @@
     </row>
     <row r="201" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B201" s="7">
         <v>29</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G201" s="3"/>
       <c r="H201" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I201" s="23">
         <v>-0.74</v>
@@ -17185,7 +17209,7 @@
         <v>112.77</v>
       </c>
       <c r="K201" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L201" s="3" t="b">
         <v>1</v>
@@ -17195,26 +17219,26 @@
     </row>
     <row r="202" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B202" s="7">
         <v>29</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G202" s="3"/>
       <c r="H202" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I202" s="24">
         <v>10.43</v>
@@ -17223,7 +17247,7 @@
         <v>170.31</v>
       </c>
       <c r="K202" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L202" s="3" t="b">
         <v>1</v>
@@ -17233,26 +17257,26 @@
     </row>
     <row r="203" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B203" s="7">
         <v>29</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E203" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G203" s="3"/>
       <c r="H203" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I203" s="23">
         <v>26.8</v>
@@ -17261,7 +17285,7 @@
         <v>-136.21</v>
       </c>
       <c r="K203" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L203" s="3" t="b">
         <v>1</v>
@@ -17270,26 +17294,26 @@
     </row>
     <row r="204" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B204" s="7">
         <v>29</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E204" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G204" s="3"/>
       <c r="H204" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I204" s="24">
         <v>65.44</v>
@@ -17298,7 +17322,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K204" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L204" s="3" t="b">
         <v>1</v>
@@ -17307,26 +17331,26 @@
     </row>
     <row r="205" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B205" s="7">
         <v>29</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E205" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I205" s="25">
         <v>58.71</v>
@@ -17335,7 +17359,7 @@
         <v>-1.51</v>
       </c>
       <c r="K205" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L205" s="3" t="b">
         <v>1</v>
@@ -17344,25 +17368,25 @@
     </row>
     <row r="206" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B206" s="7">
         <v>29</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I206" s="23">
         <v>-24.61</v>
@@ -17371,7 +17395,7 @@
         <v>176.91</v>
       </c>
       <c r="K206" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L206" s="3" t="b">
         <v>1</v>
@@ -17380,25 +17404,25 @@
     </row>
     <row r="207" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B207" s="7">
         <v>30</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I207" s="24">
         <v>-11.7</v>
@@ -17407,7 +17431,7 @@
         <v>-3.78</v>
       </c>
       <c r="K207" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L207" s="3" t="b">
         <v>1</v>
@@ -17416,26 +17440,26 @@
     </row>
     <row r="208" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B208" s="7">
         <v>30</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E208" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G208" s="3"/>
       <c r="H208" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I208" s="23">
         <v>-0.74</v>
@@ -17444,7 +17468,7 @@
         <v>112.77</v>
       </c>
       <c r="K208" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L208" s="3" t="b">
         <v>1</v>
@@ -17453,26 +17477,26 @@
     </row>
     <row r="209" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B209" s="7">
         <v>30</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E209" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G209" s="3"/>
       <c r="H209" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I209" s="24">
         <v>10.43</v>
@@ -17481,7 +17505,7 @@
         <v>170.31</v>
       </c>
       <c r="K209" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L209" s="3" t="b">
         <v>1</v>
@@ -17490,26 +17514,26 @@
     </row>
     <row r="210" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B210" s="7">
         <v>30</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E210" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G210" s="3"/>
       <c r="H210" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I210" s="23">
         <v>26.8</v>
@@ -17518,7 +17542,7 @@
         <v>-136.21</v>
       </c>
       <c r="K210" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L210" s="3" t="b">
         <v>1</v>
@@ -17527,26 +17551,26 @@
     </row>
     <row r="211" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B211" s="7">
         <v>30</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E211" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G211" s="3"/>
       <c r="H211" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I211" s="24">
         <v>65.44</v>
@@ -17555,7 +17579,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K211" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L211" s="3" t="b">
         <v>1</v>
@@ -17564,26 +17588,26 @@
     </row>
     <row r="212" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B212" s="7">
         <v>30</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E212" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G212" s="3"/>
       <c r="H212" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I212" s="25">
         <v>58.71</v>
@@ -17592,7 +17616,7 @@
         <v>-1.51</v>
       </c>
       <c r="K212" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L212" s="3" t="b">
         <v>1</v>
@@ -17601,25 +17625,25 @@
     </row>
     <row r="213" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B213" s="7">
         <v>30</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H213" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I213" s="23">
         <v>-24.61</v>
@@ -17628,7 +17652,7 @@
         <v>176.91</v>
       </c>
       <c r="K213" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L213" s="3" t="b">
         <v>1</v>
@@ -17637,25 +17661,25 @@
     </row>
     <row r="214" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B214" s="7">
         <v>31</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H214" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I214" s="24">
         <v>-11.7</v>
@@ -17664,7 +17688,7 @@
         <v>-3.78</v>
       </c>
       <c r="K214" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L214" s="3" t="b">
         <v>1</v>
@@ -17673,26 +17697,26 @@
     </row>
     <row r="215" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B215" s="7">
         <v>31</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E215" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G215" s="3"/>
       <c r="H215" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I215" s="23">
         <v>-0.74</v>
@@ -17701,7 +17725,7 @@
         <v>112.77</v>
       </c>
       <c r="K215" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L215" s="3" t="b">
         <v>1</v>
@@ -17710,26 +17734,26 @@
     </row>
     <row r="216" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B216" s="7">
         <v>31</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E216" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I216" s="24">
         <v>10.43</v>
@@ -17738,7 +17762,7 @@
         <v>170.31</v>
       </c>
       <c r="K216" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L216" s="3" t="b">
         <v>1</v>
@@ -17747,26 +17771,26 @@
     </row>
     <row r="217" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B217" s="7">
         <v>31</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E217" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G217" s="3"/>
       <c r="H217" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I217" s="23">
         <v>26.8</v>
@@ -17775,7 +17799,7 @@
         <v>-136.21</v>
       </c>
       <c r="K217" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L217" s="3" t="b">
         <v>1</v>
@@ -17784,26 +17808,26 @@
     </row>
     <row r="218" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B218" s="7">
         <v>31</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E218" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G218" s="3"/>
       <c r="H218" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I218" s="24">
         <v>65.44</v>
@@ -17812,7 +17836,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K218" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L218" s="3" t="b">
         <v>1</v>
@@ -17821,26 +17845,26 @@
     </row>
     <row r="219" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B219" s="7">
         <v>31</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E219" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G219" s="3"/>
       <c r="H219" s="25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I219" s="25">
         <v>58.71</v>
@@ -17849,7 +17873,7 @@
         <v>-1.51</v>
       </c>
       <c r="K219" s="25" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L219" s="3" t="b">
         <v>1</v>
@@ -17858,25 +17882,25 @@
     </row>
     <row r="220" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B220" s="7">
         <v>31</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H220" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I220" s="23">
         <v>-24.61</v>
@@ -17885,7 +17909,7 @@
         <v>176.91</v>
       </c>
       <c r="K220" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L220" s="3" t="b">
         <v>1</v>
@@ -17894,25 +17918,25 @@
     </row>
     <row r="221" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B221" s="7">
         <v>32</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H221" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I221" s="24">
         <v>-11.7</v>
@@ -17921,7 +17945,7 @@
         <v>-3.78</v>
       </c>
       <c r="K221" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L221" s="3" t="b">
         <v>1</v>
@@ -17930,26 +17954,26 @@
     </row>
     <row r="222" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B222" s="7">
         <v>32</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E222" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G222" s="3"/>
       <c r="H222" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I222" s="23">
         <v>-0.74</v>
@@ -17958,7 +17982,7 @@
         <v>112.77</v>
       </c>
       <c r="K222" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L222" s="3" t="b">
         <v>1</v>
@@ -17967,26 +17991,26 @@
     </row>
     <row r="223" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B223" s="7">
         <v>32</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E223" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G223" s="3"/>
       <c r="H223" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I223" s="24">
         <v>10.43</v>
@@ -17995,7 +18019,7 @@
         <v>170.31</v>
       </c>
       <c r="K223" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L223" s="3" t="b">
         <v>1</v>
@@ -18004,26 +18028,26 @@
     </row>
     <row r="224" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B224" s="7">
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E224" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G224" s="3"/>
       <c r="H224" s="23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I224" s="23">
         <v>26.8</v>
@@ -18032,7 +18056,7 @@
         <v>-136.21</v>
       </c>
       <c r="K224" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L224" s="3" t="b">
         <v>1</v>
@@ -18041,26 +18065,26 @@
     </row>
     <row r="225" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B225" s="7">
         <v>32</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E225" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G225" s="3"/>
       <c r="H225" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I225" s="24">
         <v>65.44</v>
@@ -18069,7 +18093,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K225" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L225" s="3" t="b">
         <v>1</v>
@@ -18078,26 +18102,26 @@
     </row>
     <row r="226" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B226" s="7">
         <v>32</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E226" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G226" s="3"/>
       <c r="H226" s="25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I226" s="25">
         <v>58.71</v>
@@ -18106,7 +18130,7 @@
         <v>-1.51</v>
       </c>
       <c r="K226" s="25" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L226" s="3" t="b">
         <v>1</v>
@@ -20872,7 +20896,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.2" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B1" s="40" t="s">
         <v>149</v>
@@ -20902,7 +20926,7 @@
         <v>163</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20910,34 +20934,34 @@
         <v>4</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H2" s="42">
         <v>18</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20945,22 +20969,22 @@
         <v>5</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D3" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" s="41" t="s">
         <v>179</v>
       </c>
-      <c r="E3" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>176</v>
-      </c>
       <c r="G3" s="41" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H3" s="41">
         <v>22.5</v>
@@ -20969,10 +20993,10 @@
         <v>33</v>
       </c>
       <c r="J3" s="41" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K3" s="59" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20980,22 +21004,22 @@
         <v>6</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H4" s="42">
         <v>32.799999999999997</v>
@@ -21004,10 +21028,10 @@
         <v>33</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K4" s="59" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21015,20 +21039,20 @@
         <v>7</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="41" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G5" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H5" s="41">
         <v>40</v>
@@ -21040,7 +21064,7 @@
         <v>49</v>
       </c>
       <c r="K5" s="59" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21048,22 +21072,22 @@
         <v>8</v>
       </c>
       <c r="B6" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>293</v>
-      </c>
       <c r="D6" s="45" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H6" s="42">
         <v>100</v>
@@ -21072,10 +21096,10 @@
         <v>33</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21083,22 +21107,22 @@
         <v>11</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H7" s="41">
         <v>18</v>
@@ -21110,7 +21134,7 @@
         <v>49</v>
       </c>
       <c r="K7" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21118,22 +21142,22 @@
         <v>12</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H8" s="42">
         <v>15.82</v>
@@ -21142,10 +21166,10 @@
         <v>33</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21153,20 +21177,20 @@
         <v>13</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="41" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H9" s="41">
         <v>45.65</v>
@@ -21175,10 +21199,10 @@
         <v>33</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K9" s="59" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21186,20 +21210,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="42" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H10" s="42">
         <v>40</v>
@@ -21208,10 +21232,10 @@
         <v>33</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21219,20 +21243,20 @@
         <v>15</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="41" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H11" s="41">
         <v>100</v>
@@ -21241,10 +21265,10 @@
         <v>33</v>
       </c>
       <c r="J11" s="41" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K11" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21252,18 +21276,18 @@
         <v>18</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="45"/>
       <c r="E12" s="52" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H12" s="52">
         <v>18</v>
@@ -21272,10 +21296,10 @@
         <v>33</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21283,18 +21307,18 @@
         <v>19</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="49"/>
       <c r="E13" s="52" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G13" s="41" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H13" s="52">
         <v>22</v>
@@ -21303,10 +21327,10 @@
         <v>33</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K13" s="59" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21314,18 +21338,18 @@
         <v>20</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="45"/>
       <c r="E14" s="52" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H14" s="52">
         <v>32</v>
@@ -21334,10 +21358,10 @@
         <v>33</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21345,18 +21369,18 @@
         <v>21</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="49"/>
       <c r="E15" s="52" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H15" s="52">
         <v>40</v>
@@ -21365,10 +21389,10 @@
         <v>33</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K15" s="59" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21376,20 +21400,20 @@
         <v>22</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D16" s="45"/>
       <c r="E16" s="52" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F16" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H16" s="52">
         <v>100</v>
@@ -21398,10 +21422,10 @@
         <v>33</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K16" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21409,20 +21433,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H17" s="52">
         <v>18</v>
@@ -21431,10 +21455,10 @@
         <v>33</v>
       </c>
       <c r="J17" s="53" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K17" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21442,20 +21466,20 @@
         <v>26</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="45" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E18" s="55" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G18" s="42" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H18" s="52">
         <v>22</v>
@@ -21464,10 +21488,10 @@
         <v>33</v>
       </c>
       <c r="J18" s="53" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K18" s="59" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21475,18 +21499,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="49"/>
       <c r="E19" s="52" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H19" s="52">
         <v>32</v>
@@ -21495,10 +21519,10 @@
         <v>33</v>
       </c>
       <c r="J19" s="53" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K19" s="59" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21506,20 +21530,20 @@
         <v>28</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D20" s="45"/>
       <c r="E20" s="57" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H20" s="58">
         <v>40</v>
@@ -21528,10 +21552,10 @@
         <v>33</v>
       </c>
       <c r="J20" s="27" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K20" s="59" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21539,22 +21563,22 @@
         <v>29</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H21" s="52">
         <v>100</v>
@@ -21563,10 +21587,10 @@
         <v>33</v>
       </c>
       <c r="J21" s="53" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K21" s="59" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -21639,16 +21663,16 @@
         <v>148</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F1" s="30"/>
     </row>
@@ -21660,7 +21684,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D2" s="31">
         <v>1</v>
@@ -21672,13 +21696,13 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="31" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>103</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D3" s="31">
         <v>2</v>
@@ -22720,10 +22744,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="29" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
@@ -22732,10 +22756,10 @@
     </row>
     <row r="2" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -22744,10 +22768,10 @@
     </row>
     <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
@@ -22756,10 +22780,10 @@
     </row>
     <row r="4" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="31" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4417440-3DDA-42DE-9899-8E53FE343FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B0BBF6-45A9-49E0-9321-145912F9B112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="338">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -585,9 +585,6 @@
     <t>GF</t>
   </si>
   <si>
-    <t>HS1 1</t>
-  </si>
-  <si>
     <t>navigation</t>
   </si>
   <si>
@@ -600,15 +597,9 @@
     <t>45°</t>
   </si>
   <si>
-    <t>HS1 2</t>
-  </si>
-  <si>
     <t>Previous</t>
   </si>
   <si>
-    <t>HS1 3</t>
-  </si>
-  <si>
     <t>info</t>
   </si>
   <si>
@@ -633,9 +624,6 @@
     <t>"Hey, Check this our new premium collections of the Safas"</t>
   </si>
   <si>
-    <t>HS1 4</t>
-  </si>
-  <si>
     <t>[https://images.homedepot-static.com/lifestyleimages/1024x682/85912049-ef4c-4208-94ba-7c4776a420290.jpeg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-3.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-5.jpg]</t>
   </si>
   <si>
@@ -648,9 +636,6 @@
     <t>"Hey, Check this our new premium collections of the Tables"</t>
   </si>
   <si>
-    <t>HS1 5</t>
-  </si>
-  <si>
     <t>[https://www.ikea.com/us/en/home-design/images/graphics/dashboard/try-product-together.png],[https://cdn.apartmenttherapy.info/image/upload/v1554217999/at/house%20tours%20stock%20archive/7f6d6749cdc500dd3a8c93d2e1c6ad6aa7be7dec.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-1.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-2.jpg],[https://contentgrid.homedepot-static.com/hdus/en_US/DTCCOMNEW/Articles/best-furniture-for-your-home-2022-section-3.jpg]</t>
   </si>
   <si>
@@ -660,13 +645,7 @@
     <t>"Hey, Check this our new premium collections of the Beds"</t>
   </si>
   <si>
-    <t>HS1 6</t>
-  </si>
-  <si>
     <t>Premium Chairs</t>
-  </si>
-  <si>
-    <t>HS1 7</t>
   </si>
   <si>
     <t>https://www.ikea.com/sa/en/images/products/soederhamn-corner-sofa-4-seat-with-open-end-tonerud-grey__1057823_pe849006_s5.jpg</t>
@@ -1002,9 +981,6 @@
   </si>
   <si>
     <t>SL#</t>
-  </si>
-  <si>
-    <t>HS1 8</t>
   </si>
   <si>
     <t>HS1-01</t>
@@ -2094,13 +2070,13 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2120,7 +2096,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>30</v>
@@ -2135,7 +2111,7 @@
         <v>32</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>34</v>
@@ -2171,7 +2147,7 @@
         <v>36</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="X2" s="10" t="b">
         <v>1</v>
@@ -2180,13 +2156,13 @@
         <v>1</v>
       </c>
       <c r="Z2" s="37" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
       </c>
       <c r="AB2" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2206,7 +2182,7 @@
         <v>38</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>30</v>
@@ -2266,13 +2242,13 @@
         <v>1</v>
       </c>
       <c r="Z3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
       </c>
       <c r="AB3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2292,7 +2268,7 @@
         <v>43</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>30</v>
@@ -2353,7 +2329,7 @@
         <v>45750</v>
       </c>
       <c r="AB4" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2373,7 +2349,7 @@
         <v>48</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>30</v>
@@ -2449,10 +2425,10 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>30</v>
@@ -2514,7 +2490,7 @@
         <v>45750</v>
       </c>
       <c r="AB6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2534,7 +2510,7 @@
         <v>57</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -2596,7 +2572,7 @@
         <v>45750</v>
       </c>
       <c r="AB7" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2616,7 +2592,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>30</v>
@@ -2680,7 +2656,7 @@
         <v>45750</v>
       </c>
       <c r="AB8" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2700,7 +2676,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>30</v>
@@ -2764,7 +2740,7 @@
         <v>45750</v>
       </c>
       <c r="AB9" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2784,7 +2760,7 @@
         <v>77</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>30</v>
@@ -2848,7 +2824,7 @@
         <v>45750</v>
       </c>
       <c r="AB10" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2868,7 +2844,7 @@
         <v>82</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>30</v>
@@ -2930,7 +2906,7 @@
         <v>45750</v>
       </c>
       <c r="AB11" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2950,7 +2926,7 @@
         <v>86</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>30</v>
@@ -3014,7 +2990,7 @@
         <v>45750</v>
       </c>
       <c r="AB12" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3034,7 +3010,7 @@
         <v>92</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>30</v>
@@ -3098,7 +3074,7 @@
         <v>45750</v>
       </c>
       <c r="AB13" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3118,7 +3094,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>30</v>
@@ -3182,7 +3158,7 @@
         <v>45750</v>
       </c>
       <c r="AB14" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3202,7 +3178,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>30</v>
@@ -3266,7 +3242,7 @@
         <v>45750</v>
       </c>
       <c r="AB15" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3286,7 +3262,7 @@
         <v>105</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>30</v>
@@ -3350,7 +3326,7 @@
         <v>45750</v>
       </c>
       <c r="AB16" s="38" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3370,7 +3346,7 @@
         <v>110</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>30</v>
@@ -3434,7 +3410,7 @@
         <v>45750</v>
       </c>
       <c r="AB17" s="38" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3454,7 +3430,7 @@
         <v>114</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>30</v>
@@ -3518,7 +3494,7 @@
         <v>45750</v>
       </c>
       <c r="AB18" s="38" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3538,7 +3514,7 @@
         <v>119</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>30</v>
@@ -3602,7 +3578,7 @@
         <v>45750</v>
       </c>
       <c r="AB19" s="38" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3622,7 +3598,7 @@
         <v>126</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>30</v>
@@ -3686,7 +3662,7 @@
         <v>45750</v>
       </c>
       <c r="AB20" s="38" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3706,7 +3682,7 @@
         <v>132</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>30</v>
@@ -3770,7 +3746,7 @@
         <v>45750</v>
       </c>
       <c r="AB21" s="38" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3790,7 +3766,7 @@
         <v>136</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>30</v>
@@ -3854,7 +3830,7 @@
         <v>45750</v>
       </c>
       <c r="AB22" s="38" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3874,7 +3850,7 @@
         <v>140</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>30</v>
@@ -3934,13 +3910,13 @@
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AA23" s="12">
         <v>45750</v>
       </c>
       <c r="AB23" s="38" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -3960,7 +3936,7 @@
         <v>144</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>30</v>
@@ -4024,7 +4000,7 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4035,7 +4011,7 @@
         <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D25" s="4">
         <v>24</v>
@@ -4044,7 +4020,7 @@
         <v>144</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I25" s="3" t="b">
         <v>1</v>
@@ -4080,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="U25" s="9" t="b">
         <v>1</v>
@@ -4102,7 +4078,7 @@
         <v>45750</v>
       </c>
       <c r="AB25" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4113,7 +4089,7 @@
         <v>117</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D26" s="4">
         <v>25</v>
@@ -4122,7 +4098,7 @@
         <v>144</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="I26" s="3" t="b">
         <v>1</v>
@@ -4158,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="U26" s="9" t="b">
         <v>1</v>
@@ -4180,7 +4156,7 @@
         <v>45750</v>
       </c>
       <c r="AB26" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4191,7 +4167,7 @@
         <v>117</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D27" s="4">
         <v>26</v>
@@ -4200,7 +4176,7 @@
         <v>144</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="I27" s="3" t="b">
         <v>1</v>
@@ -4236,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="U27" s="9" t="b">
         <v>1</v>
@@ -4258,7 +4234,7 @@
         <v>45750</v>
       </c>
       <c r="AB27" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4269,7 +4245,7 @@
         <v>117</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D28" s="4">
         <v>27</v>
@@ -4278,7 +4254,7 @@
         <v>144</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="I28" s="3" t="b">
         <v>1</v>
@@ -4314,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="U28" s="9" t="b">
         <v>1</v>
@@ -4336,7 +4312,7 @@
         <v>45750</v>
       </c>
       <c r="AB28" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4347,7 +4323,7 @@
         <v>117</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D29" s="4">
         <v>28</v>
@@ -4356,7 +4332,7 @@
         <v>144</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="I29" s="3" t="b">
         <v>1</v>
@@ -4392,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="U29" s="9" t="b">
         <v>1</v>
@@ -4414,7 +4390,7 @@
         <v>45750</v>
       </c>
       <c r="AB29" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4425,7 +4401,7 @@
         <v>117</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D30" s="4">
         <v>29</v>
@@ -4434,7 +4410,7 @@
         <v>144</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I30" s="3" t="b">
         <v>1</v>
@@ -4470,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="U30" s="9" t="b">
         <v>1</v>
@@ -4492,7 +4468,7 @@
         <v>45750</v>
       </c>
       <c r="AB30" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4503,7 +4479,7 @@
         <v>117</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D31" s="4">
         <v>30</v>
@@ -4512,7 +4488,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="39" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="I31" s="3" t="b">
         <v>1</v>
@@ -4548,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="U31" s="9" t="b">
         <v>1</v>
@@ -4570,7 +4546,7 @@
         <v>45750</v>
       </c>
       <c r="AB31" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -4581,7 +4557,7 @@
         <v>117</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D32" s="4">
         <v>31</v>
@@ -4590,7 +4566,7 @@
         <v>144</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="I32" s="3" t="b">
         <v>1</v>
@@ -4626,7 +4602,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="U32" s="9" t="b">
         <v>1</v>
@@ -4648,7 +4624,7 @@
         <v>45750</v>
       </c>
       <c r="AB32" s="38" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="4:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -9594,7 +9570,7 @@
         <v>164</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
@@ -9615,16 +9591,16 @@
         <v>35</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I2" s="23">
         <v>-18.66</v>
@@ -9633,7 +9609,7 @@
         <v>3.6</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L2" s="3" t="b">
         <v>1</v>
@@ -9655,16 +9631,16 @@
         <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>171</v>
+        <v>297</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I3" s="24">
         <v>-17.899999999999999</v>
@@ -9673,7 +9649,7 @@
         <v>80.739999999999995</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L3" s="3" t="b">
         <v>1</v>
@@ -9695,16 +9671,16 @@
         <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>173</v>
+        <v>298</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I4" s="24">
         <v>-6.94</v>
@@ -9713,7 +9689,7 @@
         <v>77.06</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L4" s="3" t="b">
         <v>1</v>
@@ -9735,14 +9711,14 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I5" s="23">
         <v>13.3</v>
@@ -9751,7 +9727,7 @@
         <v>-50.58</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L5" s="3" t="b">
         <v>1</v>
@@ -9775,14 +9751,14 @@
         <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>187</v>
+        <v>300</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I6" s="24">
         <v>-12.48</v>
@@ -9791,7 +9767,7 @@
         <v>-13.11</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L6" s="13" t="b">
         <v>0</v>
@@ -9815,14 +9791,14 @@
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>191</v>
+        <v>301</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I7" s="23">
         <v>-17.02</v>
@@ -9831,7 +9807,7 @@
         <v>17.059999999999999</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L7" s="3" t="b">
         <v>1</v>
@@ -9855,14 +9831,14 @@
         <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I8" s="24">
         <v>-9.15</v>
@@ -9871,7 +9847,7 @@
         <v>49.78</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L8" s="3" t="b">
         <v>1</v>
@@ -9898,11 +9874,11 @@
         <v>303</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I9" s="25">
         <v>35.43</v>
@@ -9911,7 +9887,7 @@
         <v>63.03</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L9" s="3" t="b">
         <v>1</v>
@@ -9936,13 +9912,13 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I10" s="23">
         <v>-24.61</v>
@@ -9951,7 +9927,7 @@
         <v>176.91</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L10" s="3" t="b">
         <v>1</v>
@@ -9974,13 +9950,13 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I11" s="24">
         <v>-11.7</v>
@@ -9989,7 +9965,7 @@
         <v>-3.78</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L11" s="3" t="b">
         <v>1</v>
@@ -10011,14 +9987,14 @@
         <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I12" s="23">
         <v>-0.74</v>
@@ -10027,7 +10003,7 @@
         <v>112.77</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L12" s="3" t="b">
         <v>1</v>
@@ -10049,14 +10025,14 @@
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I13" s="24">
         <v>10.43</v>
@@ -10065,7 +10041,7 @@
         <v>170.31</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L13" s="3" t="b">
         <v>1</v>
@@ -10087,14 +10063,14 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I14" s="23">
         <v>26.8</v>
@@ -10103,7 +10079,7 @@
         <v>-136.21</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L14" s="3" t="b">
         <v>1</v>
@@ -10125,14 +10101,14 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I15" s="24">
         <v>65.44</v>
@@ -10141,7 +10117,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L15" s="3" t="b">
         <v>1</v>
@@ -10163,14 +10139,14 @@
         <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I16" s="25">
         <v>58.71</v>
@@ -10179,7 +10155,7 @@
         <v>-1.51</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L16" s="3" t="b">
         <v>1</v>
@@ -10202,13 +10178,13 @@
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I17" s="23">
         <v>-24.61</v>
@@ -10217,7 +10193,7 @@
         <v>176.91</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L17" s="3" t="b">
         <v>1</v>
@@ -10240,13 +10216,13 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I18" s="24">
         <v>-11.7</v>
@@ -10255,7 +10231,7 @@
         <v>-3.78</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L18" s="3" t="b">
         <v>1</v>
@@ -10277,14 +10253,14 @@
         <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I19" s="23">
         <v>-0.74</v>
@@ -10293,7 +10269,7 @@
         <v>112.77</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L19" s="3" t="b">
         <v>1</v>
@@ -10315,14 +10291,14 @@
         <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I20" s="24">
         <v>10.43</v>
@@ -10331,7 +10307,7 @@
         <v>170.31</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L20" s="3" t="b">
         <v>1</v>
@@ -10353,14 +10329,14 @@
         <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I21" s="23">
         <v>26.8</v>
@@ -10369,7 +10345,7 @@
         <v>-136.21</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L21" s="3" t="b">
         <v>1</v>
@@ -10391,14 +10367,14 @@
         <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I22" s="24">
         <v>65.44</v>
@@ -10407,7 +10383,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L22" s="3" t="b">
         <v>1</v>
@@ -10429,14 +10405,14 @@
         <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I23" s="25">
         <v>58.71</v>
@@ -10445,7 +10421,7 @@
         <v>-1.51</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L23" s="3" t="b">
         <v>1</v>
@@ -10468,13 +10444,13 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>169</v>
       </c>
       <c r="I24" s="23">
         <v>-24.61</v>
@@ -10483,7 +10459,7 @@
         <v>176.91</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L24" s="3" t="b">
         <v>1</v>
@@ -10506,13 +10482,13 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I25" s="24">
         <v>-11.7</v>
@@ -10521,7 +10497,7 @@
         <v>-3.78</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L25" s="3" t="b">
         <v>1</v>
@@ -10543,14 +10519,14 @@
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I26" s="23">
         <v>-0.74</v>
@@ -10559,7 +10535,7 @@
         <v>112.77</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L26" s="3" t="b">
         <v>1</v>
@@ -10581,14 +10557,14 @@
         <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I27" s="24">
         <v>10.43</v>
@@ -10597,7 +10573,7 @@
         <v>170.31</v>
       </c>
       <c r="K27" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L27" s="3" t="b">
         <v>1</v>
@@ -10619,14 +10595,14 @@
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I28" s="23">
         <v>26.8</v>
@@ -10635,7 +10611,7 @@
         <v>-136.21</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L28" s="3" t="b">
         <v>1</v>
@@ -10657,14 +10633,14 @@
         <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I29" s="24">
         <v>65.44</v>
@@ -10673,7 +10649,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K29" s="26" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L29" s="3" t="b">
         <v>1</v>
@@ -10695,14 +10671,14 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I30" s="25">
         <v>58.71</v>
@@ -10711,7 +10687,7 @@
         <v>-1.51</v>
       </c>
       <c r="K30" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L30" s="3" t="b">
         <v>1</v>
@@ -10734,13 +10710,13 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I31" s="23">
         <v>-24.61</v>
@@ -10749,7 +10725,7 @@
         <v>176.91</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L31" s="3" t="b">
         <v>1</v>
@@ -10772,13 +10748,13 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I32" s="24">
         <v>-11.7</v>
@@ -10787,7 +10763,7 @@
         <v>-3.78</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L32" s="3" t="b">
         <v>1</v>
@@ -10809,14 +10785,14 @@
         <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I33" s="23">
         <v>-0.74</v>
@@ -10825,7 +10801,7 @@
         <v>112.77</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L33" s="3" t="b">
         <v>1</v>
@@ -10847,14 +10823,14 @@
         <v>53</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I34" s="24">
         <v>10.43</v>
@@ -10863,7 +10839,7 @@
         <v>170.31</v>
       </c>
       <c r="K34" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L34" s="3" t="b">
         <v>1</v>
@@ -10885,14 +10861,14 @@
         <v>53</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I35" s="23">
         <v>26.8</v>
@@ -10901,7 +10877,7 @@
         <v>-136.21</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L35" s="3" t="b">
         <v>1</v>
@@ -10923,14 +10899,14 @@
         <v>53</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I36" s="24">
         <v>65.44</v>
@@ -10939,7 +10915,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K36" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L36" s="3" t="b">
         <v>1</v>
@@ -10961,14 +10937,14 @@
         <v>53</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I37" s="25">
         <v>58.71</v>
@@ -10977,7 +10953,7 @@
         <v>-1.51</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L37" s="3" t="b">
         <v>1</v>
@@ -11000,13 +10976,13 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I38" s="23">
         <v>-24.61</v>
@@ -11015,7 +10991,7 @@
         <v>176.91</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L38" s="3" t="b">
         <v>1</v>
@@ -11038,13 +11014,13 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I39" s="24">
         <v>-11.7</v>
@@ -11053,7 +11029,7 @@
         <v>-3.78</v>
       </c>
       <c r="K39" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L39" s="3" t="b">
         <v>1</v>
@@ -11075,14 +11051,14 @@
         <v>62</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I40" s="23">
         <v>-0.74</v>
@@ -11091,7 +11067,7 @@
         <v>112.77</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L40" s="3" t="b">
         <v>1</v>
@@ -11113,14 +11089,14 @@
         <v>62</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I41" s="24">
         <v>10.43</v>
@@ -11129,7 +11105,7 @@
         <v>170.31</v>
       </c>
       <c r="K41" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L41" s="3" t="b">
         <v>1</v>
@@ -11151,14 +11127,14 @@
         <v>62</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I42" s="23">
         <v>26.8</v>
@@ -11167,7 +11143,7 @@
         <v>-136.21</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L42" s="3" t="b">
         <v>1</v>
@@ -11189,14 +11165,14 @@
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I43" s="24">
         <v>65.44</v>
@@ -11205,7 +11181,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K43" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L43" s="3" t="b">
         <v>1</v>
@@ -11227,14 +11203,14 @@
         <v>62</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I44" s="25">
         <v>58.71</v>
@@ -11243,7 +11219,7 @@
         <v>-1.51</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L44" s="3" t="b">
         <v>1</v>
@@ -11266,13 +11242,13 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I45" s="23">
         <v>-24.61</v>
@@ -11281,7 +11257,7 @@
         <v>176.91</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L45" s="3" t="b">
         <v>1</v>
@@ -11304,13 +11280,13 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I46" s="24">
         <v>-11.7</v>
@@ -11319,7 +11295,7 @@
         <v>-3.78</v>
       </c>
       <c r="K46" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L46" s="3" t="b">
         <v>1</v>
@@ -11341,14 +11317,14 @@
         <v>67</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="23">
         <v>-0.74</v>
@@ -11357,7 +11333,7 @@
         <v>112.77</v>
       </c>
       <c r="K47" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L47" s="3" t="b">
         <v>1</v>
@@ -11379,14 +11355,14 @@
         <v>67</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I48" s="24">
         <v>10.43</v>
@@ -11395,7 +11371,7 @@
         <v>170.31</v>
       </c>
       <c r="K48" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L48" s="3" t="b">
         <v>1</v>
@@ -11417,14 +11393,14 @@
         <v>67</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I49" s="23">
         <v>26.8</v>
@@ -11433,7 +11409,7 @@
         <v>-136.21</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L49" s="3" t="b">
         <v>1</v>
@@ -11455,14 +11431,14 @@
         <v>67</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I50" s="24">
         <v>65.44</v>
@@ -11471,7 +11447,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K50" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L50" s="3" t="b">
         <v>1</v>
@@ -11493,14 +11469,14 @@
         <v>67</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I51" s="25">
         <v>58.71</v>
@@ -11509,7 +11485,7 @@
         <v>-1.51</v>
       </c>
       <c r="K51" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L51" s="3" t="b">
         <v>1</v>
@@ -11532,13 +11508,13 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="H52" s="24" t="s">
-        <v>169</v>
       </c>
       <c r="I52" s="23">
         <v>-15.9</v>
@@ -11547,7 +11523,7 @@
         <v>100.17</v>
       </c>
       <c r="K52" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L52" s="3" t="b">
         <v>1</v>
@@ -11570,13 +11546,13 @@
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I53" s="24">
         <v>-7.08</v>
@@ -11585,7 +11561,7 @@
         <v>-86.86</v>
       </c>
       <c r="K53" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L53" s="3" t="b">
         <v>1</v>
@@ -11607,14 +11583,14 @@
         <v>74</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I54" s="23">
         <v>-0.74</v>
@@ -11623,7 +11599,7 @@
         <v>112.77</v>
       </c>
       <c r="K54" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L54" s="3" t="b">
         <v>1</v>
@@ -11645,14 +11621,14 @@
         <v>74</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I55" s="24">
         <v>10.43</v>
@@ -11661,7 +11637,7 @@
         <v>170.31</v>
       </c>
       <c r="K55" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L55" s="3" t="b">
         <v>1</v>
@@ -11683,14 +11659,14 @@
         <v>74</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I56" s="23">
         <v>26.8</v>
@@ -11699,7 +11675,7 @@
         <v>-136.21</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L56" s="3" t="b">
         <v>1</v>
@@ -11721,14 +11697,14 @@
         <v>74</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I57" s="24">
         <v>65.44</v>
@@ -11737,7 +11713,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K57" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L57" s="3" t="b">
         <v>1</v>
@@ -11759,14 +11735,14 @@
         <v>74</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I58" s="25">
         <v>58.71</v>
@@ -11775,7 +11751,7 @@
         <v>-1.51</v>
       </c>
       <c r="K58" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L58" s="3" t="b">
         <v>1</v>
@@ -11798,13 +11774,13 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="H59" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I59" s="23">
         <v>-24.61</v>
@@ -11813,7 +11789,7 @@
         <v>176.91</v>
       </c>
       <c r="K59" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L59" s="3" t="b">
         <v>1</v>
@@ -11836,13 +11812,13 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I60" s="24">
         <v>-11.7</v>
@@ -11851,7 +11827,7 @@
         <v>-3.78</v>
       </c>
       <c r="K60" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L60" s="3" t="b">
         <v>1</v>
@@ -11873,14 +11849,14 @@
         <v>79</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I61" s="23">
         <v>-0.74</v>
@@ -11889,7 +11865,7 @@
         <v>112.77</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L61" s="3" t="b">
         <v>1</v>
@@ -11911,14 +11887,14 @@
         <v>79</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I62" s="24">
         <v>10.43</v>
@@ -11927,7 +11903,7 @@
         <v>170.31</v>
       </c>
       <c r="K62" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L62" s="3" t="b">
         <v>1</v>
@@ -11949,14 +11925,14 @@
         <v>79</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I63" s="23">
         <v>26.8</v>
@@ -11965,7 +11941,7 @@
         <v>-136.21</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L63" s="3" t="b">
         <v>1</v>
@@ -11987,14 +11963,14 @@
         <v>79</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I64" s="24">
         <v>65.44</v>
@@ -12003,7 +11979,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K64" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L64" s="3" t="b">
         <v>1</v>
@@ -12025,14 +12001,14 @@
         <v>79</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I65" s="25">
         <v>58.71</v>
@@ -12041,7 +12017,7 @@
         <v>-1.51</v>
       </c>
       <c r="K65" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L65" s="3" t="b">
         <v>1</v>
@@ -12064,13 +12040,13 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G66" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I66" s="23">
         <v>-24.61</v>
@@ -12079,7 +12055,7 @@
         <v>176.91</v>
       </c>
       <c r="K66" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L66" s="3" t="b">
         <v>1</v>
@@ -12102,13 +12078,13 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I67" s="24">
         <v>-11.7</v>
@@ -12117,7 +12093,7 @@
         <v>-3.78</v>
       </c>
       <c r="K67" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L67" s="3" t="b">
         <v>1</v>
@@ -12139,14 +12115,14 @@
         <v>83</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I68" s="23">
         <v>-0.74</v>
@@ -12155,7 +12131,7 @@
         <v>112.77</v>
       </c>
       <c r="K68" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L68" s="3" t="b">
         <v>1</v>
@@ -12177,14 +12153,14 @@
         <v>83</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I69" s="24">
         <v>10.43</v>
@@ -12193,7 +12169,7 @@
         <v>170.31</v>
       </c>
       <c r="K69" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L69" s="3" t="b">
         <v>1</v>
@@ -12215,14 +12191,14 @@
         <v>83</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I70" s="23">
         <v>26.8</v>
@@ -12231,7 +12207,7 @@
         <v>-136.21</v>
       </c>
       <c r="K70" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L70" s="3" t="b">
         <v>1</v>
@@ -12253,14 +12229,14 @@
         <v>83</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I71" s="24">
         <v>65.44</v>
@@ -12269,7 +12245,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K71" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L71" s="3" t="b">
         <v>1</v>
@@ -12291,14 +12267,14 @@
         <v>83</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I72" s="25">
         <v>58.71</v>
@@ -12307,7 +12283,7 @@
         <v>-1.51</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L72" s="3" t="b">
         <v>1</v>
@@ -12330,13 +12306,13 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G73" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="H73" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H73" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I73" s="23">
         <v>-24.61</v>
@@ -12345,7 +12321,7 @@
         <v>176.91</v>
       </c>
       <c r="K73" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L73" s="3" t="b">
         <v>1</v>
@@ -12368,13 +12344,13 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I74" s="24">
         <v>-11.7</v>
@@ -12383,7 +12359,7 @@
         <v>-3.78</v>
       </c>
       <c r="K74" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L74" s="3" t="b">
         <v>1</v>
@@ -12405,14 +12381,14 @@
         <v>87</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I75" s="23">
         <v>-0.74</v>
@@ -12421,7 +12397,7 @@
         <v>112.77</v>
       </c>
       <c r="K75" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L75" s="3" t="b">
         <v>1</v>
@@ -12443,14 +12419,14 @@
         <v>87</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I76" s="24">
         <v>10.43</v>
@@ -12459,7 +12435,7 @@
         <v>170.31</v>
       </c>
       <c r="K76" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L76" s="3" t="b">
         <v>1</v>
@@ -12481,14 +12457,14 @@
         <v>87</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I77" s="23">
         <v>26.8</v>
@@ -12497,7 +12473,7 @@
         <v>-136.21</v>
       </c>
       <c r="K77" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L77" s="3" t="b">
         <v>1</v>
@@ -12519,14 +12495,14 @@
         <v>87</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I78" s="24">
         <v>65.44</v>
@@ -12535,7 +12511,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K78" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L78" s="3" t="b">
         <v>1</v>
@@ -12557,14 +12533,14 @@
         <v>87</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I79" s="25">
         <v>58.71</v>
@@ -12573,7 +12549,7 @@
         <v>-1.51</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L79" s="3" t="b">
         <v>1</v>
@@ -12596,13 +12572,13 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="H80" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="H80" s="24" t="s">
-        <v>169</v>
       </c>
       <c r="I80" s="23">
         <v>-24.61</v>
@@ -12611,7 +12587,7 @@
         <v>176.91</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L80" s="3" t="b">
         <v>1</v>
@@ -12634,13 +12610,13 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I81" s="24">
         <v>-11.7</v>
@@ -12649,7 +12625,7 @@
         <v>-3.78</v>
       </c>
       <c r="K81" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L81" s="3" t="b">
         <v>1</v>
@@ -12671,14 +12647,14 @@
         <v>93</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I82" s="23">
         <v>-0.74</v>
@@ -12687,7 +12663,7 @@
         <v>112.77</v>
       </c>
       <c r="K82" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L82" s="3" t="b">
         <v>1</v>
@@ -12709,14 +12685,14 @@
         <v>93</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I83" s="24">
         <v>10.43</v>
@@ -12725,7 +12701,7 @@
         <v>170.31</v>
       </c>
       <c r="K83" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L83" s="3" t="b">
         <v>1</v>
@@ -12747,14 +12723,14 @@
         <v>93</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I84" s="23">
         <v>26.8</v>
@@ -12763,7 +12739,7 @@
         <v>-136.21</v>
       </c>
       <c r="K84" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L84" s="3" t="b">
         <v>1</v>
@@ -12785,14 +12761,14 @@
         <v>93</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I85" s="24">
         <v>65.44</v>
@@ -12801,7 +12777,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K85" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L85" s="3" t="b">
         <v>1</v>
@@ -12823,14 +12799,14 @@
         <v>93</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I86" s="25">
         <v>58.71</v>
@@ -12839,7 +12815,7 @@
         <v>-1.51</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L86" s="3" t="b">
         <v>1</v>
@@ -12862,13 +12838,13 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G87" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="H87" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I87" s="23">
         <v>-24.61</v>
@@ -12877,7 +12853,7 @@
         <v>176.91</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L87" s="3" t="b">
         <v>1</v>
@@ -12900,13 +12876,13 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I88" s="24">
         <v>-11.7</v>
@@ -12915,7 +12891,7 @@
         <v>-3.78</v>
       </c>
       <c r="K88" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L88" s="3" t="b">
         <v>1</v>
@@ -12937,14 +12913,14 @@
         <v>97</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I89" s="23">
         <v>-0.74</v>
@@ -12953,7 +12929,7 @@
         <v>112.77</v>
       </c>
       <c r="K89" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L89" s="3" t="b">
         <v>1</v>
@@ -12975,14 +12951,14 @@
         <v>97</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I90" s="24">
         <v>10.43</v>
@@ -12991,7 +12967,7 @@
         <v>170.31</v>
       </c>
       <c r="K90" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L90" s="3" t="b">
         <v>1</v>
@@ -13013,14 +12989,14 @@
         <v>97</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I91" s="23">
         <v>26.8</v>
@@ -13029,7 +13005,7 @@
         <v>-136.21</v>
       </c>
       <c r="K91" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L91" s="3" t="b">
         <v>1</v>
@@ -13051,14 +13027,14 @@
         <v>97</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I92" s="24">
         <v>65.44</v>
@@ -13067,7 +13043,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K92" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L92" s="3" t="b">
         <v>1</v>
@@ -13089,14 +13065,14 @@
         <v>97</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I93" s="25">
         <v>58.71</v>
@@ -13105,7 +13081,7 @@
         <v>-1.51</v>
       </c>
       <c r="K93" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L93" s="3" t="b">
         <v>1</v>
@@ -13128,13 +13104,13 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G94" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I94" s="23">
         <v>-24.61</v>
@@ -13143,7 +13119,7 @@
         <v>176.91</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L94" s="3" t="b">
         <v>1</v>
@@ -13166,13 +13142,13 @@
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I95" s="24">
         <v>-11.7</v>
@@ -13181,7 +13157,7 @@
         <v>-3.78</v>
       </c>
       <c r="K95" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L95" s="3" t="b">
         <v>1</v>
@@ -13203,14 +13179,14 @@
         <v>101</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I96" s="23">
         <v>-0.74</v>
@@ -13219,7 +13195,7 @@
         <v>112.77</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L96" s="3" t="b">
         <v>1</v>
@@ -13241,14 +13217,14 @@
         <v>101</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I97" s="24">
         <v>10.43</v>
@@ -13257,7 +13233,7 @@
         <v>170.31</v>
       </c>
       <c r="K97" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L97" s="3" t="b">
         <v>1</v>
@@ -13279,14 +13255,14 @@
         <v>101</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I98" s="23">
         <v>26.8</v>
@@ -13295,7 +13271,7 @@
         <v>-136.21</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L98" s="3" t="b">
         <v>1</v>
@@ -13317,14 +13293,14 @@
         <v>101</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I99" s="24">
         <v>65.44</v>
@@ -13333,7 +13309,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K99" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L99" s="3" t="b">
         <v>1</v>
@@ -13355,14 +13331,14 @@
         <v>101</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I100" s="25">
         <v>58.71</v>
@@ -13371,7 +13347,7 @@
         <v>-1.51</v>
       </c>
       <c r="K100" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L100" s="3" t="b">
         <v>1</v>
@@ -13381,7 +13357,7 @@
     </row>
     <row r="101" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B101" s="7">
         <v>15</v>
@@ -13394,13 +13370,13 @@
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G101" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H101" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I101" s="23">
         <v>-24.61</v>
@@ -13409,7 +13385,7 @@
         <v>176.91</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L101" s="3" t="b">
         <v>1</v>
@@ -13419,7 +13395,7 @@
     </row>
     <row r="102" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B102" s="7">
         <v>15</v>
@@ -13432,13 +13408,13 @@
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I102" s="24">
         <v>-11.7</v>
@@ -13447,7 +13423,7 @@
         <v>-3.78</v>
       </c>
       <c r="K102" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L102" s="3" t="b">
         <v>1</v>
@@ -13457,7 +13433,7 @@
     </row>
     <row r="103" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B103" s="7">
         <v>15</v>
@@ -13469,14 +13445,14 @@
         <v>106</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I103" s="23">
         <v>-0.74</v>
@@ -13485,7 +13461,7 @@
         <v>112.77</v>
       </c>
       <c r="K103" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L103" s="3" t="b">
         <v>1</v>
@@ -13495,7 +13471,7 @@
     </row>
     <row r="104" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B104" s="7">
         <v>15</v>
@@ -13507,14 +13483,14 @@
         <v>106</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I104" s="24">
         <v>10.43</v>
@@ -13523,7 +13499,7 @@
         <v>170.31</v>
       </c>
       <c r="K104" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L104" s="3" t="b">
         <v>1</v>
@@ -13533,7 +13509,7 @@
     </row>
     <row r="105" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B105" s="7">
         <v>15</v>
@@ -13545,14 +13521,14 @@
         <v>106</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I105" s="23">
         <v>26.8</v>
@@ -13561,7 +13537,7 @@
         <v>-136.21</v>
       </c>
       <c r="K105" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L105" s="3" t="b">
         <v>1</v>
@@ -13571,7 +13547,7 @@
     </row>
     <row r="106" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B106" s="7">
         <v>15</v>
@@ -13583,14 +13559,14 @@
         <v>106</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I106" s="24">
         <v>65.44</v>
@@ -13599,7 +13575,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K106" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L106" s="3" t="b">
         <v>1</v>
@@ -13609,7 +13585,7 @@
     </row>
     <row r="107" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B107" s="7">
         <v>15</v>
@@ -13621,14 +13597,14 @@
         <v>106</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I107" s="25">
         <v>58.71</v>
@@ -13637,7 +13613,7 @@
         <v>-1.51</v>
       </c>
       <c r="K107" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L107" s="3" t="b">
         <v>1</v>
@@ -13647,7 +13623,7 @@
     </row>
     <row r="108" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B108" s="7">
         <v>16</v>
@@ -13660,13 +13636,13 @@
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G108" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="H108" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="H108" s="24" t="s">
-        <v>169</v>
       </c>
       <c r="I108" s="23">
         <v>-24.61</v>
@@ -13675,7 +13651,7 @@
         <v>176.91</v>
       </c>
       <c r="K108" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L108" s="3" t="b">
         <v>1</v>
@@ -13685,7 +13661,7 @@
     </row>
     <row r="109" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B109" s="7">
         <v>16</v>
@@ -13698,13 +13674,13 @@
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H109" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I109" s="24">
         <v>-11.7</v>
@@ -13713,7 +13689,7 @@
         <v>-3.78</v>
       </c>
       <c r="K109" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L109" s="3" t="b">
         <v>1</v>
@@ -13723,7 +13699,7 @@
     </row>
     <row r="110" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B110" s="7">
         <v>16</v>
@@ -13735,14 +13711,14 @@
         <v>111</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I110" s="23">
         <v>-0.74</v>
@@ -13751,7 +13727,7 @@
         <v>112.77</v>
       </c>
       <c r="K110" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L110" s="3" t="b">
         <v>1</v>
@@ -13761,7 +13737,7 @@
     </row>
     <row r="111" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B111" s="7">
         <v>16</v>
@@ -13773,14 +13749,14 @@
         <v>111</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I111" s="24">
         <v>10.43</v>
@@ -13789,7 +13765,7 @@
         <v>170.31</v>
       </c>
       <c r="K111" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L111" s="3" t="b">
         <v>1</v>
@@ -13799,7 +13775,7 @@
     </row>
     <row r="112" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B112" s="7">
         <v>16</v>
@@ -13811,14 +13787,14 @@
         <v>111</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I112" s="23">
         <v>26.8</v>
@@ -13827,7 +13803,7 @@
         <v>-136.21</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L112" s="3" t="b">
         <v>1</v>
@@ -13837,7 +13813,7 @@
     </row>
     <row r="113" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B113" s="7">
         <v>16</v>
@@ -13849,14 +13825,14 @@
         <v>111</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I113" s="24">
         <v>65.44</v>
@@ -13865,7 +13841,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K113" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L113" s="3" t="b">
         <v>1</v>
@@ -13875,7 +13851,7 @@
     </row>
     <row r="114" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B114" s="7">
         <v>16</v>
@@ -13887,14 +13863,14 @@
         <v>111</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I114" s="25">
         <v>58.71</v>
@@ -13903,7 +13879,7 @@
         <v>-1.51</v>
       </c>
       <c r="K114" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L114" s="3" t="b">
         <v>1</v>
@@ -13913,7 +13889,7 @@
     </row>
     <row r="115" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B115" s="7">
         <v>17</v>
@@ -13926,13 +13902,13 @@
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G115" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="H115" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I115" s="23">
         <v>-24.61</v>
@@ -13941,7 +13917,7 @@
         <v>176.91</v>
       </c>
       <c r="K115" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L115" s="3" t="b">
         <v>1</v>
@@ -13951,7 +13927,7 @@
     </row>
     <row r="116" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B116" s="7">
         <v>17</v>
@@ -13964,13 +13940,13 @@
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I116" s="24">
         <v>-11.7</v>
@@ -13979,7 +13955,7 @@
         <v>-3.78</v>
       </c>
       <c r="K116" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L116" s="3" t="b">
         <v>1</v>
@@ -13989,7 +13965,7 @@
     </row>
     <row r="117" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B117" s="7">
         <v>17</v>
@@ -14001,14 +13977,14 @@
         <v>115</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I117" s="23">
         <v>-0.74</v>
@@ -14017,7 +13993,7 @@
         <v>112.77</v>
       </c>
       <c r="K117" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L117" s="3" t="b">
         <v>1</v>
@@ -14027,7 +14003,7 @@
     </row>
     <row r="118" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B118" s="7">
         <v>17</v>
@@ -14039,14 +14015,14 @@
         <v>115</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I118" s="24">
         <v>10.43</v>
@@ -14055,7 +14031,7 @@
         <v>170.31</v>
       </c>
       <c r="K118" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L118" s="3" t="b">
         <v>1</v>
@@ -14065,7 +14041,7 @@
     </row>
     <row r="119" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B119" s="7">
         <v>17</v>
@@ -14077,14 +14053,14 @@
         <v>115</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I119" s="23">
         <v>26.8</v>
@@ -14093,7 +14069,7 @@
         <v>-136.21</v>
       </c>
       <c r="K119" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L119" s="3" t="b">
         <v>1</v>
@@ -14103,7 +14079,7 @@
     </row>
     <row r="120" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B120" s="7">
         <v>17</v>
@@ -14115,14 +14091,14 @@
         <v>115</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I120" s="24">
         <v>65.44</v>
@@ -14131,7 +14107,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K120" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L120" s="3" t="b">
         <v>1</v>
@@ -14141,7 +14117,7 @@
     </row>
     <row r="121" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B121" s="7">
         <v>17</v>
@@ -14153,14 +14129,14 @@
         <v>115</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I121" s="25">
         <v>58.71</v>
@@ -14169,7 +14145,7 @@
         <v>-1.51</v>
       </c>
       <c r="K121" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L121" s="3" t="b">
         <v>1</v>
@@ -14179,7 +14155,7 @@
     </row>
     <row r="122" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B122" s="7">
         <v>18</v>
@@ -14192,13 +14168,13 @@
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G122" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="H122" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I122" s="23">
         <v>-24.61</v>
@@ -14207,7 +14183,7 @@
         <v>176.91</v>
       </c>
       <c r="K122" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L122" s="3" t="b">
         <v>1</v>
@@ -14217,7 +14193,7 @@
     </row>
     <row r="123" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B123" s="7">
         <v>18</v>
@@ -14230,13 +14206,13 @@
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I123" s="24">
         <v>-11.7</v>
@@ -14245,7 +14221,7 @@
         <v>-3.78</v>
       </c>
       <c r="K123" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L123" s="3" t="b">
         <v>1</v>
@@ -14255,7 +14231,7 @@
     </row>
     <row r="124" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B124" s="7">
         <v>18</v>
@@ -14267,14 +14243,14 @@
         <v>123</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I124" s="23">
         <v>-0.74</v>
@@ -14283,7 +14259,7 @@
         <v>112.77</v>
       </c>
       <c r="K124" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L124" s="3" t="b">
         <v>1</v>
@@ -14293,7 +14269,7 @@
     </row>
     <row r="125" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B125" s="7">
         <v>18</v>
@@ -14305,14 +14281,14 @@
         <v>123</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I125" s="24">
         <v>10.43</v>
@@ -14321,7 +14297,7 @@
         <v>170.31</v>
       </c>
       <c r="K125" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L125" s="3" t="b">
         <v>1</v>
@@ -14331,7 +14307,7 @@
     </row>
     <row r="126" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B126" s="7">
         <v>18</v>
@@ -14343,14 +14319,14 @@
         <v>123</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I126" s="23">
         <v>26.8</v>
@@ -14359,7 +14335,7 @@
         <v>-136.21</v>
       </c>
       <c r="K126" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L126" s="3" t="b">
         <v>1</v>
@@ -14369,7 +14345,7 @@
     </row>
     <row r="127" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B127" s="7">
         <v>18</v>
@@ -14381,14 +14357,14 @@
         <v>123</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I127" s="24">
         <v>65.44</v>
@@ -14397,7 +14373,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K127" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L127" s="3" t="b">
         <v>1</v>
@@ -14407,7 +14383,7 @@
     </row>
     <row r="128" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B128" s="7">
         <v>18</v>
@@ -14419,14 +14395,14 @@
         <v>123</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G128" s="3"/>
       <c r="H128" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I128" s="25">
         <v>58.71</v>
@@ -14435,7 +14411,7 @@
         <v>-1.51</v>
       </c>
       <c r="K128" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L128" s="3" t="b">
         <v>1</v>
@@ -14445,7 +14421,7 @@
     </row>
     <row r="129" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B129" s="7">
         <v>19</v>
@@ -14458,13 +14434,13 @@
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G129" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="H129" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H129" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I129" s="23">
         <v>-24.61</v>
@@ -14473,7 +14449,7 @@
         <v>176.91</v>
       </c>
       <c r="K129" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L129" s="3" t="b">
         <v>1</v>
@@ -14483,7 +14459,7 @@
     </row>
     <row r="130" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B130" s="7">
         <v>19</v>
@@ -14496,13 +14472,13 @@
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H130" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I130" s="24">
         <v>-11.7</v>
@@ -14511,7 +14487,7 @@
         <v>-3.78</v>
       </c>
       <c r="K130" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L130" s="3" t="b">
         <v>1</v>
@@ -14521,7 +14497,7 @@
     </row>
     <row r="131" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B131" s="7">
         <v>19</v>
@@ -14533,14 +14509,14 @@
         <v>129</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G131" s="3"/>
       <c r="H131" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I131" s="23">
         <v>-0.74</v>
@@ -14549,7 +14525,7 @@
         <v>112.77</v>
       </c>
       <c r="K131" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L131" s="3" t="b">
         <v>1</v>
@@ -14559,7 +14535,7 @@
     </row>
     <row r="132" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B132" s="7">
         <v>19</v>
@@ -14571,14 +14547,14 @@
         <v>129</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I132" s="24">
         <v>10.43</v>
@@ -14587,7 +14563,7 @@
         <v>170.31</v>
       </c>
       <c r="K132" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L132" s="3" t="b">
         <v>1</v>
@@ -14597,7 +14573,7 @@
     </row>
     <row r="133" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B133" s="7">
         <v>19</v>
@@ -14609,14 +14585,14 @@
         <v>129</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I133" s="23">
         <v>26.8</v>
@@ -14625,7 +14601,7 @@
         <v>-136.21</v>
       </c>
       <c r="K133" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L133" s="3" t="b">
         <v>1</v>
@@ -14635,7 +14611,7 @@
     </row>
     <row r="134" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B134" s="7">
         <v>19</v>
@@ -14647,14 +14623,14 @@
         <v>129</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G134" s="3"/>
       <c r="H134" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I134" s="24">
         <v>65.44</v>
@@ -14663,7 +14639,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K134" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L134" s="3" t="b">
         <v>1</v>
@@ -14673,7 +14649,7 @@
     </row>
     <row r="135" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B135" s="7">
         <v>19</v>
@@ -14685,14 +14661,14 @@
         <v>129</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G135" s="3"/>
       <c r="H135" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I135" s="25">
         <v>58.71</v>
@@ -14701,7 +14677,7 @@
         <v>-1.51</v>
       </c>
       <c r="K135" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L135" s="3" t="b">
         <v>1</v>
@@ -14711,7 +14687,7 @@
     </row>
     <row r="136" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B136" s="7">
         <v>20</v>
@@ -14724,13 +14700,13 @@
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H136" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I136" s="23">
         <v>-24.61</v>
@@ -14739,7 +14715,7 @@
         <v>176.91</v>
       </c>
       <c r="K136" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L136" s="3" t="b">
         <v>1</v>
@@ -14749,7 +14725,7 @@
     </row>
     <row r="137" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B137" s="7">
         <v>20</v>
@@ -14762,13 +14738,13 @@
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H137" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I137" s="24">
         <v>-11.7</v>
@@ -14777,7 +14753,7 @@
         <v>-3.78</v>
       </c>
       <c r="K137" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L137" s="3" t="b">
         <v>1</v>
@@ -14787,7 +14763,7 @@
     </row>
     <row r="138" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B138" s="7">
         <v>20</v>
@@ -14799,14 +14775,14 @@
         <v>133</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I138" s="23">
         <v>-0.74</v>
@@ -14815,7 +14791,7 @@
         <v>112.77</v>
       </c>
       <c r="K138" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L138" s="3" t="b">
         <v>1</v>
@@ -14825,7 +14801,7 @@
     </row>
     <row r="139" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B139" s="7">
         <v>20</v>
@@ -14837,14 +14813,14 @@
         <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I139" s="24">
         <v>10.43</v>
@@ -14853,7 +14829,7 @@
         <v>170.31</v>
       </c>
       <c r="K139" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L139" s="3" t="b">
         <v>1</v>
@@ -14863,7 +14839,7 @@
     </row>
     <row r="140" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B140" s="7">
         <v>20</v>
@@ -14875,14 +14851,14 @@
         <v>133</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I140" s="23">
         <v>26.8</v>
@@ -14891,7 +14867,7 @@
         <v>-136.21</v>
       </c>
       <c r="K140" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L140" s="3" t="b">
         <v>1</v>
@@ -14901,7 +14877,7 @@
     </row>
     <row r="141" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B141" s="7">
         <v>20</v>
@@ -14913,14 +14889,14 @@
         <v>133</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I141" s="24">
         <v>65.44</v>
@@ -14929,7 +14905,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K141" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L141" s="3" t="b">
         <v>1</v>
@@ -14939,7 +14915,7 @@
     </row>
     <row r="142" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B142" s="7">
         <v>20</v>
@@ -14951,14 +14927,14 @@
         <v>133</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G142" s="3"/>
       <c r="H142" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I142" s="25">
         <v>58.71</v>
@@ -14967,7 +14943,7 @@
         <v>-1.51</v>
       </c>
       <c r="K142" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L142" s="3" t="b">
         <v>1</v>
@@ -14977,7 +14953,7 @@
     </row>
     <row r="143" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B143" s="7">
         <v>21</v>
@@ -14990,13 +14966,13 @@
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G143" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="H143" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H143" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I143" s="23">
         <v>-24.61</v>
@@ -15005,7 +14981,7 @@
         <v>176.91</v>
       </c>
       <c r="K143" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L143" s="3" t="b">
         <v>1</v>
@@ -15015,7 +14991,7 @@
     </row>
     <row r="144" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B144" s="7">
         <v>21</v>
@@ -15028,13 +15004,13 @@
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I144" s="24">
         <v>-11.7</v>
@@ -15043,7 +15019,7 @@
         <v>-3.78</v>
       </c>
       <c r="K144" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L144" s="3" t="b">
         <v>1</v>
@@ -15053,7 +15029,7 @@
     </row>
     <row r="145" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B145" s="7">
         <v>21</v>
@@ -15065,14 +15041,14 @@
         <v>137</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I145" s="23">
         <v>-0.74</v>
@@ -15081,7 +15057,7 @@
         <v>112.77</v>
       </c>
       <c r="K145" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L145" s="3" t="b">
         <v>1</v>
@@ -15091,7 +15067,7 @@
     </row>
     <row r="146" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B146" s="7">
         <v>21</v>
@@ -15103,14 +15079,14 @@
         <v>137</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G146" s="3"/>
       <c r="H146" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I146" s="24">
         <v>10.43</v>
@@ -15119,7 +15095,7 @@
         <v>170.31</v>
       </c>
       <c r="K146" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L146" s="3" t="b">
         <v>1</v>
@@ -15129,7 +15105,7 @@
     </row>
     <row r="147" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B147" s="7">
         <v>21</v>
@@ -15141,14 +15117,14 @@
         <v>137</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G147" s="3"/>
       <c r="H147" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I147" s="23">
         <v>26.8</v>
@@ -15157,7 +15133,7 @@
         <v>-136.21</v>
       </c>
       <c r="K147" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L147" s="3" t="b">
         <v>1</v>
@@ -15167,7 +15143,7 @@
     </row>
     <row r="148" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B148" s="7">
         <v>21</v>
@@ -15179,14 +15155,14 @@
         <v>137</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I148" s="24">
         <v>65.44</v>
@@ -15195,7 +15171,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K148" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L148" s="3" t="b">
         <v>1</v>
@@ -15205,7 +15181,7 @@
     </row>
     <row r="149" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B149" s="7">
         <v>21</v>
@@ -15217,14 +15193,14 @@
         <v>137</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I149" s="25">
         <v>58.71</v>
@@ -15233,7 +15209,7 @@
         <v>-1.51</v>
       </c>
       <c r="K149" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L149" s="3" t="b">
         <v>1</v>
@@ -15243,7 +15219,7 @@
     </row>
     <row r="150" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B150" s="7">
         <v>22</v>
@@ -15256,13 +15232,13 @@
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G150" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G150" s="3" t="s">
+      <c r="H150" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H150" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I150" s="23">
         <v>-24.61</v>
@@ -15271,7 +15247,7 @@
         <v>176.91</v>
       </c>
       <c r="K150" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L150" s="3" t="b">
         <v>1</v>
@@ -15281,7 +15257,7 @@
     </row>
     <row r="151" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B151" s="7">
         <v>22</v>
@@ -15294,13 +15270,13 @@
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I151" s="24">
         <v>-11.7</v>
@@ -15309,7 +15285,7 @@
         <v>-3.78</v>
       </c>
       <c r="K151" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L151" s="3" t="b">
         <v>1</v>
@@ -15319,7 +15295,7 @@
     </row>
     <row r="152" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B152" s="7">
         <v>22</v>
@@ -15331,14 +15307,14 @@
         <v>141</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G152" s="3"/>
       <c r="H152" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I152" s="23">
         <v>-0.74</v>
@@ -15347,7 +15323,7 @@
         <v>112.77</v>
       </c>
       <c r="K152" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L152" s="3" t="b">
         <v>1</v>
@@ -15357,7 +15333,7 @@
     </row>
     <row r="153" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B153" s="7">
         <v>22</v>
@@ -15369,14 +15345,14 @@
         <v>141</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G153" s="3"/>
       <c r="H153" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I153" s="24">
         <v>10.43</v>
@@ -15385,7 +15361,7 @@
         <v>170.31</v>
       </c>
       <c r="K153" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L153" s="3" t="b">
         <v>1</v>
@@ -15395,7 +15371,7 @@
     </row>
     <row r="154" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B154" s="7">
         <v>22</v>
@@ -15407,14 +15383,14 @@
         <v>141</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G154" s="3"/>
       <c r="H154" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I154" s="23">
         <v>26.8</v>
@@ -15423,7 +15399,7 @@
         <v>-136.21</v>
       </c>
       <c r="K154" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L154" s="3" t="b">
         <v>1</v>
@@ -15433,7 +15409,7 @@
     </row>
     <row r="155" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B155" s="7">
         <v>22</v>
@@ -15445,14 +15421,14 @@
         <v>141</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G155" s="3"/>
       <c r="H155" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I155" s="24">
         <v>65.44</v>
@@ -15461,7 +15437,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K155" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L155" s="3" t="b">
         <v>1</v>
@@ -15471,7 +15447,7 @@
     </row>
     <row r="156" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B156" s="7">
         <v>22</v>
@@ -15483,14 +15459,14 @@
         <v>141</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G156" s="3"/>
       <c r="H156" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I156" s="25">
         <v>58.71</v>
@@ -15499,7 +15475,7 @@
         <v>-1.51</v>
       </c>
       <c r="K156" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L156" s="3" t="b">
         <v>1</v>
@@ -15509,7 +15485,7 @@
     </row>
     <row r="157" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B157" s="7">
         <v>23</v>
@@ -15522,13 +15498,13 @@
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G157" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G157" s="3" t="s">
+      <c r="H157" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H157" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I157" s="23">
         <v>-24.61</v>
@@ -15537,7 +15513,7 @@
         <v>176.91</v>
       </c>
       <c r="K157" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L157" s="3" t="b">
         <v>1</v>
@@ -15547,7 +15523,7 @@
     </row>
     <row r="158" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B158" s="7">
         <v>23</v>
@@ -15560,13 +15536,13 @@
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H158" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I158" s="24">
         <v>-11.7</v>
@@ -15575,7 +15551,7 @@
         <v>-3.78</v>
       </c>
       <c r="K158" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L158" s="3" t="b">
         <v>1</v>
@@ -15585,7 +15561,7 @@
     </row>
     <row r="159" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B159" s="7">
         <v>23</v>
@@ -15597,14 +15573,14 @@
         <v>146</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G159" s="3"/>
       <c r="H159" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I159" s="23">
         <v>-0.74</v>
@@ -15613,7 +15589,7 @@
         <v>112.77</v>
       </c>
       <c r="K159" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L159" s="3" t="b">
         <v>1</v>
@@ -15623,7 +15599,7 @@
     </row>
     <row r="160" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B160" s="7">
         <v>23</v>
@@ -15635,14 +15611,14 @@
         <v>146</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G160" s="3"/>
       <c r="H160" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I160" s="24">
         <v>10.43</v>
@@ -15651,7 +15627,7 @@
         <v>170.31</v>
       </c>
       <c r="K160" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L160" s="3" t="b">
         <v>1</v>
@@ -15661,7 +15637,7 @@
     </row>
     <row r="161" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B161" s="7">
         <v>23</v>
@@ -15673,14 +15649,14 @@
         <v>146</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G161" s="3"/>
       <c r="H161" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I161" s="23">
         <v>26.8</v>
@@ -15689,7 +15665,7 @@
         <v>-136.21</v>
       </c>
       <c r="K161" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L161" s="3" t="b">
         <v>1</v>
@@ -15699,7 +15675,7 @@
     </row>
     <row r="162" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B162" s="7">
         <v>23</v>
@@ -15711,14 +15687,14 @@
         <v>146</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G162" s="3"/>
       <c r="H162" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I162" s="24">
         <v>65.44</v>
@@ -15727,7 +15703,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K162" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L162" s="3" t="b">
         <v>1</v>
@@ -15737,7 +15713,7 @@
     </row>
     <row r="163" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B163" s="7">
         <v>23</v>
@@ -15749,14 +15725,14 @@
         <v>146</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G163" s="3"/>
       <c r="H163" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I163" s="25">
         <v>58.71</v>
@@ -15765,7 +15741,7 @@
         <v>-1.51</v>
       </c>
       <c r="K163" s="25" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L163" s="3" t="b">
         <v>1</v>
@@ -15775,26 +15751,26 @@
     </row>
     <row r="164" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B164" s="7">
         <v>24</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G164" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G164" s="3" t="s">
+      <c r="H164" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="H164" s="24" t="s">
-        <v>169</v>
       </c>
       <c r="I164" s="23">
         <v>-24.61</v>
@@ -15803,7 +15779,7 @@
         <v>176.91</v>
       </c>
       <c r="K164" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L164" s="3" t="b">
         <v>1</v>
@@ -15813,26 +15789,26 @@
     </row>
     <row r="165" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B165" s="7">
         <v>24</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H165" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I165" s="24">
         <v>-11.7</v>
@@ -15841,7 +15817,7 @@
         <v>-3.78</v>
       </c>
       <c r="K165" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L165" s="3" t="b">
         <v>1</v>
@@ -15851,26 +15827,26 @@
     </row>
     <row r="166" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B166" s="7">
         <v>24</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G166" s="3"/>
       <c r="H166" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I166" s="23">
         <v>-0.74</v>
@@ -15879,7 +15855,7 @@
         <v>112.77</v>
       </c>
       <c r="K166" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L166" s="3" t="b">
         <v>1</v>
@@ -15889,26 +15865,26 @@
     </row>
     <row r="167" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B167" s="7">
         <v>24</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G167" s="3"/>
       <c r="H167" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I167" s="24">
         <v>10.43</v>
@@ -15917,7 +15893,7 @@
         <v>170.31</v>
       </c>
       <c r="K167" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L167" s="3" t="b">
         <v>1</v>
@@ -15927,26 +15903,26 @@
     </row>
     <row r="168" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B168" s="7">
         <v>24</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G168" s="3"/>
       <c r="H168" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I168" s="23">
         <v>26.8</v>
@@ -15955,7 +15931,7 @@
         <v>-136.21</v>
       </c>
       <c r="K168" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L168" s="3" t="b">
         <v>1</v>
@@ -15965,26 +15941,26 @@
     </row>
     <row r="169" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B169" s="7">
         <v>24</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G169" s="3"/>
       <c r="H169" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I169" s="24">
         <v>65.44</v>
@@ -15993,7 +15969,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K169" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L169" s="3" t="b">
         <v>1</v>
@@ -16003,26 +15979,26 @@
     </row>
     <row r="170" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B170" s="7">
         <v>24</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G170" s="3"/>
       <c r="H170" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I170" s="25">
         <v>58.71</v>
@@ -16031,7 +16007,7 @@
         <v>-1.51</v>
       </c>
       <c r="K170" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L170" s="3" t="b">
         <v>1</v>
@@ -16041,26 +16017,26 @@
     </row>
     <row r="171" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B171" s="7">
         <v>25</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E171" s="3"/>
       <c r="F171" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G171" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G171" s="3" t="s">
+      <c r="H171" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H171" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I171" s="23">
         <v>-24.61</v>
@@ -16069,7 +16045,7 @@
         <v>176.91</v>
       </c>
       <c r="K171" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L171" s="3" t="b">
         <v>1</v>
@@ -16079,26 +16055,26 @@
     </row>
     <row r="172" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B172" s="7">
         <v>25</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I172" s="24">
         <v>-11.7</v>
@@ -16107,7 +16083,7 @@
         <v>-3.78</v>
       </c>
       <c r="K172" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L172" s="3" t="b">
         <v>1</v>
@@ -16117,26 +16093,26 @@
     </row>
     <row r="173" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B173" s="7">
         <v>25</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G173" s="3"/>
       <c r="H173" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I173" s="23">
         <v>-0.74</v>
@@ -16145,7 +16121,7 @@
         <v>112.77</v>
       </c>
       <c r="K173" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L173" s="3" t="b">
         <v>1</v>
@@ -16155,26 +16131,26 @@
     </row>
     <row r="174" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B174" s="7">
         <v>25</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G174" s="3"/>
       <c r="H174" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I174" s="24">
         <v>10.43</v>
@@ -16183,7 +16159,7 @@
         <v>170.31</v>
       </c>
       <c r="K174" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L174" s="3" t="b">
         <v>1</v>
@@ -16193,26 +16169,26 @@
     </row>
     <row r="175" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B175" s="7">
         <v>25</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G175" s="3"/>
       <c r="H175" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I175" s="23">
         <v>26.8</v>
@@ -16221,7 +16197,7 @@
         <v>-136.21</v>
       </c>
       <c r="K175" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L175" s="3" t="b">
         <v>1</v>
@@ -16231,26 +16207,26 @@
     </row>
     <row r="176" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B176" s="7">
         <v>25</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G176" s="3"/>
       <c r="H176" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I176" s="24">
         <v>65.44</v>
@@ -16259,7 +16235,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K176" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L176" s="3" t="b">
         <v>1</v>
@@ -16269,26 +16245,26 @@
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B177" s="7">
         <v>25</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G177" s="3"/>
       <c r="H177" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I177" s="25">
         <v>58.71</v>
@@ -16297,7 +16273,7 @@
         <v>-1.51</v>
       </c>
       <c r="K177" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L177" s="3" t="b">
         <v>1</v>
@@ -16307,26 +16283,26 @@
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B178" s="7">
         <v>25</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E178" s="3"/>
       <c r="F178" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G178" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G178" s="3" t="s">
+      <c r="H178" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H178" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I178" s="23">
         <v>-24.61</v>
@@ -16335,7 +16311,7 @@
         <v>176.91</v>
       </c>
       <c r="K178" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L178" s="3" t="b">
         <v>1</v>
@@ -16345,26 +16321,26 @@
     </row>
     <row r="179" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B179" s="7">
         <v>26</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E179" s="3"/>
       <c r="F179" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I179" s="24">
         <v>-11.7</v>
@@ -16373,7 +16349,7 @@
         <v>-3.78</v>
       </c>
       <c r="K179" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L179" s="3" t="b">
         <v>1</v>
@@ -16383,26 +16359,26 @@
     </row>
     <row r="180" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B180" s="7">
         <v>26</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G180" s="3"/>
       <c r="H180" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I180" s="23">
         <v>-0.74</v>
@@ -16411,7 +16387,7 @@
         <v>112.77</v>
       </c>
       <c r="K180" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L180" s="3" t="b">
         <v>1</v>
@@ -16421,26 +16397,26 @@
     </row>
     <row r="181" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B181" s="7">
         <v>26</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G181" s="3"/>
       <c r="H181" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I181" s="24">
         <v>10.43</v>
@@ -16449,7 +16425,7 @@
         <v>170.31</v>
       </c>
       <c r="K181" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L181" s="3" t="b">
         <v>1</v>
@@ -16459,26 +16435,26 @@
     </row>
     <row r="182" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B182" s="7">
         <v>26</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G182" s="3"/>
       <c r="H182" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I182" s="23">
         <v>26.8</v>
@@ -16487,7 +16463,7 @@
         <v>-136.21</v>
       </c>
       <c r="K182" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L182" s="3" t="b">
         <v>1</v>
@@ -16497,26 +16473,26 @@
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B183" s="7">
         <v>26</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G183" s="3"/>
       <c r="H183" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I183" s="24">
         <v>65.44</v>
@@ -16525,7 +16501,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K183" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L183" s="3" t="b">
         <v>1</v>
@@ -16535,26 +16511,26 @@
     </row>
     <row r="184" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B184" s="7">
         <v>26</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G184" s="3"/>
       <c r="H184" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I184" s="25">
         <v>58.71</v>
@@ -16563,7 +16539,7 @@
         <v>-1.51</v>
       </c>
       <c r="K184" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L184" s="3" t="b">
         <v>1</v>
@@ -16573,26 +16549,26 @@
     </row>
     <row r="185" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B185" s="7">
         <v>26</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E185" s="3"/>
       <c r="F185" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G185" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G185" s="3" t="s">
+      <c r="H185" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H185" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I185" s="23">
         <v>-24.61</v>
@@ -16601,7 +16577,7 @@
         <v>176.91</v>
       </c>
       <c r="K185" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L185" s="3" t="b">
         <v>1</v>
@@ -16611,26 +16587,26 @@
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B186" s="7">
         <v>27</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E186" s="3"/>
       <c r="F186" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H186" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I186" s="24">
         <v>-11.7</v>
@@ -16639,7 +16615,7 @@
         <v>-3.78</v>
       </c>
       <c r="K186" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L186" s="3" t="b">
         <v>1</v>
@@ -16649,26 +16625,26 @@
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B187" s="7">
         <v>27</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G187" s="3"/>
       <c r="H187" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I187" s="23">
         <v>-0.74</v>
@@ -16677,7 +16653,7 @@
         <v>112.77</v>
       </c>
       <c r="K187" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L187" s="3" t="b">
         <v>1</v>
@@ -16687,26 +16663,26 @@
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B188" s="7">
         <v>27</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G188" s="3"/>
       <c r="H188" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I188" s="24">
         <v>10.43</v>
@@ -16715,7 +16691,7 @@
         <v>170.31</v>
       </c>
       <c r="K188" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L188" s="3" t="b">
         <v>1</v>
@@ -16725,26 +16701,26 @@
     </row>
     <row r="189" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B189" s="7">
         <v>27</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G189" s="3"/>
       <c r="H189" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I189" s="23">
         <v>26.8</v>
@@ -16753,7 +16729,7 @@
         <v>-136.21</v>
       </c>
       <c r="K189" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L189" s="3" t="b">
         <v>1</v>
@@ -16763,26 +16739,26 @@
     </row>
     <row r="190" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B190" s="7">
         <v>27</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G190" s="3"/>
       <c r="H190" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I190" s="24">
         <v>65.44</v>
@@ -16791,7 +16767,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K190" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L190" s="3" t="b">
         <v>1</v>
@@ -16801,26 +16777,26 @@
     </row>
     <row r="191" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B191" s="7">
         <v>27</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G191" s="3"/>
       <c r="H191" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I191" s="25">
         <v>58.71</v>
@@ -16829,7 +16805,7 @@
         <v>-1.51</v>
       </c>
       <c r="K191" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L191" s="3" t="b">
         <v>1</v>
@@ -16839,26 +16815,26 @@
     </row>
     <row r="192" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B192" s="7">
         <v>27</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E192" s="3"/>
       <c r="F192" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H192" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I192" s="23">
         <v>-24.61</v>
@@ -16867,7 +16843,7 @@
         <v>176.91</v>
       </c>
       <c r="K192" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L192" s="3" t="b">
         <v>1</v>
@@ -16877,26 +16853,26 @@
     </row>
     <row r="193" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B193" s="7">
         <v>28</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E193" s="3"/>
       <c r="F193" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H193" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I193" s="24">
         <v>-11.7</v>
@@ -16905,7 +16881,7 @@
         <v>-3.78</v>
       </c>
       <c r="K193" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L193" s="3" t="b">
         <v>1</v>
@@ -16915,26 +16891,26 @@
     </row>
     <row r="194" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B194" s="7">
         <v>28</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G194" s="3"/>
       <c r="H194" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I194" s="23">
         <v>-0.74</v>
@@ -16943,7 +16919,7 @@
         <v>112.77</v>
       </c>
       <c r="K194" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L194" s="3" t="b">
         <v>1</v>
@@ -16953,26 +16929,26 @@
     </row>
     <row r="195" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B195" s="7">
         <v>28</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G195" s="3"/>
       <c r="H195" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I195" s="24">
         <v>10.43</v>
@@ -16981,7 +16957,7 @@
         <v>170.31</v>
       </c>
       <c r="K195" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L195" s="3" t="b">
         <v>1</v>
@@ -16991,26 +16967,26 @@
     </row>
     <row r="196" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B196" s="7">
         <v>28</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G196" s="3"/>
       <c r="H196" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I196" s="23">
         <v>26.8</v>
@@ -17019,7 +16995,7 @@
         <v>-136.21</v>
       </c>
       <c r="K196" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L196" s="3" t="b">
         <v>1</v>
@@ -17029,26 +17005,26 @@
     </row>
     <row r="197" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B197" s="7">
         <v>28</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G197" s="3"/>
       <c r="H197" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I197" s="24">
         <v>65.44</v>
@@ -17057,7 +17033,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K197" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L197" s="3" t="b">
         <v>1</v>
@@ -17067,26 +17043,26 @@
     </row>
     <row r="198" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B198" s="7">
         <v>28</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I198" s="25">
         <v>58.71</v>
@@ -17095,7 +17071,7 @@
         <v>-1.51</v>
       </c>
       <c r="K198" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L198" s="3" t="b">
         <v>1</v>
@@ -17105,26 +17081,26 @@
     </row>
     <row r="199" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B199" s="7">
         <v>28</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E199" s="3"/>
       <c r="F199" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G199" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G199" s="3" t="s">
+      <c r="H199" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H199" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I199" s="23">
         <v>-24.61</v>
@@ -17133,7 +17109,7 @@
         <v>176.91</v>
       </c>
       <c r="K199" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L199" s="3" t="b">
         <v>1</v>
@@ -17143,26 +17119,26 @@
     </row>
     <row r="200" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B200" s="7">
         <v>29</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E200" s="3"/>
       <c r="F200" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I200" s="24">
         <v>-11.7</v>
@@ -17171,7 +17147,7 @@
         <v>-3.78</v>
       </c>
       <c r="K200" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L200" s="3" t="b">
         <v>1</v>
@@ -17181,26 +17157,26 @@
     </row>
     <row r="201" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B201" s="7">
         <v>29</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G201" s="3"/>
       <c r="H201" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I201" s="23">
         <v>-0.74</v>
@@ -17209,7 +17185,7 @@
         <v>112.77</v>
       </c>
       <c r="K201" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L201" s="3" t="b">
         <v>1</v>
@@ -17219,26 +17195,26 @@
     </row>
     <row r="202" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B202" s="7">
         <v>29</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G202" s="3"/>
       <c r="H202" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I202" s="24">
         <v>10.43</v>
@@ -17247,7 +17223,7 @@
         <v>170.31</v>
       </c>
       <c r="K202" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L202" s="3" t="b">
         <v>1</v>
@@ -17257,26 +17233,26 @@
     </row>
     <row r="203" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B203" s="7">
         <v>29</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E203" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G203" s="3"/>
       <c r="H203" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I203" s="23">
         <v>26.8</v>
@@ -17285,7 +17261,7 @@
         <v>-136.21</v>
       </c>
       <c r="K203" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L203" s="3" t="b">
         <v>1</v>
@@ -17294,26 +17270,26 @@
     </row>
     <row r="204" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B204" s="7">
         <v>29</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E204" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G204" s="3"/>
       <c r="H204" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I204" s="24">
         <v>65.44</v>
@@ -17322,7 +17298,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K204" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L204" s="3" t="b">
         <v>1</v>
@@ -17331,26 +17307,26 @@
     </row>
     <row r="205" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B205" s="7">
         <v>29</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E205" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I205" s="25">
         <v>58.71</v>
@@ -17359,7 +17335,7 @@
         <v>-1.51</v>
       </c>
       <c r="K205" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L205" s="3" t="b">
         <v>1</v>
@@ -17368,25 +17344,25 @@
     </row>
     <row r="206" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B206" s="7">
         <v>29</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="F206" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G206" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G206" s="3" t="s">
+      <c r="H206" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H206" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I206" s="23">
         <v>-24.61</v>
@@ -17395,7 +17371,7 @@
         <v>176.91</v>
       </c>
       <c r="K206" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L206" s="3" t="b">
         <v>1</v>
@@ -17404,25 +17380,25 @@
     </row>
     <row r="207" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B207" s="7">
         <v>30</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I207" s="24">
         <v>-11.7</v>
@@ -17431,7 +17407,7 @@
         <v>-3.78</v>
       </c>
       <c r="K207" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L207" s="3" t="b">
         <v>1</v>
@@ -17440,26 +17416,26 @@
     </row>
     <row r="208" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B208" s="7">
         <v>30</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E208" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G208" s="3"/>
       <c r="H208" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I208" s="23">
         <v>-0.74</v>
@@ -17468,7 +17444,7 @@
         <v>112.77</v>
       </c>
       <c r="K208" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L208" s="3" t="b">
         <v>1</v>
@@ -17477,26 +17453,26 @@
     </row>
     <row r="209" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B209" s="7">
         <v>30</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E209" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G209" s="3"/>
       <c r="H209" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I209" s="24">
         <v>10.43</v>
@@ -17505,7 +17481,7 @@
         <v>170.31</v>
       </c>
       <c r="K209" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L209" s="3" t="b">
         <v>1</v>
@@ -17514,26 +17490,26 @@
     </row>
     <row r="210" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B210" s="7">
         <v>30</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E210" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G210" s="3"/>
       <c r="H210" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I210" s="23">
         <v>26.8</v>
@@ -17542,7 +17518,7 @@
         <v>-136.21</v>
       </c>
       <c r="K210" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L210" s="3" t="b">
         <v>1</v>
@@ -17551,26 +17527,26 @@
     </row>
     <row r="211" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B211" s="7">
         <v>30</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E211" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G211" s="3"/>
       <c r="H211" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I211" s="24">
         <v>65.44</v>
@@ -17579,7 +17555,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K211" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L211" s="3" t="b">
         <v>1</v>
@@ -17588,26 +17564,26 @@
     </row>
     <row r="212" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B212" s="7">
         <v>30</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E212" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G212" s="3"/>
       <c r="H212" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I212" s="25">
         <v>58.71</v>
@@ -17616,7 +17592,7 @@
         <v>-1.51</v>
       </c>
       <c r="K212" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L212" s="3" t="b">
         <v>1</v>
@@ -17625,25 +17601,25 @@
     </row>
     <row r="213" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B213" s="7">
         <v>30</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F213" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G213" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G213" s="3" t="s">
+      <c r="H213" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H213" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I213" s="23">
         <v>-24.61</v>
@@ -17652,7 +17628,7 @@
         <v>176.91</v>
       </c>
       <c r="K213" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L213" s="3" t="b">
         <v>1</v>
@@ -17661,25 +17637,25 @@
     </row>
     <row r="214" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B214" s="7">
         <v>31</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H214" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I214" s="24">
         <v>-11.7</v>
@@ -17688,7 +17664,7 @@
         <v>-3.78</v>
       </c>
       <c r="K214" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L214" s="3" t="b">
         <v>1</v>
@@ -17697,26 +17673,26 @@
     </row>
     <row r="215" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B215" s="7">
         <v>31</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E215" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G215" s="3"/>
       <c r="H215" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I215" s="23">
         <v>-0.74</v>
@@ -17725,7 +17701,7 @@
         <v>112.77</v>
       </c>
       <c r="K215" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L215" s="3" t="b">
         <v>1</v>
@@ -17734,26 +17710,26 @@
     </row>
     <row r="216" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B216" s="7">
         <v>31</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E216" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I216" s="24">
         <v>10.43</v>
@@ -17762,7 +17738,7 @@
         <v>170.31</v>
       </c>
       <c r="K216" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L216" s="3" t="b">
         <v>1</v>
@@ -17771,26 +17747,26 @@
     </row>
     <row r="217" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B217" s="7">
         <v>31</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E217" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G217" s="3"/>
       <c r="H217" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I217" s="23">
         <v>26.8</v>
@@ -17799,7 +17775,7 @@
         <v>-136.21</v>
       </c>
       <c r="K217" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L217" s="3" t="b">
         <v>1</v>
@@ -17808,26 +17784,26 @@
     </row>
     <row r="218" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B218" s="7">
         <v>31</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E218" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G218" s="3"/>
       <c r="H218" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I218" s="24">
         <v>65.44</v>
@@ -17836,7 +17812,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K218" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L218" s="3" t="b">
         <v>1</v>
@@ -17845,26 +17821,26 @@
     </row>
     <row r="219" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B219" s="7">
         <v>31</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E219" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G219" s="3"/>
       <c r="H219" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I219" s="25">
         <v>58.71</v>
@@ -17873,7 +17849,7 @@
         <v>-1.51</v>
       </c>
       <c r="K219" s="25" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L219" s="3" t="b">
         <v>1</v>
@@ -17882,25 +17858,25 @@
     </row>
     <row r="220" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B220" s="7">
         <v>31</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F220" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G220" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G220" s="3" t="s">
+      <c r="H220" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="H220" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="I220" s="23">
         <v>-24.61</v>
@@ -17909,7 +17885,7 @@
         <v>176.91</v>
       </c>
       <c r="K220" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L220" s="3" t="b">
         <v>1</v>
@@ -17918,25 +17894,25 @@
     </row>
     <row r="221" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B221" s="7">
         <v>32</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H221" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I221" s="24">
         <v>-11.7</v>
@@ -17945,7 +17921,7 @@
         <v>-3.78</v>
       </c>
       <c r="K221" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L221" s="3" t="b">
         <v>1</v>
@@ -17954,26 +17930,26 @@
     </row>
     <row r="222" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B222" s="7">
         <v>32</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E222" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G222" s="3"/>
       <c r="H222" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I222" s="23">
         <v>-0.74</v>
@@ -17982,7 +17958,7 @@
         <v>112.77</v>
       </c>
       <c r="K222" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L222" s="3" t="b">
         <v>1</v>
@@ -17991,26 +17967,26 @@
     </row>
     <row r="223" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B223" s="7">
         <v>32</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E223" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G223" s="3"/>
       <c r="H223" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I223" s="24">
         <v>10.43</v>
@@ -18019,7 +17995,7 @@
         <v>170.31</v>
       </c>
       <c r="K223" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L223" s="3" t="b">
         <v>1</v>
@@ -18028,26 +18004,26 @@
     </row>
     <row r="224" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B224" s="7">
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E224" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G224" s="3"/>
       <c r="H224" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I224" s="23">
         <v>26.8</v>
@@ -18056,7 +18032,7 @@
         <v>-136.21</v>
       </c>
       <c r="K224" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L224" s="3" t="b">
         <v>1</v>
@@ -18065,26 +18041,26 @@
     </row>
     <row r="225" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B225" s="7">
         <v>32</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E225" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G225" s="3"/>
       <c r="H225" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I225" s="24">
         <v>65.44</v>
@@ -18093,7 +18069,7 @@
         <v>-80.069999999999993</v>
       </c>
       <c r="K225" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L225" s="3" t="b">
         <v>1</v>
@@ -18102,26 +18078,26 @@
     </row>
     <row r="226" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B226" s="7">
         <v>32</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E226" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G226" s="3"/>
       <c r="H226" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I226" s="25">
         <v>58.71</v>
@@ -18130,7 +18106,7 @@
         <v>-1.51</v>
       </c>
       <c r="K226" s="25" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L226" s="3" t="b">
         <v>1</v>
@@ -20896,7 +20872,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.2" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B1" s="40" t="s">
         <v>149</v>
@@ -20926,7 +20902,7 @@
         <v>163</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20934,34 +20910,34 @@
         <v>4</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D2" s="45" t="s">
+        <v>174</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" s="46" t="s">
         <v>177</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>180</v>
       </c>
       <c r="H2" s="42">
         <v>18</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20969,22 +20945,22 @@
         <v>5</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G3" s="41" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H3" s="41">
         <v>22.5</v>
@@ -20993,10 +20969,10 @@
         <v>33</v>
       </c>
       <c r="J3" s="41" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K3" s="59" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21004,22 +20980,22 @@
         <v>6</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H4" s="42">
         <v>32.799999999999997</v>
@@ -21028,10 +21004,10 @@
         <v>33</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K4" s="59" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21039,20 +21015,20 @@
         <v>7</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="41" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G5" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H5" s="41">
         <v>40</v>
@@ -21064,7 +21040,7 @@
         <v>49</v>
       </c>
       <c r="K5" s="59" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21072,22 +21048,22 @@
         <v>8</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H6" s="42">
         <v>100</v>
@@ -21096,10 +21072,10 @@
         <v>33</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21107,22 +21083,22 @@
         <v>11</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H7" s="41">
         <v>18</v>
@@ -21134,7 +21110,7 @@
         <v>49</v>
       </c>
       <c r="K7" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21142,22 +21118,22 @@
         <v>12</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H8" s="42">
         <v>15.82</v>
@@ -21166,10 +21142,10 @@
         <v>33</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21177,20 +21153,20 @@
         <v>13</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H9" s="41">
         <v>45.65</v>
@@ -21199,10 +21175,10 @@
         <v>33</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K9" s="59" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21210,20 +21186,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="42" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H10" s="42">
         <v>40</v>
@@ -21232,10 +21208,10 @@
         <v>33</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21243,20 +21219,20 @@
         <v>15</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="41" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H11" s="41">
         <v>100</v>
@@ -21265,10 +21241,10 @@
         <v>33</v>
       </c>
       <c r="J11" s="41" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K11" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21276,18 +21252,18 @@
         <v>18</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="45"/>
       <c r="E12" s="52" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H12" s="52">
         <v>18</v>
@@ -21296,10 +21272,10 @@
         <v>33</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21307,18 +21283,18 @@
         <v>19</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="49"/>
       <c r="E13" s="52" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G13" s="41" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H13" s="52">
         <v>22</v>
@@ -21327,10 +21303,10 @@
         <v>33</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K13" s="59" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21338,18 +21314,18 @@
         <v>20</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="45"/>
       <c r="E14" s="52" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H14" s="52">
         <v>32</v>
@@ -21358,10 +21334,10 @@
         <v>33</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21369,18 +21345,18 @@
         <v>21</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="49"/>
       <c r="E15" s="52" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H15" s="52">
         <v>40</v>
@@ -21389,10 +21365,10 @@
         <v>33</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="K15" s="59" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21400,20 +21376,20 @@
         <v>22</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D16" s="45"/>
       <c r="E16" s="52" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F16" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H16" s="52">
         <v>100</v>
@@ -21422,10 +21398,10 @@
         <v>33</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K16" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21433,20 +21409,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H17" s="52">
         <v>18</v>
@@ -21455,10 +21431,10 @@
         <v>33</v>
       </c>
       <c r="J17" s="53" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K17" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21466,20 +21442,20 @@
         <v>26</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="45" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E18" s="55" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G18" s="42" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H18" s="52">
         <v>22</v>
@@ -21488,10 +21464,10 @@
         <v>33</v>
       </c>
       <c r="J18" s="53" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K18" s="59" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21499,18 +21475,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="49"/>
       <c r="E19" s="52" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H19" s="52">
         <v>32</v>
@@ -21519,10 +21495,10 @@
         <v>33</v>
       </c>
       <c r="J19" s="53" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K19" s="59" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21530,20 +21506,20 @@
         <v>28</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D20" s="45"/>
       <c r="E20" s="57" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H20" s="58">
         <v>40</v>
@@ -21552,10 +21528,10 @@
         <v>33</v>
       </c>
       <c r="J20" s="27" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="K20" s="59" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21563,22 +21539,22 @@
         <v>29</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H21" s="52">
         <v>100</v>
@@ -21587,10 +21563,10 @@
         <v>33</v>
       </c>
       <c r="J21" s="53" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K21" s="59" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -21663,16 +21639,16 @@
         <v>148</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F1" s="30"/>
     </row>
@@ -21684,7 +21660,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D2" s="31">
         <v>1</v>
@@ -21696,13 +21672,13 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="31" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>103</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D3" s="31">
         <v>2</v>
@@ -22744,10 +22720,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="29" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
@@ -22756,10 +22732,10 @@
     </row>
     <row r="2" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="31" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -22768,10 +22744,10 @@
     </row>
     <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
@@ -22780,10 +22756,10 @@
     </row>
     <row r="4" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="31" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B0BBF6-45A9-49E0-9321-145912F9B112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000D8C82-2E2F-4E77-899A-746C104E2AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="323">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1007,15 +1007,6 @@
     <t>HS1-08</t>
   </si>
   <si>
-    <t>HS2-06</t>
-  </si>
-  <si>
-    <t>HS2-07</t>
-  </si>
-  <si>
-    <t>HS2-08</t>
-  </si>
-  <si>
     <t>Slide-32</t>
   </si>
   <si>
@@ -1065,42 +1056,6 @@
   </si>
   <si>
     <t>HS1-20</t>
-  </si>
-  <si>
-    <t>HS2-09</t>
-  </si>
-  <si>
-    <t>HS2-10</t>
-  </si>
-  <si>
-    <t>HS3-11</t>
-  </si>
-  <si>
-    <t>HS4-17</t>
-  </si>
-  <si>
-    <t>HS3-12</t>
-  </si>
-  <si>
-    <t>HS3-13</t>
-  </si>
-  <si>
-    <t>HS3-14</t>
-  </si>
-  <si>
-    <t>HS3-15</t>
-  </si>
-  <si>
-    <t>HS4-16</t>
-  </si>
-  <si>
-    <t>HS4-18</t>
-  </si>
-  <si>
-    <t>HS4-19</t>
-  </si>
-  <si>
-    <t>HS4-20</t>
   </si>
   <si>
     <t>Shop Now i-frame</t>
@@ -9910,7 +9865,9 @@
       <c r="D10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F10" s="3" t="s">
         <v>166</v>
       </c>
@@ -9948,7 +9905,9 @@
       <c r="D11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="F11" s="3" t="s">
         <v>166</v>
       </c>
@@ -9987,7 +9946,7 @@
         <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>171</v>
@@ -10025,7 +9984,7 @@
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>171</v>
@@ -10063,7 +10022,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>171</v>
@@ -10101,7 +10060,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>171</v>
@@ -10139,7 +10098,7 @@
         <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>171</v>
@@ -10176,7 +10135,9 @@
       <c r="D17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F17" s="3" t="s">
         <v>166</v>
       </c>
@@ -10214,7 +10175,9 @@
       <c r="D18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="F18" s="3" t="s">
         <v>166</v>
       </c>
@@ -10253,7 +10216,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>171</v>
@@ -10291,7 +10254,7 @@
         <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>171</v>
@@ -10329,7 +10292,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>171</v>
@@ -10367,7 +10330,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>171</v>
@@ -10405,7 +10368,7 @@
         <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>171</v>
@@ -10442,7 +10405,9 @@
       <c r="D24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="F24" s="3" t="s">
         <v>166</v>
       </c>
@@ -10480,7 +10445,9 @@
       <c r="D25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F25" s="3" t="s">
         <v>166</v>
       </c>
@@ -10519,7 +10486,7 @@
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>171</v>
@@ -10557,7 +10524,7 @@
         <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>171</v>
@@ -10595,7 +10562,7 @@
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>171</v>
@@ -10633,7 +10600,7 @@
         <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>171</v>
@@ -10671,7 +10638,7 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>171</v>
@@ -10708,7 +10675,9 @@
       <c r="D31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F31" s="3" t="s">
         <v>166</v>
       </c>
@@ -10746,7 +10715,9 @@
       <c r="D32" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F32" s="3" t="s">
         <v>166</v>
       </c>
@@ -10785,7 +10756,7 @@
         <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>171</v>
@@ -10823,7 +10794,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>171</v>
@@ -10861,7 +10832,7 @@
         <v>53</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>171</v>
@@ -10899,7 +10870,7 @@
         <v>53</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>171</v>
@@ -10937,7 +10908,7 @@
         <v>53</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>171</v>
@@ -10974,7 +10945,9 @@
       <c r="D38" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="3"/>
+      <c r="E38" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F38" s="3" t="s">
         <v>166</v>
       </c>
@@ -11012,7 +10985,9 @@
       <c r="D39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="3"/>
+      <c r="E39" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="F39" s="3" t="s">
         <v>166</v>
       </c>
@@ -11051,7 +11026,7 @@
         <v>62</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>171</v>
@@ -11089,7 +11064,7 @@
         <v>62</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>171</v>
@@ -11127,7 +11102,7 @@
         <v>62</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>171</v>
@@ -11165,7 +11140,7 @@
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>171</v>
@@ -11203,7 +11178,7 @@
         <v>62</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>171</v>
@@ -11240,7 +11215,9 @@
       <c r="D45" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F45" s="3" t="s">
         <v>166</v>
       </c>
@@ -11278,7 +11255,9 @@
       <c r="D46" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E46" s="3"/>
+      <c r="E46" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F46" s="3" t="s">
         <v>166</v>
       </c>
@@ -11317,7 +11296,7 @@
         <v>67</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>171</v>
@@ -11355,7 +11334,7 @@
         <v>67</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>171</v>
@@ -11393,7 +11372,7 @@
         <v>67</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>171</v>
@@ -11431,7 +11410,7 @@
         <v>67</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>171</v>
@@ -11469,7 +11448,7 @@
         <v>67</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>171</v>
@@ -11506,7 +11485,9 @@
       <c r="D52" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="3"/>
+      <c r="E52" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F52" s="3" t="s">
         <v>166</v>
       </c>
@@ -11544,7 +11525,9 @@
       <c r="D53" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E53" s="3"/>
+      <c r="E53" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F53" s="3" t="s">
         <v>166</v>
       </c>
@@ -11583,7 +11566,7 @@
         <v>74</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>171</v>
@@ -11621,7 +11604,7 @@
         <v>74</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>171</v>
@@ -11659,7 +11642,7 @@
         <v>74</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>171</v>
@@ -11697,7 +11680,7 @@
         <v>74</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>171</v>
@@ -11735,7 +11718,7 @@
         <v>74</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>171</v>
@@ -11772,7 +11755,9 @@
       <c r="D59" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E59" s="3"/>
+      <c r="E59" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F59" s="3" t="s">
         <v>166</v>
       </c>
@@ -11810,7 +11795,9 @@
       <c r="D60" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E60" s="3"/>
+      <c r="E60" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F60" s="3" t="s">
         <v>166</v>
       </c>
@@ -11849,7 +11836,7 @@
         <v>79</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>171</v>
@@ -11887,7 +11874,7 @@
         <v>79</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>171</v>
@@ -11925,7 +11912,7 @@
         <v>79</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>171</v>
@@ -11963,7 +11950,7 @@
         <v>79</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>171</v>
@@ -12001,7 +11988,7 @@
         <v>79</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>171</v>
@@ -12038,7 +12025,9 @@
       <c r="D66" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E66" s="3"/>
+      <c r="E66" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F66" s="3" t="s">
         <v>166</v>
       </c>
@@ -12076,7 +12065,9 @@
       <c r="D67" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E67" s="3"/>
+      <c r="E67" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F67" s="3" t="s">
         <v>166</v>
       </c>
@@ -12115,7 +12106,7 @@
         <v>83</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>171</v>
@@ -12153,7 +12144,7 @@
         <v>83</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>171</v>
@@ -12191,7 +12182,7 @@
         <v>83</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>171</v>
@@ -12229,7 +12220,7 @@
         <v>83</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>171</v>
@@ -12267,7 +12258,7 @@
         <v>83</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>171</v>
@@ -12304,7 +12295,9 @@
       <c r="D73" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E73" s="3"/>
+      <c r="E73" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F73" s="3" t="s">
         <v>166</v>
       </c>
@@ -12342,7 +12335,9 @@
       <c r="D74" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E74" s="3"/>
+      <c r="E74" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F74" s="3" t="s">
         <v>166</v>
       </c>
@@ -12381,7 +12376,7 @@
         <v>87</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>171</v>
@@ -12419,7 +12414,7 @@
         <v>87</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>171</v>
@@ -12457,7 +12452,7 @@
         <v>87</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>171</v>
@@ -12495,7 +12490,7 @@
         <v>87</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>171</v>
@@ -12533,7 +12528,7 @@
         <v>87</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>171</v>
@@ -12570,7 +12565,9 @@
       <c r="D80" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E80" s="3"/>
+      <c r="E80" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F80" s="3" t="s">
         <v>166</v>
       </c>
@@ -12608,7 +12605,9 @@
       <c r="D81" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E81" s="3"/>
+      <c r="E81" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F81" s="3" t="s">
         <v>166</v>
       </c>
@@ -12647,7 +12646,7 @@
         <v>93</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>171</v>
@@ -12685,7 +12684,7 @@
         <v>93</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>171</v>
@@ -12723,7 +12722,7 @@
         <v>93</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>171</v>
@@ -12761,7 +12760,7 @@
         <v>93</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>334</v>
+        <v>296</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>171</v>
@@ -12799,7 +12798,7 @@
         <v>93</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>171</v>
@@ -12836,7 +12835,9 @@
       <c r="D87" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E87" s="3"/>
+      <c r="E87" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="F87" s="3" t="s">
         <v>166</v>
       </c>
@@ -12874,7 +12875,9 @@
       <c r="D88" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E88" s="3"/>
+      <c r="E88" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F88" s="3" t="s">
         <v>166</v>
       </c>
@@ -12913,7 +12916,7 @@
         <v>97</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>171</v>
@@ -12951,7 +12954,7 @@
         <v>97</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>171</v>
@@ -12989,7 +12992,7 @@
         <v>97</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>171</v>
@@ -13027,7 +13030,7 @@
         <v>97</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>171</v>
@@ -13065,7 +13068,7 @@
         <v>97</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>171</v>
@@ -13102,7 +13105,9 @@
       <c r="D94" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E94" s="3"/>
+      <c r="E94" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="F94" s="3" t="s">
         <v>166</v>
       </c>
@@ -13140,7 +13145,9 @@
       <c r="D95" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E95" s="3"/>
+      <c r="E95" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F95" s="3" t="s">
         <v>166</v>
       </c>
@@ -13179,7 +13186,7 @@
         <v>101</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>171</v>
@@ -13217,7 +13224,7 @@
         <v>101</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>171</v>
@@ -13255,7 +13262,7 @@
         <v>101</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>171</v>
@@ -13293,7 +13300,7 @@
         <v>101</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>171</v>
@@ -13331,7 +13338,7 @@
         <v>101</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>171</v>
@@ -13368,7 +13375,9 @@
       <c r="D101" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E101" s="3"/>
+      <c r="E101" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="F101" s="3" t="s">
         <v>166</v>
       </c>
@@ -13406,7 +13415,9 @@
       <c r="D102" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E102" s="3"/>
+      <c r="E102" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="F102" s="3" t="s">
         <v>166</v>
       </c>
@@ -13445,7 +13456,7 @@
         <v>106</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>171</v>
@@ -13483,7 +13494,7 @@
         <v>106</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>171</v>
@@ -13521,7 +13532,7 @@
         <v>106</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>171</v>
@@ -13559,7 +13570,7 @@
         <v>106</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>171</v>
@@ -13597,7 +13608,7 @@
         <v>106</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>171</v>
@@ -13634,7 +13645,9 @@
       <c r="D108" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E108" s="3"/>
+      <c r="E108" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="F108" s="3" t="s">
         <v>166</v>
       </c>
@@ -13672,7 +13685,9 @@
       <c r="D109" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E109" s="3"/>
+      <c r="E109" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="F109" s="3" t="s">
         <v>166</v>
       </c>
@@ -13711,7 +13726,7 @@
         <v>111</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>171</v>
@@ -13749,7 +13764,7 @@
         <v>111</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>171</v>
@@ -13787,7 +13802,7 @@
         <v>111</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>171</v>
@@ -13825,7 +13840,7 @@
         <v>111</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>171</v>
@@ -13863,7 +13878,7 @@
         <v>111</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>171</v>
@@ -13900,7 +13915,9 @@
       <c r="D115" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E115" s="3"/>
+      <c r="E115" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F115" s="3" t="s">
         <v>166</v>
       </c>
@@ -13938,7 +13955,9 @@
       <c r="D116" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E116" s="3"/>
+      <c r="E116" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="F116" s="3" t="s">
         <v>166</v>
       </c>
@@ -13977,7 +13996,7 @@
         <v>115</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>171</v>
@@ -14015,7 +14034,7 @@
         <v>115</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>171</v>
@@ -14053,7 +14072,7 @@
         <v>115</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>171</v>
@@ -14091,7 +14110,7 @@
         <v>115</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>171</v>
@@ -14129,7 +14148,7 @@
         <v>115</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>171</v>
@@ -14166,7 +14185,9 @@
       <c r="D122" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E122" s="3"/>
+      <c r="E122" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F122" s="3" t="s">
         <v>166</v>
       </c>
@@ -14204,7 +14225,9 @@
       <c r="D123" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E123" s="3"/>
+      <c r="E123" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="F123" s="3" t="s">
         <v>166</v>
       </c>
@@ -14243,7 +14266,7 @@
         <v>123</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>171</v>
@@ -14281,7 +14304,7 @@
         <v>123</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>171</v>
@@ -14319,7 +14342,7 @@
         <v>123</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>171</v>
@@ -14357,7 +14380,7 @@
         <v>123</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>171</v>
@@ -14395,7 +14418,7 @@
         <v>123</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>171</v>
@@ -14432,7 +14455,9 @@
       <c r="D129" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E129" s="3"/>
+      <c r="E129" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="F129" s="3" t="s">
         <v>166</v>
       </c>
@@ -14470,7 +14495,9 @@
       <c r="D130" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E130" s="3"/>
+      <c r="E130" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F130" s="3" t="s">
         <v>166</v>
       </c>
@@ -14509,7 +14536,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>171</v>
@@ -14547,7 +14574,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>171</v>
@@ -14585,7 +14612,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>171</v>
@@ -14623,7 +14650,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>171</v>
@@ -14661,7 +14688,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>171</v>
@@ -14698,7 +14725,9 @@
       <c r="D136" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E136" s="3"/>
+      <c r="E136" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F136" s="3" t="s">
         <v>166</v>
       </c>
@@ -14736,7 +14765,9 @@
       <c r="D137" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E137" s="3"/>
+      <c r="E137" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="F137" s="3" t="s">
         <v>166</v>
       </c>
@@ -14775,7 +14806,7 @@
         <v>133</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>171</v>
@@ -14813,7 +14844,7 @@
         <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>171</v>
@@ -14851,7 +14882,7 @@
         <v>133</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>171</v>
@@ -14889,7 +14920,7 @@
         <v>133</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>171</v>
@@ -14927,7 +14958,7 @@
         <v>133</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>171</v>
@@ -14964,7 +14995,9 @@
       <c r="D143" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E143" s="3"/>
+      <c r="E143" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F143" s="3" t="s">
         <v>166</v>
       </c>
@@ -15002,7 +15035,9 @@
       <c r="D144" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E144" s="3"/>
+      <c r="E144" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="F144" s="3" t="s">
         <v>166</v>
       </c>
@@ -15230,7 +15265,9 @@
       <c r="D150" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E150" s="3"/>
+      <c r="E150" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F150" s="3" t="s">
         <v>166</v>
       </c>
@@ -15268,7 +15305,9 @@
       <c r="D151" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E151" s="3"/>
+      <c r="E151" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F151" s="3" t="s">
         <v>166</v>
       </c>
@@ -15307,7 +15346,7 @@
         <v>141</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>171</v>
@@ -15345,7 +15384,7 @@
         <v>141</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>171</v>
@@ -15383,7 +15422,7 @@
         <v>141</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>171</v>
@@ -15421,7 +15460,7 @@
         <v>141</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>171</v>
@@ -15459,7 +15498,7 @@
         <v>141</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>171</v>
@@ -15496,7 +15535,9 @@
       <c r="D157" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E157" s="3"/>
+      <c r="E157" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F157" s="3" t="s">
         <v>166</v>
       </c>
@@ -15534,7 +15575,9 @@
       <c r="D158" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E158" s="3"/>
+      <c r="E158" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F158" s="3" t="s">
         <v>166</v>
       </c>
@@ -15573,7 +15616,7 @@
         <v>146</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>171</v>
@@ -15611,7 +15654,7 @@
         <v>146</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>171</v>
@@ -15649,7 +15692,7 @@
         <v>146</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>171</v>
@@ -15687,7 +15730,7 @@
         <v>146</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>171</v>
@@ -15725,7 +15768,7 @@
         <v>146</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>171</v>
@@ -15762,7 +15805,9 @@
       <c r="D164" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E164" s="3"/>
+      <c r="E164" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F164" s="3" t="s">
         <v>166</v>
       </c>
@@ -15800,7 +15845,9 @@
       <c r="D165" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E165" s="3"/>
+      <c r="E165" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F165" s="3" t="s">
         <v>166</v>
       </c>
@@ -15839,7 +15886,7 @@
         <v>263</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>171</v>
@@ -15877,7 +15924,7 @@
         <v>263</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>171</v>
@@ -15915,7 +15962,7 @@
         <v>263</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>171</v>
@@ -15953,7 +16000,7 @@
         <v>263</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>171</v>
@@ -15991,7 +16038,7 @@
         <v>263</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>171</v>
@@ -16028,7 +16075,9 @@
       <c r="D171" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E171" s="3"/>
+      <c r="E171" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F171" s="3" t="s">
         <v>166</v>
       </c>
@@ -16066,7 +16115,9 @@
       <c r="D172" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E172" s="3"/>
+      <c r="E172" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F172" s="3" t="s">
         <v>166</v>
       </c>
@@ -16105,7 +16156,7 @@
         <v>264</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>171</v>
@@ -16143,7 +16194,7 @@
         <v>264</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>171</v>
@@ -16181,7 +16232,7 @@
         <v>264</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>171</v>
@@ -16219,7 +16270,7 @@
         <v>264</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>171</v>
@@ -16257,7 +16308,7 @@
         <v>264</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>171</v>
@@ -16294,7 +16345,9 @@
       <c r="D178" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E178" s="3"/>
+      <c r="E178" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F178" s="3" t="s">
         <v>166</v>
       </c>
@@ -16332,7 +16385,9 @@
       <c r="D179" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E179" s="3"/>
+      <c r="E179" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F179" s="3" t="s">
         <v>166</v>
       </c>
@@ -16371,7 +16426,7 @@
         <v>265</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>171</v>
@@ -16409,7 +16464,7 @@
         <v>265</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>171</v>
@@ -16447,7 +16502,7 @@
         <v>265</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>171</v>
@@ -16485,7 +16540,7 @@
         <v>265</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>171</v>
@@ -16523,7 +16578,7 @@
         <v>265</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>171</v>
@@ -16560,7 +16615,9 @@
       <c r="D185" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E185" s="3"/>
+      <c r="E185" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F185" s="3" t="s">
         <v>166</v>
       </c>
@@ -16598,7 +16655,9 @@
       <c r="D186" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E186" s="3"/>
+      <c r="E186" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="F186" s="3" t="s">
         <v>166</v>
       </c>
@@ -16637,7 +16696,7 @@
         <v>266</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>171</v>
@@ -16675,7 +16734,7 @@
         <v>266</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>171</v>
@@ -16713,7 +16772,7 @@
         <v>266</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>171</v>
@@ -16751,7 +16810,7 @@
         <v>266</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>171</v>
@@ -16789,7 +16848,7 @@
         <v>266</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>171</v>
@@ -16826,7 +16885,9 @@
       <c r="D192" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E192" s="3"/>
+      <c r="E192" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="F192" s="3" t="s">
         <v>166</v>
       </c>
@@ -16864,7 +16925,9 @@
       <c r="D193" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E193" s="3"/>
+      <c r="E193" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F193" s="3" t="s">
         <v>166</v>
       </c>
@@ -16903,7 +16966,7 @@
         <v>267</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>171</v>
@@ -16941,7 +17004,7 @@
         <v>267</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>171</v>
@@ -16979,7 +17042,7 @@
         <v>267</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>171</v>
@@ -17017,7 +17080,7 @@
         <v>267</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>334</v>
+        <v>296</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>171</v>
@@ -17055,7 +17118,7 @@
         <v>267</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>171</v>
@@ -17092,7 +17155,9 @@
       <c r="D199" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E199" s="3"/>
+      <c r="E199" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="F199" s="3" t="s">
         <v>166</v>
       </c>
@@ -17130,7 +17195,9 @@
       <c r="D200" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E200" s="3"/>
+      <c r="E200" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F200" s="3" t="s">
         <v>166</v>
       </c>
@@ -17169,7 +17236,7 @@
         <v>268</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>171</v>
@@ -17207,7 +17274,7 @@
         <v>268</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>171</v>
@@ -17245,7 +17312,7 @@
         <v>268</v>
       </c>
       <c r="E203" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>171</v>
@@ -17282,7 +17349,7 @@
         <v>268</v>
       </c>
       <c r="E204" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>171</v>
@@ -17319,7 +17386,7 @@
         <v>268</v>
       </c>
       <c r="E205" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>171</v>
@@ -17355,6 +17422,9 @@
       <c r="D206" s="3" t="s">
         <v>268</v>
       </c>
+      <c r="E206" t="s">
+        <v>297</v>
+      </c>
       <c r="F206" s="3" t="s">
         <v>166</v>
       </c>
@@ -17391,6 +17461,9 @@
       <c r="D207" s="3" t="s">
         <v>278</v>
       </c>
+      <c r="E207" t="s">
+        <v>298</v>
+      </c>
       <c r="F207" s="3" t="s">
         <v>166</v>
       </c>
@@ -17428,7 +17501,7 @@
         <v>278</v>
       </c>
       <c r="E208" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>171</v>
@@ -17465,7 +17538,7 @@
         <v>278</v>
       </c>
       <c r="E209" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>171</v>
@@ -17502,7 +17575,7 @@
         <v>278</v>
       </c>
       <c r="E210" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>171</v>
@@ -17539,7 +17612,7 @@
         <v>278</v>
       </c>
       <c r="E211" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>171</v>
@@ -17576,7 +17649,7 @@
         <v>278</v>
       </c>
       <c r="E212" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>171</v>
@@ -17612,6 +17685,9 @@
       <c r="D213" s="3" t="s">
         <v>278</v>
       </c>
+      <c r="E213" t="s">
+        <v>297</v>
+      </c>
       <c r="F213" s="3" t="s">
         <v>166</v>
       </c>
@@ -17648,6 +17724,9 @@
       <c r="D214" s="3" t="s">
         <v>279</v>
       </c>
+      <c r="E214" t="s">
+        <v>298</v>
+      </c>
       <c r="F214" s="3" t="s">
         <v>166</v>
       </c>
@@ -17685,7 +17764,7 @@
         <v>279</v>
       </c>
       <c r="E215" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>171</v>
@@ -17722,7 +17801,7 @@
         <v>279</v>
       </c>
       <c r="E216" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>171</v>
@@ -17759,7 +17838,7 @@
         <v>279</v>
       </c>
       <c r="E217" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>171</v>
@@ -17796,7 +17875,7 @@
         <v>279</v>
       </c>
       <c r="E218" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>171</v>
@@ -17833,7 +17912,7 @@
         <v>279</v>
       </c>
       <c r="E219" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>171</v>
@@ -17869,6 +17948,9 @@
       <c r="D220" s="3" t="s">
         <v>279</v>
       </c>
+      <c r="E220" t="s">
+        <v>296</v>
+      </c>
       <c r="F220" s="3" t="s">
         <v>166</v>
       </c>
@@ -17900,10 +17982,13 @@
         <v>32</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
+      </c>
+      <c r="E221" t="s">
+        <v>297</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>166</v>
@@ -17936,13 +18021,13 @@
         <v>32</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E222" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>171</v>
@@ -17973,13 +18058,13 @@
         <v>32</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E223" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>171</v>
@@ -18010,13 +18095,13 @@
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E224" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>171</v>
@@ -18047,13 +18132,13 @@
         <v>32</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E225" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>171</v>
@@ -18084,13 +18169,13 @@
         <v>32</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E226" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>171</v>
@@ -20902,7 +20987,7 @@
         <v>163</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20937,7 +21022,7 @@
         <v>178</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20972,7 +21057,7 @@
         <v>182</v>
       </c>
       <c r="K3" s="59" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21007,7 +21092,7 @@
         <v>185</v>
       </c>
       <c r="K4" s="59" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21040,7 +21125,7 @@
         <v>49</v>
       </c>
       <c r="K5" s="59" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21075,7 +21160,7 @@
         <v>189</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21110,7 +21195,7 @@
         <v>49</v>
       </c>
       <c r="K7" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21145,7 +21230,7 @@
         <v>182</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21178,7 +21263,7 @@
         <v>185</v>
       </c>
       <c r="K9" s="59" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21186,7 +21271,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C10" s="44" t="s">
         <v>241</v>
@@ -21211,7 +21296,7 @@
         <v>191</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21219,7 +21304,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>241</v>
@@ -21244,7 +21329,7 @@
         <v>189</v>
       </c>
       <c r="K11" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21252,7 +21337,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="45"/>
@@ -21275,7 +21360,7 @@
         <v>178</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21283,7 +21368,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="49"/>
@@ -21306,7 +21391,7 @@
         <v>182</v>
       </c>
       <c r="K13" s="59" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21314,7 +21399,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="45"/>
@@ -21337,7 +21422,7 @@
         <v>185</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21345,7 +21430,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="49"/>
@@ -21368,7 +21453,7 @@
         <v>191</v>
       </c>
       <c r="K15" s="59" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21376,7 +21461,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C16" s="44" t="s">
         <v>239</v>
@@ -21401,7 +21486,7 @@
         <v>189</v>
       </c>
       <c r="K16" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21409,7 +21494,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
@@ -21434,7 +21519,7 @@
         <v>178</v>
       </c>
       <c r="K17" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21442,7 +21527,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="45" t="s">
@@ -21467,7 +21552,7 @@
         <v>182</v>
       </c>
       <c r="K18" s="59" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21475,7 +21560,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="49"/>
@@ -21498,7 +21583,7 @@
         <v>185</v>
       </c>
       <c r="K19" s="59" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21506,7 +21591,7 @@
         <v>28</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C20" s="44" t="s">
         <v>241</v>
@@ -21531,7 +21616,7 @@
         <v>191</v>
       </c>
       <c r="K20" s="59" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21539,7 +21624,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C21" s="51" t="s">
         <v>241</v>
@@ -21566,7 +21651,7 @@
         <v>189</v>
       </c>
       <c r="K21" s="59" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000D8C82-2E2F-4E77-899A-746C104E2AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D175665E-2A1D-43E4-A05F-91BE98A3DFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -9666,7 +9666,7 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>171</v>
@@ -9706,7 +9706,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>171</v>
@@ -9746,7 +9746,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>171</v>
@@ -9786,7 +9786,7 @@
         <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>171</v>
@@ -9826,7 +9826,7 @@
         <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>171</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D175665E-2A1D-43E4-A05F-91BE98A3DFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2849CA60-DB9D-42C4-A2FA-0FD7D43F2431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -49,6 +49,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>[Threaded comment]
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2449" uniqueCount="326">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -809,18 +810,6 @@
     <t>Show,X:8,Y:18,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
   </si>
   <si>
-    <t>Top:200,https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg</t>
-  </si>
-  <si>
-    <t>Top:200,https://cdn-icons-png.freepik.com/512/9783/9783549.png</t>
-  </si>
-  <si>
-    <t>Top:200,https://cdn-icons-png.freepik.com/512/16695/16695235.png</t>
-  </si>
-  <si>
-    <t>Top:200,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png</t>
-  </si>
-  <si>
     <t>GF 5K</t>
   </si>
   <si>
@@ -968,18 +957,6 @@
     <t>Slide-51</t>
   </si>
   <si>
-    <t>Right:100,https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg</t>
-  </si>
-  <si>
-    <t>Top:100,https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
-  </si>
-  <si>
-    <t>Bottom:200,https://cdn-icons-png.freepik.com/512/9783/9783549.png</t>
-  </si>
-  <si>
-    <t>Top:50,https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
-  </si>
-  <si>
     <t>SL#</t>
   </si>
   <si>
@@ -1062,6 +1039,39 @@
   </si>
   <si>
     <t>https://www.extra.com/en-sa/accessories/electrical/lights/c/6-633-18/facet/?q=%3Arelevance%3Atype%3APRODUCT&amp;text=&amp;pg=1&amp;pageSize=24&amp;sort=relevance</t>
+  </si>
+  <si>
+    <t>Hotspot Line Data</t>
+  </si>
+  <si>
+    <t>Right:100</t>
+  </si>
+  <si>
+    <t>Top:200</t>
+  </si>
+  <si>
+    <t>Top:100</t>
+  </si>
+  <si>
+    <t>Top:50</t>
+  </si>
+  <si>
+    <t>Bottom:200</t>
+  </si>
+  <si>
+    <t>https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg</t>
+  </si>
+  <si>
+    <t>https://static.vecteezy.com/system/resources/previews/043/602/284/non_2x/dining-chair-multi-color-circle-icon-vector.jpg</t>
+  </si>
+  <si>
+    <t>https://cdn-icons-png.freepik.com/512/9783/9783549.png</t>
+  </si>
+  <si>
+    <t>https://cdn-icons-png.freepik.com/512/16695/16695235.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1081,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1093,12 +1103,14 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1109,6 +1121,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1121,6 +1134,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1136,12 +1150,14 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1152,12 +1168,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="5"/>
@@ -1169,17 +1187,27 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1311,7 +1339,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1434,10 +1462,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1468,12 +1496,42 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1609,24 +1667,24 @@
   </dxfs>
   <tableStyles count="4">
     <tableStyle name="1. Scenes Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="firstRowStripe" dxfId="13"/>
-      <tableStyleElement type="secondRowStripe" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
     <tableStyle name="2. Hotspots Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="secondRowStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="3. Floors Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
     <tableStyle name="4. Styles Sheet (Custom CSS)-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1668,7 +1726,7 @@
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Floor map Details"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Floor Map Active"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Get Pitch/Yaw Data"/>
-    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="2"/>
+    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="3"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Scen Identifier"/>
     <tableColumn id="28" xr3:uid="{F3D3E641-7A49-4E3D-A155-18F57FACDDFD}" name="Map Data"/>
   </tableColumns>
@@ -1677,8 +1735,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:M226">
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:N226">
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="FloorID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Scene Order"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="SceneID"/>
@@ -1690,8 +1748,9 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Pitch"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Yaw"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Rotation"/>
+    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="0"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Hotspot Hover Active"/>
-    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="2. Hotspots Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2051,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>30</v>
@@ -2081,7 +2140,7 @@
         <v>2.15</v>
       </c>
       <c r="P2" s="3">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="Q2" s="3">
         <v>-2</v>
@@ -2137,7 +2196,7 @@
         <v>38</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>30</v>
@@ -2167,7 +2226,7 @@
         <v>-116.05</v>
       </c>
       <c r="P3" s="3">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="Q3" s="3">
         <v>-2</v>
@@ -2223,7 +2282,7 @@
         <v>43</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>30</v>
@@ -2253,7 +2312,7 @@
         <v>-43.36</v>
       </c>
       <c r="P4" s="3">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q4" s="3">
         <v>-2</v>
@@ -2304,7 +2363,7 @@
         <v>48</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>30</v>
@@ -2334,7 +2393,7 @@
         <v>-4.79</v>
       </c>
       <c r="P5" s="3">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q5" s="3">
         <v>-2</v>
@@ -2380,10 +2439,10 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>30</v>
@@ -2465,7 +2524,7 @@
         <v>57</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -2547,7 +2606,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>30</v>
@@ -2631,7 +2690,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>30</v>
@@ -2715,7 +2774,7 @@
         <v>77</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>30</v>
@@ -2799,7 +2858,7 @@
         <v>82</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>30</v>
@@ -2881,7 +2940,7 @@
         <v>86</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>30</v>
@@ -2965,7 +3024,7 @@
         <v>92</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>30</v>
@@ -3049,7 +3108,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>30</v>
@@ -3133,7 +3192,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>30</v>
@@ -3217,7 +3276,7 @@
         <v>105</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>30</v>
@@ -3301,7 +3360,7 @@
         <v>110</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>30</v>
@@ -3385,7 +3444,7 @@
         <v>114</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>30</v>
@@ -3469,7 +3528,7 @@
         <v>119</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>30</v>
@@ -3553,7 +3612,7 @@
         <v>126</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>30</v>
@@ -3637,7 +3696,7 @@
         <v>132</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>30</v>
@@ -3721,7 +3780,7 @@
         <v>136</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>30</v>
@@ -3805,7 +3864,7 @@
         <v>140</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>30</v>
@@ -3891,7 +3950,7 @@
         <v>144</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>30</v>
@@ -3966,7 +4025,7 @@
         <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D25" s="4">
         <v>24</v>
@@ -3975,7 +4034,7 @@
         <v>144</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I25" s="3" t="b">
         <v>1</v>
@@ -4011,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="U25" s="9" t="b">
         <v>1</v>
@@ -4044,7 +4103,7 @@
         <v>117</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D26" s="4">
         <v>25</v>
@@ -4053,7 +4112,7 @@
         <v>144</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I26" s="3" t="b">
         <v>1</v>
@@ -4089,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="U26" s="9" t="b">
         <v>1</v>
@@ -4122,7 +4181,7 @@
         <v>117</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D27" s="4">
         <v>26</v>
@@ -4131,7 +4190,7 @@
         <v>144</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I27" s="3" t="b">
         <v>1</v>
@@ -4167,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="U27" s="9" t="b">
         <v>1</v>
@@ -4200,7 +4259,7 @@
         <v>117</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D28" s="4">
         <v>27</v>
@@ -4209,7 +4268,7 @@
         <v>144</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I28" s="3" t="b">
         <v>1</v>
@@ -4245,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="U28" s="9" t="b">
         <v>1</v>
@@ -4278,7 +4337,7 @@
         <v>117</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D29" s="4">
         <v>28</v>
@@ -4287,7 +4346,7 @@
         <v>144</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I29" s="3" t="b">
         <v>1</v>
@@ -4323,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="U29" s="9" t="b">
         <v>1</v>
@@ -4356,7 +4415,7 @@
         <v>117</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D30" s="4">
         <v>29</v>
@@ -4365,7 +4424,7 @@
         <v>144</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I30" s="3" t="b">
         <v>1</v>
@@ -4401,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="U30" s="9" t="b">
         <v>1</v>
@@ -4434,7 +4493,7 @@
         <v>117</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D31" s="4">
         <v>30</v>
@@ -4443,7 +4502,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="39" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I31" s="3" t="b">
         <v>1</v>
@@ -4479,7 +4538,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="U31" s="9" t="b">
         <v>1</v>
@@ -4512,7 +4571,7 @@
         <v>117</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D32" s="4">
         <v>31</v>
@@ -4521,7 +4580,7 @@
         <v>144</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I32" s="3" t="b">
         <v>1</v>
@@ -4557,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="U32" s="9" t="b">
         <v>1</v>
@@ -9419,7 +9478,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -9469,7 +9528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q993"/>
+  <dimension ref="A1:R993"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="10.71875" customWidth="1"/>
@@ -9479,15 +9538,15 @@
     <col min="6" max="6" width="11.77734375" customWidth="1"/>
     <col min="7" max="7" width="17.109375" customWidth="1"/>
     <col min="10" max="10" width="17.609375" customWidth="1"/>
-    <col min="11" max="11" width="8.609375" customWidth="1"/>
-    <col min="12" max="12" width="22.5" customWidth="1"/>
-    <col min="13" max="13" width="20.0546875" customWidth="1"/>
-    <col min="14" max="14" width="18.109375" customWidth="1"/>
-    <col min="16" max="16" width="8.609375" style="36" customWidth="1"/>
-    <col min="17" max="21" width="8.609375" customWidth="1"/>
+    <col min="11" max="12" width="8.609375" customWidth="1"/>
+    <col min="13" max="13" width="22.5" customWidth="1"/>
+    <col min="14" max="14" width="20.0546875" customWidth="1"/>
+    <col min="15" max="15" width="18.109375" customWidth="1"/>
+    <col min="17" max="17" width="8.609375" style="36" customWidth="1"/>
+    <col min="18" max="22" width="8.609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="33.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="33.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>148</v>
       </c>
@@ -9522,17 +9581,20 @@
         <v>155</v>
       </c>
       <c r="L1" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="M1" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="N1" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="N1" s="22"/>
       <c r="O1" s="22"/>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
-    </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R1" s="22"/>
+    </row>
+    <row r="2" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>165</v>
       </c>
@@ -9546,7 +9608,7 @@
         <v>35</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>166</v>
@@ -9566,13 +9628,14 @@
       <c r="K2" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="36"/>
-      <c r="P2"/>
-    </row>
-    <row r="3" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="36"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>165</v>
       </c>
@@ -9586,13 +9649,13 @@
         <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>166</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>168</v>
@@ -9606,13 +9669,14 @@
       <c r="K3" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="36"/>
-      <c r="P3"/>
-    </row>
-    <row r="4" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="36"/>
+      <c r="Q3"/>
+    </row>
+    <row r="4" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>165</v>
       </c>
@@ -9626,7 +9690,7 @@
         <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>166</v>
@@ -9646,13 +9710,14 @@
       <c r="K4" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="7"/>
-      <c r="P4"/>
-    </row>
-    <row r="5" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" s="7"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>165</v>
       </c>
@@ -9666,7 +9731,7 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>171</v>
@@ -9684,15 +9749,18 @@
       <c r="K5" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="36">
+      <c r="L5" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="M5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="36">
         <v>5</v>
       </c>
-      <c r="P5"/>
-    </row>
-    <row r="6" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q5"/>
+    </row>
+    <row r="6" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>165</v>
       </c>
@@ -9706,7 +9774,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>171</v>
@@ -9724,15 +9792,18 @@
       <c r="K6" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L6" s="13" t="b">
+      <c r="L6" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M6" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="M6" s="36">
+      <c r="N6" s="36">
         <v>2</v>
       </c>
-      <c r="P6"/>
-    </row>
-    <row r="7" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q6"/>
+    </row>
+    <row r="7" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>165</v>
       </c>
@@ -9746,7 +9817,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>171</v>
@@ -9764,15 +9835,18 @@
       <c r="K7" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="36">
+      <c r="L7" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="M7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="36">
         <v>4</v>
       </c>
-      <c r="P7"/>
-    </row>
-    <row r="8" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q7"/>
+    </row>
+    <row r="8" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>165</v>
       </c>
@@ -9786,7 +9860,7 @@
         <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>171</v>
@@ -9804,15 +9878,18 @@
       <c r="K8" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="36">
-        <v>1</v>
-      </c>
-      <c r="P8"/>
-    </row>
-    <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L8" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q8"/>
+    </row>
+    <row r="9" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>165</v>
       </c>
@@ -9826,7 +9903,7 @@
         <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>171</v>
@@ -9844,15 +9921,18 @@
       <c r="K9" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="36">
+      <c r="L9" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="M9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="36">
         <v>3</v>
       </c>
-      <c r="P9"/>
-    </row>
-    <row r="10" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q9"/>
+    </row>
+    <row r="10" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>165</v>
       </c>
@@ -9866,7 +9946,7 @@
         <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>166</v>
@@ -9886,13 +9966,14 @@
       <c r="K10" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="36"/>
-      <c r="P10"/>
-    </row>
-    <row r="11" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L10" s="3"/>
+      <c r="M10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" s="36"/>
+      <c r="Q10"/>
+    </row>
+    <row r="11" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>165</v>
       </c>
@@ -9906,7 +9987,7 @@
         <v>40</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>166</v>
@@ -9926,13 +10007,14 @@
       <c r="K11" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L11" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="36"/>
-      <c r="P11"/>
-    </row>
-    <row r="12" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" s="36"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>165</v>
       </c>
@@ -9946,7 +10028,7 @@
         <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>171</v>
@@ -9964,13 +10046,16 @@
       <c r="K12" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="36"/>
-      <c r="P12"/>
-    </row>
-    <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L12" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" s="36"/>
+      <c r="Q12"/>
+    </row>
+    <row r="13" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>165</v>
       </c>
@@ -9984,7 +10069,7 @@
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>171</v>
@@ -10002,13 +10087,16 @@
       <c r="K13" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="36"/>
-      <c r="P13"/>
-    </row>
-    <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L13" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" s="36"/>
+      <c r="Q13"/>
+    </row>
+    <row r="14" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>165</v>
       </c>
@@ -10022,7 +10110,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>171</v>
@@ -10040,13 +10128,16 @@
       <c r="K14" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="36"/>
-      <c r="P14"/>
-    </row>
-    <row r="15" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L14" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" s="36"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>165</v>
       </c>
@@ -10060,7 +10151,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>171</v>
@@ -10078,13 +10169,16 @@
       <c r="K15" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="36"/>
-      <c r="P15"/>
-    </row>
-    <row r="16" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L15" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" s="36"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>165</v>
       </c>
@@ -10098,7 +10192,7 @@
         <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>171</v>
@@ -10116,13 +10210,16 @@
       <c r="K16" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="36"/>
-      <c r="P16"/>
-    </row>
-    <row r="17" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L16" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" s="36"/>
+      <c r="Q16"/>
+    </row>
+    <row r="17" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>165</v>
       </c>
@@ -10136,7 +10233,7 @@
         <v>45</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>166</v>
@@ -10156,13 +10253,14 @@
       <c r="K17" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="36"/>
-      <c r="P17"/>
-    </row>
-    <row r="18" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L17" s="60"/>
+      <c r="M17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" s="36"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>165</v>
       </c>
@@ -10176,7 +10274,7 @@
         <v>45</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>166</v>
@@ -10196,13 +10294,14 @@
       <c r="K18" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="36"/>
-      <c r="P18"/>
-    </row>
-    <row r="19" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L18" s="61"/>
+      <c r="M18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" s="36"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>165</v>
       </c>
@@ -10216,7 +10315,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>171</v>
@@ -10234,13 +10333,16 @@
       <c r="K19" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="36"/>
-      <c r="P19"/>
-    </row>
-    <row r="20" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L19" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" s="36"/>
+      <c r="Q19"/>
+    </row>
+    <row r="20" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>165</v>
       </c>
@@ -10254,7 +10356,7 @@
         <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>171</v>
@@ -10272,13 +10374,16 @@
       <c r="K20" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="36"/>
-      <c r="P20"/>
-    </row>
-    <row r="21" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L20" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" s="36"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>165</v>
       </c>
@@ -10292,7 +10397,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>171</v>
@@ -10310,13 +10415,16 @@
       <c r="K21" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L21" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="36"/>
-      <c r="P21"/>
-    </row>
-    <row r="22" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L21" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" s="36"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
         <v>165</v>
       </c>
@@ -10330,7 +10438,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>171</v>
@@ -10348,13 +10456,16 @@
       <c r="K22" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="36"/>
-      <c r="P22"/>
-    </row>
-    <row r="23" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L22" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" s="36"/>
+      <c r="Q22"/>
+    </row>
+    <row r="23" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
         <v>165</v>
       </c>
@@ -10368,7 +10479,7 @@
         <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>171</v>
@@ -10386,13 +10497,16 @@
       <c r="K23" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="36"/>
-      <c r="P23"/>
-    </row>
-    <row r="24" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L23" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" s="36"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>165</v>
       </c>
@@ -10406,7 +10520,7 @@
         <v>50</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>166</v>
@@ -10426,13 +10540,14 @@
       <c r="K24" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="36"/>
-      <c r="P24"/>
-    </row>
-    <row r="25" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L24" s="60"/>
+      <c r="M24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" s="36"/>
+      <c r="Q24"/>
+    </row>
+    <row r="25" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -10446,7 +10561,7 @@
         <v>50</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>166</v>
@@ -10466,13 +10581,14 @@
       <c r="K25" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="36"/>
-      <c r="P25"/>
-    </row>
-    <row r="26" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L25" s="61"/>
+      <c r="M25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" s="36"/>
+      <c r="Q25"/>
+    </row>
+    <row r="26" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
         <v>165</v>
       </c>
@@ -10486,7 +10602,7 @@
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>171</v>
@@ -10504,13 +10620,16 @@
       <c r="K26" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L26" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="36"/>
-      <c r="P26"/>
-    </row>
-    <row r="27" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L26" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" s="36"/>
+      <c r="Q26"/>
+    </row>
+    <row r="27" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>165</v>
       </c>
@@ -10524,7 +10643,7 @@
         <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>171</v>
@@ -10542,13 +10661,16 @@
       <c r="K27" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L27" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" s="36"/>
-      <c r="P27"/>
-    </row>
-    <row r="28" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L27" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" s="36"/>
+      <c r="Q27"/>
+    </row>
+    <row r="28" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
         <v>165</v>
       </c>
@@ -10562,7 +10684,7 @@
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>171</v>
@@ -10580,13 +10702,16 @@
       <c r="K28" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L28" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" s="36"/>
-      <c r="P28"/>
-    </row>
-    <row r="29" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L28" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" s="36"/>
+      <c r="Q28"/>
+    </row>
+    <row r="29" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
         <v>165</v>
       </c>
@@ -10600,7 +10725,7 @@
         <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>171</v>
@@ -10618,13 +10743,16 @@
       <c r="K29" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="L29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M29" s="36"/>
-      <c r="P29"/>
-    </row>
-    <row r="30" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L29" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" s="36"/>
+      <c r="Q29"/>
+    </row>
+    <row r="30" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
         <v>165</v>
       </c>
@@ -10638,7 +10766,7 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>171</v>
@@ -10656,13 +10784,16 @@
       <c r="K30" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M30" s="36"/>
-      <c r="P30"/>
-    </row>
-    <row r="31" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L30" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" s="36"/>
+      <c r="Q30"/>
+    </row>
+    <row r="31" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
         <v>165</v>
       </c>
@@ -10676,7 +10807,7 @@
         <v>53</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>166</v>
@@ -10696,13 +10827,14 @@
       <c r="K31" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M31" s="36"/>
-      <c r="P31"/>
-    </row>
-    <row r="32" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L31" s="60"/>
+      <c r="M31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" s="36"/>
+      <c r="Q31"/>
+    </row>
+    <row r="32" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
         <v>165</v>
       </c>
@@ -10716,7 +10848,7 @@
         <v>53</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>166</v>
@@ -10736,13 +10868,14 @@
       <c r="K32" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" s="36"/>
-      <c r="P32"/>
-    </row>
-    <row r="33" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L32" s="61"/>
+      <c r="M32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" s="36"/>
+      <c r="Q32"/>
+    </row>
+    <row r="33" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
         <v>165</v>
       </c>
@@ -10756,7 +10889,7 @@
         <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>171</v>
@@ -10774,13 +10907,16 @@
       <c r="K33" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M33" s="36"/>
-      <c r="P33"/>
-    </row>
-    <row r="34" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L33" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N33" s="36"/>
+      <c r="Q33"/>
+    </row>
+    <row r="34" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
         <v>165</v>
       </c>
@@ -10794,7 +10930,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>171</v>
@@ -10812,13 +10948,16 @@
       <c r="K34" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M34" s="36"/>
-      <c r="P34"/>
-    </row>
-    <row r="35" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L34" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" s="36"/>
+      <c r="Q34"/>
+    </row>
+    <row r="35" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
         <v>165</v>
       </c>
@@ -10832,7 +10971,7 @@
         <v>53</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>171</v>
@@ -10850,13 +10989,16 @@
       <c r="K35" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M35" s="36"/>
-      <c r="P35"/>
-    </row>
-    <row r="36" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L35" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="36"/>
+      <c r="Q35"/>
+    </row>
+    <row r="36" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
         <v>165</v>
       </c>
@@ -10870,7 +11012,7 @@
         <v>53</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>171</v>
@@ -10888,13 +11030,16 @@
       <c r="K36" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" s="36"/>
-      <c r="P36"/>
-    </row>
-    <row r="37" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L36" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="36"/>
+      <c r="Q36"/>
+    </row>
+    <row r="37" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
         <v>165</v>
       </c>
@@ -10908,7 +11053,7 @@
         <v>53</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>171</v>
@@ -10926,13 +11071,16 @@
       <c r="K37" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M37" s="36"/>
-      <c r="P37"/>
-    </row>
-    <row r="38" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L37" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="36"/>
+      <c r="Q37"/>
+    </row>
+    <row r="38" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
         <v>165</v>
       </c>
@@ -10946,7 +11094,7 @@
         <v>62</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>166</v>
@@ -10966,13 +11114,14 @@
       <c r="K38" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L38" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" s="36"/>
-      <c r="P38"/>
-    </row>
-    <row r="39" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L38" s="60"/>
+      <c r="M38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="36"/>
+      <c r="Q38"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
         <v>165</v>
       </c>
@@ -10986,7 +11135,7 @@
         <v>62</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>166</v>
@@ -11006,13 +11155,14 @@
       <c r="K39" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M39" s="36"/>
-      <c r="P39"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L39" s="61"/>
+      <c r="M39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="36"/>
+      <c r="Q39"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
         <v>165</v>
       </c>
@@ -11026,7 +11176,7 @@
         <v>62</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>171</v>
@@ -11044,13 +11194,16 @@
       <c r="K40" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M40" s="36"/>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L40" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="36"/>
+      <c r="Q40"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
         <v>165</v>
       </c>
@@ -11064,7 +11217,7 @@
         <v>62</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>171</v>
@@ -11082,13 +11235,16 @@
       <c r="K41" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M41" s="36"/>
-      <c r="P41"/>
-    </row>
-    <row r="42" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L41" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N41" s="36"/>
+      <c r="Q41"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
         <v>165</v>
       </c>
@@ -11102,7 +11258,7 @@
         <v>62</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>171</v>
@@ -11120,13 +11276,16 @@
       <c r="K42" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" s="36"/>
-      <c r="P42"/>
-    </row>
-    <row r="43" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L42" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" s="36"/>
+      <c r="Q42"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="3" t="s">
         <v>165</v>
       </c>
@@ -11140,7 +11299,7 @@
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>171</v>
@@ -11158,13 +11317,16 @@
       <c r="K43" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" s="36"/>
-      <c r="P43"/>
-    </row>
-    <row r="44" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L43" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N43" s="36"/>
+      <c r="Q43"/>
+    </row>
+    <row r="44" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="3" t="s">
         <v>165</v>
       </c>
@@ -11178,7 +11340,7 @@
         <v>62</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>171</v>
@@ -11196,13 +11358,16 @@
       <c r="K44" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" s="36"/>
-      <c r="P44"/>
-    </row>
-    <row r="45" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L44" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N44" s="36"/>
+      <c r="Q44"/>
+    </row>
+    <row r="45" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="3" t="s">
         <v>165</v>
       </c>
@@ -11216,7 +11381,7 @@
         <v>67</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>166</v>
@@ -11236,13 +11401,14 @@
       <c r="K45" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L45" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="36"/>
-      <c r="P45"/>
-    </row>
-    <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L45" s="60"/>
+      <c r="M45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="36"/>
+      <c r="Q45"/>
+    </row>
+    <row r="46" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
         <v>165</v>
       </c>
@@ -11256,7 +11422,7 @@
         <v>67</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>166</v>
@@ -11276,13 +11442,14 @@
       <c r="K46" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L46" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="36"/>
-      <c r="P46"/>
-    </row>
-    <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L46" s="61"/>
+      <c r="M46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" s="36"/>
+      <c r="Q46"/>
+    </row>
+    <row r="47" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3" t="s">
         <v>165</v>
       </c>
@@ -11296,7 +11463,7 @@
         <v>67</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>171</v>
@@ -11314,13 +11481,16 @@
       <c r="K47" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L47" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" s="36"/>
-      <c r="P47"/>
-    </row>
-    <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L47" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" s="36"/>
+      <c r="Q47"/>
+    </row>
+    <row r="48" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="3" t="s">
         <v>165</v>
       </c>
@@ -11334,7 +11504,7 @@
         <v>67</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>171</v>
@@ -11352,13 +11522,16 @@
       <c r="K48" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L48" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" s="36"/>
-      <c r="P48"/>
-    </row>
-    <row r="49" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L48" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" s="36"/>
+      <c r="Q48"/>
+    </row>
+    <row r="49" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3" t="s">
         <v>165</v>
       </c>
@@ -11372,7 +11545,7 @@
         <v>67</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>171</v>
@@ -11390,13 +11563,16 @@
       <c r="K49" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L49" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="36"/>
-      <c r="P49"/>
-    </row>
-    <row r="50" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L49" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="36"/>
+      <c r="Q49"/>
+    </row>
+    <row r="50" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3" t="s">
         <v>165</v>
       </c>
@@ -11410,7 +11586,7 @@
         <v>67</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>171</v>
@@ -11428,13 +11604,16 @@
       <c r="K50" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L50" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="36"/>
-      <c r="P50"/>
-    </row>
-    <row r="51" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L50" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" s="36"/>
+      <c r="Q50"/>
+    </row>
+    <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3" t="s">
         <v>165</v>
       </c>
@@ -11448,7 +11627,7 @@
         <v>67</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>171</v>
@@ -11466,13 +11645,16 @@
       <c r="K51" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L51" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="36"/>
-      <c r="P51"/>
-    </row>
-    <row r="52" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L51" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" s="36"/>
+      <c r="Q51"/>
+    </row>
+    <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
         <v>165</v>
       </c>
@@ -11486,7 +11668,7 @@
         <v>74</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>166</v>
@@ -11506,13 +11688,14 @@
       <c r="K52" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L52" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" s="36"/>
-      <c r="P52"/>
-    </row>
-    <row r="53" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L52" s="60"/>
+      <c r="M52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="36"/>
+      <c r="Q52"/>
+    </row>
+    <row r="53" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="3" t="s">
         <v>165</v>
       </c>
@@ -11526,7 +11709,7 @@
         <v>74</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>166</v>
@@ -11546,13 +11729,14 @@
       <c r="K53" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L53" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" s="36"/>
-      <c r="P53"/>
-    </row>
-    <row r="54" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L53" s="61"/>
+      <c r="M53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" s="36"/>
+      <c r="Q53"/>
+    </row>
+    <row r="54" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="3" t="s">
         <v>165</v>
       </c>
@@ -11566,7 +11750,7 @@
         <v>74</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>171</v>
@@ -11584,13 +11768,16 @@
       <c r="K54" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L54" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54" s="36"/>
-      <c r="P54"/>
-    </row>
-    <row r="55" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L54" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" s="36"/>
+      <c r="Q54"/>
+    </row>
+    <row r="55" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="3" t="s">
         <v>165</v>
       </c>
@@ -11604,7 +11791,7 @@
         <v>74</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>171</v>
@@ -11622,13 +11809,16 @@
       <c r="K55" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L55" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" s="36"/>
-      <c r="P55"/>
-    </row>
-    <row r="56" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L55" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" s="36"/>
+      <c r="Q55"/>
+    </row>
+    <row r="56" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3" t="s">
         <v>165</v>
       </c>
@@ -11642,7 +11832,7 @@
         <v>74</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>171</v>
@@ -11660,13 +11850,16 @@
       <c r="K56" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L56" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M56" s="36"/>
-      <c r="P56"/>
-    </row>
-    <row r="57" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L56" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" s="36"/>
+      <c r="Q56"/>
+    </row>
+    <row r="57" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3" t="s">
         <v>165</v>
       </c>
@@ -11680,7 +11873,7 @@
         <v>74</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>171</v>
@@ -11698,13 +11891,16 @@
       <c r="K57" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L57" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M57" s="36"/>
-      <c r="P57"/>
-    </row>
-    <row r="58" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L57" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" s="36"/>
+      <c r="Q57"/>
+    </row>
+    <row r="58" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3" t="s">
         <v>165</v>
       </c>
@@ -11718,7 +11914,7 @@
         <v>74</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>171</v>
@@ -11736,13 +11932,16 @@
       <c r="K58" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L58" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M58" s="36"/>
-      <c r="P58"/>
-    </row>
-    <row r="59" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L58" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" s="36"/>
+      <c r="Q58"/>
+    </row>
+    <row r="59" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="3" t="s">
         <v>165</v>
       </c>
@@ -11756,7 +11955,7 @@
         <v>79</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>166</v>
@@ -11776,13 +11975,14 @@
       <c r="K59" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L59" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M59" s="36"/>
-      <c r="P59"/>
-    </row>
-    <row r="60" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L59" s="60"/>
+      <c r="M59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" s="36"/>
+      <c r="Q59"/>
+    </row>
+    <row r="60" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3" t="s">
         <v>165</v>
       </c>
@@ -11796,7 +11996,7 @@
         <v>79</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>166</v>
@@ -11816,13 +12016,14 @@
       <c r="K60" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L60" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M60" s="36"/>
-      <c r="P60"/>
-    </row>
-    <row r="61" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L60" s="61"/>
+      <c r="M60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" s="36"/>
+      <c r="Q60"/>
+    </row>
+    <row r="61" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="3" t="s">
         <v>165</v>
       </c>
@@ -11836,7 +12037,7 @@
         <v>79</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>171</v>
@@ -11854,13 +12055,16 @@
       <c r="K61" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L61" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M61" s="36"/>
-      <c r="P61"/>
-    </row>
-    <row r="62" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L61" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="36"/>
+      <c r="Q61"/>
+    </row>
+    <row r="62" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="3" t="s">
         <v>165</v>
       </c>
@@ -11874,7 +12078,7 @@
         <v>79</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>171</v>
@@ -11892,13 +12096,16 @@
       <c r="K62" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L62" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M62" s="36"/>
-      <c r="P62"/>
-    </row>
-    <row r="63" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L62" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" s="36"/>
+      <c r="Q62"/>
+    </row>
+    <row r="63" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3" t="s">
         <v>165</v>
       </c>
@@ -11912,7 +12119,7 @@
         <v>79</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>171</v>
@@ -11930,13 +12137,16 @@
       <c r="K63" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L63" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M63" s="36"/>
-      <c r="P63"/>
-    </row>
-    <row r="64" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L63" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="36"/>
+      <c r="Q63"/>
+    </row>
+    <row r="64" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="3" t="s">
         <v>165</v>
       </c>
@@ -11950,7 +12160,7 @@
         <v>79</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>171</v>
@@ -11968,13 +12178,16 @@
       <c r="K64" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L64" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M64" s="36"/>
-      <c r="P64"/>
-    </row>
-    <row r="65" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" s="36"/>
+      <c r="Q64"/>
+    </row>
+    <row r="65" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="3" t="s">
         <v>165</v>
       </c>
@@ -11988,7 +12201,7 @@
         <v>79</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>171</v>
@@ -12006,13 +12219,16 @@
       <c r="K65" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L65" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M65" s="36"/>
-      <c r="P65"/>
-    </row>
-    <row r="66" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L65" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N65" s="36"/>
+      <c r="Q65"/>
+    </row>
+    <row r="66" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3" t="s">
         <v>165</v>
       </c>
@@ -12026,7 +12242,7 @@
         <v>83</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>166</v>
@@ -12046,13 +12262,14 @@
       <c r="K66" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L66" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M66" s="36"/>
-      <c r="P66"/>
-    </row>
-    <row r="67" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L66" s="60"/>
+      <c r="M66" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" s="36"/>
+      <c r="Q66"/>
+    </row>
+    <row r="67" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3" t="s">
         <v>165</v>
       </c>
@@ -12066,7 +12283,7 @@
         <v>83</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>166</v>
@@ -12086,13 +12303,14 @@
       <c r="K67" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L67" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M67" s="36"/>
-      <c r="P67"/>
-    </row>
-    <row r="68" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L67" s="61"/>
+      <c r="M67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" s="36"/>
+      <c r="Q67"/>
+    </row>
+    <row r="68" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3" t="s">
         <v>165</v>
       </c>
@@ -12106,7 +12324,7 @@
         <v>83</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>171</v>
@@ -12124,13 +12342,16 @@
       <c r="K68" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L68" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M68" s="36"/>
-      <c r="P68"/>
-    </row>
-    <row r="69" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L68" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" s="36"/>
+      <c r="Q68"/>
+    </row>
+    <row r="69" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
         <v>165</v>
       </c>
@@ -12144,7 +12365,7 @@
         <v>83</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>171</v>
@@ -12162,13 +12383,16 @@
       <c r="K69" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L69" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M69" s="36"/>
-      <c r="P69"/>
-    </row>
-    <row r="70" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L69" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" s="36"/>
+      <c r="Q69"/>
+    </row>
+    <row r="70" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3" t="s">
         <v>165</v>
       </c>
@@ -12182,7 +12406,7 @@
         <v>83</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>171</v>
@@ -12200,13 +12424,16 @@
       <c r="K70" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L70" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M70" s="36"/>
-      <c r="P70"/>
-    </row>
-    <row r="71" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L70" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M70" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" s="36"/>
+      <c r="Q70"/>
+    </row>
+    <row r="71" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3" t="s">
         <v>165</v>
       </c>
@@ -12220,7 +12447,7 @@
         <v>83</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>171</v>
@@ -12238,13 +12465,16 @@
       <c r="K71" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L71" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M71" s="36"/>
-      <c r="P71"/>
-    </row>
-    <row r="72" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L71" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N71" s="36"/>
+      <c r="Q71"/>
+    </row>
+    <row r="72" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3" t="s">
         <v>165</v>
       </c>
@@ -12258,7 +12488,7 @@
         <v>83</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>171</v>
@@ -12276,13 +12506,16 @@
       <c r="K72" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L72" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M72" s="36"/>
-      <c r="P72"/>
-    </row>
-    <row r="73" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L72" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M72" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" s="36"/>
+      <c r="Q72"/>
+    </row>
+    <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3" t="s">
         <v>165</v>
       </c>
@@ -12296,7 +12529,7 @@
         <v>87</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>166</v>
@@ -12316,13 +12549,14 @@
       <c r="K73" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L73" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M73" s="36"/>
-      <c r="P73"/>
-    </row>
-    <row r="74" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L73" s="60"/>
+      <c r="M73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" s="36"/>
+      <c r="Q73"/>
+    </row>
+    <row r="74" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3" t="s">
         <v>165</v>
       </c>
@@ -12336,7 +12570,7 @@
         <v>87</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>166</v>
@@ -12356,13 +12590,14 @@
       <c r="K74" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L74" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M74" s="36"/>
-      <c r="P74"/>
-    </row>
-    <row r="75" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L74" s="61"/>
+      <c r="M74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" s="36"/>
+      <c r="Q74"/>
+    </row>
+    <row r="75" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3" t="s">
         <v>165</v>
       </c>
@@ -12376,7 +12611,7 @@
         <v>87</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>171</v>
@@ -12394,13 +12629,16 @@
       <c r="K75" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L75" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M75" s="36"/>
-      <c r="P75"/>
-    </row>
-    <row r="76" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L75" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" s="36"/>
+      <c r="Q75"/>
+    </row>
+    <row r="76" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3" t="s">
         <v>165</v>
       </c>
@@ -12414,7 +12652,7 @@
         <v>87</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>171</v>
@@ -12432,13 +12670,16 @@
       <c r="K76" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L76" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M76" s="36"/>
-      <c r="P76"/>
-    </row>
-    <row r="77" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L76" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M76" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" s="36"/>
+      <c r="Q76"/>
+    </row>
+    <row r="77" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3" t="s">
         <v>165</v>
       </c>
@@ -12452,7 +12693,7 @@
         <v>87</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>171</v>
@@ -12470,13 +12711,16 @@
       <c r="K77" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L77" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M77" s="36"/>
-      <c r="P77"/>
-    </row>
-    <row r="78" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L77" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N77" s="36"/>
+      <c r="Q77"/>
+    </row>
+    <row r="78" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3" t="s">
         <v>165</v>
       </c>
@@ -12490,7 +12734,7 @@
         <v>87</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>171</v>
@@ -12508,13 +12752,16 @@
       <c r="K78" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L78" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M78" s="36"/>
-      <c r="P78"/>
-    </row>
-    <row r="79" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L78" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M78" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" s="36"/>
+      <c r="Q78"/>
+    </row>
+    <row r="79" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3" t="s">
         <v>165</v>
       </c>
@@ -12528,7 +12775,7 @@
         <v>87</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>171</v>
@@ -12546,13 +12793,16 @@
       <c r="K79" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L79" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M79" s="36"/>
-      <c r="P79"/>
-    </row>
-    <row r="80" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L79" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M79" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N79" s="36"/>
+      <c r="Q79"/>
+    </row>
+    <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3" t="s">
         <v>165</v>
       </c>
@@ -12566,7 +12816,7 @@
         <v>93</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>166</v>
@@ -12586,13 +12836,14 @@
       <c r="K80" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L80" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M80" s="36"/>
-      <c r="P80"/>
-    </row>
-    <row r="81" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L80" s="60"/>
+      <c r="M80" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N80" s="36"/>
+      <c r="Q80"/>
+    </row>
+    <row r="81" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3" t="s">
         <v>165</v>
       </c>
@@ -12606,7 +12857,7 @@
         <v>93</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>166</v>
@@ -12626,13 +12877,14 @@
       <c r="K81" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L81" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M81" s="36"/>
-      <c r="P81"/>
-    </row>
-    <row r="82" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L81" s="61"/>
+      <c r="M81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" s="36"/>
+      <c r="Q81"/>
+    </row>
+    <row r="82" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="3" t="s">
         <v>165</v>
       </c>
@@ -12646,7 +12898,7 @@
         <v>93</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>171</v>
@@ -12664,13 +12916,16 @@
       <c r="K82" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L82" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M82" s="36"/>
-      <c r="P82"/>
-    </row>
-    <row r="83" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L82" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M82" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N82" s="36"/>
+      <c r="Q82"/>
+    </row>
+    <row r="83" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3" t="s">
         <v>165</v>
       </c>
@@ -12684,7 +12939,7 @@
         <v>93</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>171</v>
@@ -12702,13 +12957,16 @@
       <c r="K83" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L83" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M83" s="36"/>
-      <c r="P83"/>
-    </row>
-    <row r="84" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L83" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N83" s="36"/>
+      <c r="Q83"/>
+    </row>
+    <row r="84" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3" t="s">
         <v>165</v>
       </c>
@@ -12722,7 +12980,7 @@
         <v>93</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>171</v>
@@ -12740,13 +12998,16 @@
       <c r="K84" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L84" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M84" s="36"/>
-      <c r="P84"/>
-    </row>
-    <row r="85" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L84" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M84" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N84" s="36"/>
+      <c r="Q84"/>
+    </row>
+    <row r="85" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3" t="s">
         <v>165</v>
       </c>
@@ -12760,7 +13021,7 @@
         <v>93</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>171</v>
@@ -12778,13 +13039,16 @@
       <c r="K85" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L85" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M85" s="36"/>
-      <c r="P85"/>
-    </row>
-    <row r="86" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L85" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M85" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N85" s="36"/>
+      <c r="Q85"/>
+    </row>
+    <row r="86" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3" t="s">
         <v>165</v>
       </c>
@@ -12798,7 +13062,7 @@
         <v>93</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>171</v>
@@ -12816,13 +13080,16 @@
       <c r="K86" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L86" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M86" s="36"/>
-      <c r="P86"/>
-    </row>
-    <row r="87" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L86" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M86" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N86" s="36"/>
+      <c r="Q86"/>
+    </row>
+    <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="3" t="s">
         <v>165</v>
       </c>
@@ -12836,7 +13103,7 @@
         <v>97</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>166</v>
@@ -12856,13 +13123,14 @@
       <c r="K87" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L87" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M87" s="36"/>
-      <c r="P87"/>
-    </row>
-    <row r="88" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L87" s="60"/>
+      <c r="M87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N87" s="36"/>
+      <c r="Q87"/>
+    </row>
+    <row r="88" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
         <v>165</v>
       </c>
@@ -12876,7 +13144,7 @@
         <v>97</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>166</v>
@@ -12896,13 +13164,14 @@
       <c r="K88" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L88" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M88" s="36"/>
-      <c r="P88"/>
-    </row>
-    <row r="89" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L88" s="61"/>
+      <c r="M88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N88" s="36"/>
+      <c r="Q88"/>
+    </row>
+    <row r="89" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3" t="s">
         <v>165</v>
       </c>
@@ -12916,7 +13185,7 @@
         <v>97</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>171</v>
@@ -12934,13 +13203,16 @@
       <c r="K89" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L89" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M89" s="36"/>
-      <c r="P89"/>
-    </row>
-    <row r="90" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L89" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M89" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N89" s="36"/>
+      <c r="Q89"/>
+    </row>
+    <row r="90" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3" t="s">
         <v>165</v>
       </c>
@@ -12954,7 +13226,7 @@
         <v>97</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>171</v>
@@ -12972,13 +13244,16 @@
       <c r="K90" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L90" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M90" s="36"/>
-      <c r="P90"/>
-    </row>
-    <row r="91" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L90" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M90" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N90" s="36"/>
+      <c r="Q90"/>
+    </row>
+    <row r="91" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="3" t="s">
         <v>165</v>
       </c>
@@ -12992,7 +13267,7 @@
         <v>97</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>171</v>
@@ -13010,13 +13285,16 @@
       <c r="K91" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L91" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M91" s="36"/>
-      <c r="P91"/>
-    </row>
-    <row r="92" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L91" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N91" s="36"/>
+      <c r="Q91"/>
+    </row>
+    <row r="92" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="3" t="s">
         <v>165</v>
       </c>
@@ -13030,7 +13308,7 @@
         <v>97</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>171</v>
@@ -13048,13 +13326,16 @@
       <c r="K92" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L92" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M92" s="36"/>
-      <c r="P92"/>
-    </row>
-    <row r="93" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L92" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M92" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N92" s="36"/>
+      <c r="Q92"/>
+    </row>
+    <row r="93" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3" t="s">
         <v>165</v>
       </c>
@@ -13068,7 +13349,7 @@
         <v>97</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>171</v>
@@ -13086,13 +13367,16 @@
       <c r="K93" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L93" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M93" s="36"/>
-      <c r="P93"/>
-    </row>
-    <row r="94" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L93" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M93" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N93" s="36"/>
+      <c r="Q93"/>
+    </row>
+    <row r="94" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3" t="s">
         <v>165</v>
       </c>
@@ -13106,7 +13390,7 @@
         <v>101</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>166</v>
@@ -13126,13 +13410,14 @@
       <c r="K94" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L94" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M94" s="36"/>
-      <c r="P94"/>
-    </row>
-    <row r="95" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L94" s="60"/>
+      <c r="M94" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N94" s="36"/>
+      <c r="Q94"/>
+    </row>
+    <row r="95" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3" t="s">
         <v>165</v>
       </c>
@@ -13146,7 +13431,7 @@
         <v>101</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>166</v>
@@ -13166,13 +13451,14 @@
       <c r="K95" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L95" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M95" s="36"/>
-      <c r="P95"/>
-    </row>
-    <row r="96" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L95" s="61"/>
+      <c r="M95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N95" s="36"/>
+      <c r="Q95"/>
+    </row>
+    <row r="96" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3" t="s">
         <v>165</v>
       </c>
@@ -13186,7 +13472,7 @@
         <v>101</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>171</v>
@@ -13204,13 +13490,16 @@
       <c r="K96" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L96" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M96" s="36"/>
-      <c r="P96"/>
-    </row>
-    <row r="97" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L96" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M96" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N96" s="36"/>
+      <c r="Q96"/>
+    </row>
+    <row r="97" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3" t="s">
         <v>165</v>
       </c>
@@ -13224,7 +13513,7 @@
         <v>101</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>171</v>
@@ -13242,13 +13531,16 @@
       <c r="K97" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L97" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M97" s="36"/>
-      <c r="P97"/>
-    </row>
-    <row r="98" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L97" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N97" s="36"/>
+      <c r="Q97"/>
+    </row>
+    <row r="98" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3" t="s">
         <v>165</v>
       </c>
@@ -13262,7 +13554,7 @@
         <v>101</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>171</v>
@@ -13280,13 +13572,16 @@
       <c r="K98" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L98" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M98" s="36"/>
-      <c r="P98"/>
-    </row>
-    <row r="99" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L98" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M98" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N98" s="36"/>
+      <c r="Q98"/>
+    </row>
+    <row r="99" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3" t="s">
         <v>165</v>
       </c>
@@ -13300,7 +13595,7 @@
         <v>101</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>171</v>
@@ -13318,13 +13613,16 @@
       <c r="K99" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L99" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M99" s="36"/>
-      <c r="P99"/>
-    </row>
-    <row r="100" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L99" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N99" s="36"/>
+      <c r="Q99"/>
+    </row>
+    <row r="100" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3" t="s">
         <v>165</v>
       </c>
@@ -13338,7 +13636,7 @@
         <v>101</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>171</v>
@@ -13356,13 +13654,16 @@
       <c r="K100" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L100" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M100" s="36"/>
-      <c r="P100"/>
-    </row>
-    <row r="101" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L100" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M100" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N100" s="36"/>
+      <c r="Q100"/>
+    </row>
+    <row r="101" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3" t="s">
         <v>194</v>
       </c>
@@ -13376,7 +13677,7 @@
         <v>106</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>166</v>
@@ -13396,13 +13697,14 @@
       <c r="K101" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L101" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M101" s="36"/>
-      <c r="P101"/>
-    </row>
-    <row r="102" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L101" s="60"/>
+      <c r="M101" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" s="36"/>
+      <c r="Q101"/>
+    </row>
+    <row r="102" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3" t="s">
         <v>194</v>
       </c>
@@ -13416,7 +13718,7 @@
         <v>106</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>166</v>
@@ -13436,13 +13738,14 @@
       <c r="K102" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L102" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M102" s="36"/>
-      <c r="P102"/>
-    </row>
-    <row r="103" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L102" s="61"/>
+      <c r="M102" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" s="36"/>
+      <c r="Q102"/>
+    </row>
+    <row r="103" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
         <v>194</v>
       </c>
@@ -13456,7 +13759,7 @@
         <v>106</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>171</v>
@@ -13474,13 +13777,16 @@
       <c r="K103" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L103" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M103" s="36"/>
-      <c r="P103"/>
-    </row>
-    <row r="104" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L103" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" s="36"/>
+      <c r="Q103"/>
+    </row>
+    <row r="104" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
         <v>194</v>
       </c>
@@ -13494,7 +13800,7 @@
         <v>106</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>171</v>
@@ -13512,13 +13818,16 @@
       <c r="K104" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L104" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M104" s="36"/>
-      <c r="P104"/>
-    </row>
-    <row r="105" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L104" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M104" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N104" s="36"/>
+      <c r="Q104"/>
+    </row>
+    <row r="105" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3" t="s">
         <v>194</v>
       </c>
@@ -13532,7 +13841,7 @@
         <v>106</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>171</v>
@@ -13550,13 +13859,16 @@
       <c r="K105" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L105" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M105" s="36"/>
-      <c r="P105"/>
-    </row>
-    <row r="106" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L105" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M105" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N105" s="36"/>
+      <c r="Q105"/>
+    </row>
+    <row r="106" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
         <v>194</v>
       </c>
@@ -13570,7 +13882,7 @@
         <v>106</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>171</v>
@@ -13588,13 +13900,16 @@
       <c r="K106" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L106" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M106" s="36"/>
-      <c r="P106"/>
-    </row>
-    <row r="107" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L106" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M106" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N106" s="36"/>
+      <c r="Q106"/>
+    </row>
+    <row r="107" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
         <v>194</v>
       </c>
@@ -13608,7 +13923,7 @@
         <v>106</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>171</v>
@@ -13626,13 +13941,16 @@
       <c r="K107" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L107" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M107" s="36"/>
-      <c r="P107"/>
-    </row>
-    <row r="108" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L107" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N107" s="36"/>
+      <c r="Q107"/>
+    </row>
+    <row r="108" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
         <v>194</v>
       </c>
@@ -13646,7 +13964,7 @@
         <v>111</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>166</v>
@@ -13666,13 +13984,14 @@
       <c r="K108" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L108" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M108" s="36"/>
-      <c r="P108"/>
-    </row>
-    <row r="109" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L108" s="60"/>
+      <c r="M108" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N108" s="36"/>
+      <c r="Q108"/>
+    </row>
+    <row r="109" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
         <v>194</v>
       </c>
@@ -13686,7 +14005,7 @@
         <v>111</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>166</v>
@@ -13706,13 +14025,14 @@
       <c r="K109" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L109" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M109" s="36"/>
-      <c r="P109"/>
-    </row>
-    <row r="110" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L109" s="61"/>
+      <c r="M109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N109" s="36"/>
+      <c r="Q109"/>
+    </row>
+    <row r="110" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
         <v>194</v>
       </c>
@@ -13726,7 +14046,7 @@
         <v>111</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>171</v>
@@ -13744,13 +14064,16 @@
       <c r="K110" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L110" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M110" s="36"/>
-      <c r="P110"/>
-    </row>
-    <row r="111" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L110" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M110" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N110" s="36"/>
+      <c r="Q110"/>
+    </row>
+    <row r="111" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3" t="s">
         <v>194</v>
       </c>
@@ -13764,7 +14087,7 @@
         <v>111</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>171</v>
@@ -13782,13 +14105,16 @@
       <c r="K111" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L111" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M111" s="36"/>
-      <c r="P111"/>
-    </row>
-    <row r="112" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L111" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N111" s="36"/>
+      <c r="Q111"/>
+    </row>
+    <row r="112" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
         <v>194</v>
       </c>
@@ -13802,7 +14128,7 @@
         <v>111</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>171</v>
@@ -13820,13 +14146,16 @@
       <c r="K112" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L112" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M112" s="36"/>
-      <c r="P112"/>
-    </row>
-    <row r="113" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L112" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M112" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N112" s="36"/>
+      <c r="Q112"/>
+    </row>
+    <row r="113" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
         <v>194</v>
       </c>
@@ -13840,7 +14169,7 @@
         <v>111</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>171</v>
@@ -13858,13 +14187,16 @@
       <c r="K113" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L113" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M113" s="36"/>
-      <c r="P113"/>
-    </row>
-    <row r="114" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L113" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M113" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N113" s="36"/>
+      <c r="Q113"/>
+    </row>
+    <row r="114" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
         <v>194</v>
       </c>
@@ -13878,7 +14210,7 @@
         <v>111</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>171</v>
@@ -13896,13 +14228,16 @@
       <c r="K114" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L114" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M114" s="36"/>
-      <c r="P114"/>
-    </row>
-    <row r="115" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L114" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M114" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N114" s="36"/>
+      <c r="Q114"/>
+    </row>
+    <row r="115" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
         <v>194</v>
       </c>
@@ -13916,7 +14251,7 @@
         <v>115</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>166</v>
@@ -13936,13 +14271,14 @@
       <c r="K115" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L115" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M115" s="36"/>
-      <c r="P115"/>
-    </row>
-    <row r="116" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L115" s="60"/>
+      <c r="M115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N115" s="36"/>
+      <c r="Q115"/>
+    </row>
+    <row r="116" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
         <v>194</v>
       </c>
@@ -13956,7 +14292,7 @@
         <v>115</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>166</v>
@@ -13976,13 +14312,14 @@
       <c r="K116" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L116" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M116" s="36"/>
-      <c r="P116"/>
-    </row>
-    <row r="117" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L116" s="61"/>
+      <c r="M116" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N116" s="36"/>
+      <c r="Q116"/>
+    </row>
+    <row r="117" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
         <v>194</v>
       </c>
@@ -13996,7 +14333,7 @@
         <v>115</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>171</v>
@@ -14014,13 +14351,16 @@
       <c r="K117" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L117" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M117" s="36"/>
-      <c r="P117"/>
-    </row>
-    <row r="118" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L117" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N117" s="36"/>
+      <c r="Q117"/>
+    </row>
+    <row r="118" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
         <v>194</v>
       </c>
@@ -14034,7 +14374,7 @@
         <v>115</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>171</v>
@@ -14052,13 +14392,16 @@
       <c r="K118" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L118" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M118" s="36"/>
-      <c r="P118"/>
-    </row>
-    <row r="119" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L118" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M118" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N118" s="36"/>
+      <c r="Q118"/>
+    </row>
+    <row r="119" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
         <v>194</v>
       </c>
@@ -14072,7 +14415,7 @@
         <v>115</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>171</v>
@@ -14090,13 +14433,16 @@
       <c r="K119" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L119" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M119" s="36"/>
-      <c r="P119"/>
-    </row>
-    <row r="120" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L119" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N119" s="36"/>
+      <c r="Q119"/>
+    </row>
+    <row r="120" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
         <v>194</v>
       </c>
@@ -14110,7 +14456,7 @@
         <v>115</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>171</v>
@@ -14128,13 +14474,16 @@
       <c r="K120" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L120" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M120" s="36"/>
-      <c r="P120"/>
-    </row>
-    <row r="121" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L120" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M120" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N120" s="36"/>
+      <c r="Q120"/>
+    </row>
+    <row r="121" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3" t="s">
         <v>194</v>
       </c>
@@ -14148,7 +14497,7 @@
         <v>115</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>171</v>
@@ -14166,13 +14515,16 @@
       <c r="K121" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L121" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M121" s="36"/>
-      <c r="P121"/>
-    </row>
-    <row r="122" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L121" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N121" s="36"/>
+      <c r="Q121"/>
+    </row>
+    <row r="122" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
         <v>194</v>
       </c>
@@ -14186,7 +14538,7 @@
         <v>123</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>166</v>
@@ -14206,13 +14558,14 @@
       <c r="K122" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L122" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M122" s="36"/>
-      <c r="P122"/>
-    </row>
-    <row r="123" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L122" s="60"/>
+      <c r="M122" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N122" s="36"/>
+      <c r="Q122"/>
+    </row>
+    <row r="123" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
         <v>194</v>
       </c>
@@ -14226,7 +14579,7 @@
         <v>123</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>166</v>
@@ -14246,13 +14599,14 @@
       <c r="K123" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L123" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M123" s="36"/>
-      <c r="P123"/>
-    </row>
-    <row r="124" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L123" s="61"/>
+      <c r="M123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N123" s="36"/>
+      <c r="Q123"/>
+    </row>
+    <row r="124" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
         <v>194</v>
       </c>
@@ -14266,7 +14620,7 @@
         <v>123</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>171</v>
@@ -14284,13 +14638,16 @@
       <c r="K124" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L124" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M124" s="36"/>
-      <c r="P124"/>
-    </row>
-    <row r="125" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L124" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M124" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N124" s="36"/>
+      <c r="Q124"/>
+    </row>
+    <row r="125" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
         <v>194</v>
       </c>
@@ -14304,7 +14661,7 @@
         <v>123</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>171</v>
@@ -14322,13 +14679,16 @@
       <c r="K125" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L125" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M125" s="36"/>
-      <c r="P125"/>
-    </row>
-    <row r="126" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L125" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N125" s="36"/>
+      <c r="Q125"/>
+    </row>
+    <row r="126" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
         <v>194</v>
       </c>
@@ -14342,7 +14702,7 @@
         <v>123</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>171</v>
@@ -14360,13 +14720,16 @@
       <c r="K126" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L126" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M126" s="36"/>
-      <c r="P126"/>
-    </row>
-    <row r="127" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L126" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M126" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N126" s="36"/>
+      <c r="Q126"/>
+    </row>
+    <row r="127" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
         <v>194</v>
       </c>
@@ -14380,7 +14743,7 @@
         <v>123</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>171</v>
@@ -14398,13 +14761,16 @@
       <c r="K127" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L127" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M127" s="36"/>
-      <c r="P127"/>
-    </row>
-    <row r="128" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L127" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N127" s="36"/>
+      <c r="Q127"/>
+    </row>
+    <row r="128" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
         <v>194</v>
       </c>
@@ -14418,7 +14784,7 @@
         <v>123</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>171</v>
@@ -14436,13 +14802,16 @@
       <c r="K128" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L128" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M128" s="36"/>
-      <c r="P128"/>
-    </row>
-    <row r="129" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L128" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M128" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N128" s="36"/>
+      <c r="Q128"/>
+    </row>
+    <row r="129" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
         <v>194</v>
       </c>
@@ -14456,7 +14825,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>166</v>
@@ -14476,13 +14845,14 @@
       <c r="K129" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L129" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M129" s="36"/>
-      <c r="P129"/>
-    </row>
-    <row r="130" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L129" s="60"/>
+      <c r="M129" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N129" s="36"/>
+      <c r="Q129"/>
+    </row>
+    <row r="130" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
         <v>194</v>
       </c>
@@ -14496,7 +14866,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>166</v>
@@ -14516,13 +14886,14 @@
       <c r="K130" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L130" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M130" s="36"/>
-      <c r="P130"/>
-    </row>
-    <row r="131" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L130" s="61"/>
+      <c r="M130" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N130" s="36"/>
+      <c r="Q130"/>
+    </row>
+    <row r="131" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
         <v>194</v>
       </c>
@@ -14536,7 +14907,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>171</v>
@@ -14554,13 +14925,16 @@
       <c r="K131" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L131" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M131" s="36"/>
-      <c r="P131"/>
-    </row>
-    <row r="132" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L131" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N131" s="36"/>
+      <c r="Q131"/>
+    </row>
+    <row r="132" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
         <v>194</v>
       </c>
@@ -14574,7 +14948,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>171</v>
@@ -14592,13 +14966,16 @@
       <c r="K132" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L132" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M132" s="36"/>
-      <c r="P132"/>
-    </row>
-    <row r="133" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L132" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M132" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N132" s="36"/>
+      <c r="Q132"/>
+    </row>
+    <row r="133" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
         <v>194</v>
       </c>
@@ -14612,7 +14989,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>171</v>
@@ -14630,13 +15007,16 @@
       <c r="K133" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L133" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M133" s="36"/>
-      <c r="P133"/>
-    </row>
-    <row r="134" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L133" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N133" s="36"/>
+      <c r="Q133"/>
+    </row>
+    <row r="134" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3" t="s">
         <v>194</v>
       </c>
@@ -14650,7 +15030,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>171</v>
@@ -14668,13 +15048,16 @@
       <c r="K134" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L134" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M134" s="36"/>
-      <c r="P134"/>
-    </row>
-    <row r="135" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L134" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M134" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N134" s="36"/>
+      <c r="Q134"/>
+    </row>
+    <row r="135" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3" t="s">
         <v>194</v>
       </c>
@@ -14688,7 +15071,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>171</v>
@@ -14706,13 +15089,16 @@
       <c r="K135" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L135" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M135" s="36"/>
-      <c r="P135"/>
-    </row>
-    <row r="136" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L135" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N135" s="36"/>
+      <c r="Q135"/>
+    </row>
+    <row r="136" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3" t="s">
         <v>194</v>
       </c>
@@ -14726,7 +15112,7 @@
         <v>133</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>166</v>
@@ -14746,13 +15132,14 @@
       <c r="K136" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L136" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M136" s="36"/>
-      <c r="P136"/>
-    </row>
-    <row r="137" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L136" s="60"/>
+      <c r="M136" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N136" s="36"/>
+      <c r="Q136"/>
+    </row>
+    <row r="137" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
         <v>194</v>
       </c>
@@ -14766,7 +15153,7 @@
         <v>133</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>166</v>
@@ -14786,13 +15173,14 @@
       <c r="K137" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L137" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M137" s="36"/>
-      <c r="P137"/>
-    </row>
-    <row r="138" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L137" s="61"/>
+      <c r="M137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N137" s="36"/>
+      <c r="Q137"/>
+    </row>
+    <row r="138" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3" t="s">
         <v>194</v>
       </c>
@@ -14806,7 +15194,7 @@
         <v>133</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>171</v>
@@ -14824,13 +15212,16 @@
       <c r="K138" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L138" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M138" s="36"/>
-      <c r="P138"/>
-    </row>
-    <row r="139" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L138" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M138" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N138" s="36"/>
+      <c r="Q138"/>
+    </row>
+    <row r="139" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3" t="s">
         <v>194</v>
       </c>
@@ -14844,7 +15235,7 @@
         <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>171</v>
@@ -14862,13 +15253,16 @@
       <c r="K139" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L139" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M139" s="36"/>
-      <c r="P139"/>
-    </row>
-    <row r="140" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L139" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N139" s="36"/>
+      <c r="Q139"/>
+    </row>
+    <row r="140" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3" t="s">
         <v>194</v>
       </c>
@@ -14882,7 +15276,7 @@
         <v>133</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>171</v>
@@ -14900,13 +15294,16 @@
       <c r="K140" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L140" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M140" s="36"/>
-      <c r="P140"/>
-    </row>
-    <row r="141" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L140" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M140" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N140" s="36"/>
+      <c r="Q140"/>
+    </row>
+    <row r="141" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3" t="s">
         <v>194</v>
       </c>
@@ -14920,7 +15317,7 @@
         <v>133</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>171</v>
@@ -14938,13 +15335,16 @@
       <c r="K141" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L141" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M141" s="36"/>
-      <c r="P141"/>
-    </row>
-    <row r="142" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L141" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N141" s="36"/>
+      <c r="Q141"/>
+    </row>
+    <row r="142" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
         <v>194</v>
       </c>
@@ -14958,7 +15358,7 @@
         <v>133</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>171</v>
@@ -14976,13 +15376,16 @@
       <c r="K142" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L142" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M142" s="36"/>
-      <c r="P142"/>
-    </row>
-    <row r="143" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L142" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M142" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N142" s="36"/>
+      <c r="Q142"/>
+    </row>
+    <row r="143" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
         <v>194</v>
       </c>
@@ -14996,7 +15399,7 @@
         <v>137</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>166</v>
@@ -15016,13 +15419,14 @@
       <c r="K143" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L143" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M143" s="36"/>
-      <c r="P143"/>
-    </row>
-    <row r="144" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L143" s="60"/>
+      <c r="M143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N143" s="36"/>
+      <c r="Q143"/>
+    </row>
+    <row r="144" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3" t="s">
         <v>194</v>
       </c>
@@ -15036,7 +15440,7 @@
         <v>137</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>166</v>
@@ -15056,13 +15460,14 @@
       <c r="K144" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L144" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M144" s="36"/>
-      <c r="P144"/>
-    </row>
-    <row r="145" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L144" s="61"/>
+      <c r="M144" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N144" s="36"/>
+      <c r="Q144"/>
+    </row>
+    <row r="145" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3" t="s">
         <v>194</v>
       </c>
@@ -15076,7 +15481,7 @@
         <v>137</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>171</v>
@@ -15094,13 +15499,16 @@
       <c r="K145" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L145" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M145" s="36"/>
-      <c r="P145"/>
-    </row>
-    <row r="146" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L145" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N145" s="36"/>
+      <c r="Q145"/>
+    </row>
+    <row r="146" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3" t="s">
         <v>194</v>
       </c>
@@ -15114,7 +15522,7 @@
         <v>137</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>171</v>
@@ -15132,13 +15540,16 @@
       <c r="K146" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L146" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M146" s="36"/>
-      <c r="P146"/>
-    </row>
-    <row r="147" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L146" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M146" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N146" s="36"/>
+      <c r="Q146"/>
+    </row>
+    <row r="147" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3" t="s">
         <v>194</v>
       </c>
@@ -15152,7 +15563,7 @@
         <v>137</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>171</v>
@@ -15170,13 +15581,16 @@
       <c r="K147" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L147" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M147" s="36"/>
-      <c r="P147"/>
-    </row>
-    <row r="148" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L147" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N147" s="36"/>
+      <c r="Q147"/>
+    </row>
+    <row r="148" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3" t="s">
         <v>194</v>
       </c>
@@ -15190,7 +15604,7 @@
         <v>137</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>171</v>
@@ -15208,13 +15622,16 @@
       <c r="K148" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L148" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M148" s="36"/>
-      <c r="P148"/>
-    </row>
-    <row r="149" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L148" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M148" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N148" s="36"/>
+      <c r="Q148"/>
+    </row>
+    <row r="149" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3" t="s">
         <v>194</v>
       </c>
@@ -15228,7 +15645,7 @@
         <v>137</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>171</v>
@@ -15246,13 +15663,16 @@
       <c r="K149" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L149" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M149" s="36"/>
-      <c r="P149"/>
-    </row>
-    <row r="150" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L149" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M149" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N149" s="36"/>
+      <c r="Q149"/>
+    </row>
+    <row r="150" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3" t="s">
         <v>194</v>
       </c>
@@ -15266,7 +15686,7 @@
         <v>141</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>166</v>
@@ -15286,13 +15706,14 @@
       <c r="K150" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L150" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M150" s="36"/>
-      <c r="P150"/>
-    </row>
-    <row r="151" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L150" s="60"/>
+      <c r="M150" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N150" s="36"/>
+      <c r="Q150"/>
+    </row>
+    <row r="151" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3" t="s">
         <v>194</v>
       </c>
@@ -15306,7 +15727,7 @@
         <v>141</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>166</v>
@@ -15326,13 +15747,14 @@
       <c r="K151" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L151" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M151" s="36"/>
-      <c r="P151"/>
-    </row>
-    <row r="152" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L151" s="61"/>
+      <c r="M151" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N151" s="36"/>
+      <c r="Q151"/>
+    </row>
+    <row r="152" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3" t="s">
         <v>194</v>
       </c>
@@ -15346,7 +15768,7 @@
         <v>141</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>171</v>
@@ -15364,13 +15786,16 @@
       <c r="K152" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L152" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M152" s="36"/>
-      <c r="P152"/>
-    </row>
-    <row r="153" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L152" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M152" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N152" s="36"/>
+      <c r="Q152"/>
+    </row>
+    <row r="153" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3" t="s">
         <v>194</v>
       </c>
@@ -15384,7 +15809,7 @@
         <v>141</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>171</v>
@@ -15402,13 +15827,16 @@
       <c r="K153" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L153" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M153" s="36"/>
-      <c r="P153"/>
-    </row>
-    <row r="154" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L153" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N153" s="36"/>
+      <c r="Q153"/>
+    </row>
+    <row r="154" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3" t="s">
         <v>194</v>
       </c>
@@ -15422,7 +15850,7 @@
         <v>141</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>171</v>
@@ -15440,13 +15868,16 @@
       <c r="K154" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L154" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M154" s="36"/>
-      <c r="P154"/>
-    </row>
-    <row r="155" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L154" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M154" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N154" s="36"/>
+      <c r="Q154"/>
+    </row>
+    <row r="155" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3" t="s">
         <v>194</v>
       </c>
@@ -15460,7 +15891,7 @@
         <v>141</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>171</v>
@@ -15478,13 +15909,16 @@
       <c r="K155" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L155" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M155" s="36"/>
-      <c r="P155"/>
-    </row>
-    <row r="156" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L155" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N155" s="36"/>
+      <c r="Q155"/>
+    </row>
+    <row r="156" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
         <v>194</v>
       </c>
@@ -15498,7 +15932,7 @@
         <v>141</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>171</v>
@@ -15516,13 +15950,16 @@
       <c r="K156" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L156" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M156" s="36"/>
-      <c r="P156"/>
-    </row>
-    <row r="157" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L156" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M156" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N156" s="36"/>
+      <c r="Q156"/>
+    </row>
+    <row r="157" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3" t="s">
         <v>194</v>
       </c>
@@ -15536,7 +15973,7 @@
         <v>146</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>166</v>
@@ -15556,13 +15993,14 @@
       <c r="K157" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L157" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M157" s="36"/>
-      <c r="P157"/>
-    </row>
-    <row r="158" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L157" s="60"/>
+      <c r="M157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N157" s="36"/>
+      <c r="Q157"/>
+    </row>
+    <row r="158" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3" t="s">
         <v>194</v>
       </c>
@@ -15576,7 +16014,7 @@
         <v>146</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>166</v>
@@ -15596,13 +16034,14 @@
       <c r="K158" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L158" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M158" s="36"/>
-      <c r="P158"/>
-    </row>
-    <row r="159" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L158" s="61"/>
+      <c r="M158" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N158" s="36"/>
+      <c r="Q158"/>
+    </row>
+    <row r="159" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
         <v>194</v>
       </c>
@@ -15616,7 +16055,7 @@
         <v>146</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>171</v>
@@ -15634,13 +16073,16 @@
       <c r="K159" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L159" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M159" s="36"/>
-      <c r="P159"/>
-    </row>
-    <row r="160" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L159" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N159" s="36"/>
+      <c r="Q159"/>
+    </row>
+    <row r="160" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3" t="s">
         <v>194</v>
       </c>
@@ -15654,7 +16096,7 @@
         <v>146</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>171</v>
@@ -15672,13 +16114,16 @@
       <c r="K160" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L160" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M160" s="36"/>
-      <c r="P160"/>
-    </row>
-    <row r="161" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L160" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M160" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N160" s="36"/>
+      <c r="Q160"/>
+    </row>
+    <row r="161" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3" t="s">
         <v>194</v>
       </c>
@@ -15692,7 +16137,7 @@
         <v>146</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>171</v>
@@ -15710,13 +16155,16 @@
       <c r="K161" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L161" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M161" s="36"/>
-      <c r="P161"/>
-    </row>
-    <row r="162" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L161" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M161" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N161" s="36"/>
+      <c r="Q161"/>
+    </row>
+    <row r="162" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
         <v>194</v>
       </c>
@@ -15730,7 +16178,7 @@
         <v>146</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>171</v>
@@ -15748,13 +16196,16 @@
       <c r="K162" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L162" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M162" s="36"/>
-      <c r="P162"/>
-    </row>
-    <row r="163" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L162" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M162" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N162" s="36"/>
+      <c r="Q162"/>
+    </row>
+    <row r="163" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3" t="s">
         <v>194</v>
       </c>
@@ -15768,7 +16219,7 @@
         <v>146</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>171</v>
@@ -15786,13 +16237,16 @@
       <c r="K163" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="L163" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M163" s="36"/>
-      <c r="P163"/>
-    </row>
-    <row r="164" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L163" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M163" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N163" s="36"/>
+      <c r="Q163"/>
+    </row>
+    <row r="164" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="3" t="s">
         <v>194</v>
       </c>
@@ -15800,13 +16254,13 @@
         <v>24</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>166</v>
@@ -15826,13 +16280,14 @@
       <c r="K164" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L164" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M164" s="7"/>
-      <c r="N164" s="3"/>
-    </row>
-    <row r="165" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L164" s="60"/>
+      <c r="M164" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N164" s="7"/>
+      <c r="O164" s="3"/>
+    </row>
+    <row r="165" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3" t="s">
         <v>194</v>
       </c>
@@ -15840,13 +16295,13 @@
         <v>24</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>166</v>
@@ -15866,13 +16321,14 @@
       <c r="K165" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L165" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M165" s="7"/>
-      <c r="N165" s="3"/>
-    </row>
-    <row r="166" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L165" s="61"/>
+      <c r="M165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N165" s="7"/>
+      <c r="O165" s="3"/>
+    </row>
+    <row r="166" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3" t="s">
         <v>194</v>
       </c>
@@ -15880,13 +16336,13 @@
         <v>24</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>171</v>
@@ -15904,13 +16360,16 @@
       <c r="K166" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L166" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M166" s="7"/>
-      <c r="N166" s="3"/>
-    </row>
-    <row r="167" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L166" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M166" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N166" s="7"/>
+      <c r="O166" s="3"/>
+    </row>
+    <row r="167" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="3" t="s">
         <v>194</v>
       </c>
@@ -15918,13 +16377,13 @@
         <v>24</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>171</v>
@@ -15942,13 +16401,16 @@
       <c r="K167" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L167" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M167" s="7"/>
-      <c r="N167" s="3"/>
-    </row>
-    <row r="168" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L167" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M167" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N167" s="7"/>
+      <c r="O167" s="3"/>
+    </row>
+    <row r="168" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="3" t="s">
         <v>194</v>
       </c>
@@ -15956,13 +16418,13 @@
         <v>24</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>171</v>
@@ -15980,13 +16442,16 @@
       <c r="K168" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L168" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M168" s="7"/>
-      <c r="N168" s="3"/>
-    </row>
-    <row r="169" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L168" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M168" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N168" s="7"/>
+      <c r="O168" s="3"/>
+    </row>
+    <row r="169" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3" t="s">
         <v>194</v>
       </c>
@@ -15994,13 +16459,13 @@
         <v>24</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>171</v>
@@ -16018,13 +16483,16 @@
       <c r="K169" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L169" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M169" s="7"/>
-      <c r="N169" s="3"/>
-    </row>
-    <row r="170" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L169" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M169" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N169" s="7"/>
+      <c r="O169" s="3"/>
+    </row>
+    <row r="170" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3" t="s">
         <v>194</v>
       </c>
@@ -16032,13 +16500,13 @@
         <v>24</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>171</v>
@@ -16056,13 +16524,16 @@
       <c r="K170" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L170" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M170" s="7"/>
-      <c r="N170" s="3"/>
-    </row>
-    <row r="171" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L170" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M170" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N170" s="7"/>
+      <c r="O170" s="3"/>
+    </row>
+    <row r="171" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3" t="s">
         <v>194</v>
       </c>
@@ -16070,13 +16541,13 @@
         <v>25</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>166</v>
@@ -16096,13 +16567,14 @@
       <c r="K171" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L171" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M171" s="7"/>
-      <c r="N171" s="3"/>
-    </row>
-    <row r="172" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L171" s="60"/>
+      <c r="M171" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N171" s="7"/>
+      <c r="O171" s="3"/>
+    </row>
+    <row r="172" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3" t="s">
         <v>194</v>
       </c>
@@ -16110,13 +16582,13 @@
         <v>25</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>166</v>
@@ -16136,13 +16608,14 @@
       <c r="K172" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L172" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M172" s="7"/>
-      <c r="N172" s="3"/>
-    </row>
-    <row r="173" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L172" s="61"/>
+      <c r="M172" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N172" s="7"/>
+      <c r="O172" s="3"/>
+    </row>
+    <row r="173" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3" t="s">
         <v>194</v>
       </c>
@@ -16150,13 +16623,13 @@
         <v>25</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>171</v>
@@ -16174,13 +16647,16 @@
       <c r="K173" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L173" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M173" s="7"/>
-      <c r="N173" s="3"/>
-    </row>
-    <row r="174" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L173" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M173" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N173" s="7"/>
+      <c r="O173" s="3"/>
+    </row>
+    <row r="174" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3" t="s">
         <v>194</v>
       </c>
@@ -16188,13 +16664,13 @@
         <v>25</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>171</v>
@@ -16212,13 +16688,16 @@
       <c r="K174" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L174" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M174" s="7"/>
-      <c r="N174" s="3"/>
-    </row>
-    <row r="175" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L174" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M174" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N174" s="7"/>
+      <c r="O174" s="3"/>
+    </row>
+    <row r="175" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3" t="s">
         <v>194</v>
       </c>
@@ -16226,13 +16705,13 @@
         <v>25</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>171</v>
@@ -16250,13 +16729,16 @@
       <c r="K175" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L175" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M175" s="7"/>
-      <c r="N175" s="3"/>
-    </row>
-    <row r="176" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L175" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M175" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N175" s="7"/>
+      <c r="O175" s="3"/>
+    </row>
+    <row r="176" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3" t="s">
         <v>194</v>
       </c>
@@ -16264,13 +16746,13 @@
         <v>25</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>171</v>
@@ -16288,13 +16770,16 @@
       <c r="K176" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L176" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M176" s="7"/>
-      <c r="N176" s="3"/>
-    </row>
-    <row r="177" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L176" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M176" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N176" s="7"/>
+      <c r="O176" s="3"/>
+    </row>
+    <row r="177" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3" t="s">
         <v>194</v>
       </c>
@@ -16302,13 +16787,13 @@
         <v>25</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>171</v>
@@ -16326,13 +16811,16 @@
       <c r="K177" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L177" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M177" s="7"/>
-      <c r="N177" s="3"/>
-    </row>
-    <row r="178" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L177" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M177" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N177" s="7"/>
+      <c r="O177" s="3"/>
+    </row>
+    <row r="178" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="3" t="s">
         <v>194</v>
       </c>
@@ -16340,13 +16828,13 @@
         <v>25</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>166</v>
@@ -16366,13 +16854,14 @@
       <c r="K178" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L178" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M178" s="7"/>
-      <c r="N178" s="3"/>
-    </row>
-    <row r="179" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L178" s="60"/>
+      <c r="M178" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N178" s="7"/>
+      <c r="O178" s="3"/>
+    </row>
+    <row r="179" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3" t="s">
         <v>194</v>
       </c>
@@ -16380,13 +16869,13 @@
         <v>26</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>166</v>
@@ -16406,13 +16895,14 @@
       <c r="K179" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L179" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M179" s="7"/>
-      <c r="N179" s="3"/>
-    </row>
-    <row r="180" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L179" s="61"/>
+      <c r="M179" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N179" s="7"/>
+      <c r="O179" s="3"/>
+    </row>
+    <row r="180" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3" t="s">
         <v>194</v>
       </c>
@@ -16420,13 +16910,13 @@
         <v>26</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>171</v>
@@ -16444,13 +16934,16 @@
       <c r="K180" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L180" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M180" s="7"/>
-      <c r="N180" s="3"/>
-    </row>
-    <row r="181" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L180" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M180" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N180" s="7"/>
+      <c r="O180" s="3"/>
+    </row>
+    <row r="181" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3" t="s">
         <v>194</v>
       </c>
@@ -16458,13 +16951,13 @@
         <v>26</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>171</v>
@@ -16482,13 +16975,16 @@
       <c r="K181" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L181" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M181" s="7"/>
-      <c r="N181" s="3"/>
-    </row>
-    <row r="182" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L181" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M181" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N181" s="7"/>
+      <c r="O181" s="3"/>
+    </row>
+    <row r="182" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3" t="s">
         <v>194</v>
       </c>
@@ -16496,13 +16992,13 @@
         <v>26</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>171</v>
@@ -16520,13 +17016,16 @@
       <c r="K182" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L182" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M182" s="7"/>
-      <c r="N182" s="3"/>
-    </row>
-    <row r="183" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L182" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M182" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N182" s="7"/>
+      <c r="O182" s="3"/>
+    </row>
+    <row r="183" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3" t="s">
         <v>194</v>
       </c>
@@ -16534,13 +17033,13 @@
         <v>26</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>171</v>
@@ -16558,13 +17057,16 @@
       <c r="K183" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L183" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M183" s="7"/>
-      <c r="N183" s="3"/>
-    </row>
-    <row r="184" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L183" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M183" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N183" s="7"/>
+      <c r="O183" s="3"/>
+    </row>
+    <row r="184" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3" t="s">
         <v>194</v>
       </c>
@@ -16572,13 +17074,13 @@
         <v>26</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>171</v>
@@ -16596,13 +17098,16 @@
       <c r="K184" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L184" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M184" s="7"/>
-      <c r="N184" s="3"/>
-    </row>
-    <row r="185" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L184" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M184" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N184" s="7"/>
+      <c r="O184" s="3"/>
+    </row>
+    <row r="185" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3" t="s">
         <v>194</v>
       </c>
@@ -16610,13 +17115,13 @@
         <v>26</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>166</v>
@@ -16636,13 +17141,14 @@
       <c r="K185" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L185" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M185" s="7"/>
-      <c r="N185" s="3"/>
-    </row>
-    <row r="186" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L185" s="60"/>
+      <c r="M185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N185" s="7"/>
+      <c r="O185" s="3"/>
+    </row>
+    <row r="186" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3" t="s">
         <v>194</v>
       </c>
@@ -16650,13 +17156,13 @@
         <v>27</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>166</v>
@@ -16676,13 +17182,14 @@
       <c r="K186" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L186" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M186" s="7"/>
-      <c r="N186" s="3"/>
-    </row>
-    <row r="187" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L186" s="61"/>
+      <c r="M186" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N186" s="7"/>
+      <c r="O186" s="3"/>
+    </row>
+    <row r="187" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3" t="s">
         <v>194</v>
       </c>
@@ -16690,13 +17197,13 @@
         <v>27</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>171</v>
@@ -16714,13 +17221,16 @@
       <c r="K187" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L187" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M187" s="7"/>
-      <c r="N187" s="3"/>
-    </row>
-    <row r="188" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L187" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N187" s="7"/>
+      <c r="O187" s="3"/>
+    </row>
+    <row r="188" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3" t="s">
         <v>194</v>
       </c>
@@ -16728,13 +17238,13 @@
         <v>27</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>171</v>
@@ -16752,13 +17262,16 @@
       <c r="K188" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L188" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M188" s="7"/>
-      <c r="N188" s="3"/>
-    </row>
-    <row r="189" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L188" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M188" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N188" s="7"/>
+      <c r="O188" s="3"/>
+    </row>
+    <row r="189" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3" t="s">
         <v>194</v>
       </c>
@@ -16766,13 +17279,13 @@
         <v>27</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>171</v>
@@ -16790,13 +17303,16 @@
       <c r="K189" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L189" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M189" s="7"/>
-      <c r="N189" s="3"/>
-    </row>
-    <row r="190" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L189" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M189" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N189" s="7"/>
+      <c r="O189" s="3"/>
+    </row>
+    <row r="190" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3" t="s">
         <v>194</v>
       </c>
@@ -16804,13 +17320,13 @@
         <v>27</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>171</v>
@@ -16828,13 +17344,16 @@
       <c r="K190" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L190" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M190" s="7"/>
-      <c r="N190" s="3"/>
-    </row>
-    <row r="191" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L190" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M190" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N190" s="7"/>
+      <c r="O190" s="3"/>
+    </row>
+    <row r="191" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3" t="s">
         <v>194</v>
       </c>
@@ -16842,13 +17361,13 @@
         <v>27</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>171</v>
@@ -16866,13 +17385,16 @@
       <c r="K191" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L191" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M191" s="7"/>
-      <c r="N191" s="3"/>
-    </row>
-    <row r="192" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L191" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M191" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N191" s="7"/>
+      <c r="O191" s="3"/>
+    </row>
+    <row r="192" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3" t="s">
         <v>194</v>
       </c>
@@ -16880,13 +17402,13 @@
         <v>27</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>166</v>
@@ -16906,13 +17428,14 @@
       <c r="K192" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L192" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M192" s="7"/>
-      <c r="N192" s="3"/>
-    </row>
-    <row r="193" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L192" s="60"/>
+      <c r="M192" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N192" s="7"/>
+      <c r="O192" s="3"/>
+    </row>
+    <row r="193" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3" t="s">
         <v>194</v>
       </c>
@@ -16920,13 +17443,13 @@
         <v>28</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>166</v>
@@ -16946,13 +17469,14 @@
       <c r="K193" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L193" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M193" s="7"/>
-      <c r="N193" s="3"/>
-    </row>
-    <row r="194" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L193" s="61"/>
+      <c r="M193" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N193" s="7"/>
+      <c r="O193" s="3"/>
+    </row>
+    <row r="194" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3" t="s">
         <v>194</v>
       </c>
@@ -16960,13 +17484,13 @@
         <v>28</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>171</v>
@@ -16984,13 +17508,16 @@
       <c r="K194" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L194" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M194" s="7"/>
-      <c r="N194" s="3"/>
-    </row>
-    <row r="195" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L194" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M194" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N194" s="7"/>
+      <c r="O194" s="3"/>
+    </row>
+    <row r="195" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3" t="s">
         <v>194</v>
       </c>
@@ -16998,13 +17525,13 @@
         <v>28</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>171</v>
@@ -17022,13 +17549,16 @@
       <c r="K195" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L195" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M195" s="7"/>
-      <c r="N195" s="3"/>
-    </row>
-    <row r="196" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L195" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M195" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N195" s="7"/>
+      <c r="O195" s="3"/>
+    </row>
+    <row r="196" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3" t="s">
         <v>194</v>
       </c>
@@ -17036,13 +17566,13 @@
         <v>28</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>171</v>
@@ -17060,13 +17590,16 @@
       <c r="K196" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L196" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M196" s="7"/>
-      <c r="N196" s="3"/>
-    </row>
-    <row r="197" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L196" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M196" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N196" s="7"/>
+      <c r="O196" s="3"/>
+    </row>
+    <row r="197" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3" t="s">
         <v>194</v>
       </c>
@@ -17074,13 +17607,13 @@
         <v>28</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>171</v>
@@ -17098,13 +17631,16 @@
       <c r="K197" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L197" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M197" s="7"/>
-      <c r="N197" s="3"/>
-    </row>
-    <row r="198" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L197" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M197" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N197" s="7"/>
+      <c r="O197" s="3"/>
+    </row>
+    <row r="198" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3" t="s">
         <v>194</v>
       </c>
@@ -17112,13 +17648,13 @@
         <v>28</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>171</v>
@@ -17136,13 +17672,16 @@
       <c r="K198" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L198" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M198" s="7"/>
-      <c r="N198" s="3"/>
-    </row>
-    <row r="199" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L198" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M198" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N198" s="7"/>
+      <c r="O198" s="3"/>
+    </row>
+    <row r="199" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3" t="s">
         <v>194</v>
       </c>
@@ -17150,13 +17689,13 @@
         <v>28</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>166</v>
@@ -17176,13 +17715,14 @@
       <c r="K199" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L199" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M199" s="7"/>
-      <c r="N199" s="3"/>
-    </row>
-    <row r="200" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L199" s="60"/>
+      <c r="M199" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N199" s="7"/>
+      <c r="O199" s="3"/>
+    </row>
+    <row r="200" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="3" t="s">
         <v>194</v>
       </c>
@@ -17190,13 +17730,13 @@
         <v>29</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>166</v>
@@ -17216,13 +17756,14 @@
       <c r="K200" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L200" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M200" s="7"/>
-      <c r="N200" s="3"/>
-    </row>
-    <row r="201" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L200" s="61"/>
+      <c r="M200" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N200" s="7"/>
+      <c r="O200" s="3"/>
+    </row>
+    <row r="201" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3" t="s">
         <v>194</v>
       </c>
@@ -17230,13 +17771,13 @@
         <v>29</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>171</v>
@@ -17254,13 +17795,16 @@
       <c r="K201" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L201" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M201" s="7"/>
-      <c r="N201" s="3"/>
-    </row>
-    <row r="202" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L201" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M201" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N201" s="7"/>
+      <c r="O201" s="3"/>
+    </row>
+    <row r="202" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3" t="s">
         <v>194</v>
       </c>
@@ -17268,13 +17812,13 @@
         <v>29</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>171</v>
@@ -17292,13 +17836,16 @@
       <c r="K202" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L202" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M202" s="7"/>
-      <c r="N202" s="3"/>
-    </row>
-    <row r="203" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L202" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M202" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N202" s="7"/>
+      <c r="O202" s="3"/>
+    </row>
+    <row r="203" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3" t="s">
         <v>194</v>
       </c>
@@ -17306,13 +17853,13 @@
         <v>29</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E203" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>171</v>
@@ -17330,12 +17877,15 @@
       <c r="K203" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L203" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M203" s="7"/>
-    </row>
-    <row r="204" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L203" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M203" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N203" s="7"/>
+    </row>
+    <row r="204" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3" t="s">
         <v>194</v>
       </c>
@@ -17343,13 +17893,13 @@
         <v>29</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E204" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>171</v>
@@ -17367,12 +17917,15 @@
       <c r="K204" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L204" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M204" s="7"/>
-    </row>
-    <row r="205" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L204" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M204" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N204" s="7"/>
+    </row>
+    <row r="205" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3" t="s">
         <v>194</v>
       </c>
@@ -17380,13 +17933,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E205" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>171</v>
@@ -17404,12 +17957,15 @@
       <c r="K205" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L205" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M205" s="7"/>
-    </row>
-    <row r="206" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L205" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M205" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N205" s="7"/>
+    </row>
+    <row r="206" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3" t="s">
         <v>194</v>
       </c>
@@ -17417,13 +17973,13 @@
         <v>29</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E206" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>166</v>
@@ -17443,12 +17999,13 @@
       <c r="K206" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L206" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M206" s="7"/>
-    </row>
-    <row r="207" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L206" s="60"/>
+      <c r="M206" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N206" s="7"/>
+    </row>
+    <row r="207" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3" t="s">
         <v>194</v>
       </c>
@@ -17456,13 +18013,13 @@
         <v>30</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E207" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>166</v>
@@ -17482,12 +18039,13 @@
       <c r="K207" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L207" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M207" s="7"/>
-    </row>
-    <row r="208" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L207" s="61"/>
+      <c r="M207" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N207" s="7"/>
+    </row>
+    <row r="208" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3" t="s">
         <v>194</v>
       </c>
@@ -17495,13 +18053,13 @@
         <v>30</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E208" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>171</v>
@@ -17519,12 +18077,15 @@
       <c r="K208" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L208" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M208" s="7"/>
-    </row>
-    <row r="209" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L208" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M208" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N208" s="7"/>
+    </row>
+    <row r="209" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3" t="s">
         <v>194</v>
       </c>
@@ -17532,13 +18093,13 @@
         <v>30</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E209" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>171</v>
@@ -17556,12 +18117,15 @@
       <c r="K209" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L209" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M209" s="7"/>
-    </row>
-    <row r="210" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L209" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M209" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N209" s="7"/>
+    </row>
+    <row r="210" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3" t="s">
         <v>194</v>
       </c>
@@ -17569,13 +18133,13 @@
         <v>30</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E210" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>171</v>
@@ -17593,12 +18157,15 @@
       <c r="K210" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L210" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M210" s="7"/>
-    </row>
-    <row r="211" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L210" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M210" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N210" s="7"/>
+    </row>
+    <row r="211" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3" t="s">
         <v>194</v>
       </c>
@@ -17606,13 +18173,13 @@
         <v>30</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E211" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>171</v>
@@ -17630,12 +18197,15 @@
       <c r="K211" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L211" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M211" s="7"/>
-    </row>
-    <row r="212" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L211" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M211" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N211" s="7"/>
+    </row>
+    <row r="212" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3" t="s">
         <v>194</v>
       </c>
@@ -17643,13 +18213,13 @@
         <v>30</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E212" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>171</v>
@@ -17667,12 +18237,15 @@
       <c r="K212" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L212" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M212" s="7"/>
-    </row>
-    <row r="213" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L212" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M212" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N212" s="7"/>
+    </row>
+    <row r="213" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3" t="s">
         <v>194</v>
       </c>
@@ -17680,13 +18253,13 @@
         <v>30</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E213" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>166</v>
@@ -17706,12 +18279,13 @@
       <c r="K213" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L213" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M213" s="7"/>
-    </row>
-    <row r="214" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L213" s="60"/>
+      <c r="M213" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N213" s="7"/>
+    </row>
+    <row r="214" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3" t="s">
         <v>194</v>
       </c>
@@ -17719,13 +18293,13 @@
         <v>31</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E214" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>166</v>
@@ -17745,12 +18319,13 @@
       <c r="K214" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L214" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M214" s="7"/>
-    </row>
-    <row r="215" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L214" s="61"/>
+      <c r="M214" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N214" s="7"/>
+    </row>
+    <row r="215" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3" t="s">
         <v>194</v>
       </c>
@@ -17758,13 +18333,13 @@
         <v>31</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E215" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>171</v>
@@ -17782,12 +18357,15 @@
       <c r="K215" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L215" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M215" s="7"/>
-    </row>
-    <row r="216" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L215" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M215" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N215" s="7"/>
+    </row>
+    <row r="216" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3" t="s">
         <v>194</v>
       </c>
@@ -17795,13 +18373,13 @@
         <v>31</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E216" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>171</v>
@@ -17819,12 +18397,15 @@
       <c r="K216" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L216" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M216" s="7"/>
-    </row>
-    <row r="217" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L216" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M216" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N216" s="7"/>
+    </row>
+    <row r="217" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3" t="s">
         <v>194</v>
       </c>
@@ -17832,13 +18413,13 @@
         <v>31</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E217" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>171</v>
@@ -17856,12 +18437,15 @@
       <c r="K217" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L217" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M217" s="7"/>
-    </row>
-    <row r="218" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L217" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M217" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N217" s="7"/>
+    </row>
+    <row r="218" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3" t="s">
         <v>194</v>
       </c>
@@ -17869,13 +18453,13 @@
         <v>31</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E218" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>171</v>
@@ -17893,12 +18477,15 @@
       <c r="K218" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L218" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M218" s="7"/>
-    </row>
-    <row r="219" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L218" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M218" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N218" s="7"/>
+    </row>
+    <row r="219" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3" t="s">
         <v>194</v>
       </c>
@@ -17906,13 +18493,13 @@
         <v>31</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E219" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>171</v>
@@ -17930,12 +18517,15 @@
       <c r="K219" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="L219" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M219" s="7"/>
-    </row>
-    <row r="220" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L219" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M219" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N219" s="7"/>
+    </row>
+    <row r="220" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3" t="s">
         <v>194</v>
       </c>
@@ -17943,13 +18533,13 @@
         <v>31</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E220" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>166</v>
@@ -17969,12 +18559,13 @@
       <c r="K220" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="L220" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M220" s="7"/>
-    </row>
-    <row r="221" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L220" s="60"/>
+      <c r="M220" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N220" s="7"/>
+    </row>
+    <row r="221" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3" t="s">
         <v>194</v>
       </c>
@@ -17982,13 +18573,13 @@
         <v>32</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E221" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>166</v>
@@ -18008,12 +18599,13 @@
       <c r="K221" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L221" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M221" s="7"/>
-    </row>
-    <row r="222" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L221" s="61"/>
+      <c r="M221" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N221" s="7"/>
+    </row>
+    <row r="222" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="3" t="s">
         <v>194</v>
       </c>
@@ -18021,13 +18613,13 @@
         <v>32</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E222" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>171</v>
@@ -18045,12 +18637,15 @@
       <c r="K222" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L222" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M222" s="7"/>
-    </row>
-    <row r="223" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L222" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M222" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N222" s="7"/>
+    </row>
+    <row r="223" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="3" t="s">
         <v>194</v>
       </c>
@@ -18058,13 +18653,13 @@
         <v>32</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E223" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>171</v>
@@ -18082,12 +18677,15 @@
       <c r="K223" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L223" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M223" s="7"/>
-    </row>
-    <row r="224" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L223" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M223" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N223" s="7"/>
+    </row>
+    <row r="224" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3" t="s">
         <v>194</v>
       </c>
@@ -18095,13 +18693,13 @@
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E224" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>171</v>
@@ -18119,12 +18717,15 @@
       <c r="K224" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="L224" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M224" s="7"/>
-    </row>
-    <row r="225" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L224" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M224" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N224" s="7"/>
+    </row>
+    <row r="225" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3" t="s">
         <v>194</v>
       </c>
@@ -18132,13 +18733,13 @@
         <v>32</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E225" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>171</v>
@@ -18156,12 +18757,15 @@
       <c r="K225" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L225" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M225" s="7"/>
-    </row>
-    <row r="226" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L225" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M225" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N225" s="7"/>
+    </row>
+    <row r="226" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="3" t="s">
         <v>194</v>
       </c>
@@ -18169,13 +18773,13 @@
         <v>32</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E226" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>171</v>
@@ -18193,64 +18797,67 @@
       <c r="K226" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="L226" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M226" s="7"/>
-    </row>
-    <row r="227" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L226" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M226" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N226" s="7"/>
+    </row>
+    <row r="227" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F227" s="28"/>
       <c r="G227" s="28"/>
     </row>
-    <row r="228" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F228" s="28"/>
       <c r="G228" s="28"/>
     </row>
-    <row r="229" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F229" s="28"/>
       <c r="G229" s="28"/>
     </row>
-    <row r="230" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F230" s="28"/>
       <c r="G230" s="28"/>
     </row>
-    <row r="231" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F231" s="28"/>
       <c r="G231" s="28"/>
     </row>
-    <row r="232" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F232" s="28"/>
       <c r="G232" s="28"/>
     </row>
-    <row r="233" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F233" s="28"/>
       <c r="G233" s="28"/>
     </row>
-    <row r="234" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F234" s="28"/>
       <c r="G234" s="28"/>
     </row>
-    <row r="235" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F235" s="28"/>
       <c r="G235" s="28"/>
     </row>
-    <row r="236" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F236" s="28"/>
       <c r="G236" s="28"/>
     </row>
-    <row r="237" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F237" s="28"/>
       <c r="G237" s="28"/>
     </row>
-    <row r="238" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F238" s="28"/>
       <c r="G238" s="28"/>
     </row>
-    <row r="239" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F239" s="28"/>
       <c r="G239" s="28"/>
     </row>
-    <row r="240" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F240" s="28"/>
       <c r="G240" s="28"/>
     </row>
@@ -20944,7 +21551,7 @@
   <cols>
     <col min="1" max="1" width="7.609375" style="43"/>
     <col min="2" max="2" width="15.38671875" customWidth="1"/>
-    <col min="3" max="3" width="22.609375" customWidth="1"/>
+    <col min="3" max="3" width="50.94140625" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" customWidth="1"/>
     <col min="5" max="5" width="23.44140625" customWidth="1"/>
     <col min="6" max="6" width="25.83203125" customWidth="1"/>
@@ -20957,7 +21564,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.2" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B1" s="40" t="s">
         <v>149</v>
@@ -20987,7 +21594,7 @@
         <v>163</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -20995,10 +21602,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>296</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>291</v>
+        <v>288</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>321</v>
       </c>
       <c r="D2" s="45" t="s">
         <v>174</v>
@@ -21022,7 +21629,7 @@
         <v>178</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21030,10 +21637,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>238</v>
+        <v>321</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>179</v>
@@ -21057,7 +21664,7 @@
         <v>182</v>
       </c>
       <c r="K3" s="59" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21065,10 +21672,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>298</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>292</v>
+        <v>290</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>322</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>183</v>
@@ -21092,7 +21699,7 @@
         <v>185</v>
       </c>
       <c r="K4" s="59" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21100,10 +21707,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>294</v>
+        <v>291</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>322</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="41" t="s">
@@ -21125,7 +21732,7 @@
         <v>49</v>
       </c>
       <c r="K5" s="59" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21133,10 +21740,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>300</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>293</v>
+        <v>292</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>323</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>208</v>
@@ -21160,7 +21767,7 @@
         <v>189</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21168,10 +21775,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>301</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>239</v>
+        <v>293</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>323</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>187</v>
@@ -21195,7 +21802,7 @@
         <v>49</v>
       </c>
       <c r="K7" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21203,10 +21810,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>302</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>240</v>
+        <v>294</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>324</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>190</v>
@@ -21230,7 +21837,7 @@
         <v>182</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21238,10 +21845,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>240</v>
+        <v>295</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>324</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="41" t="s">
@@ -21263,7 +21870,7 @@
         <v>185</v>
       </c>
       <c r="K9" s="59" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21271,10 +21878,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>309</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>241</v>
+        <v>301</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>325</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="42" t="s">
@@ -21296,7 +21903,7 @@
         <v>191</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21304,10 +21911,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>241</v>
+        <v>302</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>325</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="41" t="s">
@@ -21329,7 +21936,7 @@
         <v>189</v>
       </c>
       <c r="K11" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21337,7 +21944,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="45"/>
@@ -21360,7 +21967,7 @@
         <v>178</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21368,7 +21975,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="49"/>
@@ -21391,7 +21998,7 @@
         <v>182</v>
       </c>
       <c r="K13" s="59" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21399,7 +22006,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="45"/>
@@ -21422,7 +22029,7 @@
         <v>185</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21430,7 +22037,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="49"/>
@@ -21453,7 +22060,7 @@
         <v>191</v>
       </c>
       <c r="K15" s="59" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21461,10 +22068,10 @@
         <v>22</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>315</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>239</v>
+        <v>307</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>323</v>
       </c>
       <c r="D16" s="45"/>
       <c r="E16" s="52" t="s">
@@ -21486,7 +22093,7 @@
         <v>189</v>
       </c>
       <c r="K16" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21494,7 +22101,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
@@ -21519,7 +22126,7 @@
         <v>178</v>
       </c>
       <c r="K17" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21527,7 +22134,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="45" t="s">
@@ -21552,7 +22159,7 @@
         <v>182</v>
       </c>
       <c r="K18" s="59" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21560,7 +22167,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="49"/>
@@ -21583,7 +22190,7 @@
         <v>185</v>
       </c>
       <c r="K19" s="59" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21591,10 +22198,10 @@
         <v>28</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>319</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>241</v>
+        <v>311</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>325</v>
       </c>
       <c r="D20" s="45"/>
       <c r="E20" s="57" t="s">
@@ -21616,7 +22223,7 @@
         <v>191</v>
       </c>
       <c r="K20" s="59" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="12.6" x14ac:dyDescent="0.4">
@@ -21624,10 +22231,10 @@
         <v>29</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>241</v>
+        <v>312</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>325</v>
       </c>
       <c r="D21" s="49" t="s">
         <v>187</v>
@@ -21651,15 +22258,15 @@
         <v>189</v>
       </c>
       <c r="K21" s="59" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{6339E7B0-DD91-43F9-9AA6-7575AE99BA81}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{6339E7B0-DD91-43F9-9AA6-7575AE99BA81}"/>
     <hyperlink ref="G2" r:id="rId2" xr:uid="{DC80D7AF-69FB-4AAA-9743-02E8CB5F9079}"/>
-    <hyperlink ref="C3" r:id="rId3" display="https://static.vecteezy.com/system/resources/previews/054/250/025/non_2x/round-table-icon-design-symbol-vector.jpg" xr:uid="{A36D2DA1-4E0F-463F-BD52-823614E6F14F}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{A36D2DA1-4E0F-463F-BD52-823614E6F14F}"/>
     <hyperlink ref="I3" r:id="rId4" xr:uid="{738B9507-8B22-40D6-BDF3-FFDA91DE87D0}"/>
     <hyperlink ref="I4" r:id="rId5" xr:uid="{2CF77598-3EF2-4C04-B577-6076A34E9EE1}"/>
     <hyperlink ref="J5" r:id="rId6" xr:uid="{3AEABC4D-2D5C-4B33-A11F-9E6767FF7514}"/>
@@ -21668,8 +22275,8 @@
     <hyperlink ref="J7" r:id="rId9" xr:uid="{01FFD6B0-7C64-48E1-85C5-C64A49956307}"/>
     <hyperlink ref="I8" r:id="rId10" xr:uid="{41651FDF-D68A-4A66-81C6-6AD85DE23FD9}"/>
     <hyperlink ref="I9" r:id="rId11" xr:uid="{7A5E544D-B0DA-4DF2-B0C0-212A31F2A80F}"/>
-    <hyperlink ref="C10" r:id="rId12" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{5BC5963B-3916-439B-9D2F-5531AB6E9425}"/>
-    <hyperlink ref="C11" r:id="rId13" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{2E3C5B4A-D7B4-4F34-832E-7B28AE6A218C}"/>
+    <hyperlink ref="C10" r:id="rId12" xr:uid="{5BC5963B-3916-439B-9D2F-5531AB6E9425}"/>
+    <hyperlink ref="C11" r:id="rId13" xr:uid="{2E3C5B4A-D7B4-4F34-832E-7B28AE6A218C}"/>
     <hyperlink ref="G12" r:id="rId14" xr:uid="{8B42E5A2-C150-46E6-B84A-DA0391FFA844}"/>
     <hyperlink ref="I12" r:id="rId15" xr:uid="{790A0EE4-1017-405C-8848-CC0D9825D731}"/>
     <hyperlink ref="I13" r:id="rId16" xr:uid="{764E6654-EFE2-4BA2-88CA-00AE8F329884}"/>
@@ -21678,8 +22285,8 @@
     <hyperlink ref="I17" r:id="rId19" xr:uid="{7086DBCC-8681-4066-9B71-B7DF4F3E2D30}"/>
     <hyperlink ref="I18" r:id="rId20" xr:uid="{7FEAFFCA-16F0-4E78-91E4-FD82A1D3B0C4}"/>
     <hyperlink ref="I19" r:id="rId21" xr:uid="{F20DF1DC-2961-454E-911C-ABF0A6E1F404}"/>
-    <hyperlink ref="C20" r:id="rId22" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{EA695AE7-AC33-45C1-9A23-9E4D47F22F81}"/>
-    <hyperlink ref="C21" r:id="rId23" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png" xr:uid="{BDD9060C-BB64-40F9-9378-CACE644C50DE}"/>
+    <hyperlink ref="C20" r:id="rId22" xr:uid="{EA695AE7-AC33-45C1-9A23-9E4D47F22F81}"/>
+    <hyperlink ref="C21" r:id="rId23" xr:uid="{BDD9060C-BB64-40F9-9378-CACE644C50DE}"/>
     <hyperlink ref="K2" r:id="rId24" xr:uid="{A87BB04B-B72D-4A86-BEEA-8BA449F0988B}"/>
     <hyperlink ref="K6" r:id="rId25" xr:uid="{00FB0EE0-C588-4769-B7E3-0083DFEF0525}"/>
     <hyperlink ref="K7" r:id="rId26" xr:uid="{9CB4FD52-CAD2-4D4D-9553-FDF72B33FAA8}"/>
@@ -21700,9 +22307,16 @@
     <hyperlink ref="K18" r:id="rId41" xr:uid="{BFA9A033-AABB-4EA6-AA1E-7D3026867594}"/>
     <hyperlink ref="K19" r:id="rId42" xr:uid="{D15E29DE-9055-4D1E-A061-94CD9CD385A7}"/>
     <hyperlink ref="K20" r:id="rId43" xr:uid="{21E0BFBF-876B-451F-A4D6-CEF3E93F675C}"/>
+    <hyperlink ref="C4" r:id="rId44" xr:uid="{BEC335F0-C276-4E80-8294-C8CFFD879BE8}"/>
+    <hyperlink ref="C5" r:id="rId45" xr:uid="{B868FE14-E188-4B17-AFEB-D6B4C4A942D9}"/>
+    <hyperlink ref="C6" r:id="rId46" xr:uid="{400AE60C-D361-4C44-980A-E9DED67D11C2}"/>
+    <hyperlink ref="C7" r:id="rId47" xr:uid="{E41E327A-9DCA-4EAC-95D8-3CE3040CD28B}"/>
+    <hyperlink ref="C8" r:id="rId48" xr:uid="{91C8FB8B-79DC-4417-8259-B1DD9EF5CC29}"/>
+    <hyperlink ref="C9" r:id="rId49" xr:uid="{311F0620-89FE-400B-B5B1-F5F4B6263053}"/>
+    <hyperlink ref="C16" r:id="rId50" xr:uid="{7902F696-8305-4236-B7B1-2A4014E977E9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId44"/>
+  <pageSetup orientation="landscape" r:id="rId51"/>
 </worksheet>
 </file>
 

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2849CA60-DB9D-42C4-A2FA-0FD7D43F2431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970CC869-23D2-4A8E-BED4-DF5ED3FA1DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -1044,9 +1044,6 @@
     <t>Hotspot Line Data</t>
   </si>
   <si>
-    <t>Right:100</t>
-  </si>
-  <si>
     <t>Top:200</t>
   </si>
   <si>
@@ -1072,6 +1069,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/hs1 3.png</t>
+  </si>
+  <si>
+    <t>Right:0</t>
   </si>
 </sst>
 </file>
@@ -1510,6 +1510,24 @@
   <dxfs count="16">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1531,24 +1549,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF404040"/>
-        <name val="Inter"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1748,9 +1748,9 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Pitch"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Yaw"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Rotation"/>
-    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="2"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Hotspot Hover Active"/>
-    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="2. Hotspots Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2004,7 +2004,7 @@
     <col min="23" max="23" width="30" customWidth="1"/>
     <col min="24" max="26" width="18.71875" customWidth="1"/>
     <col min="27" max="27" width="12.5" customWidth="1"/>
-    <col min="28" max="28" width="65.0546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="96.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.4">
@@ -9478,7 +9478,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -9750,7 +9750,7 @@
         <v>173</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="M5" s="3" t="b">
         <v>1</v>
@@ -9793,7 +9793,7 @@
         <v>173</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M6" s="13" t="b">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>173</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M7" s="3" t="b">
         <v>1</v>
@@ -9879,7 +9879,7 @@
         <v>173</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M8" s="3" t="b">
         <v>1</v>
@@ -9922,7 +9922,7 @@
         <v>173</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M9" s="3" t="b">
         <v>1</v>
@@ -10047,7 +10047,7 @@
         <v>173</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M12" s="3" t="b">
         <v>1</v>
@@ -10088,7 +10088,7 @@
         <v>173</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M13" s="3" t="b">
         <v>1</v>
@@ -10129,7 +10129,7 @@
         <v>173</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M14" s="3" t="b">
         <v>1</v>
@@ -10170,7 +10170,7 @@
         <v>173</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M15" s="3" t="b">
         <v>1</v>
@@ -10211,7 +10211,7 @@
         <v>173</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M16" s="3" t="b">
         <v>1</v>
@@ -10334,7 +10334,7 @@
         <v>173</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M19" s="3" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>173</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M20" s="3" t="b">
         <v>1</v>
@@ -10416,7 +10416,7 @@
         <v>173</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M21" s="3" t="b">
         <v>1</v>
@@ -10457,7 +10457,7 @@
         <v>173</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M22" s="3" t="b">
         <v>1</v>
@@ -10498,7 +10498,7 @@
         <v>173</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M23" s="3" t="b">
         <v>1</v>
@@ -10621,7 +10621,7 @@
         <v>173</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M26" s="3" t="b">
         <v>1</v>
@@ -10662,7 +10662,7 @@
         <v>173</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M27" s="3" t="b">
         <v>1</v>
@@ -10703,7 +10703,7 @@
         <v>173</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M28" s="3" t="b">
         <v>1</v>
@@ -10744,7 +10744,7 @@
         <v>173</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M29" s="3" t="b">
         <v>1</v>
@@ -10785,7 +10785,7 @@
         <v>173</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M30" s="3" t="b">
         <v>1</v>
@@ -10908,7 +10908,7 @@
         <v>173</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M33" s="3" t="b">
         <v>1</v>
@@ -10949,7 +10949,7 @@
         <v>173</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M34" s="3" t="b">
         <v>1</v>
@@ -10990,7 +10990,7 @@
         <v>173</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M35" s="3" t="b">
         <v>1</v>
@@ -11031,7 +11031,7 @@
         <v>173</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M36" s="3" t="b">
         <v>1</v>
@@ -11072,7 +11072,7 @@
         <v>173</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M37" s="3" t="b">
         <v>1</v>
@@ -11195,7 +11195,7 @@
         <v>173</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M40" s="3" t="b">
         <v>1</v>
@@ -11236,7 +11236,7 @@
         <v>173</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M41" s="3" t="b">
         <v>1</v>
@@ -11277,7 +11277,7 @@
         <v>173</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M42" s="3" t="b">
         <v>1</v>
@@ -11318,7 +11318,7 @@
         <v>173</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M43" s="3" t="b">
         <v>1</v>
@@ -11359,7 +11359,7 @@
         <v>173</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M44" s="3" t="b">
         <v>1</v>
@@ -11482,7 +11482,7 @@
         <v>173</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M47" s="3" t="b">
         <v>1</v>
@@ -11523,7 +11523,7 @@
         <v>173</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M48" s="3" t="b">
         <v>1</v>
@@ -11564,7 +11564,7 @@
         <v>173</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M49" s="3" t="b">
         <v>1</v>
@@ -11605,7 +11605,7 @@
         <v>173</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M50" s="3" t="b">
         <v>1</v>
@@ -11646,7 +11646,7 @@
         <v>173</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M51" s="3" t="b">
         <v>1</v>
@@ -11769,7 +11769,7 @@
         <v>173</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M54" s="3" t="b">
         <v>1</v>
@@ -11810,7 +11810,7 @@
         <v>173</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M55" s="3" t="b">
         <v>1</v>
@@ -11851,7 +11851,7 @@
         <v>173</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M56" s="3" t="b">
         <v>1</v>
@@ -11892,7 +11892,7 @@
         <v>173</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M57" s="3" t="b">
         <v>1</v>
@@ -11933,7 +11933,7 @@
         <v>173</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M58" s="3" t="b">
         <v>1</v>
@@ -12056,7 +12056,7 @@
         <v>173</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M61" s="3" t="b">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         <v>173</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M62" s="3" t="b">
         <v>1</v>
@@ -12138,7 +12138,7 @@
         <v>173</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M63" s="3" t="b">
         <v>1</v>
@@ -12179,7 +12179,7 @@
         <v>173</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M64" s="3" t="b">
         <v>1</v>
@@ -12220,7 +12220,7 @@
         <v>173</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M65" s="3" t="b">
         <v>1</v>
@@ -12343,7 +12343,7 @@
         <v>173</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M68" s="3" t="b">
         <v>1</v>
@@ -12384,7 +12384,7 @@
         <v>173</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M69" s="3" t="b">
         <v>1</v>
@@ -12425,7 +12425,7 @@
         <v>173</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M70" s="3" t="b">
         <v>1</v>
@@ -12466,7 +12466,7 @@
         <v>173</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M71" s="3" t="b">
         <v>1</v>
@@ -12507,7 +12507,7 @@
         <v>173</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M72" s="3" t="b">
         <v>1</v>
@@ -12630,7 +12630,7 @@
         <v>173</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M75" s="3" t="b">
         <v>1</v>
@@ -12671,7 +12671,7 @@
         <v>173</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M76" s="3" t="b">
         <v>1</v>
@@ -12712,7 +12712,7 @@
         <v>173</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M77" s="3" t="b">
         <v>1</v>
@@ -12753,7 +12753,7 @@
         <v>173</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M78" s="3" t="b">
         <v>1</v>
@@ -12794,7 +12794,7 @@
         <v>173</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M79" s="3" t="b">
         <v>1</v>
@@ -12917,7 +12917,7 @@
         <v>173</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M82" s="3" t="b">
         <v>1</v>
@@ -12958,7 +12958,7 @@
         <v>173</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M83" s="3" t="b">
         <v>1</v>
@@ -12999,7 +12999,7 @@
         <v>173</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M84" s="3" t="b">
         <v>1</v>
@@ -13040,7 +13040,7 @@
         <v>173</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M85" s="3" t="b">
         <v>1</v>
@@ -13081,7 +13081,7 @@
         <v>173</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M86" s="3" t="b">
         <v>1</v>
@@ -13204,7 +13204,7 @@
         <v>173</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M89" s="3" t="b">
         <v>1</v>
@@ -13245,7 +13245,7 @@
         <v>173</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M90" s="3" t="b">
         <v>1</v>
@@ -13286,7 +13286,7 @@
         <v>173</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M91" s="3" t="b">
         <v>1</v>
@@ -13327,7 +13327,7 @@
         <v>173</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M92" s="3" t="b">
         <v>1</v>
@@ -13368,7 +13368,7 @@
         <v>173</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M93" s="3" t="b">
         <v>1</v>
@@ -13491,7 +13491,7 @@
         <v>173</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M96" s="3" t="b">
         <v>1</v>
@@ -13532,7 +13532,7 @@
         <v>173</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M97" s="3" t="b">
         <v>1</v>
@@ -13573,7 +13573,7 @@
         <v>173</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M98" s="3" t="b">
         <v>1</v>
@@ -13614,7 +13614,7 @@
         <v>173</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M99" s="3" t="b">
         <v>1</v>
@@ -13655,7 +13655,7 @@
         <v>173</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M100" s="3" t="b">
         <v>1</v>
@@ -13778,7 +13778,7 @@
         <v>173</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M103" s="3" t="b">
         <v>1</v>
@@ -13819,7 +13819,7 @@
         <v>173</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M104" s="3" t="b">
         <v>1</v>
@@ -13860,7 +13860,7 @@
         <v>173</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M105" s="3" t="b">
         <v>1</v>
@@ -13901,7 +13901,7 @@
         <v>173</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M106" s="3" t="b">
         <v>1</v>
@@ -13942,7 +13942,7 @@
         <v>173</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M107" s="3" t="b">
         <v>1</v>
@@ -14065,7 +14065,7 @@
         <v>173</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M110" s="3" t="b">
         <v>1</v>
@@ -14106,7 +14106,7 @@
         <v>173</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M111" s="3" t="b">
         <v>1</v>
@@ -14147,7 +14147,7 @@
         <v>173</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M112" s="3" t="b">
         <v>1</v>
@@ -14188,7 +14188,7 @@
         <v>173</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M113" s="3" t="b">
         <v>1</v>
@@ -14229,7 +14229,7 @@
         <v>173</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M114" s="3" t="b">
         <v>1</v>
@@ -14352,7 +14352,7 @@
         <v>173</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M117" s="3" t="b">
         <v>1</v>
@@ -14393,7 +14393,7 @@
         <v>173</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M118" s="3" t="b">
         <v>1</v>
@@ -14434,7 +14434,7 @@
         <v>173</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M119" s="3" t="b">
         <v>1</v>
@@ -14475,7 +14475,7 @@
         <v>173</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M120" s="3" t="b">
         <v>1</v>
@@ -14516,7 +14516,7 @@
         <v>173</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M121" s="3" t="b">
         <v>1</v>
@@ -14639,7 +14639,7 @@
         <v>173</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M124" s="3" t="b">
         <v>1</v>
@@ -14680,7 +14680,7 @@
         <v>173</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M125" s="3" t="b">
         <v>1</v>
@@ -14721,7 +14721,7 @@
         <v>173</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M126" s="3" t="b">
         <v>1</v>
@@ -14762,7 +14762,7 @@
         <v>173</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M127" s="3" t="b">
         <v>1</v>
@@ -14803,7 +14803,7 @@
         <v>173</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M128" s="3" t="b">
         <v>1</v>
@@ -14926,7 +14926,7 @@
         <v>173</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M131" s="3" t="b">
         <v>1</v>
@@ -14967,7 +14967,7 @@
         <v>173</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M132" s="3" t="b">
         <v>1</v>
@@ -15008,7 +15008,7 @@
         <v>173</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M133" s="3" t="b">
         <v>1</v>
@@ -15049,7 +15049,7 @@
         <v>173</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M134" s="3" t="b">
         <v>1</v>
@@ -15090,7 +15090,7 @@
         <v>173</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M135" s="3" t="b">
         <v>1</v>
@@ -15213,7 +15213,7 @@
         <v>173</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M138" s="3" t="b">
         <v>1</v>
@@ -15254,7 +15254,7 @@
         <v>173</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M139" s="3" t="b">
         <v>1</v>
@@ -15295,7 +15295,7 @@
         <v>173</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M140" s="3" t="b">
         <v>1</v>
@@ -15336,7 +15336,7 @@
         <v>173</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M141" s="3" t="b">
         <v>1</v>
@@ -15377,7 +15377,7 @@
         <v>173</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M142" s="3" t="b">
         <v>1</v>
@@ -15500,7 +15500,7 @@
         <v>173</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M145" s="3" t="b">
         <v>1</v>
@@ -15541,7 +15541,7 @@
         <v>173</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M146" s="3" t="b">
         <v>1</v>
@@ -15582,7 +15582,7 @@
         <v>173</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M147" s="3" t="b">
         <v>1</v>
@@ -15623,7 +15623,7 @@
         <v>173</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M148" s="3" t="b">
         <v>1</v>
@@ -15664,7 +15664,7 @@
         <v>173</v>
       </c>
       <c r="L149" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M149" s="3" t="b">
         <v>1</v>
@@ -15787,7 +15787,7 @@
         <v>173</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M152" s="3" t="b">
         <v>1</v>
@@ -15828,7 +15828,7 @@
         <v>173</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M153" s="3" t="b">
         <v>1</v>
@@ -15869,7 +15869,7 @@
         <v>173</v>
       </c>
       <c r="L154" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M154" s="3" t="b">
         <v>1</v>
@@ -15910,7 +15910,7 @@
         <v>173</v>
       </c>
       <c r="L155" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M155" s="3" t="b">
         <v>1</v>
@@ -15951,7 +15951,7 @@
         <v>173</v>
       </c>
       <c r="L156" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M156" s="3" t="b">
         <v>1</v>
@@ -16074,7 +16074,7 @@
         <v>173</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M159" s="3" t="b">
         <v>1</v>
@@ -16115,7 +16115,7 @@
         <v>173</v>
       </c>
       <c r="L160" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M160" s="3" t="b">
         <v>1</v>
@@ -16156,7 +16156,7 @@
         <v>173</v>
       </c>
       <c r="L161" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M161" s="3" t="b">
         <v>1</v>
@@ -16197,7 +16197,7 @@
         <v>173</v>
       </c>
       <c r="L162" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M162" s="3" t="b">
         <v>1</v>
@@ -16238,7 +16238,7 @@
         <v>173</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M163" s="3" t="b">
         <v>1</v>
@@ -16361,7 +16361,7 @@
         <v>173</v>
       </c>
       <c r="L166" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M166" s="3" t="b">
         <v>1</v>
@@ -16402,7 +16402,7 @@
         <v>173</v>
       </c>
       <c r="L167" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M167" s="3" t="b">
         <v>1</v>
@@ -16443,7 +16443,7 @@
         <v>173</v>
       </c>
       <c r="L168" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M168" s="3" t="b">
         <v>1</v>
@@ -16484,7 +16484,7 @@
         <v>173</v>
       </c>
       <c r="L169" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M169" s="3" t="b">
         <v>1</v>
@@ -16525,7 +16525,7 @@
         <v>173</v>
       </c>
       <c r="L170" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M170" s="3" t="b">
         <v>1</v>
@@ -16648,7 +16648,7 @@
         <v>173</v>
       </c>
       <c r="L173" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M173" s="3" t="b">
         <v>1</v>
@@ -16689,7 +16689,7 @@
         <v>173</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M174" s="3" t="b">
         <v>1</v>
@@ -16730,7 +16730,7 @@
         <v>173</v>
       </c>
       <c r="L175" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M175" s="3" t="b">
         <v>1</v>
@@ -16771,7 +16771,7 @@
         <v>173</v>
       </c>
       <c r="L176" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M176" s="3" t="b">
         <v>1</v>
@@ -16812,7 +16812,7 @@
         <v>173</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M177" s="3" t="b">
         <v>1</v>
@@ -16935,7 +16935,7 @@
         <v>173</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M180" s="3" t="b">
         <v>1</v>
@@ -16976,7 +16976,7 @@
         <v>173</v>
       </c>
       <c r="L181" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M181" s="3" t="b">
         <v>1</v>
@@ -17017,7 +17017,7 @@
         <v>173</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M182" s="3" t="b">
         <v>1</v>
@@ -17058,7 +17058,7 @@
         <v>173</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M183" s="3" t="b">
         <v>1</v>
@@ -17099,7 +17099,7 @@
         <v>173</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M184" s="3" t="b">
         <v>1</v>
@@ -17222,7 +17222,7 @@
         <v>173</v>
       </c>
       <c r="L187" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M187" s="3" t="b">
         <v>1</v>
@@ -17263,7 +17263,7 @@
         <v>173</v>
       </c>
       <c r="L188" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M188" s="3" t="b">
         <v>1</v>
@@ -17304,7 +17304,7 @@
         <v>173</v>
       </c>
       <c r="L189" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M189" s="3" t="b">
         <v>1</v>
@@ -17345,7 +17345,7 @@
         <v>173</v>
       </c>
       <c r="L190" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M190" s="3" t="b">
         <v>1</v>
@@ -17386,7 +17386,7 @@
         <v>173</v>
       </c>
       <c r="L191" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M191" s="3" t="b">
         <v>1</v>
@@ -17509,7 +17509,7 @@
         <v>173</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M194" s="3" t="b">
         <v>1</v>
@@ -17550,7 +17550,7 @@
         <v>173</v>
       </c>
       <c r="L195" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M195" s="3" t="b">
         <v>1</v>
@@ -17591,7 +17591,7 @@
         <v>173</v>
       </c>
       <c r="L196" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M196" s="3" t="b">
         <v>1</v>
@@ -17632,7 +17632,7 @@
         <v>173</v>
       </c>
       <c r="L197" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M197" s="3" t="b">
         <v>1</v>
@@ -17673,7 +17673,7 @@
         <v>173</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M198" s="3" t="b">
         <v>1</v>
@@ -17796,7 +17796,7 @@
         <v>173</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M201" s="3" t="b">
         <v>1</v>
@@ -17837,7 +17837,7 @@
         <v>173</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M202" s="3" t="b">
         <v>1</v>
@@ -17878,7 +17878,7 @@
         <v>173</v>
       </c>
       <c r="L203" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M203" s="3" t="b">
         <v>1</v>
@@ -17918,7 +17918,7 @@
         <v>173</v>
       </c>
       <c r="L204" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M204" s="3" t="b">
         <v>1</v>
@@ -17958,7 +17958,7 @@
         <v>173</v>
       </c>
       <c r="L205" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M205" s="3" t="b">
         <v>1</v>
@@ -18078,7 +18078,7 @@
         <v>173</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M208" s="3" t="b">
         <v>1</v>
@@ -18118,7 +18118,7 @@
         <v>173</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M209" s="3" t="b">
         <v>1</v>
@@ -18158,7 +18158,7 @@
         <v>173</v>
       </c>
       <c r="L210" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M210" s="3" t="b">
         <v>1</v>
@@ -18198,7 +18198,7 @@
         <v>173</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M211" s="3" t="b">
         <v>1</v>
@@ -18238,7 +18238,7 @@
         <v>173</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M212" s="3" t="b">
         <v>1</v>
@@ -18358,7 +18358,7 @@
         <v>173</v>
       </c>
       <c r="L215" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M215" s="3" t="b">
         <v>1</v>
@@ -18398,7 +18398,7 @@
         <v>173</v>
       </c>
       <c r="L216" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M216" s="3" t="b">
         <v>1</v>
@@ -18438,7 +18438,7 @@
         <v>173</v>
       </c>
       <c r="L217" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M217" s="3" t="b">
         <v>1</v>
@@ -18478,7 +18478,7 @@
         <v>173</v>
       </c>
       <c r="L218" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M218" s="3" t="b">
         <v>1</v>
@@ -18518,7 +18518,7 @@
         <v>173</v>
       </c>
       <c r="L219" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M219" s="3" t="b">
         <v>1</v>
@@ -18638,7 +18638,7 @@
         <v>173</v>
       </c>
       <c r="L222" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M222" s="3" t="b">
         <v>1</v>
@@ -18678,7 +18678,7 @@
         <v>173</v>
       </c>
       <c r="L223" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M223" s="3" t="b">
         <v>1</v>
@@ -18718,7 +18718,7 @@
         <v>173</v>
       </c>
       <c r="L224" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M224" s="3" t="b">
         <v>1</v>
@@ -18758,7 +18758,7 @@
         <v>173</v>
       </c>
       <c r="L225" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M225" s="3" t="b">
         <v>1</v>
@@ -18798,7 +18798,7 @@
         <v>173</v>
       </c>
       <c r="L226" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M226" s="3" t="b">
         <v>1</v>
@@ -21605,7 +21605,7 @@
         <v>288</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D2" s="45" t="s">
         <v>174</v>
@@ -21640,7 +21640,7 @@
         <v>289</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>179</v>
@@ -21675,7 +21675,7 @@
         <v>290</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>183</v>
@@ -21710,7 +21710,7 @@
         <v>291</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="41" t="s">
@@ -21743,7 +21743,7 @@
         <v>292</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>208</v>
@@ -21778,7 +21778,7 @@
         <v>293</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>187</v>
@@ -21813,7 +21813,7 @@
         <v>294</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>190</v>
@@ -21848,7 +21848,7 @@
         <v>295</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="41" t="s">
@@ -21881,7 +21881,7 @@
         <v>301</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="42" t="s">
@@ -21914,7 +21914,7 @@
         <v>302</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="41" t="s">
@@ -22071,7 +22071,7 @@
         <v>307</v>
       </c>
       <c r="C16" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D16" s="45"/>
       <c r="E16" s="52" t="s">
@@ -22201,7 +22201,7 @@
         <v>311</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D20" s="45"/>
       <c r="E20" s="57" t="s">
@@ -22234,7 +22234,7 @@
         <v>312</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D21" s="49" t="s">
         <v>187</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970CC869-23D2-4A8E-BED4-DF5ED3FA1DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3564ABAF-5387-4390-A0CA-11B37BBCCD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="2. Hotspots Sheet" sheetId="2" r:id="rId2"/>
     <sheet name="3. Hotspot Datas" sheetId="5" r:id="rId3"/>
-    <sheet name="4. Floors Sheet" sheetId="3" r:id="rId4"/>
+    <sheet name="4. Question Answers" sheetId="6" r:id="rId4"/>
     <sheet name="5. Styles Sheet (Custom CSS)" sheetId="4" r:id="rId5"/>
+    <sheet name="6. Floors Sheet" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2449" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="331">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1073,6 +1074,21 @@
   <si>
     <t>Right:0</t>
   </si>
+  <si>
+    <t>Qestions and answers</t>
+  </si>
+  <si>
+    <t>Answer Audio URL or TTS</t>
+  </si>
+  <si>
+    <t>Answer Media URL</t>
+  </si>
+  <si>
+    <t>Illus Magnetic Track Light: 5 Common Questions</t>
+  </si>
+  <si>
+    <t>[Question01:What are the main benefits of Illus Magnetic Track Lights?,Answer01:Illus Magnetic Track Lights offer unparalleled flexibility, allowing you to easily reposition or add light fixtures without tools. They provide a sleek, minimalist aesthetic, are highly energy-efficient, and offer versatile lighting solutions for various spaces.],[Question02:How easy is it to install Illus Magnetic Track Lighting systems?,Answer02:Installation is generally straightforward, designed for both professionals and DIY enthusiasts. The magnetic connection simplifies the process of attaching and detaching light modules, making setup and modification quick and easy compared to traditional track systems.],[Question03:Can Illus Magnetic Track Lights be used in any room?,Answer03:Yes, their versatile design makes them suitable for a wide range of applications, including living rooms, kitchens, bedrooms, offices, retail spaces, and art galleries. They are particularly effective where flexible and adaptable lighting is desired.],[Question04:What types of light fixtures are compatible with Illus Magnetic Tracks?,Answer04:Illus Magnetic Tracks are compatible with a variety of magnetic-based light fixtures, including spotlights, floodlights, pendant lights, and linear lights. This allows for diverse lighting designs and functionalities within a single system.],[Question05:Are Illus Magnetic Track Lights energy-efficient?,Answer05:Absolutely. Most Illus Magnetic Track Light systems utilize LED technology, which is highly energy-efficient, offering significant savings on electricity bills and a longer lifespan compared to traditional lighting sources.]</t>
+  </si>
 </sst>
 </file>
 
@@ -1081,7 +1097,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1209,6 +1225,10 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Inter"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1339,7 +1359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1502,12 +1522,54 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1517,6 +1579,30 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1667,24 +1753,24 @@
   </dxfs>
   <tableStyles count="4">
     <tableStyle name="1. Scenes Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="secondRowStripe" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
     </tableStyle>
     <tableStyle name="2. Hotspots Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="secondRowStripe" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
     <tableStyle name="3. Floors Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="secondRowStripe" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
     <tableStyle name="4. Styles Sheet (Custom CSS)-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" dxfId="5"/>
-      <tableStyleElement type="secondRowStripe" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1726,7 +1812,7 @@
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Floor map Details"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Floor Map Active"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Get Pitch/Yaw Data"/>
-    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="3"/>
+    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="5"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Scen Identifier"/>
     <tableColumn id="28" xr3:uid="{F3D3E641-7A49-4E3D-A155-18F57FACDDFD}" name="Map Data"/>
   </tableColumns>
@@ -1748,22 +1834,23 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Pitch"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Yaw"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Rotation"/>
-    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="4"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Hotspot Hover Active"/>
-    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="2. Hotspots Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="A1:E3">
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="FloorID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="FloorName"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ThumbnailURL"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Order"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Floor Thumb Active"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A1982990-8932-4703-94E4-180C79928346}" name="Table_36" displayName="Table_36" ref="A1:F6">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{AC2068F9-4426-4263-A845-5946EB10AED0}" name="SL#"/>
+    <tableColumn id="2" xr3:uid="{3D9EE8D6-E76E-45C3-BCE6-12CC183EE067}" name="Hotspot Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{A97AF90C-72ED-4B03-A59A-8CA0E1A8B08B}" name="Title" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{D20C3793-59AA-4FED-9D83-26F7442A226B}" name="Qestions and answers"/>
+    <tableColumn id="4" xr3:uid="{061E7697-FC0B-487F-9C65-88C25FA344FC}" name="Answer Audio URL or TTS"/>
+    <tableColumn id="5" xr3:uid="{6BF83100-29F6-4DAC-9D40-8965E58C45A5}" name="Answer Media URL"/>
   </tableColumns>
   <tableStyleInfo name="3. Floors Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1776,6 +1863,19 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="CSS Rules"/>
   </tableColumns>
   <tableStyleInfo name="4. Styles Sheet (Custom CSS)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="A1:E3">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="FloorID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="FloorName"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ThumbnailURL"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Order"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Floor Thumb Active"/>
+  </tableColumns>
+  <tableStyleInfo name="3. Floors Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2089,7 +2189,7 @@
       <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="62" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2124,7 +2224,7 @@
       <c r="J2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="64" t="s">
         <v>214</v>
       </c>
       <c r="L2" s="6" t="s">
@@ -2143,7 +2243,7 @@
         <v>105</v>
       </c>
       <c r="Q2" s="3">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="R2" s="3">
         <v>0</v>
@@ -2229,7 +2329,7 @@
         <v>105</v>
       </c>
       <c r="Q3" s="3">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -2374,7 +2474,7 @@
       <c r="I5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="64" t="s">
         <v>49</v>
       </c>
       <c r="K5" s="5" t="s">
@@ -9478,7 +9578,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -9516,12 +9616,13 @@
     <hyperlink ref="J31" r:id="rId33" xr:uid="{CF4E9A91-67F0-423E-BCEC-C74885AF5BC9}"/>
     <hyperlink ref="J32" r:id="rId34" xr:uid="{ECDBC281-C876-447B-A095-FEDCE057629B}"/>
     <hyperlink ref="F7" r:id="rId35" xr:uid="{96C1421D-6554-4D9E-8F52-9DE18E04463E}"/>
+    <hyperlink ref="K2" r:id="rId36" xr:uid="{504E9C15-B158-443E-98D6-19F9F0801143}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId36"/>
-  <legacyDrawing r:id="rId37"/>
+  <pageSetup orientation="landscape" r:id="rId37"/>
+  <legacyDrawing r:id="rId38"/>
   <tableParts count="1">
-    <tablePart r:id="rId38"/>
+    <tablePart r:id="rId39"/>
   </tableParts>
 </worksheet>
 </file>
@@ -22321,6 +22422,2193 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9379027C-E3D3-47ED-99BC-9D546DD86D06}">
+  <dimension ref="A1:G985"/>
+  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="27.609375" customWidth="1"/>
+    <col min="4" max="4" width="38.21875" customWidth="1"/>
+    <col min="5" max="5" width="33.38671875" customWidth="1"/>
+    <col min="6" max="6" width="34.5" customWidth="1"/>
+    <col min="7" max="27" width="8.609375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>329</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>330</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="31"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="30"/>
+    </row>
+    <row r="4" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="31"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="33"/>
+    </row>
+    <row r="5" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="31"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="33"/>
+    </row>
+    <row r="6" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="31"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+    </row>
+    <row r="7" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="17" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="18" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="20" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="22" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="26" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="33" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="34" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="35" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="37" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="38" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="41" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="42" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="56" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="64" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="65" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="66" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="67" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="68" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="69" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="70" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="71" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="72" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="73" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="74" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="75" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="76" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="77" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="78" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="79" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="80" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="81" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="82" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="83" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="84" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="85" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="86" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="87" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="88" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="89" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="90" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="91" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="92" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="93" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="94" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="95" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="96" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="97" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="98" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="99" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="100" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="101" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="102" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="103" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="104" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="105" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="106" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="107" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="108" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="109" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="110" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="111" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="112" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="113" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="114" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="115" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="116" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="117" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="118" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="119" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="120" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="121" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="122" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="123" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="124" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="125" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="126" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="127" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="128" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="129" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="130" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="131" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="132" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="133" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="134" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="135" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="136" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="137" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="138" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="139" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="140" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="141" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="142" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="143" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="144" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="145" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="146" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="147" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="148" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="149" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="150" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="151" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="152" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="153" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="154" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="155" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="156" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="157" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="158" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="159" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="160" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="161" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="162" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="163" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="164" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="165" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="166" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="167" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="168" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="169" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="170" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="171" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="172" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="173" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="174" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="175" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="176" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="177" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="178" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="179" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="180" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="181" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="182" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="183" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="184" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="185" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="186" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="187" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="188" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="189" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="190" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="191" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="192" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="193" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="194" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="195" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="196" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="197" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="198" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="199" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="200" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="201" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="202" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="203" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="204" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="205" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="206" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="207" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="208" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="209" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="210" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="211" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="212" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="213" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="214" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="215" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="216" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="217" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="218" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="219" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="220" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="221" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="222" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="223" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="224" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="225" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="226" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="227" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="228" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="229" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="230" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="231" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="232" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="233" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="234" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="235" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="236" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="237" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="238" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="239" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="240" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="241" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="242" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="243" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="244" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="245" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="246" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="247" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="248" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="249" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="250" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="251" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="252" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="253" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="254" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="255" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="256" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="257" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="258" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="259" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="260" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="261" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="262" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="263" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="264" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="265" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="266" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="267" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="268" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="269" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="270" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="271" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="272" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="273" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="274" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="275" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="276" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="277" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="278" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="279" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="280" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="281" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="282" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="283" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="284" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="285" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="286" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="287" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="288" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="289" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="290" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="291" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="292" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="293" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="294" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="295" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="296" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="297" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="298" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="299" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="300" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="301" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="302" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="303" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="304" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="305" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="306" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="307" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="308" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="309" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="310" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="311" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="312" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="313" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="314" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="315" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="316" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="317" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="318" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="319" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="320" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="321" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="322" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="323" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="324" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="325" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="326" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="327" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="328" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="329" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="330" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="331" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="332" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="333" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="334" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="335" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="336" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="337" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="338" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="339" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="340" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="341" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="342" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="343" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="344" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="345" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="346" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="347" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="348" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="349" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="350" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="351" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="352" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="353" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="354" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="355" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="356" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="357" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="358" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="359" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="360" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="361" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="362" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="363" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="364" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="365" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="366" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="367" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="368" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="369" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="370" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="371" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="372" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="373" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="374" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="375" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="376" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="377" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="378" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="379" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="380" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="381" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="382" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="383" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="384" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="385" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="386" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="387" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="388" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="389" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="390" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="391" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="392" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="393" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="394" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="395" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="396" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="397" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="398" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="399" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="400" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="401" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="402" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="403" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="404" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="405" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="406" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="407" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="408" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="409" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="410" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="411" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="412" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="413" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="414" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="415" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="416" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="417" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="418" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="419" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="420" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="421" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="422" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="423" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="424" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="425" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="426" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="427" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="428" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="429" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="430" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="431" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="432" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="433" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="434" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="435" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="436" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="437" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="438" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="439" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="440" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="441" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="442" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="443" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="444" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="445" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="446" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="447" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="448" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="449" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="450" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="451" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="452" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="453" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="454" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="455" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="456" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="457" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="458" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="459" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="460" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="461" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="462" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="463" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="464" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="465" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="466" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="467" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="468" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="469" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="470" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="471" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="472" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="473" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="474" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="475" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="476" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="477" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="478" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="479" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="480" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="481" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="482" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="483" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="484" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="485" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="486" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="487" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="488" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="489" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="490" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="491" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="492" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="493" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="494" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="495" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="496" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="497" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="498" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="499" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="500" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="501" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="502" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="503" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="504" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="505" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="506" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="507" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="508" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="509" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="510" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="511" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="512" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="513" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="514" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="515" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="516" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="517" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="518" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="519" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="520" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="521" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="522" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="523" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="524" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="525" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="526" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="527" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="528" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="529" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="530" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="531" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="532" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="533" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="534" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="535" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="536" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="537" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="538" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="539" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="540" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="541" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="542" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="543" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="544" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="545" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="546" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="547" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="548" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="549" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="550" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="551" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="552" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="553" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="554" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="555" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="556" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="557" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="558" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="559" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="560" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="561" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="562" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="563" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="564" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="565" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="566" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="567" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="568" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="569" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="570" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="571" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="572" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="573" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="574" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="575" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="576" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="577" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="578" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="579" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="580" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="581" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="582" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="583" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="584" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="585" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="586" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="587" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="588" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="589" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="590" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="591" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="592" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="593" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="594" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="595" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="596" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="597" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="598" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="599" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="600" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="601" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="602" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="603" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="604" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="605" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="606" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="607" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="608" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="609" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="610" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="611" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="612" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="613" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="614" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="615" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="616" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="617" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="618" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="619" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="620" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="621" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="622" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="623" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="624" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="625" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="626" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="627" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="628" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="629" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="630" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="631" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="632" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="633" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="634" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="635" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="636" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="637" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="638" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="639" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="640" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="641" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="642" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="643" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="644" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="645" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="646" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="647" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="648" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="649" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="650" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="651" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="652" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="653" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="654" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="655" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="656" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="657" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="658" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="659" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="660" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="661" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="662" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="663" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="664" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="665" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="666" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="667" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="668" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="669" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="670" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="671" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="672" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="673" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="674" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="675" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="676" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="677" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="678" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="679" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="680" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="681" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="682" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="683" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="684" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="685" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="686" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="687" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="688" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="689" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="690" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="691" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="692" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="693" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="694" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="695" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="696" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="697" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="698" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="699" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="700" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="701" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="702" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="703" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="704" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="705" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="706" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="707" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="708" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="709" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="710" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="711" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="712" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="713" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="714" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="715" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="716" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="717" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="718" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="719" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="720" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="721" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="722" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="723" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="724" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="725" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="726" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="727" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="728" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="729" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="730" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="731" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="732" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="733" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="734" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="735" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="736" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="737" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="738" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="739" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="740" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="741" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="742" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="743" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="744" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="745" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="746" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="747" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="748" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="749" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="750" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="751" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="752" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="753" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="754" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="755" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="756" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="757" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="758" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="759" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="760" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="761" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="762" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="763" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="764" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="765" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="766" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="767" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="768" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="769" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="770" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="771" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="772" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="773" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="774" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="775" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="776" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="777" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="778" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="779" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="780" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="781" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="782" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="783" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="784" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="785" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="786" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="787" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="788" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="789" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="790" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="791" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="792" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="793" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="794" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="795" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="796" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="797" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="798" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="799" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="800" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="801" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="802" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="803" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="804" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="805" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="806" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="807" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="808" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="809" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="810" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="811" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="812" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="813" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="814" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="815" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="816" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="817" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="818" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="819" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="820" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="821" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="822" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="823" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="824" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="825" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="826" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="827" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="828" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="829" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="830" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="831" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="832" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="833" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="834" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="835" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="836" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="837" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="838" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="839" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="840" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="841" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="842" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="843" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="844" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="845" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="846" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="847" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="848" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="849" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="850" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="851" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="852" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="853" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="854" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="855" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="856" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="857" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="858" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="859" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="860" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="861" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="862" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="863" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="864" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="865" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="866" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="867" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="868" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="869" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="870" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="871" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="872" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="873" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="874" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="875" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="876" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="877" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="878" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="879" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="880" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="881" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="882" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="883" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="884" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="885" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="886" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="887" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="888" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="889" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="890" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="891" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="892" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="893" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="894" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="895" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="896" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="897" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="898" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="899" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="900" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="901" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="902" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="903" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="904" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="905" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="906" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="907" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="908" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="909" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="910" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="911" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="912" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="913" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="914" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="915" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="916" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="917" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="918" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="919" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="920" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="921" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="922" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="923" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="924" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="925" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="926" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="927" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="928" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="929" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="930" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="931" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="932" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="933" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="934" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="935" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="936" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="937" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="938" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="939" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="940" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="941" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="942" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="943" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="944" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="945" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="946" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="947" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="948" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="949" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="950" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="951" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="952" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="953" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="954" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="955" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="956" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="957" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="958" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="959" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="960" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="961" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="962" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="963" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="964" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="965" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="966" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="967" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="968" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="969" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="970" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="971" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="972" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="973" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="974" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="975" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="976" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="977" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="978" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="979" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="980" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="981" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="982" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="983" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="984" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="985" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{47F76424-D73E-4DC3-987A-1DF0EE7BC291}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="69.5" customWidth="1"/>
+    <col min="3" max="26" width="8.609375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="2" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+    </row>
+    <row r="4" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+    </row>
+    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+    </row>
+    <row r="7" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="30"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+    </row>
+    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+    </row>
+    <row r="10" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+    </row>
+    <row r="12" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="17" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="18" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="20" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="22" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="26" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="33" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="34" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="35" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="37" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="38" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="41" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="42" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="56" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="64" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="65" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="66" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="67" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="68" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="69" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="70" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="71" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="72" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="73" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="74" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="75" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="76" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="77" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="78" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="79" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="80" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="81" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="82" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="83" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="84" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="85" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="86" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="87" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="88" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="89" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="90" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="91" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="92" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="93" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="94" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="95" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="96" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="97" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="98" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="99" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="100" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="101" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="102" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="103" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="104" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="105" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="106" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="107" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="108" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="109" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="110" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="111" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="112" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="113" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="114" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="115" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="116" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="117" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="118" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="119" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="120" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="121" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="122" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="123" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="124" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="125" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="126" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="127" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="128" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="129" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="130" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="131" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="132" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="133" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="134" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="135" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="136" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="137" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="138" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="139" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="140" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="141" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="142" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="143" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="144" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="145" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="146" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="147" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="148" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="149" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="150" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="151" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="152" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="153" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="154" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="155" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="156" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="157" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="158" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="159" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="160" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="161" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="162" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="163" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="164" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="165" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="166" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="167" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="168" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="169" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="170" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="171" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="172" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="173" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="174" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="175" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="176" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="177" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="178" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="179" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="180" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="181" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="182" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="183" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="184" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="185" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="186" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="187" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="188" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="189" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="190" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="191" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="192" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="193" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="194" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="195" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="196" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="197" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="198" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="199" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="200" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="201" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="202" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="203" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="204" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="205" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="206" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="207" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="208" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="209" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="210" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="211" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="212" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="213" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="214" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="215" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="216" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="217" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="218" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="219" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="220" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="221" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="222" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="223" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="224" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="225" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="226" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="227" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="228" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="229" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="230" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="231" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="232" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="233" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="234" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="235" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="236" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="237" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="238" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="239" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="240" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="241" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="242" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="243" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="244" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="245" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="246" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="247" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="248" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="249" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="250" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="251" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="252" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="253" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="254" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="255" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="256" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="257" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="258" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="259" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="260" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="261" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="262" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="263" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="264" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="265" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="266" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="267" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="268" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="269" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="270" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="271" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="272" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="273" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="274" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="275" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="276" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="277" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="278" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="279" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="280" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="281" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="282" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="283" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="284" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="285" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="286" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="287" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="288" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="289" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="290" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="291" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="292" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="293" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="294" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="295" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="296" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="297" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="298" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="299" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="300" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="301" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="302" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="303" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="304" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="305" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="306" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="307" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="308" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="309" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="310" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="311" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="312" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="313" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="314" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="315" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="316" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="317" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="318" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="319" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="320" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="321" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="322" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="323" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="324" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="325" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="326" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="327" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="328" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="329" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="330" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="331" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="332" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="333" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="334" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="335" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="336" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="337" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="338" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="339" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="340" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="341" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="342" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="343" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="344" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="345" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="346" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="347" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="348" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="349" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="350" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="351" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="352" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="353" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="354" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="355" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="356" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="357" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="358" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="359" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="360" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="361" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="362" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="363" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="364" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="365" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="366" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="367" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="368" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="369" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="370" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="371" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="372" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="373" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="374" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="375" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="376" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="377" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="378" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="379" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="380" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="381" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="382" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="383" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="384" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="385" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="386" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="387" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="388" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="389" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="390" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="391" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="392" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="393" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="394" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="395" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="396" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="397" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="398" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="399" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="400" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="401" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="402" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="403" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="404" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="405" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="406" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="407" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="408" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="409" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="410" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="411" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="412" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="413" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="414" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="415" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="416" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="417" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="418" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="419" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="420" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="421" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="422" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="423" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="424" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="425" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="426" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="427" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="428" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="429" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="430" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="431" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="432" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="433" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="434" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="435" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="436" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="437" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="438" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="439" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="440" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="441" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="442" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="443" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="444" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="445" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="446" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="447" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="448" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="449" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="450" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="451" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="452" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="453" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="454" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="455" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="456" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="457" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="458" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="459" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="460" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="461" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="462" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="463" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="464" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="465" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="466" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="467" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="468" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="469" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="470" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="471" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="472" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="473" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="474" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="475" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="476" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="477" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="478" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="479" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="480" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="481" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="482" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="483" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="484" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="485" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="486" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="487" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="488" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="489" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="490" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="491" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="492" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="493" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="494" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="495" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="496" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="497" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="498" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="499" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="500" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="501" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="502" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="503" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="504" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="505" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="506" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="507" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="508" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="509" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="510" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="511" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="512" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="513" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="514" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="515" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="516" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="517" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="518" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="519" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="520" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="521" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="522" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="523" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="524" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="525" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="526" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="527" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="528" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="529" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="530" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="531" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="532" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="533" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="534" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="535" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="536" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="537" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="538" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="539" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="540" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="541" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="542" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="543" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="544" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="545" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="546" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="547" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="548" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="549" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="550" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="551" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="552" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="553" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="554" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="555" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="556" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="557" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="558" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="559" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="560" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="561" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="562" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="563" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="564" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="565" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="566" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="567" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="568" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="569" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="570" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="571" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="572" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="573" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="574" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="575" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="576" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="577" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="578" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="579" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="580" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="581" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="582" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="583" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="584" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="585" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="586" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="587" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="588" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="589" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="590" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="591" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="592" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="593" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="594" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="595" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="596" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="597" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="598" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="599" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="600" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="601" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="602" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="603" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="604" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="605" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="606" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="607" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="608" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="609" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="610" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="611" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="612" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="613" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="614" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="615" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="616" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="617" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="618" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="619" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="620" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="621" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="622" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="623" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="624" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="625" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="626" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="627" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="628" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="629" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="630" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="631" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="632" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="633" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="634" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="635" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="636" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="637" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="638" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="639" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="640" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="641" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="642" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="643" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="644" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="645" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="646" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="647" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="648" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="649" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="650" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="651" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="652" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="653" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="654" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="655" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="656" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="657" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="658" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="659" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="660" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="661" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="662" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="663" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="664" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="665" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="666" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="667" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="668" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="669" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="670" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="671" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="672" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="673" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="674" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="675" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="676" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="677" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="678" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="679" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="680" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="681" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="682" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="683" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="684" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="685" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="686" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="687" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="688" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="689" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="690" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="691" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="692" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="693" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="694" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="695" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="696" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="697" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="698" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="699" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="700" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="701" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="702" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="703" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="704" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="705" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="706" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="707" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="708" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="709" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="710" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="711" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="712" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="713" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="714" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="715" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="716" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="717" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="718" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="719" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="720" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="721" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="722" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="723" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="724" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="725" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="726" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="727" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="728" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="729" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="730" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="731" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="732" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="733" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="734" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="735" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="736" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="737" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="738" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="739" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="740" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="741" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="742" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="743" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="744" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="745" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="746" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="747" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="748" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="749" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="750" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="751" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="752" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="753" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="754" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="755" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="756" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="757" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="758" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="759" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="760" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="761" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="762" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="763" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="764" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="765" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="766" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="767" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="768" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="769" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="770" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="771" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="772" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="773" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="774" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="775" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="776" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="777" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="778" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="779" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="780" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="781" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="782" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="783" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="784" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="785" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="786" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="787" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="788" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="789" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="790" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="791" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="792" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="793" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="794" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="795" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="796" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="797" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="798" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="799" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="800" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="801" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="802" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="803" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="804" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="805" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="806" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="807" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="808" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="809" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="810" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="811" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="812" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="813" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="814" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="815" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="816" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="817" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="818" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="819" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="820" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="821" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="822" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="823" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="824" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="825" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="826" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="827" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="828" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="829" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="830" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="831" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="832" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="833" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="834" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="835" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="836" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="837" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="838" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="839" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="840" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="841" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="842" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="843" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="844" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="845" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="846" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="847" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="848" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="849" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="850" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="851" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="852" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="853" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="854" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="855" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="856" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="857" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="858" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="859" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="860" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="861" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="862" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="863" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="864" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="865" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="866" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="867" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="868" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="869" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="870" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="871" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="872" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="873" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="874" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="875" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="876" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="877" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="878" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="879" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="880" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="881" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="882" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="883" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="884" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="885" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="886" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="887" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="888" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="889" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="890" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="891" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="892" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="893" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="894" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="895" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="896" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="897" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="898" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="899" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="900" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="901" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="902" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="903" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="904" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="905" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="906" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="907" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="908" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="909" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="910" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="911" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="912" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="913" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="914" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="915" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="916" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="917" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="918" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="919" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="920" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="921" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="922" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="923" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="924" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="925" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="926" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="927" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="928" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="929" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="930" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="931" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="932" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="933" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="934" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="935" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="936" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="937" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="938" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="939" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="940" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="941" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="942" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="943" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="944" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="945" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="946" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="947" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="948" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="949" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="950" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="951" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="952" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="953" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="954" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="955" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="956" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="957" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="958" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="959" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="960" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="961" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="962" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="963" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="964" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="965" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="966" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="967" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="968" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="969" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="970" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="971" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="972" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="973" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="974" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="975" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="976" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="977" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="978" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="979" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="980" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="981" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="982" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="983" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="984" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="985" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="986" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="987" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="988" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="989" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="990" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="991" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="992" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="993" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="994" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="995" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="996" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="997" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="998" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="999" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1000" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -23405,1116 +25693,4 @@
     <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F1000"/>
-  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
-    <col min="2" max="2" width="69.5" customWidth="1"/>
-    <col min="3" max="26" width="8.609375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-    </row>
-    <row r="4" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-    </row>
-    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-    </row>
-    <row r="6" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-    </row>
-    <row r="7" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-    </row>
-    <row r="8" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-    </row>
-    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-    </row>
-    <row r="10" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-    </row>
-    <row r="11" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-    </row>
-    <row r="12" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="17" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="18" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="20" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="26" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="27" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="28" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="33" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="43" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="65" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="66" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="67" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="68" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="69" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="70" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="71" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="72" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="73" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="74" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="75" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="76" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="77" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="78" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="79" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="80" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="81" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="82" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="83" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="84" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="85" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="86" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="87" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="88" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="89" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="90" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="91" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="92" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="93" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="94" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="95" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="96" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="97" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="98" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="99" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="100" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="101" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="102" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="103" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="104" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="105" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="106" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="107" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="108" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="109" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="110" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="111" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="112" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="113" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="114" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="115" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="116" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="117" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="118" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="119" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="120" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="121" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="122" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="123" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="124" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="125" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="126" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="127" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="128" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="129" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="130" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="131" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="132" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="133" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="134" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="135" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="136" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="137" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="138" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="139" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="140" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="141" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="142" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="143" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="144" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="145" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="146" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="147" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="148" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="149" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="150" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="151" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="152" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="153" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="154" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="155" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="156" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="157" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="158" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="159" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="160" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="161" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="162" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="163" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="164" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="165" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="166" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="167" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="168" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="169" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="170" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="171" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="172" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="173" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="174" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="175" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="176" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="177" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="178" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="179" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="180" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="181" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="182" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="183" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="184" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="185" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="186" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="187" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="188" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="189" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="190" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="191" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="192" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="193" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="194" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="195" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="196" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="197" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="198" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="199" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="200" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="201" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="202" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="203" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="204" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="205" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="206" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="207" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="208" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="209" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="210" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="211" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="212" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="213" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="214" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="215" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="216" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="217" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="218" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="219" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="220" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="221" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="222" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="223" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="224" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="225" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="226" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="227" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="228" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="229" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="230" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="231" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="232" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="233" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="234" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="235" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="236" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="237" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="238" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="239" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="240" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="241" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="242" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="243" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="244" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="245" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="246" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="247" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="248" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="249" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="250" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="251" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="252" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="253" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="254" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="255" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="256" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="257" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="258" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="259" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="260" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="261" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="262" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="263" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="264" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="265" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="266" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="267" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="268" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="269" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="270" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="271" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="272" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="273" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="274" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="275" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="276" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="277" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="278" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="279" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="280" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="281" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="282" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="283" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="284" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="285" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="286" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="287" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="288" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="289" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="290" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="291" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="292" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="293" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="294" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="295" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="296" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="297" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="298" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="299" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="300" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="301" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="302" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="303" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="304" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="305" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="306" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="307" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="308" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="309" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="310" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="311" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="312" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="313" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="314" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="315" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="316" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="317" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="318" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="319" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="320" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="321" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="322" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="323" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="324" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="325" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="326" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="327" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="328" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="329" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="330" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="331" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="332" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="333" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="334" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="335" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="336" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="337" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="338" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="339" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="340" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="341" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="342" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="343" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="344" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="345" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="346" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="347" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="348" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="349" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="350" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="351" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="352" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="353" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="354" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="355" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="356" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="357" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="358" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="359" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="360" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="361" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="362" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="363" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="364" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="365" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="366" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="367" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="368" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="369" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="370" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="371" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="372" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="373" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="374" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="375" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="376" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="377" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="378" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="379" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="380" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="381" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="382" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="383" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="384" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="385" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="386" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="387" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="388" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="389" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="390" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="391" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="392" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="393" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="394" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="395" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="396" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="397" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="398" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="399" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="400" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="401" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="402" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="403" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="404" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="405" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="406" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="407" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="408" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="409" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="410" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="411" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="412" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="413" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="414" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="415" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="416" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="417" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="418" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="419" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="420" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="421" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="422" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="423" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="424" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="425" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="426" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="427" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="428" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="429" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="430" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="431" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="432" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="433" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="434" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="435" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="436" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="437" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="438" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="439" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="440" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="441" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="442" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="443" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="444" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="445" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="446" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="447" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="448" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="449" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="450" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="451" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="452" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="453" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="454" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="455" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="456" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="457" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="458" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="459" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="460" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="461" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="462" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="463" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="464" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="465" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="466" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="467" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="468" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="469" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="470" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="471" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="472" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="473" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="474" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="475" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="476" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="477" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="478" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="479" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="480" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="481" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="482" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="483" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="484" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="485" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="486" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="487" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="488" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="489" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="490" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="491" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="492" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="493" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="494" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="495" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="496" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="497" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="498" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="499" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="500" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="501" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="502" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="503" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="504" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="505" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="506" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="507" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="508" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="509" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="510" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="511" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="512" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="513" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="514" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="515" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="516" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="517" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="518" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="519" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="520" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="521" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="522" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="523" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="524" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="525" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="526" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="527" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="528" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="529" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="530" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="531" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="532" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="533" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="534" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="535" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="536" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="537" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="538" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="539" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="540" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="541" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="542" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="543" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="544" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="545" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="546" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="547" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="548" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="549" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="550" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="551" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="552" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="553" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="554" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="555" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="556" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="557" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="558" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="559" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="560" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="561" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="562" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="563" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="564" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="565" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="566" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="567" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="568" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="569" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="570" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="571" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="572" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="573" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="574" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="575" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="576" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="577" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="578" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="579" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="580" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="581" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="582" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="583" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="584" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="585" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="586" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="587" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="588" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="589" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="590" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="591" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="592" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="593" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="594" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="595" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="596" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="597" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="598" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="599" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="600" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="601" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="602" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="603" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="604" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="605" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="606" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="607" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="608" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="609" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="610" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="611" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="612" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="613" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="614" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="615" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="616" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="617" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="618" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="619" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="620" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="621" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="622" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="623" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="624" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="625" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="626" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="627" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="628" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="629" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="630" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="631" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="632" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="633" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="634" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="635" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="636" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="637" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="638" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="639" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="640" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="641" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="642" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="643" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="644" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="645" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="646" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="647" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="648" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="649" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="650" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="651" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="652" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="653" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="654" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="655" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="656" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="657" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="658" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="659" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="660" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="661" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="662" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="663" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="664" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="665" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="666" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="667" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="668" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="669" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="670" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="671" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="672" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="673" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="674" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="675" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="676" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="677" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="678" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="679" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="680" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="681" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="682" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="683" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="684" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="685" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="686" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="687" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="688" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="689" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="690" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="691" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="692" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="693" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="694" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="695" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="696" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="697" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="698" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="699" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="700" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="701" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="702" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="703" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="704" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="705" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="706" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="707" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="708" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="709" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="710" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="711" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="712" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="713" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="714" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="715" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="716" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="717" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="718" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="719" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="720" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="721" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="722" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="723" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="724" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="725" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="726" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="727" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="728" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="729" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="730" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="731" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="732" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="733" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="734" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="735" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="736" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="737" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="738" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="739" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="740" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="741" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="742" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="743" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="744" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="745" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="746" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="747" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="748" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="749" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="750" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="751" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="752" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="753" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="754" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="755" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="756" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="757" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="758" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="759" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="760" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="761" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="762" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="763" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="764" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="765" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="766" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="767" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="768" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="769" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="770" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="771" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="772" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="773" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="774" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="775" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="776" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="777" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="778" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="779" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="780" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="781" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="782" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="783" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="784" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="785" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="786" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="787" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="788" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="789" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="790" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="791" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="792" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="793" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="794" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="795" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="796" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="797" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="798" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="799" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="800" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="801" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="802" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="803" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="804" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="805" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="806" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="807" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="808" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="809" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="810" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="811" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="812" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="813" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="814" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="815" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="816" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="817" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="818" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="819" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="820" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="821" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="822" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="823" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="824" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="825" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="826" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="827" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="828" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="829" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="830" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="831" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="832" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="833" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="834" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="835" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="836" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="837" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="838" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="839" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="840" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="841" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="842" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="843" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="844" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="845" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="846" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="847" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="848" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="849" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="850" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="851" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="852" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="853" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="854" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="855" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="856" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="857" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="858" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="859" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="860" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="861" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="862" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="863" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="864" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="865" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="866" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="867" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="868" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="869" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="870" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="871" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="872" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="873" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="874" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="875" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="876" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="877" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="878" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="879" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="880" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="881" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="882" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="883" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="884" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="885" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="886" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="887" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="888" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="889" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="890" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="891" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="892" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="893" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="894" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="895" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="896" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="897" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="898" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="899" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="900" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="901" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="902" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="903" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="904" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="905" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="906" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="907" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="908" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="909" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="910" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="911" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="912" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="913" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="914" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="915" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="916" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="917" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="918" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="919" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="920" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="921" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="922" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="923" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="924" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="925" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="926" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="927" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="928" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="929" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="930" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="931" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="932" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="933" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="934" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="935" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="936" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="937" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="938" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="939" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="940" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="941" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="942" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="943" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="944" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="945" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="946" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="947" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="948" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="949" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="950" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="951" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="952" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="953" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="954" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="955" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="956" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="957" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="958" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="959" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="960" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="961" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="962" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="963" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="964" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="965" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="966" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="967" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="968" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="969" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="970" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="971" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="972" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="973" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="974" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="975" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="976" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="977" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="978" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="979" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="980" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="981" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="982" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="983" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="984" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="985" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="986" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="987" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="988" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="989" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="990" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="991" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="992" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="993" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="994" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="995" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="996" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="997" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="998" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="999" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="1000" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3564ABAF-5387-4390-A0CA-11B37BBCCD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5CDF46-1E38-4947-8D95-C921E571BDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="333">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1089,6 +1089,37 @@
   <si>
     <t>[Question01:What are the main benefits of Illus Magnetic Track Lights?,Answer01:Illus Magnetic Track Lights offer unparalleled flexibility, allowing you to easily reposition or add light fixtures without tools. They provide a sleek, minimalist aesthetic, are highly energy-efficient, and offer versatile lighting solutions for various spaces.],[Question02:How easy is it to install Illus Magnetic Track Lighting systems?,Answer02:Installation is generally straightforward, designed for both professionals and DIY enthusiasts. The magnetic connection simplifies the process of attaching and detaching light modules, making setup and modification quick and easy compared to traditional track systems.],[Question03:Can Illus Magnetic Track Lights be used in any room?,Answer03:Yes, their versatile design makes them suitable for a wide range of applications, including living rooms, kitchens, bedrooms, offices, retail spaces, and art galleries. They are particularly effective where flexible and adaptable lighting is desired.],[Question04:What types of light fixtures are compatible with Illus Magnetic Tracks?,Answer04:Illus Magnetic Tracks are compatible with a variety of magnetic-based light fixtures, including spotlights, floodlights, pendant lights, and linear lights. This allows for diverse lighting designs and functionalities within a single system.],[Question05:Are Illus Magnetic Track Lights energy-efficient?,Answer05:Absolutely. Most Illus Magnetic Track Light systems utilize LED technology, which is highly energy-efficient, offering significant savings on electricity bills and a longer lifespan compared to traditional lighting sources.]</t>
   </si>
+  <si>
+    <t>Hotspot Icon URL</t>
+  </si>
+  <si>
+    <r>
+      <t>Rotate X:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>68°</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1097,7 +1128,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1230,6 +1261,15 @@
       <sz val="10"/>
       <name val="Inter"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1359,7 +1399,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1539,6 +1579,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1821,8 +1864,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:N226">
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:O226">
+  <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="FloorID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Scene Order"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="SceneID"/>
@@ -1837,6 +1880,7 @@
     <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="4"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Hotspot Hover Active"/>
     <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{9C4C8152-4844-4261-A684-0FACC6958478}" name="Hotspot Icon URL"/>
   </tableColumns>
   <tableStyleInfo name="2. Hotspots Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9642,7 +9686,7 @@
     <col min="11" max="12" width="8.609375" customWidth="1"/>
     <col min="13" max="13" width="22.5" customWidth="1"/>
     <col min="14" max="14" width="20.0546875" customWidth="1"/>
-    <col min="15" max="15" width="18.109375" customWidth="1"/>
+    <col min="15" max="15" width="94.94140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.609375" style="36" customWidth="1"/>
     <col min="18" max="22" width="8.609375" customWidth="1"/>
   </cols>
@@ -9690,7 +9734,9 @@
       <c r="N1" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="O1" s="22"/>
+      <c r="O1" s="68" t="s">
+        <v>331</v>
+      </c>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
       <c r="R1" s="22"/>
@@ -9734,6 +9780,9 @@
         <v>1</v>
       </c>
       <c r="N2" s="36"/>
+      <c r="O2" s="59" t="s">
+        <v>332</v>
+      </c>
       <c r="Q2"/>
     </row>
     <row r="3" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -21637,10 +21686,13 @@
     <row r="993" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg" xr:uid="{AB6510A7-7390-46EE-95A5-CAD1462285D0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21723,7 +21775,7 @@
       <c r="H2" s="42">
         <v>18</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="46" t="s">
         <v>214</v>
       </c>
       <c r="J2" s="42" t="s">
@@ -22415,9 +22467,10 @@
     <hyperlink ref="C8" r:id="rId48" xr:uid="{91C8FB8B-79DC-4417-8259-B1DD9EF5CC29}"/>
     <hyperlink ref="C9" r:id="rId49" xr:uid="{311F0620-89FE-400B-B5B1-F5F4B6263053}"/>
     <hyperlink ref="C16" r:id="rId50" xr:uid="{7902F696-8305-4236-B7B1-2A4014E977E9}"/>
+    <hyperlink ref="I2" r:id="rId51" xr:uid="{BD5D484B-9903-4C02-9782-03A45E8336BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId51"/>
+  <pageSetup orientation="landscape" r:id="rId52"/>
 </worksheet>
 </file>
 

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5CDF46-1E38-4947-8D95-C921E571BDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB724EE2-C39D-4D27-844A-ABCF9EEED0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1093,32 +1093,7 @@
     <t>Hotspot Icon URL</t>
   </si>
   <si>
-    <r>
-      <t>Rotate X:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color theme="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>68°</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color theme="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
-    </r>
+    <t>Rotate X:68°,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1103,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1260,15 +1235,6 @@
     <font>
       <sz val="10"/>
       <name val="Inter"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB724EE2-C39D-4D27-844A-ABCF9EEED0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AFDED7-55A9-44C9-A92F-12E1D94E45DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="333">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -9790,6 +9790,9 @@
         <v>1</v>
       </c>
       <c r="N3" s="36"/>
+      <c r="O3" s="59" t="s">
+        <v>332</v>
+      </c>
       <c r="Q3"/>
     </row>
     <row r="4" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -9831,6 +9834,9 @@
         <v>1</v>
       </c>
       <c r="N4" s="7"/>
+      <c r="O4" s="59" t="s">
+        <v>332</v>
+      </c>
       <c r="Q4"/>
     </row>
     <row r="5" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -21654,11 +21660,12 @@
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg" xr:uid="{AB6510A7-7390-46EE-95A5-CAD1462285D0}"/>
+    <hyperlink ref="O3:O4" r:id="rId2" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg" xr:uid="{52463748-F332-4555-9531-8ADF55FB4B22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId2"/>
+  <pageSetup orientation="landscape" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AFDED7-55A9-44C9-A92F-12E1D94E45DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07DFA27-AB1E-45B1-810A-E73C844647BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1093,7 +1093,7 @@
     <t>Hotspot Icon URL</t>
   </si>
   <si>
-    <t>Rotate X:68°,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
+    <t>Size:30px,Rotate X:68°,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
   </si>
 </sst>
 </file>
@@ -21660,7 +21660,7 @@
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg" xr:uid="{AB6510A7-7390-46EE-95A5-CAD1462285D0}"/>
-    <hyperlink ref="O3:O4" r:id="rId2" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg" xr:uid="{52463748-F332-4555-9531-8ADF55FB4B22}"/>
+    <hyperlink ref="O3:O4" r:id="rId2" display="https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg" xr:uid="{9FCA092C-CC0D-4718-8629-4DB97872B602}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId3"/>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07DFA27-AB1E-45B1-810A-E73C844647BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6220B753-265E-4F13-B2A4-22F1D31BBD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="334">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1094,6 +1094,9 @@
   </si>
   <si>
     <t>Size:30px,Rotate X:68°,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
+  </si>
+  <si>
+    <t>Size:80px,Rotate X:68°,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
   </si>
 </sst>
 </file>
@@ -9652,7 +9655,7 @@
     <col min="11" max="12" width="8.609375" customWidth="1"/>
     <col min="13" max="13" width="22.5" customWidth="1"/>
     <col min="14" max="14" width="20.0546875" customWidth="1"/>
-    <col min="15" max="15" width="94.94140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="104.38671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.609375" style="36" customWidth="1"/>
     <col min="18" max="22" width="8.609375" customWidth="1"/>
   </cols>
@@ -9747,7 +9750,7 @@
       </c>
       <c r="N2" s="36"/>
       <c r="O2" s="59" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q2"/>
     </row>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6220B753-265E-4F13-B2A4-22F1D31BBD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8847CDF4-24E9-4B64-9E7A-ACE57B0BA1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="335">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1097,6 +1097,9 @@
   </si>
   <si>
     <t>Size:80px,Rotate X:68°,Y:0°,Z:0°,Perspective:130°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
+  </si>
+  <si>
+    <t>Size:30px,Rotate X:68°,Y:0°,Z:0°,Perspective:160°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
   </si>
 </sst>
 </file>
@@ -9838,7 +9841,7 @@
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="59" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q4"/>
     </row>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B170E9-89D5-4061-9325-66F32D7C7C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0A3829-9E69-4D29-A13B-10BDDDA6CC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="339">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1378,6 +1378,9 @@
   </si>
   <si>
     <t>QNA</t>
+  </si>
+  <si>
+    <t>QNA Hotspot Custon ICON</t>
   </si>
 </sst>
 </file>
@@ -1664,7 +1667,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1861,12 +1864,39 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <name val="Inter"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2114,24 +2144,24 @@
   </dxfs>
   <tableStyles count="4">
     <tableStyle name="1. Scenes Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="firstRowStripe" dxfId="22"/>
-      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="firstRowStripe" dxfId="23"/>
+      <tableStyleElement type="secondRowStripe" dxfId="22"/>
     </tableStyle>
     <tableStyle name="2. Hotspots Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="secondRowStripe" dxfId="19"/>
     </tableStyle>
     <tableStyle name="3. Floors Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="secondRowStripe" dxfId="16"/>
     </tableStyle>
     <tableStyle name="4. Styles Sheet (Custom CSS)-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="firstRowStripe" dxfId="13"/>
-      <tableStyleElement type="secondRowStripe" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2173,7 +2203,7 @@
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Floor map Details"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Floor Map Active"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Get Pitch/Yaw Data"/>
-    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="11"/>
+    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="12"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Scen Identifier"/>
     <tableColumn id="28" xr3:uid="{F3D3E641-7A49-4E3D-A155-18F57FACDDFD}" name="Map Data"/>
   </tableColumns>
@@ -2195,9 +2225,9 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Pitch"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Yaw"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Rotation"/>
-    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="11"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Hotspot Hover Active"/>
-    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{9C4C8152-4844-4261-A684-0FACC6958478}" name="Hotspot Icon URL"/>
   </tableColumns>
   <tableStyleInfo name="2. Hotspots Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2205,14 +2235,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A1982990-8932-4703-94E4-180C79928346}" name="Table_36" displayName="Table_36" ref="A1:F4" dataDxfId="2">
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AC2068F9-4426-4263-A845-5946EB10AED0}" name="SL#" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{3D9EE8D6-E76E-45C3-BCE6-12CC183EE067}" name="Hotspot Name" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{A97AF90C-72ED-4B03-A59A-8CA0E1A8B08B}" name="Title" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{D20C3793-59AA-4FED-9D83-26F7442A226B}" name="Qestions and answers" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{061E7697-FC0B-487F-9C65-88C25FA344FC}" name="Answer Audio URL or TTS" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{6BF83100-29F6-4DAC-9D40-8965E58C45A5}" name="Answer Media URL" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A1982990-8932-4703-94E4-180C79928346}" name="Table_36" displayName="Table_36" ref="A1:G4" dataDxfId="3">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{AC2068F9-4426-4263-A845-5946EB10AED0}" name="SL#" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{3D9EE8D6-E76E-45C3-BCE6-12CC183EE067}" name="Hotspot Name" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{243D11AF-E320-4A63-B33E-DB4DEE02C26D}" name="QNA Hotspot Custon ICON" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{A97AF90C-72ED-4B03-A59A-8CA0E1A8B08B}" name="Title" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{D20C3793-59AA-4FED-9D83-26F7442A226B}" name="Qestions and answers" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{061E7697-FC0B-487F-9C65-88C25FA344FC}" name="Answer Audio URL or TTS" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{6BF83100-29F6-4DAC-9D40-8965E58C45A5}" name="Answer Media URL" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="1. Scenes Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9940,7 +9971,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -23008,19 +23039,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9379027C-E3D3-47ED-99BC-9D546DD86D06}">
-  <dimension ref="A1:H983"/>
+  <dimension ref="A1:I983"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="27.609375" customWidth="1"/>
-    <col min="4" max="4" width="138.94140625" customWidth="1"/>
-    <col min="5" max="5" width="33.38671875" customWidth="1"/>
-    <col min="6" max="6" width="34.5" customWidth="1"/>
-    <col min="7" max="27" width="8.609375" customWidth="1"/>
+    <col min="3" max="3" width="13.609375" customWidth="1"/>
+    <col min="4" max="4" width="27.609375" customWidth="1"/>
+    <col min="5" max="5" width="138.94140625" customWidth="1"/>
+    <col min="6" max="6" width="33.38671875" customWidth="1"/>
+    <col min="7" max="7" width="34.5" customWidth="1"/>
+    <col min="8" max="28" width="8.609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="40.5" customHeight="1">
+    <row r="1" spans="1:9" ht="52.5" customHeight="1">
       <c r="A1" s="29" t="s">
         <v>287</v>
       </c>
@@ -23028,90 +23060,102 @@
         <v>149</v>
       </c>
       <c r="C1" s="63" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" s="63" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="E1" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="F1" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="G1" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:8" ht="123">
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:9" ht="123">
       <c r="A2" s="68">
         <v>1</v>
       </c>
       <c r="B2" s="69" t="s">
         <v>288</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="74" t="s">
+        <v>323</v>
+      </c>
+      <c r="D2" s="70" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="E2" s="70" t="s">
         <v>334</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="F2" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="72"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="67"/>
-    </row>
-    <row r="3" spans="1:8" ht="100.5" customHeight="1">
+      <c r="G2" s="72"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="67"/>
+    </row>
+    <row r="3" spans="1:9" ht="100.5" customHeight="1">
       <c r="A3" s="68">
         <v>1</v>
       </c>
       <c r="B3" s="69" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="74" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="70" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="E3" s="70" t="s">
         <v>334</v>
       </c>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="71"/>
+      <c r="G3" s="72" t="s">
         <v>214</v>
       </c>
-      <c r="G3" s="30"/>
-    </row>
-    <row r="4" spans="1:8" ht="108.9" customHeight="1">
+      <c r="H3" s="30"/>
+    </row>
+    <row r="4" spans="1:9" ht="108.9" customHeight="1">
       <c r="A4" s="68">
         <v>1</v>
       </c>
       <c r="B4" s="69" t="s">
         <v>290</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="74" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="70" t="s">
         <v>336</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="E4" s="70" t="s">
         <v>334</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="F4" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="G4" s="72" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="12" customHeight="1"/>
-    <row r="6" spans="1:8" ht="12" customHeight="1"/>
-    <row r="7" spans="1:8" ht="12" customHeight="1"/>
-    <row r="8" spans="1:8" ht="12" customHeight="1"/>
-    <row r="9" spans="1:8" ht="12" customHeight="1"/>
-    <row r="10" spans="1:8" ht="12" customHeight="1"/>
-    <row r="11" spans="1:8" ht="12" customHeight="1"/>
-    <row r="12" spans="1:8" ht="12" customHeight="1"/>
-    <row r="13" spans="1:8" ht="12" customHeight="1"/>
-    <row r="14" spans="1:8" ht="12" customHeight="1"/>
-    <row r="15" spans="1:8" ht="12" customHeight="1"/>
-    <row r="16" spans="1:8" ht="12" customHeight="1"/>
+    <row r="5" spans="1:9" ht="12" customHeight="1"/>
+    <row r="6" spans="1:9" ht="12" customHeight="1"/>
+    <row r="7" spans="1:9" ht="12" customHeight="1"/>
+    <row r="8" spans="1:9" ht="12" customHeight="1"/>
+    <row r="9" spans="1:9" ht="12" customHeight="1"/>
+    <row r="10" spans="1:9" ht="12" customHeight="1"/>
+    <row r="11" spans="1:9" ht="12" customHeight="1"/>
+    <row r="12" spans="1:9" ht="12" customHeight="1"/>
+    <row r="13" spans="1:9" ht="12" customHeight="1"/>
+    <row r="14" spans="1:9" ht="12" customHeight="1"/>
+    <row r="15" spans="1:9" ht="12" customHeight="1"/>
+    <row r="16" spans="1:9" ht="12" customHeight="1"/>
     <row r="17" ht="12" customHeight="1"/>
     <row r="18" ht="12" customHeight="1"/>
     <row r="19" ht="12" customHeight="1"/>
@@ -24081,13 +24125,16 @@
     <row r="983" ht="12" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{05BC715E-E711-455E-821B-E85633EF3067}"/>
-    <hyperlink ref="F4" r:id="rId2" xr:uid="{746D765C-3507-4A06-BBE0-F8B6061F0F6A}"/>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{05BC715E-E711-455E-821B-E85633EF3067}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{746D765C-3507-4A06-BBE0-F8B6061F0F6A}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{9279F6D0-641C-49D6-B7E1-11BD4E45CCE8}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{B5D20B47-F34E-42CB-A216-2576EE0D51F1}"/>
+    <hyperlink ref="C4" r:id="rId5" xr:uid="{0C210614-9EEA-41D0-A2A0-711DE83FA584}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId3"/>
+  <pageSetup orientation="landscape" r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0A3829-9E69-4D29-A13B-10BDDDA6CC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79ADB394-B0BE-47D8-B7FB-CAB94061DC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1076,9 +1076,6 @@
   </si>
   <si>
     <t>Qestions and answers</t>
-  </si>
-  <si>
-    <t>Answer Audio URL or TTS</t>
   </si>
   <si>
     <t>Answer Media URL</t>
@@ -1381,6 +1378,9 @@
   </si>
   <si>
     <t>QNA Hotspot Custon ICON</t>
+  </si>
+  <si>
+    <t>Answer Audio URL</t>
   </si>
 </sst>
 </file>
@@ -2242,7 +2242,7 @@
     <tableColumn id="7" xr3:uid="{243D11AF-E320-4A63-B33E-DB4DEE02C26D}" name="QNA Hotspot Custon ICON" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{A97AF90C-72ED-4B03-A59A-8CA0E1A8B08B}" name="Title" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{D20C3793-59AA-4FED-9D83-26F7442A226B}" name="Qestions and answers" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{061E7697-FC0B-487F-9C65-88C25FA344FC}" name="Answer Audio URL or TTS" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{061E7697-FC0B-487F-9C65-88C25FA344FC}" name="Answer Audio URL" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{6BF83100-29F6-4DAC-9D40-8965E58C45A5}" name="Answer Media URL" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="1. Scenes Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -10084,7 +10084,7 @@
         <v>207</v>
       </c>
       <c r="O1" s="65" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="N2" s="36"/>
       <c r="O2" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q2"/>
     </row>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="N3" s="36"/>
       <c r="O3" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="59" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q4"/>
     </row>
@@ -10368,7 +10368,7 @@
         <v>291</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="3" t="s">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="N10" s="36"/>
       <c r="O10" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q10"/>
     </row>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="N11" s="36"/>
       <c r="O11" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q11"/>
     </row>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="N17" s="36"/>
       <c r="O17" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q17"/>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="N18" s="36"/>
       <c r="O18" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q18"/>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="N24" s="36"/>
       <c r="O24" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q24"/>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="N25" s="36"/>
       <c r="O25" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q25"/>
     </row>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="N31" s="36"/>
       <c r="O31" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q31"/>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="N32" s="36"/>
       <c r="O32" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q32"/>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="N38" s="36"/>
       <c r="O38" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q38"/>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="N39" s="36"/>
       <c r="O39" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q39"/>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="N45" s="36"/>
       <c r="O45" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q45"/>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="N46" s="36"/>
       <c r="O46" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q46"/>
     </row>
@@ -12236,7 +12236,7 @@
       </c>
       <c r="N52" s="36"/>
       <c r="O52" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q52"/>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="N53" s="36"/>
       <c r="O53" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q53"/>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="N59" s="36"/>
       <c r="O59" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q59"/>
     </row>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="N60" s="36"/>
       <c r="O60" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q60"/>
     </row>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="N66" s="36"/>
       <c r="O66" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q66"/>
     </row>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="N67" s="36"/>
       <c r="O67" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q67"/>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="N73" s="36"/>
       <c r="O73" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q73"/>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="N74" s="36"/>
       <c r="O74" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q74"/>
     </row>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="N80" s="36"/>
       <c r="O80" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q80"/>
     </row>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="N81" s="36"/>
       <c r="O81" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q81"/>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="N87" s="36"/>
       <c r="O87" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q87"/>
     </row>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="N88" s="36"/>
       <c r="O88" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q88"/>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="N94" s="36"/>
       <c r="O94" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q94"/>
     </row>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="N95" s="36"/>
       <c r="O95" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q95"/>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="N101" s="36"/>
       <c r="O101" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q101"/>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="N102" s="36"/>
       <c r="O102" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q102"/>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="N108" s="36"/>
       <c r="O108" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q108"/>
     </row>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="N109" s="36"/>
       <c r="O109" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q109"/>
     </row>
@@ -14873,7 +14873,7 @@
       </c>
       <c r="N115" s="36"/>
       <c r="O115" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q115"/>
     </row>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="N116" s="36"/>
       <c r="O116" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q116"/>
     </row>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="N122" s="36"/>
       <c r="O122" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q122"/>
     </row>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="N123" s="36"/>
       <c r="O123" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q123"/>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="N129" s="36"/>
       <c r="O129" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q129"/>
     </row>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="N130" s="36"/>
       <c r="O130" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q130"/>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="N136" s="36"/>
       <c r="O136" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q136"/>
     </row>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="N137" s="36"/>
       <c r="O137" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q137"/>
     </row>
@@ -16045,7 +16045,7 @@
       </c>
       <c r="N143" s="36"/>
       <c r="O143" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q143"/>
     </row>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="N144" s="36"/>
       <c r="O144" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q144"/>
     </row>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="N150" s="36"/>
       <c r="O150" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q150"/>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="N151" s="36"/>
       <c r="O151" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q151"/>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="N157" s="36"/>
       <c r="O157" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q157"/>
     </row>
@@ -16675,7 +16675,7 @@
       </c>
       <c r="N158" s="36"/>
       <c r="O158" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q158"/>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="N164" s="7"/>
       <c r="O164" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="165" spans="1:17" ht="12" customHeight="1">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="N165" s="7"/>
       <c r="O165" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="166" spans="1:17" ht="12" customHeight="1">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="N171" s="7"/>
       <c r="O171" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="172" spans="1:17" ht="12" customHeight="1">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="N172" s="7"/>
       <c r="O172" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="173" spans="1:17" ht="12" customHeight="1">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="N178" s="7"/>
       <c r="O178" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="179" spans="1:15" ht="12" customHeight="1">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="N179" s="7"/>
       <c r="O179" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="180" spans="1:15" ht="12" customHeight="1">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="N185" s="7"/>
       <c r="O185" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="186" spans="1:15" ht="12" customHeight="1">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="N186" s="7"/>
       <c r="O186" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="187" spans="1:15" ht="12" customHeight="1">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="N192" s="7"/>
       <c r="O192" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="193" spans="1:15" ht="12" customHeight="1">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="N193" s="7"/>
       <c r="O193" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="194" spans="1:15" ht="12" customHeight="1">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="N199" s="7"/>
       <c r="O199" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="200" spans="1:15" ht="12" customHeight="1">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="N200" s="7"/>
       <c r="O200" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="201" spans="1:15" ht="12" customHeight="1">
@@ -18667,7 +18667,7 @@
       </c>
       <c r="N206" s="7"/>
       <c r="O206" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="207" spans="1:15" ht="12" customHeight="1">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="N207" s="7"/>
       <c r="O207" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="208" spans="1:15" ht="12" customHeight="1">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N213" s="7"/>
       <c r="O213" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="214" spans="1:15" ht="12" customHeight="1">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="N214" s="7"/>
       <c r="O214" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="215" spans="1:15" ht="12" customHeight="1">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="N220" s="7"/>
       <c r="O220" s="59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="221" spans="1:15" ht="12" customHeight="1">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="N221" s="7"/>
       <c r="O221" s="59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="222" spans="1:15" ht="12" customHeight="1">
@@ -23060,7 +23060,7 @@
         <v>149</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D1" s="63" t="s">
         <v>158</v>
@@ -23069,10 +23069,10 @@
         <v>326</v>
       </c>
       <c r="F1" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="G1" s="29" t="s">
         <v>327</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>328</v>
       </c>
       <c r="H1" s="30"/>
     </row>
@@ -23081,16 +23081,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C2" s="74" t="s">
         <v>323</v>
       </c>
       <c r="D2" s="70" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E2" s="70" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F2" s="71" t="s">
         <v>49</v>
@@ -23104,16 +23104,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="69" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C3" s="74" t="s">
         <v>323</v>
       </c>
       <c r="D3" s="70" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F3" s="71"/>
       <c r="G3" s="72" t="s">
@@ -23126,16 +23126,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C4" s="74" t="s">
         <v>323</v>
       </c>
       <c r="D4" s="70" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E4" s="70" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F4" s="71" t="s">
         <v>49</v>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79ADB394-B0BE-47D8-B7FB-CAB94061DC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A96111C-CB85-471F-9D38-F5942022DE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="341">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1382,6 +1382,12 @@
   <si>
     <t>Answer Audio URL</t>
   </si>
+  <si>
+    <t>[Answer01:],[Answer02:],[Answer03:https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3],[Answer04:],[Answer05:https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/VoiceOverAR.mp3]</t>
+  </si>
+  <si>
+    <t>[Answer01:],[Answer02:],[Answer03:],[Answer04:https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4],[Answer05:]</t>
+  </si>
 </sst>
 </file>
 
@@ -1390,7 +1396,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1538,6 +1544,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1667,7 +1679,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1867,12 +1879,15 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -1906,11 +1921,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -2144,24 +2154,24 @@
   </dxfs>
   <tableStyles count="4">
     <tableStyle name="1. Scenes Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="24"/>
-      <tableStyleElement type="firstRowStripe" dxfId="23"/>
-      <tableStyleElement type="secondRowStripe" dxfId="22"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="secondRowStripe" dxfId="21"/>
     </tableStyle>
     <tableStyle name="2. Hotspots Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="firstRowStripe" dxfId="20"/>
-      <tableStyleElement type="secondRowStripe" dxfId="19"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
     <tableStyle name="3. Floors Sheet-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="firstRowStripe" dxfId="17"/>
-      <tableStyleElement type="secondRowStripe" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
     </tableStyle>
     <tableStyle name="4. Styles Sheet (Custom CSS)-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="secondRowStripe" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2203,7 +2213,7 @@
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Floor map Details"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Floor Map Active"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Get Pitch/Yaw Data"/>
-    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="12"/>
+    <tableColumn id="27" xr3:uid="{B8D9CC4B-E1D7-4DEF-B6F9-3EC298839093}" name="PromotionURL" dataDxfId="11"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Scen Identifier"/>
     <tableColumn id="28" xr3:uid="{F3D3E641-7A49-4E3D-A155-18F57FACDDFD}" name="Map Data"/>
   </tableColumns>
@@ -2225,9 +2235,9 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Pitch"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Yaw"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Rotation"/>
-    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{86990357-BCC2-4C19-8578-7CD9B17DA412}" name="Hotspot Line Data" dataDxfId="10"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Hotspot Hover Active"/>
-    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="10"/>
+    <tableColumn id="21" xr3:uid="{CEDACC9D-580B-4870-8178-91329C0A721E}" name="Delay Hotspot Tour" dataDxfId="9"/>
     <tableColumn id="13" xr3:uid="{9C4C8152-4844-4261-A684-0FACC6958478}" name="Hotspot Icon URL"/>
   </tableColumns>
   <tableStyleInfo name="2. Hotspots Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2235,15 +2245,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A1982990-8932-4703-94E4-180C79928346}" name="Table_36" displayName="Table_36" ref="A1:G4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A1982990-8932-4703-94E4-180C79928346}" name="Table_36" displayName="Table_36" ref="A1:G4" dataDxfId="2">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AC2068F9-4426-4263-A845-5946EB10AED0}" name="SL#" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{3D9EE8D6-E76E-45C3-BCE6-12CC183EE067}" name="Hotspot Name" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{AC2068F9-4426-4263-A845-5946EB10AED0}" name="SL#" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{3D9EE8D6-E76E-45C3-BCE6-12CC183EE067}" name="Hotspot Name" dataDxfId="7"/>
     <tableColumn id="7" xr3:uid="{243D11AF-E320-4A63-B33E-DB4DEE02C26D}" name="QNA Hotspot Custon ICON" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{A97AF90C-72ED-4B03-A59A-8CA0E1A8B08B}" name="Title" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{D20C3793-59AA-4FED-9D83-26F7442A226B}" name="Qestions and answers" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{061E7697-FC0B-487F-9C65-88C25FA344FC}" name="Answer Audio URL" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{6BF83100-29F6-4DAC-9D40-8965E58C45A5}" name="Answer Media URL" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{A97AF90C-72ED-4B03-A59A-8CA0E1A8B08B}" name="Title" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{D20C3793-59AA-4FED-9D83-26F7442A226B}" name="Qestions and answers" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{061E7697-FC0B-487F-9C65-88C25FA344FC}" name="Answer Audio URL" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{6BF83100-29F6-4DAC-9D40-8965E58C45A5}" name="Answer Media URL" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="1. Scenes Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -23092,10 +23102,12 @@
       <c r="E2" s="70" t="s">
         <v>333</v>
       </c>
-      <c r="F2" s="71" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="72"/>
+      <c r="F2" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="G2" s="75" t="s">
+        <v>340</v>
+      </c>
       <c r="H2" s="66"/>
       <c r="I2" s="67"/>
     </row>
@@ -23137,7 +23149,7 @@
       <c r="E4" s="70" t="s">
         <v>333</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="72" t="s">
         <v>49</v>
       </c>
       <c r="G4" s="72" t="s">
@@ -24130,11 +24142,12 @@
     <hyperlink ref="C2" r:id="rId3" xr:uid="{9279F6D0-641C-49D6-B7E1-11BD4E45CCE8}"/>
     <hyperlink ref="C3" r:id="rId4" xr:uid="{B5D20B47-F34E-42CB-A216-2576EE0D51F1}"/>
     <hyperlink ref="C4" r:id="rId5" xr:uid="{0C210614-9EEA-41D0-A2A0-711DE83FA584}"/>
+    <hyperlink ref="F4" r:id="rId6" xr:uid="{E91A2EED-8C62-4829-AE2B-1CCD55A90EBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId6"/>
+  <pageSetup orientation="landscape" r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>

--- a/360MasterData.xlsx
+++ b/360MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9F63E1-CC14-47CA-9685-84F3CAE74407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7658C43-674E-4D02-BE0B-7AE5627FAD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2635" uniqueCount="362">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -671,72 +671,6 @@
   </si>
   <si>
     <t>Map Data</t>
-  </si>
-  <si>
-    <t>Show,X:1.5,Y:1,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Hide,X:2,Y:2,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:5,Y:5,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:9,Y:9,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:10,Y:10,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:11,Y:11,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:14,Y:14,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Hide,X:3,Y:3,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Hide,X:6,Y:6,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Hide,X:7,Y:7,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Hide,X:8,Y:8,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Hide,X:12,Y:12,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Hide,X:13,Y:13,[https://cdn-5.urmy.net/images/plans/DSD/bulk/SG-FP-1.jpg]</t>
-  </si>
-  <si>
-    <t>Show,X:15,Y:15,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Hide,X:16,Y:16,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Hide,X:17,Y:17,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Show,X:18,Y:18,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Hide,X:19,Y:19,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Hide,X:20,Y:20,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Show,X:15,Y:3,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Hide,X:16,Y:20,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
-  </si>
-  <si>
-    <t>Show,X:8,Y:18,[https://assets.architecturaldesigns.com/plan_assets/86021/original/86021bw_f1_1479214455.png]</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/IMG0044.jpg</t>
@@ -1464,6 +1398,66 @@
   <si>
     <t>[Answer01:https://www.youtube.com/watch?v=4boHccMeaVE],[Answer02:],[Answer03:],[Answer04:https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/RimLock.mp4],[Answer05:]</t>
   </si>
+  <si>
+    <t>Show,X:3.5,Y:6,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP01.png]</t>
+  </si>
+  <si>
+    <t>Hide,X:3,Y:3,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP01.png]</t>
+  </si>
+  <si>
+    <t>Show,X:6,Y:8,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP01.png]</t>
+  </si>
+  <si>
+    <t>Show,X:14,Y:9,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP01.png]</t>
+  </si>
+  <si>
+    <t>Show,X:10,Y:15,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP01.png]</t>
+  </si>
+  <si>
+    <t>Show,X:5,Y:9,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP02.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:5,Y:9,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP02.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:9,Y:13,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP02.jpg]</t>
+  </si>
+  <si>
+    <t>Hide,X:13,Y:11,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP02.jpg]</t>
+  </si>
+  <si>
+    <t>Sow,X:17,Y:10,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP02.jpg]</t>
+  </si>
+  <si>
+    <t>Show,X:8,Y:6,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP03.png]</t>
+  </si>
+  <si>
+    <t>Show,X:12,Y:10,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP03.png]</t>
+  </si>
+  <si>
+    <t>Show,X:14,Y:15,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP03.png]</t>
+  </si>
+  <si>
+    <t>Hide,X:8,Y:8,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP04.webp]</t>
+  </si>
+  <si>
+    <t>Hide,X:13,Y:13,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP04.webp]</t>
+  </si>
+  <si>
+    <t>Hide,X:12,Y:12,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP04.webp]</t>
+  </si>
+  <si>
+    <t>Show,X:10,Y:5,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP04.webp]</t>
+  </si>
+  <si>
+    <t>Show,X:14,Y:6,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP04.webp]</t>
+  </si>
+  <si>
+    <t>Show,X:10,Y:12,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP04.webp]</t>
+  </si>
+  <si>
+    <t>Show,X:4,Y:16,[https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/MAP04.webp]</t>
+  </si>
 </sst>
 </file>
 
@@ -1632,7 +1626,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1673,6 +1667,24 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1760,7 +1772,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1957,6 +1969,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2673,7 +2688,7 @@
     </row>
     <row r="2" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -2685,13 +2700,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>29</v>
@@ -2753,13 +2768,13 @@
       <c r="AA2" s="12">
         <v>45750</v>
       </c>
-      <c r="AB2" t="s">
-        <v>192</v>
+      <c r="AB2" s="75" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -2771,13 +2786,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>29</v>
@@ -2839,13 +2854,13 @@
       <c r="AA3" s="12">
         <v>45750</v>
       </c>
-      <c r="AB3" t="s">
-        <v>193</v>
+      <c r="AB3" s="75" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2857,13 +2872,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>40</v>
@@ -2920,13 +2935,13 @@
       <c r="AA4" s="12">
         <v>45750</v>
       </c>
-      <c r="AB4" t="s">
-        <v>199</v>
+      <c r="AB4" s="75" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -2938,13 +2953,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>29</v>
@@ -3002,10 +3017,11 @@
       <c r="AA5" s="12">
         <v>45750</v>
       </c>
+      <c r="AB5" s="75"/>
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -3017,13 +3033,13 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>29</v>
@@ -3081,13 +3097,13 @@
       <c r="AA6" s="12">
         <v>45750</v>
       </c>
-      <c r="AB6" t="s">
-        <v>194</v>
+      <c r="AB6" s="75" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>50</v>
@@ -3099,13 +3115,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>52</v>
@@ -3163,13 +3179,13 @@
       <c r="AA7" s="12">
         <v>45750</v>
       </c>
-      <c r="AB7" t="s">
-        <v>200</v>
+      <c r="AB7" s="75" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>50</v>
@@ -3181,13 +3197,13 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>29</v>
@@ -3247,13 +3263,13 @@
       <c r="AA8" s="12">
         <v>45750</v>
       </c>
-      <c r="AB8" t="s">
-        <v>201</v>
+      <c r="AB8" s="74" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>50</v>
@@ -3265,13 +3281,13 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>29</v>
@@ -3331,13 +3347,13 @@
       <c r="AA9" s="12">
         <v>45750</v>
       </c>
-      <c r="AB9" t="s">
-        <v>202</v>
+      <c r="AB9" s="74" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>50</v>
@@ -3349,13 +3365,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>29</v>
@@ -3415,13 +3431,13 @@
       <c r="AA10" s="12">
         <v>45750</v>
       </c>
-      <c r="AB10" t="s">
-        <v>195</v>
+      <c r="AB10" s="74" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>50</v>
@@ -3433,13 +3449,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>29</v>
@@ -3497,13 +3513,13 @@
       <c r="AA11" s="12">
         <v>45750</v>
       </c>
-      <c r="AB11" t="s">
-        <v>196</v>
+      <c r="AB11" s="74" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>50</v>
@@ -3515,13 +3531,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>29</v>
@@ -3581,13 +3597,13 @@
       <c r="AA12" s="12">
         <v>45750</v>
       </c>
-      <c r="AB12" t="s">
-        <v>197</v>
+      <c r="AB12" s="74" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>79</v>
@@ -3599,13 +3615,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>29</v>
@@ -3665,13 +3681,13 @@
       <c r="AA13" s="12">
         <v>45750</v>
       </c>
-      <c r="AB13" t="s">
-        <v>203</v>
+      <c r="AB13" s="74" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>79</v>
@@ -3683,13 +3699,13 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>29</v>
@@ -3749,13 +3765,13 @@
       <c r="AA14" s="12">
         <v>45750</v>
       </c>
-      <c r="AB14" t="s">
-        <v>204</v>
+      <c r="AB14" s="74" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>79</v>
@@ -3767,13 +3783,13 @@
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>29</v>
@@ -3833,13 +3849,13 @@
       <c r="AA15" s="12">
         <v>45750</v>
       </c>
-      <c r="AB15" t="s">
-        <v>198</v>
+      <c r="AB15" s="74" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
@@ -3851,13 +3867,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>29</v>
@@ -3917,13 +3933,13 @@
       <c r="AA16" s="12">
         <v>45750</v>
       </c>
-      <c r="AB16" s="38" t="s">
-        <v>205</v>
+      <c r="AB16" s="74" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>27</v>
@@ -3935,13 +3951,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>29</v>
@@ -4001,13 +4017,13 @@
       <c r="AA17" s="12">
         <v>45750</v>
       </c>
-      <c r="AB17" s="38" t="s">
-        <v>206</v>
+      <c r="AB17" s="74" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
@@ -4019,13 +4035,13 @@
         <v>17</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>29</v>
@@ -4085,13 +4101,13 @@
       <c r="AA18" s="12">
         <v>45750</v>
       </c>
-      <c r="AB18" s="38" t="s">
-        <v>207</v>
+      <c r="AB18" s="74" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>100</v>
@@ -4103,13 +4119,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>40</v>
@@ -4169,13 +4185,11 @@
       <c r="AA19" s="12">
         <v>45750</v>
       </c>
-      <c r="AB19" s="38" t="s">
-        <v>208</v>
-      </c>
+      <c r="AB19" s="76"/>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>100</v>
@@ -4187,13 +4201,13 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>29</v>
@@ -4253,13 +4267,13 @@
       <c r="AA20" s="12">
         <v>45750</v>
       </c>
-      <c r="AB20" s="38" t="s">
-        <v>209</v>
+      <c r="AB20" s="76" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>100</v>
@@ -4271,13 +4285,13 @@
         <v>20</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>29</v>
@@ -4337,13 +4351,13 @@
       <c r="AA21" s="12">
         <v>45750</v>
       </c>
-      <c r="AB21" s="38" t="s">
-        <v>210</v>
+      <c r="AB21" s="76" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>100</v>
@@ -4355,13 +4369,13 @@
         <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>29</v>
@@ -4421,13 +4435,13 @@
       <c r="AA22" s="12">
         <v>45750</v>
       </c>
-      <c r="AB22" s="38" t="s">
-        <v>213</v>
+      <c r="AB22" s="76" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>100</v>
@@ -4439,13 +4453,13 @@
         <v>22</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>29</v>
@@ -4508,12 +4522,12 @@
         <v>45750</v>
       </c>
       <c r="AB23" s="38" t="s">
-        <v>211</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>100</v>
@@ -4525,13 +4539,13 @@
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="G24" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>29</v>
@@ -4592,30 +4606,30 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="38" t="s">
-        <v>212</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="D25" s="4">
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="G25" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>29</v>
@@ -4654,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="U25" s="9" t="b">
         <v>1</v>
@@ -4663,7 +4677,7 @@
         <v>92</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="X25" s="10" t="b">
         <v>1</v>
@@ -4676,30 +4690,30 @@
         <v>45750</v>
       </c>
       <c r="AB25" s="38" t="s">
-        <v>212</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="D26" s="4">
         <v>25</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>29</v>
@@ -4738,7 +4752,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="U26" s="9" t="b">
         <v>1</v>
@@ -4747,7 +4761,7 @@
         <v>92</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="X26" s="10" t="b">
         <v>1</v>
@@ -4760,30 +4774,30 @@
         <v>45750</v>
       </c>
       <c r="AB26" s="38" t="s">
-        <v>212</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="D27" s="4">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="G27" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>29</v>
@@ -4822,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="U27" s="9" t="b">
         <v>1</v>
@@ -4831,7 +4845,7 @@
         <v>92</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="X27" s="10" t="b">
         <v>1</v>
@@ -4844,30 +4858,30 @@
         <v>45750</v>
       </c>
       <c r="AB27" s="38" t="s">
-        <v>212</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="D28" s="4">
         <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="G28" s="39" t="s">
         <v>338</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>243</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>360</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>29</v>
@@ -4906,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="U28" s="9" t="b">
         <v>1</v>
@@ -4928,30 +4942,30 @@
         <v>45750</v>
       </c>
       <c r="AB28" s="38" t="s">
-        <v>212</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="D29" s="4">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="G29" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>29</v>
@@ -4990,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="U29" s="9" t="b">
         <v>1</v>
@@ -4999,7 +5013,7 @@
         <v>92</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="X29" s="10" t="b">
         <v>1</v>
@@ -5012,30 +5026,30 @@
         <v>45750</v>
       </c>
       <c r="AB29" s="38" t="s">
-        <v>212</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="D30" s="4">
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="G30" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>29</v>
@@ -5074,7 +5088,7 @@
         <v>1</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="U30" s="9" t="b">
         <v>1</v>
@@ -5083,7 +5097,7 @@
         <v>92</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="X30" s="10" t="b">
         <v>1</v>
@@ -5096,30 +5110,30 @@
         <v>45750</v>
       </c>
       <c r="AB30" s="38" t="s">
-        <v>212</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D31" s="4">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="F31" s="39" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="G31" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>29</v>
@@ -5158,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="U31" s="9" t="b">
         <v>1</v>
@@ -5167,7 +5181,7 @@
         <v>92</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="X31" s="10" t="b">
         <v>1</v>
@@ -5180,30 +5194,30 @@
         <v>45750</v>
       </c>
       <c r="AB31" s="38" t="s">
-        <v>212</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="D32" s="4">
         <v>31</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="G32" s="39" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>29</v>
@@ -5242,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="U32" s="9" t="b">
         <v>1</v>
@@ -5251,7 +5265,7 @@
         <v>92</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="X32" s="10" t="b">
         <v>1</v>
@@ -5264,7 +5278,7 @@
         <v>45750</v>
       </c>
       <c r="AB32" s="38" t="s">
-        <v>212</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="4:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -10207,7 +10221,7 @@
         <v>132</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>141</v>
@@ -10216,7 +10230,7 @@
         <v>184</v>
       </c>
       <c r="O1" s="65" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
@@ -10236,7 +10250,7 @@
         <v>33</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>143</v>
@@ -10262,7 +10276,7 @@
       </c>
       <c r="N2" s="36"/>
       <c r="O2" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q2"/>
     </row>
@@ -10280,7 +10294,7 @@
         <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>143</v>
@@ -10306,7 +10320,7 @@
       </c>
       <c r="N3" s="36"/>
       <c r="O3" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -10324,7 +10338,7 @@
         <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>143</v>
@@ -10350,7 +10364,7 @@
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="59" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="Q4"/>
     </row>
@@ -10368,7 +10382,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>143</v>
@@ -10392,7 +10406,7 @@
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="59" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="Q5"/>
     </row>
@@ -10410,7 +10424,7 @@
         <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>143</v>
@@ -10434,7 +10448,7 @@
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="59" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="Q6"/>
     </row>
@@ -10452,7 +10466,7 @@
         <v>33</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>143</v>
@@ -10476,7 +10490,7 @@
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="59" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="Q7"/>
     </row>
@@ -10494,10 +10508,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="3" t="s">
@@ -10513,7 +10527,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="M8" s="3" t="b">
         <v>1</v>
@@ -10535,10 +10549,10 @@
         <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="3" t="s">
@@ -10554,7 +10568,7 @@
         <v>150</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="M9" s="3" t="b">
         <v>1</v>
@@ -10576,7 +10590,7 @@
         <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>148</v>
@@ -10595,7 +10609,7 @@
         <v>150</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="M10" s="3" t="b">
         <v>1</v>
@@ -10619,7 +10633,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>148</v>
@@ -10638,7 +10652,7 @@
         <v>150</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="M11" s="3" t="b">
         <v>1</v>
@@ -10662,7 +10676,7 @@
         <v>33</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>148</v>
@@ -10681,7 +10695,7 @@
         <v>150</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="M12" s="3" t="b">
         <v>1</v>
@@ -10705,7 +10719,7 @@
         <v>33</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>148</v>
@@ -10724,7 +10738,7 @@
         <v>150</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="M13" s="3" t="b">
         <v>1</v>
@@ -10748,7 +10762,7 @@
         <v>33</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>148</v>
@@ -10767,7 +10781,7 @@
         <v>150</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="M14" s="3" t="b">
         <v>1</v>
@@ -10791,7 +10805,7 @@
         <v>33</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>148</v>
@@ -10810,7 +10824,7 @@
         <v>150</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M15" s="3" t="b">
         <v>1</v>
@@ -10834,7 +10848,7 @@
         <v>33</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>148</v>
@@ -10853,7 +10867,7 @@
         <v>150</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M16" s="3" t="b">
         <v>1</v>
@@ -10877,7 +10891,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>148</v>
@@ -10896,7 +10910,7 @@
         <v>150</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M17" s="3" t="b">
         <v>1</v>
@@ -10920,7 +10934,7 @@
         <v>33</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>148</v>
@@ -10939,7 +10953,7 @@
         <v>150</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M18" s="3" t="b">
         <v>1</v>
@@ -10963,7 +10977,7 @@
         <v>33</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>148</v>
@@ -10982,7 +10996,7 @@
         <v>150</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="M19" s="3" t="b">
         <v>1</v>
@@ -11006,7 +11020,7 @@
         <v>37</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>143</v>
@@ -11032,7 +11046,7 @@
       </c>
       <c r="N20" s="36"/>
       <c r="O20" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q20"/>
     </row>
@@ -11050,7 +11064,7 @@
         <v>37</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>143</v>
@@ -11076,7 +11090,7 @@
       </c>
       <c r="N21" s="36"/>
       <c r="O21" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q21"/>
     </row>
@@ -11094,7 +11108,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>148</v>
@@ -11113,7 +11127,7 @@
         <v>150</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M22" s="3" t="b">
         <v>1</v>
@@ -11136,7 +11150,7 @@
         <v>37</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>148</v>
@@ -11155,7 +11169,7 @@
         <v>150</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M23" s="3" t="b">
         <v>1</v>
@@ -11177,7 +11191,7 @@
         <v>37</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>148</v>
@@ -11196,7 +11210,7 @@
         <v>150</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M24" s="3" t="b">
         <v>1</v>
@@ -11218,7 +11232,7 @@
         <v>37</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>148</v>
@@ -11237,7 +11251,7 @@
         <v>150</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M25" s="3" t="b">
         <v>1</v>
@@ -11259,7 +11273,7 @@
         <v>37</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>148</v>
@@ -11278,7 +11292,7 @@
         <v>150</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M26" s="3" t="b">
         <v>1</v>
@@ -11300,7 +11314,7 @@
         <v>41</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>143</v>
@@ -11326,7 +11340,7 @@
       </c>
       <c r="N27" s="36"/>
       <c r="O27" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q27"/>
     </row>
@@ -11344,7 +11358,7 @@
         <v>41</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>143</v>
@@ -11370,7 +11384,7 @@
       </c>
       <c r="N28" s="36"/>
       <c r="O28" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q28"/>
     </row>
@@ -11388,7 +11402,7 @@
         <v>41</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>148</v>
@@ -11407,7 +11421,7 @@
         <v>150</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M29" s="3" t="b">
         <v>1</v>
@@ -11429,7 +11443,7 @@
         <v>41</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>148</v>
@@ -11448,7 +11462,7 @@
         <v>150</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M30" s="3" t="b">
         <v>1</v>
@@ -11470,7 +11484,7 @@
         <v>41</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>148</v>
@@ -11489,7 +11503,7 @@
         <v>150</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M31" s="3" t="b">
         <v>1</v>
@@ -11511,7 +11525,7 @@
         <v>41</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>148</v>
@@ -11530,7 +11544,7 @@
         <v>150</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M32" s="3" t="b">
         <v>1</v>
@@ -11552,7 +11566,7 @@
         <v>41</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>148</v>
@@ -11571,7 +11585,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M33" s="3" t="b">
         <v>1</v>
@@ -11593,7 +11607,7 @@
         <v>45</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>143</v>
@@ -11619,7 +11633,7 @@
       </c>
       <c r="N34" s="36"/>
       <c r="O34" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q34"/>
     </row>
@@ -11637,7 +11651,7 @@
         <v>45</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>143</v>
@@ -11663,7 +11677,7 @@
       </c>
       <c r="N35" s="36"/>
       <c r="O35" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q35"/>
     </row>
@@ -11681,7 +11695,7 @@
         <v>45</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>148</v>
@@ -11700,7 +11714,7 @@
         <v>150</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M36" s="3" t="b">
         <v>1</v>
@@ -11722,7 +11736,7 @@
         <v>45</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>148</v>
@@ -11741,7 +11755,7 @@
         <v>150</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M37" s="3" t="b">
         <v>1</v>
@@ -11763,7 +11777,7 @@
         <v>45</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>148</v>
@@ -11782,7 +11796,7 @@
         <v>150</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M38" s="3" t="b">
         <v>1</v>
@@ -11804,7 +11818,7 @@
         <v>45</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>148</v>
@@ -11823,7 +11837,7 @@
         <v>150</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M39" s="3" t="b">
         <v>1</v>
@@ -11845,7 +11859,7 @@
         <v>45</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>148</v>
@@ -11864,7 +11878,7 @@
         <v>150</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M40" s="3" t="b">
         <v>1</v>
@@ -11886,7 +11900,7 @@
         <v>48</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>143</v>
@@ -11912,7 +11926,7 @@
       </c>
       <c r="N41" s="36"/>
       <c r="O41" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q41"/>
     </row>
@@ -11930,7 +11944,7 @@
         <v>48</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>143</v>
@@ -11956,7 +11970,7 @@
       </c>
       <c r="N42" s="36"/>
       <c r="O42" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q42"/>
     </row>
@@ -11974,7 +11988,7 @@
         <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>148</v>
@@ -11993,7 +12007,7 @@
         <v>150</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M43" s="3" t="b">
         <v>1</v>
@@ -12015,7 +12029,7 @@
         <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>148</v>
@@ -12034,7 +12048,7 @@
         <v>150</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M44" s="3" t="b">
         <v>1</v>
@@ -12056,7 +12070,7 @@
         <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>148</v>
@@ -12075,7 +12089,7 @@
         <v>150</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M45" s="3" t="b">
         <v>1</v>
@@ -12097,7 +12111,7 @@
         <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>148</v>
@@ -12116,7 +12130,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M46" s="3" t="b">
         <v>1</v>
@@ -12138,7 +12152,7 @@
         <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>148</v>
@@ -12157,7 +12171,7 @@
         <v>150</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M47" s="3" t="b">
         <v>1</v>
@@ -12179,7 +12193,7 @@
         <v>56</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>143</v>
@@ -12205,7 +12219,7 @@
       </c>
       <c r="N48" s="36"/>
       <c r="O48" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q48"/>
     </row>
@@ -12223,7 +12237,7 @@
         <v>56</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>143</v>
@@ -12249,7 +12263,7 @@
       </c>
       <c r="N49" s="36"/>
       <c r="O49" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q49"/>
     </row>
@@ -12267,7 +12281,7 @@
         <v>56</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>148</v>
@@ -12286,7 +12300,7 @@
         <v>150</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M50" s="3" t="b">
         <v>1</v>
@@ -12308,7 +12322,7 @@
         <v>56</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>148</v>
@@ -12327,7 +12341,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M51" s="3" t="b">
         <v>1</v>
@@ -12349,7 +12363,7 @@
         <v>56</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>148</v>
@@ -12368,7 +12382,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M52" s="3" t="b">
         <v>1</v>
@@ -12390,7 +12404,7 @@
         <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>148</v>
@@ -12409,7 +12423,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M53" s="3" t="b">
         <v>1</v>
@@ -12431,7 +12445,7 @@
         <v>56</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>148</v>
@@ -12450,7 +12464,7 @@
         <v>150</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M54" s="3" t="b">
         <v>1</v>
@@ -12472,7 +12486,7 @@
         <v>60</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>143</v>
@@ -12498,7 +12512,7 @@
       </c>
       <c r="N55" s="36"/>
       <c r="O55" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q55"/>
     </row>
@@ -12516,7 +12530,7 @@
         <v>60</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>143</v>
@@ -12542,7 +12556,7 @@
       </c>
       <c r="N56" s="36"/>
       <c r="O56" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q56"/>
     </row>
@@ -12560,7 +12574,7 @@
         <v>60</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>148</v>
@@ -12579,7 +12593,7 @@
         <v>150</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M57" s="3" t="b">
         <v>1</v>
@@ -12601,7 +12615,7 @@
         <v>60</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>148</v>
@@ -12620,7 +12634,7 @@
         <v>150</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M58" s="3" t="b">
         <v>1</v>
@@ -12642,7 +12656,7 @@
         <v>60</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>148</v>
@@ -12661,7 +12675,7 @@
         <v>150</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M59" s="3" t="b">
         <v>1</v>
@@ -12683,7 +12697,7 @@
         <v>60</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>148</v>
@@ -12702,7 +12716,7 @@
         <v>150</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M60" s="3" t="b">
         <v>1</v>
@@ -12724,7 +12738,7 @@
         <v>60</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>148</v>
@@ -12743,7 +12757,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M61" s="3" t="b">
         <v>1</v>
@@ -12765,7 +12779,7 @@
         <v>66</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>143</v>
@@ -12791,7 +12805,7 @@
       </c>
       <c r="N62" s="36"/>
       <c r="O62" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q62"/>
     </row>
@@ -12809,7 +12823,7 @@
         <v>66</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>143</v>
@@ -12835,7 +12849,7 @@
       </c>
       <c r="N63" s="36"/>
       <c r="O63" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q63"/>
     </row>
@@ -12853,7 +12867,7 @@
         <v>66</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>148</v>
@@ -12872,7 +12886,7 @@
         <v>150</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M64" s="3" t="b">
         <v>1</v>
@@ -12894,7 +12908,7 @@
         <v>66</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>148</v>
@@ -12913,7 +12927,7 @@
         <v>150</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M65" s="3" t="b">
         <v>1</v>
@@ -12935,7 +12949,7 @@
         <v>66</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>148</v>
@@ -12954,7 +12968,7 @@
         <v>150</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M66" s="3" t="b">
         <v>1</v>
@@ -12976,7 +12990,7 @@
         <v>66</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>148</v>
@@ -12995,7 +13009,7 @@
         <v>150</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M67" s="3" t="b">
         <v>1</v>
@@ -13017,7 +13031,7 @@
         <v>66</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>148</v>
@@ -13036,7 +13050,7 @@
         <v>150</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M68" s="3" t="b">
         <v>1</v>
@@ -13058,7 +13072,7 @@
         <v>70</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>143</v>
@@ -13084,7 +13098,7 @@
       </c>
       <c r="N69" s="36"/>
       <c r="O69" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q69"/>
     </row>
@@ -13102,7 +13116,7 @@
         <v>70</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>143</v>
@@ -13128,7 +13142,7 @@
       </c>
       <c r="N70" s="36"/>
       <c r="O70" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q70"/>
     </row>
@@ -13146,7 +13160,7 @@
         <v>70</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>148</v>
@@ -13165,7 +13179,7 @@
         <v>150</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M71" s="3" t="b">
         <v>1</v>
@@ -13187,7 +13201,7 @@
         <v>70</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>148</v>
@@ -13206,7 +13220,7 @@
         <v>150</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M72" s="3" t="b">
         <v>1</v>
@@ -13228,7 +13242,7 @@
         <v>70</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>148</v>
@@ -13247,7 +13261,7 @@
         <v>150</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M73" s="3" t="b">
         <v>1</v>
@@ -13269,7 +13283,7 @@
         <v>70</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>148</v>
@@ -13288,7 +13302,7 @@
         <v>150</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M74" s="3" t="b">
         <v>1</v>
@@ -13310,7 +13324,7 @@
         <v>70</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>148</v>
@@ -13329,7 +13343,7 @@
         <v>150</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M75" s="3" t="b">
         <v>1</v>
@@ -13351,7 +13365,7 @@
         <v>73</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>143</v>
@@ -13377,7 +13391,7 @@
       </c>
       <c r="N76" s="36"/>
       <c r="O76" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q76"/>
     </row>
@@ -13395,7 +13409,7 @@
         <v>73</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>143</v>
@@ -13421,7 +13435,7 @@
       </c>
       <c r="N77" s="36"/>
       <c r="O77" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q77"/>
     </row>
@@ -13439,7 +13453,7 @@
         <v>73</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>148</v>
@@ -13458,7 +13472,7 @@
         <v>150</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M78" s="3" t="b">
         <v>1</v>
@@ -13480,7 +13494,7 @@
         <v>73</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>148</v>
@@ -13499,7 +13513,7 @@
         <v>150</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M79" s="3" t="b">
         <v>1</v>
@@ -13521,7 +13535,7 @@
         <v>73</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>148</v>
@@ -13540,7 +13554,7 @@
         <v>150</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M80" s="3" t="b">
         <v>1</v>
@@ -13562,7 +13576,7 @@
         <v>73</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>148</v>
@@ -13581,7 +13595,7 @@
         <v>150</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M81" s="3" t="b">
         <v>1</v>
@@ -13603,7 +13617,7 @@
         <v>73</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>148</v>
@@ -13622,7 +13636,7 @@
         <v>150</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M82" s="3" t="b">
         <v>1</v>
@@ -13644,7 +13658,7 @@
         <v>76</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>143</v>
@@ -13670,7 +13684,7 @@
       </c>
       <c r="N83" s="36"/>
       <c r="O83" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q83"/>
     </row>
@@ -13688,7 +13702,7 @@
         <v>76</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>143</v>
@@ -13714,7 +13728,7 @@
       </c>
       <c r="N84" s="36"/>
       <c r="O84" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q84"/>
     </row>
@@ -13732,7 +13746,7 @@
         <v>76</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>148</v>
@@ -13751,7 +13765,7 @@
         <v>150</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M85" s="3" t="b">
         <v>1</v>
@@ -13773,7 +13787,7 @@
         <v>76</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>148</v>
@@ -13792,7 +13806,7 @@
         <v>150</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M86" s="3" t="b">
         <v>1</v>
@@ -13814,7 +13828,7 @@
         <v>76</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>148</v>
@@ -13833,7 +13847,7 @@
         <v>150</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M87" s="3" t="b">
         <v>1</v>
@@ -13855,7 +13869,7 @@
         <v>76</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>148</v>
@@ -13874,7 +13888,7 @@
         <v>150</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M88" s="3" t="b">
         <v>1</v>
@@ -13896,7 +13910,7 @@
         <v>76</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>148</v>
@@ -13915,7 +13929,7 @@
         <v>150</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M89" s="3" t="b">
         <v>1</v>
@@ -13937,7 +13951,7 @@
         <v>81</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>143</v>
@@ -13963,7 +13977,7 @@
       </c>
       <c r="N90" s="36"/>
       <c r="O90" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q90"/>
     </row>
@@ -13981,7 +13995,7 @@
         <v>81</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>143</v>
@@ -14007,7 +14021,7 @@
       </c>
       <c r="N91" s="36"/>
       <c r="O91" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q91"/>
     </row>
@@ -14025,7 +14039,7 @@
         <v>81</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>148</v>
@@ -14044,7 +14058,7 @@
         <v>150</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M92" s="3" t="b">
         <v>1</v>
@@ -14066,7 +14080,7 @@
         <v>81</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>148</v>
@@ -14085,7 +14099,7 @@
         <v>150</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M93" s="3" t="b">
         <v>1</v>
@@ -14107,7 +14121,7 @@
         <v>81</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>148</v>
@@ -14126,7 +14140,7 @@
         <v>150</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M94" s="3" t="b">
         <v>1</v>
@@ -14148,7 +14162,7 @@
         <v>81</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>148</v>
@@ -14167,7 +14181,7 @@
         <v>150</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M95" s="3" t="b">
         <v>1</v>
@@ -14189,7 +14203,7 @@
         <v>81</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>148</v>
@@ -14208,7 +14222,7 @@
         <v>150</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M96" s="3" t="b">
         <v>1</v>
@@ -14230,7 +14244,7 @@
         <v>84</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>143</v>
@@ -14256,7 +14270,7 @@
       </c>
       <c r="N97" s="36"/>
       <c r="O97" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q97"/>
     </row>
@@ -14274,7 +14288,7 @@
         <v>84</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>143</v>
@@ -14300,7 +14314,7 @@
       </c>
       <c r="N98" s="36"/>
       <c r="O98" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q98"/>
     </row>
@@ -14318,7 +14332,7 @@
         <v>84</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>148</v>
@@ -14337,7 +14351,7 @@
         <v>150</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M99" s="3" t="b">
         <v>1</v>
@@ -14359,7 +14373,7 @@
         <v>84</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>148</v>
@@ -14378,7 +14392,7 @@
         <v>150</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M100" s="3" t="b">
         <v>1</v>
@@ -14400,7 +14414,7 @@
         <v>84</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>148</v>
@@ -14419,7 +14433,7 @@
         <v>150</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M101" s="3" t="b">
         <v>1</v>
@@ -14441,7 +14455,7 @@
         <v>84</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>148</v>
@@ -14460,7 +14474,7 @@
         <v>150</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M102" s="3" t="b">
         <v>1</v>
@@ -14482,7 +14496,7 @@
         <v>84</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>148</v>
@@ -14501,7 +14515,7 @@
         <v>150</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M103" s="3" t="b">
         <v>1</v>
@@ -14523,7 +14537,7 @@
         <v>87</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>143</v>
@@ -14549,7 +14563,7 @@
       </c>
       <c r="N104" s="36"/>
       <c r="O104" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q104"/>
     </row>
@@ -14567,7 +14581,7 @@
         <v>87</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>143</v>
@@ -14593,7 +14607,7 @@
       </c>
       <c r="N105" s="36"/>
       <c r="O105" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q105"/>
     </row>
@@ -14611,7 +14625,7 @@
         <v>87</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>148</v>
@@ -14630,7 +14644,7 @@
         <v>150</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M106" s="3" t="b">
         <v>1</v>
@@ -14652,7 +14666,7 @@
         <v>87</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>148</v>
@@ -14671,7 +14685,7 @@
         <v>150</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M107" s="3" t="b">
         <v>1</v>
@@ -14693,7 +14707,7 @@
         <v>87</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>148</v>
@@ -14712,7 +14726,7 @@
         <v>150</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M108" s="3" t="b">
         <v>1</v>
@@ -14734,7 +14748,7 @@
         <v>87</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>148</v>
@@ -14753,7 +14767,7 @@
         <v>150</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M109" s="3" t="b">
         <v>1</v>
@@ -14775,7 +14789,7 @@
         <v>87</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>148</v>
@@ -14794,7 +14808,7 @@
         <v>150</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M110" s="3" t="b">
         <v>1</v>
@@ -14816,7 +14830,7 @@
         <v>91</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>143</v>
@@ -14842,7 +14856,7 @@
       </c>
       <c r="N111" s="36"/>
       <c r="O111" s="59" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="Q111"/>
     </row>
@@ -14860,7 +14874,7 @@
         <v>91</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>143</v>
@@ -14886,7 +14900,7 @@
       </c>
       <c r="N112" s="36"/>
       <c r="O112" s="59" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q112"/>
     </row>
@@ -14904,7 +14918,7 @@
         <v>91</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>148</v>
@@ -14923,7 +14937,7 @@
         <v>150</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="M113" s="3" t="b">
         <v>1</v>
@@ -14945,7 +14959,7 @@
         <v>91</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>148</v>
@@ -14964,7 +14978,7 @@
         <v>150</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>287</v>
+        <v>265</v>
       